--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -41956,6 +41956,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1809">
+      <c r="A1809" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1809" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C1809" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D1809" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="E1809" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="F1809" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="G1809" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -41979,6 +41979,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1810">
+      <c r="A1810" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1810" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C1810" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="D1810" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="E1810" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="F1810" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="G1810" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -42002,6 +42002,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1811">
+      <c r="A1811" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1811" t="n">
+        <v>65000</v>
+      </c>
+      <c r="C1811" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D1811" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="E1811" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="F1811" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="G1811" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -42025,6 +42025,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1812">
+      <c r="A1812" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1812" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1812" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D1812" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="E1812" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="F1812" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="G1812" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -41866,22 +41866,22 @@
     </row>
     <row r="1805">
       <c r="A1805" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1805" t="n">
-        <v>13000</v>
+        <v>11000</v>
       </c>
       <c r="C1805" t="n">
-        <v>2.27999997138977</v>
+        <v>2.25999999046326</v>
       </c>
       <c r="D1805" t="n">
-        <v>2.24000000953674</v>
+        <v>2.22000002861023</v>
       </c>
       <c r="E1805" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="F1805" t="n">
         <v>2.25999999046326</v>
-      </c>
-      <c r="F1805" t="n">
-        <v>2.24000000953674</v>
       </c>
       <c r="G1805" t="s">
         <v>7</v>
@@ -41889,16 +41889,16 @@
     </row>
     <row r="1806">
       <c r="A1806" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1806" t="n">
-        <v>6000</v>
+        <v>13000</v>
       </c>
       <c r="C1806" t="n">
-        <v>2.25999999046326</v>
+        <v>2.27999997138977</v>
       </c>
       <c r="D1806" t="n">
-        <v>2.22000002861023</v>
+        <v>2.24000000953674</v>
       </c>
       <c r="E1806" t="n">
         <v>2.25999999046326</v>
@@ -41912,19 +41912,19 @@
     </row>
     <row r="1807">
       <c r="A1807" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1807" t="n">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="C1807" t="n">
-        <v>2.24000000953674</v>
+        <v>2.25999999046326</v>
       </c>
       <c r="D1807" t="n">
-        <v>2.24000000953674</v>
+        <v>2.22000002861023</v>
       </c>
       <c r="E1807" t="n">
-        <v>2.24000000953674</v>
+        <v>2.25999999046326</v>
       </c>
       <c r="F1807" t="n">
         <v>2.24000000953674</v>
@@ -41935,19 +41935,19 @@
     </row>
     <row r="1808">
       <c r="A1808" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1808" t="n">
-        <v>24000</v>
+        <v>1000</v>
       </c>
       <c r="C1808" t="n">
-        <v>2.25999999046326</v>
+        <v>2.24000000953674</v>
       </c>
       <c r="D1808" t="n">
-        <v>2.20000004768372</v>
+        <v>2.24000000953674</v>
       </c>
       <c r="E1808" t="n">
-        <v>2.25999999046326</v>
+        <v>2.24000000953674</v>
       </c>
       <c r="F1808" t="n">
         <v>2.24000000953674</v>
@@ -41958,22 +41958,22 @@
     </row>
     <row r="1809">
       <c r="A1809" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1809" t="n">
-        <v>21000</v>
+        <v>24000</v>
       </c>
       <c r="C1809" t="n">
-        <v>2.24000000953674</v>
+        <v>2.25999999046326</v>
       </c>
       <c r="D1809" t="n">
         <v>2.20000004768372</v>
       </c>
       <c r="E1809" t="n">
-        <v>2.20000004768372</v>
+        <v>2.25999999046326</v>
       </c>
       <c r="F1809" t="n">
-        <v>2.22000002861023</v>
+        <v>2.24000000953674</v>
       </c>
       <c r="G1809" t="s">
         <v>7</v>
@@ -41981,22 +41981,22 @@
     </row>
     <row r="1810">
       <c r="A1810" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1810" t="n">
-        <v>9000</v>
+        <v>21000</v>
       </c>
       <c r="C1810" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D1810" t="n">
         <v>2.20000004768372</v>
-      </c>
-      <c r="D1810" t="n">
-        <v>2.1800000667572</v>
       </c>
       <c r="E1810" t="n">
         <v>2.20000004768372</v>
       </c>
       <c r="F1810" t="n">
-        <v>2.1800000667572</v>
+        <v>2.22000002861023</v>
       </c>
       <c r="G1810" t="s">
         <v>7</v>
@@ -42004,22 +42004,22 @@
     </row>
     <row r="1811">
       <c r="A1811" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1811" t="n">
-        <v>65000</v>
+        <v>9000</v>
       </c>
       <c r="C1811" t="n">
-        <v>2.24000000953674</v>
+        <v>2.20000004768372</v>
       </c>
       <c r="D1811" t="n">
-        <v>2.14000010490417</v>
+        <v>2.1800000667572</v>
       </c>
       <c r="E1811" t="n">
         <v>2.20000004768372</v>
       </c>
       <c r="F1811" t="n">
-        <v>2.22000002861023</v>
+        <v>2.1800000667572</v>
       </c>
       <c r="G1811" t="s">
         <v>7</v>
@@ -42027,10 +42027,10 @@
     </row>
     <row r="1812">
       <c r="A1812" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1812" t="n">
-        <v>2000</v>
+        <v>65000</v>
       </c>
       <c r="C1812" t="n">
         <v>2.24000000953674</v>
@@ -42042,9 +42042,32 @@
         <v>2.20000004768372</v>
       </c>
       <c r="F1812" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="G1812" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1813" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1813" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D1813" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="E1813" t="n">
         <v>2.20000004768372</v>
       </c>
-      <c r="G1812" t="s">
+      <c r="F1813" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="G1813" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>1.30437564849854</v>
+        <v>1.30437552928925</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>1.50020003318787</v>
       </c>
       <c r="G3" t="n">
-        <v>1.31330490112305</v>
+        <v>1.31330502033234</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G7" t="n">
-        <v>1.58888709545135</v>
+        <v>1.58888697624207</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G8" t="n">
-        <v>1.63265812397003</v>
+        <v>1.63265800476074</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G9" t="n">
-        <v>1.72019994258881</v>
+        <v>1.7202000617981</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G10" t="n">
-        <v>1.87339854240417</v>
+        <v>1.87339866161346</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G13" t="n">
-        <v>3.17777419090271</v>
+        <v>3.17777395248413</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G14" t="n">
-        <v>3.69427156448364</v>
+        <v>3.6942720413208</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3.93938899040222</v>
+        <v>3.9393892288208</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3.93938899040222</v>
+        <v>3.9393892288208</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>3.8781099319458</v>
+        <v>3.87810969352722</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G20" t="n">
-        <v>3.66800928115845</v>
+        <v>3.66800904273987</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G21" t="n">
-        <v>3.52794218063354</v>
+        <v>3.52794241905212</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>3.57171273231506</v>
+        <v>3.57171297073364</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G24" t="n">
-        <v>3.69427156448364</v>
+        <v>3.6942720413208</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G25" t="n">
-        <v>3.55420446395874</v>
+        <v>3.55420470237732</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G28" t="n">
-        <v>3.42289161682129</v>
+        <v>3.42289185523987</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G29" t="n">
-        <v>3.51918768882751</v>
+        <v>3.51918792724609</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G31" t="n">
-        <v>3.48417115211487</v>
+        <v>3.48417091369629</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>3.40976047515869</v>
+        <v>3.40976023674011</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.75</v>
       </c>
       <c r="G38" t="n">
-        <v>3.28282427787781</v>
+        <v>3.28282451629639</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>3.17777419090271</v>
+        <v>3.17777395248413</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G42" t="n">
-        <v>2.78383493423462</v>
+        <v>2.78383541107178</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G43" t="n">
-        <v>2.62188243865967</v>
+        <v>2.62188220024109</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G46" t="n">
-        <v>2.98080468177795</v>
+        <v>2.98080444335938</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G48" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>2.73130989074707</v>
+        <v>2.73130965232849</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>2.77945780754089</v>
+        <v>2.77945804595947</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.125</v>
       </c>
       <c r="G52" t="n">
-        <v>2.7356870174408</v>
+        <v>2.73568725585938</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G54" t="n">
-        <v>2.89763951301575</v>
+        <v>2.89763975143433</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>2.81009769439697</v>
+        <v>2.81009793281555</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G56" t="n">
-        <v>2.90639400482178</v>
+        <v>2.9063937664032</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G59" t="n">
-        <v>2.78383493423462</v>
+        <v>2.78383541107178</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G62" t="n">
-        <v>2.81009769439697</v>
+        <v>2.81009793281555</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>2.8276059627533</v>
+        <v>2.82760620117188</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>2.8276059627533</v>
+        <v>2.82760620117188</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>2.78383493423462</v>
+        <v>2.78383541107178</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G74" t="n">
-        <v>2.8494918346405</v>
+        <v>2.84949159622192</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G76" t="n">
-        <v>2.78383493423462</v>
+        <v>2.78383541107178</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>2.77945780754089</v>
+        <v>2.77945804595947</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>2.77070355415344</v>
+        <v>2.77070379257202</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>2.72693276405334</v>
+        <v>2.72693252563477</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G82" t="n">
-        <v>2.74006414413452</v>
+        <v>2.74006390571594</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G84" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G94" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G95" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>2.8276059627533</v>
+        <v>2.82760620117188</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>4.39460802078247</v>
+        <v>4.39460754394531</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G109" t="n">
-        <v>3.96565198898315</v>
+        <v>3.965651512146</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.375</v>
       </c>
       <c r="G111" t="n">
-        <v>3.82996201515198</v>
+        <v>3.82996153831482</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G113" t="n">
-        <v>3.52794218063354</v>
+        <v>3.52794241905212</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>3.65487813949585</v>
+        <v>3.65487837791443</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G115" t="n">
-        <v>3.7730598449707</v>
+        <v>3.77305936813354</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>3.97878289222717</v>
+        <v>3.97878336906433</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>3.91312646865845</v>
+        <v>3.91312670707703</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>3.86060166358948</v>
+        <v>3.8606014251709</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G119" t="n">
-        <v>3.7993221282959</v>
+        <v>3.79932236671448</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>3.84746980667114</v>
+        <v>3.84747004508972</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G121" t="n">
-        <v>3.8912410736084</v>
+        <v>3.89124155044556</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G122" t="n">
-        <v>3.92625856399536</v>
+        <v>3.92625832557678</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>4.28955745697021</v>
+        <v>4.28955698013306</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>4.18013000488281</v>
+        <v>4.18012952804565</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>4.28518009185791</v>
+        <v>4.28518056869507</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>3.97002911567688</v>
+        <v>3.97002863883972</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G131" t="n">
-        <v>4.04006242752075</v>
+        <v>4.04006195068359</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G132" t="n">
-        <v>4.00504541397095</v>
+        <v>4.00504589080811</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G137" t="n">
-        <v>3.98753690719604</v>
+        <v>3.98753714561462</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G138" t="n">
-        <v>3.99629163742065</v>
+        <v>3.99629187583923</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G139" t="n">
-        <v>4.21952438354492</v>
+        <v>4.21952390670776</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G140" t="n">
-        <v>4.13635921478271</v>
+        <v>4.13635873794556</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>4.19326066970825</v>
+        <v>4.19326114654541</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G142" t="n">
-        <v>4.32895088195801</v>
+        <v>4.32895183563232</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G143" t="n">
-        <v>5.16497707366943</v>
+        <v>5.16497755050659</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G145" t="n">
-        <v>4.46464109420776</v>
+        <v>4.46464061737061</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G146" t="n">
-        <v>4.38585329055786</v>
+        <v>4.38585376739502</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>3.85184717178345</v>
+        <v>3.85184741020203</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G150" t="n">
-        <v>3.78181409835815</v>
+        <v>3.78181385993958</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G151" t="n">
-        <v>3.80369853973389</v>
+        <v>3.80369901657104</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>3.7993221282959</v>
+        <v>3.79932236671448</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G153" t="n">
-        <v>3.33097219467163</v>
+        <v>3.33097243309021</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G155" t="n">
-        <v>3.19965934753418</v>
+        <v>3.19965958595276</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>2.73130989074707</v>
+        <v>2.73130965232849</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>2.77508115768433</v>
+        <v>2.77508091926575</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G161" t="n">
-        <v>2.95891904830933</v>
+        <v>2.95891928672791</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G163" t="n">
-        <v>3.22154521942139</v>
+        <v>3.22154498100281</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G165" t="n">
-        <v>3.58046746253967</v>
+        <v>3.58046698570251</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.75555086135864</v>
+        <v>3.75555062294006</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G167" t="n">
-        <v>3.71177983283997</v>
+        <v>3.71178007125854</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>3.62861514091492</v>
+        <v>3.62861490249634</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>3.66800928115845</v>
+        <v>3.66800904273987</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G171" t="n">
-        <v>3.73366594314575</v>
+        <v>3.73366546630859</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G173" t="n">
-        <v>3.95252084732056</v>
+        <v>3.95252013206482</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.85184717178345</v>
+        <v>3.85184741020203</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>4.07070207595825</v>
+        <v>4.07070302963257</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>4.07070207595825</v>
+        <v>4.07070302963257</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>3.68114042282104</v>
+        <v>3.68113994598389</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G179" t="n">
-        <v>3.70302557945251</v>
+        <v>3.70302629470825</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G180" t="n">
-        <v>3.83433938026428</v>
+        <v>3.8343391418457</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G181" t="n">
-        <v>3.8781099319458</v>
+        <v>3.87810969352722</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G182" t="n">
-        <v>3.70302557945251</v>
+        <v>3.70302629470825</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>3.80807590484619</v>
+        <v>3.80807614326477</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>3.85184717178345</v>
+        <v>3.85184741020203</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>3.86935591697693</v>
+        <v>3.86935567855835</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G187" t="n">
-        <v>3.86060166358948</v>
+        <v>3.8606014251709</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>3.77743673324585</v>
+        <v>3.77743649482727</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G190" t="n">
-        <v>3.78224849700928</v>
+        <v>3.78224897384644</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G192" t="n">
-        <v>3.78668808937073</v>
+        <v>3.78668785095215</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G194" t="n">
-        <v>3.74673438072205</v>
+        <v>3.7467348575592</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G195" t="n">
-        <v>3.78224849700928</v>
+        <v>3.78224897384644</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>4.25</v>
       </c>
       <c r="G196" t="n">
-        <v>3.77337002754211</v>
+        <v>3.77337026596069</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>3.7911274433136</v>
+        <v>3.79112720489502</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G198" t="n">
-        <v>3.91098713874817</v>
+        <v>3.91098761558533</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>4.5</v>
       </c>
       <c r="G199" t="n">
-        <v>3.99533343315125</v>
+        <v>3.99533319473267</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G200" t="n">
-        <v>3.86215567588806</v>
+        <v>3.8621551990509</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G201" t="n">
-        <v>3.83552026748657</v>
+        <v>3.83552002906799</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>3.8310809135437</v>
+        <v>3.83108067512512</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G204" t="n">
-        <v>3.82220220565796</v>
+        <v>3.82220244407654</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G205" t="n">
-        <v>3.82220220565796</v>
+        <v>3.82220244407654</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90654826164246</v>
+        <v>3.90654802322388</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>3.86215567588806</v>
+        <v>3.8621551990509</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>3.86215567588806</v>
+        <v>3.8621551990509</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G211" t="n">
-        <v>3.81776332855225</v>
+        <v>3.81776309013367</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>3.95981884002686</v>
+        <v>3.95981907844543</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>3.91986536979675</v>
+        <v>3.91986608505249</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>4.03084707260132</v>
+        <v>4.03084754943848</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G218" t="n">
-        <v>3.96425867080688</v>
+        <v>3.96425914764404</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>3.95094013214111</v>
+        <v>3.95094037055969</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>4.01752948760986</v>
+        <v>4.01752996444702</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G222" t="n">
-        <v>4.06636190414429</v>
+        <v>4.06636142730713</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G223" t="n">
-        <v>4.04416513442993</v>
+        <v>4.04416465759277</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>3.95981884002686</v>
+        <v>3.95981907844543</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>3.97313737869263</v>
+        <v>3.97313666343689</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.5</v>
       </c>
       <c r="G228" t="n">
-        <v>3.99533343315125</v>
+        <v>3.99533319473267</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>4.01309013366699</v>
+        <v>4.01309061050415</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G231" t="n">
-        <v>4.06636190414429</v>
+        <v>4.06636142730713</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.5</v>
       </c>
       <c r="G232" t="n">
-        <v>3.99533343315125</v>
+        <v>3.99533319473267</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G234" t="n">
-        <v>4.06636190414429</v>
+        <v>4.06636142730713</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G235" t="n">
-        <v>4.08411884307861</v>
+        <v>4.08411836624146</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>4.3327169418335</v>
+        <v>4.33271646499634</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G242" t="n">
-        <v>4.41262292861938</v>
+        <v>4.41262340545654</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G244" t="n">
-        <v>4.16846466064453</v>
+        <v>4.16846418380737</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>4.3105206489563</v>
+        <v>4.31052017211914</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>4.875</v>
       </c>
       <c r="G247" t="n">
-        <v>4.32827758789062</v>
+        <v>4.32827806472778</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G252" t="n">
-        <v>4.02196884155273</v>
+        <v>4.02196836471558</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G253" t="n">
-        <v>3.86215567588806</v>
+        <v>3.8621551990509</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G255" t="n">
-        <v>3.96425867080688</v>
+        <v>3.96425914764404</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>4.06636190414429</v>
+        <v>4.06636142730713</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>4.2883243560791</v>
+        <v>4.28832387924194</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>4.15070676803589</v>
+        <v>4.15070724487305</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>4.1951003074646</v>
+        <v>4.19509983062744</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G261" t="n">
-        <v>4.09299755096436</v>
+        <v>4.0929970741272</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>4.01309013366699</v>
+        <v>4.01309061050415</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G264" t="n">
-        <v>4.05748319625854</v>
+        <v>4.05748271942139</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>4.04416513442993</v>
+        <v>4.04416465759277</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>4.08411884307861</v>
+        <v>4.08411836624146</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G268" t="n">
-        <v>4.05748319625854</v>
+        <v>4.05748271942139</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>3.90654826164246</v>
+        <v>3.90654802322388</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G271" t="n">
-        <v>3.95094013214111</v>
+        <v>3.95094037055969</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>3.95981884002686</v>
+        <v>3.95981907844543</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G274" t="n">
-        <v>3.95537996292114</v>
+        <v>3.95537972450256</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>3.84883737564087</v>
+        <v>3.84883785247803</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G278" t="n">
-        <v>3.84883737564087</v>
+        <v>3.84883785247803</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G279" t="n">
-        <v>3.81776332855225</v>
+        <v>3.81776309013367</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>4.25</v>
       </c>
       <c r="G280" t="n">
-        <v>3.77337002754211</v>
+        <v>3.77337026596069</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>4.25</v>
       </c>
       <c r="G281" t="n">
-        <v>3.77337002754211</v>
+        <v>3.77337026596069</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>3.81332397460938</v>
+        <v>3.8133237361908</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G283" t="n">
-        <v>3.81776332855225</v>
+        <v>3.81776309013367</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G284" t="n">
-        <v>3.80444526672363</v>
+        <v>3.80444502830505</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>4.25</v>
       </c>
       <c r="G285" t="n">
-        <v>3.77337002754211</v>
+        <v>3.77337026596069</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G288" t="n">
-        <v>3.74673438072205</v>
+        <v>3.7467348575592</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G289" t="n">
-        <v>3.74673438072205</v>
+        <v>3.7467348575592</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G293" t="n">
-        <v>3.82220220565796</v>
+        <v>3.82220244407654</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G294" t="n">
-        <v>3.81776332855225</v>
+        <v>3.81776309013367</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>3.69346380233765</v>
+        <v>3.69346356391907</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G297" t="n">
-        <v>3.72453856468201</v>
+        <v>3.72453880310059</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G301" t="n">
-        <v>3.50701451301575</v>
+        <v>3.50701475143433</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G302" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59579992294312</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G307" t="n">
-        <v>3.6224353313446</v>
+        <v>3.62243556976318</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>3.60911774635315</v>
+        <v>3.60911798477173</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G312" t="n">
-        <v>3.46262240409851</v>
+        <v>3.46262216567993</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>3.41822957992554</v>
+        <v>3.41822934150696</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G314" t="n">
-        <v>3.41822957992554</v>
+        <v>3.41822934150696</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G316" t="n">
-        <v>3.43154716491699</v>
+        <v>3.43154740333557</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G317" t="n">
-        <v>3.2317807674408</v>
+        <v>3.23178100585938</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G318" t="n">
-        <v>3.19626665115356</v>
+        <v>3.19626641273499</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>3.19626665115356</v>
+        <v>3.19626641273499</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G321" t="n">
-        <v>3.09860277175903</v>
+        <v>3.09860301017761</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G322" t="n">
-        <v>3.16519165039062</v>
+        <v>3.1651918888092</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>3.24065899848938</v>
+        <v>3.24065923690796</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G324" t="n">
-        <v>3.2317807674408</v>
+        <v>3.23178100585938</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>3.19626665115356</v>
+        <v>3.19626641273499</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G327" t="n">
-        <v>3.19626665115356</v>
+        <v>3.19626641273499</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G328" t="n">
-        <v>3.29393029212952</v>
+        <v>3.29393005371094</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G329" t="n">
-        <v>3.17407035827637</v>
+        <v>3.17407011985779</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G331" t="n">
-        <v>3.4271080493927</v>
+        <v>3.42710781097412</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G332" t="n">
-        <v>3.50701451301575</v>
+        <v>3.50701475143433</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>3.46262240409851</v>
+        <v>3.46262216567993</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>3.46262240409851</v>
+        <v>3.46262216567993</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>3.43598651885986</v>
+        <v>3.43598675727844</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G340" t="n">
-        <v>3.81332397460938</v>
+        <v>3.8133237361908</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G343" t="n">
-        <v>3.58248209953308</v>
+        <v>3.5824818611145</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59579992294312</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G347" t="n">
-        <v>3.81776332855225</v>
+        <v>3.81776309013367</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G348" t="n">
-        <v>3.74673438072205</v>
+        <v>3.7467348575592</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G349" t="n">
-        <v>3.76893091201782</v>
+        <v>3.76893067359924</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G350" t="n">
-        <v>3.76893091201782</v>
+        <v>3.76893067359924</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G351" t="n">
-        <v>3.95094013214111</v>
+        <v>3.95094037055969</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>4.03084707260132</v>
+        <v>4.03084754943848</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.5</v>
       </c>
       <c r="G356" t="n">
-        <v>3.99533343315125</v>
+        <v>3.99533319473267</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>3.97313737869263</v>
+        <v>3.97313666343689</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G359" t="n">
-        <v>3.90210890769958</v>
+        <v>3.90210866928101</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G360" t="n">
-        <v>3.90654826164246</v>
+        <v>3.90654802322388</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>3.96425867080688</v>
+        <v>3.96425914764404</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>3.98201608657837</v>
+        <v>3.98201584815979</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G364" t="n">
-        <v>3.96869707107544</v>
+        <v>3.9686975479126</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>3.96425867080688</v>
+        <v>3.96425914764404</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>3.97313737869263</v>
+        <v>3.97313666343689</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G371" t="n">
-        <v>3.76449131965637</v>
+        <v>3.76449179649353</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G372" t="n">
-        <v>3.73341727256775</v>
+        <v>3.73341655731201</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G374" t="n">
-        <v>3.76449131965637</v>
+        <v>3.76449179649353</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G376" t="n">
-        <v>3.76449131965637</v>
+        <v>3.76449179649353</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>3.5292112827301</v>
+        <v>3.52921080589294</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G383" t="n">
-        <v>3.63575291633606</v>
+        <v>3.63575315475464</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59579992294312</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>3.7911274433136</v>
+        <v>3.79112720489502</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G391" t="n">
-        <v>3.90210890769958</v>
+        <v>3.90210866928101</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G392" t="n">
-        <v>3.75561308860779</v>
+        <v>3.75561356544495</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G393" t="n">
-        <v>3.6224353313446</v>
+        <v>3.62243556976318</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G395" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59579992294312</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G396" t="n">
-        <v>3.56916427612305</v>
+        <v>3.56916451454163</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G400" t="n">
-        <v>3.58248209953308</v>
+        <v>3.5824818611145</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G403" t="n">
-        <v>3.56472492218018</v>
+        <v>3.56472516059875</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>3.60911774635315</v>
+        <v>3.60911798477173</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G405" t="n">
-        <v>3.53808975219727</v>
+        <v>3.53808927536011</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G407" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59579992294312</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G415" t="n">
-        <v>3.60911774635315</v>
+        <v>3.60911798477173</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G417" t="n">
-        <v>3.64552760124207</v>
+        <v>3.64552783966064</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G420" t="n">
-        <v>3.65462970733643</v>
+        <v>3.654629945755</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G421" t="n">
-        <v>3.69559073448181</v>
+        <v>3.69559097290039</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G422" t="n">
-        <v>3.69559073448181</v>
+        <v>3.69559097290039</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G423" t="n">
-        <v>3.70014214515686</v>
+        <v>3.70014238357544</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G424" t="n">
-        <v>3.72289848327637</v>
+        <v>3.72289824485779</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>3.75020551681519</v>
+        <v>3.75020575523376</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G428" t="n">
-        <v>3.72289848327637</v>
+        <v>3.72289824485779</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G429" t="n">
-        <v>3.72289848327637</v>
+        <v>3.72289824485779</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G430" t="n">
-        <v>3.71379566192627</v>
+        <v>3.71379590034485</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>3.65918111801147</v>
+        <v>3.65918135643005</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G438" t="n">
-        <v>3.71379566192627</v>
+        <v>3.71379590034485</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G443" t="n">
-        <v>3.77751326560974</v>
+        <v>3.77751302719116</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G445" t="n">
-        <v>3.75020551681519</v>
+        <v>3.75020575523376</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G446" t="n">
-        <v>3.72289848327637</v>
+        <v>3.72289824485779</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G450" t="n">
-        <v>3.75020551681519</v>
+        <v>3.75020575523376</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>3.77751326560974</v>
+        <v>3.77751302719116</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G452" t="n">
-        <v>3.75020551681519</v>
+        <v>3.75020575523376</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>3.69559073448181</v>
+        <v>3.69559097290039</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G457" t="n">
-        <v>3.65918111801147</v>
+        <v>3.65918135643005</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G461" t="n">
-        <v>3.65918111801147</v>
+        <v>3.65918135643005</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.75</v>
       </c>
       <c r="G473" t="n">
-        <v>3.41341519355774</v>
+        <v>3.41341543197632</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G474" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G485" t="n">
-        <v>3.48623466491699</v>
+        <v>3.48623490333557</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G488" t="n">
-        <v>3.38610792160034</v>
+        <v>3.38610816001892</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>3.75</v>
       </c>
       <c r="G491" t="n">
-        <v>3.41341519355774</v>
+        <v>3.41341543197632</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>3.39521026611328</v>
+        <v>3.39521050453186</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G496" t="n">
-        <v>3.52264451980591</v>
+        <v>3.52264475822449</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G498" t="n">
-        <v>3.52264451980591</v>
+        <v>3.52264475822449</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G501" t="n">
-        <v>3.53174710273743</v>
+        <v>3.53174734115601</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G503" t="n">
-        <v>3.53174710273743</v>
+        <v>3.53174734115601</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G505" t="n">
-        <v>3.49533700942993</v>
+        <v>3.49533724784851</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>3.44982504844666</v>
+        <v>3.44982528686523</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>3.75</v>
       </c>
       <c r="G507" t="n">
-        <v>3.41341519355774</v>
+        <v>3.41341543197632</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G512" t="n">
-        <v>3.38610792160034</v>
+        <v>3.38610816001892</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G516" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G518" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G523" t="n">
-        <v>3.25867390632629</v>
+        <v>3.25867366790771</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G524" t="n">
-        <v>3.30418610572815</v>
+        <v>3.30418586730957</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G526" t="n">
-        <v>3.30418610572815</v>
+        <v>3.30418586730957</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G527" t="n">
-        <v>3.29508352279663</v>
+        <v>3.29508328437805</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>3.29508352279663</v>
+        <v>3.29508328437805</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G537" t="n">
-        <v>3.24046874046326</v>
+        <v>3.24046897888184</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G543" t="n">
-        <v>3.29508352279663</v>
+        <v>3.29508328437805</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G544" t="n">
-        <v>3.24957156181335</v>
+        <v>3.24957132339478</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G547" t="n">
-        <v>3.24957156181335</v>
+        <v>3.24957132339478</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G549" t="n">
-        <v>3.13123989105225</v>
+        <v>3.13123965263367</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G550" t="n">
-        <v>3.13123989105225</v>
+        <v>3.13123965263367</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G556" t="n">
-        <v>3.09483003616333</v>
+        <v>3.09482979774475</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G558" t="n">
-        <v>2.86726880073547</v>
+        <v>2.86726903915405</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G560" t="n">
-        <v>2.81265425682068</v>
+        <v>2.8126540184021</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>2.63970804214478</v>
+        <v>2.6397078037262</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.67611765861511</v>
+        <v>2.67611742019653</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.75</v>
       </c>
       <c r="G575" t="n">
-        <v>2.50317120552063</v>
+        <v>2.50317144393921</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.75</v>
       </c>
       <c r="G579" t="n">
-        <v>2.50317120552063</v>
+        <v>2.50317144393921</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G580" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.75</v>
       </c>
       <c r="G587" t="n">
-        <v>2.50317120552063</v>
+        <v>2.50317144393921</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G589" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G599" t="n">
-        <v>2.41214680671692</v>
+        <v>2.4121470451355</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G600" t="n">
-        <v>2.41214680671692</v>
+        <v>2.4121470451355</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G610" t="n">
-        <v>2.32112240791321</v>
+        <v>2.32112216949463</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G611" t="n">
-        <v>2.41214680671692</v>
+        <v>2.4121470451355</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G612" t="n">
-        <v>2.40304446220398</v>
+        <v>2.40304470062256</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G631" t="n">
-        <v>2.44855642318726</v>
+        <v>2.44855666160583</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G633" t="n">
-        <v>2.41214680671692</v>
+        <v>2.4121470451355</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G634" t="n">
-        <v>2.41214680671692</v>
+        <v>2.4121470451355</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G635" t="n">
-        <v>2.44855642318726</v>
+        <v>2.44855666160583</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G636" t="n">
-        <v>2.44855642318726</v>
+        <v>2.44855666160583</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G637" t="n">
-        <v>2.32112240791321</v>
+        <v>2.32112216949463</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G639" t="n">
-        <v>2.18458604812622</v>
+        <v>2.18458580970764</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G640" t="n">
-        <v>2.18458604812622</v>
+        <v>2.18458580970764</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>2.08445882797241</v>
+        <v>2.08445906639099</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G645" t="n">
-        <v>2.01163959503174</v>
+        <v>2.01163935661316</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>2.08445882797241</v>
+        <v>2.08445906639099</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>2.18458604812622</v>
+        <v>2.18458580970764</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>2.08445882797241</v>
+        <v>2.08445906639099</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G654" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.46676158905029</v>
+        <v>2.46676135063171</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G659" t="n">
-        <v>2.40304446220398</v>
+        <v>2.40304470062256</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G665" t="n">
-        <v>2.17548370361328</v>
+        <v>2.1754834651947</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>2.18458604812622</v>
+        <v>2.18458580970764</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>2.18458604812622</v>
+        <v>2.18458580970764</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G672" t="n">
-        <v>2.14817595481873</v>
+        <v>2.14817571640015</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G674" t="n">
-        <v>2.12997078895569</v>
+        <v>2.12997102737427</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>2.08445882797241</v>
+        <v>2.08445906639099</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>2.08445882797241</v>
+        <v>2.08445906639099</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G697" t="n">
-        <v>1.94792234897614</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G698" t="n">
-        <v>1.94792234897614</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G699" t="n">
-        <v>1.94792234897614</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G700" t="n">
-        <v>1.94792234897614</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G701" t="n">
-        <v>1.94792234897614</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>1.72491252422333</v>
+        <v>1.72491264343262</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G709" t="n">
-        <v>1.69760513305664</v>
+        <v>1.69760525226593</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G717" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132237911224</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G721" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G722" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G723" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G724" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G729" t="n">
-        <v>1.69305396080017</v>
+        <v>1.69305408000946</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G736" t="n">
-        <v>1.64754176139832</v>
+        <v>1.64754164218903</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G737" t="n">
-        <v>1.66574680805206</v>
+        <v>1.66574668884277</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G738" t="n">
-        <v>1.66574680805206</v>
+        <v>1.66574668884277</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G739" t="n">
-        <v>1.76587355136871</v>
+        <v>1.765873670578</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G740" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G743" t="n">
-        <v>1.92061483860016</v>
+        <v>1.92061507701874</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G749" t="n">
-        <v>1.92061483860016</v>
+        <v>1.92061507701874</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G750" t="n">
-        <v>1.91151237487793</v>
+        <v>1.91151261329651</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G751" t="n">
-        <v>1.92061483860016</v>
+        <v>1.92061507701874</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G752" t="n">
-        <v>1.91151237487793</v>
+        <v>1.91151261329651</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G759" t="n">
-        <v>1.94792234897614</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G763" t="n">
-        <v>2.13907361030579</v>
+        <v>2.13907337188721</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G764" t="n">
-        <v>2.14817595481873</v>
+        <v>2.14817571640015</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G765" t="n">
-        <v>2.14817595481873</v>
+        <v>2.14817571640015</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G775" t="n">
-        <v>2.12997078895569</v>
+        <v>2.12997102737427</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>2.01163959503174</v>
+        <v>2.01163935661316</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>2.01163959503174</v>
+        <v>2.01163935661316</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G800" t="n">
-        <v>1.95702469348907</v>
+        <v>1.95702493190765</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G801" t="n">
-        <v>1.85689783096313</v>
+        <v>1.85689795017242</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.85689783096313</v>
+        <v>1.85689795017242</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G810" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G812" t="n">
-        <v>1.87510275840759</v>
+        <v>1.87510287761688</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G813" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G815" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G816" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G819" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G820" t="n">
-        <v>1.77952718734741</v>
+        <v>1.7795273065567</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G821" t="n">
-        <v>1.76587355136871</v>
+        <v>1.765873670578</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G822" t="n">
-        <v>1.76587355136871</v>
+        <v>1.765873670578</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G823" t="n">
-        <v>1.76587355136871</v>
+        <v>1.765873670578</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G830" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.72491252422333</v>
+        <v>1.72491264343262</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1.875</v>
       </c>
       <c r="G834" t="n">
-        <v>1.70670759677887</v>
+        <v>1.70670771598816</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G837" t="n">
-        <v>1.66574680805206</v>
+        <v>1.66574668884277</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G838" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G851" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G852" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G856" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132237911224</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G857" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132237911224</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G858" t="n">
-        <v>1.76587355136871</v>
+        <v>1.765873670578</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G859" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G860" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G861" t="n">
-        <v>1.7431173324585</v>
+        <v>1.74311745166779</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G862" t="n">
-        <v>1.7431173324585</v>
+        <v>1.74311745166779</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.875</v>
       </c>
       <c r="G864" t="n">
-        <v>1.70670759677887</v>
+        <v>1.70670771598816</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>1.875</v>
       </c>
       <c r="G865" t="n">
-        <v>1.70670759677887</v>
+        <v>1.70670771598816</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G866" t="n">
-        <v>1.6885027885437</v>
+        <v>1.68850266933441</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G867" t="n">
-        <v>1.6885027885437</v>
+        <v>1.68850266933441</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G869" t="n">
-        <v>1.64754176139832</v>
+        <v>1.64754164218903</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G870" t="n">
-        <v>1.62023437023163</v>
+        <v>1.62023448944092</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G871" t="n">
-        <v>1.62023437023163</v>
+        <v>1.62023448944092</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G874" t="n">
-        <v>1.66574680805206</v>
+        <v>1.66574668884277</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>1.72491252422333</v>
+        <v>1.72491264343262</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G878" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G883" t="n">
-        <v>1.85689783096313</v>
+        <v>1.85689795017242</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G884" t="n">
-        <v>1.85689783096313</v>
+        <v>1.85689795017242</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>1.85689783096313</v>
+        <v>1.85689795017242</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G886" t="n">
-        <v>1.85689783096313</v>
+        <v>1.85689795017242</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G893" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G894" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G895" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G896" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G898" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G899" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G902" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G903" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G904" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G905" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G906" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132237911224</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G919" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G923" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132237911224</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G924" t="n">
-        <v>1.77952718734741</v>
+        <v>1.7795273065567</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G928" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G929" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G930" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G931" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G932" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G936" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G937" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>1.85689783096313</v>
+        <v>1.85689795017242</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G944" t="n">
-        <v>1.87510275840759</v>
+        <v>1.87510287761688</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G945" t="n">
-        <v>1.87510275840759</v>
+        <v>1.87510287761688</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G952" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G955" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G958" t="n">
-        <v>1.76587355136871</v>
+        <v>1.765873670578</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G964" t="n">
-        <v>1.76587355136871</v>
+        <v>1.765873670578</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G966" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G967" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G988" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G989" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G990" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G998" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G999" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.47795939445496</v>
+        <v>1.47795927524567</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.47795939445496</v>
+        <v>1.47795927524567</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.4971536397934</v>
+        <v>1.49715352058411</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.36279356479645</v>
+        <v>1.36279368400574</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.36279356479645</v>
+        <v>1.36279368400574</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.36279356479645</v>
+        <v>1.36279368400574</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.42997372150421</v>
+        <v>1.42997360229492</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.42997372150421</v>
+        <v>1.42997360229492</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.42997372150421</v>
+        <v>1.42997360229492</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.42997372150421</v>
+        <v>1.42997360229492</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1192" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.95781624317169</v>
+        <v>1.95781636238098</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.95781624317169</v>
+        <v>1.95781636238098</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.84265053272247</v>
+        <v>1.84265065193176</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1209" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.4971536397934</v>
+        <v>1.49715352058411</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1237" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1238" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.01539897918701</v>
+        <v>2.01539921760559</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.8906364440918</v>
+        <v>1.89063632488251</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.8906364440918</v>
+        <v>1.89063632488251</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1314" t="n">
-        <v>1.8618448972702</v>
+        <v>1.86184501647949</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.8906364440918</v>
+        <v>1.89063632488251</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -47562,6 +47562,32 @@
         <v>2.22000002861023</v>
       </c>
       <c r="H1815" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1816" t="n">
+        <v>51000</v>
+      </c>
+      <c r="C1816" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="D1816" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="E1816" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="F1816" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="G1816" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="H1816" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -577,7 +577,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G8" t="n">
-        <v>1.63265800476074</v>
+        <v>1.63265812397003</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G10" t="n">
-        <v>1.87339866161346</v>
+        <v>1.87339878082275</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G14" t="n">
-        <v>3.6942720413208</v>
+        <v>3.69427180290222</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3.9393892288208</v>
+        <v>3.93938946723938</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3.9393892288208</v>
+        <v>3.93938946723938</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>3.87810969352722</v>
+        <v>3.87810945510864</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G20" t="n">
-        <v>3.66800904273987</v>
+        <v>3.66800928115845</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G21" t="n">
-        <v>3.52794241905212</v>
+        <v>3.52794218063354</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G24" t="n">
-        <v>3.6942720413208</v>
+        <v>3.69427180290222</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G27" t="n">
-        <v>3.51043391227722</v>
+        <v>3.51043367385864</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G31" t="n">
-        <v>3.48417091369629</v>
+        <v>3.48417115211487</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G32" t="n">
-        <v>3.45353126525879</v>
+        <v>3.45353102684021</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>3.40976023674011</v>
+        <v>3.40976047515869</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.75</v>
       </c>
       <c r="G38" t="n">
-        <v>3.28282451629639</v>
+        <v>3.28282475471497</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G46" t="n">
-        <v>2.98080444335938</v>
+        <v>2.9808042049408</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>2.77945804595947</v>
+        <v>2.77945780754089</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.125</v>
       </c>
       <c r="G52" t="n">
-        <v>2.73568725585938</v>
+        <v>2.7356870174408</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>2.81009793281555</v>
+        <v>2.81009769439697</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G61" t="n">
-        <v>2.85824584960938</v>
+        <v>2.8582456111908</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G62" t="n">
-        <v>2.81009793281555</v>
+        <v>2.81009769439697</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G64" t="n">
-        <v>2.84073734283447</v>
+        <v>2.84073710441589</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G73" t="n">
-        <v>2.87137699127197</v>
+        <v>2.87137722969055</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>2.77945804595947</v>
+        <v>2.77945780754089</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>2.72693252563477</v>
+        <v>2.72693276405334</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G80" t="n">
-        <v>2.83198308944702</v>
+        <v>2.8319833278656</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G82" t="n">
-        <v>2.74006390571594</v>
+        <v>2.74006414413452</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>2.84073734283447</v>
+        <v>2.84073710441589</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G92" t="n">
-        <v>2.87137699127197</v>
+        <v>2.87137722969055</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.86700010299683</v>
+        <v>2.86700034141541</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>4.11447286605835</v>
+        <v>4.11447334289551</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G113" t="n">
-        <v>3.52794241905212</v>
+        <v>3.52794218063354</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G115" t="n">
-        <v>3.77305936813354</v>
+        <v>3.77305960655212</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>3.97878336906433</v>
+        <v>3.97878360748291</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>3.91312670707703</v>
+        <v>3.91312646865845</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G119" t="n">
-        <v>3.79932236671448</v>
+        <v>3.79932188987732</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>3.84747004508972</v>
+        <v>3.84746980667114</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G121" t="n">
-        <v>3.89124155044556</v>
+        <v>3.89124202728271</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G122" t="n">
-        <v>3.92625832557678</v>
+        <v>3.9262580871582</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>4.28955698013306</v>
+        <v>4.28955745697021</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>4.24578619003296</v>
+        <v>4.24578666687012</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G128" t="n">
-        <v>4.16699886322021</v>
+        <v>4.16699838638306</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G131" t="n">
-        <v>4.04006195068359</v>
+        <v>4.04006242752075</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>3.9568977355957</v>
+        <v>3.95689749717712</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G137" t="n">
-        <v>3.98753714561462</v>
+        <v>3.98753690719604</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G142" t="n">
-        <v>4.32895183563232</v>
+        <v>4.32895135879517</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G143" t="n">
-        <v>5.16497755050659</v>
+        <v>5.16497707366943</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G150" t="n">
-        <v>3.78181385993958</v>
+        <v>3.78181409835815</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G151" t="n">
-        <v>3.80369901657104</v>
+        <v>3.80369925498962</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>3.79932236671448</v>
+        <v>3.79932188987732</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G154" t="n">
-        <v>3.08147788047791</v>
+        <v>3.08147811889648</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G157" t="n">
-        <v>2.45555281639099</v>
+        <v>2.45555257797241</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G162" t="n">
-        <v>3.08147788047791</v>
+        <v>3.08147811889648</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G163" t="n">
-        <v>3.22154498100281</v>
+        <v>3.22154521942139</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G165" t="n">
-        <v>3.58046698570251</v>
+        <v>3.58046722412109</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.75555062294006</v>
+        <v>3.75555086135864</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G167" t="n">
-        <v>3.71178007125854</v>
+        <v>3.71177983283997</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>3.62861490249634</v>
+        <v>3.62861514091492</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G169" t="n">
-        <v>3.60672974586487</v>
+        <v>3.60672998428345</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>3.66800904273987</v>
+        <v>3.66800928115845</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G172" t="n">
-        <v>3.68551731109619</v>
+        <v>3.68551754951477</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G173" t="n">
-        <v>3.95252013206482</v>
+        <v>3.9525203704834</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G175" t="n">
-        <v>3.94376635551453</v>
+        <v>3.94376659393311</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>4.07070302963257</v>
+        <v>4.07070255279541</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>4.07070302963257</v>
+        <v>4.07070255279541</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G179" t="n">
-        <v>3.70302629470825</v>
+        <v>3.70302605628967</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G181" t="n">
-        <v>3.87810969352722</v>
+        <v>3.87810945510864</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G182" t="n">
-        <v>3.70302629470825</v>
+        <v>3.70302605628967</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G189" t="n">
-        <v>3.7511739730835</v>
+        <v>3.75117421150208</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>3.7289776802063</v>
+        <v>3.72897791862488</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>3.79112720489502</v>
+        <v>3.7911274433136</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>4.5</v>
       </c>
       <c r="G199" t="n">
-        <v>3.99533319473267</v>
+        <v>3.99533343315125</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G201" t="n">
-        <v>3.83552002906799</v>
+        <v>3.83552026748657</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>3.83108067512512</v>
+        <v>3.83108043670654</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G204" t="n">
-        <v>3.82220244407654</v>
+        <v>3.82220220565796</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G205" t="n">
-        <v>3.82220244407654</v>
+        <v>3.82220220565796</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>3.7289776802063</v>
+        <v>3.72897791862488</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90654802322388</v>
+        <v>3.90654826164246</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G211" t="n">
-        <v>3.81776309013367</v>
+        <v>3.81776332855225</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>3.95981907844543</v>
+        <v>3.95981931686401</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>3.91986608505249</v>
+        <v>3.91986584663391</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G218" t="n">
-        <v>3.96425914764404</v>
+        <v>3.96425867080688</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>3.95094037055969</v>
+        <v>3.95094013214111</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>3.95981907844543</v>
+        <v>3.95981931686401</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G226" t="n">
-        <v>4.00421190261841</v>
+        <v>4.00421142578125</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>3.97313666343689</v>
+        <v>3.97313642501831</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.5</v>
       </c>
       <c r="G228" t="n">
-        <v>3.99533319473267</v>
+        <v>3.99533343315125</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>4.01309061050415</v>
+        <v>4.01309013366699</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.5</v>
       </c>
       <c r="G232" t="n">
-        <v>3.99533319473267</v>
+        <v>3.99533343315125</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.48365163803101</v>
+        <v>4.48365211486816</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>4.40374517440796</v>
+        <v>4.4037446975708</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>4.33271646499634</v>
+        <v>4.3327169418335</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G243" t="n">
-        <v>4.31939888000488</v>
+        <v>4.31939935684204</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G244" t="n">
-        <v>4.16846418380737</v>
+        <v>4.16846466064453</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>4.31052017211914</v>
+        <v>4.3105206489563</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G250" t="n">
-        <v>4.29720306396484</v>
+        <v>4.29720258712769</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G255" t="n">
-        <v>3.96425914764404</v>
+        <v>3.96425867080688</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>4.19953918457031</v>
+        <v>4.19953966140747</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G262" t="n">
-        <v>4.08855772018433</v>
+        <v>4.08855819702148</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>4.01309061050415</v>
+        <v>4.01309013366699</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G264" t="n">
-        <v>4.05748271942139</v>
+        <v>4.05748319625854</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G268" t="n">
-        <v>4.05748271942139</v>
+        <v>4.05748319625854</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>3.90654802322388</v>
+        <v>3.90654826164246</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G271" t="n">
-        <v>3.95094037055969</v>
+        <v>3.95094013214111</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>3.95981907844543</v>
+        <v>3.95981931686401</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G274" t="n">
-        <v>3.95537972450256</v>
+        <v>3.95537996292114</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G279" t="n">
-        <v>3.81776309013367</v>
+        <v>3.81776332855225</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>3.8133237361908</v>
+        <v>3.81332349777222</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G283" t="n">
-        <v>3.81776309013367</v>
+        <v>3.81776332855225</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G284" t="n">
-        <v>3.80444502830505</v>
+        <v>3.80444526672363</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>3.7289776802063</v>
+        <v>3.72897791862488</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G293" t="n">
-        <v>3.82220244407654</v>
+        <v>3.82220220565796</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G294" t="n">
-        <v>3.81776309013367</v>
+        <v>3.81776332855225</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>3.69790291786194</v>
+        <v>3.69790267944336</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G297" t="n">
-        <v>3.72453880310059</v>
+        <v>3.72453856468201</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G300" t="n">
-        <v>3.59136080741882</v>
+        <v>3.5913610458374</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G302" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>3.64019250869751</v>
+        <v>3.64019274711609</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G306" t="n">
-        <v>3.57804322242737</v>
+        <v>3.57804298400879</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>3.60911798477173</v>
+        <v>3.60911774635315</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G311" t="n">
-        <v>3.50257539749146</v>
+        <v>3.50257515907288</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>3.41822934150696</v>
+        <v>3.41822957992554</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G314" t="n">
-        <v>3.41822934150696</v>
+        <v>3.41822957992554</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G316" t="n">
-        <v>3.43154740333557</v>
+        <v>3.43154716491699</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G317" t="n">
-        <v>3.23178100585938</v>
+        <v>3.2317807674408</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G318" t="n">
-        <v>3.19626641273499</v>
+        <v>3.19626665115356</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>3.19626641273499</v>
+        <v>3.19626665115356</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G321" t="n">
-        <v>3.09860301017761</v>
+        <v>3.09860277175903</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G324" t="n">
-        <v>3.23178100585938</v>
+        <v>3.2317807674408</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>3.19626641273499</v>
+        <v>3.19626665115356</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G327" t="n">
-        <v>3.19626641273499</v>
+        <v>3.19626665115356</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G329" t="n">
-        <v>3.17407011985779</v>
+        <v>3.17407035827637</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>3.38271546363831</v>
+        <v>3.38271570205688</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>3.43598675727844</v>
+        <v>3.43598651885986</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G340" t="n">
-        <v>3.8133237361908</v>
+        <v>3.81332349777222</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>3.64019250869751</v>
+        <v>3.64019274711609</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G342" t="n">
-        <v>3.64907121658325</v>
+        <v>3.64907097816467</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G343" t="n">
-        <v>3.5824818611145</v>
+        <v>3.58248209953308</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G344" t="n">
-        <v>3.57804322242737</v>
+        <v>3.57804298400879</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G347" t="n">
-        <v>3.81776309013367</v>
+        <v>3.81776332855225</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G351" t="n">
-        <v>3.95094037055969</v>
+        <v>3.95094013214111</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G353" t="n">
-        <v>3.94650173187256</v>
+        <v>3.94650220870972</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.5</v>
       </c>
       <c r="G356" t="n">
-        <v>3.99533319473267</v>
+        <v>3.99533343315125</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>3.97313666343689</v>
+        <v>3.97313642501831</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G359" t="n">
-        <v>3.90210866928101</v>
+        <v>3.90210843086243</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G360" t="n">
-        <v>3.90654802322388</v>
+        <v>3.90654826164246</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>3.96425914764404</v>
+        <v>3.96425867080688</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>3.92874431610107</v>
+        <v>3.92874455451965</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>3.98201584815979</v>
+        <v>3.98201560974121</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>3.96425914764404</v>
+        <v>3.96425867080688</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>3.97313666343689</v>
+        <v>3.97313642501831</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>3.8532772064209</v>
+        <v>3.85327672958374</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G371" t="n">
-        <v>3.76449179649353</v>
+        <v>3.76449155807495</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G374" t="n">
-        <v>3.76449179649353</v>
+        <v>3.76449155807495</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G376" t="n">
-        <v>3.76449179649353</v>
+        <v>3.76449155807495</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G377" t="n">
-        <v>3.7289776802063</v>
+        <v>3.72897791862488</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>3.64019250869751</v>
+        <v>3.64019274711609</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>3.52921080589294</v>
+        <v>3.52921104431152</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G384" t="n">
-        <v>3.64019250869751</v>
+        <v>3.64019274711609</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G385" t="n">
-        <v>3.60467839241028</v>
+        <v>3.60467863082886</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G389" t="n">
-        <v>3.64907121658325</v>
+        <v>3.64907097816467</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>3.79112720489502</v>
+        <v>3.7911274433136</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G391" t="n">
-        <v>3.90210866928101</v>
+        <v>3.90210843086243</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G392" t="n">
-        <v>3.75561356544495</v>
+        <v>3.75561332702637</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G395" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>3.59136080741882</v>
+        <v>3.5913610458374</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G400" t="n">
-        <v>3.5824818611145</v>
+        <v>3.58248209953308</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G401" t="n">
-        <v>3.57804322242737</v>
+        <v>3.57804298400879</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>3.60911798477173</v>
+        <v>3.60911774635315</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G407" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G410" t="n">
-        <v>3.60467839241028</v>
+        <v>3.60467863082886</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G414" t="n">
-        <v>3.60467839241028</v>
+        <v>3.60467863082886</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G415" t="n">
-        <v>3.60911798477173</v>
+        <v>3.60911774635315</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -47588,6 +47588,32 @@
         <v>2.24000000953674</v>
       </c>
       <c r="H1816" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1817" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C1817" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="D1817" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="E1817" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F1817" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="G1817" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="H1817" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>1.30437552928925</v>
+        <v>1.30437564849854</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>1.50020003318787</v>
       </c>
       <c r="G3" t="n">
-        <v>1.31330502033234</v>
+        <v>1.31330490112305</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G7" t="n">
-        <v>1.58888697624207</v>
+        <v>1.58888709545135</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7202000617981</v>
+        <v>1.72019994258881</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G10" t="n">
-        <v>1.87339878082275</v>
+        <v>1.87339854240417</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G13" t="n">
-        <v>3.17777395248413</v>
+        <v>3.17777419090271</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G14" t="n">
-        <v>3.69427180290222</v>
+        <v>3.69427156448364</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3.93938946723938</v>
+        <v>3.93938899040222</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3.93938946723938</v>
+        <v>3.93938899040222</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>3.87810945510864</v>
+        <v>3.8781099319458</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>3.57171297073364</v>
+        <v>3.57171273231506</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G24" t="n">
-        <v>3.69427180290222</v>
+        <v>3.69427156448364</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G25" t="n">
-        <v>3.55420470237732</v>
+        <v>3.55420446395874</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G27" t="n">
-        <v>3.51043367385864</v>
+        <v>3.51043391227722</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G28" t="n">
-        <v>3.42289185523987</v>
+        <v>3.42289161682129</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G29" t="n">
-        <v>3.51918792724609</v>
+        <v>3.51918768882751</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G32" t="n">
-        <v>3.45353102684021</v>
+        <v>3.45353126525879</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.75</v>
       </c>
       <c r="G38" t="n">
-        <v>3.28282475471497</v>
+        <v>3.28282427787781</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>3.17777395248413</v>
+        <v>3.17777419090271</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G42" t="n">
-        <v>2.78383541107178</v>
+        <v>2.78383493423462</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G43" t="n">
-        <v>2.62188220024109</v>
+        <v>2.62188243865967</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G46" t="n">
-        <v>2.9808042049408</v>
+        <v>2.98080468177795</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G48" t="n">
-        <v>2.83636021614075</v>
+        <v>2.83636045455933</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>2.73130965232849</v>
+        <v>2.73130989074707</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G54" t="n">
-        <v>2.89763975143433</v>
+        <v>2.89763951301575</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G56" t="n">
-        <v>2.9063937664032</v>
+        <v>2.90639400482178</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G59" t="n">
-        <v>2.78383541107178</v>
+        <v>2.78383493423462</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G61" t="n">
-        <v>2.8582456111908</v>
+        <v>2.85824584960938</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G64" t="n">
-        <v>2.84073710441589</v>
+        <v>2.84073734283447</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>2.82760620117188</v>
+        <v>2.8276059627533</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>2.82760620117188</v>
+        <v>2.8276059627533</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>2.83636021614075</v>
+        <v>2.83636045455933</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>2.78383541107178</v>
+        <v>2.78383493423462</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G73" t="n">
-        <v>2.87137722969055</v>
+        <v>2.87137699127197</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G74" t="n">
-        <v>2.84949159622192</v>
+        <v>2.8494918346405</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G76" t="n">
-        <v>2.78383541107178</v>
+        <v>2.78383493423462</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>2.77070379257202</v>
+        <v>2.77070355415344</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G80" t="n">
-        <v>2.8319833278656</v>
+        <v>2.83198308944702</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G84" t="n">
-        <v>2.83636021614075</v>
+        <v>2.83636045455933</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>2.84073710441589</v>
+        <v>2.84073734283447</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G92" t="n">
-        <v>2.87137722969055</v>
+        <v>2.87137699127197</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G94" t="n">
-        <v>2.83636021614075</v>
+        <v>2.83636045455933</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G95" t="n">
-        <v>2.83636021614075</v>
+        <v>2.83636045455933</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>2.82760620117188</v>
+        <v>2.8276059627533</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.86700034141541</v>
+        <v>2.86700010299683</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>4.39460754394531</v>
+        <v>4.39460802078247</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G109" t="n">
-        <v>3.965651512146</v>
+        <v>3.96565198898315</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>4.11447334289551</v>
+        <v>4.11447286605835</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.375</v>
       </c>
       <c r="G111" t="n">
-        <v>3.82996153831482</v>
+        <v>3.82996201515198</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>3.65487837791443</v>
+        <v>3.65487813949585</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G115" t="n">
-        <v>3.77305960655212</v>
+        <v>3.7730598449707</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>3.97878360748291</v>
+        <v>3.97878289222717</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>3.8606014251709</v>
+        <v>3.86060166358948</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G119" t="n">
-        <v>3.79932188987732</v>
+        <v>3.7993221282959</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G121" t="n">
-        <v>3.89124202728271</v>
+        <v>3.8912410736084</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G122" t="n">
-        <v>3.9262580871582</v>
+        <v>3.92625856399536</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>4.18012952804565</v>
+        <v>4.18013000488281</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>4.24578666687012</v>
+        <v>4.24578619003296</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>4.28518056869507</v>
+        <v>4.28518009185791</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G128" t="n">
-        <v>4.16699838638306</v>
+        <v>4.16699886322021</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>3.97002863883972</v>
+        <v>3.97002911567688</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G132" t="n">
-        <v>4.00504589080811</v>
+        <v>4.00504541397095</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>3.95689749717712</v>
+        <v>3.9568977355957</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G138" t="n">
-        <v>3.99629187583923</v>
+        <v>3.99629163742065</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G139" t="n">
-        <v>4.21952390670776</v>
+        <v>4.21952438354492</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G140" t="n">
-        <v>4.13635873794556</v>
+        <v>4.13635921478271</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>4.19326114654541</v>
+        <v>4.19326066970825</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G142" t="n">
-        <v>4.32895135879517</v>
+        <v>4.32895088195801</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G145" t="n">
-        <v>4.46464061737061</v>
+        <v>4.46464109420776</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G146" t="n">
-        <v>4.38585376739502</v>
+        <v>4.38585329055786</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>3.85184741020203</v>
+        <v>3.85184717178345</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G151" t="n">
-        <v>3.80369925498962</v>
+        <v>3.80369853973389</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>3.79932188987732</v>
+        <v>3.7993221282959</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G153" t="n">
-        <v>3.33097243309021</v>
+        <v>3.33097219467163</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G154" t="n">
-        <v>3.08147811889648</v>
+        <v>3.08147788047791</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G155" t="n">
-        <v>3.19965958595276</v>
+        <v>3.19965934753418</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G157" t="n">
-        <v>2.45555257797241</v>
+        <v>2.45555281639099</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>2.73130965232849</v>
+        <v>2.73130989074707</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>2.77508091926575</v>
+        <v>2.77508115768433</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G161" t="n">
-        <v>2.95891928672791</v>
+        <v>2.95891904830933</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G162" t="n">
-        <v>3.08147811889648</v>
+        <v>3.08147788047791</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G165" t="n">
-        <v>3.58046722412109</v>
+        <v>3.58046746253967</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G169" t="n">
-        <v>3.60672998428345</v>
+        <v>3.60672974586487</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G171" t="n">
-        <v>3.73366546630859</v>
+        <v>3.73366594314575</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G172" t="n">
-        <v>3.68551754951477</v>
+        <v>3.68551731109619</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G173" t="n">
-        <v>3.9525203704834</v>
+        <v>3.95252084732056</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.85184741020203</v>
+        <v>3.85184717178345</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G175" t="n">
-        <v>3.94376659393311</v>
+        <v>3.94376635551453</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>4.07070255279541</v>
+        <v>4.07070207595825</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>4.07070255279541</v>
+        <v>4.07070207595825</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>3.68113994598389</v>
+        <v>3.68114042282104</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G179" t="n">
-        <v>3.70302605628967</v>
+        <v>3.70302557945251</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G180" t="n">
-        <v>3.8343391418457</v>
+        <v>3.83433938026428</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G181" t="n">
-        <v>3.87810945510864</v>
+        <v>3.8781099319458</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G182" t="n">
-        <v>3.70302605628967</v>
+        <v>3.70302557945251</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>3.80807614326477</v>
+        <v>3.80807590484619</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>3.85184741020203</v>
+        <v>3.85184717178345</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>3.86935567855835</v>
+        <v>3.86935591697693</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G187" t="n">
-        <v>3.8606014251709</v>
+        <v>3.86060166358948</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>3.77743649482727</v>
+        <v>3.77743673324585</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G189" t="n">
-        <v>3.75117421150208</v>
+        <v>3.7511739730835</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G190" t="n">
-        <v>3.78224897384644</v>
+        <v>3.78224849700928</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>3.72897791862488</v>
+        <v>3.7289776802063</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G192" t="n">
-        <v>3.78668785095215</v>
+        <v>3.78668808937073</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G194" t="n">
-        <v>3.7467348575592</v>
+        <v>3.74673438072205</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G195" t="n">
-        <v>3.78224897384644</v>
+        <v>3.78224849700928</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>4.25</v>
       </c>
       <c r="G196" t="n">
-        <v>3.77337026596069</v>
+        <v>3.77337002754211</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G198" t="n">
-        <v>3.91098761558533</v>
+        <v>3.91098713874817</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G200" t="n">
-        <v>3.8621551990509</v>
+        <v>3.86215567588806</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>3.83108043670654</v>
+        <v>3.8310809135437</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>3.72897791862488</v>
+        <v>3.7289776802063</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>3.8621551990509</v>
+        <v>3.86215567588806</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>3.8621551990509</v>
+        <v>3.86215567588806</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>3.95981931686401</v>
+        <v>3.95981884002686</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>3.91986584663391</v>
+        <v>3.91986536979675</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>4.03084754943848</v>
+        <v>4.03084707260132</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>4.01752996444702</v>
+        <v>4.01752948760986</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G222" t="n">
-        <v>4.06636142730713</v>
+        <v>4.06636190414429</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G223" t="n">
-        <v>4.04416465759277</v>
+        <v>4.04416513442993</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>3.95981931686401</v>
+        <v>3.95981884002686</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G226" t="n">
-        <v>4.00421142578125</v>
+        <v>4.00421190261841</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>3.97313642501831</v>
+        <v>3.97313737869263</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G231" t="n">
-        <v>4.06636142730713</v>
+        <v>4.06636190414429</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G234" t="n">
-        <v>4.06636142730713</v>
+        <v>4.06636190414429</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G235" t="n">
-        <v>4.08411836624146</v>
+        <v>4.08411884307861</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.48365211486816</v>
+        <v>4.48365163803101</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>4.4037446975708</v>
+        <v>4.40374517440796</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G242" t="n">
-        <v>4.41262340545654</v>
+        <v>4.41262292861938</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G243" t="n">
-        <v>4.31939935684204</v>
+        <v>4.31939888000488</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>4.875</v>
       </c>
       <c r="G247" t="n">
-        <v>4.32827806472778</v>
+        <v>4.32827758789062</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G250" t="n">
-        <v>4.29720258712769</v>
+        <v>4.29720306396484</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G252" t="n">
-        <v>4.02196836471558</v>
+        <v>4.02196884155273</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G253" t="n">
-        <v>3.8621551990509</v>
+        <v>3.86215567588806</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>4.06636142730713</v>
+        <v>4.06636190414429</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>4.28832387924194</v>
+        <v>4.2883243560791</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>4.19953966140747</v>
+        <v>4.19953918457031</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>4.15070724487305</v>
+        <v>4.15070676803589</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>4.19509983062744</v>
+        <v>4.1951003074646</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G261" t="n">
-        <v>4.0929970741272</v>
+        <v>4.09299755096436</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G262" t="n">
-        <v>4.08855819702148</v>
+        <v>4.08855772018433</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>4.04416465759277</v>
+        <v>4.04416513442993</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>4.08411836624146</v>
+        <v>4.08411884307861</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>3.95981931686401</v>
+        <v>3.95981884002686</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>3.84883785247803</v>
+        <v>3.84883737564087</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G278" t="n">
-        <v>3.84883785247803</v>
+        <v>3.84883737564087</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>4.25</v>
       </c>
       <c r="G280" t="n">
-        <v>3.77337026596069</v>
+        <v>3.77337002754211</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>4.25</v>
       </c>
       <c r="G281" t="n">
-        <v>3.77337026596069</v>
+        <v>3.77337002754211</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>3.81332349777222</v>
+        <v>3.81332397460938</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>4.25</v>
       </c>
       <c r="G285" t="n">
-        <v>3.77337026596069</v>
+        <v>3.77337002754211</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>3.72897791862488</v>
+        <v>3.7289776802063</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G288" t="n">
-        <v>3.7467348575592</v>
+        <v>3.74673438072205</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G289" t="n">
-        <v>3.7467348575592</v>
+        <v>3.74673438072205</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>3.69790267944336</v>
+        <v>3.69790291786194</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>3.69346356391907</v>
+        <v>3.69346380233765</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G300" t="n">
-        <v>3.5913610458374</v>
+        <v>3.59136080741882</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G301" t="n">
-        <v>3.50701475143433</v>
+        <v>3.50701451301575</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>3.64019274711609</v>
+        <v>3.64019250869751</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G306" t="n">
-        <v>3.57804298400879</v>
+        <v>3.57804322242737</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G307" t="n">
-        <v>3.62243556976318</v>
+        <v>3.6224353313446</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G311" t="n">
-        <v>3.50257515907288</v>
+        <v>3.50257539749146</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G312" t="n">
-        <v>3.46262216567993</v>
+        <v>3.46262240409851</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G322" t="n">
-        <v>3.1651918888092</v>
+        <v>3.16519165039062</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>3.24065923690796</v>
+        <v>3.24065899848938</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G328" t="n">
-        <v>3.29393005371094</v>
+        <v>3.29393029212952</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G331" t="n">
-        <v>3.42710781097412</v>
+        <v>3.4271080493927</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G332" t="n">
-        <v>3.50701475143433</v>
+        <v>3.50701451301575</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>3.46262216567993</v>
+        <v>3.46262240409851</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>3.46262216567993</v>
+        <v>3.46262240409851</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>3.38271570205688</v>
+        <v>3.38271546363831</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G340" t="n">
-        <v>3.81332349777222</v>
+        <v>3.81332397460938</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>3.64019274711609</v>
+        <v>3.64019250869751</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G342" t="n">
-        <v>3.64907097816467</v>
+        <v>3.64907121658325</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G344" t="n">
-        <v>3.57804298400879</v>
+        <v>3.57804322242737</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G348" t="n">
-        <v>3.7467348575592</v>
+        <v>3.74673438072205</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G349" t="n">
-        <v>3.76893067359924</v>
+        <v>3.76893091201782</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G350" t="n">
-        <v>3.76893067359924</v>
+        <v>3.76893091201782</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G353" t="n">
-        <v>3.94650220870972</v>
+        <v>3.94650173187256</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>4.03084754943848</v>
+        <v>4.03084707260132</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>3.97313642501831</v>
+        <v>3.97313737869263</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G359" t="n">
-        <v>3.90210843086243</v>
+        <v>3.90210890769958</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>3.92874455451965</v>
+        <v>3.92874431610107</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>3.98201560974121</v>
+        <v>3.98201608657837</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G364" t="n">
-        <v>3.9686975479126</v>
+        <v>3.96869707107544</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>3.97313642501831</v>
+        <v>3.97313737869263</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>3.85327672958374</v>
+        <v>3.8532772064209</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G371" t="n">
-        <v>3.76449155807495</v>
+        <v>3.76449131965637</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G372" t="n">
-        <v>3.73341655731201</v>
+        <v>3.73341727256775</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G374" t="n">
-        <v>3.76449155807495</v>
+        <v>3.76449131965637</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G376" t="n">
-        <v>3.76449155807495</v>
+        <v>3.76449131965637</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G377" t="n">
-        <v>3.72897791862488</v>
+        <v>3.7289776802063</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>3.64019274711609</v>
+        <v>3.64019250869751</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>3.52921104431152</v>
+        <v>3.5292112827301</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G383" t="n">
-        <v>3.63575315475464</v>
+        <v>3.63575291633606</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G384" t="n">
-        <v>3.64019274711609</v>
+        <v>3.64019250869751</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G385" t="n">
-        <v>3.60467863082886</v>
+        <v>3.60467839241028</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G389" t="n">
-        <v>3.64907097816467</v>
+        <v>3.64907121658325</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G391" t="n">
-        <v>3.90210843086243</v>
+        <v>3.90210890769958</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G392" t="n">
-        <v>3.75561332702637</v>
+        <v>3.75561308860779</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G393" t="n">
-        <v>3.62243556976318</v>
+        <v>3.6224353313446</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G396" t="n">
-        <v>3.56916451454163</v>
+        <v>3.56916427612305</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>3.5913610458374</v>
+        <v>3.59136080741882</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G401" t="n">
-        <v>3.57804298400879</v>
+        <v>3.57804322242737</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G403" t="n">
-        <v>3.56472516059875</v>
+        <v>3.56472492218018</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G405" t="n">
-        <v>3.53808927536011</v>
+        <v>3.53808975219727</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G410" t="n">
-        <v>3.60467863082886</v>
+        <v>3.60467839241028</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G414" t="n">
-        <v>3.60467863082886</v>
+        <v>3.60467839241028</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G417" t="n">
-        <v>3.64552783966064</v>
+        <v>3.64552760124207</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G420" t="n">
-        <v>3.654629945755</v>
+        <v>3.65462970733643</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G421" t="n">
-        <v>3.69559097290039</v>
+        <v>3.69559073448181</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G422" t="n">
-        <v>3.69559097290039</v>
+        <v>3.69559073448181</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G423" t="n">
-        <v>3.70014238357544</v>
+        <v>3.70014214515686</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G424" t="n">
-        <v>3.72289824485779</v>
+        <v>3.72289848327637</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>3.75020575523376</v>
+        <v>3.75020551681519</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G428" t="n">
-        <v>3.72289824485779</v>
+        <v>3.72289848327637</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G429" t="n">
-        <v>3.72289824485779</v>
+        <v>3.72289848327637</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G430" t="n">
-        <v>3.71379590034485</v>
+        <v>3.71379566192627</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>3.65918135643005</v>
+        <v>3.65918111801147</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G438" t="n">
-        <v>3.71379590034485</v>
+        <v>3.71379566192627</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G443" t="n">
-        <v>3.77751302719116</v>
+        <v>3.77751326560974</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G445" t="n">
-        <v>3.75020575523376</v>
+        <v>3.75020551681519</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G446" t="n">
-        <v>3.72289824485779</v>
+        <v>3.72289848327637</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G450" t="n">
-        <v>3.75020575523376</v>
+        <v>3.75020551681519</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>3.77751302719116</v>
+        <v>3.77751326560974</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G452" t="n">
-        <v>3.75020575523376</v>
+        <v>3.75020551681519</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>3.69559097290039</v>
+        <v>3.69559073448181</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G457" t="n">
-        <v>3.65918135643005</v>
+        <v>3.65918111801147</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G461" t="n">
-        <v>3.65918135643005</v>
+        <v>3.65918111801147</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>3.37700533866882</v>
+        <v>3.3770055770874</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>3.37700533866882</v>
+        <v>3.3770055770874</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.75</v>
       </c>
       <c r="G473" t="n">
-        <v>3.41341543197632</v>
+        <v>3.41341519355774</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G474" t="n">
-        <v>3.37700533866882</v>
+        <v>3.3770055770874</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>3.37700533866882</v>
+        <v>3.3770055770874</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>3.37700533866882</v>
+        <v>3.3770055770874</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G485" t="n">
-        <v>3.48623490333557</v>
+        <v>3.48623466491699</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G488" t="n">
-        <v>3.38610816001892</v>
+        <v>3.38610792160034</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>3.75</v>
       </c>
       <c r="G491" t="n">
-        <v>3.41341543197632</v>
+        <v>3.41341519355774</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>3.39521050453186</v>
+        <v>3.39521026611328</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G496" t="n">
-        <v>3.52264475822449</v>
+        <v>3.52264451980591</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G498" t="n">
-        <v>3.52264475822449</v>
+        <v>3.52264451980591</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G501" t="n">
-        <v>3.53174734115601</v>
+        <v>3.53174710273743</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G503" t="n">
-        <v>3.53174734115601</v>
+        <v>3.53174710273743</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G505" t="n">
-        <v>3.49533724784851</v>
+        <v>3.49533700942993</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>3.44982528686523</v>
+        <v>3.44982504844666</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>3.75</v>
       </c>
       <c r="G507" t="n">
-        <v>3.41341543197632</v>
+        <v>3.41341519355774</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G512" t="n">
-        <v>3.38610816001892</v>
+        <v>3.38610792160034</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>3.37700533866882</v>
+        <v>3.3770055770874</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G516" t="n">
-        <v>3.37700533866882</v>
+        <v>3.3770055770874</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G518" t="n">
-        <v>3.37700533866882</v>
+        <v>3.3770055770874</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G523" t="n">
-        <v>3.25867366790771</v>
+        <v>3.25867390632629</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G524" t="n">
-        <v>3.30418586730957</v>
+        <v>3.30418610572815</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G526" t="n">
-        <v>3.30418586730957</v>
+        <v>3.30418610572815</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G527" t="n">
-        <v>3.29508328437805</v>
+        <v>3.29508352279663</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>3.29508328437805</v>
+        <v>3.29508352279663</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G537" t="n">
-        <v>3.24046897888184</v>
+        <v>3.24046874046326</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G543" t="n">
-        <v>3.29508328437805</v>
+        <v>3.29508352279663</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G544" t="n">
-        <v>3.24957132339478</v>
+        <v>3.24957156181335</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G547" t="n">
-        <v>3.24957132339478</v>
+        <v>3.24957156181335</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G549" t="n">
-        <v>3.13123965263367</v>
+        <v>3.13123989105225</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G550" t="n">
-        <v>3.13123965263367</v>
+        <v>3.13123989105225</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G556" t="n">
-        <v>3.09482979774475</v>
+        <v>3.09483003616333</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G558" t="n">
-        <v>2.86726903915405</v>
+        <v>2.86726880073547</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G560" t="n">
-        <v>2.8126540184021</v>
+        <v>2.81265425682068</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>2.6397078037262</v>
+        <v>2.63970804214478</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.67611742019653</v>
+        <v>2.67611765861511</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>2.53958106040955</v>
+        <v>2.53958082199097</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.75</v>
       </c>
       <c r="G575" t="n">
-        <v>2.50317144393921</v>
+        <v>2.50317120552063</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>2.53958106040955</v>
+        <v>2.53958082199097</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.75</v>
       </c>
       <c r="G579" t="n">
-        <v>2.50317144393921</v>
+        <v>2.50317120552063</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G580" t="n">
-        <v>2.57599091529846</v>
+        <v>2.57599067687988</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>2.57599091529846</v>
+        <v>2.57599067687988</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>2.57599091529846</v>
+        <v>2.57599067687988</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.75</v>
       </c>
       <c r="G587" t="n">
-        <v>2.50317144393921</v>
+        <v>2.50317120552063</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>2.53958106040955</v>
+        <v>2.53958082199097</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G589" t="n">
-        <v>2.53958106040955</v>
+        <v>2.53958082199097</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>2.57599091529846</v>
+        <v>2.57599067687988</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>2.57599091529846</v>
+        <v>2.57599067687988</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>2.57599091529846</v>
+        <v>2.57599067687988</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G599" t="n">
-        <v>2.4121470451355</v>
+        <v>2.41214680671692</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G600" t="n">
-        <v>2.4121470451355</v>
+        <v>2.41214680671692</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G610" t="n">
-        <v>2.32112216949463</v>
+        <v>2.32112240791321</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G611" t="n">
-        <v>2.4121470451355</v>
+        <v>2.41214680671692</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G612" t="n">
-        <v>2.40304470062256</v>
+        <v>2.40304446220398</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G631" t="n">
-        <v>2.44855666160583</v>
+        <v>2.44855642318726</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G633" t="n">
-        <v>2.4121470451355</v>
+        <v>2.41214680671692</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G634" t="n">
-        <v>2.4121470451355</v>
+        <v>2.41214680671692</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G635" t="n">
-        <v>2.44855666160583</v>
+        <v>2.44855642318726</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G636" t="n">
-        <v>2.44855666160583</v>
+        <v>2.44855642318726</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G637" t="n">
-        <v>2.32112216949463</v>
+        <v>2.32112240791321</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G639" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G640" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>2.08445906639099</v>
+        <v>2.08445882797241</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G645" t="n">
-        <v>2.01163935661316</v>
+        <v>2.01163959503174</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>2.08445906639099</v>
+        <v>2.08445882797241</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>2.08445906639099</v>
+        <v>2.08445882797241</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G654" t="n">
-        <v>2.12086868286133</v>
+        <v>2.12086844444275</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.46676135063171</v>
+        <v>2.46676158905029</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G659" t="n">
-        <v>2.40304470062256</v>
+        <v>2.40304446220398</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G665" t="n">
-        <v>2.1754834651947</v>
+        <v>2.17548370361328</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G672" t="n">
-        <v>2.14817571640015</v>
+        <v>2.14817595481873</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G674" t="n">
-        <v>2.12997102737427</v>
+        <v>2.12997078895569</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>2.08445906639099</v>
+        <v>2.08445882797241</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>2.12086868286133</v>
+        <v>2.12086844444275</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>2.08445906639099</v>
+        <v>2.08445882797241</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>2.12086868286133</v>
+        <v>2.12086844444275</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G697" t="n">
-        <v>1.94792258739471</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G698" t="n">
-        <v>1.94792258739471</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G699" t="n">
-        <v>1.94792258739471</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G700" t="n">
-        <v>1.94792258739471</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G701" t="n">
-        <v>1.94792258739471</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>1.72491264343262</v>
+        <v>1.72491252422333</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G709" t="n">
-        <v>1.69760525226593</v>
+        <v>1.69760513305664</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G717" t="n">
-        <v>1.76132237911224</v>
+        <v>1.76132225990295</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G721" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G722" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G723" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G724" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G729" t="n">
-        <v>1.69305408000946</v>
+        <v>1.69305396080017</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G736" t="n">
-        <v>1.64754164218903</v>
+        <v>1.64754176139832</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G737" t="n">
-        <v>1.66574668884277</v>
+        <v>1.66574680805206</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G738" t="n">
-        <v>1.66574668884277</v>
+        <v>1.66574680805206</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G739" t="n">
-        <v>1.765873670578</v>
+        <v>1.76587355136871</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G740" t="n">
-        <v>2.12086868286133</v>
+        <v>2.12086844444275</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G743" t="n">
-        <v>1.92061507701874</v>
+        <v>1.92061483860016</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G749" t="n">
-        <v>1.92061507701874</v>
+        <v>1.92061483860016</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G750" t="n">
-        <v>1.91151261329651</v>
+        <v>1.91151237487793</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G751" t="n">
-        <v>1.92061507701874</v>
+        <v>1.92061483860016</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G752" t="n">
-        <v>1.91151261329651</v>
+        <v>1.91151237487793</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G759" t="n">
-        <v>1.94792258739471</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G763" t="n">
-        <v>2.13907337188721</v>
+        <v>2.13907361030579</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G764" t="n">
-        <v>2.14817571640015</v>
+        <v>2.14817595481873</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G765" t="n">
-        <v>2.14817571640015</v>
+        <v>2.14817595481873</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G775" t="n">
-        <v>2.12997102737427</v>
+        <v>2.12997078895569</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>2.01163935661316</v>
+        <v>2.01163959503174</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>2.01163935661316</v>
+        <v>2.01163959503174</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G800" t="n">
-        <v>1.95702493190765</v>
+        <v>1.95702469348907</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G801" t="n">
-        <v>1.85689795017242</v>
+        <v>1.85689783096313</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.85689795017242</v>
+        <v>1.85689783096313</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G810" t="n">
-        <v>1.8477954864502</v>
+        <v>1.84779536724091</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G812" t="n">
-        <v>1.87510287761688</v>
+        <v>1.87510275840759</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G813" t="n">
-        <v>1.8477954864502</v>
+        <v>1.84779536724091</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G815" t="n">
-        <v>1.82959067821503</v>
+        <v>1.82959055900574</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G816" t="n">
-        <v>1.82959067821503</v>
+        <v>1.82959055900574</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G819" t="n">
-        <v>1.82959067821503</v>
+        <v>1.82959055900574</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G820" t="n">
-        <v>1.7795273065567</v>
+        <v>1.77952718734741</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G821" t="n">
-        <v>1.765873670578</v>
+        <v>1.76587355136871</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G822" t="n">
-        <v>1.765873670578</v>
+        <v>1.76587355136871</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G823" t="n">
-        <v>1.765873670578</v>
+        <v>1.76587355136871</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G830" t="n">
-        <v>1.79318082332611</v>
+        <v>1.7931809425354</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.72491264343262</v>
+        <v>1.72491252422333</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1.875</v>
       </c>
       <c r="G834" t="n">
-        <v>1.70670771598816</v>
+        <v>1.70670759677887</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G837" t="n">
-        <v>1.66574668884277</v>
+        <v>1.66574680805206</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G838" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G851" t="n">
-        <v>1.81138563156128</v>
+        <v>1.81138575077057</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G852" t="n">
-        <v>1.81138563156128</v>
+        <v>1.81138575077057</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G856" t="n">
-        <v>1.76132237911224</v>
+        <v>1.76132225990295</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G857" t="n">
-        <v>1.76132237911224</v>
+        <v>1.76132225990295</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G858" t="n">
-        <v>1.765873670578</v>
+        <v>1.76587355136871</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G859" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G860" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G861" t="n">
-        <v>1.74311745166779</v>
+        <v>1.7431173324585</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G862" t="n">
-        <v>1.74311745166779</v>
+        <v>1.7431173324585</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.875</v>
       </c>
       <c r="G864" t="n">
-        <v>1.70670771598816</v>
+        <v>1.70670759677887</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>1.875</v>
       </c>
       <c r="G865" t="n">
-        <v>1.70670771598816</v>
+        <v>1.70670759677887</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G866" t="n">
-        <v>1.68850266933441</v>
+        <v>1.6885027885437</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G867" t="n">
-        <v>1.68850266933441</v>
+        <v>1.6885027885437</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G869" t="n">
-        <v>1.64754164218903</v>
+        <v>1.64754176139832</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G870" t="n">
-        <v>1.62023448944092</v>
+        <v>1.62023437023163</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G871" t="n">
-        <v>1.62023448944092</v>
+        <v>1.62023437023163</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G874" t="n">
-        <v>1.66574668884277</v>
+        <v>1.66574680805206</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>1.72491264343262</v>
+        <v>1.72491252422333</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G878" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G883" t="n">
-        <v>1.85689795017242</v>
+        <v>1.85689783096313</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G884" t="n">
-        <v>1.85689795017242</v>
+        <v>1.85689783096313</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>1.85689795017242</v>
+        <v>1.85689783096313</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G886" t="n">
-        <v>1.85689795017242</v>
+        <v>1.85689783096313</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G893" t="n">
-        <v>1.79318082332611</v>
+        <v>1.7931809425354</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G894" t="n">
-        <v>1.79318082332611</v>
+        <v>1.7931809425354</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G895" t="n">
-        <v>1.81138563156128</v>
+        <v>1.81138575077057</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G896" t="n">
-        <v>1.82959067821503</v>
+        <v>1.82959055900574</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G898" t="n">
-        <v>1.81138563156128</v>
+        <v>1.81138575077057</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G899" t="n">
-        <v>1.81138563156128</v>
+        <v>1.81138575077057</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G902" t="n">
-        <v>1.82959067821503</v>
+        <v>1.82959055900574</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G903" t="n">
-        <v>1.8477954864502</v>
+        <v>1.84779536724091</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G904" t="n">
-        <v>1.8477954864502</v>
+        <v>1.84779536724091</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G905" t="n">
-        <v>1.82959067821503</v>
+        <v>1.82959055900574</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G906" t="n">
-        <v>1.82959067821503</v>
+        <v>1.82959055900574</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>1.76132237911224</v>
+        <v>1.76132225990295</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G919" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G923" t="n">
-        <v>1.76132237911224</v>
+        <v>1.76132225990295</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G924" t="n">
-        <v>1.7795273065567</v>
+        <v>1.77952718734741</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G928" t="n">
-        <v>1.8477954864502</v>
+        <v>1.84779536724091</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G929" t="n">
-        <v>1.81138563156128</v>
+        <v>1.81138575077057</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G930" t="n">
-        <v>1.81138563156128</v>
+        <v>1.81138575077057</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G931" t="n">
-        <v>1.8477954864502</v>
+        <v>1.84779536724091</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G932" t="n">
-        <v>1.8477954864502</v>
+        <v>1.84779536724091</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G936" t="n">
-        <v>1.8477954864502</v>
+        <v>1.84779536724091</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G937" t="n">
-        <v>1.8477954864502</v>
+        <v>1.84779536724091</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>1.85689795017242</v>
+        <v>1.85689783096313</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G944" t="n">
-        <v>1.87510287761688</v>
+        <v>1.87510275840759</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G945" t="n">
-        <v>1.87510287761688</v>
+        <v>1.87510275840759</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G952" t="n">
-        <v>1.81138563156128</v>
+        <v>1.81138575077057</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G955" t="n">
-        <v>1.79318082332611</v>
+        <v>1.7931809425354</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G958" t="n">
-        <v>1.765873670578</v>
+        <v>1.76587355136871</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G964" t="n">
-        <v>1.765873670578</v>
+        <v>1.76587355136871</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G966" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G967" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G988" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G989" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G990" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G998" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G999" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.62191653251648</v>
+        <v>1.62191641330719</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.52594518661499</v>
+        <v>1.5259450674057</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.41077935695648</v>
+        <v>1.41077947616577</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.47795927524567</v>
+        <v>1.47795939445496</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.52594518661499</v>
+        <v>1.5259450674057</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.52594518661499</v>
+        <v>1.5259450674057</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.52594518661499</v>
+        <v>1.5259450674057</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.47795927524567</v>
+        <v>1.47795939445496</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.52594518661499</v>
+        <v>1.5259450674057</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.49715352058411</v>
+        <v>1.4971536397934</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.36279368400574</v>
+        <v>1.36279356479645</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.41077935695648</v>
+        <v>1.41077947616577</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.41077935695648</v>
+        <v>1.41077947616577</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.39158511161804</v>
+        <v>1.39158523082733</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.36279368400574</v>
+        <v>1.36279356479645</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.36279368400574</v>
+        <v>1.36279356479645</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.42997360229492</v>
+        <v>1.42997372150421</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.39158511161804</v>
+        <v>1.39158523082733</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.42997360229492</v>
+        <v>1.42997372150421</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.41077935695648</v>
+        <v>1.41077947616577</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.39158511161804</v>
+        <v>1.39158523082733</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.42997360229492</v>
+        <v>1.42997372150421</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.42997360229492</v>
+        <v>1.42997372150421</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.41077935695648</v>
+        <v>1.41077947616577</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.39158511161804</v>
+        <v>1.39158523082733</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.39158511161804</v>
+        <v>1.39158523082733</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.39158511161804</v>
+        <v>1.39158523082733</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.39158511161804</v>
+        <v>1.39158523082733</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.62191653251648</v>
+        <v>1.62191641330719</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1192" t="n">
-        <v>1.52594518661499</v>
+        <v>1.5259450674057</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.95781636238098</v>
+        <v>1.95781624317169</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.95781636238098</v>
+        <v>1.95781624317169</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.84265065193176</v>
+        <v>1.84265053272247</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1209" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.49715352058411</v>
+        <v>1.4971536397934</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1237" t="n">
-        <v>1.62191653251648</v>
+        <v>1.62191641330719</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1238" t="n">
-        <v>1.62191653251648</v>
+        <v>1.62191641330719</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.62191653251648</v>
+        <v>1.62191641330719</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.62191653251648</v>
+        <v>1.62191641330719</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.62191653251648</v>
+        <v>1.62191641330719</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.01539921760559</v>
+        <v>2.01539897918701</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.89063632488251</v>
+        <v>1.8906364440918</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.89063632488251</v>
+        <v>1.8906364440918</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1314" t="n">
-        <v>1.86184501647949</v>
+        <v>1.8618448972702</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.89063632488251</v>
+        <v>1.8906364440918</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -47614,6 +47614,32 @@
         <v>2.22000002861023</v>
       </c>
       <c r="H1817" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1818" t="n">
+        <v>85000</v>
+      </c>
+      <c r="C1818" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="D1818" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E1818" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F1818" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="G1818" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="H1818" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>1.30437564849854</v>
+        <v>1.30437552928925</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>1.50020003318787</v>
       </c>
       <c r="G3" t="n">
-        <v>1.31330490112305</v>
+        <v>1.31330502033234</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G5" t="n">
-        <v>1.62828099727631</v>
+        <v>1.62828087806702</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G6" t="n">
-        <v>1.62828099727631</v>
+        <v>1.62828087806702</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G7" t="n">
-        <v>1.58888709545135</v>
+        <v>1.58888697624207</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G8" t="n">
-        <v>1.63265812397003</v>
+        <v>1.63265788555145</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G9" t="n">
-        <v>1.72019994258881</v>
+        <v>1.7202000617981</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G10" t="n">
-        <v>1.87339854240417</v>
+        <v>1.87339842319489</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.18854951858521</v>
+        <v>2.18854975700378</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G13" t="n">
-        <v>3.17777419090271</v>
+        <v>3.17777395248413</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3.93938899040222</v>
+        <v>3.93938875198364</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3.93938899040222</v>
+        <v>3.93938875198364</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>3.8781099319458</v>
+        <v>3.87810969352722</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G21" t="n">
-        <v>3.52794218063354</v>
+        <v>3.52794241905212</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>3.57171273231506</v>
+        <v>3.57171297073364</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>3.43164587020874</v>
+        <v>3.43164563179016</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G25" t="n">
-        <v>3.55420446395874</v>
+        <v>3.55420470237732</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G29" t="n">
-        <v>3.51918768882751</v>
+        <v>3.51918792724609</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>3.53669619560242</v>
+        <v>3.536696434021</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>3.40976047515869</v>
+        <v>3.40976023674011</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G34" t="n">
-        <v>3.43164587020874</v>
+        <v>3.43164563179016</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G35" t="n">
-        <v>3.43164587020874</v>
+        <v>3.43164563179016</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G36" t="n">
-        <v>3.41413736343384</v>
+        <v>3.41413712501526</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G37" t="n">
-        <v>3.41413736343384</v>
+        <v>3.41413712501526</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>3.17777419090271</v>
+        <v>3.17777395248413</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G42" t="n">
-        <v>2.78383493423462</v>
+        <v>2.78383541107178</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G43" t="n">
-        <v>2.62188243865967</v>
+        <v>2.62188220024109</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G47" t="n">
-        <v>2.78821206092834</v>
+        <v>2.78821229934692</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G48" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>2.77945780754089</v>
+        <v>2.77945828437805</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G54" t="n">
-        <v>2.89763951301575</v>
+        <v>2.89763975143433</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>2.81009769439697</v>
+        <v>2.81009793281555</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G56" t="n">
-        <v>2.90639400482178</v>
+        <v>2.9063937664032</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G59" t="n">
-        <v>2.78383493423462</v>
+        <v>2.78383541107178</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.25</v>
       </c>
       <c r="G60" t="n">
-        <v>2.8451144695282</v>
+        <v>2.84511423110962</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G61" t="n">
-        <v>2.85824584960938</v>
+        <v>2.85824608802795</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G62" t="n">
-        <v>2.81009769439697</v>
+        <v>2.81009793281555</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.25</v>
       </c>
       <c r="G63" t="n">
-        <v>2.8451144695282</v>
+        <v>2.84511423110962</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G65" t="n">
-        <v>2.82322883605957</v>
+        <v>2.82322907447815</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G66" t="n">
-        <v>2.82322883605957</v>
+        <v>2.82322907447815</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>2.82322883605957</v>
+        <v>2.82322907447815</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>2.8276059627533</v>
+        <v>2.82760620117188</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>2.8276059627533</v>
+        <v>2.82760620117188</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>2.78821206092834</v>
+        <v>2.78821229934692</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>2.78383493423462</v>
+        <v>2.78383541107178</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G75" t="n">
-        <v>2.78821206092834</v>
+        <v>2.78821229934692</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G76" t="n">
-        <v>2.78383493423462</v>
+        <v>2.78383541107178</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>2.77945780754089</v>
+        <v>2.77945828437805</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>2.72693276405334</v>
+        <v>2.72693252563477</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.25</v>
       </c>
       <c r="G83" t="n">
-        <v>2.8451144695282</v>
+        <v>2.84511423110962</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G84" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G85" t="n">
-        <v>2.78821206092834</v>
+        <v>2.78821229934692</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.25</v>
       </c>
       <c r="G91" t="n">
-        <v>2.8451144695282</v>
+        <v>2.84511423110962</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G94" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G95" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>2.8276059627533</v>
+        <v>2.82760620117188</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G100" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G101" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G102" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G106" t="n">
-        <v>2.99831295013428</v>
+        <v>2.99831318855286</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.375</v>
       </c>
       <c r="G111" t="n">
-        <v>3.82996201515198</v>
+        <v>3.8299617767334</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G113" t="n">
-        <v>3.52794218063354</v>
+        <v>3.52794241905212</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G115" t="n">
-        <v>3.7730598449707</v>
+        <v>3.77305936813354</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>3.97878289222717</v>
+        <v>3.97878336906433</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>3.91312646865845</v>
+        <v>3.91312670707703</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>3.86060166358948</v>
+        <v>3.8606014251709</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>3.84746980667114</v>
+        <v>3.84747004508972</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G121" t="n">
-        <v>3.8912410736084</v>
+        <v>3.89124155044556</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G122" t="n">
-        <v>3.92625856399536</v>
+        <v>3.92625832557678</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G128" t="n">
-        <v>4.16699886322021</v>
+        <v>4.16699838638306</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G131" t="n">
-        <v>4.04006242752075</v>
+        <v>4.04006195068359</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G132" t="n">
-        <v>4.00504541397095</v>
+        <v>4.00504589080811</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.625</v>
       </c>
       <c r="G133" t="n">
-        <v>4.0488166809082</v>
+        <v>4.04881715774536</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G134" t="n">
-        <v>4.02693128585815</v>
+        <v>4.026930809021</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>3.9568977355957</v>
+        <v>3.95689725875854</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G137" t="n">
-        <v>3.98753690719604</v>
+        <v>3.98753714561462</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G138" t="n">
-        <v>3.99629163742065</v>
+        <v>3.99629235267639</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G139" t="n">
-        <v>4.21952438354492</v>
+        <v>4.21952390670776</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G140" t="n">
-        <v>4.13635921478271</v>
+        <v>4.13635873794556</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>4.19326066970825</v>
+        <v>4.19326114654541</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G142" t="n">
-        <v>4.32895088195801</v>
+        <v>4.32895183563232</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G146" t="n">
-        <v>4.38585329055786</v>
+        <v>4.38585376739502</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G147" t="n">
-        <v>4.25454044342041</v>
+        <v>4.25454092025757</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>3.85184717178345</v>
+        <v>3.85184693336487</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.625</v>
       </c>
       <c r="G149" t="n">
-        <v>4.0488166809082</v>
+        <v>4.04881715774536</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G150" t="n">
-        <v>3.78181409835815</v>
+        <v>3.781813621521</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G151" t="n">
-        <v>3.80369853973389</v>
+        <v>3.80369925498962</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G153" t="n">
-        <v>3.33097219467163</v>
+        <v>3.33097267150879</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>2.77508115768433</v>
+        <v>2.77508091926575</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G161" t="n">
-        <v>2.95891904830933</v>
+        <v>2.95891928672791</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G163" t="n">
-        <v>3.22154521942139</v>
+        <v>3.22154474258423</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G164" t="n">
-        <v>3.53669619560242</v>
+        <v>3.536696434021</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G165" t="n">
-        <v>3.58046746253967</v>
+        <v>3.58046722412109</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>3.62861514091492</v>
+        <v>3.6286153793335</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G171" t="n">
-        <v>3.73366594314575</v>
+        <v>3.73366570472717</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G172" t="n">
-        <v>3.68551731109619</v>
+        <v>3.68551778793335</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G173" t="n">
-        <v>3.95252084732056</v>
+        <v>3.95252060890198</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.85184717178345</v>
+        <v>3.85184693336487</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>4.07070207595825</v>
+        <v>4.07070255279541</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>4.07070207595825</v>
+        <v>4.07070255279541</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G179" t="n">
-        <v>3.70302557945251</v>
+        <v>3.70302605628967</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G180" t="n">
-        <v>3.83433938026428</v>
+        <v>3.83433866500854</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G181" t="n">
-        <v>3.8781099319458</v>
+        <v>3.87810969352722</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G182" t="n">
-        <v>3.70302557945251</v>
+        <v>3.70302605628967</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>3.80807590484619</v>
+        <v>3.80807614326477</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>3.85184717178345</v>
+        <v>3.85184693336487</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G185" t="n">
-        <v>3.79056787490845</v>
+        <v>3.79056763648987</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>3.86935591697693</v>
+        <v>3.86935567855835</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G187" t="n">
-        <v>3.86060166358948</v>
+        <v>3.8606014251709</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G190" t="n">
-        <v>3.78224849700928</v>
+        <v>3.78224897384644</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G193" t="n">
-        <v>3.66682815551758</v>
+        <v>3.66682839393616</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G195" t="n">
-        <v>3.78224849700928</v>
+        <v>3.78224897384644</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>3.7911274433136</v>
+        <v>3.79112720489502</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G198" t="n">
-        <v>3.91098713874817</v>
+        <v>3.91098809242249</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>4.5</v>
       </c>
       <c r="G199" t="n">
-        <v>3.99533343315125</v>
+        <v>3.99533295631409</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G200" t="n">
-        <v>3.86215567588806</v>
+        <v>3.8621551990509</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G201" t="n">
-        <v>3.83552026748657</v>
+        <v>3.83551979064941</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G203" t="n">
-        <v>3.71122050285339</v>
+        <v>3.71122074127197</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G206" t="n">
-        <v>3.80888414382935</v>
+        <v>3.80888438224792</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90654826164246</v>
+        <v>3.9065477848053</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>3.86215567588806</v>
+        <v>3.8621551990509</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>3.86215567588806</v>
+        <v>3.8621551990509</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G211" t="n">
-        <v>3.81776332855225</v>
+        <v>3.81776261329651</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>3.95981884002686</v>
+        <v>3.95981907844543</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>3.91986536979675</v>
+        <v>3.91986608505249</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>3.80888414382935</v>
+        <v>3.80888438224792</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G217" t="n">
-        <v>3.94206237792969</v>
+        <v>3.94206190109253</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G218" t="n">
-        <v>3.96425867080688</v>
+        <v>3.96425914764404</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>3.95094013214111</v>
+        <v>3.95094037055969</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>4.01752948760986</v>
+        <v>4.01752996444702</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G221" t="n">
-        <v>4.0486044883728</v>
+        <v>4.04860401153564</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G222" t="n">
-        <v>4.06636190414429</v>
+        <v>4.06636095046997</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G223" t="n">
-        <v>4.04416513442993</v>
+        <v>4.04416465759277</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G224" t="n">
-        <v>4.0486044883728</v>
+        <v>4.04860401153564</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>3.95981884002686</v>
+        <v>3.95981907844543</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G226" t="n">
-        <v>4.00421190261841</v>
+        <v>4.00421237945557</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>3.97313737869263</v>
+        <v>3.97313690185547</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.5</v>
       </c>
       <c r="G228" t="n">
-        <v>3.99533343315125</v>
+        <v>3.99533295631409</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G231" t="n">
-        <v>4.06636190414429</v>
+        <v>4.06636095046997</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.5</v>
       </c>
       <c r="G232" t="n">
-        <v>3.99533343315125</v>
+        <v>3.99533295631409</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G233" t="n">
-        <v>4.0486044883728</v>
+        <v>4.04860401153564</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G234" t="n">
-        <v>4.06636190414429</v>
+        <v>4.06636095046997</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G235" t="n">
-        <v>4.08411884307861</v>
+        <v>4.0841178894043</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.48365163803101</v>
+        <v>4.48365211486816</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>4.40374517440796</v>
+        <v>4.40374565124512</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G242" t="n">
-        <v>4.41262292861938</v>
+        <v>4.41262340545654</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>4.3105206489563</v>
+        <v>4.31052017211914</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>4.875</v>
       </c>
       <c r="G247" t="n">
-        <v>4.32827758789062</v>
+        <v>4.32827711105347</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>4.26168870925903</v>
+        <v>4.26168918609619</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G249" t="n">
-        <v>4.26168870925903</v>
+        <v>4.26168918609619</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G250" t="n">
-        <v>4.29720306396484</v>
+        <v>4.297203540802</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G253" t="n">
-        <v>3.86215567588806</v>
+        <v>3.8621551990509</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G254" t="n">
-        <v>3.88879132270813</v>
+        <v>3.88879084587097</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G255" t="n">
-        <v>3.96425867080688</v>
+        <v>3.96425914764404</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>4.06636190414429</v>
+        <v>4.06636095046997</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>4.2883243560791</v>
+        <v>4.28832387924194</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>4.15070676803589</v>
+        <v>4.15070772171021</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>4.1951003074646</v>
+        <v>4.19509983062744</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G261" t="n">
-        <v>4.09299755096436</v>
+        <v>4.0929970741272</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>4.04416513442993</v>
+        <v>4.04416465759277</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>4.08411884307861</v>
+        <v>4.0841178894043</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G269" t="n">
-        <v>3.94206237792969</v>
+        <v>3.94206190109253</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>3.90654826164246</v>
+        <v>3.9065477848053</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G271" t="n">
-        <v>3.95094013214111</v>
+        <v>3.95094037055969</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>3.95981884002686</v>
+        <v>3.95981907844543</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G274" t="n">
-        <v>3.95537996292114</v>
+        <v>3.95537972450256</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G276" t="n">
-        <v>3.84439849853516</v>
+        <v>3.84439826011658</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>3.84883737564087</v>
+        <v>3.84883785247803</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G278" t="n">
-        <v>3.84883737564087</v>
+        <v>3.84883785247803</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G279" t="n">
-        <v>3.81776332855225</v>
+        <v>3.81776261329651</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>3.81332397460938</v>
+        <v>3.8133237361908</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G283" t="n">
-        <v>3.81776332855225</v>
+        <v>3.81776261329651</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G284" t="n">
-        <v>3.80444526672363</v>
+        <v>3.80444502830505</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G290" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692169189453</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G291" t="n">
-        <v>3.71122050285339</v>
+        <v>3.71122074127197</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G292" t="n">
-        <v>3.80888414382935</v>
+        <v>3.80888438224792</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G294" t="n">
-        <v>3.81776332855225</v>
+        <v>3.81776261329651</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>3.69346380233765</v>
+        <v>3.69346356391907</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692169189453</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G303" t="n">
-        <v>3.63131403923035</v>
+        <v>3.63131427764893</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G307" t="n">
-        <v>3.6224353313446</v>
+        <v>3.62243556976318</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>3.60911774635315</v>
+        <v>3.60911798477173</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692169189453</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G312" t="n">
-        <v>3.46262240409851</v>
+        <v>3.46262192726135</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>3.41822957992554</v>
+        <v>3.41822934150696</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G314" t="n">
-        <v>3.41822957992554</v>
+        <v>3.41822934150696</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G316" t="n">
-        <v>3.43154716491699</v>
+        <v>3.43154740333557</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G318" t="n">
-        <v>3.19626665115356</v>
+        <v>3.19626641273499</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>3.19626665115356</v>
+        <v>3.19626641273499</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G321" t="n">
-        <v>3.09860277175903</v>
+        <v>3.09860301017761</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G322" t="n">
-        <v>3.16519165039062</v>
+        <v>3.16519212722778</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>3.19626665115356</v>
+        <v>3.19626641273499</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G327" t="n">
-        <v>3.19626665115356</v>
+        <v>3.19626641273499</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G328" t="n">
-        <v>3.29393029212952</v>
+        <v>3.29393005371094</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G331" t="n">
-        <v>3.4271080493927</v>
+        <v>3.42710781097412</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>3.46262240409851</v>
+        <v>3.46262192726135</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>3.46262240409851</v>
+        <v>3.46262192726135</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>3.38271546363831</v>
+        <v>3.38271522521973</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>3.43598651885986</v>
+        <v>3.43598628044128</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G338" t="n">
-        <v>3.37827610969543</v>
+        <v>3.37827634811401</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G340" t="n">
-        <v>3.81332397460938</v>
+        <v>3.8133237361908</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G343" t="n">
-        <v>3.58248209953308</v>
+        <v>3.5824818611145</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G347" t="n">
-        <v>3.81776332855225</v>
+        <v>3.81776261329651</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G351" t="n">
-        <v>3.95094013214111</v>
+        <v>3.95094037055969</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.5</v>
       </c>
       <c r="G356" t="n">
-        <v>3.99533343315125</v>
+        <v>3.99533295631409</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>3.97313737869263</v>
+        <v>3.97313690185547</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G359" t="n">
-        <v>3.90210890769958</v>
+        <v>3.90210866928101</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G360" t="n">
-        <v>3.90654826164246</v>
+        <v>3.9065477848053</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>3.96425867080688</v>
+        <v>3.96425914764404</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>3.92874431610107</v>
+        <v>3.92874479293823</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>3.98201608657837</v>
+        <v>3.98201584815979</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G364" t="n">
-        <v>3.96869707107544</v>
+        <v>3.9686975479126</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>3.96425867080688</v>
+        <v>3.96425914764404</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>3.97313737869263</v>
+        <v>3.97313690185547</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>3.8532772064209</v>
+        <v>3.85327696800232</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G371" t="n">
-        <v>3.76449131965637</v>
+        <v>3.76449155807495</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G372" t="n">
-        <v>3.73341727256775</v>
+        <v>3.73341703414917</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G373" t="n">
-        <v>3.71122050285339</v>
+        <v>3.71122074127197</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G374" t="n">
-        <v>3.76449131965637</v>
+        <v>3.76449155807495</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G375" t="n">
-        <v>3.71122050285339</v>
+        <v>3.71122074127197</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G376" t="n">
-        <v>3.76449131965637</v>
+        <v>3.76449155807495</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G378" t="n">
-        <v>3.63131403923035</v>
+        <v>3.63131427764893</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>3.5292112827301</v>
+        <v>3.52921080589294</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G383" t="n">
-        <v>3.63575291633606</v>
+        <v>3.63575315475464</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G386" t="n">
-        <v>3.63131403923035</v>
+        <v>3.63131427764893</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G387" t="n">
-        <v>3.63131403923035</v>
+        <v>3.63131427764893</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>3.7911274433136</v>
+        <v>3.79112720489502</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G391" t="n">
-        <v>3.90210890769958</v>
+        <v>3.90210866928101</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G392" t="n">
-        <v>3.75561308860779</v>
+        <v>3.75561332702637</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G393" t="n">
-        <v>3.6224353313446</v>
+        <v>3.62243556976318</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G396" t="n">
-        <v>3.56916427612305</v>
+        <v>3.56916451454163</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G397" t="n">
-        <v>3.61355710029602</v>
+        <v>3.6135573387146</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G400" t="n">
-        <v>3.58248209953308</v>
+        <v>3.5824818611145</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G403" t="n">
-        <v>3.56472492218018</v>
+        <v>3.56472516059875</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>3.60911774635315</v>
+        <v>3.60911798477173</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G405" t="n">
-        <v>3.53808975219727</v>
+        <v>3.53808951377869</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692169189453</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>3.6845850944519</v>
+        <v>3.68458533287048</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G411" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692169189453</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G412" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692169189453</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G415" t="n">
-        <v>3.60911774635315</v>
+        <v>3.60911798477173</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G420" t="n">
-        <v>3.65462970733643</v>
+        <v>3.654629945755</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G421" t="n">
-        <v>3.69559073448181</v>
+        <v>3.69559097290039</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G422" t="n">
-        <v>3.69559073448181</v>
+        <v>3.69559097290039</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G423" t="n">
-        <v>3.70014214515686</v>
+        <v>3.70014238357544</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>3.75020551681519</v>
+        <v>3.75020575523376</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G426" t="n">
-        <v>3.7593080997467</v>
+        <v>3.75930833816528</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G430" t="n">
-        <v>3.71379566192627</v>
+        <v>3.71379590034485</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G433" t="n">
-        <v>3.70469355583191</v>
+        <v>3.70469379425049</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>3.65918111801147</v>
+        <v>3.65918135643005</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G437" t="n">
-        <v>3.7593080997467</v>
+        <v>3.75930833816528</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G438" t="n">
-        <v>3.71379566192627</v>
+        <v>3.71379590034485</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G439" t="n">
-        <v>3.70469355583191</v>
+        <v>3.70469379425049</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G445" t="n">
-        <v>3.75020551681519</v>
+        <v>3.75020575523376</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G448" t="n">
-        <v>3.80482006072998</v>
+        <v>3.80482029914856</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G449" t="n">
-        <v>3.7593080997467</v>
+        <v>3.75930833816528</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G450" t="n">
-        <v>3.75020551681519</v>
+        <v>3.75020575523376</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G452" t="n">
-        <v>3.75020551681519</v>
+        <v>3.75020575523376</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G454" t="n">
-        <v>3.70469355583191</v>
+        <v>3.70469379425049</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>3.69559073448181</v>
+        <v>3.69559097290039</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G456" t="n">
-        <v>3.68648862838745</v>
+        <v>3.68648886680603</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G457" t="n">
-        <v>3.65918111801147</v>
+        <v>3.65918135643005</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>3.68648862838745</v>
+        <v>3.68648886680603</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G459" t="n">
-        <v>3.67738604545593</v>
+        <v>3.67738628387451</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G461" t="n">
-        <v>3.65918111801147</v>
+        <v>3.65918135643005</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G465" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G466" t="n">
-        <v>3.42251801490784</v>
+        <v>3.42251753807068</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G471" t="n">
-        <v>3.42251801490784</v>
+        <v>3.42251753807068</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G474" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G476" t="n">
-        <v>3.44072270393372</v>
+        <v>3.44072246551514</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>3.43162035942078</v>
+        <v>3.4316201210022</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>3.43162035942078</v>
+        <v>3.4316201210022</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G482" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G483" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G484" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G487" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G494" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G495" t="n">
-        <v>3.56815695762634</v>
+        <v>3.56815671920776</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G496" t="n">
-        <v>3.52264451980591</v>
+        <v>3.52264428138733</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G498" t="n">
-        <v>3.52264451980591</v>
+        <v>3.52264428138733</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G499" t="n">
-        <v>3.43162035942078</v>
+        <v>3.4316201210022</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>3.43162035942078</v>
+        <v>3.4316201210022</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G502" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G504" t="n">
-        <v>3.44072270393372</v>
+        <v>3.44072246551514</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>3.44982504844666</v>
+        <v>3.44982481002808</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G511" t="n">
-        <v>3.42251801490784</v>
+        <v>3.42251753807068</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G513" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G516" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G517" t="n">
-        <v>3.34969830513</v>
+        <v>3.34969806671143</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G518" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G519" t="n">
-        <v>3.31328868865967</v>
+        <v>3.31328845024109</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G520" t="n">
-        <v>3.31328868865967</v>
+        <v>3.31328845024109</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G521" t="n">
-        <v>3.28598093986511</v>
+        <v>3.28598117828369</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G524" t="n">
-        <v>3.30418610572815</v>
+        <v>3.30418586730957</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G525" t="n">
-        <v>3.31328868865967</v>
+        <v>3.31328845024109</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G526" t="n">
-        <v>3.30418610572815</v>
+        <v>3.30418586730957</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G527" t="n">
-        <v>3.29508352279663</v>
+        <v>3.29508328437805</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>3.29508352279663</v>
+        <v>3.29508328437805</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G529" t="n">
-        <v>3.31328868865967</v>
+        <v>3.31328845024109</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G530" t="n">
-        <v>3.28598093986511</v>
+        <v>3.28598117828369</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G531" t="n">
-        <v>3.28598093986511</v>
+        <v>3.28598117828369</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G533" t="n">
-        <v>3.32239103317261</v>
+        <v>3.32239079475403</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G534" t="n">
-        <v>3.28598093986511</v>
+        <v>3.28598117828369</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G537" t="n">
-        <v>3.24046874046326</v>
+        <v>3.24046897888184</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G539" t="n">
-        <v>3.1949565410614</v>
+        <v>3.19495677947998</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>3.5</v>
       </c>
       <c r="G541" t="n">
-        <v>3.18585419654846</v>
+        <v>3.18585443496704</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G542" t="n">
-        <v>3.1949565410614</v>
+        <v>3.19495677947998</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G543" t="n">
-        <v>3.29508352279663</v>
+        <v>3.29508328437805</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G544" t="n">
-        <v>3.24957156181335</v>
+        <v>3.24957132339478</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G547" t="n">
-        <v>3.24957156181335</v>
+        <v>3.24957132339478</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G548" t="n">
-        <v>3.1949565410614</v>
+        <v>3.19495677947998</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G549" t="n">
-        <v>3.13123989105225</v>
+        <v>3.13123965263367</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G550" t="n">
-        <v>3.13123989105225</v>
+        <v>3.13123965263367</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G555" t="n">
-        <v>3.15854692459106</v>
+        <v>3.15854716300964</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G558" t="n">
-        <v>2.86726880073547</v>
+        <v>2.86726903915405</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G560" t="n">
-        <v>2.81265425682068</v>
+        <v>2.8126540184021</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>2.63970804214478</v>
+        <v>2.6397078037262</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G565" t="n">
-        <v>2.66701507568359</v>
+        <v>2.66701531410217</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G572" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.75</v>
       </c>
       <c r="G575" t="n">
-        <v>2.50317120552063</v>
+        <v>2.50317144393921</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.75</v>
       </c>
       <c r="G579" t="n">
-        <v>2.50317120552063</v>
+        <v>2.50317144393921</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G584" t="n">
-        <v>2.53047847747803</v>
+        <v>2.53047871589661</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G586" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.75</v>
       </c>
       <c r="G587" t="n">
-        <v>2.50317120552063</v>
+        <v>2.50317144393921</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G589" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G592" t="n">
-        <v>2.45765900611877</v>
+        <v>2.45765924453735</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G593" t="n">
-        <v>2.52137613296509</v>
+        <v>2.52137637138367</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G599" t="n">
-        <v>2.41214680671692</v>
+        <v>2.4121470451355</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G600" t="n">
-        <v>2.41214680671692</v>
+        <v>2.4121470451355</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.35753202438354</v>
+        <v>2.35753226280212</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G604" t="n">
-        <v>2.35753202438354</v>
+        <v>2.35753226280212</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G607" t="n">
-        <v>2.33022475242615</v>
+        <v>2.33022499084473</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G608" t="n">
-        <v>2.33022475242615</v>
+        <v>2.33022499084473</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G609" t="n">
-        <v>2.24830269813538</v>
+        <v>2.24830293655396</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G611" t="n">
-        <v>2.41214680671692</v>
+        <v>2.4121470451355</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G612" t="n">
-        <v>2.40304446220398</v>
+        <v>2.40304470062256</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G613" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G615" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G616" t="n">
-        <v>2.52137613296509</v>
+        <v>2.52137637138367</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G617" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G618" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>2.34842967987061</v>
+        <v>2.34842991828918</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G625" t="n">
-        <v>2.34842967987061</v>
+        <v>2.34842991828918</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G626" t="n">
-        <v>2.34842967987061</v>
+        <v>2.34842991828918</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G630" t="n">
-        <v>2.45765900611877</v>
+        <v>2.45765924453735</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G631" t="n">
-        <v>2.44855642318726</v>
+        <v>2.44855690002441</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G633" t="n">
-        <v>2.41214680671692</v>
+        <v>2.4121470451355</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G634" t="n">
-        <v>2.41214680671692</v>
+        <v>2.4121470451355</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G635" t="n">
-        <v>2.44855642318726</v>
+        <v>2.44855690002441</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G636" t="n">
-        <v>2.44855642318726</v>
+        <v>2.44855690002441</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G638" t="n">
-        <v>2.25740528106689</v>
+        <v>2.25740551948547</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G644" t="n">
-        <v>2.05715179443359</v>
+        <v>2.05715155601501</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G645" t="n">
-        <v>2.01163959503174</v>
+        <v>2.01163935661316</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G648" t="n">
-        <v>2.16638112068176</v>
+        <v>2.16638088226318</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G649" t="n">
-        <v>2.07535648345947</v>
+        <v>2.07535624504089</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G650" t="n">
-        <v>2.09356141090393</v>
+        <v>2.09356117248535</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G657" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G659" t="n">
-        <v>2.40304446220398</v>
+        <v>2.40304470062256</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>2.2027907371521</v>
+        <v>2.20279097557068</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G664" t="n">
-        <v>2.25740528106689</v>
+        <v>2.25740551948547</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G665" t="n">
-        <v>2.17548370361328</v>
+        <v>2.1754834651947</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G667" t="n">
-        <v>2.21189308166504</v>
+        <v>2.21189332008362</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G668" t="n">
-        <v>2.21189308166504</v>
+        <v>2.21189332008362</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G669" t="n">
-        <v>2.16638112068176</v>
+        <v>2.16638088226318</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G672" t="n">
-        <v>2.14817595481873</v>
+        <v>2.14817571640015</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G674" t="n">
-        <v>2.12997078895569</v>
+        <v>2.12997102737427</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.25</v>
       </c>
       <c r="G678" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G680" t="n">
-        <v>2.07535648345947</v>
+        <v>2.07535624504089</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G682" t="n">
-        <v>2.05715179443359</v>
+        <v>2.05715155601501</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>2.25</v>
       </c>
       <c r="G683" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G685" t="n">
-        <v>2.05715179443359</v>
+        <v>2.05715155601501</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.25</v>
       </c>
       <c r="G688" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G690" t="n">
-        <v>2.00253701210022</v>
+        <v>2.00253677368164</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G691" t="n">
-        <v>1.96612727642059</v>
+        <v>1.9661271572113</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G692" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G693" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G694" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G695" t="n">
-        <v>1.98433232307434</v>
+        <v>1.98433196544647</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G696" t="n">
-        <v>2.00253701210022</v>
+        <v>2.00253677368164</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G702" t="n">
-        <v>1.92971742153168</v>
+        <v>1.92971730232239</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G703" t="n">
-        <v>1.90241003036499</v>
+        <v>1.90241014957428</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G704" t="n">
-        <v>1.90241003036499</v>
+        <v>1.90241014957428</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G707" t="n">
-        <v>1.674849152565</v>
+        <v>1.67484903335571</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>1.72491252422333</v>
+        <v>1.72491240501404</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G710" t="n">
-        <v>1.73856616020203</v>
+        <v>1.73856604099274</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G711" t="n">
-        <v>1.77497601509094</v>
+        <v>1.77497589588165</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G712" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G713" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G714" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G716" t="n">
-        <v>1.73856616020203</v>
+        <v>1.73856604099274</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G717" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132214069366</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G718" t="n">
-        <v>1.73856616020203</v>
+        <v>1.73856604099274</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G719" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G720" t="n">
-        <v>1.71125900745392</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G725" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G726" t="n">
-        <v>1.71125900745392</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G727" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G728" t="n">
-        <v>1.72036135196686</v>
+        <v>1.72036123275757</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G730" t="n">
-        <v>1.65664434432983</v>
+        <v>1.65664422512054</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G736" t="n">
-        <v>1.64754176139832</v>
+        <v>1.64754164218903</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G737" t="n">
-        <v>1.66574680805206</v>
+        <v>1.66574668884277</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G738" t="n">
-        <v>1.66574680805206</v>
+        <v>1.66574668884277</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G744" t="n">
-        <v>1.96612727642059</v>
+        <v>1.9661271572113</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G745" t="n">
-        <v>1.98433232307434</v>
+        <v>1.98433196544647</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G746" t="n">
-        <v>1.92971742153168</v>
+        <v>1.92971730232239</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G747" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G748" t="n">
-        <v>1.97522974014282</v>
+        <v>1.97522962093353</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G750" t="n">
-        <v>1.91151237487793</v>
+        <v>1.91151261329651</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G752" t="n">
-        <v>1.91151237487793</v>
+        <v>1.91151261329651</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G755" t="n">
-        <v>1.90241003036499</v>
+        <v>1.90241014957428</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G756" t="n">
-        <v>1.92971742153168</v>
+        <v>1.92971730232239</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G757" t="n">
-        <v>1.90241003036499</v>
+        <v>1.90241014957428</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G758" t="n">
-        <v>1.92971742153168</v>
+        <v>1.92971730232239</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G762" t="n">
-        <v>2.24830269813538</v>
+        <v>2.24830293655396</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G763" t="n">
-        <v>2.13907361030579</v>
+        <v>2.13907337188721</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G764" t="n">
-        <v>2.14817595481873</v>
+        <v>2.14817571640015</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G765" t="n">
-        <v>2.14817595481873</v>
+        <v>2.14817571640015</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G766" t="n">
-        <v>2.09356141090393</v>
+        <v>2.09356117248535</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>2.09356141090393</v>
+        <v>2.09356117248535</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>2.25</v>
       </c>
       <c r="G768" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>2.25</v>
       </c>
       <c r="G769" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G770" t="n">
-        <v>2.00253701210022</v>
+        <v>2.00253677368164</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G771" t="n">
-        <v>2.00253701210022</v>
+        <v>2.00253677368164</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G772" t="n">
-        <v>2.05715179443359</v>
+        <v>2.05715155601501</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G773" t="n">
-        <v>2.05715179443359</v>
+        <v>2.05715155601501</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G774" t="n">
-        <v>2.05715179443359</v>
+        <v>2.05715155601501</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G775" t="n">
-        <v>2.12997078895569</v>
+        <v>2.12997102737427</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>2.09356141090393</v>
+        <v>2.09356117248535</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G779" t="n">
-        <v>2.06625413894653</v>
+        <v>2.06625390052795</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G780" t="n">
-        <v>2.06625413894653</v>
+        <v>2.06625390052795</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G781" t="n">
-        <v>2.06625413894653</v>
+        <v>2.06625390052795</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G791" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>2.01163959503174</v>
+        <v>2.01163935661316</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>2.01163959503174</v>
+        <v>2.01163935661316</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.25</v>
       </c>
       <c r="G795" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>2.25</v>
       </c>
       <c r="G796" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.25</v>
       </c>
       <c r="G797" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G799" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G801" t="n">
-        <v>1.85689783096313</v>
+        <v>1.85689795017242</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.85689783096313</v>
+        <v>1.85689795017242</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G808" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G809" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G810" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G812" t="n">
-        <v>1.87510275840759</v>
+        <v>1.87510287761688</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G813" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G815" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G816" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G818" t="n">
-        <v>1.90241003036499</v>
+        <v>1.90241014957428</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G819" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G826" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G830" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G831" t="n">
-        <v>1.77042484283447</v>
+        <v>1.77042472362518</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G832" t="n">
-        <v>1.71125900745392</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.72491252422333</v>
+        <v>1.72491240501404</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G837" t="n">
-        <v>1.66574680805206</v>
+        <v>1.66574668884277</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G839" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G840" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G841" t="n">
-        <v>1.71125900745392</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G842" t="n">
-        <v>1.71125900745392</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G843" t="n">
-        <v>1.71125900745392</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G844" t="n">
-        <v>1.71125900745392</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G845" t="n">
-        <v>1.71125900745392</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G849" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G850" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G855" t="n">
-        <v>1.77042484283447</v>
+        <v>1.77042472362518</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G856" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132214069366</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G857" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132214069366</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G863" t="n">
-        <v>1.73401498794556</v>
+        <v>1.73401486873627</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G866" t="n">
-        <v>1.6885027885437</v>
+        <v>1.68850266933441</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G867" t="n">
-        <v>1.6885027885437</v>
+        <v>1.68850266933441</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G868" t="n">
-        <v>1.674849152565</v>
+        <v>1.67484903335571</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G869" t="n">
-        <v>1.64754176139832</v>
+        <v>1.64754164218903</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G870" t="n">
-        <v>1.62023437023163</v>
+        <v>1.62023448944092</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G871" t="n">
-        <v>1.62023437023163</v>
+        <v>1.62023448944092</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G872" t="n">
-        <v>1.6611955165863</v>
+        <v>1.66119539737701</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G873" t="n">
-        <v>1.6611955165863</v>
+        <v>1.66119539737701</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G874" t="n">
-        <v>1.66574680805206</v>
+        <v>1.66574668884277</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>1.72491252422333</v>
+        <v>1.72491240501404</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G876" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G879" t="n">
-        <v>1.79773211479187</v>
+        <v>1.79773199558258</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G880" t="n">
-        <v>1.79773211479187</v>
+        <v>1.79773199558258</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G881" t="n">
-        <v>1.79773211479187</v>
+        <v>1.79773199558258</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G882" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G883" t="n">
-        <v>1.85689783096313</v>
+        <v>1.85689795017242</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G884" t="n">
-        <v>1.85689783096313</v>
+        <v>1.85689795017242</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>1.85689783096313</v>
+        <v>1.85689795017242</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G886" t="n">
-        <v>1.85689783096313</v>
+        <v>1.85689795017242</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G887" t="n">
-        <v>1.88420534133911</v>
+        <v>1.88420522212982</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G888" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G890" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G893" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G894" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G896" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G902" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G903" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G904" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G905" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G906" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G911" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G912" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G913" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132214069366</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G921" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G922" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G923" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132214069366</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G928" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G931" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G932" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G936" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G937" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G938" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>1.85689783096313</v>
+        <v>1.85689795017242</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G940" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G942" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G943" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G944" t="n">
-        <v>1.87510275840759</v>
+        <v>1.87510287761688</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G945" t="n">
-        <v>1.87510275840759</v>
+        <v>1.87510287761688</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G946" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G947" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G948" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G954" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G955" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G956" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G959" t="n">
-        <v>1.72036135196686</v>
+        <v>1.72036123275757</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G960" t="n">
-        <v>1.72036135196686</v>
+        <v>1.72036123275757</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G961" t="n">
-        <v>1.72036135196686</v>
+        <v>1.72036123275757</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G962" t="n">
-        <v>1.72036135196686</v>
+        <v>1.72036123275757</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G963" t="n">
-        <v>1.72036135196686</v>
+        <v>1.72036123275757</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G966" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G967" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G988" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G989" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G990" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G998" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G999" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.47795939445496</v>
+        <v>1.47795927524567</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.47795939445496</v>
+        <v>1.47795927524567</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.4971536397934</v>
+        <v>1.49715352058411</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.36279356479645</v>
+        <v>1.36279368400574</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.36279356479645</v>
+        <v>1.36279368400574</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.36279356479645</v>
+        <v>1.36279368400574</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.42997372150421</v>
+        <v>1.42997360229492</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.42997372150421</v>
+        <v>1.42997360229492</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.42997372150421</v>
+        <v>1.42997360229492</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.42997372150421</v>
+        <v>1.42997360229492</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1192" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.95781624317169</v>
+        <v>1.95781636238098</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.95781624317169</v>
+        <v>1.95781636238098</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.84265053272247</v>
+        <v>1.84265065193176</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1209" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.4971536397934</v>
+        <v>1.49715352058411</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1237" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1238" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.01539897918701</v>
+        <v>2.01539921760559</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.8906364440918</v>
+        <v>1.89063632488251</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.8906364440918</v>
+        <v>1.89063632488251</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1314" t="n">
-        <v>1.8618448972702</v>
+        <v>1.86184501647949</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.8906364440918</v>
+        <v>1.89063632488251</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -47640,6 +47640,32 @@
         <v>2.35999989509583</v>
       </c>
       <c r="H1818" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1819" t="n">
+        <v>55000</v>
+      </c>
+      <c r="C1819" t="n">
+        <v>2.42000007629395</v>
+      </c>
+      <c r="D1819" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="E1819" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="F1819" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="G1819" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="H1819" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>1.30437552928925</v>
+        <v>1.30437564849854</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G5" t="n">
-        <v>1.62828099727631</v>
+        <v>1.62828075885773</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G6" t="n">
-        <v>1.62828099727631</v>
+        <v>1.62828075885773</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G7" t="n">
-        <v>1.58888697624207</v>
+        <v>1.58888709545135</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G8" t="n">
-        <v>1.63265812397003</v>
+        <v>1.63265800476074</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G9" t="n">
-        <v>1.72020018100739</v>
+        <v>1.72019994258881</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G13" t="n">
-        <v>3.17777395248413</v>
+        <v>3.17777419090271</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3.9393892288208</v>
+        <v>3.93938970565796</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3.9393892288208</v>
+        <v>3.93938970565796</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G20" t="n">
-        <v>3.66800928115845</v>
+        <v>3.66800951957703</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>3.57171297073364</v>
+        <v>3.57171273231506</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>3.43164587020874</v>
+        <v>3.43164563179016</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G25" t="n">
-        <v>3.55420422554016</v>
+        <v>3.55420470237732</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G27" t="n">
-        <v>3.51043343544006</v>
+        <v>3.51043391227722</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G29" t="n">
-        <v>3.51918768882751</v>
+        <v>3.51918745040894</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>3.53669619560242</v>
+        <v>3.536696434021</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G32" t="n">
-        <v>3.45353126525879</v>
+        <v>3.45353102684021</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>3.40976023674011</v>
+        <v>3.40976047515869</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G34" t="n">
-        <v>3.43164587020874</v>
+        <v>3.43164563179016</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G35" t="n">
-        <v>3.43164587020874</v>
+        <v>3.43164563179016</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.75</v>
       </c>
       <c r="G38" t="n">
-        <v>3.28282451629639</v>
+        <v>3.28282427787781</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>3.28720164299011</v>
+        <v>3.28720188140869</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>3.17777395248413</v>
+        <v>3.17777419090271</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G41" t="n">
-        <v>2.9370334148407</v>
+        <v>2.93703365325928</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G45" t="n">
-        <v>2.98518180847168</v>
+        <v>2.98518204689026</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G46" t="n">
-        <v>2.98080444335938</v>
+        <v>2.98080468177795</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G47" t="n">
-        <v>2.78821206092834</v>
+        <v>2.78821229934692</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G48" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>2.73130989074707</v>
+        <v>2.73130965232849</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G50" t="n">
-        <v>2.74881839752197</v>
+        <v>2.74881863594055</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>2.77945780754089</v>
+        <v>2.77945804595947</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.125</v>
       </c>
       <c r="G52" t="n">
-        <v>2.7356870174408</v>
+        <v>2.73568725585938</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>2.81009769439697</v>
+        <v>2.81009793281555</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.25</v>
       </c>
       <c r="G60" t="n">
-        <v>2.8451144695282</v>
+        <v>2.84511470794678</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G61" t="n">
-        <v>2.85824584960938</v>
+        <v>2.85824608802795</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G62" t="n">
-        <v>2.81009769439697</v>
+        <v>2.81009793281555</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.25</v>
       </c>
       <c r="G63" t="n">
-        <v>2.8451144695282</v>
+        <v>2.84511470794678</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G64" t="n">
-        <v>2.84073710441589</v>
+        <v>2.84073734283447</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G65" t="n">
-        <v>2.82322859764099</v>
+        <v>2.82322907447815</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G66" t="n">
-        <v>2.82322859764099</v>
+        <v>2.82322907447815</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>2.82322859764099</v>
+        <v>2.82322907447815</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>2.78821206092834</v>
+        <v>2.78821229934692</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G73" t="n">
-        <v>2.87137699127197</v>
+        <v>2.87137722969055</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G74" t="n">
-        <v>2.8494918346405</v>
+        <v>2.84949159622192</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G75" t="n">
-        <v>2.78821206092834</v>
+        <v>2.78821229934692</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>2.77945780754089</v>
+        <v>2.77945804595947</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>2.7707040309906</v>
+        <v>2.77070379257202</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>2.72693300247192</v>
+        <v>2.72693276405334</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G82" t="n">
-        <v>2.7400643825531</v>
+        <v>2.74006414413452</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.25</v>
       </c>
       <c r="G83" t="n">
-        <v>2.8451144695282</v>
+        <v>2.84511470794678</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G84" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G85" t="n">
-        <v>2.78821206092834</v>
+        <v>2.78821229934692</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>2.84073710441589</v>
+        <v>2.84073734283447</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.25</v>
       </c>
       <c r="G91" t="n">
-        <v>2.8451144695282</v>
+        <v>2.84511470794678</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G92" t="n">
-        <v>2.87137699127197</v>
+        <v>2.87137722969055</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G94" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G95" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.86699986457825</v>
+        <v>2.86700010299683</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G100" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G101" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G102" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G106" t="n">
-        <v>2.9983127117157</v>
+        <v>2.99831318855286</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>4.39460754394531</v>
+        <v>4.39460802078247</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G109" t="n">
-        <v>3.96565198898315</v>
+        <v>3.96565246582031</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>4.11447286605835</v>
+        <v>4.11447334289551</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.375</v>
       </c>
       <c r="G111" t="n">
-        <v>3.8299617767334</v>
+        <v>3.82996129989624</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G115" t="n">
-        <v>3.77305936813354</v>
+        <v>3.77305912971497</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>3.97878360748291</v>
+        <v>3.97878289222717</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>3.91312646865845</v>
+        <v>3.91312623023987</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>3.8606014251709</v>
+        <v>3.86060118675232</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G119" t="n">
-        <v>3.79932260513306</v>
+        <v>3.7993221282959</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>3.84747004508972</v>
+        <v>3.84747052192688</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G121" t="n">
-        <v>3.89124155044556</v>
+        <v>3.89124131202698</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G124" t="n">
-        <v>4.1713752746582</v>
+        <v>4.17137575149536</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>4.1801290512085</v>
+        <v>4.18012952804565</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>4.28518056869507</v>
+        <v>4.28518009185791</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G128" t="n">
-        <v>4.16699838638306</v>
+        <v>4.16699886322021</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G129" t="n">
-        <v>4.06194829940796</v>
+        <v>4.0619478225708</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>3.97002911567688</v>
+        <v>3.97002863883972</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G131" t="n">
-        <v>4.04006242752075</v>
+        <v>4.04006290435791</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.625</v>
       </c>
       <c r="G133" t="n">
-        <v>4.04881715774536</v>
+        <v>4.0488166809082</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>3.95689797401428</v>
+        <v>3.9568977355957</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G137" t="n">
-        <v>3.98753690719604</v>
+        <v>3.98753714561462</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G138" t="n">
-        <v>3.99629235267639</v>
+        <v>3.99629139900208</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G139" t="n">
-        <v>4.21952342987061</v>
+        <v>4.21952390670776</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G143" t="n">
-        <v>5.16497707366943</v>
+        <v>5.16497659683228</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G144" t="n">
-        <v>4.76228475570679</v>
+        <v>4.76228380203247</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G145" t="n">
-        <v>4.46464061737061</v>
+        <v>4.46464157104492</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G146" t="n">
-        <v>4.38585376739502</v>
+        <v>4.38585329055786</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>3.85184717178345</v>
+        <v>3.85184741020203</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.625</v>
       </c>
       <c r="G149" t="n">
-        <v>4.04881715774536</v>
+        <v>4.0488166809082</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G151" t="n">
-        <v>3.80369925498962</v>
+        <v>3.80369901657104</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>3.79932260513306</v>
+        <v>3.7993221282959</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G154" t="n">
-        <v>3.08147788047791</v>
+        <v>3.08147764205933</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G155" t="n">
-        <v>3.19965934753418</v>
+        <v>3.19965958595276</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G156" t="n">
-        <v>2.72255563735962</v>
+        <v>2.7225558757782</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>2.73130989074707</v>
+        <v>2.73130965232849</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G162" t="n">
-        <v>3.08147788047791</v>
+        <v>3.08147764205933</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G163" t="n">
-        <v>3.22154498100281</v>
+        <v>3.22154521942139</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G164" t="n">
-        <v>3.53669619560242</v>
+        <v>3.536696434021</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G167" t="n">
-        <v>3.71178007125854</v>
+        <v>3.71177959442139</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G169" t="n">
-        <v>3.60672998428345</v>
+        <v>3.60672950744629</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>3.66800928115845</v>
+        <v>3.66800951957703</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G172" t="n">
-        <v>3.68551754951477</v>
+        <v>3.68551731109619</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G173" t="n">
-        <v>3.95252084732056</v>
+        <v>3.95252060890198</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.85184717178345</v>
+        <v>3.85184741020203</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G175" t="n">
-        <v>3.94376659393311</v>
+        <v>3.94376635551453</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>4.07070207595825</v>
+        <v>4.07070302963257</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>4.07070207595825</v>
+        <v>4.07070302963257</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>3.68114018440247</v>
+        <v>3.68114042282104</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>3.80807614326477</v>
+        <v>3.80807638168335</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>3.85184717178345</v>
+        <v>3.85184741020203</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G185" t="n">
-        <v>3.79056763648987</v>
+        <v>3.79056787490845</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>3.86935615539551</v>
+        <v>3.86935591697693</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G187" t="n">
-        <v>3.8606014251709</v>
+        <v>3.86060118675232</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>3.77743697166443</v>
+        <v>3.77743649482727</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G189" t="n">
-        <v>3.75117421150208</v>
+        <v>3.75117373466492</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G190" t="n">
-        <v>3.78224921226501</v>
+        <v>3.78224897384644</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G194" t="n">
-        <v>3.74673461914062</v>
+        <v>3.7467348575592</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G195" t="n">
-        <v>3.78224921226501</v>
+        <v>3.78224897384644</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>4.25</v>
       </c>
       <c r="G196" t="n">
-        <v>3.77337002754211</v>
+        <v>3.77337026596069</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G198" t="n">
-        <v>3.91098809242249</v>
+        <v>3.91098761558533</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G201" t="n">
-        <v>3.83552026748657</v>
+        <v>3.83552002906799</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>3.8310809135437</v>
+        <v>3.83108067512512</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G203" t="n">
-        <v>3.71122074127197</v>
+        <v>3.71122050285339</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G204" t="n">
-        <v>3.82220220565796</v>
+        <v>3.82220244407654</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G205" t="n">
-        <v>3.82220220565796</v>
+        <v>3.82220244407654</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G206" t="n">
-        <v>3.80888438224792</v>
+        <v>3.80888414382935</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>3.95981955528259</v>
+        <v>3.95981907844543</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>3.80888438224792</v>
+        <v>3.80888414382935</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>3.95981955528259</v>
+        <v>3.95981907844543</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G226" t="n">
-        <v>4.00421237945557</v>
+        <v>4.00421190261841</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>3.97313690185547</v>
+        <v>3.97313666343689</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G236" t="n">
-        <v>4.10187578201294</v>
+        <v>4.10187530517578</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.48365211486816</v>
+        <v>4.48365163803101</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>4.875</v>
       </c>
       <c r="G247" t="n">
-        <v>4.32827758789062</v>
+        <v>4.32827806472778</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G252" t="n">
-        <v>4.02196884155273</v>
+        <v>4.02196836471558</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G264" t="n">
-        <v>4.05748319625854</v>
+        <v>4.05748271942139</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G268" t="n">
-        <v>4.05748319625854</v>
+        <v>4.05748271942139</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>3.95981955528259</v>
+        <v>3.95981907844543</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G276" t="n">
-        <v>3.84439826011658</v>
+        <v>3.84439849853516</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>4.25</v>
       </c>
       <c r="G280" t="n">
-        <v>3.77337002754211</v>
+        <v>3.77337026596069</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>4.25</v>
       </c>
       <c r="G281" t="n">
-        <v>3.77337002754211</v>
+        <v>3.77337026596069</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G284" t="n">
-        <v>3.80444526672363</v>
+        <v>3.80444502830505</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>4.25</v>
       </c>
       <c r="G285" t="n">
-        <v>3.77337002754211</v>
+        <v>3.77337026596069</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G288" t="n">
-        <v>3.74673461914062</v>
+        <v>3.7467348575592</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G289" t="n">
-        <v>3.74673461914062</v>
+        <v>3.7467348575592</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G291" t="n">
-        <v>3.71122074127197</v>
+        <v>3.71122050285339</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G292" t="n">
-        <v>3.80888438224792</v>
+        <v>3.80888414382935</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G293" t="n">
-        <v>3.82220220565796</v>
+        <v>3.82220244407654</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>3.69790267944336</v>
+        <v>3.69790291786194</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G297" t="n">
-        <v>3.72453856468201</v>
+        <v>3.72453880310059</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G306" t="n">
-        <v>3.57804298400879</v>
+        <v>3.57804322242737</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>3.41822957992554</v>
+        <v>3.41822934150696</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G314" t="n">
-        <v>3.41822957992554</v>
+        <v>3.41822934150696</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G317" t="n">
-        <v>3.2317807674408</v>
+        <v>3.23178100585938</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G322" t="n">
-        <v>3.16519212722778</v>
+        <v>3.1651918888092</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>3.24065899848938</v>
+        <v>3.24065923690796</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G324" t="n">
-        <v>3.2317807674408</v>
+        <v>3.23178100585938</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G329" t="n">
-        <v>3.17407035827637</v>
+        <v>3.17407011985779</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G330" t="n">
-        <v>3.19182729721069</v>
+        <v>3.19182753562927</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G331" t="n">
-        <v>3.4271080493927</v>
+        <v>3.42710781097412</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G333" t="n">
-        <v>3.49813652038574</v>
+        <v>3.49813628196716</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>3.43598651885986</v>
+        <v>3.43598675727844</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G338" t="n">
-        <v>3.37827634811401</v>
+        <v>3.37827610969543</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G342" t="n">
-        <v>3.64907097816467</v>
+        <v>3.64907121658325</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G344" t="n">
-        <v>3.57804298400879</v>
+        <v>3.57804322242737</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G346" t="n">
-        <v>3.56028580665588</v>
+        <v>3.56028604507446</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G348" t="n">
-        <v>3.74673461914062</v>
+        <v>3.7467348575592</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>3.97313690185547</v>
+        <v>3.97313666343689</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>3.92874479293823</v>
+        <v>3.92874431610107</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>3.97313690185547</v>
+        <v>3.97313666343689</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>3.85327744483948</v>
+        <v>3.8532772064209</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G372" t="n">
-        <v>3.73341679573059</v>
+        <v>3.73341655731201</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G373" t="n">
-        <v>3.71122074127197</v>
+        <v>3.71122050285339</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G375" t="n">
-        <v>3.71122074127197</v>
+        <v>3.71122050285339</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G380" t="n">
-        <v>3.51589345932007</v>
+        <v>3.51589322090149</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>3.51589345932007</v>
+        <v>3.51589322090149</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G385" t="n">
-        <v>3.6046781539917</v>
+        <v>3.60467839241028</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G389" t="n">
-        <v>3.64907097816467</v>
+        <v>3.64907121658325</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G392" t="n">
-        <v>3.75561332702637</v>
+        <v>3.75561356544495</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G396" t="n">
-        <v>3.56916427612305</v>
+        <v>3.56916451454163</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G398" t="n">
-        <v>3.56028580665588</v>
+        <v>3.56028604507446</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G401" t="n">
-        <v>3.57804298400879</v>
+        <v>3.57804322242737</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G405" t="n">
-        <v>3.53808951377869</v>
+        <v>3.53808927536011</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G410" t="n">
-        <v>3.6046781539917</v>
+        <v>3.60467839241028</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>3.6268744468689</v>
+        <v>3.62687468528748</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G414" t="n">
-        <v>3.6046781539917</v>
+        <v>3.60467839241028</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G416" t="n">
-        <v>3.71834683418274</v>
+        <v>3.71834707260132</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G417" t="n">
-        <v>3.64552760124207</v>
+        <v>3.64552783966064</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G418" t="n">
-        <v>3.66828370094299</v>
+        <v>3.66828393936157</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G421" t="n">
-        <v>3.69559073448181</v>
+        <v>3.69559097290039</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G422" t="n">
-        <v>3.69559073448181</v>
+        <v>3.69559097290039</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G431" t="n">
-        <v>3.66828370094299</v>
+        <v>3.66828393936157</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G432" t="n">
-        <v>3.66828370094299</v>
+        <v>3.66828393936157</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>3.65918111801147</v>
+        <v>3.65918135643005</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G435" t="n">
-        <v>3.6136691570282</v>
+        <v>3.61366891860962</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G440" t="n">
-        <v>3.74110317230225</v>
+        <v>3.74110341072083</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G444" t="n">
-        <v>3.74110317230225</v>
+        <v>3.74110341072083</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G448" t="n">
-        <v>3.80482029914856</v>
+        <v>3.80482006072998</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G453" t="n">
-        <v>3.74110317230225</v>
+        <v>3.74110341072083</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>3.69559073448181</v>
+        <v>3.69559097290039</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G457" t="n">
-        <v>3.65918111801147</v>
+        <v>3.65918135643005</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G460" t="n">
-        <v>3.66828370094299</v>
+        <v>3.66828393936157</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G461" t="n">
-        <v>3.65918111801147</v>
+        <v>3.65918135643005</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G462" t="n">
-        <v>3.50443983078003</v>
+        <v>3.50443959236145</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G463" t="n">
-        <v>3.51354217529297</v>
+        <v>3.51354193687439</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G464" t="n">
-        <v>3.50443983078003</v>
+        <v>3.50443959236145</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G466" t="n">
-        <v>3.42251777648926</v>
+        <v>3.42251801490784</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G470" t="n">
-        <v>3.40431308746338</v>
+        <v>3.4043128490448</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G471" t="n">
-        <v>3.42251777648926</v>
+        <v>3.42251801490784</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G479" t="n">
-        <v>3.40431308746338</v>
+        <v>3.4043128490448</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G496" t="n">
-        <v>3.52264451980591</v>
+        <v>3.52264475822449</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G497" t="n">
-        <v>3.50443983078003</v>
+        <v>3.50443959236145</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G498" t="n">
-        <v>3.52264451980591</v>
+        <v>3.52264475822449</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>3.44982504844666</v>
+        <v>3.44982528686523</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G511" t="n">
-        <v>3.42251777648926</v>
+        <v>3.42251801490784</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G517" t="n">
-        <v>3.34969806671143</v>
+        <v>3.34969830513</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G519" t="n">
-        <v>3.31328845024109</v>
+        <v>3.31328868865967</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G520" t="n">
-        <v>3.31328845024109</v>
+        <v>3.31328868865967</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G523" t="n">
-        <v>3.25867390632629</v>
+        <v>3.25867366790771</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G525" t="n">
-        <v>3.31328845024109</v>
+        <v>3.31328868865967</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G529" t="n">
-        <v>3.31328845024109</v>
+        <v>3.31328868865967</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G533" t="n">
-        <v>3.32239079475403</v>
+        <v>3.32239103317261</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G539" t="n">
-        <v>3.19495677947998</v>
+        <v>3.1949565410614</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>3.5</v>
       </c>
       <c r="G541" t="n">
-        <v>3.18585443496704</v>
+        <v>3.18585419654846</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G542" t="n">
-        <v>3.19495677947998</v>
+        <v>3.1949565410614</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G548" t="n">
-        <v>3.19495677947998</v>
+        <v>3.1949565410614</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G555" t="n">
-        <v>3.15854716300964</v>
+        <v>3.15854692459106</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G556" t="n">
-        <v>3.09483003616333</v>
+        <v>3.09482979774475</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G565" t="n">
-        <v>2.66701531410217</v>
+        <v>2.66701507568359</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.67611765861511</v>
+        <v>2.67611742019653</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.75</v>
       </c>
       <c r="G575" t="n">
-        <v>2.50317120552063</v>
+        <v>2.50317144393921</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.75</v>
       </c>
       <c r="G579" t="n">
-        <v>2.50317120552063</v>
+        <v>2.50317144393921</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G580" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G585" t="n">
-        <v>2.51227355003357</v>
+        <v>2.51227378845215</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.75</v>
       </c>
       <c r="G587" t="n">
-        <v>2.50317120552063</v>
+        <v>2.50317144393921</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G589" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G590" t="n">
-        <v>2.49406862258911</v>
+        <v>2.49406886100769</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G592" t="n">
-        <v>2.45765924453735</v>
+        <v>2.45765900611877</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.35753226280212</v>
+        <v>2.35753202438354</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G604" t="n">
-        <v>2.35753226280212</v>
+        <v>2.35753202438354</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G614" t="n">
-        <v>2.51227355003357</v>
+        <v>2.51227378845215</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>2.34842991828918</v>
+        <v>2.34842967987061</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G625" t="n">
-        <v>2.34842991828918</v>
+        <v>2.34842967987061</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G626" t="n">
-        <v>2.34842991828918</v>
+        <v>2.34842967987061</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G630" t="n">
-        <v>2.45765924453735</v>
+        <v>2.45765900611877</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G631" t="n">
-        <v>2.44855690002441</v>
+        <v>2.44855666160583</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G635" t="n">
-        <v>2.44855690002441</v>
+        <v>2.44855666160583</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G636" t="n">
-        <v>2.44855690002441</v>
+        <v>2.44855666160583</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G641" t="n">
-        <v>2.11176633834839</v>
+        <v>2.11176609992981</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G642" t="n">
-        <v>2.11176633834839</v>
+        <v>2.11176609992981</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G645" t="n">
-        <v>2.01163959503174</v>
+        <v>2.01163935661316</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G648" t="n">
-        <v>2.16638088226318</v>
+        <v>2.16638112068176</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G652" t="n">
-        <v>2.11176633834839</v>
+        <v>2.11176609992981</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G653" t="n">
-        <v>2.19368815422058</v>
+        <v>2.19368839263916</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G654" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.46676158905029</v>
+        <v>2.46676135063171</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G658" t="n">
-        <v>2.51227355003357</v>
+        <v>2.51227378845215</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G661" t="n">
-        <v>2.11176633834839</v>
+        <v>2.11176609992981</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>2.15727829933167</v>
+        <v>2.15727853775024</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G663" t="n">
-        <v>2.29381489753723</v>
+        <v>2.29381513595581</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G666" t="n">
-        <v>2.15727829933167</v>
+        <v>2.15727853775024</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G669" t="n">
-        <v>2.16638088226318</v>
+        <v>2.16638112068176</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G673" t="n">
-        <v>2.11176633834839</v>
+        <v>2.11176609992981</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G679" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G681" t="n">
-        <v>2.10266399383545</v>
+        <v>2.10266375541687</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G686" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G687" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G689" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G691" t="n">
-        <v>1.96612739562988</v>
+        <v>1.96612727642059</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G695" t="n">
-        <v>1.98433220386505</v>
+        <v>1.98433232307434</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G697" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G698" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G699" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G700" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G701" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G703" t="n">
-        <v>1.90241014957428</v>
+        <v>1.90241003036499</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G704" t="n">
-        <v>1.90241014957428</v>
+        <v>1.90241003036499</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G705" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G707" t="n">
-        <v>1.67484903335571</v>
+        <v>1.674849152565</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>1.72491252422333</v>
+        <v>1.72491264343262</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G717" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132237911224</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G720" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G726" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G730" t="n">
-        <v>1.65664422512054</v>
+        <v>1.65664434432983</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G740" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G741" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G742" t="n">
-        <v>2.0298445224762</v>
+        <v>2.02984428405762</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G743" t="n">
-        <v>1.92061495780945</v>
+        <v>1.92061507701874</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G744" t="n">
-        <v>1.96612739562988</v>
+        <v>1.96612727642059</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G745" t="n">
-        <v>1.98433220386505</v>
+        <v>1.98433232307434</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G748" t="n">
-        <v>1.97522985935211</v>
+        <v>1.97522974014282</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G749" t="n">
-        <v>1.92061495780945</v>
+        <v>1.92061507701874</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G751" t="n">
-        <v>1.92061495780945</v>
+        <v>1.92061507701874</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G755" t="n">
-        <v>1.90241014957428</v>
+        <v>1.90241003036499</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G757" t="n">
-        <v>1.90241014957428</v>
+        <v>1.90241003036499</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G759" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G760" t="n">
-        <v>1.93882012367249</v>
+        <v>1.9388200044632</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G761" t="n">
-        <v>2.0298445224762</v>
+        <v>2.02984428405762</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G777" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G778" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G782" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G783" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G784" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G785" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G786" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G787" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G788" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G789" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G790" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>2.01163959503174</v>
+        <v>2.01163935661316</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>2.01163959503174</v>
+        <v>2.01163935661316</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G794" t="n">
-        <v>2.0298445224762</v>
+        <v>2.02984428405762</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G798" t="n">
-        <v>2.0298445224762</v>
+        <v>2.02984428405762</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G810" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G813" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G815" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G816" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G818" t="n">
-        <v>1.90241014957428</v>
+        <v>1.90241003036499</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G819" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G829" t="n">
-        <v>1.75677108764648</v>
+        <v>1.75677096843719</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G830" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G832" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.72491252422333</v>
+        <v>1.72491264343262</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G841" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G842" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G843" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G844" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G845" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G846" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G851" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G852" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G854" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G856" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132237911224</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G857" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132237911224</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G868" t="n">
-        <v>1.67484903335571</v>
+        <v>1.674849152565</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G872" t="n">
-        <v>1.66119539737701</v>
+        <v>1.6611955165863</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G873" t="n">
-        <v>1.66119539737701</v>
+        <v>1.6611955165863</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>1.72491252422333</v>
+        <v>1.72491264343262</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G887" t="n">
-        <v>1.88420522212982</v>
+        <v>1.88420534133911</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G893" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G894" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G895" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G896" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G898" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G899" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G900" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G902" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G903" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G904" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G905" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G906" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G909" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G910" t="n">
-        <v>1.78862977027893</v>
+        <v>1.78862965106964</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G914" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G915" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G916" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G917" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132237911224</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G920" t="n">
-        <v>1.75677108764648</v>
+        <v>1.75677096843719</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G923" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132237911224</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G928" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G929" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G930" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G931" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G932" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G936" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G937" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G950" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G951" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G952" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G953" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G955" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G957" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -47718,6 +47718,32 @@
         <v>2.1800000667572</v>
       </c>
       <c r="H1821" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1822" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C1822" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="D1822" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="E1822" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="F1822" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="G1822" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="H1822" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -42340,8 +42340,31 @@
       <c r="E1825" t="n">
         <v>2.03999996185303</v>
       </c>
-      <c r="F1825"/>
+      <c r="F1825" t="n">
+        <v>2.05999994277954</v>
+      </c>
       <c r="G1825" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="A1826" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1826" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C1826" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="D1826" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="E1826" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="F1826"/>
+      <c r="G1826" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -42363,8 +42363,31 @@
       <c r="E1826" t="n">
         <v>2.03999996185303</v>
       </c>
-      <c r="F1826"/>
+      <c r="F1826" t="n">
+        <v>2.16000008583069</v>
+      </c>
       <c r="G1826" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1827" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C1827" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="D1827" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="E1827" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="F1827"/>
+      <c r="G1827" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -42386,8 +42386,31 @@
       <c r="E1827" t="n">
         <v>2.14000010490417</v>
       </c>
-      <c r="F1827"/>
+      <c r="F1827" t="n">
+        <v>2.11999988555908</v>
+      </c>
       <c r="G1827" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1828" t="n">
+        <v>13000</v>
+      </c>
+      <c r="C1828" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="D1828" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="E1828" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="F1828"/>
+      <c r="G1828" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -42409,8 +42409,31 @@
       <c r="E1828" t="n">
         <v>2.14000010490417</v>
       </c>
-      <c r="F1828"/>
+      <c r="F1828" t="n">
+        <v>2.14000010490417</v>
+      </c>
       <c r="G1828" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1829" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1829" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="D1829" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="E1829" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="F1829"/>
+      <c r="G1829" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -42439,6 +42439,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1830">
+      <c r="A1830" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1830" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1830" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="D1830" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="E1830" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="F1830" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="G1830" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -473,7 +473,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G4" t="n">
-        <v>1.40067183971405</v>
+        <v>1.40067172050476</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G5" t="n">
-        <v>1.62828099727631</v>
+        <v>1.62828087806702</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G6" t="n">
-        <v>1.62828099727631</v>
+        <v>1.62828087806702</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G7" t="n">
-        <v>1.58888721466064</v>
+        <v>1.58888709545135</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G8" t="n">
-        <v>1.63265812397003</v>
+        <v>1.63265800476074</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G9" t="n">
-        <v>1.72020018100739</v>
+        <v>1.72019994258881</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G10" t="n">
-        <v>1.87339878082275</v>
+        <v>1.87339866161346</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G13" t="n">
-        <v>3.17777442932129</v>
+        <v>3.17777419090271</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3.9393892288208</v>
+        <v>3.93938970565796</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3.9393892288208</v>
+        <v>3.93938970565796</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>3.87810945510864</v>
+        <v>3.87811017036438</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G21" t="n">
-        <v>3.52794241905212</v>
+        <v>3.52794218063354</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>3.57171297073364</v>
+        <v>3.57171273231506</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G25" t="n">
-        <v>3.55420470237732</v>
+        <v>3.55420446395874</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G28" t="n">
-        <v>3.42289185523987</v>
+        <v>3.42289161682129</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>3.53669619560242</v>
+        <v>3.536696434021</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G31" t="n">
-        <v>3.48417139053345</v>
+        <v>3.48417115211487</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G32" t="n">
-        <v>3.45353150367737</v>
+        <v>3.45353126525879</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.75</v>
       </c>
       <c r="G38" t="n">
-        <v>3.28282427787781</v>
+        <v>3.28282451629639</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>3.28720164299011</v>
+        <v>3.28720188140869</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>3.17777442932129</v>
+        <v>3.17777419090271</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G41" t="n">
-        <v>2.9370334148407</v>
+        <v>2.93703365325928</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G42" t="n">
-        <v>2.7838351726532</v>
+        <v>2.78383541107178</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G45" t="n">
-        <v>2.98518204689026</v>
+        <v>2.98518180847168</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G48" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83635997772217</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>2.73130965232849</v>
+        <v>2.73130989074707</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>2.77945756912231</v>
+        <v>2.77945804595947</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.125</v>
       </c>
       <c r="G52" t="n">
-        <v>2.73568677902222</v>
+        <v>2.7356870174408</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>2.88450860977173</v>
+        <v>2.88450837135315</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G54" t="n">
-        <v>2.89763975143433</v>
+        <v>2.89763951301575</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>2.81009769439697</v>
+        <v>2.81009793281555</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G56" t="n">
-        <v>2.9063937664032</v>
+        <v>2.90639400482178</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>2.8013436794281</v>
+        <v>2.80134344100952</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G59" t="n">
-        <v>2.7838351726532</v>
+        <v>2.78383541107178</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.25</v>
       </c>
       <c r="G60" t="n">
-        <v>2.8451144695282</v>
+        <v>2.84511470794678</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G62" t="n">
-        <v>2.81009769439697</v>
+        <v>2.81009793281555</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.25</v>
       </c>
       <c r="G63" t="n">
-        <v>2.8451144695282</v>
+        <v>2.84511470794678</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G65" t="n">
-        <v>2.82322883605957</v>
+        <v>2.82322907447815</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G66" t="n">
-        <v>2.82322883605957</v>
+        <v>2.82322907447815</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>2.82322883605957</v>
+        <v>2.82322907447815</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83635997772217</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>2.7838351726532</v>
+        <v>2.78383541107178</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G74" t="n">
-        <v>2.84949159622192</v>
+        <v>2.8494918346405</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G76" t="n">
-        <v>2.7838351726532</v>
+        <v>2.78383541107178</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>2.77945756912231</v>
+        <v>2.77945804595947</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>2.72693276405334</v>
+        <v>2.72693300247192</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.8013436794281</v>
+        <v>2.80134344100952</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.25</v>
       </c>
       <c r="G83" t="n">
-        <v>2.8451144695282</v>
+        <v>2.84511470794678</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G84" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83635997772217</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G87" t="n">
-        <v>2.8013436794281</v>
+        <v>2.80134344100952</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G88" t="n">
-        <v>2.8013436794281</v>
+        <v>2.80134344100952</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.25</v>
       </c>
       <c r="G91" t="n">
-        <v>2.8451144695282</v>
+        <v>2.84511470794678</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G94" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83635997772217</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G95" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83635997772217</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G96" t="n">
-        <v>2.8013436794281</v>
+        <v>2.80134344100952</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>2.88450860977173</v>
+        <v>2.88450837135315</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.86700010299683</v>
+        <v>2.86699986457825</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G100" t="n">
-        <v>2.88450860977173</v>
+        <v>2.88450837135315</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G101" t="n">
-        <v>2.88450860977173</v>
+        <v>2.88450837135315</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G102" t="n">
-        <v>2.88450860977173</v>
+        <v>2.88450837135315</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G106" t="n">
-        <v>2.9983127117157</v>
+        <v>2.99831295013428</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>4.39460802078247</v>
+        <v>4.39460754394531</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G109" t="n">
-        <v>3.96565246582031</v>
+        <v>3.96565198898315</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.375</v>
       </c>
       <c r="G111" t="n">
-        <v>3.82996201515198</v>
+        <v>3.82996225357056</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G112" t="n">
-        <v>3.64174675941467</v>
+        <v>3.64174652099609</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G113" t="n">
-        <v>3.52794241905212</v>
+        <v>3.52794218063354</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>3.65487837791443</v>
+        <v>3.65487813949585</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G115" t="n">
-        <v>3.77305936813354</v>
+        <v>3.77305912971497</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>3.97878360748291</v>
+        <v>3.97878289222717</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>3.91312599182129</v>
+        <v>3.91312623023987</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>3.8606014251709</v>
+        <v>3.86060214042664</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G119" t="n">
-        <v>3.7993221282959</v>
+        <v>3.79932260513306</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>3.8474702835083</v>
+        <v>3.84747052192688</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G121" t="n">
-        <v>3.89124155044556</v>
+        <v>3.89124131202698</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G122" t="n">
-        <v>3.9262580871582</v>
+        <v>3.92625832557678</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>4.28955745697021</v>
+        <v>4.28955698013306</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G124" t="n">
-        <v>4.17137479782104</v>
+        <v>4.1713752746582</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>4.18012952804565</v>
+        <v>4.18013000488281</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>4.2457857131958</v>
+        <v>4.24578619003296</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>4.28518056869507</v>
+        <v>4.28518009185791</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G129" t="n">
-        <v>4.0619478225708</v>
+        <v>4.06194829940796</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>3.97002911567688</v>
+        <v>3.97002863883972</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G131" t="n">
-        <v>4.04006290435791</v>
+        <v>4.04006195068359</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G132" t="n">
-        <v>4.00504541397095</v>
+        <v>4.00504589080811</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>3.95689797401428</v>
+        <v>3.9568977355957</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G137" t="n">
-        <v>3.98753690719604</v>
+        <v>3.98753714561462</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G139" t="n">
-        <v>4.21952438354492</v>
+        <v>4.21952342987061</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G140" t="n">
-        <v>4.13635873794556</v>
+        <v>4.1363582611084</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>4.19326162338257</v>
+        <v>4.19326114654541</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G142" t="n">
-        <v>4.32895135879517</v>
+        <v>4.32895183563232</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G143" t="n">
-        <v>5.16497755050659</v>
+        <v>5.16497707366943</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G146" t="n">
-        <v>4.38585329055786</v>
+        <v>4.38585376739502</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>3.85184717178345</v>
+        <v>3.85184693336487</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G150" t="n">
-        <v>3.78181385993958</v>
+        <v>3.78181409835815</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G151" t="n">
-        <v>3.80369877815247</v>
+        <v>3.80369901657104</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>3.7993221282959</v>
+        <v>3.79932260513306</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G154" t="n">
-        <v>3.08147788047791</v>
+        <v>3.08147764205933</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G155" t="n">
-        <v>3.1996591091156</v>
+        <v>3.19965934753418</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G156" t="n">
-        <v>2.7225558757782</v>
+        <v>2.72255563735962</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G157" t="n">
-        <v>2.45555257797241</v>
+        <v>2.45555281639099</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>2.73130965232849</v>
+        <v>2.73130989074707</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G161" t="n">
-        <v>2.95891928672791</v>
+        <v>2.95891904830933</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G162" t="n">
-        <v>3.08147788047791</v>
+        <v>3.08147764205933</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G164" t="n">
-        <v>3.53669619560242</v>
+        <v>3.536696434021</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G167" t="n">
-        <v>3.71177959442139</v>
+        <v>3.71178007125854</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G169" t="n">
-        <v>3.60672974586487</v>
+        <v>3.60672950744629</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G171" t="n">
-        <v>3.73366594314575</v>
+        <v>3.73366546630859</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G172" t="n">
-        <v>3.68551802635193</v>
+        <v>3.68551754951477</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G173" t="n">
-        <v>3.9525203704834</v>
+        <v>3.95252060890198</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.85184717178345</v>
+        <v>3.85184693336487</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G175" t="n">
-        <v>3.94376611709595</v>
+        <v>3.94376635551453</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>4.07070207595825</v>
+        <v>4.07070255279541</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>4.07070207595825</v>
+        <v>4.07070255279541</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>3.68114018440247</v>
+        <v>3.68114042282104</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G180" t="n">
-        <v>3.8343391418457</v>
+        <v>3.83433866500854</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G181" t="n">
-        <v>3.87810945510864</v>
+        <v>3.87811017036438</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>3.85184717178345</v>
+        <v>3.85184693336487</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G185" t="n">
-        <v>3.79056763648987</v>
+        <v>3.79056787490845</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>3.86935591697693</v>
+        <v>3.86935639381409</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G187" t="n">
-        <v>3.8606014251709</v>
+        <v>3.86060214042664</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>3.77743697166443</v>
+        <v>3.77743649482727</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G189" t="n">
-        <v>3.75117421150208</v>
+        <v>3.75117373466492</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G190" t="n">
-        <v>3.78224873542786</v>
+        <v>3.78224897384644</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>3.7289776802063</v>
+        <v>3.72897720336914</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G192" t="n">
-        <v>3.78668832778931</v>
+        <v>3.78668785095215</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G195" t="n">
-        <v>3.78224873542786</v>
+        <v>3.78224897384644</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>3.7911274433136</v>
+        <v>3.79112720489502</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G200" t="n">
-        <v>3.86215543746948</v>
+        <v>3.86215567588806</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>3.8310809135437</v>
+        <v>3.83108067512512</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G203" t="n">
-        <v>3.71122074127197</v>
+        <v>3.71122050285339</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G206" t="n">
-        <v>3.80888438224792</v>
+        <v>3.80888414382935</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>3.7289776802063</v>
+        <v>3.72897720336914</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>3.86215543746948</v>
+        <v>3.86215567588806</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>3.86215543746948</v>
+        <v>3.86215567588806</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G211" t="n">
-        <v>3.81776332855225</v>
+        <v>3.81776261329651</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>3.95981931686401</v>
+        <v>3.95981907844543</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>3.91986560821533</v>
+        <v>3.91986608505249</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>3.80888438224792</v>
+        <v>3.80888414382935</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>4.03084707260132</v>
+        <v>4.03084754943848</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G216" t="n">
-        <v>3.91542649269104</v>
+        <v>3.9154269695282</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G218" t="n">
-        <v>3.96425843238831</v>
+        <v>3.96425914764404</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>3.95094037055969</v>
+        <v>3.95094060897827</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>4.01752996444702</v>
+        <v>4.01752948760986</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G222" t="n">
-        <v>4.06636142730713</v>
+        <v>4.06636095046997</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>3.95981931686401</v>
+        <v>3.95981907844543</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G226" t="n">
-        <v>4.00421190261841</v>
+        <v>4.00421237945557</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>3.97313714027405</v>
+        <v>3.97313690185547</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G230" t="n">
-        <v>3.9864547252655</v>
+        <v>3.98645448684692</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G231" t="n">
-        <v>4.06636142730713</v>
+        <v>4.06636095046997</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G234" t="n">
-        <v>4.06636142730713</v>
+        <v>4.06636095046997</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G236" t="n">
-        <v>4.10187578201294</v>
+        <v>4.10187530517578</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.48365163803101</v>
+        <v>4.48365211486816</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G240" t="n">
-        <v>4.43481969833374</v>
+        <v>4.43481922149658</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G243" t="n">
-        <v>4.31939840316772</v>
+        <v>4.31939888000488</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G244" t="n">
-        <v>4.16846418380737</v>
+        <v>4.16846466064453</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G245" t="n">
-        <v>4.24393129348755</v>
+        <v>4.24393224716187</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>4.875</v>
       </c>
       <c r="G247" t="n">
-        <v>4.32827806472778</v>
+        <v>4.32827758789062</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G251" t="n">
-        <v>4.25281095504761</v>
+        <v>4.25281047821045</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G252" t="n">
-        <v>4.02196931838989</v>
+        <v>4.02196884155273</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G253" t="n">
-        <v>3.86215543746948</v>
+        <v>3.86215567588806</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G255" t="n">
-        <v>3.96425843238831</v>
+        <v>3.96425914764404</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>4.06636142730713</v>
+        <v>4.06636095046997</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>4.2883243560791</v>
+        <v>4.28832387924194</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G262" t="n">
-        <v>4.08855772018433</v>
+        <v>4.08855724334717</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G265" t="n">
-        <v>4.03528690338135</v>
+        <v>4.03528642654419</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G271" t="n">
-        <v>3.95094037055969</v>
+        <v>3.95094060897827</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>3.95981931686401</v>
+        <v>3.95981907844543</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>3.99089407920837</v>
+        <v>3.99089384078979</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G274" t="n">
-        <v>3.95537996292114</v>
+        <v>3.95538020133972</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G276" t="n">
-        <v>3.84439826011658</v>
+        <v>3.84439849853516</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>3.84883785247803</v>
+        <v>3.84883737564087</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G278" t="n">
-        <v>3.84883785247803</v>
+        <v>3.84883737564087</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G279" t="n">
-        <v>3.81776332855225</v>
+        <v>3.81776261329651</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G283" t="n">
-        <v>3.81776332855225</v>
+        <v>3.81776261329651</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G284" t="n">
-        <v>3.80444526672363</v>
+        <v>3.80444502830505</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>3.7289776802063</v>
+        <v>3.72897720336914</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G291" t="n">
-        <v>3.71122074127197</v>
+        <v>3.71122050285339</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G292" t="n">
-        <v>3.80888438224792</v>
+        <v>3.80888414382935</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G294" t="n">
-        <v>3.81776332855225</v>
+        <v>3.81776261329651</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>3.69790315628052</v>
+        <v>3.69790291786194</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>3.69346380233765</v>
+        <v>3.69346356391907</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G302" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59579992294312</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G303" t="n">
-        <v>3.63131403923035</v>
+        <v>3.63131427764893</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>3.64019227027893</v>
+        <v>3.64019250869751</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G307" t="n">
-        <v>3.62243556976318</v>
+        <v>3.6224353313446</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G312" t="n">
-        <v>3.46262240409851</v>
+        <v>3.46262216567993</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>3.41822957992554</v>
+        <v>3.41822934150696</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G314" t="n">
-        <v>3.41822957992554</v>
+        <v>3.41822934150696</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G315" t="n">
-        <v>3.33388376235962</v>
+        <v>3.3338840007782</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G317" t="n">
-        <v>3.2317807674408</v>
+        <v>3.23178100585938</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G320" t="n">
-        <v>3.16075253486633</v>
+        <v>3.16075229644775</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G321" t="n">
-        <v>3.09860277175903</v>
+        <v>3.09860301017761</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G324" t="n">
-        <v>3.2317807674408</v>
+        <v>3.23178100585938</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G326" t="n">
-        <v>3.16075253486633</v>
+        <v>3.16075229644775</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G328" t="n">
-        <v>3.2939305305481</v>
+        <v>3.29393029212952</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G329" t="n">
-        <v>3.17407011985779</v>
+        <v>3.17407035827637</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G331" t="n">
-        <v>3.4271080493927</v>
+        <v>3.42710781097412</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G333" t="n">
-        <v>3.49813628196716</v>
+        <v>3.49813652038574</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>3.46262240409851</v>
+        <v>3.46262216567993</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>3.46262240409851</v>
+        <v>3.46262216567993</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>3.64019227027893</v>
+        <v>3.64019250869751</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G342" t="n">
-        <v>3.64907145500183</v>
+        <v>3.64907121658325</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G343" t="n">
-        <v>3.58248209953308</v>
+        <v>3.5824818611145</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59579992294312</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G347" t="n">
-        <v>3.81776332855225</v>
+        <v>3.81776261329651</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G349" t="n">
-        <v>3.7689311504364</v>
+        <v>3.76893067359924</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G350" t="n">
-        <v>3.7689311504364</v>
+        <v>3.76893067359924</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G351" t="n">
-        <v>3.95094037055969</v>
+        <v>3.95094060897827</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G352" t="n">
-        <v>3.89323091506958</v>
+        <v>3.893230676651</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G353" t="n">
-        <v>3.94650173187256</v>
+        <v>3.9465012550354</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>4.03084707260132</v>
+        <v>4.03084754943848</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G355" t="n">
-        <v>3.91542649269104</v>
+        <v>3.9154269695282</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>3.97313714027405</v>
+        <v>3.97313690185547</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G358" t="n">
-        <v>3.99977231025696</v>
+        <v>3.99977278709412</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G359" t="n">
-        <v>3.90210890769958</v>
+        <v>3.90210914611816</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>3.96425843238831</v>
+        <v>3.96425914764404</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>3.98201560974121</v>
+        <v>3.98201584815979</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G364" t="n">
-        <v>3.96869707107544</v>
+        <v>3.9686975479126</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G365" t="n">
-        <v>3.9864547252655</v>
+        <v>3.98645448684692</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G366" t="n">
-        <v>3.99977231025696</v>
+        <v>3.99977278709412</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>3.96425843238831</v>
+        <v>3.96425914764404</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G368" t="n">
-        <v>3.99977231025696</v>
+        <v>3.99977278709412</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>3.97313714027405</v>
+        <v>3.97313690185547</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>3.85327696800232</v>
+        <v>3.8532772064209</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G371" t="n">
-        <v>3.76449131965637</v>
+        <v>3.76449179649353</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G372" t="n">
-        <v>3.73341679573059</v>
+        <v>3.73341703414917</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G373" t="n">
-        <v>3.71122074127197</v>
+        <v>3.71122050285339</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G374" t="n">
-        <v>3.76449131965637</v>
+        <v>3.76449179649353</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G375" t="n">
-        <v>3.71122074127197</v>
+        <v>3.71122050285339</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G376" t="n">
-        <v>3.76449131965637</v>
+        <v>3.76449179649353</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G377" t="n">
-        <v>3.7289776802063</v>
+        <v>3.72897720336914</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G378" t="n">
-        <v>3.63131403923035</v>
+        <v>3.63131427764893</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>3.64019227027893</v>
+        <v>3.64019250869751</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>3.52921104431152</v>
+        <v>3.52921080589294</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G383" t="n">
-        <v>3.63575315475464</v>
+        <v>3.63575339317322</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G384" t="n">
-        <v>3.64019227027893</v>
+        <v>3.64019250869751</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G385" t="n">
-        <v>3.60467863082886</v>
+        <v>3.6046781539917</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G386" t="n">
-        <v>3.63131403923035</v>
+        <v>3.63131427764893</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G387" t="n">
-        <v>3.63131403923035</v>
+        <v>3.63131427764893</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59579992294312</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G389" t="n">
-        <v>3.64907145500183</v>
+        <v>3.64907121658325</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>3.7911274433136</v>
+        <v>3.79112720489502</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G391" t="n">
-        <v>3.90210890769958</v>
+        <v>3.90210914611816</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G392" t="n">
-        <v>3.75561332702637</v>
+        <v>3.75561356544495</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G393" t="n">
-        <v>3.62243556976318</v>
+        <v>3.6224353313446</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G395" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59579992294312</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G400" t="n">
-        <v>3.58248209953308</v>
+        <v>3.5824818611145</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G403" t="n">
-        <v>3.56472516059875</v>
+        <v>3.56472492218018</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G407" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59579992294312</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>3.6845850944519</v>
+        <v>3.68458533287048</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G410" t="n">
-        <v>3.60467863082886</v>
+        <v>3.6046781539917</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>3.62687492370605</v>
+        <v>3.62687468528748</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G414" t="n">
-        <v>3.60467863082886</v>
+        <v>3.6046781539917</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G416" t="n">
-        <v>3.71834683418274</v>
+        <v>3.71834707260132</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G418" t="n">
-        <v>3.66828370094299</v>
+        <v>3.66828393936157</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G420" t="n">
-        <v>3.654629945755</v>
+        <v>3.65462970733643</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G423" t="n">
-        <v>3.70014238357544</v>
+        <v>3.70014214515686</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G424" t="n">
-        <v>3.72289824485779</v>
+        <v>3.72289848327637</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>3.75020575523376</v>
+        <v>3.75020551681519</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G428" t="n">
-        <v>3.72289824485779</v>
+        <v>3.72289848327637</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G429" t="n">
-        <v>3.72289824485779</v>
+        <v>3.72289848327637</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G430" t="n">
-        <v>3.71379590034485</v>
+        <v>3.71379566192627</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G431" t="n">
-        <v>3.66828370094299</v>
+        <v>3.66828393936157</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G432" t="n">
-        <v>3.66828370094299</v>
+        <v>3.66828393936157</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G435" t="n">
-        <v>3.6136691570282</v>
+        <v>3.61366891860962</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G438" t="n">
-        <v>3.71379590034485</v>
+        <v>3.71379566192627</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G440" t="n">
-        <v>3.74110317230225</v>
+        <v>3.74110341072083</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G443" t="n">
-        <v>3.77751302719116</v>
+        <v>3.77751326560974</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G444" t="n">
-        <v>3.74110317230225</v>
+        <v>3.74110341072083</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G445" t="n">
-        <v>3.75020575523376</v>
+        <v>3.75020551681519</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G446" t="n">
-        <v>3.72289824485779</v>
+        <v>3.72289848327637</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G448" t="n">
-        <v>3.80482029914856</v>
+        <v>3.80482006072998</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G450" t="n">
-        <v>3.75020575523376</v>
+        <v>3.75020551681519</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>3.77751302719116</v>
+        <v>3.77751326560974</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G452" t="n">
-        <v>3.75020575523376</v>
+        <v>3.75020551681519</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G453" t="n">
-        <v>3.74110317230225</v>
+        <v>3.74110341072083</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G460" t="n">
-        <v>3.66828370094299</v>
+        <v>3.66828393936157</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G462" t="n">
-        <v>3.50443983078003</v>
+        <v>3.50443959236145</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G463" t="n">
-        <v>3.51354217529297</v>
+        <v>3.51354193687439</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G464" t="n">
-        <v>3.50443983078003</v>
+        <v>3.50443959236145</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G466" t="n">
-        <v>3.42251777648926</v>
+        <v>3.42251801490784</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>3.37700533866882</v>
+        <v>3.3770055770874</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>3.37700533866882</v>
+        <v>3.3770055770874</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G470" t="n">
-        <v>3.40431308746338</v>
+        <v>3.4043128490448</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G471" t="n">
-        <v>3.42251777648926</v>
+        <v>3.42251801490784</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.75</v>
       </c>
       <c r="G473" t="n">
-        <v>3.41341543197632</v>
+        <v>3.41341519355774</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G474" t="n">
-        <v>3.37700533866882</v>
+        <v>3.3770055770874</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>3.37700533866882</v>
+        <v>3.3770055770874</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G479" t="n">
-        <v>3.40431308746338</v>
+        <v>3.4043128490448</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>3.37700533866882</v>
+        <v>3.3770055770874</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G485" t="n">
-        <v>3.48623490333557</v>
+        <v>3.48623466491699</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G488" t="n">
-        <v>3.38610816001892</v>
+        <v>3.38610792160034</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>3.75</v>
       </c>
       <c r="G491" t="n">
-        <v>3.41341543197632</v>
+        <v>3.41341519355774</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>3.39521050453186</v>
+        <v>3.39521026611328</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G497" t="n">
-        <v>3.50443983078003</v>
+        <v>3.50443959236145</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G501" t="n">
-        <v>3.53174734115601</v>
+        <v>3.53174710273743</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G503" t="n">
-        <v>3.53174734115601</v>
+        <v>3.53174710273743</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G505" t="n">
-        <v>3.49533724784851</v>
+        <v>3.49533700942993</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>3.75</v>
       </c>
       <c r="G507" t="n">
-        <v>3.41341543197632</v>
+        <v>3.41341519355774</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G511" t="n">
-        <v>3.42251777648926</v>
+        <v>3.42251801490784</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G512" t="n">
-        <v>3.38610816001892</v>
+        <v>3.38610792160034</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>3.37700533866882</v>
+        <v>3.3770055770874</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G516" t="n">
-        <v>3.37700533866882</v>
+        <v>3.3770055770874</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G517" t="n">
-        <v>3.34969806671143</v>
+        <v>3.34969830513</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G518" t="n">
-        <v>3.37700533866882</v>
+        <v>3.3770055770874</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G519" t="n">
-        <v>3.31328845024109</v>
+        <v>3.31328868865967</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G520" t="n">
-        <v>3.31328845024109</v>
+        <v>3.31328868865967</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G524" t="n">
-        <v>3.30418586730957</v>
+        <v>3.30418610572815</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G525" t="n">
-        <v>3.31328845024109</v>
+        <v>3.31328868865967</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G526" t="n">
-        <v>3.30418586730957</v>
+        <v>3.30418610572815</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G527" t="n">
-        <v>3.29508328437805</v>
+        <v>3.29508352279663</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>3.29508328437805</v>
+        <v>3.29508352279663</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G529" t="n">
-        <v>3.31328845024109</v>
+        <v>3.31328868865967</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G533" t="n">
-        <v>3.32239079475403</v>
+        <v>3.32239103317261</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G537" t="n">
-        <v>3.24046897888184</v>
+        <v>3.24046874046326</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G539" t="n">
-        <v>3.19495677947998</v>
+        <v>3.1949565410614</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>3.5</v>
       </c>
       <c r="G541" t="n">
-        <v>3.18585443496704</v>
+        <v>3.18585419654846</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G542" t="n">
-        <v>3.19495677947998</v>
+        <v>3.1949565410614</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G543" t="n">
-        <v>3.29508328437805</v>
+        <v>3.29508352279663</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G544" t="n">
-        <v>3.24957132339478</v>
+        <v>3.24957156181335</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G547" t="n">
-        <v>3.24957132339478</v>
+        <v>3.24957156181335</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G548" t="n">
-        <v>3.19495677947998</v>
+        <v>3.1949565410614</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G549" t="n">
-        <v>3.13123965263367</v>
+        <v>3.13123989105225</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G550" t="n">
-        <v>3.13123965263367</v>
+        <v>3.13123989105225</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G555" t="n">
-        <v>3.15854716300964</v>
+        <v>3.15854692459106</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G558" t="n">
-        <v>2.86726903915405</v>
+        <v>2.86726880073547</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G560" t="n">
-        <v>2.8126540184021</v>
+        <v>2.81265425682068</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>2.6397078037262</v>
+        <v>2.63970804214478</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G565" t="n">
-        <v>2.66701531410217</v>
+        <v>2.66701507568359</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G585" t="n">
-        <v>2.51227355003357</v>
+        <v>2.51227378845215</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G590" t="n">
-        <v>2.49406862258911</v>
+        <v>2.49406886100769</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G592" t="n">
-        <v>2.45765924453735</v>
+        <v>2.45765900611877</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G599" t="n">
-        <v>2.4121470451355</v>
+        <v>2.41214680671692</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G600" t="n">
-        <v>2.4121470451355</v>
+        <v>2.41214680671692</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.35753226280212</v>
+        <v>2.35753202438354</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G604" t="n">
-        <v>2.35753226280212</v>
+        <v>2.35753202438354</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G610" t="n">
-        <v>2.32112216949463</v>
+        <v>2.32112240791321</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G611" t="n">
-        <v>2.4121470451355</v>
+        <v>2.41214680671692</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G612" t="n">
-        <v>2.40304470062256</v>
+        <v>2.40304446220398</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G614" t="n">
-        <v>2.51227355003357</v>
+        <v>2.51227378845215</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>2.34842991828918</v>
+        <v>2.34842967987061</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G625" t="n">
-        <v>2.34842991828918</v>
+        <v>2.34842967987061</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G626" t="n">
-        <v>2.34842991828918</v>
+        <v>2.34842967987061</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G630" t="n">
-        <v>2.45765924453735</v>
+        <v>2.45765900611877</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G631" t="n">
-        <v>2.44855690002441</v>
+        <v>2.44855642318726</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G633" t="n">
-        <v>2.4121470451355</v>
+        <v>2.41214680671692</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G634" t="n">
-        <v>2.4121470451355</v>
+        <v>2.41214680671692</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G635" t="n">
-        <v>2.44855690002441</v>
+        <v>2.44855642318726</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G636" t="n">
-        <v>2.44855690002441</v>
+        <v>2.44855642318726</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G637" t="n">
-        <v>2.32112216949463</v>
+        <v>2.32112240791321</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G639" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G640" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G641" t="n">
-        <v>2.11176633834839</v>
+        <v>2.11176609992981</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G642" t="n">
-        <v>2.11176633834839</v>
+        <v>2.11176609992981</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>2.08445906639099</v>
+        <v>2.08445882797241</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>2.08445906639099</v>
+        <v>2.08445882797241</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G648" t="n">
-        <v>2.16638088226318</v>
+        <v>2.16638112068176</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>2.08445906639099</v>
+        <v>2.08445882797241</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G652" t="n">
-        <v>2.11176633834839</v>
+        <v>2.11176609992981</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G653" t="n">
-        <v>2.19368815422058</v>
+        <v>2.19368839263916</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G658" t="n">
-        <v>2.51227355003357</v>
+        <v>2.51227378845215</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G659" t="n">
-        <v>2.40304470062256</v>
+        <v>2.40304446220398</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G661" t="n">
-        <v>2.11176633834839</v>
+        <v>2.11176609992981</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>2.15727829933167</v>
+        <v>2.15727853775024</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G663" t="n">
-        <v>2.29381489753723</v>
+        <v>2.29381513595581</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G665" t="n">
-        <v>2.1754834651947</v>
+        <v>2.17548370361328</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G666" t="n">
-        <v>2.15727829933167</v>
+        <v>2.15727853775024</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G669" t="n">
-        <v>2.16638088226318</v>
+        <v>2.16638112068176</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G672" t="n">
-        <v>2.14817571640015</v>
+        <v>2.14817595481873</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G673" t="n">
-        <v>2.11176633834839</v>
+        <v>2.11176609992981</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G674" t="n">
-        <v>2.12997102737427</v>
+        <v>2.12997078895569</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>2.08445906639099</v>
+        <v>2.08445882797241</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>2.08445906639099</v>
+        <v>2.08445882797241</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G679" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G681" t="n">
-        <v>2.10266399383545</v>
+        <v>2.10266375541687</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G686" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G687" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G689" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G691" t="n">
-        <v>1.96612739562988</v>
+        <v>1.96612727642059</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G695" t="n">
-        <v>1.98433220386505</v>
+        <v>1.98433232307434</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G697" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G698" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G699" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G700" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G701" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G703" t="n">
-        <v>1.90241014957428</v>
+        <v>1.90241003036499</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G704" t="n">
-        <v>1.90241014957428</v>
+        <v>1.90241003036499</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G705" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G707" t="n">
-        <v>1.67484903335571</v>
+        <v>1.674849152565</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G709" t="n">
-        <v>1.69760525226593</v>
+        <v>1.69760513305664</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G720" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G721" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G722" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G723" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G724" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G726" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G729" t="n">
-        <v>1.69305408000946</v>
+        <v>1.69305396080017</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G730" t="n">
-        <v>1.65664422512054</v>
+        <v>1.65664434432983</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G736" t="n">
-        <v>1.64754164218903</v>
+        <v>1.64754176139832</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G737" t="n">
-        <v>1.66574668884277</v>
+        <v>1.66574680805206</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G738" t="n">
-        <v>1.66574668884277</v>
+        <v>1.66574680805206</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G739" t="n">
-        <v>1.765873670578</v>
+        <v>1.76587355136871</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G741" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G742" t="n">
-        <v>2.0298445224762</v>
+        <v>2.02984428405762</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G743" t="n">
-        <v>1.92061495780945</v>
+        <v>1.92061483860016</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G744" t="n">
-        <v>1.96612739562988</v>
+        <v>1.96612727642059</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G745" t="n">
-        <v>1.98433220386505</v>
+        <v>1.98433232307434</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G748" t="n">
-        <v>1.97522985935211</v>
+        <v>1.97522974014282</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G749" t="n">
-        <v>1.92061495780945</v>
+        <v>1.92061483860016</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G750" t="n">
-        <v>1.91151261329651</v>
+        <v>1.91151237487793</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G751" t="n">
-        <v>1.92061495780945</v>
+        <v>1.92061483860016</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G752" t="n">
-        <v>1.91151261329651</v>
+        <v>1.91151237487793</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G755" t="n">
-        <v>1.90241014957428</v>
+        <v>1.90241003036499</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G757" t="n">
-        <v>1.90241014957428</v>
+        <v>1.90241003036499</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G759" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G760" t="n">
-        <v>1.93882012367249</v>
+        <v>1.9388200044632</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G761" t="n">
-        <v>2.0298445224762</v>
+        <v>2.02984428405762</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G763" t="n">
-        <v>2.13907337188721</v>
+        <v>2.13907361030579</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G764" t="n">
-        <v>2.14817571640015</v>
+        <v>2.14817595481873</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G765" t="n">
-        <v>2.14817571640015</v>
+        <v>2.14817595481873</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G775" t="n">
-        <v>2.12997102737427</v>
+        <v>2.12997078895569</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G777" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G778" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G782" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G783" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G784" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G785" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G786" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G787" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G788" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G789" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G790" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G794" t="n">
-        <v>2.0298445224762</v>
+        <v>2.02984428405762</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G798" t="n">
-        <v>2.0298445224762</v>
+        <v>2.02984428405762</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G800" t="n">
-        <v>1.95702493190765</v>
+        <v>1.95702469348907</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G801" t="n">
-        <v>1.85689795017242</v>
+        <v>1.85689783096313</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.85689795017242</v>
+        <v>1.85689783096313</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G812" t="n">
-        <v>1.87510287761688</v>
+        <v>1.87510275840759</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G818" t="n">
-        <v>1.90241014957428</v>
+        <v>1.90241003036499</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G820" t="n">
-        <v>1.7795273065567</v>
+        <v>1.77952718734741</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G821" t="n">
-        <v>1.765873670578</v>
+        <v>1.76587355136871</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G822" t="n">
-        <v>1.765873670578</v>
+        <v>1.76587355136871</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G823" t="n">
-        <v>1.765873670578</v>
+        <v>1.76587355136871</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G829" t="n">
-        <v>1.75677108764648</v>
+        <v>1.75677096843719</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G832" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1.875</v>
       </c>
       <c r="G834" t="n">
-        <v>1.70670771598816</v>
+        <v>1.70670759677887</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G837" t="n">
-        <v>1.66574668884277</v>
+        <v>1.66574680805206</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G838" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G841" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G842" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G843" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G844" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G845" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G846" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G854" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G858" t="n">
-        <v>1.765873670578</v>
+        <v>1.76587355136871</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G859" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G860" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G861" t="n">
-        <v>1.74311745166779</v>
+        <v>1.7431173324585</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G862" t="n">
-        <v>1.74311745166779</v>
+        <v>1.7431173324585</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.875</v>
       </c>
       <c r="G864" t="n">
-        <v>1.70670771598816</v>
+        <v>1.70670759677887</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>1.875</v>
       </c>
       <c r="G865" t="n">
-        <v>1.70670771598816</v>
+        <v>1.70670759677887</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G866" t="n">
-        <v>1.68850266933441</v>
+        <v>1.6885027885437</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G867" t="n">
-        <v>1.68850266933441</v>
+        <v>1.6885027885437</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G868" t="n">
-        <v>1.67484903335571</v>
+        <v>1.674849152565</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G869" t="n">
-        <v>1.64754164218903</v>
+        <v>1.64754176139832</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G870" t="n">
-        <v>1.62023448944092</v>
+        <v>1.62023437023163</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G871" t="n">
-        <v>1.62023448944092</v>
+        <v>1.62023437023163</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G872" t="n">
-        <v>1.66119539737701</v>
+        <v>1.6611955165863</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G873" t="n">
-        <v>1.66119539737701</v>
+        <v>1.6611955165863</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G874" t="n">
-        <v>1.66574668884277</v>
+        <v>1.66574680805206</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G878" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G883" t="n">
-        <v>1.85689795017242</v>
+        <v>1.85689783096313</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G884" t="n">
-        <v>1.85689795017242</v>
+        <v>1.85689783096313</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>1.85689795017242</v>
+        <v>1.85689783096313</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G886" t="n">
-        <v>1.85689795017242</v>
+        <v>1.85689783096313</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G887" t="n">
-        <v>1.88420522212982</v>
+        <v>1.88420534133911</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G900" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G909" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G910" t="n">
-        <v>1.78862977027893</v>
+        <v>1.78862965106964</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G914" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G915" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G916" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G917" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G919" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G920" t="n">
-        <v>1.75677108764648</v>
+        <v>1.75677096843719</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G924" t="n">
-        <v>1.7795273065567</v>
+        <v>1.77952718734741</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>1.85689795017242</v>
+        <v>1.85689783096313</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G944" t="n">
-        <v>1.87510287761688</v>
+        <v>1.87510275840759</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G945" t="n">
-        <v>1.87510287761688</v>
+        <v>1.87510275840759</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G950" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G951" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G953" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G957" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G958" t="n">
-        <v>1.765873670578</v>
+        <v>1.76587355136871</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G964" t="n">
-        <v>1.765873670578</v>
+        <v>1.76587355136871</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G966" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G967" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G988" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G989" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G990" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G998" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G999" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.62191653251648</v>
+        <v>1.62191641330719</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.52594518661499</v>
+        <v>1.5259450674057</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.41077935695648</v>
+        <v>1.41077947616577</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.47795927524567</v>
+        <v>1.47795939445496</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.52594518661499</v>
+        <v>1.5259450674057</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.52594518661499</v>
+        <v>1.5259450674057</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.52594518661499</v>
+        <v>1.5259450674057</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.47795927524567</v>
+        <v>1.47795939445496</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.52594518661499</v>
+        <v>1.5259450674057</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.49715352058411</v>
+        <v>1.4971536397934</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.36279368400574</v>
+        <v>1.36279356479645</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.41077935695648</v>
+        <v>1.41077947616577</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.41077935695648</v>
+        <v>1.41077947616577</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.39158511161804</v>
+        <v>1.39158523082733</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.36279368400574</v>
+        <v>1.36279356479645</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.36279368400574</v>
+        <v>1.36279356479645</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.42997360229492</v>
+        <v>1.42997372150421</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.39158511161804</v>
+        <v>1.39158523082733</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.42997360229492</v>
+        <v>1.42997372150421</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.41077935695648</v>
+        <v>1.41077947616577</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.39158511161804</v>
+        <v>1.39158523082733</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.42997360229492</v>
+        <v>1.42997372150421</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.42997360229492</v>
+        <v>1.42997372150421</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.41077935695648</v>
+        <v>1.41077947616577</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.39158511161804</v>
+        <v>1.39158523082733</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.39158511161804</v>
+        <v>1.39158523082733</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.39158511161804</v>
+        <v>1.39158523082733</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.39158511161804</v>
+        <v>1.39158523082733</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.62191653251648</v>
+        <v>1.62191641330719</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1192" t="n">
-        <v>1.52594518661499</v>
+        <v>1.5259450674057</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.95781636238098</v>
+        <v>1.95781624317169</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.95781636238098</v>
+        <v>1.95781624317169</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.84265065193176</v>
+        <v>1.84265053272247</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1209" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.49715352058411</v>
+        <v>1.4971536397934</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1237" t="n">
-        <v>1.62191653251648</v>
+        <v>1.62191641330719</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1238" t="n">
-        <v>1.62191653251648</v>
+        <v>1.62191641330719</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.62191653251648</v>
+        <v>1.62191641330719</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.62191653251648</v>
+        <v>1.62191641330719</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.62191653251648</v>
+        <v>1.62191641330719</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.01539921760559</v>
+        <v>2.01539897918701</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.89063632488251</v>
+        <v>1.8906364440918</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.89063632488251</v>
+        <v>1.8906364440918</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1314" t="n">
-        <v>1.86184501647949</v>
+        <v>1.8618448972702</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.89063632488251</v>
+        <v>1.8906364440918</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -48004,6 +48004,32 @@
         <v>2.14000010490417</v>
       </c>
       <c r="H1832" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1833" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1833" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="D1833" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="E1833" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="F1833" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="G1833" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="H1833" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -499,7 +499,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G5" t="n">
-        <v>1.62828087806702</v>
+        <v>1.62828099727631</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G6" t="n">
-        <v>1.62828087806702</v>
+        <v>1.62828099727631</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G9" t="n">
-        <v>1.72019994258881</v>
+        <v>1.7202000617981</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G10" t="n">
-        <v>1.87339866161346</v>
+        <v>1.87339878082275</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.18854975700378</v>
+        <v>2.18854951858521</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G12" t="n">
-        <v>2.59124279022217</v>
+        <v>2.59124302864075</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3.93938970565796</v>
+        <v>3.93938946723938</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3.93938970565796</v>
+        <v>3.93938946723938</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>3.87811017036438</v>
+        <v>3.8781099319458</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>3.57171273231506</v>
+        <v>3.57171297073364</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G27" t="n">
-        <v>3.51043367385864</v>
+        <v>3.51043391227722</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>3.536696434021</v>
+        <v>3.53669619560242</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G31" t="n">
-        <v>3.48417115211487</v>
+        <v>3.48417139053345</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>3.28720188140869</v>
+        <v>3.28720164299011</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G42" t="n">
-        <v>2.78383541107178</v>
+        <v>2.7838351726532</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G46" t="n">
-        <v>2.98080468177795</v>
+        <v>2.98080492019653</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G47" t="n">
-        <v>2.78821229934692</v>
+        <v>2.78821206092834</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G48" t="n">
-        <v>2.83635997772217</v>
+        <v>2.83636045455933</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>2.73130989074707</v>
+        <v>2.73130965232849</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.125</v>
       </c>
       <c r="G52" t="n">
-        <v>2.7356870174408</v>
+        <v>2.73568725585938</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G54" t="n">
-        <v>2.89763951301575</v>
+        <v>2.89763975143433</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>2.81009793281555</v>
+        <v>2.81009769439697</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G59" t="n">
-        <v>2.78383541107178</v>
+        <v>2.7838351726532</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.25</v>
       </c>
       <c r="G60" t="n">
-        <v>2.84511470794678</v>
+        <v>2.8451144695282</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G61" t="n">
-        <v>2.85824584960938</v>
+        <v>2.85824608802795</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G62" t="n">
-        <v>2.81009793281555</v>
+        <v>2.81009769439697</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.25</v>
       </c>
       <c r="G63" t="n">
-        <v>2.84511470794678</v>
+        <v>2.8451144695282</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G64" t="n">
-        <v>2.84073734283447</v>
+        <v>2.84073710441589</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G65" t="n">
-        <v>2.82322907447815</v>
+        <v>2.82322883605957</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G66" t="n">
-        <v>2.82322907447815</v>
+        <v>2.82322883605957</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>2.82322907447815</v>
+        <v>2.82322883605957</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>2.82760620117188</v>
+        <v>2.8276059627533</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>2.82760620117188</v>
+        <v>2.8276059627533</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>2.83635997772217</v>
+        <v>2.83636045455933</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>2.78821229934692</v>
+        <v>2.78821206092834</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>2.78383541107178</v>
+        <v>2.7838351726532</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G74" t="n">
-        <v>2.8494918346405</v>
+        <v>2.84949159622192</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G75" t="n">
-        <v>2.78821229934692</v>
+        <v>2.78821206092834</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G76" t="n">
-        <v>2.78383541107178</v>
+        <v>2.7838351726532</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>2.77070379257202</v>
+        <v>2.77070355415344</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>2.72693300247192</v>
+        <v>2.72693252563477</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.25</v>
       </c>
       <c r="G83" t="n">
-        <v>2.84511470794678</v>
+        <v>2.8451144695282</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G84" t="n">
-        <v>2.83635997772217</v>
+        <v>2.83636045455933</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G85" t="n">
-        <v>2.78821229934692</v>
+        <v>2.78821206092834</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>2.84073734283447</v>
+        <v>2.84073710441589</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.25</v>
       </c>
       <c r="G91" t="n">
-        <v>2.84511470794678</v>
+        <v>2.8451144695282</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G94" t="n">
-        <v>2.83635997772217</v>
+        <v>2.83636045455933</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G95" t="n">
-        <v>2.83635997772217</v>
+        <v>2.83636045455933</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>2.82760620117188</v>
+        <v>2.8276059627533</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.86699986457825</v>
+        <v>2.86700010299683</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>4.39460754394531</v>
+        <v>4.39460802078247</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>4.11447381973267</v>
+        <v>4.11447334289551</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.375</v>
       </c>
       <c r="G111" t="n">
-        <v>3.82996225357056</v>
+        <v>3.82996201515198</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>3.65487813949585</v>
+        <v>3.65487837791443</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>3.97878289222717</v>
+        <v>3.97878336906433</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>3.91312623023987</v>
+        <v>3.91312599182129</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>3.86060214042664</v>
+        <v>3.86060166358948</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G119" t="n">
-        <v>3.79932260513306</v>
+        <v>3.7993221282959</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>3.84747052192688</v>
+        <v>3.8474702835083</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G121" t="n">
-        <v>3.89124131202698</v>
+        <v>3.89124155044556</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G122" t="n">
-        <v>3.92625832557678</v>
+        <v>3.9262580871582</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>4.28955698013306</v>
+        <v>4.28955745697021</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>4.18013000488281</v>
+        <v>4.18012952804565</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>4.28518009185791</v>
+        <v>4.28518056869507</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G128" t="n">
-        <v>4.16699838638306</v>
+        <v>4.16699886322021</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G129" t="n">
-        <v>4.06194829940796</v>
+        <v>4.0619478225708</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>3.97002863883972</v>
+        <v>3.97002911567688</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G131" t="n">
-        <v>4.04006195068359</v>
+        <v>4.04006242752075</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G132" t="n">
-        <v>4.00504589080811</v>
+        <v>4.00504493713379</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G136" t="n">
-        <v>4.02255392074585</v>
+        <v>4.02255439758301</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G137" t="n">
-        <v>3.98753714561462</v>
+        <v>3.98753690719604</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G138" t="n">
-        <v>3.99629139900208</v>
+        <v>3.99629163742065</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G139" t="n">
-        <v>4.21952342987061</v>
+        <v>4.21952390670776</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G140" t="n">
-        <v>4.1363582611084</v>
+        <v>4.13635873794556</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G142" t="n">
-        <v>4.32895183563232</v>
+        <v>4.32895135879517</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G143" t="n">
-        <v>5.16497707366943</v>
+        <v>5.16497755050659</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G145" t="n">
-        <v>4.46464109420776</v>
+        <v>4.46464157104492</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G147" t="n">
-        <v>4.25454044342041</v>
+        <v>4.25454092025757</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>3.85184693336487</v>
+        <v>3.85184717178345</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>3.79932260513306</v>
+        <v>3.7993221282959</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G153" t="n">
-        <v>3.33097267150879</v>
+        <v>3.33097243309021</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G154" t="n">
-        <v>3.08147764205933</v>
+        <v>3.08147788047791</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>2.73130989074707</v>
+        <v>2.73130965232849</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>2.77508091926575</v>
+        <v>2.77508115768433</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G162" t="n">
-        <v>3.08147764205933</v>
+        <v>3.08147788047791</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G164" t="n">
-        <v>3.536696434021</v>
+        <v>3.53669619560242</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.75555109977722</v>
+        <v>3.7555513381958</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G167" t="n">
-        <v>3.71178007125854</v>
+        <v>3.71177983283997</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G171" t="n">
-        <v>3.73366546630859</v>
+        <v>3.73366594314575</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G172" t="n">
-        <v>3.68551754951477</v>
+        <v>3.68551778793335</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G173" t="n">
-        <v>3.95252060890198</v>
+        <v>3.9525203704834</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.85184693336487</v>
+        <v>3.85184717178345</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>4.07070255279541</v>
+        <v>4.07070207595825</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>4.07070255279541</v>
+        <v>4.07070207595825</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>3.68114042282104</v>
+        <v>3.68114018440247</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G179" t="n">
-        <v>3.70302605628967</v>
+        <v>3.70302581787109</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G180" t="n">
-        <v>3.83433866500854</v>
+        <v>3.83433890342712</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G181" t="n">
-        <v>3.87811017036438</v>
+        <v>3.8781099319458</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G182" t="n">
-        <v>3.70302605628967</v>
+        <v>3.70302581787109</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>3.85184693336487</v>
+        <v>3.85184717178345</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G185" t="n">
-        <v>3.79056787490845</v>
+        <v>3.79056763648987</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>3.86935639381409</v>
+        <v>3.86935591697693</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G187" t="n">
-        <v>3.86060214042664</v>
+        <v>3.86060166358948</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>3.77743649482727</v>
+        <v>3.77743673324585</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G189" t="n">
-        <v>3.75117373466492</v>
+        <v>3.75117421150208</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G190" t="n">
-        <v>3.78224897384644</v>
+        <v>3.78224849700928</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>3.72897720336914</v>
+        <v>3.7289776802063</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G192" t="n">
-        <v>3.78668785095215</v>
+        <v>3.78668832778931</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G195" t="n">
-        <v>3.78224897384644</v>
+        <v>3.78224849700928</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>3.79112720489502</v>
+        <v>3.7911274433136</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>4.5</v>
       </c>
       <c r="G199" t="n">
-        <v>3.99533319473267</v>
+        <v>3.99533343315125</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G201" t="n">
-        <v>3.83552002906799</v>
+        <v>3.83552026748657</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>3.83108067512512</v>
+        <v>3.8310809135437</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G203" t="n">
-        <v>3.71122050285339</v>
+        <v>3.71122074127197</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G204" t="n">
-        <v>3.82220196723938</v>
+        <v>3.82220220565796</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G205" t="n">
-        <v>3.82220196723938</v>
+        <v>3.82220220565796</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G206" t="n">
-        <v>3.80888414382935</v>
+        <v>3.8088846206665</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>3.72897720336914</v>
+        <v>3.7289776802063</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90654802322388</v>
+        <v>3.9065477848053</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G211" t="n">
-        <v>3.81776261329651</v>
+        <v>3.81776332855225</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>3.95981907844543</v>
+        <v>3.95981931686401</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>3.91986608505249</v>
+        <v>3.91986584663391</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>3.80888414382935</v>
+        <v>3.8088846206665</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>4.03084754943848</v>
+        <v>4.03084707260132</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G216" t="n">
-        <v>3.9154269695282</v>
+        <v>3.91542649269104</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G218" t="n">
-        <v>3.96425914764404</v>
+        <v>3.96425819396973</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>3.95094060897827</v>
+        <v>3.95094013214111</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G222" t="n">
-        <v>4.06636095046997</v>
+        <v>4.06636190414429</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>3.95981907844543</v>
+        <v>3.95981931686401</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G226" t="n">
-        <v>4.00421237945557</v>
+        <v>4.00421190261841</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>3.97313690185547</v>
+        <v>3.97313737869263</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.5</v>
       </c>
       <c r="G228" t="n">
-        <v>3.99533319473267</v>
+        <v>3.99533343315125</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>4.01309061050415</v>
+        <v>4.01309013366699</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G230" t="n">
-        <v>3.98645448684692</v>
+        <v>3.98645496368408</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G231" t="n">
-        <v>4.06636095046997</v>
+        <v>4.06636190414429</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.5</v>
       </c>
       <c r="G232" t="n">
-        <v>3.99533319473267</v>
+        <v>3.99533343315125</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G234" t="n">
-        <v>4.06636095046997</v>
+        <v>4.06636190414429</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G240" t="n">
-        <v>4.43481922149658</v>
+        <v>4.43481969833374</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G242" t="n">
-        <v>4.41262340545654</v>
+        <v>4.41262292861938</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G245" t="n">
-        <v>4.24393224716187</v>
+        <v>4.24393177032471</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>4.3105206489563</v>
+        <v>4.31052112579346</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>4.875</v>
       </c>
       <c r="G247" t="n">
-        <v>4.32827758789062</v>
+        <v>4.32827806472778</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>4.26168918609619</v>
+        <v>4.26168870925903</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G249" t="n">
-        <v>4.26168918609619</v>
+        <v>4.26168870925903</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G255" t="n">
-        <v>3.96425914764404</v>
+        <v>3.96425819396973</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>4.06636095046997</v>
+        <v>4.06636190414429</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G262" t="n">
-        <v>4.08855724334717</v>
+        <v>4.08855772018433</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>4.01309061050415</v>
+        <v>4.01309013366699</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G265" t="n">
-        <v>4.03528642654419</v>
+        <v>4.03528690338135</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>3.90654802322388</v>
+        <v>3.9065477848053</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G271" t="n">
-        <v>3.95094060897827</v>
+        <v>3.95094013214111</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>3.95981907844543</v>
+        <v>3.95981931686401</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G274" t="n">
-        <v>3.95538020133972</v>
+        <v>3.95537996292114</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G276" t="n">
-        <v>3.84439849853516</v>
+        <v>3.844398021698</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>3.84883737564087</v>
+        <v>3.84883785247803</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G278" t="n">
-        <v>3.84883737564087</v>
+        <v>3.84883785247803</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G279" t="n">
-        <v>3.81776261329651</v>
+        <v>3.81776332855225</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>3.8133237361908</v>
+        <v>3.81332349777222</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G283" t="n">
-        <v>3.81776261329651</v>
+        <v>3.81776332855225</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G284" t="n">
-        <v>3.80444502830505</v>
+        <v>3.80444526672363</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>3.72897720336914</v>
+        <v>3.7289776802063</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G291" t="n">
-        <v>3.71122050285339</v>
+        <v>3.71122074127197</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G292" t="n">
-        <v>3.80888414382935</v>
+        <v>3.8088846206665</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G293" t="n">
-        <v>3.82220196723938</v>
+        <v>3.82220220565796</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G294" t="n">
-        <v>3.81776261329651</v>
+        <v>3.81776332855225</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>3.69790291786194</v>
+        <v>3.69790315628052</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G302" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580039978027</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G303" t="n">
-        <v>3.63131427764893</v>
+        <v>3.63131403923035</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>3.64019250869751</v>
+        <v>3.64019227027893</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G306" t="n">
-        <v>3.57804322242737</v>
+        <v>3.57804298400879</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G307" t="n">
-        <v>3.6224353313446</v>
+        <v>3.62243556976318</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G311" t="n">
-        <v>3.50257563591003</v>
+        <v>3.50257539749146</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G312" t="n">
-        <v>3.46262216567993</v>
+        <v>3.46262240409851</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>3.41822934150696</v>
+        <v>3.41822957992554</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G314" t="n">
-        <v>3.41822934150696</v>
+        <v>3.41822957992554</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G315" t="n">
-        <v>3.3338840007782</v>
+        <v>3.33388376235962</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G317" t="n">
-        <v>3.23178100585938</v>
+        <v>3.2317807674408</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G321" t="n">
-        <v>3.09860301017761</v>
+        <v>3.09860277175903</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G324" t="n">
-        <v>3.23178100585938</v>
+        <v>3.2317807674408</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G333" t="n">
-        <v>3.49813652038574</v>
+        <v>3.49813628196716</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>3.46262216567993</v>
+        <v>3.46262240409851</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>3.46262216567993</v>
+        <v>3.46262240409851</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G338" t="n">
-        <v>3.37827634811401</v>
+        <v>3.37827610969543</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G340" t="n">
-        <v>3.8133237361908</v>
+        <v>3.81332349777222</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>3.64019250869751</v>
+        <v>3.64019227027893</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G343" t="n">
-        <v>3.5824818611145</v>
+        <v>3.58248209953308</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G344" t="n">
-        <v>3.57804322242737</v>
+        <v>3.57804298400879</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580039978027</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G347" t="n">
-        <v>3.81776261329651</v>
+        <v>3.81776332855225</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G349" t="n">
-        <v>3.76893067359924</v>
+        <v>3.76893091201782</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G350" t="n">
-        <v>3.76893067359924</v>
+        <v>3.76893091201782</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G351" t="n">
-        <v>3.95094060897827</v>
+        <v>3.95094013214111</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G353" t="n">
-        <v>3.9465012550354</v>
+        <v>3.94650173187256</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>4.03084754943848</v>
+        <v>4.03084707260132</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G355" t="n">
-        <v>3.9154269695282</v>
+        <v>3.91542649269104</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.5</v>
       </c>
       <c r="G356" t="n">
-        <v>3.99533319473267</v>
+        <v>3.99533343315125</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>3.97313690185547</v>
+        <v>3.97313737869263</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G359" t="n">
-        <v>3.90210914611816</v>
+        <v>3.90210890769958</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G360" t="n">
-        <v>3.90654802322388</v>
+        <v>3.9065477848053</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>3.96425914764404</v>
+        <v>3.96425819396973</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>3.92874431610107</v>
+        <v>3.92874455451965</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>3.98201584815979</v>
+        <v>3.98201560974121</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G364" t="n">
-        <v>3.9686975479126</v>
+        <v>3.96869707107544</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G365" t="n">
-        <v>3.98645448684692</v>
+        <v>3.98645496368408</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>3.96425914764404</v>
+        <v>3.96425819396973</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>3.97313690185547</v>
+        <v>3.97313737869263</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>3.8532772064209</v>
+        <v>3.85327672958374</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G371" t="n">
-        <v>3.76449179649353</v>
+        <v>3.76449131965637</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G372" t="n">
-        <v>3.73341703414917</v>
+        <v>3.73341679573059</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G373" t="n">
-        <v>3.71122050285339</v>
+        <v>3.71122074127197</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G374" t="n">
-        <v>3.76449179649353</v>
+        <v>3.76449131965637</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G375" t="n">
-        <v>3.71122050285339</v>
+        <v>3.71122074127197</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G376" t="n">
-        <v>3.76449179649353</v>
+        <v>3.76449131965637</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G377" t="n">
-        <v>3.72897720336914</v>
+        <v>3.7289776802063</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G378" t="n">
-        <v>3.63131427764893</v>
+        <v>3.63131403923035</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>3.64019250869751</v>
+        <v>3.64019227027893</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>3.52921080589294</v>
+        <v>3.52921104431152</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G383" t="n">
-        <v>3.63575339317322</v>
+        <v>3.63575315475464</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G384" t="n">
-        <v>3.64019250869751</v>
+        <v>3.64019227027893</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G385" t="n">
-        <v>3.6046781539917</v>
+        <v>3.60467839241028</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G386" t="n">
-        <v>3.63131427764893</v>
+        <v>3.63131403923035</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G387" t="n">
-        <v>3.63131427764893</v>
+        <v>3.63131403923035</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580039978027</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>3.79112720489502</v>
+        <v>3.7911274433136</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G391" t="n">
-        <v>3.90210914611816</v>
+        <v>3.90210890769958</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G392" t="n">
-        <v>3.75561356544495</v>
+        <v>3.75561332702637</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G393" t="n">
-        <v>3.6224353313446</v>
+        <v>3.62243556976318</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G395" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580039978027</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G396" t="n">
-        <v>3.56916427612305</v>
+        <v>3.56916403770447</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G400" t="n">
-        <v>3.5824818611145</v>
+        <v>3.58248209953308</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G401" t="n">
-        <v>3.57804322242737</v>
+        <v>3.57804298400879</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G407" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580039978027</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>3.68458533287048</v>
+        <v>3.6845850944519</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G410" t="n">
-        <v>3.6046781539917</v>
+        <v>3.60467839241028</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>3.62687468528748</v>
+        <v>3.62687492370605</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G414" t="n">
-        <v>3.6046781539917</v>
+        <v>3.60467839241028</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G417" t="n">
-        <v>3.64552760124207</v>
+        <v>3.64552783966064</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G420" t="n">
-        <v>3.65462970733643</v>
+        <v>3.654629945755</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G421" t="n">
-        <v>3.69559073448181</v>
+        <v>3.69559097290039</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G422" t="n">
-        <v>3.69559073448181</v>
+        <v>3.69559097290039</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G423" t="n">
-        <v>3.70014214515686</v>
+        <v>3.70014238357544</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G424" t="n">
-        <v>3.72289848327637</v>
+        <v>3.72289824485779</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>3.75020551681519</v>
+        <v>3.75020575523376</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G428" t="n">
-        <v>3.72289848327637</v>
+        <v>3.72289824485779</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G429" t="n">
-        <v>3.72289848327637</v>
+        <v>3.72289824485779</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G430" t="n">
-        <v>3.71379566192627</v>
+        <v>3.71379590034485</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>3.65918111801147</v>
+        <v>3.65918135643005</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G438" t="n">
-        <v>3.71379566192627</v>
+        <v>3.71379590034485</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G443" t="n">
-        <v>3.77751326560974</v>
+        <v>3.77751302719116</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G445" t="n">
-        <v>3.75020551681519</v>
+        <v>3.75020575523376</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G446" t="n">
-        <v>3.72289848327637</v>
+        <v>3.72289824485779</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G450" t="n">
-        <v>3.75020551681519</v>
+        <v>3.75020575523376</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>3.77751326560974</v>
+        <v>3.77751302719116</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G452" t="n">
-        <v>3.75020551681519</v>
+        <v>3.75020575523376</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>3.69559073448181</v>
+        <v>3.69559097290039</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G457" t="n">
-        <v>3.65918111801147</v>
+        <v>3.65918135643005</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G461" t="n">
-        <v>3.65918111801147</v>
+        <v>3.65918135643005</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.75</v>
       </c>
       <c r="G473" t="n">
-        <v>3.41341519355774</v>
+        <v>3.41341543197632</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G474" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G485" t="n">
-        <v>3.48623466491699</v>
+        <v>3.48623490333557</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G488" t="n">
-        <v>3.38610792160034</v>
+        <v>3.38610816001892</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>3.75</v>
       </c>
       <c r="G491" t="n">
-        <v>3.41341519355774</v>
+        <v>3.41341543197632</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>3.39521026611328</v>
+        <v>3.39521050453186</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G496" t="n">
-        <v>3.52264451980591</v>
+        <v>3.52264475822449</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G498" t="n">
-        <v>3.52264451980591</v>
+        <v>3.52264475822449</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G501" t="n">
-        <v>3.53174710273743</v>
+        <v>3.53174734115601</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G503" t="n">
-        <v>3.53174710273743</v>
+        <v>3.53174734115601</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G505" t="n">
-        <v>3.49533700942993</v>
+        <v>3.49533724784851</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>3.44982504844666</v>
+        <v>3.44982528686523</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>3.75</v>
       </c>
       <c r="G507" t="n">
-        <v>3.41341519355774</v>
+        <v>3.41341543197632</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G512" t="n">
-        <v>3.38610792160034</v>
+        <v>3.38610816001892</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G516" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G518" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G523" t="n">
-        <v>3.25867390632629</v>
+        <v>3.25867366790771</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G524" t="n">
-        <v>3.30418610572815</v>
+        <v>3.30418586730957</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G526" t="n">
-        <v>3.30418610572815</v>
+        <v>3.30418586730957</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G527" t="n">
-        <v>3.29508352279663</v>
+        <v>3.29508328437805</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>3.29508352279663</v>
+        <v>3.29508328437805</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G537" t="n">
-        <v>3.24046874046326</v>
+        <v>3.24046897888184</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G543" t="n">
-        <v>3.29508352279663</v>
+        <v>3.29508328437805</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G544" t="n">
-        <v>3.24957156181335</v>
+        <v>3.24957132339478</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G547" t="n">
-        <v>3.24957156181335</v>
+        <v>3.24957132339478</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G549" t="n">
-        <v>3.13123989105225</v>
+        <v>3.13123965263367</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G550" t="n">
-        <v>3.13123989105225</v>
+        <v>3.13123965263367</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G556" t="n">
-        <v>3.09483003616333</v>
+        <v>3.09482979774475</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G558" t="n">
-        <v>2.86726880073547</v>
+        <v>2.86726903915405</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G560" t="n">
-        <v>2.81265425682068</v>
+        <v>2.8126540184021</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>2.63970804214478</v>
+        <v>2.6397078037262</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.67611765861511</v>
+        <v>2.67611742019653</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.75</v>
       </c>
       <c r="G575" t="n">
-        <v>2.50317120552063</v>
+        <v>2.50317144393921</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.75</v>
       </c>
       <c r="G579" t="n">
-        <v>2.50317120552063</v>
+        <v>2.50317144393921</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G580" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.75</v>
       </c>
       <c r="G587" t="n">
-        <v>2.50317120552063</v>
+        <v>2.50317144393921</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G589" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G599" t="n">
-        <v>2.41214680671692</v>
+        <v>2.4121470451355</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G600" t="n">
-        <v>2.41214680671692</v>
+        <v>2.4121470451355</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G610" t="n">
-        <v>2.32112240791321</v>
+        <v>2.32112216949463</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G611" t="n">
-        <v>2.41214680671692</v>
+        <v>2.4121470451355</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G612" t="n">
-        <v>2.40304446220398</v>
+        <v>2.40304470062256</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G631" t="n">
-        <v>2.44855642318726</v>
+        <v>2.44855666160583</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G633" t="n">
-        <v>2.41214680671692</v>
+        <v>2.4121470451355</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G634" t="n">
-        <v>2.41214680671692</v>
+        <v>2.4121470451355</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G635" t="n">
-        <v>2.44855642318726</v>
+        <v>2.44855666160583</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G636" t="n">
-        <v>2.44855642318726</v>
+        <v>2.44855666160583</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G637" t="n">
-        <v>2.32112240791321</v>
+        <v>2.32112216949463</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G639" t="n">
-        <v>2.18458604812622</v>
+        <v>2.18458580970764</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G640" t="n">
-        <v>2.18458604812622</v>
+        <v>2.18458580970764</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>2.08445882797241</v>
+        <v>2.08445906639099</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G645" t="n">
-        <v>2.01163959503174</v>
+        <v>2.01163935661316</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>2.08445882797241</v>
+        <v>2.08445906639099</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>2.18458604812622</v>
+        <v>2.18458580970764</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>2.08445882797241</v>
+        <v>2.08445906639099</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G654" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.46676158905029</v>
+        <v>2.46676135063171</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G659" t="n">
-        <v>2.40304446220398</v>
+        <v>2.40304470062256</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G665" t="n">
-        <v>2.17548370361328</v>
+        <v>2.1754834651947</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>2.18458604812622</v>
+        <v>2.18458580970764</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>2.18458604812622</v>
+        <v>2.18458580970764</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G672" t="n">
-        <v>2.14817595481873</v>
+        <v>2.14817571640015</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G674" t="n">
-        <v>2.12997078895569</v>
+        <v>2.12997102737427</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>2.08445882797241</v>
+        <v>2.08445906639099</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>2.08445882797241</v>
+        <v>2.08445906639099</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G697" t="n">
-        <v>1.94792234897614</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G698" t="n">
-        <v>1.94792234897614</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G699" t="n">
-        <v>1.94792234897614</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G700" t="n">
-        <v>1.94792234897614</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G701" t="n">
-        <v>1.94792234897614</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>1.72491252422333</v>
+        <v>1.72491264343262</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G709" t="n">
-        <v>1.69760513305664</v>
+        <v>1.69760525226593</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G717" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132237911224</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G721" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G722" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G723" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G724" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G729" t="n">
-        <v>1.69305396080017</v>
+        <v>1.69305408000946</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G736" t="n">
-        <v>1.64754176139832</v>
+        <v>1.64754164218903</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G737" t="n">
-        <v>1.66574680805206</v>
+        <v>1.66574668884277</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G738" t="n">
-        <v>1.66574680805206</v>
+        <v>1.66574668884277</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G739" t="n">
-        <v>1.76587355136871</v>
+        <v>1.765873670578</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G740" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G743" t="n">
-        <v>1.92061483860016</v>
+        <v>1.92061507701874</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G749" t="n">
-        <v>1.92061483860016</v>
+        <v>1.92061507701874</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G750" t="n">
-        <v>1.91151237487793</v>
+        <v>1.91151261329651</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G751" t="n">
-        <v>1.92061483860016</v>
+        <v>1.92061507701874</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G752" t="n">
-        <v>1.91151237487793</v>
+        <v>1.91151261329651</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G759" t="n">
-        <v>1.94792234897614</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G763" t="n">
-        <v>2.13907361030579</v>
+        <v>2.13907337188721</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G764" t="n">
-        <v>2.14817595481873</v>
+        <v>2.14817571640015</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G765" t="n">
-        <v>2.14817595481873</v>
+        <v>2.14817571640015</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G775" t="n">
-        <v>2.12997078895569</v>
+        <v>2.12997102737427</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>2.01163959503174</v>
+        <v>2.01163935661316</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>2.01163959503174</v>
+        <v>2.01163935661316</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G800" t="n">
-        <v>1.95702469348907</v>
+        <v>1.95702493190765</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G801" t="n">
-        <v>1.85689783096313</v>
+        <v>1.85689795017242</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.85689783096313</v>
+        <v>1.85689795017242</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G810" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G812" t="n">
-        <v>1.87510275840759</v>
+        <v>1.87510287761688</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G813" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G815" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G816" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G819" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G820" t="n">
-        <v>1.77952718734741</v>
+        <v>1.7795273065567</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G821" t="n">
-        <v>1.76587355136871</v>
+        <v>1.765873670578</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G822" t="n">
-        <v>1.76587355136871</v>
+        <v>1.765873670578</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G823" t="n">
-        <v>1.76587355136871</v>
+        <v>1.765873670578</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G830" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.72491252422333</v>
+        <v>1.72491264343262</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1.875</v>
       </c>
       <c r="G834" t="n">
-        <v>1.70670759677887</v>
+        <v>1.70670771598816</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G837" t="n">
-        <v>1.66574680805206</v>
+        <v>1.66574668884277</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G838" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G851" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G852" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G856" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132237911224</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G857" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132237911224</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G858" t="n">
-        <v>1.76587355136871</v>
+        <v>1.765873670578</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G859" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G860" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G861" t="n">
-        <v>1.7431173324585</v>
+        <v>1.74311745166779</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G862" t="n">
-        <v>1.7431173324585</v>
+        <v>1.74311745166779</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.875</v>
       </c>
       <c r="G864" t="n">
-        <v>1.70670759677887</v>
+        <v>1.70670771598816</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>1.875</v>
       </c>
       <c r="G865" t="n">
-        <v>1.70670759677887</v>
+        <v>1.70670771598816</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G866" t="n">
-        <v>1.6885027885437</v>
+        <v>1.68850266933441</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G867" t="n">
-        <v>1.6885027885437</v>
+        <v>1.68850266933441</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G869" t="n">
-        <v>1.64754176139832</v>
+        <v>1.64754164218903</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G870" t="n">
-        <v>1.62023437023163</v>
+        <v>1.62023448944092</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G871" t="n">
-        <v>1.62023437023163</v>
+        <v>1.62023448944092</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G874" t="n">
-        <v>1.66574680805206</v>
+        <v>1.66574668884277</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>1.72491252422333</v>
+        <v>1.72491264343262</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G878" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G883" t="n">
-        <v>1.85689783096313</v>
+        <v>1.85689795017242</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G884" t="n">
-        <v>1.85689783096313</v>
+        <v>1.85689795017242</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>1.85689783096313</v>
+        <v>1.85689795017242</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G886" t="n">
-        <v>1.85689783096313</v>
+        <v>1.85689795017242</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G893" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G894" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G895" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G896" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G898" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G899" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G902" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G903" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G904" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G905" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G906" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132237911224</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G919" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G923" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132237911224</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G924" t="n">
-        <v>1.77952718734741</v>
+        <v>1.7795273065567</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G928" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G929" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G930" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G931" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G932" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G936" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G937" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>1.85689783096313</v>
+        <v>1.85689795017242</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G944" t="n">
-        <v>1.87510275840759</v>
+        <v>1.87510287761688</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G945" t="n">
-        <v>1.87510275840759</v>
+        <v>1.87510287761688</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G952" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G955" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G958" t="n">
-        <v>1.76587355136871</v>
+        <v>1.765873670578</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G964" t="n">
-        <v>1.76587355136871</v>
+        <v>1.765873670578</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G966" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G967" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G988" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G989" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G990" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G998" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G999" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.47795939445496</v>
+        <v>1.47795927524567</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.47795939445496</v>
+        <v>1.47795927524567</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.4971536397934</v>
+        <v>1.49715352058411</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.36279356479645</v>
+        <v>1.36279368400574</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.36279356479645</v>
+        <v>1.36279368400574</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.36279356479645</v>
+        <v>1.36279368400574</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.42997372150421</v>
+        <v>1.42997360229492</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.42997372150421</v>
+        <v>1.42997360229492</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.42997372150421</v>
+        <v>1.42997360229492</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.42997372150421</v>
+        <v>1.42997360229492</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1192" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.95781624317169</v>
+        <v>1.95781636238098</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.95781624317169</v>
+        <v>1.95781636238098</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.84265053272247</v>
+        <v>1.84265065193176</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1209" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.4971536397934</v>
+        <v>1.49715352058411</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1237" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1238" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.01539897918701</v>
+        <v>2.01539921760559</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.8906364440918</v>
+        <v>1.89063632488251</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.8906364440918</v>
+        <v>1.89063632488251</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1314" t="n">
-        <v>1.8618448972702</v>
+        <v>1.86184501647949</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.8906364440918</v>
+        <v>1.89063632488251</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -48030,6 +48030,32 @@
         <v>2.14000010490417</v>
       </c>
       <c r="H1833" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1834" t="n">
+        <v>28000</v>
+      </c>
+      <c r="C1834" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="D1834" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="E1834" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="F1834" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="G1834" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="H1834" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>1.30437564849854</v>
+        <v>1.30437552928925</v>
       </c>
       <c r="H2" t="n">
         <v>322000</v>
@@ -456,7 +456,7 @@
         <v>1.50020003318787</v>
       </c>
       <c r="G3" t="n">
-        <v>1.31330502033234</v>
+        <v>1.31330490112305</v>
       </c>
       <c r="H3" t="n">
         <v>35000</v>
@@ -485,7 +485,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G4" t="n">
-        <v>1.40067172050476</v>
+        <v>1.40067160129547</v>
       </c>
       <c r="H4" t="n">
         <v>193000</v>
@@ -514,7 +514,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G5" t="n">
-        <v>1.62828087806702</v>
+        <v>1.62828099727631</v>
       </c>
       <c r="H5" t="n">
         <v>169000</v>
@@ -543,7 +543,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G6" t="n">
-        <v>1.62828087806702</v>
+        <v>1.62828099727631</v>
       </c>
       <c r="H6" t="n">
         <v>470000</v>
@@ -688,7 +688,7 @@
         <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.18854951858521</v>
+        <v>2.18854975700378</v>
       </c>
       <c r="H11" t="n">
         <v>315000</v>
@@ -717,7 +717,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G12" t="n">
-        <v>2.59124302864075</v>
+        <v>2.59124255180359</v>
       </c>
       <c r="H12" t="n">
         <v>261000</v>
@@ -833,7 +833,7 @@
         <v>4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3.93938970565796</v>
+        <v>3.93938946723938</v>
       </c>
       <c r="H16" t="n">
         <v>669000</v>
@@ -862,7 +862,7 @@
         <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>3.50167965888977</v>
+        <v>3.50167918205261</v>
       </c>
       <c r="H17" t="n">
         <v>598000</v>
@@ -891,7 +891,7 @@
         <v>4.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3.93938970565796</v>
+        <v>3.93938946723938</v>
       </c>
       <c r="H18" t="n">
         <v>489000</v>
@@ -920,7 +920,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>3.8781099319458</v>
+        <v>3.87810969352722</v>
       </c>
       <c r="H19" t="n">
         <v>592000</v>
@@ -949,7 +949,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G20" t="n">
-        <v>3.66800904273987</v>
+        <v>3.66800928115845</v>
       </c>
       <c r="H20" t="n">
         <v>302000</v>
@@ -978,7 +978,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G21" t="n">
-        <v>3.52794218063354</v>
+        <v>3.52794241905212</v>
       </c>
       <c r="H21" t="n">
         <v>356000</v>
@@ -1007,7 +1007,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>3.57171297073364</v>
+        <v>3.57171273231506</v>
       </c>
       <c r="H22" t="n">
         <v>212000</v>
@@ -1036,7 +1036,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>3.43164563179016</v>
+        <v>3.43164587020874</v>
       </c>
       <c r="H23" t="n">
         <v>116000</v>
@@ -1123,7 +1123,7 @@
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>3.50167965888977</v>
+        <v>3.50167918205261</v>
       </c>
       <c r="H26" t="n">
         <v>145000</v>
@@ -1152,7 +1152,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G27" t="n">
-        <v>3.51043367385864</v>
+        <v>3.51043391227722</v>
       </c>
       <c r="H27" t="n">
         <v>25000</v>
@@ -1239,7 +1239,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>3.536696434021</v>
+        <v>3.53669619560242</v>
       </c>
       <c r="H30" t="n">
         <v>95000</v>
@@ -1297,7 +1297,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G32" t="n">
-        <v>3.45353126525879</v>
+        <v>3.45353150367737</v>
       </c>
       <c r="H32" t="n">
         <v>39000</v>
@@ -1355,7 +1355,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G34" t="n">
-        <v>3.43164563179016</v>
+        <v>3.43164587020874</v>
       </c>
       <c r="H34" t="n">
         <v>27000</v>
@@ -1384,7 +1384,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G35" t="n">
-        <v>3.43164563179016</v>
+        <v>3.43164587020874</v>
       </c>
       <c r="H35" t="n">
         <v>28000</v>
@@ -1413,7 +1413,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G36" t="n">
-        <v>3.41413736343384</v>
+        <v>3.41413760185242</v>
       </c>
       <c r="H36" t="n">
         <v>60000</v>
@@ -1442,7 +1442,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G37" t="n">
-        <v>3.41413736343384</v>
+        <v>3.41413760185242</v>
       </c>
       <c r="H37" t="n">
         <v>48000</v>
@@ -1471,7 +1471,7 @@
         <v>3.75</v>
       </c>
       <c r="G38" t="n">
-        <v>3.28282427787781</v>
+        <v>3.28282403945923</v>
       </c>
       <c r="H38" t="n">
         <v>41000</v>
@@ -1500,7 +1500,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>3.28720188140869</v>
+        <v>3.28720164299011</v>
       </c>
       <c r="H39" t="n">
         <v>64000</v>
@@ -1558,7 +1558,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G41" t="n">
-        <v>2.93703389167786</v>
+        <v>2.93703365325928</v>
       </c>
       <c r="H41" t="n">
         <v>317000</v>
@@ -1616,7 +1616,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G43" t="n">
-        <v>2.62188243865967</v>
+        <v>2.62188220024109</v>
       </c>
       <c r="H43" t="n">
         <v>68000</v>
@@ -1645,7 +1645,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>2.34612512588501</v>
+        <v>2.34612536430359</v>
       </c>
       <c r="H44" t="n">
         <v>226000</v>
@@ -1703,7 +1703,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G46" t="n">
-        <v>2.98080468177795</v>
+        <v>2.98080492019653</v>
       </c>
       <c r="H46" t="n">
         <v>492000</v>
@@ -1761,7 +1761,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G48" t="n">
-        <v>2.83635997772217</v>
+        <v>2.83636045455933</v>
       </c>
       <c r="H48" t="n">
         <v>52000</v>
@@ -1790,7 +1790,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>2.73130989074707</v>
+        <v>2.73130965232849</v>
       </c>
       <c r="H49" t="n">
         <v>52000</v>
@@ -1848,7 +1848,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>2.77945828437805</v>
+        <v>2.77945780754089</v>
       </c>
       <c r="H51" t="n">
         <v>28000</v>
@@ -1935,7 +1935,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G54" t="n">
-        <v>2.89763951301575</v>
+        <v>2.89763975143433</v>
       </c>
       <c r="H54" t="n">
         <v>60000</v>
@@ -2051,7 +2051,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>2.80134344100952</v>
+        <v>2.80134320259094</v>
       </c>
       <c r="H58" t="n">
         <v>74000</v>
@@ -2341,7 +2341,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>2.82760620117188</v>
+        <v>2.8276059627533</v>
       </c>
       <c r="H68" t="n">
         <v>24000</v>
@@ -2370,7 +2370,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>2.82760620117188</v>
+        <v>2.8276059627533</v>
       </c>
       <c r="H69" t="n">
         <v>9000</v>
@@ -2399,7 +2399,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>2.83635997772217</v>
+        <v>2.83636045455933</v>
       </c>
       <c r="H70" t="n">
         <v>21000</v>
@@ -2602,7 +2602,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>2.77945828437805</v>
+        <v>2.77945780754089</v>
       </c>
       <c r="H77" t="n">
         <v>18000</v>
@@ -2631,7 +2631,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>2.77070379257202</v>
+        <v>2.7707040309906</v>
       </c>
       <c r="H78" t="n">
         <v>13000</v>
@@ -2660,7 +2660,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>2.72693300247192</v>
+        <v>2.72693276405334</v>
       </c>
       <c r="H79" t="n">
         <v>6000</v>
@@ -2718,7 +2718,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.80134344100952</v>
+        <v>2.80134320259094</v>
       </c>
       <c r="H81" t="n">
         <v>20000</v>
@@ -2747,7 +2747,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G82" t="n">
-        <v>2.74006414413452</v>
+        <v>2.7400643825531</v>
       </c>
       <c r="H82" t="n">
         <v>7000</v>
@@ -2805,7 +2805,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G84" t="n">
-        <v>2.83635997772217</v>
+        <v>2.83636045455933</v>
       </c>
       <c r="H84" t="n">
         <v>12000</v>
@@ -2892,7 +2892,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G87" t="n">
-        <v>2.80134344100952</v>
+        <v>2.80134320259094</v>
       </c>
       <c r="H87" t="n">
         <v>20000</v>
@@ -2921,7 +2921,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G88" t="n">
-        <v>2.80134344100952</v>
+        <v>2.80134320259094</v>
       </c>
       <c r="H88" t="n">
         <v>49000</v>
@@ -3095,7 +3095,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G94" t="n">
-        <v>2.83635997772217</v>
+        <v>2.83636045455933</v>
       </c>
       <c r="H94" t="n">
         <v>27000</v>
@@ -3124,7 +3124,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G95" t="n">
-        <v>2.83635997772217</v>
+        <v>2.83636045455933</v>
       </c>
       <c r="H95" t="n">
         <v>11000</v>
@@ -3153,7 +3153,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G96" t="n">
-        <v>2.80134344100952</v>
+        <v>2.80134320259094</v>
       </c>
       <c r="H96" t="n">
         <v>9000</v>
@@ -3211,7 +3211,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>2.82760620117188</v>
+        <v>2.8276059627533</v>
       </c>
       <c r="H98" t="n">
         <v>4000</v>
@@ -3240,7 +3240,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.86699986457825</v>
+        <v>2.86700034141541</v>
       </c>
       <c r="H99" t="n">
         <v>3000</v>
@@ -3443,7 +3443,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G106" t="n">
-        <v>2.99831318855286</v>
+        <v>2.9983127117157</v>
       </c>
       <c r="H106" t="n">
         <v>52000</v>
@@ -3472,7 +3472,7 @@
         <v>4</v>
       </c>
       <c r="G107" t="n">
-        <v>3.50167965888977</v>
+        <v>3.50167918205261</v>
       </c>
       <c r="H107" t="n">
         <v>164000</v>
@@ -3530,7 +3530,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G109" t="n">
-        <v>3.96565198898315</v>
+        <v>3.96565222740173</v>
       </c>
       <c r="H109" t="n">
         <v>596000</v>
@@ -3559,7 +3559,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>4.11447334289551</v>
+        <v>4.11447286605835</v>
       </c>
       <c r="H110" t="n">
         <v>568000</v>
@@ -3588,7 +3588,7 @@
         <v>4.375</v>
       </c>
       <c r="G111" t="n">
-        <v>3.82996225357056</v>
+        <v>3.82996201515198</v>
       </c>
       <c r="H111" t="n">
         <v>247000</v>
@@ -3617,7 +3617,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G112" t="n">
-        <v>3.64174652099609</v>
+        <v>3.64174628257751</v>
       </c>
       <c r="H112" t="n">
         <v>202000</v>
@@ -3646,7 +3646,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G113" t="n">
-        <v>3.52794218063354</v>
+        <v>3.52794241905212</v>
       </c>
       <c r="H113" t="n">
         <v>87000</v>
@@ -3704,7 +3704,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G115" t="n">
-        <v>3.77305912971497</v>
+        <v>3.77305936813354</v>
       </c>
       <c r="H115" t="n">
         <v>88000</v>
@@ -3733,7 +3733,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>3.97878289222717</v>
+        <v>3.97878313064575</v>
       </c>
       <c r="H116" t="n">
         <v>371000</v>
@@ -3762,7 +3762,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>3.91312623023987</v>
+        <v>3.91312670707703</v>
       </c>
       <c r="H117" t="n">
         <v>152000</v>
@@ -3791,7 +3791,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>3.86060214042664</v>
+        <v>3.86060118675232</v>
       </c>
       <c r="H118" t="n">
         <v>82000</v>
@@ -3820,7 +3820,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G119" t="n">
-        <v>3.79932236671448</v>
+        <v>3.79932260513306</v>
       </c>
       <c r="H119" t="n">
         <v>66000</v>
@@ -3878,7 +3878,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G121" t="n">
-        <v>3.89124131202698</v>
+        <v>3.89124155044556</v>
       </c>
       <c r="H121" t="n">
         <v>84000</v>
@@ -3907,7 +3907,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G122" t="n">
-        <v>3.92625784873962</v>
+        <v>3.92625832557678</v>
       </c>
       <c r="H122" t="n">
         <v>35000</v>
@@ -3965,7 +3965,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G124" t="n">
-        <v>4.1713752746582</v>
+        <v>4.17137575149536</v>
       </c>
       <c r="H124" t="n">
         <v>181000</v>
@@ -3994,7 +3994,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>4.18013000488281</v>
+        <v>4.18013048171997</v>
       </c>
       <c r="H125" t="n">
         <v>73000</v>
@@ -4081,7 +4081,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G128" t="n">
-        <v>4.16699886322021</v>
+        <v>4.16699838638306</v>
       </c>
       <c r="H128" t="n">
         <v>58000</v>
@@ -4139,7 +4139,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>3.97002863883972</v>
+        <v>3.97002911567688</v>
       </c>
       <c r="H130" t="n">
         <v>38000</v>
@@ -4168,7 +4168,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G131" t="n">
-        <v>4.04006242752075</v>
+        <v>4.04006290435791</v>
       </c>
       <c r="H131" t="n">
         <v>36000</v>
@@ -4197,7 +4197,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G132" t="n">
-        <v>4.00504541397095</v>
+        <v>4.00504589080811</v>
       </c>
       <c r="H132" t="n">
         <v>14000</v>
@@ -4226,7 +4226,7 @@
         <v>4.625</v>
       </c>
       <c r="G133" t="n">
-        <v>4.04881620407104</v>
+        <v>4.0488166809082</v>
       </c>
       <c r="H133" t="n">
         <v>7000</v>
@@ -4313,7 +4313,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G136" t="n">
-        <v>4.02255392074585</v>
+        <v>4.02255439758301</v>
       </c>
       <c r="H136" t="n">
         <v>19000</v>
@@ -4342,7 +4342,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G137" t="n">
-        <v>3.98753762245178</v>
+        <v>3.98753714561462</v>
       </c>
       <c r="H137" t="n">
         <v>27000</v>
@@ -4429,7 +4429,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G140" t="n">
-        <v>4.1363582611084</v>
+        <v>4.13635921478271</v>
       </c>
       <c r="H140" t="n">
         <v>97000</v>
@@ -4487,7 +4487,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G142" t="n">
-        <v>4.32895183563232</v>
+        <v>4.32895088195801</v>
       </c>
       <c r="H142" t="n">
         <v>162000</v>
@@ -4661,7 +4661,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>3.85184717178345</v>
+        <v>3.85184741020203</v>
       </c>
       <c r="H148" t="n">
         <v>192000</v>
@@ -4690,7 +4690,7 @@
         <v>4.625</v>
       </c>
       <c r="G149" t="n">
-        <v>4.04881620407104</v>
+        <v>4.0488166809082</v>
       </c>
       <c r="H149" t="n">
         <v>105000</v>
@@ -4719,7 +4719,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G150" t="n">
-        <v>3.78181385993958</v>
+        <v>3.781813621521</v>
       </c>
       <c r="H150" t="n">
         <v>94000</v>
@@ -4748,7 +4748,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G151" t="n">
-        <v>3.80369877815247</v>
+        <v>3.80369901657104</v>
       </c>
       <c r="H151" t="n">
         <v>89000</v>
@@ -4777,7 +4777,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>3.79932236671448</v>
+        <v>3.79932260513306</v>
       </c>
       <c r="H152" t="n">
         <v>69000</v>
@@ -4835,7 +4835,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G154" t="n">
-        <v>3.08147764205933</v>
+        <v>3.08147788047791</v>
       </c>
       <c r="H154" t="n">
         <v>57000</v>
@@ -4922,7 +4922,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G157" t="n">
-        <v>2.45555305480957</v>
+        <v>2.45555233955383</v>
       </c>
       <c r="H157" t="n">
         <v>83000</v>
@@ -4951,7 +4951,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>2.73130989074707</v>
+        <v>2.73130965232849</v>
       </c>
       <c r="H158" t="n">
         <v>60000</v>
@@ -4980,7 +4980,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>2.77508091926575</v>
+        <v>2.77508115768433</v>
       </c>
       <c r="H159" t="n">
         <v>58000</v>
@@ -5038,7 +5038,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G161" t="n">
-        <v>2.95891904830933</v>
+        <v>2.95891928672791</v>
       </c>
       <c r="H161" t="n">
         <v>30000</v>
@@ -5067,7 +5067,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G162" t="n">
-        <v>3.08147764205933</v>
+        <v>3.08147788047791</v>
       </c>
       <c r="H162" t="n">
         <v>37000</v>
@@ -5125,7 +5125,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G164" t="n">
-        <v>3.536696434021</v>
+        <v>3.53669619560242</v>
       </c>
       <c r="H164" t="n">
         <v>67000</v>
@@ -5154,7 +5154,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G165" t="n">
-        <v>3.58046722412109</v>
+        <v>3.58046746253967</v>
       </c>
       <c r="H165" t="n">
         <v>47000</v>
@@ -5183,7 +5183,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.75555109977722</v>
+        <v>3.75555086135864</v>
       </c>
       <c r="H166" t="n">
         <v>119000</v>
@@ -5212,7 +5212,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G167" t="n">
-        <v>3.71178007125854</v>
+        <v>3.71177983283997</v>
       </c>
       <c r="H167" t="n">
         <v>54000</v>
@@ -5241,7 +5241,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>3.62861514091492</v>
+        <v>3.62861490249634</v>
       </c>
       <c r="H168" t="n">
         <v>19000</v>
@@ -5270,7 +5270,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G169" t="n">
-        <v>3.60672926902771</v>
+        <v>3.60672950744629</v>
       </c>
       <c r="H169" t="n">
         <v>15000</v>
@@ -5299,7 +5299,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>3.66800904273987</v>
+        <v>3.66800928115845</v>
       </c>
       <c r="H170" t="n">
         <v>26000</v>
@@ -5386,7 +5386,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G173" t="n">
-        <v>3.95252060890198</v>
+        <v>3.95252084732056</v>
       </c>
       <c r="H173" t="n">
         <v>72000</v>
@@ -5415,7 +5415,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.85184717178345</v>
+        <v>3.85184741020203</v>
       </c>
       <c r="H174" t="n">
         <v>74000</v>
@@ -5444,7 +5444,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G175" t="n">
-        <v>3.94376635551453</v>
+        <v>3.94376683235168</v>
       </c>
       <c r="H175" t="n">
         <v>24000</v>
@@ -5473,7 +5473,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>4.07070255279541</v>
+        <v>4.07070207595825</v>
       </c>
       <c r="H176" t="n">
         <v>44000</v>
@@ -5502,7 +5502,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>4.07070255279541</v>
+        <v>4.07070207595825</v>
       </c>
       <c r="H177" t="n">
         <v>17000</v>
@@ -5531,7 +5531,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>3.68114066123962</v>
+        <v>3.68114042282104</v>
       </c>
       <c r="H178" t="n">
         <v>51000</v>
@@ -5560,7 +5560,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G179" t="n">
-        <v>3.70302605628967</v>
+        <v>3.70302581787109</v>
       </c>
       <c r="H179" t="n">
         <v>30000</v>
@@ -5589,7 +5589,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G180" t="n">
-        <v>3.83433866500854</v>
+        <v>3.83433890342712</v>
       </c>
       <c r="H180" t="n">
         <v>29000</v>
@@ -5618,7 +5618,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G181" t="n">
-        <v>3.8781099319458</v>
+        <v>3.87810969352722</v>
       </c>
       <c r="H181" t="n">
         <v>9000</v>
@@ -5647,7 +5647,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G182" t="n">
-        <v>3.70302605628967</v>
+        <v>3.70302581787109</v>
       </c>
       <c r="H182" t="n">
         <v>15000</v>
@@ -5676,7 +5676,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>3.80807638168335</v>
+        <v>3.80807614326477</v>
       </c>
       <c r="H183" t="n">
         <v>2000</v>
@@ -5705,7 +5705,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>3.85184717178345</v>
+        <v>3.85184741020203</v>
       </c>
       <c r="H184" t="n">
         <v>8000</v>
@@ -5734,7 +5734,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G185" t="n">
-        <v>3.79056787490845</v>
+        <v>3.79056763648987</v>
       </c>
       <c r="H185" t="n">
         <v>4000</v>
@@ -5763,7 +5763,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>3.86935591697693</v>
+        <v>3.86935544013977</v>
       </c>
       <c r="H186" t="n">
         <v>15000</v>
@@ -5792,7 +5792,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G187" t="n">
-        <v>3.86060214042664</v>
+        <v>3.86060118675232</v>
       </c>
       <c r="H187" t="n">
         <v>5000</v>
@@ -5821,7 +5821,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>3.77743697166443</v>
+        <v>3.77743673324585</v>
       </c>
       <c r="H188" t="n">
         <v>7000</v>
@@ -5850,7 +5850,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G189" t="n">
-        <v>3.75117373466492</v>
+        <v>3.75117421150208</v>
       </c>
       <c r="H189" t="n">
         <v>22000</v>
@@ -5879,7 +5879,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G190" t="n">
-        <v>3.78224921226501</v>
+        <v>3.78224873542786</v>
       </c>
       <c r="H190" t="n">
         <v>11000</v>
@@ -5908,7 +5908,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>3.72897744178772</v>
+        <v>3.7289776802063</v>
       </c>
       <c r="H191" t="n">
         <v>5000</v>
@@ -5966,7 +5966,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G193" t="n">
-        <v>3.666827917099</v>
+        <v>3.66682815551758</v>
       </c>
       <c r="H193" t="n">
         <v>9000</v>
@@ -5995,7 +5995,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G194" t="n">
-        <v>3.74673438072205</v>
+        <v>3.74673461914062</v>
       </c>
       <c r="H194" t="n">
         <v>3000</v>
@@ -6024,7 +6024,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G195" t="n">
-        <v>3.78224921226501</v>
+        <v>3.78224873542786</v>
       </c>
       <c r="H195" t="n">
         <v>8000</v>
@@ -6053,7 +6053,7 @@
         <v>4.25</v>
       </c>
       <c r="G196" t="n">
-        <v>3.77337026596069</v>
+        <v>3.77337002754211</v>
       </c>
       <c r="H196" t="n">
         <v>7000</v>
@@ -6082,7 +6082,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>3.7911274433136</v>
+        <v>3.79112720489502</v>
       </c>
       <c r="H197" t="n">
         <v>2000</v>
@@ -6140,7 +6140,7 @@
         <v>4.5</v>
       </c>
       <c r="G199" t="n">
-        <v>3.99533367156982</v>
+        <v>3.99533343315125</v>
       </c>
       <c r="H199" t="n">
         <v>99000</v>
@@ -6169,7 +6169,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G200" t="n">
-        <v>3.86215543746948</v>
+        <v>3.8621551990509</v>
       </c>
       <c r="H200" t="n">
         <v>46000</v>
@@ -6198,7 +6198,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G201" t="n">
-        <v>3.83552050590515</v>
+        <v>3.83551979064941</v>
       </c>
       <c r="H201" t="n">
         <v>15000</v>
@@ -6285,7 +6285,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G204" t="n">
-        <v>3.82220220565796</v>
+        <v>3.82220196723938</v>
       </c>
       <c r="H204" t="n">
         <v>7000</v>
@@ -6314,7 +6314,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G205" t="n">
-        <v>3.82220220565796</v>
+        <v>3.82220196723938</v>
       </c>
       <c r="H205" t="n">
         <v>12000</v>
@@ -6343,7 +6343,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G206" t="n">
-        <v>3.80888438224792</v>
+        <v>3.80888414382935</v>
       </c>
       <c r="H206" t="n">
         <v>6000</v>
@@ -6372,7 +6372,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>3.72897744178772</v>
+        <v>3.7289776802063</v>
       </c>
       <c r="H207" t="n">
         <v>6000</v>
@@ -6401,7 +6401,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90654802322388</v>
+        <v>3.90654826164246</v>
       </c>
       <c r="H208" t="n">
         <v>30000</v>
@@ -6430,7 +6430,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>3.86215543746948</v>
+        <v>3.8621551990509</v>
       </c>
       <c r="H209" t="n">
         <v>8000</v>
@@ -6459,7 +6459,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>3.86215543746948</v>
+        <v>3.8621551990509</v>
       </c>
       <c r="H210" t="n">
         <v>2000</v>
@@ -6575,7 +6575,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>3.80888438224792</v>
+        <v>3.80888414382935</v>
       </c>
       <c r="H214" t="n">
         <v>28000</v>
@@ -6604,7 +6604,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>4.03084754943848</v>
+        <v>4.03084707260132</v>
       </c>
       <c r="H215" t="n">
         <v>41000</v>
@@ -6633,7 +6633,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G216" t="n">
-        <v>3.9154269695282</v>
+        <v>3.91542625427246</v>
       </c>
       <c r="H216" t="n">
         <v>19000</v>
@@ -6662,7 +6662,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G217" t="n">
-        <v>3.94206237792969</v>
+        <v>3.94206213951111</v>
       </c>
       <c r="H217" t="n">
         <v>13000</v>
@@ -6691,7 +6691,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G218" t="n">
-        <v>3.96425914764404</v>
+        <v>3.96425867080688</v>
       </c>
       <c r="H218" t="n">
         <v>43000</v>
@@ -6720,7 +6720,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>3.95094060897827</v>
+        <v>3.95094037055969</v>
       </c>
       <c r="H219" t="n">
         <v>12000</v>
@@ -6749,7 +6749,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>4.01752948760986</v>
+        <v>4.01752996444702</v>
       </c>
       <c r="H220" t="n">
         <v>10000</v>
@@ -6923,7 +6923,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G226" t="n">
-        <v>4.00421237945557</v>
+        <v>4.00421142578125</v>
       </c>
       <c r="H226" t="n">
         <v>2000</v>
@@ -6952,7 +6952,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>3.97313690185547</v>
+        <v>3.97313737869263</v>
       </c>
       <c r="H227" t="n">
         <v>9000</v>
@@ -6981,7 +6981,7 @@
         <v>4.5</v>
       </c>
       <c r="G228" t="n">
-        <v>3.99533367156982</v>
+        <v>3.99533343315125</v>
       </c>
       <c r="H228" t="n">
         <v>7000</v>
@@ -7010,7 +7010,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>4.01309061050415</v>
+        <v>4.01309013366699</v>
       </c>
       <c r="H229" t="n">
         <v>13000</v>
@@ -7039,7 +7039,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G230" t="n">
-        <v>3.98645448684692</v>
+        <v>3.9864547252655</v>
       </c>
       <c r="H230" t="n">
         <v>16000</v>
@@ -7097,7 +7097,7 @@
         <v>4.5</v>
       </c>
       <c r="G232" t="n">
-        <v>3.99533367156982</v>
+        <v>3.99533343315125</v>
       </c>
       <c r="H232" t="n">
         <v>19000</v>
@@ -7184,7 +7184,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G235" t="n">
-        <v>4.08411884307861</v>
+        <v>4.08411836624146</v>
       </c>
       <c r="H235" t="n">
         <v>10000</v>
@@ -7271,7 +7271,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.48365211486816</v>
+        <v>4.48365163803101</v>
       </c>
       <c r="H238" t="n">
         <v>99000</v>
@@ -7300,7 +7300,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>4.40374565124512</v>
+        <v>4.40374517440796</v>
       </c>
       <c r="H239" t="n">
         <v>37000</v>
@@ -7358,7 +7358,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>4.3327169418335</v>
+        <v>4.33271741867065</v>
       </c>
       <c r="H241" t="n">
         <v>24000</v>
@@ -7387,7 +7387,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G242" t="n">
-        <v>4.41262340545654</v>
+        <v>4.4126238822937</v>
       </c>
       <c r="H242" t="n">
         <v>26000</v>
@@ -7445,7 +7445,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G244" t="n">
-        <v>4.16846418380737</v>
+        <v>4.16846466064453</v>
       </c>
       <c r="H244" t="n">
         <v>27000</v>
@@ -7474,7 +7474,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G245" t="n">
-        <v>4.24393177032471</v>
+        <v>4.24393224716187</v>
       </c>
       <c r="H245" t="n">
         <v>12000</v>
@@ -7503,7 +7503,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>4.3105206489563</v>
+        <v>4.31052017211914</v>
       </c>
       <c r="H246" t="n">
         <v>21000</v>
@@ -7532,7 +7532,7 @@
         <v>4.875</v>
       </c>
       <c r="G247" t="n">
-        <v>4.32827758789062</v>
+        <v>4.32827711105347</v>
       </c>
       <c r="H247" t="n">
         <v>9000</v>
@@ -7561,7 +7561,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>4.26168870925903</v>
+        <v>4.26168918609619</v>
       </c>
       <c r="H248" t="n">
         <v>29000</v>
@@ -7590,7 +7590,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G249" t="n">
-        <v>4.26168870925903</v>
+        <v>4.26168918609619</v>
       </c>
       <c r="H249" t="n">
         <v>15000</v>
@@ -7677,7 +7677,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G252" t="n">
-        <v>4.02196931838989</v>
+        <v>4.02196884155273</v>
       </c>
       <c r="H252" t="n">
         <v>35000</v>
@@ -7706,7 +7706,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G253" t="n">
-        <v>3.86215543746948</v>
+        <v>3.8621551990509</v>
       </c>
       <c r="H253" t="n">
         <v>21000</v>
@@ -7735,7 +7735,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G254" t="n">
-        <v>3.88879132270813</v>
+        <v>3.88879084587097</v>
       </c>
       <c r="H254" t="n">
         <v>21000</v>
@@ -7764,7 +7764,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G255" t="n">
-        <v>3.96425914764404</v>
+        <v>3.96425867080688</v>
       </c>
       <c r="H255" t="n">
         <v>2000</v>
@@ -7822,7 +7822,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>4.28832387924194</v>
+        <v>4.2883243560791</v>
       </c>
       <c r="H257" t="n">
         <v>48000</v>
@@ -7851,7 +7851,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>4.19953870773315</v>
+        <v>4.19953918457031</v>
       </c>
       <c r="H258" t="n">
         <v>30000</v>
@@ -7880,7 +7880,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>4.15070724487305</v>
+        <v>4.15070772171021</v>
       </c>
       <c r="H259" t="n">
         <v>48000</v>
@@ -7909,7 +7909,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>4.19509935379028</v>
+        <v>4.19509983062744</v>
       </c>
       <c r="H260" t="n">
         <v>17000</v>
@@ -7967,7 +7967,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G262" t="n">
-        <v>4.08855772018433</v>
+        <v>4.08855819702148</v>
       </c>
       <c r="H262" t="n">
         <v>17000</v>
@@ -7996,7 +7996,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>4.01309061050415</v>
+        <v>4.01309013366699</v>
       </c>
       <c r="H263" t="n">
         <v>9000</v>
@@ -8025,7 +8025,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G264" t="n">
-        <v>4.05748319625854</v>
+        <v>4.05748271942139</v>
       </c>
       <c r="H264" t="n">
         <v>17000</v>
@@ -8054,7 +8054,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G265" t="n">
-        <v>4.03528642654419</v>
+        <v>4.03528690338135</v>
       </c>
       <c r="H265" t="n">
         <v>8000</v>
@@ -8112,7 +8112,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>4.08411884307861</v>
+        <v>4.08411836624146</v>
       </c>
       <c r="H267" t="n">
         <v>3000</v>
@@ -8141,7 +8141,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G268" t="n">
-        <v>4.05748319625854</v>
+        <v>4.05748271942139</v>
       </c>
       <c r="H268" t="n">
         <v>4000</v>
@@ -8170,7 +8170,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G269" t="n">
-        <v>3.94206237792969</v>
+        <v>3.94206213951111</v>
       </c>
       <c r="H269" t="n">
         <v>21000</v>
@@ -8199,7 +8199,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>3.90654802322388</v>
+        <v>3.90654826164246</v>
       </c>
       <c r="H270" t="n">
         <v>13000</v>
@@ -8228,7 +8228,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G271" t="n">
-        <v>3.95094060897827</v>
+        <v>3.95094037055969</v>
       </c>
       <c r="H271" t="n">
         <v>7000</v>
@@ -8315,7 +8315,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G274" t="n">
-        <v>3.95538020133972</v>
+        <v>3.9553804397583</v>
       </c>
       <c r="H274" t="n">
         <v>2000</v>
@@ -8344,7 +8344,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G275" t="n">
-        <v>3.89766955375671</v>
+        <v>3.89766931533813</v>
       </c>
       <c r="H275" t="n">
         <v>17000</v>
@@ -8373,7 +8373,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G276" t="n">
-        <v>3.84439873695374</v>
+        <v>3.84439826011658</v>
       </c>
       <c r="H276" t="n">
         <v>17000</v>
@@ -8489,7 +8489,7 @@
         <v>4.25</v>
       </c>
       <c r="G280" t="n">
-        <v>3.77337026596069</v>
+        <v>3.77337002754211</v>
       </c>
       <c r="H280" t="n">
         <v>5000</v>
@@ -8518,7 +8518,7 @@
         <v>4.25</v>
       </c>
       <c r="G281" t="n">
-        <v>3.77337026596069</v>
+        <v>3.77337002754211</v>
       </c>
       <c r="H281" t="n">
         <v>4000</v>
@@ -8547,7 +8547,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>3.81332397460938</v>
+        <v>3.8133237361908</v>
       </c>
       <c r="H282" t="n">
         <v>8000</v>
@@ -8634,7 +8634,7 @@
         <v>4.25</v>
       </c>
       <c r="G285" t="n">
-        <v>3.77337026596069</v>
+        <v>3.77337002754211</v>
       </c>
       <c r="H285" t="n">
         <v>8000</v>
@@ -8663,7 +8663,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>3.72897744178772</v>
+        <v>3.7289776802063</v>
       </c>
       <c r="H286" t="n">
         <v>12000</v>
@@ -8721,7 +8721,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G288" t="n">
-        <v>3.74673438072205</v>
+        <v>3.74673461914062</v>
       </c>
       <c r="H288" t="n">
         <v>1000</v>
@@ -8750,7 +8750,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G289" t="n">
-        <v>3.74673438072205</v>
+        <v>3.74673461914062</v>
       </c>
       <c r="H289" t="n">
         <v>2000</v>
@@ -8837,7 +8837,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G292" t="n">
-        <v>3.80888438224792</v>
+        <v>3.80888414382935</v>
       </c>
       <c r="H292" t="n">
         <v>14000</v>
@@ -8866,7 +8866,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G293" t="n">
-        <v>3.82220220565796</v>
+        <v>3.82220196723938</v>
       </c>
       <c r="H293" t="n">
         <v>28000</v>
@@ -8924,7 +8924,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>3.69790267944336</v>
+        <v>3.69790291786194</v>
       </c>
       <c r="H295" t="n">
         <v>13000</v>
@@ -9069,7 +9069,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G300" t="n">
-        <v>3.59136056900024</v>
+        <v>3.59136080741882</v>
       </c>
       <c r="H300" t="n">
         <v>6000</v>
@@ -9185,7 +9185,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G304" t="n">
-        <v>3.65794920921326</v>
+        <v>3.65794944763184</v>
       </c>
       <c r="H304" t="n">
         <v>1000</v>
@@ -9214,7 +9214,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>3.64019227027893</v>
+        <v>3.64019250869751</v>
       </c>
       <c r="H305" t="n">
         <v>4000</v>
@@ -9272,7 +9272,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G307" t="n">
-        <v>3.62243556976318</v>
+        <v>3.6224353313446</v>
       </c>
       <c r="H307" t="n">
         <v>16000</v>
@@ -9417,7 +9417,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G312" t="n">
-        <v>3.46262216567993</v>
+        <v>3.46262240409851</v>
       </c>
       <c r="H312" t="n">
         <v>4000</v>
@@ -9504,7 +9504,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G315" t="n">
-        <v>3.3338840007782</v>
+        <v>3.33388376235962</v>
       </c>
       <c r="H315" t="n">
         <v>16000</v>
@@ -9591,7 +9591,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G318" t="n">
-        <v>3.19626617431641</v>
+        <v>3.19626665115356</v>
       </c>
       <c r="H318" t="n">
         <v>6000</v>
@@ -9620,7 +9620,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>3.19626617431641</v>
+        <v>3.19626665115356</v>
       </c>
       <c r="H319" t="n">
         <v>1000</v>
@@ -9649,7 +9649,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G320" t="n">
-        <v>3.16075253486633</v>
+        <v>3.16075277328491</v>
       </c>
       <c r="H320" t="n">
         <v>3000</v>
@@ -9678,7 +9678,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G321" t="n">
-        <v>3.09860324859619</v>
+        <v>3.09860301017761</v>
       </c>
       <c r="H321" t="n">
         <v>6000</v>
@@ -9707,7 +9707,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G322" t="n">
-        <v>3.1651918888092</v>
+        <v>3.16519212722778</v>
       </c>
       <c r="H322" t="n">
         <v>4000</v>
@@ -9736,7 +9736,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>3.24065899848938</v>
+        <v>3.24065923690796</v>
       </c>
       <c r="H323" t="n">
         <v>3000</v>
@@ -9794,7 +9794,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>3.19626617431641</v>
+        <v>3.19626665115356</v>
       </c>
       <c r="H325" t="n">
         <v>8000</v>
@@ -9823,7 +9823,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G326" t="n">
-        <v>3.16075253486633</v>
+        <v>3.16075277328491</v>
       </c>
       <c r="H326" t="n">
         <v>7000</v>
@@ -9852,7 +9852,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G327" t="n">
-        <v>3.19626617431641</v>
+        <v>3.19626665115356</v>
       </c>
       <c r="H327" t="n">
         <v>6000</v>
@@ -9910,7 +9910,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G329" t="n">
-        <v>3.17407035827637</v>
+        <v>3.17407059669495</v>
       </c>
       <c r="H329" t="n">
         <v>5000</v>
@@ -9939,7 +9939,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G330" t="n">
-        <v>3.19182729721069</v>
+        <v>3.19182753562927</v>
       </c>
       <c r="H330" t="n">
         <v>20000</v>
@@ -10026,7 +10026,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G333" t="n">
-        <v>3.49813652038574</v>
+        <v>3.49813628196716</v>
       </c>
       <c r="H333" t="n">
         <v>5000</v>
@@ -10055,7 +10055,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>3.46262216567993</v>
+        <v>3.46262240409851</v>
       </c>
       <c r="H334" t="n">
         <v>5000</v>
@@ -10084,7 +10084,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>3.46262216567993</v>
+        <v>3.46262240409851</v>
       </c>
       <c r="H335" t="n">
         <v>11000</v>
@@ -10113,7 +10113,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>3.38271546363831</v>
+        <v>3.38271522521973</v>
       </c>
       <c r="H336" t="n">
         <v>4000</v>
@@ -10200,7 +10200,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G339" t="n">
-        <v>3.61799597740173</v>
+        <v>3.61799621582031</v>
       </c>
       <c r="H339" t="n">
         <v>32000</v>
@@ -10229,7 +10229,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G340" t="n">
-        <v>3.81332397460938</v>
+        <v>3.8133237361908</v>
       </c>
       <c r="H340" t="n">
         <v>152000</v>
@@ -10258,7 +10258,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>3.64019227027893</v>
+        <v>3.64019250869751</v>
       </c>
       <c r="H341" t="n">
         <v>43000</v>
@@ -10287,7 +10287,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G342" t="n">
-        <v>3.64907097816467</v>
+        <v>3.64907121658325</v>
       </c>
       <c r="H342" t="n">
         <v>9000</v>
@@ -10403,7 +10403,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G346" t="n">
-        <v>3.56028580665588</v>
+        <v>3.56028604507446</v>
       </c>
       <c r="H346" t="n">
         <v>11000</v>
@@ -10461,7 +10461,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G348" t="n">
-        <v>3.74673438072205</v>
+        <v>3.74673461914062</v>
       </c>
       <c r="H348" t="n">
         <v>35000</v>
@@ -10548,7 +10548,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G351" t="n">
-        <v>3.95094060897827</v>
+        <v>3.95094037055969</v>
       </c>
       <c r="H351" t="n">
         <v>52000</v>
@@ -10635,7 +10635,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>4.03084754943848</v>
+        <v>4.03084707260132</v>
       </c>
       <c r="H354" t="n">
         <v>28000</v>
@@ -10664,7 +10664,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G355" t="n">
-        <v>3.9154269695282</v>
+        <v>3.91542625427246</v>
       </c>
       <c r="H355" t="n">
         <v>77000</v>
@@ -10693,7 +10693,7 @@
         <v>4.5</v>
       </c>
       <c r="G356" t="n">
-        <v>3.99533367156982</v>
+        <v>3.99533343315125</v>
       </c>
       <c r="H356" t="n">
         <v>22000</v>
@@ -10722,7 +10722,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>3.97313690185547</v>
+        <v>3.97313737869263</v>
       </c>
       <c r="H357" t="n">
         <v>25000</v>
@@ -10751,7 +10751,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G358" t="n">
-        <v>3.99977278709412</v>
+        <v>3.9997730255127</v>
       </c>
       <c r="H358" t="n">
         <v>13000</v>
@@ -10780,7 +10780,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G359" t="n">
-        <v>3.90210914611816</v>
+        <v>3.90210866928101</v>
       </c>
       <c r="H359" t="n">
         <v>11000</v>
@@ -10809,7 +10809,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G360" t="n">
-        <v>3.90654802322388</v>
+        <v>3.90654826164246</v>
       </c>
       <c r="H360" t="n">
         <v>11000</v>
@@ -10838,7 +10838,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>3.96425914764404</v>
+        <v>3.96425867080688</v>
       </c>
       <c r="H361" t="n">
         <v>20000</v>
@@ -10867,7 +10867,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>3.92874431610107</v>
+        <v>3.92874455451965</v>
       </c>
       <c r="H362" t="n">
         <v>34000</v>
@@ -10896,7 +10896,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>3.98201584815979</v>
+        <v>3.98201608657837</v>
       </c>
       <c r="H363" t="n">
         <v>37000</v>
@@ -10925,7 +10925,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G364" t="n">
-        <v>3.9686975479126</v>
+        <v>3.96869778633118</v>
       </c>
       <c r="H364" t="n">
         <v>5000</v>
@@ -10954,7 +10954,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G365" t="n">
-        <v>3.98645448684692</v>
+        <v>3.9864547252655</v>
       </c>
       <c r="H365" t="n">
         <v>4000</v>
@@ -10983,7 +10983,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G366" t="n">
-        <v>3.99977278709412</v>
+        <v>3.9997730255127</v>
       </c>
       <c r="H366" t="n">
         <v>31000</v>
@@ -11012,7 +11012,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>3.96425914764404</v>
+        <v>3.96425867080688</v>
       </c>
       <c r="H367" t="n">
         <v>13000</v>
@@ -11041,7 +11041,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G368" t="n">
-        <v>3.99977278709412</v>
+        <v>3.9997730255127</v>
       </c>
       <c r="H368" t="n">
         <v>61000</v>
@@ -11070,7 +11070,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>3.97313690185547</v>
+        <v>3.97313737869263</v>
       </c>
       <c r="H369" t="n">
         <v>37000</v>
@@ -11099,7 +11099,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>3.85327744483948</v>
+        <v>3.8532772064209</v>
       </c>
       <c r="H370" t="n">
         <v>50000</v>
@@ -11128,7 +11128,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G371" t="n">
-        <v>3.76449179649353</v>
+        <v>3.76449155807495</v>
       </c>
       <c r="H371" t="n">
         <v>26000</v>
@@ -11215,7 +11215,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G374" t="n">
-        <v>3.76449179649353</v>
+        <v>3.76449155807495</v>
       </c>
       <c r="H374" t="n">
         <v>7000</v>
@@ -11273,7 +11273,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G376" t="n">
-        <v>3.76449179649353</v>
+        <v>3.76449155807495</v>
       </c>
       <c r="H376" t="n">
         <v>12000</v>
@@ -11302,7 +11302,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G377" t="n">
-        <v>3.72897744178772</v>
+        <v>3.7289776802063</v>
       </c>
       <c r="H377" t="n">
         <v>16000</v>
@@ -11360,7 +11360,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>3.64019227027893</v>
+        <v>3.64019250869751</v>
       </c>
       <c r="H379" t="n">
         <v>43000</v>
@@ -11389,7 +11389,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G380" t="n">
-        <v>3.51589345932007</v>
+        <v>3.51589322090149</v>
       </c>
       <c r="H380" t="n">
         <v>16000</v>
@@ -11418,7 +11418,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>3.51589345932007</v>
+        <v>3.51589322090149</v>
       </c>
       <c r="H381" t="n">
         <v>21000</v>
@@ -11505,7 +11505,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G384" t="n">
-        <v>3.64019227027893</v>
+        <v>3.64019250869751</v>
       </c>
       <c r="H384" t="n">
         <v>15000</v>
@@ -11534,7 +11534,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G385" t="n">
-        <v>3.6046781539917</v>
+        <v>3.60467839241028</v>
       </c>
       <c r="H385" t="n">
         <v>23000</v>
@@ -11650,7 +11650,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G389" t="n">
-        <v>3.64907097816467</v>
+        <v>3.64907121658325</v>
       </c>
       <c r="H389" t="n">
         <v>25000</v>
@@ -11679,7 +11679,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>3.7911274433136</v>
+        <v>3.79112720489502</v>
       </c>
       <c r="H390" t="n">
         <v>21000</v>
@@ -11708,7 +11708,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G391" t="n">
-        <v>3.90210914611816</v>
+        <v>3.90210866928101</v>
       </c>
       <c r="H391" t="n">
         <v>56000</v>
@@ -11737,7 +11737,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G392" t="n">
-        <v>3.75561356544495</v>
+        <v>3.75561332702637</v>
       </c>
       <c r="H392" t="n">
         <v>102000</v>
@@ -11766,7 +11766,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G393" t="n">
-        <v>3.62243556976318</v>
+        <v>3.6224353313446</v>
       </c>
       <c r="H393" t="n">
         <v>30000</v>
@@ -11911,7 +11911,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G398" t="n">
-        <v>3.56028580665588</v>
+        <v>3.56028604507446</v>
       </c>
       <c r="H398" t="n">
         <v>24000</v>
@@ -11940,7 +11940,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>3.59136056900024</v>
+        <v>3.59136080741882</v>
       </c>
       <c r="H399" t="n">
         <v>54000</v>
@@ -12056,7 +12056,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G403" t="n">
-        <v>3.56472492218018</v>
+        <v>3.56472516059875</v>
       </c>
       <c r="H403" t="n">
         <v>20000</v>
@@ -12114,7 +12114,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G405" t="n">
-        <v>3.53808951377869</v>
+        <v>3.53808927536011</v>
       </c>
       <c r="H405" t="n">
         <v>9000</v>
@@ -12230,7 +12230,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>3.61799597740173</v>
+        <v>3.61799621582031</v>
       </c>
       <c r="H409" t="n">
         <v>25000</v>
@@ -12259,7 +12259,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G410" t="n">
-        <v>3.6046781539917</v>
+        <v>3.60467839241028</v>
       </c>
       <c r="H410" t="n">
         <v>28000</v>
@@ -12375,7 +12375,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G414" t="n">
-        <v>3.6046781539917</v>
+        <v>3.60467839241028</v>
       </c>
       <c r="H414" t="n">
         <v>8000</v>
@@ -12462,7 +12462,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G417" t="n">
-        <v>3.64552760124207</v>
+        <v>3.64552783966064</v>
       </c>
       <c r="H417" t="n">
         <v>9000</v>
@@ -12549,7 +12549,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G420" t="n">
-        <v>3.65462970733643</v>
+        <v>3.654629945755</v>
       </c>
       <c r="H420" t="n">
         <v>23000</v>
@@ -12578,7 +12578,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G421" t="n">
-        <v>3.69559073448181</v>
+        <v>3.69559097290039</v>
       </c>
       <c r="H421" t="n">
         <v>9000</v>
@@ -12607,7 +12607,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G422" t="n">
-        <v>3.69559073448181</v>
+        <v>3.69559097290039</v>
       </c>
       <c r="H422" t="n">
         <v>2000</v>
@@ -12636,7 +12636,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G423" t="n">
-        <v>3.70014214515686</v>
+        <v>3.70014238357544</v>
       </c>
       <c r="H423" t="n">
         <v>9000</v>
@@ -12694,7 +12694,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>3.75020527839661</v>
+        <v>3.75020551681519</v>
       </c>
       <c r="H425" t="n">
         <v>18000</v>
@@ -12723,7 +12723,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G426" t="n">
-        <v>3.75930786132812</v>
+        <v>3.7593080997467</v>
       </c>
       <c r="H426" t="n">
         <v>5000</v>
@@ -12752,7 +12752,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>3.73200058937073</v>
+        <v>3.73200082778931</v>
       </c>
       <c r="H427" t="n">
         <v>10000</v>
@@ -12955,7 +12955,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>3.65918111801147</v>
+        <v>3.65918135643005</v>
       </c>
       <c r="H434" t="n">
         <v>20000</v>
@@ -13042,7 +13042,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G437" t="n">
-        <v>3.75930786132812</v>
+        <v>3.7593080997467</v>
       </c>
       <c r="H437" t="n">
         <v>23000</v>
@@ -13129,7 +13129,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G440" t="n">
-        <v>3.74110317230225</v>
+        <v>3.74110341072083</v>
       </c>
       <c r="H440" t="n">
         <v>16000</v>
@@ -13158,7 +13158,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>3.73200058937073</v>
+        <v>3.73200082778931</v>
       </c>
       <c r="H441" t="n">
         <v>17000</v>
@@ -13187,7 +13187,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G442" t="n">
-        <v>3.73200058937073</v>
+        <v>3.73200082778931</v>
       </c>
       <c r="H442" t="n">
         <v>19000</v>
@@ -13245,7 +13245,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G444" t="n">
-        <v>3.74110317230225</v>
+        <v>3.74110341072083</v>
       </c>
       <c r="H444" t="n">
         <v>23000</v>
@@ -13274,7 +13274,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G445" t="n">
-        <v>3.75020527839661</v>
+        <v>3.75020551681519</v>
       </c>
       <c r="H445" t="n">
         <v>7000</v>
@@ -13332,7 +13332,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G447" t="n">
-        <v>3.73200058937073</v>
+        <v>3.73200082778931</v>
       </c>
       <c r="H447" t="n">
         <v>10000</v>
@@ -13390,7 +13390,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G449" t="n">
-        <v>3.75930786132812</v>
+        <v>3.7593080997467</v>
       </c>
       <c r="H449" t="n">
         <v>17000</v>
@@ -13419,7 +13419,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G450" t="n">
-        <v>3.75020527839661</v>
+        <v>3.75020551681519</v>
       </c>
       <c r="H450" t="n">
         <v>8000</v>
@@ -13477,7 +13477,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G452" t="n">
-        <v>3.75020527839661</v>
+        <v>3.75020551681519</v>
       </c>
       <c r="H452" t="n">
         <v>7000</v>
@@ -13506,7 +13506,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G453" t="n">
-        <v>3.74110317230225</v>
+        <v>3.74110341072083</v>
       </c>
       <c r="H453" t="n">
         <v>6000</v>
@@ -13564,7 +13564,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>3.69559073448181</v>
+        <v>3.69559097290039</v>
       </c>
       <c r="H455" t="n">
         <v>6000</v>
@@ -13622,7 +13622,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G457" t="n">
-        <v>3.65918111801147</v>
+        <v>3.65918135643005</v>
       </c>
       <c r="H457" t="n">
         <v>15000</v>
@@ -13738,7 +13738,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G461" t="n">
-        <v>3.65918111801147</v>
+        <v>3.65918135643005</v>
       </c>
       <c r="H461" t="n">
         <v>12000</v>
@@ -13767,7 +13767,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G462" t="n">
-        <v>3.50443983078003</v>
+        <v>3.50443959236145</v>
       </c>
       <c r="H462" t="n">
         <v>214000</v>
@@ -13825,7 +13825,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G464" t="n">
-        <v>3.50443983078003</v>
+        <v>3.50443959236145</v>
       </c>
       <c r="H464" t="n">
         <v>24000</v>
@@ -13854,7 +13854,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G465" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H465" t="n">
         <v>17000</v>
@@ -13883,7 +13883,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G466" t="n">
-        <v>3.42251777648926</v>
+        <v>3.42251753807068</v>
       </c>
       <c r="H466" t="n">
         <v>3000</v>
@@ -13941,7 +13941,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H468" t="n">
         <v>2000</v>
@@ -13970,7 +13970,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H469" t="n">
         <v>12000</v>
@@ -14028,7 +14028,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G471" t="n">
-        <v>3.42251777648926</v>
+        <v>3.42251753807068</v>
       </c>
       <c r="H471" t="n">
         <v>13000</v>
@@ -14115,7 +14115,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G474" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H474" t="n">
         <v>10000</v>
@@ -14144,7 +14144,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H475" t="n">
         <v>14000</v>
@@ -14289,7 +14289,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H480" t="n">
         <v>5000</v>
@@ -14347,7 +14347,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G482" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H482" t="n">
         <v>10000</v>
@@ -14376,7 +14376,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G483" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H483" t="n">
         <v>2000</v>
@@ -14405,7 +14405,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G484" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H484" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H486" t="n">
         <v>11000</v>
@@ -14492,7 +14492,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G487" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H487" t="n">
         <v>0</v>
@@ -14695,7 +14695,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G494" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H494" t="n">
         <v>37000</v>
@@ -14782,7 +14782,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G497" t="n">
-        <v>3.50443983078003</v>
+        <v>3.50443959236145</v>
       </c>
       <c r="H497" t="n">
         <v>6000</v>
@@ -14927,7 +14927,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G502" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H502" t="n">
         <v>4000</v>
@@ -15188,7 +15188,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G511" t="n">
-        <v>3.42251777648926</v>
+        <v>3.42251753807068</v>
       </c>
       <c r="H511" t="n">
         <v>3000</v>
@@ -15246,7 +15246,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G513" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H513" t="n">
         <v>17000</v>
@@ -15304,7 +15304,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H515" t="n">
         <v>12000</v>
@@ -15333,7 +15333,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G516" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H516" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G518" t="n">
-        <v>3.3770055770874</v>
+        <v>3.37700533866882</v>
       </c>
       <c r="H518" t="n">
         <v>6000</v>
@@ -15478,7 +15478,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G521" t="n">
-        <v>3.28598093986511</v>
+        <v>3.28598117828369</v>
       </c>
       <c r="H521" t="n">
         <v>14000</v>
@@ -15507,7 +15507,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G522" t="n">
-        <v>3.27687835693359</v>
+        <v>3.27687859535217</v>
       </c>
       <c r="H522" t="n">
         <v>9000</v>
@@ -15536,7 +15536,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G523" t="n">
-        <v>3.25867366790771</v>
+        <v>3.25867390632629</v>
       </c>
       <c r="H523" t="n">
         <v>9000</v>
@@ -15739,7 +15739,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G530" t="n">
-        <v>3.28598093986511</v>
+        <v>3.28598117828369</v>
       </c>
       <c r="H530" t="n">
         <v>17000</v>
@@ -15768,7 +15768,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G531" t="n">
-        <v>3.28598093986511</v>
+        <v>3.28598117828369</v>
       </c>
       <c r="H531" t="n">
         <v>19000</v>
@@ -15797,7 +15797,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G532" t="n">
-        <v>3.27687835693359</v>
+        <v>3.27687859535217</v>
       </c>
       <c r="H532" t="n">
         <v>15000</v>
@@ -15855,7 +15855,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G534" t="n">
-        <v>3.28598093986511</v>
+        <v>3.28598117828369</v>
       </c>
       <c r="H534" t="n">
         <v>4000</v>
@@ -15913,7 +15913,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G536" t="n">
-        <v>3.27687835693359</v>
+        <v>3.27687859535217</v>
       </c>
       <c r="H536" t="n">
         <v>10000</v>
@@ -16551,7 +16551,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G558" t="n">
-        <v>2.86726880073547</v>
+        <v>2.86726903915405</v>
       </c>
       <c r="H558" t="n">
         <v>39000</v>
@@ -16609,7 +16609,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G560" t="n">
-        <v>2.81265425682068</v>
+        <v>2.8126540184021</v>
       </c>
       <c r="H560" t="n">
         <v>5000</v>
@@ -16812,7 +16812,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.67611765861511</v>
+        <v>2.67611742019653</v>
       </c>
       <c r="H567" t="n">
         <v>12000</v>
@@ -16986,7 +16986,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H573" t="n">
         <v>5000</v>
@@ -17044,7 +17044,7 @@
         <v>2.75</v>
       </c>
       <c r="G575" t="n">
-        <v>2.50317096710205</v>
+        <v>2.50317120552063</v>
       </c>
       <c r="H575" t="n">
         <v>5000</v>
@@ -17073,7 +17073,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H576" t="n">
         <v>1000</v>
@@ -17160,7 +17160,7 @@
         <v>2.75</v>
       </c>
       <c r="G579" t="n">
-        <v>2.50317096710205</v>
+        <v>2.50317120552063</v>
       </c>
       <c r="H579" t="n">
         <v>7000</v>
@@ -17305,7 +17305,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G584" t="n">
-        <v>2.53047847747803</v>
+        <v>2.53047871589661</v>
       </c>
       <c r="H584" t="n">
         <v>9000</v>
@@ -17334,7 +17334,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G585" t="n">
-        <v>2.51227355003357</v>
+        <v>2.51227378845215</v>
       </c>
       <c r="H585" t="n">
         <v>11000</v>
@@ -17392,7 +17392,7 @@
         <v>2.75</v>
       </c>
       <c r="G587" t="n">
-        <v>2.50317096710205</v>
+        <v>2.50317120552063</v>
       </c>
       <c r="H587" t="n">
         <v>7000</v>
@@ -17421,7 +17421,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H588" t="n">
         <v>18000</v>
@@ -17450,7 +17450,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G589" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H589" t="n">
         <v>8000</v>
@@ -17479,7 +17479,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G590" t="n">
-        <v>2.49406862258911</v>
+        <v>2.49406886100769</v>
       </c>
       <c r="H590" t="n">
         <v>10000</v>
@@ -17566,7 +17566,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G593" t="n">
-        <v>2.52137613296509</v>
+        <v>2.52137637138367</v>
       </c>
       <c r="H593" t="n">
         <v>27000</v>
@@ -17682,7 +17682,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G597" t="n">
-        <v>2.48496627807617</v>
+        <v>2.48496651649475</v>
       </c>
       <c r="H597" t="n">
         <v>3000</v>
@@ -17711,7 +17711,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>2.48496627807617</v>
+        <v>2.48496651649475</v>
       </c>
       <c r="H598" t="n">
         <v>2000</v>
@@ -18030,7 +18030,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G609" t="n">
-        <v>2.24830269813538</v>
+        <v>2.24830293655396</v>
       </c>
       <c r="H609" t="n">
         <v>6000</v>
@@ -18175,7 +18175,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G614" t="n">
-        <v>2.51227355003357</v>
+        <v>2.51227378845215</v>
       </c>
       <c r="H614" t="n">
         <v>2000</v>
@@ -18233,7 +18233,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G616" t="n">
-        <v>2.52137613296509</v>
+        <v>2.52137637138367</v>
       </c>
       <c r="H616" t="n">
         <v>1000</v>
@@ -18320,7 +18320,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G619" t="n">
-        <v>2.48496627807617</v>
+        <v>2.48496651649475</v>
       </c>
       <c r="H619" t="n">
         <v>6000</v>
@@ -18407,7 +18407,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G622" t="n">
-        <v>2.42124962806702</v>
+        <v>2.42124938964844</v>
       </c>
       <c r="H622" t="n">
         <v>3000</v>
@@ -19045,7 +19045,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G644" t="n">
-        <v>2.05715179443359</v>
+        <v>2.05715155601501</v>
       </c>
       <c r="H644" t="n">
         <v>11000</v>
@@ -19074,7 +19074,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G645" t="n">
-        <v>2.01163959503174</v>
+        <v>2.01163935661316</v>
       </c>
       <c r="H645" t="n">
         <v>18000</v>
@@ -19161,7 +19161,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G648" t="n">
-        <v>2.16638088226318</v>
+        <v>2.16638112068176</v>
       </c>
       <c r="H648" t="n">
         <v>7000</v>
@@ -19219,7 +19219,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G650" t="n">
-        <v>2.09356164932251</v>
+        <v>2.09356141090393</v>
       </c>
       <c r="H650" t="n">
         <v>14000</v>
@@ -19335,7 +19335,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G654" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H654" t="n">
         <v>10000</v>
@@ -19451,7 +19451,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G658" t="n">
-        <v>2.51227355003357</v>
+        <v>2.51227378845215</v>
       </c>
       <c r="H658" t="n">
         <v>43000</v>
@@ -19596,7 +19596,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G663" t="n">
-        <v>2.29381489753723</v>
+        <v>2.29381513595581</v>
       </c>
       <c r="H663" t="n">
         <v>24000</v>
@@ -19712,7 +19712,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G667" t="n">
-        <v>2.21189308166504</v>
+        <v>2.21189332008362</v>
       </c>
       <c r="H667" t="n">
         <v>9000</v>
@@ -19741,7 +19741,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G668" t="n">
-        <v>2.21189308166504</v>
+        <v>2.21189332008362</v>
       </c>
       <c r="H668" t="n">
         <v>0</v>
@@ -19770,7 +19770,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G669" t="n">
-        <v>2.16638088226318</v>
+        <v>2.16638112068176</v>
       </c>
       <c r="H669" t="n">
         <v>22000</v>
@@ -19915,7 +19915,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G674" t="n">
-        <v>2.12997078895569</v>
+        <v>2.12997102737427</v>
       </c>
       <c r="H674" t="n">
         <v>3000</v>
@@ -19973,7 +19973,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H676" t="n">
         <v>12000</v>
@@ -20031,7 +20031,7 @@
         <v>2.25</v>
       </c>
       <c r="G678" t="n">
-        <v>2.04804944992065</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H678" t="n">
         <v>3000</v>
@@ -20147,7 +20147,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G682" t="n">
-        <v>2.05715179443359</v>
+        <v>2.05715155601501</v>
       </c>
       <c r="H682" t="n">
         <v>5000</v>
@@ -20176,7 +20176,7 @@
         <v>2.25</v>
       </c>
       <c r="G683" t="n">
-        <v>2.04804944992065</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H683" t="n">
         <v>2000</v>
@@ -20205,7 +20205,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H684" t="n">
         <v>4000</v>
@@ -20234,7 +20234,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G685" t="n">
-        <v>2.05715179443359</v>
+        <v>2.05715155601501</v>
       </c>
       <c r="H685" t="n">
         <v>4000</v>
@@ -20321,7 +20321,7 @@
         <v>2.25</v>
       </c>
       <c r="G688" t="n">
-        <v>2.04804944992065</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H688" t="n">
         <v>4000</v>
@@ -20408,7 +20408,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G691" t="n">
-        <v>1.96612751483917</v>
+        <v>1.96612727642059</v>
       </c>
       <c r="H691" t="n">
         <v>5000</v>
@@ -20524,7 +20524,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G695" t="n">
-        <v>1.98433220386505</v>
+        <v>1.98433196544647</v>
       </c>
       <c r="H695" t="n">
         <v>1000</v>
@@ -20582,7 +20582,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G697" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H697" t="n">
         <v>1000</v>
@@ -20611,7 +20611,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G698" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H698" t="n">
         <v>2000</v>
@@ -20640,7 +20640,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G699" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H699" t="n">
         <v>1000</v>
@@ -20669,7 +20669,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G700" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H700" t="n">
         <v>0</v>
@@ -20698,7 +20698,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G701" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H701" t="n">
         <v>0</v>
@@ -20727,7 +20727,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G702" t="n">
-        <v>1.92971742153168</v>
+        <v>1.92971730232239</v>
       </c>
       <c r="H702" t="n">
         <v>4000</v>
@@ -21017,7 +21017,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G712" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H712" t="n">
         <v>1000</v>
@@ -21046,7 +21046,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G713" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H713" t="n">
         <v>0</v>
@@ -21075,7 +21075,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G714" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H714" t="n">
         <v>1000</v>
@@ -21220,7 +21220,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G719" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H719" t="n">
         <v>10000</v>
@@ -21249,7 +21249,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G720" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H720" t="n">
         <v>1000</v>
@@ -21394,7 +21394,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G725" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H725" t="n">
         <v>3000</v>
@@ -21423,7 +21423,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G726" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H726" t="n">
         <v>12000</v>
@@ -21452,7 +21452,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G727" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H727" t="n">
         <v>3000</v>
@@ -21742,7 +21742,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G737" t="n">
-        <v>1.66574668884277</v>
+        <v>1.66574656963348</v>
       </c>
       <c r="H737" t="n">
         <v>2000</v>
@@ -21771,7 +21771,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G738" t="n">
-        <v>1.66574668884277</v>
+        <v>1.66574656963348</v>
       </c>
       <c r="H738" t="n">
         <v>8000</v>
@@ -21829,7 +21829,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G740" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H740" t="n">
         <v>43000</v>
@@ -21945,7 +21945,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G744" t="n">
-        <v>1.96612751483917</v>
+        <v>1.96612727642059</v>
       </c>
       <c r="H744" t="n">
         <v>12000</v>
@@ -21974,7 +21974,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G745" t="n">
-        <v>1.98433220386505</v>
+        <v>1.98433196544647</v>
       </c>
       <c r="H745" t="n">
         <v>45000</v>
@@ -22003,7 +22003,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G746" t="n">
-        <v>1.92971742153168</v>
+        <v>1.92971730232239</v>
       </c>
       <c r="H746" t="n">
         <v>10000</v>
@@ -22061,7 +22061,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G748" t="n">
-        <v>1.97522985935211</v>
+        <v>1.97522962093353</v>
       </c>
       <c r="H748" t="n">
         <v>9000</v>
@@ -22119,7 +22119,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G750" t="n">
-        <v>1.91151249408722</v>
+        <v>1.91151261329651</v>
       </c>
       <c r="H750" t="n">
         <v>4000</v>
@@ -22177,7 +22177,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G752" t="n">
-        <v>1.91151249408722</v>
+        <v>1.91151261329651</v>
       </c>
       <c r="H752" t="n">
         <v>6000</v>
@@ -22206,7 +22206,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G753" t="n">
-        <v>1.86600029468536</v>
+        <v>1.86600041389465</v>
       </c>
       <c r="H753" t="n">
         <v>13000</v>
@@ -22293,7 +22293,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G756" t="n">
-        <v>1.92971742153168</v>
+        <v>1.92971730232239</v>
       </c>
       <c r="H756" t="n">
         <v>1000</v>
@@ -22351,7 +22351,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G758" t="n">
-        <v>1.92971742153168</v>
+        <v>1.92971730232239</v>
       </c>
       <c r="H758" t="n">
         <v>2000</v>
@@ -22380,7 +22380,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G759" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H759" t="n">
         <v>2000</v>
@@ -22409,7 +22409,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G760" t="n">
-        <v>1.93882012367249</v>
+        <v>1.9388200044632</v>
       </c>
       <c r="H760" t="n">
         <v>1000</v>
@@ -22467,7 +22467,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G762" t="n">
-        <v>2.24830269813538</v>
+        <v>2.24830293655396</v>
       </c>
       <c r="H762" t="n">
         <v>21000</v>
@@ -22583,7 +22583,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G766" t="n">
-        <v>2.09356164932251</v>
+        <v>2.09356141090393</v>
       </c>
       <c r="H766" t="n">
         <v>3000</v>
@@ -22612,7 +22612,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>2.09356164932251</v>
+        <v>2.09356141090393</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -22641,7 +22641,7 @@
         <v>2.25</v>
       </c>
       <c r="G768" t="n">
-        <v>2.04804944992065</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H768" t="n">
         <v>1000</v>
@@ -22670,7 +22670,7 @@
         <v>2.25</v>
       </c>
       <c r="G769" t="n">
-        <v>2.04804944992065</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H769" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G772" t="n">
-        <v>2.05715179443359</v>
+        <v>2.05715155601501</v>
       </c>
       <c r="H772" t="n">
         <v>7000</v>
@@ -22786,7 +22786,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G773" t="n">
-        <v>2.05715179443359</v>
+        <v>2.05715155601501</v>
       </c>
       <c r="H773" t="n">
         <v>2000</v>
@@ -22815,7 +22815,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G774" t="n">
-        <v>2.05715179443359</v>
+        <v>2.05715155601501</v>
       </c>
       <c r="H774" t="n">
         <v>0</v>
@@ -22844,7 +22844,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G775" t="n">
-        <v>2.12997078895569</v>
+        <v>2.12997102737427</v>
       </c>
       <c r="H775" t="n">
         <v>8000</v>
@@ -22873,7 +22873,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>2.09356164932251</v>
+        <v>2.09356141090393</v>
       </c>
       <c r="H776" t="n">
         <v>3000</v>
@@ -22960,7 +22960,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G779" t="n">
-        <v>2.06625413894653</v>
+        <v>2.06625390052795</v>
       </c>
       <c r="H779" t="n">
         <v>2000</v>
@@ -22989,7 +22989,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G780" t="n">
-        <v>2.06625413894653</v>
+        <v>2.06625390052795</v>
       </c>
       <c r="H780" t="n">
         <v>0</v>
@@ -23018,7 +23018,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G781" t="n">
-        <v>2.06625413894653</v>
+        <v>2.06625390052795</v>
       </c>
       <c r="H781" t="n">
         <v>0</v>
@@ -23337,7 +23337,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>2.01163959503174</v>
+        <v>2.01163935661316</v>
       </c>
       <c r="H792" t="n">
         <v>3000</v>
@@ -23366,7 +23366,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>2.01163959503174</v>
+        <v>2.01163935661316</v>
       </c>
       <c r="H793" t="n">
         <v>0</v>
@@ -23424,7 +23424,7 @@
         <v>2.25</v>
       </c>
       <c r="G795" t="n">
-        <v>2.04804944992065</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H795" t="n">
         <v>1000</v>
@@ -23453,7 +23453,7 @@
         <v>2.25</v>
       </c>
       <c r="G796" t="n">
-        <v>2.04804944992065</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H796" t="n">
         <v>0</v>
@@ -23482,7 +23482,7 @@
         <v>2.25</v>
       </c>
       <c r="G797" t="n">
-        <v>2.04804944992065</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H797" t="n">
         <v>0</v>
@@ -23656,7 +23656,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G803" t="n">
-        <v>1.86600029468536</v>
+        <v>1.86600041389465</v>
       </c>
       <c r="H803" t="n">
         <v>4000</v>
@@ -23772,7 +23772,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G807" t="n">
-        <v>1.86600029468536</v>
+        <v>1.86600041389465</v>
       </c>
       <c r="H807" t="n">
         <v>4000</v>
@@ -23859,7 +23859,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G810" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H810" t="n">
         <v>4000</v>
@@ -23888,7 +23888,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G811" t="n">
-        <v>1.86600029468536</v>
+        <v>1.86600041389465</v>
       </c>
       <c r="H811" t="n">
         <v>3000</v>
@@ -23917,7 +23917,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G812" t="n">
-        <v>1.8751026391983</v>
+        <v>1.87510275840759</v>
       </c>
       <c r="H812" t="n">
         <v>4000</v>
@@ -23946,7 +23946,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G813" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H813" t="n">
         <v>4000</v>
@@ -23975,7 +23975,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G814" t="n">
-        <v>1.86600029468536</v>
+        <v>1.86600041389465</v>
       </c>
       <c r="H814" t="n">
         <v>1000</v>
@@ -24004,7 +24004,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G815" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H815" t="n">
         <v>2000</v>
@@ -24033,7 +24033,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G816" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H816" t="n">
         <v>0</v>
@@ -24062,7 +24062,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G817" t="n">
-        <v>1.86600029468536</v>
+        <v>1.86600041389465</v>
       </c>
       <c r="H817" t="n">
         <v>13000</v>
@@ -24120,7 +24120,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G819" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H819" t="n">
         <v>6000</v>
@@ -24439,7 +24439,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G830" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H830" t="n">
         <v>2000</v>
@@ -24468,7 +24468,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G831" t="n">
-        <v>1.77042484283447</v>
+        <v>1.77042472362518</v>
       </c>
       <c r="H831" t="n">
         <v>1000</v>
@@ -24497,7 +24497,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G832" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H832" t="n">
         <v>8000</v>
@@ -24642,7 +24642,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G837" t="n">
-        <v>1.66574668884277</v>
+        <v>1.66574656963348</v>
       </c>
       <c r="H837" t="n">
         <v>1000</v>
@@ -24700,7 +24700,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G839" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H839" t="n">
         <v>1000</v>
@@ -24729,7 +24729,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G840" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H840" t="n">
         <v>0</v>
@@ -24758,7 +24758,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G841" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H841" t="n">
         <v>2000</v>
@@ -24787,7 +24787,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G842" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H842" t="n">
         <v>1000</v>
@@ -24816,7 +24816,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G843" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H843" t="n">
         <v>0</v>
@@ -24845,7 +24845,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G844" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H844" t="n">
         <v>0</v>
@@ -24874,7 +24874,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G845" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H845" t="n">
         <v>0</v>
@@ -24932,7 +24932,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G847" t="n">
-        <v>1.86600029468536</v>
+        <v>1.86600041389465</v>
       </c>
       <c r="H847" t="n">
         <v>19000</v>
@@ -24961,7 +24961,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G848" t="n">
-        <v>1.86600029468536</v>
+        <v>1.86600041389465</v>
       </c>
       <c r="H848" t="n">
         <v>0</v>
@@ -25164,7 +25164,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G855" t="n">
-        <v>1.77042484283447</v>
+        <v>1.77042472362518</v>
       </c>
       <c r="H855" t="n">
         <v>1000</v>
@@ -25483,7 +25483,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G866" t="n">
-        <v>1.6885027885437</v>
+        <v>1.68850266933441</v>
       </c>
       <c r="H866" t="n">
         <v>3000</v>
@@ -25512,7 +25512,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G867" t="n">
-        <v>1.6885027885437</v>
+        <v>1.68850266933441</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -25715,7 +25715,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G874" t="n">
-        <v>1.66574668884277</v>
+        <v>1.66574656963348</v>
       </c>
       <c r="H874" t="n">
         <v>7000</v>
@@ -25773,7 +25773,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G876" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H876" t="n">
         <v>2000</v>
@@ -25860,7 +25860,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G879" t="n">
-        <v>1.79773211479187</v>
+        <v>1.79773199558258</v>
       </c>
       <c r="H879" t="n">
         <v>6000</v>
@@ -25889,7 +25889,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G880" t="n">
-        <v>1.79773211479187</v>
+        <v>1.79773199558258</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -25918,7 +25918,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G881" t="n">
-        <v>1.79773211479187</v>
+        <v>1.79773199558258</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -26092,7 +26092,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G887" t="n">
-        <v>1.88420534133911</v>
+        <v>1.88420522212982</v>
       </c>
       <c r="H887" t="n">
         <v>7000</v>
@@ -26150,7 +26150,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G889" t="n">
-        <v>1.86600029468536</v>
+        <v>1.86600041389465</v>
       </c>
       <c r="H889" t="n">
         <v>3000</v>
@@ -26208,7 +26208,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G891" t="n">
-        <v>1.86600029468536</v>
+        <v>1.86600041389465</v>
       </c>
       <c r="H891" t="n">
         <v>1000</v>
@@ -26237,7 +26237,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G892" t="n">
-        <v>1.86600029468536</v>
+        <v>1.86600041389465</v>
       </c>
       <c r="H892" t="n">
         <v>0</v>
@@ -26266,7 +26266,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G893" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H893" t="n">
         <v>12000</v>
@@ -26295,7 +26295,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G894" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -26353,7 +26353,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G896" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H896" t="n">
         <v>47000</v>
@@ -26527,7 +26527,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G902" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H902" t="n">
         <v>1000</v>
@@ -26556,7 +26556,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G903" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H903" t="n">
         <v>2000</v>
@@ -26585,7 +26585,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G904" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H904" t="n">
         <v>0</v>
@@ -26614,7 +26614,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G905" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H905" t="n">
         <v>3000</v>
@@ -26643,7 +26643,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G906" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H906" t="n">
         <v>13000</v>
@@ -27078,7 +27078,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G921" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H921" t="n">
         <v>7000</v>
@@ -27107,7 +27107,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G922" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -27281,7 +27281,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G928" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H928" t="n">
         <v>29000</v>
@@ -27368,7 +27368,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G931" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H931" t="n">
         <v>2000</v>
@@ -27397,7 +27397,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G932" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H932" t="n">
         <v>3000</v>
@@ -27426,7 +27426,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G933" t="n">
-        <v>1.86600029468536</v>
+        <v>1.86600041389465</v>
       </c>
       <c r="H933" t="n">
         <v>5000</v>
@@ -27455,7 +27455,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G934" t="n">
-        <v>1.86600029468536</v>
+        <v>1.86600041389465</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -27513,7 +27513,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G936" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H936" t="n">
         <v>6000</v>
@@ -27542,7 +27542,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G937" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H937" t="n">
         <v>0</v>
@@ -27745,7 +27745,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G944" t="n">
-        <v>1.8751026391983</v>
+        <v>1.87510275840759</v>
       </c>
       <c r="H944" t="n">
         <v>1000</v>
@@ -27774,7 +27774,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G945" t="n">
-        <v>1.8751026391983</v>
+        <v>1.87510275840759</v>
       </c>
       <c r="H945" t="n">
         <v>0</v>
@@ -28064,7 +28064,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G955" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H955" t="n">
         <v>1000</v>
@@ -53561,6 +53561,35 @@
         <v>28000</v>
       </c>
       <c r="I1834" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1835" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1835" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="D1835" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="E1835" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="F1835" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="G1835" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="H1835" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1835" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>1.30437552928925</v>
+        <v>1.30437564849854</v>
       </c>
       <c r="H2" t="n">
         <v>322000</v>
@@ -485,7 +485,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G4" t="n">
-        <v>1.40067160129547</v>
+        <v>1.40067172050476</v>
       </c>
       <c r="H4" t="n">
         <v>193000</v>
@@ -659,7 +659,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G10" t="n">
-        <v>1.87339854240417</v>
+        <v>1.87339878082275</v>
       </c>
       <c r="H10" t="n">
         <v>464000</v>
@@ -688,7 +688,7 @@
         <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.18854975700378</v>
+        <v>2.18854951858521</v>
       </c>
       <c r="H11" t="n">
         <v>315000</v>
@@ -804,7 +804,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G15" t="n">
-        <v>4.56969118118286</v>
+        <v>4.56969165802002</v>
       </c>
       <c r="H15" t="n">
         <v>681000</v>
@@ -833,7 +833,7 @@
         <v>4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3.93938946723938</v>
+        <v>3.93938994407654</v>
       </c>
       <c r="H16" t="n">
         <v>669000</v>
@@ -862,7 +862,7 @@
         <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>3.50167918205261</v>
+        <v>3.50167942047119</v>
       </c>
       <c r="H17" t="n">
         <v>598000</v>
@@ -891,7 +891,7 @@
         <v>4.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3.93938946723938</v>
+        <v>3.93938994407654</v>
       </c>
       <c r="H18" t="n">
         <v>489000</v>
@@ -978,7 +978,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G21" t="n">
-        <v>3.52794241905212</v>
+        <v>3.52794218063354</v>
       </c>
       <c r="H21" t="n">
         <v>356000</v>
@@ -1007,7 +1007,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>3.57171273231506</v>
+        <v>3.57171297073364</v>
       </c>
       <c r="H22" t="n">
         <v>212000</v>
@@ -1036,7 +1036,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>3.43164587020874</v>
+        <v>3.43164563179016</v>
       </c>
       <c r="H23" t="n">
         <v>116000</v>
@@ -1123,7 +1123,7 @@
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>3.50167918205261</v>
+        <v>3.50167942047119</v>
       </c>
       <c r="H26" t="n">
         <v>145000</v>
@@ -1152,7 +1152,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G27" t="n">
-        <v>3.51043391227722</v>
+        <v>3.51043367385864</v>
       </c>
       <c r="H27" t="n">
         <v>25000</v>
@@ -1297,7 +1297,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G32" t="n">
-        <v>3.45353150367737</v>
+        <v>3.45353126525879</v>
       </c>
       <c r="H32" t="n">
         <v>39000</v>
@@ -1326,7 +1326,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>3.40976023674011</v>
+        <v>3.40976047515869</v>
       </c>
       <c r="H33" t="n">
         <v>38000</v>
@@ -1355,7 +1355,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G34" t="n">
-        <v>3.43164587020874</v>
+        <v>3.43164563179016</v>
       </c>
       <c r="H34" t="n">
         <v>27000</v>
@@ -1384,7 +1384,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G35" t="n">
-        <v>3.43164587020874</v>
+        <v>3.43164563179016</v>
       </c>
       <c r="H35" t="n">
         <v>28000</v>
@@ -1471,7 +1471,7 @@
         <v>3.75</v>
       </c>
       <c r="G38" t="n">
-        <v>3.28282403945923</v>
+        <v>3.28282427787781</v>
       </c>
       <c r="H38" t="n">
         <v>41000</v>
@@ -1558,7 +1558,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G41" t="n">
-        <v>2.93703365325928</v>
+        <v>2.9370334148407</v>
       </c>
       <c r="H41" t="n">
         <v>317000</v>
@@ -1616,7 +1616,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G43" t="n">
-        <v>2.62188220024109</v>
+        <v>2.62188243865967</v>
       </c>
       <c r="H43" t="n">
         <v>68000</v>
@@ -1674,7 +1674,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G45" t="n">
-        <v>2.98518180847168</v>
+        <v>2.98518204689026</v>
       </c>
       <c r="H45" t="n">
         <v>262000</v>
@@ -1703,7 +1703,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G46" t="n">
-        <v>2.98080492019653</v>
+        <v>2.98080444335938</v>
       </c>
       <c r="H46" t="n">
         <v>492000</v>
@@ -1761,7 +1761,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G48" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H48" t="n">
         <v>52000</v>
@@ -1819,7 +1819,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G50" t="n">
-        <v>2.74881839752197</v>
+        <v>2.74881863594055</v>
       </c>
       <c r="H50" t="n">
         <v>29000</v>
@@ -1906,7 +1906,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H53" t="n">
         <v>253000</v>
@@ -2051,7 +2051,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>2.80134320259094</v>
+        <v>2.80134344100952</v>
       </c>
       <c r="H58" t="n">
         <v>74000</v>
@@ -2109,7 +2109,7 @@
         <v>3.25</v>
       </c>
       <c r="G60" t="n">
-        <v>2.84511470794678</v>
+        <v>2.84511494636536</v>
       </c>
       <c r="H60" t="n">
         <v>46000</v>
@@ -2138,7 +2138,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G61" t="n">
-        <v>2.85824584960938</v>
+        <v>2.85824608802795</v>
       </c>
       <c r="H61" t="n">
         <v>55000</v>
@@ -2196,7 +2196,7 @@
         <v>3.25</v>
       </c>
       <c r="G63" t="n">
-        <v>2.84511470794678</v>
+        <v>2.84511494636536</v>
       </c>
       <c r="H63" t="n">
         <v>14000</v>
@@ -2399,7 +2399,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H70" t="n">
         <v>21000</v>
@@ -2486,7 +2486,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G73" t="n">
-        <v>2.87137699127197</v>
+        <v>2.87137722969055</v>
       </c>
       <c r="H73" t="n">
         <v>14000</v>
@@ -2631,7 +2631,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>2.7707040309906</v>
+        <v>2.77070379257202</v>
       </c>
       <c r="H78" t="n">
         <v>13000</v>
@@ -2689,7 +2689,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G80" t="n">
-        <v>2.83198308944702</v>
+        <v>2.83198285102844</v>
       </c>
       <c r="H80" t="n">
         <v>24000</v>
@@ -2718,7 +2718,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.80134320259094</v>
+        <v>2.80134344100952</v>
       </c>
       <c r="H81" t="n">
         <v>20000</v>
@@ -2747,7 +2747,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G82" t="n">
-        <v>2.7400643825531</v>
+        <v>2.74006414413452</v>
       </c>
       <c r="H82" t="n">
         <v>7000</v>
@@ -2776,7 +2776,7 @@
         <v>3.25</v>
       </c>
       <c r="G83" t="n">
-        <v>2.84511470794678</v>
+        <v>2.84511494636536</v>
       </c>
       <c r="H83" t="n">
         <v>61000</v>
@@ -2805,7 +2805,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G84" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H84" t="n">
         <v>12000</v>
@@ -2892,7 +2892,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G87" t="n">
-        <v>2.80134320259094</v>
+        <v>2.80134344100952</v>
       </c>
       <c r="H87" t="n">
         <v>20000</v>
@@ -2921,7 +2921,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G88" t="n">
-        <v>2.80134320259094</v>
+        <v>2.80134344100952</v>
       </c>
       <c r="H88" t="n">
         <v>49000</v>
@@ -2979,7 +2979,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G90" t="n">
-        <v>2.88888549804688</v>
+        <v>2.8888852596283</v>
       </c>
       <c r="H90" t="n">
         <v>39000</v>
@@ -3008,7 +3008,7 @@
         <v>3.25</v>
       </c>
       <c r="G91" t="n">
-        <v>2.84511470794678</v>
+        <v>2.84511494636536</v>
       </c>
       <c r="H91" t="n">
         <v>16000</v>
@@ -3037,7 +3037,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G92" t="n">
-        <v>2.87137699127197</v>
+        <v>2.87137722969055</v>
       </c>
       <c r="H92" t="n">
         <v>8000</v>
@@ -3066,7 +3066,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G93" t="n">
-        <v>2.88888549804688</v>
+        <v>2.8888852596283</v>
       </c>
       <c r="H93" t="n">
         <v>20000</v>
@@ -3095,7 +3095,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G94" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H94" t="n">
         <v>27000</v>
@@ -3124,7 +3124,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G95" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H95" t="n">
         <v>11000</v>
@@ -3153,7 +3153,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G96" t="n">
-        <v>2.80134320259094</v>
+        <v>2.80134344100952</v>
       </c>
       <c r="H96" t="n">
         <v>9000</v>
@@ -3182,7 +3182,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H97" t="n">
         <v>14000</v>
@@ -3240,7 +3240,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.86700034141541</v>
+        <v>2.86699986457825</v>
       </c>
       <c r="H99" t="n">
         <v>3000</v>
@@ -3269,7 +3269,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G100" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H100" t="n">
         <v>5000</v>
@@ -3298,7 +3298,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G101" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H101" t="n">
         <v>8000</v>
@@ -3327,7 +3327,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G102" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H102" t="n">
         <v>5000</v>
@@ -3356,7 +3356,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G103" t="n">
-        <v>2.88888549804688</v>
+        <v>2.8888852596283</v>
       </c>
       <c r="H103" t="n">
         <v>8000</v>
@@ -3385,7 +3385,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G104" t="n">
-        <v>2.88888549804688</v>
+        <v>2.8888852596283</v>
       </c>
       <c r="H104" t="n">
         <v>9000</v>
@@ -3414,7 +3414,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88888549804688</v>
+        <v>2.8888852596283</v>
       </c>
       <c r="H105" t="n">
         <v>13000</v>
@@ -3443,7 +3443,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G106" t="n">
-        <v>2.9983127117157</v>
+        <v>2.99831295013428</v>
       </c>
       <c r="H106" t="n">
         <v>52000</v>
@@ -3472,7 +3472,7 @@
         <v>4</v>
       </c>
       <c r="G107" t="n">
-        <v>3.50167918205261</v>
+        <v>3.50167942047119</v>
       </c>
       <c r="H107" t="n">
         <v>164000</v>
@@ -3559,7 +3559,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>4.11447286605835</v>
+        <v>4.11447334289551</v>
       </c>
       <c r="H110" t="n">
         <v>568000</v>
@@ -3588,7 +3588,7 @@
         <v>4.375</v>
       </c>
       <c r="G111" t="n">
-        <v>3.82996201515198</v>
+        <v>3.8299617767334</v>
       </c>
       <c r="H111" t="n">
         <v>247000</v>
@@ -3617,7 +3617,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G112" t="n">
-        <v>3.64174628257751</v>
+        <v>3.64174652099609</v>
       </c>
       <c r="H112" t="n">
         <v>202000</v>
@@ -3646,7 +3646,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G113" t="n">
-        <v>3.52794241905212</v>
+        <v>3.52794218063354</v>
       </c>
       <c r="H113" t="n">
         <v>87000</v>
@@ -3704,7 +3704,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G115" t="n">
-        <v>3.77305936813354</v>
+        <v>3.77305960655212</v>
       </c>
       <c r="H115" t="n">
         <v>88000</v>
@@ -3762,7 +3762,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>3.91312670707703</v>
+        <v>3.91312623023987</v>
       </c>
       <c r="H117" t="n">
         <v>152000</v>
@@ -3791,7 +3791,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>3.86060118675232</v>
+        <v>3.86060166358948</v>
       </c>
       <c r="H118" t="n">
         <v>82000</v>
@@ -3849,7 +3849,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>3.84747004508972</v>
+        <v>3.8474702835083</v>
       </c>
       <c r="H120" t="n">
         <v>40000</v>
@@ -3878,7 +3878,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G121" t="n">
-        <v>3.89124155044556</v>
+        <v>3.89124178886414</v>
       </c>
       <c r="H121" t="n">
         <v>84000</v>
@@ -3907,7 +3907,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G122" t="n">
-        <v>3.92625832557678</v>
+        <v>3.92625784873962</v>
       </c>
       <c r="H122" t="n">
         <v>35000</v>
@@ -3965,7 +3965,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G124" t="n">
-        <v>4.17137575149536</v>
+        <v>4.1713752746582</v>
       </c>
       <c r="H124" t="n">
         <v>181000</v>
@@ -3994,7 +3994,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>4.18013048171997</v>
+        <v>4.18013000488281</v>
       </c>
       <c r="H125" t="n">
         <v>73000</v>
@@ -4081,7 +4081,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G128" t="n">
-        <v>4.16699838638306</v>
+        <v>4.16699886322021</v>
       </c>
       <c r="H128" t="n">
         <v>58000</v>
@@ -4313,7 +4313,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G136" t="n">
-        <v>4.02255439758301</v>
+        <v>4.02255392074585</v>
       </c>
       <c r="H136" t="n">
         <v>19000</v>
@@ -4342,7 +4342,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G137" t="n">
-        <v>3.98753714561462</v>
+        <v>3.98753666877747</v>
       </c>
       <c r="H137" t="n">
         <v>27000</v>
@@ -4371,7 +4371,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G138" t="n">
-        <v>3.99629187583923</v>
+        <v>3.99629139900208</v>
       </c>
       <c r="H138" t="n">
         <v>9000</v>
@@ -4400,7 +4400,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G139" t="n">
-        <v>4.21952342987061</v>
+        <v>4.21952390670776</v>
       </c>
       <c r="H139" t="n">
         <v>149000</v>
@@ -4429,7 +4429,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G140" t="n">
-        <v>4.13635921478271</v>
+        <v>4.13635873794556</v>
       </c>
       <c r="H140" t="n">
         <v>97000</v>
@@ -4487,7 +4487,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G142" t="n">
-        <v>4.32895088195801</v>
+        <v>4.32895135879517</v>
       </c>
       <c r="H142" t="n">
         <v>162000</v>
@@ -4574,7 +4574,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G145" t="n">
-        <v>4.46464109420776</v>
+        <v>4.46464061737061</v>
       </c>
       <c r="H145" t="n">
         <v>522000</v>
@@ -4661,7 +4661,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>3.85184741020203</v>
+        <v>3.85184693336487</v>
       </c>
       <c r="H148" t="n">
         <v>192000</v>
@@ -4748,7 +4748,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G151" t="n">
-        <v>3.80369901657104</v>
+        <v>3.80369925498962</v>
       </c>
       <c r="H151" t="n">
         <v>89000</v>
@@ -4864,7 +4864,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G155" t="n">
-        <v>3.19965934753418</v>
+        <v>3.19965958595276</v>
       </c>
       <c r="H155" t="n">
         <v>17000</v>
@@ -4922,7 +4922,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G157" t="n">
-        <v>2.45555233955383</v>
+        <v>2.45555257797241</v>
       </c>
       <c r="H157" t="n">
         <v>83000</v>
@@ -5009,7 +5009,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G160" t="n">
-        <v>2.88888549804688</v>
+        <v>2.8888852596283</v>
       </c>
       <c r="H160" t="n">
         <v>26000</v>
@@ -5038,7 +5038,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G161" t="n">
-        <v>2.95891928672791</v>
+        <v>2.95891952514648</v>
       </c>
       <c r="H161" t="n">
         <v>30000</v>
@@ -5154,7 +5154,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G165" t="n">
-        <v>3.58046746253967</v>
+        <v>3.58046722412109</v>
       </c>
       <c r="H165" t="n">
         <v>47000</v>
@@ -5183,7 +5183,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.75555086135864</v>
+        <v>3.75555109977722</v>
       </c>
       <c r="H166" t="n">
         <v>119000</v>
@@ -5241,7 +5241,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>3.62861490249634</v>
+        <v>3.62861514091492</v>
       </c>
       <c r="H168" t="n">
         <v>19000</v>
@@ -5270,7 +5270,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G169" t="n">
-        <v>3.60672950744629</v>
+        <v>3.60672926902771</v>
       </c>
       <c r="H169" t="n">
         <v>15000</v>
@@ -5415,7 +5415,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.85184741020203</v>
+        <v>3.85184693336487</v>
       </c>
       <c r="H174" t="n">
         <v>74000</v>
@@ -5473,7 +5473,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>4.07070207595825</v>
+        <v>4.07070255279541</v>
       </c>
       <c r="H176" t="n">
         <v>44000</v>
@@ -5502,7 +5502,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>4.07070207595825</v>
+        <v>4.07070255279541</v>
       </c>
       <c r="H177" t="n">
         <v>17000</v>
@@ -5531,7 +5531,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>3.68114042282104</v>
+        <v>3.68114018440247</v>
       </c>
       <c r="H178" t="n">
         <v>51000</v>
@@ -5705,7 +5705,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>3.85184741020203</v>
+        <v>3.85184693336487</v>
       </c>
       <c r="H184" t="n">
         <v>8000</v>
@@ -5734,7 +5734,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G185" t="n">
-        <v>3.79056763648987</v>
+        <v>3.79056787490845</v>
       </c>
       <c r="H185" t="n">
         <v>4000</v>
@@ -5763,7 +5763,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>3.86935544013977</v>
+        <v>3.86935591697693</v>
       </c>
       <c r="H186" t="n">
         <v>15000</v>
@@ -5792,7 +5792,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G187" t="n">
-        <v>3.86060118675232</v>
+        <v>3.86060166358948</v>
       </c>
       <c r="H187" t="n">
         <v>5000</v>
@@ -5821,7 +5821,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>3.77743673324585</v>
+        <v>3.77743649482727</v>
       </c>
       <c r="H188" t="n">
         <v>7000</v>
@@ -5850,7 +5850,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G189" t="n">
-        <v>3.75117421150208</v>
+        <v>3.7511739730835</v>
       </c>
       <c r="H189" t="n">
         <v>22000</v>
@@ -5995,7 +5995,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G194" t="n">
-        <v>3.74673461914062</v>
+        <v>3.74673438072205</v>
       </c>
       <c r="H194" t="n">
         <v>3000</v>
@@ -6082,7 +6082,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>3.79112720489502</v>
+        <v>3.79112696647644</v>
       </c>
       <c r="H197" t="n">
         <v>2000</v>
@@ -6169,7 +6169,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G200" t="n">
-        <v>3.8621551990509</v>
+        <v>3.86215496063232</v>
       </c>
       <c r="H200" t="n">
         <v>46000</v>
@@ -6227,7 +6227,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>3.8310809135437</v>
+        <v>3.83108067512512</v>
       </c>
       <c r="H202" t="n">
         <v>10000</v>
@@ -6401,7 +6401,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90654826164246</v>
+        <v>3.90654802322388</v>
       </c>
       <c r="H208" t="n">
         <v>30000</v>
@@ -6430,7 +6430,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>3.8621551990509</v>
+        <v>3.86215496063232</v>
       </c>
       <c r="H209" t="n">
         <v>8000</v>
@@ -6459,7 +6459,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>3.8621551990509</v>
+        <v>3.86215496063232</v>
       </c>
       <c r="H210" t="n">
         <v>2000</v>
@@ -6517,7 +6517,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>3.95981907844543</v>
+        <v>3.95981955528259</v>
       </c>
       <c r="H212" t="n">
         <v>9000</v>
@@ -6546,7 +6546,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>3.91986608505249</v>
+        <v>3.91986584663391</v>
       </c>
       <c r="H213" t="n">
         <v>11000</v>
@@ -6691,7 +6691,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G218" t="n">
-        <v>3.96425867080688</v>
+        <v>3.96425914764404</v>
       </c>
       <c r="H218" t="n">
         <v>43000</v>
@@ -6807,7 +6807,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G222" t="n">
-        <v>4.06636095046997</v>
+        <v>4.06636142730713</v>
       </c>
       <c r="H222" t="n">
         <v>3000</v>
@@ -6836,7 +6836,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G223" t="n">
-        <v>4.04416513442993</v>
+        <v>4.04416561126709</v>
       </c>
       <c r="H223" t="n">
         <v>17000</v>
@@ -6894,7 +6894,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>3.95981907844543</v>
+        <v>3.95981955528259</v>
       </c>
       <c r="H225" t="n">
         <v>10000</v>
@@ -6923,7 +6923,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G226" t="n">
-        <v>4.00421142578125</v>
+        <v>4.00421190261841</v>
       </c>
       <c r="H226" t="n">
         <v>2000</v>
@@ -7068,7 +7068,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G231" t="n">
-        <v>4.06636095046997</v>
+        <v>4.06636142730713</v>
       </c>
       <c r="H231" t="n">
         <v>61000</v>
@@ -7155,7 +7155,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G234" t="n">
-        <v>4.06636095046997</v>
+        <v>4.06636142730713</v>
       </c>
       <c r="H234" t="n">
         <v>13000</v>
@@ -7271,7 +7271,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.48365163803101</v>
+        <v>4.48365211486816</v>
       </c>
       <c r="H238" t="n">
         <v>99000</v>
@@ -7300,7 +7300,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>4.40374517440796</v>
+        <v>4.40374565124512</v>
       </c>
       <c r="H239" t="n">
         <v>37000</v>
@@ -7503,7 +7503,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>4.31052017211914</v>
+        <v>4.3105206489563</v>
       </c>
       <c r="H246" t="n">
         <v>21000</v>
@@ -7532,7 +7532,7 @@
         <v>4.875</v>
       </c>
       <c r="G247" t="n">
-        <v>4.32827711105347</v>
+        <v>4.32827758789062</v>
       </c>
       <c r="H247" t="n">
         <v>9000</v>
@@ -7706,7 +7706,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G253" t="n">
-        <v>3.8621551990509</v>
+        <v>3.86215496063232</v>
       </c>
       <c r="H253" t="n">
         <v>21000</v>
@@ -7735,7 +7735,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G254" t="n">
-        <v>3.88879084587097</v>
+        <v>3.88879108428955</v>
       </c>
       <c r="H254" t="n">
         <v>21000</v>
@@ -7764,7 +7764,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G255" t="n">
-        <v>3.96425867080688</v>
+        <v>3.96425914764404</v>
       </c>
       <c r="H255" t="n">
         <v>2000</v>
@@ -7793,7 +7793,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>4.06636095046997</v>
+        <v>4.06636142730713</v>
       </c>
       <c r="H256" t="n">
         <v>12000</v>
@@ -8025,7 +8025,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G264" t="n">
-        <v>4.05748271942139</v>
+        <v>4.05748319625854</v>
       </c>
       <c r="H264" t="n">
         <v>17000</v>
@@ -8083,7 +8083,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>4.04416513442993</v>
+        <v>4.04416561126709</v>
       </c>
       <c r="H266" t="n">
         <v>23000</v>
@@ -8141,7 +8141,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G268" t="n">
-        <v>4.05748271942139</v>
+        <v>4.05748319625854</v>
       </c>
       <c r="H268" t="n">
         <v>4000</v>
@@ -8199,7 +8199,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>3.90654826164246</v>
+        <v>3.90654802322388</v>
       </c>
       <c r="H270" t="n">
         <v>13000</v>
@@ -8257,7 +8257,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>3.95981907844543</v>
+        <v>3.95981955528259</v>
       </c>
       <c r="H272" t="n">
         <v>11000</v>
@@ -8286,7 +8286,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>3.99089384078979</v>
+        <v>3.99089431762695</v>
       </c>
       <c r="H273" t="n">
         <v>16000</v>
@@ -8315,7 +8315,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G274" t="n">
-        <v>3.9553804397583</v>
+        <v>3.95537996292114</v>
       </c>
       <c r="H274" t="n">
         <v>2000</v>
@@ -8373,7 +8373,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G276" t="n">
-        <v>3.84439826011658</v>
+        <v>3.844398021698</v>
       </c>
       <c r="H276" t="n">
         <v>17000</v>
@@ -8605,7 +8605,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G284" t="n">
-        <v>3.80444502830505</v>
+        <v>3.80444478988647</v>
       </c>
       <c r="H284" t="n">
         <v>10000</v>
@@ -8721,7 +8721,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G288" t="n">
-        <v>3.74673461914062</v>
+        <v>3.74673438072205</v>
       </c>
       <c r="H288" t="n">
         <v>1000</v>
@@ -8750,7 +8750,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G289" t="n">
-        <v>3.74673461914062</v>
+        <v>3.74673438072205</v>
       </c>
       <c r="H289" t="n">
         <v>2000</v>
@@ -8779,7 +8779,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G290" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692121505737</v>
       </c>
       <c r="H290" t="n">
         <v>3000</v>
@@ -9040,7 +9040,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692121505737</v>
       </c>
       <c r="H299" t="n">
         <v>25000</v>
@@ -9069,7 +9069,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G300" t="n">
-        <v>3.59136080741882</v>
+        <v>3.59136056900024</v>
       </c>
       <c r="H300" t="n">
         <v>6000</v>
@@ -9156,7 +9156,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G303" t="n">
-        <v>3.63131427764893</v>
+        <v>3.63131403923035</v>
       </c>
       <c r="H303" t="n">
         <v>5000</v>
@@ -9243,7 +9243,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G306" t="n">
-        <v>3.57804322242737</v>
+        <v>3.57804298400879</v>
       </c>
       <c r="H306" t="n">
         <v>6000</v>
@@ -9330,7 +9330,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692121505737</v>
       </c>
       <c r="H309" t="n">
         <v>2000</v>
@@ -9388,7 +9388,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G311" t="n">
-        <v>3.50257563591003</v>
+        <v>3.50257539749146</v>
       </c>
       <c r="H311" t="n">
         <v>3000</v>
@@ -9417,7 +9417,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G312" t="n">
-        <v>3.46262240409851</v>
+        <v>3.46262216567993</v>
       </c>
       <c r="H312" t="n">
         <v>4000</v>
@@ -9446,7 +9446,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>3.41822957992554</v>
+        <v>3.41822934150696</v>
       </c>
       <c r="H313" t="n">
         <v>2000</v>
@@ -9475,7 +9475,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G314" t="n">
-        <v>3.41822957992554</v>
+        <v>3.41822934150696</v>
       </c>
       <c r="H314" t="n">
         <v>1000</v>
@@ -9504,7 +9504,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G315" t="n">
-        <v>3.33388376235962</v>
+        <v>3.33388352394104</v>
       </c>
       <c r="H315" t="n">
         <v>16000</v>
@@ -9649,7 +9649,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G320" t="n">
-        <v>3.16075277328491</v>
+        <v>3.16075253486633</v>
       </c>
       <c r="H320" t="n">
         <v>3000</v>
@@ -9707,7 +9707,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G322" t="n">
-        <v>3.16519212722778</v>
+        <v>3.1651918888092</v>
       </c>
       <c r="H322" t="n">
         <v>4000</v>
@@ -9823,7 +9823,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G326" t="n">
-        <v>3.16075277328491</v>
+        <v>3.16075253486633</v>
       </c>
       <c r="H326" t="n">
         <v>7000</v>
@@ -9881,7 +9881,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G328" t="n">
-        <v>3.29393029212952</v>
+        <v>3.29393005371094</v>
       </c>
       <c r="H328" t="n">
         <v>17000</v>
@@ -10055,7 +10055,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>3.46262240409851</v>
+        <v>3.46262216567993</v>
       </c>
       <c r="H334" t="n">
         <v>5000</v>
@@ -10084,7 +10084,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>3.46262240409851</v>
+        <v>3.46262216567993</v>
       </c>
       <c r="H335" t="n">
         <v>11000</v>
@@ -10113,7 +10113,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>3.38271522521973</v>
+        <v>3.38271546363831</v>
       </c>
       <c r="H336" t="n">
         <v>4000</v>
@@ -10171,7 +10171,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G338" t="n">
-        <v>3.37827634811401</v>
+        <v>3.37827610969543</v>
       </c>
       <c r="H338" t="n">
         <v>5000</v>
@@ -10200,7 +10200,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G339" t="n">
-        <v>3.61799621582031</v>
+        <v>3.61799597740173</v>
       </c>
       <c r="H339" t="n">
         <v>32000</v>
@@ -10345,7 +10345,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G344" t="n">
-        <v>3.57804322242737</v>
+        <v>3.57804298400879</v>
       </c>
       <c r="H344" t="n">
         <v>8000</v>
@@ -10461,7 +10461,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G348" t="n">
-        <v>3.74673461914062</v>
+        <v>3.74673438072205</v>
       </c>
       <c r="H348" t="n">
         <v>35000</v>
@@ -10780,7 +10780,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G359" t="n">
-        <v>3.90210866928101</v>
+        <v>3.90210890769958</v>
       </c>
       <c r="H359" t="n">
         <v>11000</v>
@@ -10809,7 +10809,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G360" t="n">
-        <v>3.90654826164246</v>
+        <v>3.90654802322388</v>
       </c>
       <c r="H360" t="n">
         <v>11000</v>
@@ -10838,7 +10838,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>3.96425867080688</v>
+        <v>3.96425914764404</v>
       </c>
       <c r="H361" t="n">
         <v>20000</v>
@@ -11012,7 +11012,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>3.96425867080688</v>
+        <v>3.96425914764404</v>
       </c>
       <c r="H367" t="n">
         <v>13000</v>
@@ -11099,7 +11099,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>3.8532772064209</v>
+        <v>3.85327672958374</v>
       </c>
       <c r="H370" t="n">
         <v>50000</v>
@@ -11331,7 +11331,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G378" t="n">
-        <v>3.63131427764893</v>
+        <v>3.63131403923035</v>
       </c>
       <c r="H378" t="n">
         <v>15000</v>
@@ -11476,7 +11476,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G383" t="n">
-        <v>3.63575315475464</v>
+        <v>3.63575291633606</v>
       </c>
       <c r="H383" t="n">
         <v>39000</v>
@@ -11563,7 +11563,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G386" t="n">
-        <v>3.63131427764893</v>
+        <v>3.63131403923035</v>
       </c>
       <c r="H386" t="n">
         <v>13000</v>
@@ -11592,7 +11592,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G387" t="n">
-        <v>3.63131427764893</v>
+        <v>3.63131403923035</v>
       </c>
       <c r="H387" t="n">
         <v>18000</v>
@@ -11679,7 +11679,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>3.79112720489502</v>
+        <v>3.79112696647644</v>
       </c>
       <c r="H390" t="n">
         <v>21000</v>
@@ -11708,7 +11708,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G391" t="n">
-        <v>3.90210866928101</v>
+        <v>3.90210890769958</v>
       </c>
       <c r="H391" t="n">
         <v>56000</v>
@@ -11737,7 +11737,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G392" t="n">
-        <v>3.75561332702637</v>
+        <v>3.75561308860779</v>
       </c>
       <c r="H392" t="n">
         <v>102000</v>
@@ -11940,7 +11940,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>3.59136080741882</v>
+        <v>3.59136056900024</v>
       </c>
       <c r="H399" t="n">
         <v>54000</v>
@@ -11998,7 +11998,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G401" t="n">
-        <v>3.57804322242737</v>
+        <v>3.57804298400879</v>
       </c>
       <c r="H401" t="n">
         <v>18000</v>
@@ -12056,7 +12056,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G403" t="n">
-        <v>3.56472516059875</v>
+        <v>3.56472492218018</v>
       </c>
       <c r="H403" t="n">
         <v>20000</v>
@@ -12143,7 +12143,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692121505737</v>
       </c>
       <c r="H406" t="n">
         <v>10000</v>
@@ -12230,7 +12230,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>3.61799621582031</v>
+        <v>3.61799597740173</v>
       </c>
       <c r="H409" t="n">
         <v>25000</v>
@@ -12288,7 +12288,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G411" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692121505737</v>
       </c>
       <c r="H411" t="n">
         <v>6000</v>
@@ -12317,7 +12317,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G412" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692121505737</v>
       </c>
       <c r="H412" t="n">
         <v>10000</v>
@@ -53590,6 +53590,64 @@
         <v>0</v>
       </c>
       <c r="I1835" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1836" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1836" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="D1836" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="E1836" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="F1836" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="G1836" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="H1836" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1836" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1837" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1837" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="D1837" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="E1837" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="F1837" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="G1837" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="H1837" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I1837" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>1.30437564849854</v>
+        <v>1.30437552928925</v>
       </c>
       <c r="H2" t="n">
         <v>322000</v>
@@ -456,7 +456,7 @@
         <v>1.50020003318787</v>
       </c>
       <c r="G3" t="n">
-        <v>1.31330490112305</v>
+        <v>1.31330502033234</v>
       </c>
       <c r="H3" t="n">
         <v>35000</v>
@@ -485,7 +485,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G4" t="n">
-        <v>1.40067172050476</v>
+        <v>1.40067183971405</v>
       </c>
       <c r="H4" t="n">
         <v>193000</v>
@@ -514,7 +514,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G5" t="n">
-        <v>1.62828099727631</v>
+        <v>1.62828087806702</v>
       </c>
       <c r="H5" t="n">
         <v>169000</v>
@@ -543,7 +543,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G6" t="n">
-        <v>1.62828099727631</v>
+        <v>1.62828087806702</v>
       </c>
       <c r="H6" t="n">
         <v>470000</v>
@@ -572,7 +572,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G7" t="n">
-        <v>1.58888709545135</v>
+        <v>1.58888697624207</v>
       </c>
       <c r="H7" t="n">
         <v>113000</v>
@@ -659,7 +659,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G10" t="n">
-        <v>1.87339878082275</v>
+        <v>1.87339866161346</v>
       </c>
       <c r="H10" t="n">
         <v>464000</v>
@@ -688,7 +688,7 @@
         <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.18854951858521</v>
+        <v>2.18854975700378</v>
       </c>
       <c r="H11" t="n">
         <v>315000</v>
@@ -717,7 +717,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G12" t="n">
-        <v>2.59124255180359</v>
+        <v>2.59124279022217</v>
       </c>
       <c r="H12" t="n">
         <v>261000</v>
@@ -746,7 +746,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G13" t="n">
-        <v>3.17777419090271</v>
+        <v>3.17777395248413</v>
       </c>
       <c r="H13" t="n">
         <v>203000</v>
@@ -775,7 +775,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G14" t="n">
-        <v>3.69427156448364</v>
+        <v>3.69427132606506</v>
       </c>
       <c r="H14" t="n">
         <v>633000</v>
@@ -833,7 +833,7 @@
         <v>4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3.93938994407654</v>
+        <v>3.9393892288208</v>
       </c>
       <c r="H16" t="n">
         <v>669000</v>
@@ -862,7 +862,7 @@
         <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>3.50167942047119</v>
+        <v>3.50167965888977</v>
       </c>
       <c r="H17" t="n">
         <v>598000</v>
@@ -891,7 +891,7 @@
         <v>4.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3.93938994407654</v>
+        <v>3.9393892288208</v>
       </c>
       <c r="H18" t="n">
         <v>489000</v>
@@ -920,7 +920,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>3.87810969352722</v>
+        <v>3.8781099319458</v>
       </c>
       <c r="H19" t="n">
         <v>592000</v>
@@ -978,7 +978,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G21" t="n">
-        <v>3.52794218063354</v>
+        <v>3.52794241905212</v>
       </c>
       <c r="H21" t="n">
         <v>356000</v>
@@ -1065,7 +1065,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G24" t="n">
-        <v>3.69427156448364</v>
+        <v>3.69427132606506</v>
       </c>
       <c r="H24" t="n">
         <v>227000</v>
@@ -1094,7 +1094,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G25" t="n">
-        <v>3.55420446395874</v>
+        <v>3.55420470237732</v>
       </c>
       <c r="H25" t="n">
         <v>275000</v>
@@ -1123,7 +1123,7 @@
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>3.50167942047119</v>
+        <v>3.50167965888977</v>
       </c>
       <c r="H26" t="n">
         <v>145000</v>
@@ -1152,7 +1152,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G27" t="n">
-        <v>3.51043367385864</v>
+        <v>3.51043391227722</v>
       </c>
       <c r="H27" t="n">
         <v>25000</v>
@@ -1210,7 +1210,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G29" t="n">
-        <v>3.51918768882751</v>
+        <v>3.51918792724609</v>
       </c>
       <c r="H29" t="n">
         <v>87000</v>
@@ -1413,7 +1413,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G36" t="n">
-        <v>3.41413760185242</v>
+        <v>3.41413736343384</v>
       </c>
       <c r="H36" t="n">
         <v>60000</v>
@@ -1442,7 +1442,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G37" t="n">
-        <v>3.41413760185242</v>
+        <v>3.41413736343384</v>
       </c>
       <c r="H37" t="n">
         <v>48000</v>
@@ -1529,7 +1529,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>3.17777419090271</v>
+        <v>3.17777395248413</v>
       </c>
       <c r="H40" t="n">
         <v>66000</v>
@@ -1558,7 +1558,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G41" t="n">
-        <v>2.9370334148407</v>
+        <v>2.93703365325928</v>
       </c>
       <c r="H41" t="n">
         <v>317000</v>
@@ -1616,7 +1616,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G43" t="n">
-        <v>2.62188243865967</v>
+        <v>2.62188220024109</v>
       </c>
       <c r="H43" t="n">
         <v>68000</v>
@@ -1703,7 +1703,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G46" t="n">
-        <v>2.98080444335938</v>
+        <v>2.98080468177795</v>
       </c>
       <c r="H46" t="n">
         <v>492000</v>
@@ -1732,7 +1732,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G47" t="n">
-        <v>2.78821206092834</v>
+        <v>2.78821229934692</v>
       </c>
       <c r="H47" t="n">
         <v>132000</v>
@@ -1819,7 +1819,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G50" t="n">
-        <v>2.74881863594055</v>
+        <v>2.74881815910339</v>
       </c>
       <c r="H50" t="n">
         <v>29000</v>
@@ -1877,7 +1877,7 @@
         <v>3.125</v>
       </c>
       <c r="G52" t="n">
-        <v>2.7356870174408</v>
+        <v>2.73568677902222</v>
       </c>
       <c r="H52" t="n">
         <v>24000</v>
@@ -1964,7 +1964,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>2.81009793281555</v>
+        <v>2.81009769439697</v>
       </c>
       <c r="H55" t="n">
         <v>73000</v>
@@ -2051,7 +2051,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>2.80134344100952</v>
+        <v>2.8013436794281</v>
       </c>
       <c r="H58" t="n">
         <v>74000</v>
@@ -2109,7 +2109,7 @@
         <v>3.25</v>
       </c>
       <c r="G60" t="n">
-        <v>2.84511494636536</v>
+        <v>2.8451144695282</v>
       </c>
       <c r="H60" t="n">
         <v>46000</v>
@@ -2167,7 +2167,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G62" t="n">
-        <v>2.81009793281555</v>
+        <v>2.81009769439697</v>
       </c>
       <c r="H62" t="n">
         <v>11000</v>
@@ -2196,7 +2196,7 @@
         <v>3.25</v>
       </c>
       <c r="G63" t="n">
-        <v>2.84511494636536</v>
+        <v>2.8451144695282</v>
       </c>
       <c r="H63" t="n">
         <v>14000</v>
@@ -2254,7 +2254,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G65" t="n">
-        <v>2.82322907447815</v>
+        <v>2.82322883605957</v>
       </c>
       <c r="H65" t="n">
         <v>17000</v>
@@ -2283,7 +2283,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G66" t="n">
-        <v>2.82322907447815</v>
+        <v>2.82322883605957</v>
       </c>
       <c r="H66" t="n">
         <v>15000</v>
@@ -2312,7 +2312,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>2.82322907447815</v>
+        <v>2.82322883605957</v>
       </c>
       <c r="H67" t="n">
         <v>1000</v>
@@ -2341,7 +2341,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>2.8276059627533</v>
+        <v>2.82760620117188</v>
       </c>
       <c r="H68" t="n">
         <v>24000</v>
@@ -2370,7 +2370,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>2.8276059627533</v>
+        <v>2.82760620117188</v>
       </c>
       <c r="H69" t="n">
         <v>9000</v>
@@ -2428,7 +2428,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>2.78821206092834</v>
+        <v>2.78821229934692</v>
       </c>
       <c r="H71" t="n">
         <v>15000</v>
@@ -2486,7 +2486,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G73" t="n">
-        <v>2.87137722969055</v>
+        <v>2.87137699127197</v>
       </c>
       <c r="H73" t="n">
         <v>14000</v>
@@ -2515,7 +2515,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G74" t="n">
-        <v>2.84949159622192</v>
+        <v>2.8494918346405</v>
       </c>
       <c r="H74" t="n">
         <v>3000</v>
@@ -2544,7 +2544,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G75" t="n">
-        <v>2.78821206092834</v>
+        <v>2.78821229934692</v>
       </c>
       <c r="H75" t="n">
         <v>10000</v>
@@ -2689,7 +2689,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G80" t="n">
-        <v>2.83198285102844</v>
+        <v>2.8319833278656</v>
       </c>
       <c r="H80" t="n">
         <v>24000</v>
@@ -2718,7 +2718,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.80134344100952</v>
+        <v>2.8013436794281</v>
       </c>
       <c r="H81" t="n">
         <v>20000</v>
@@ -2747,7 +2747,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G82" t="n">
-        <v>2.74006414413452</v>
+        <v>2.7400643825531</v>
       </c>
       <c r="H82" t="n">
         <v>7000</v>
@@ -2776,7 +2776,7 @@
         <v>3.25</v>
       </c>
       <c r="G83" t="n">
-        <v>2.84511494636536</v>
+        <v>2.8451144695282</v>
       </c>
       <c r="H83" t="n">
         <v>61000</v>
@@ -2834,7 +2834,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G85" t="n">
-        <v>2.78821206092834</v>
+        <v>2.78821229934692</v>
       </c>
       <c r="H85" t="n">
         <v>8000</v>
@@ -2892,7 +2892,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G87" t="n">
-        <v>2.80134344100952</v>
+        <v>2.8013436794281</v>
       </c>
       <c r="H87" t="n">
         <v>20000</v>
@@ -2921,7 +2921,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G88" t="n">
-        <v>2.80134344100952</v>
+        <v>2.8013436794281</v>
       </c>
       <c r="H88" t="n">
         <v>49000</v>
@@ -2979,7 +2979,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G90" t="n">
-        <v>2.8888852596283</v>
+        <v>2.88888549804688</v>
       </c>
       <c r="H90" t="n">
         <v>39000</v>
@@ -3008,7 +3008,7 @@
         <v>3.25</v>
       </c>
       <c r="G91" t="n">
-        <v>2.84511494636536</v>
+        <v>2.8451144695282</v>
       </c>
       <c r="H91" t="n">
         <v>16000</v>
@@ -3037,7 +3037,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G92" t="n">
-        <v>2.87137722969055</v>
+        <v>2.87137699127197</v>
       </c>
       <c r="H92" t="n">
         <v>8000</v>
@@ -3066,7 +3066,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G93" t="n">
-        <v>2.8888852596283</v>
+        <v>2.88888549804688</v>
       </c>
       <c r="H93" t="n">
         <v>20000</v>
@@ -3153,7 +3153,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G96" t="n">
-        <v>2.80134344100952</v>
+        <v>2.8013436794281</v>
       </c>
       <c r="H96" t="n">
         <v>9000</v>
@@ -3211,7 +3211,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>2.8276059627533</v>
+        <v>2.82760620117188</v>
       </c>
       <c r="H98" t="n">
         <v>4000</v>
@@ -3240,7 +3240,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.86699986457825</v>
+        <v>2.86700010299683</v>
       </c>
       <c r="H99" t="n">
         <v>3000</v>
@@ -3356,7 +3356,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G103" t="n">
-        <v>2.8888852596283</v>
+        <v>2.88888549804688</v>
       </c>
       <c r="H103" t="n">
         <v>8000</v>
@@ -3385,7 +3385,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G104" t="n">
-        <v>2.8888852596283</v>
+        <v>2.88888549804688</v>
       </c>
       <c r="H104" t="n">
         <v>9000</v>
@@ -3414,7 +3414,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G105" t="n">
-        <v>2.8888852596283</v>
+        <v>2.88888549804688</v>
       </c>
       <c r="H105" t="n">
         <v>13000</v>
@@ -3472,7 +3472,7 @@
         <v>4</v>
       </c>
       <c r="G107" t="n">
-        <v>3.50167942047119</v>
+        <v>3.50167965888977</v>
       </c>
       <c r="H107" t="n">
         <v>164000</v>
@@ -3501,7 +3501,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>4.39460754394531</v>
+        <v>4.39460802078247</v>
       </c>
       <c r="H108" t="n">
         <v>137000</v>
@@ -3530,7 +3530,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G109" t="n">
-        <v>3.96565222740173</v>
+        <v>3.96565198898315</v>
       </c>
       <c r="H109" t="n">
         <v>596000</v>
@@ -3559,7 +3559,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>4.11447334289551</v>
+        <v>4.11447286605835</v>
       </c>
       <c r="H110" t="n">
         <v>568000</v>
@@ -3617,7 +3617,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G112" t="n">
-        <v>3.64174652099609</v>
+        <v>3.64174675941467</v>
       </c>
       <c r="H112" t="n">
         <v>202000</v>
@@ -3646,7 +3646,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G113" t="n">
-        <v>3.52794218063354</v>
+        <v>3.52794241905212</v>
       </c>
       <c r="H113" t="n">
         <v>87000</v>
@@ -3675,7 +3675,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>3.65487790107727</v>
+        <v>3.65487813949585</v>
       </c>
       <c r="H114" t="n">
         <v>318000</v>
@@ -3704,7 +3704,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G115" t="n">
-        <v>3.77305960655212</v>
+        <v>3.77305936813354</v>
       </c>
       <c r="H115" t="n">
         <v>88000</v>
@@ -3733,7 +3733,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>3.97878313064575</v>
+        <v>3.97878360748291</v>
       </c>
       <c r="H116" t="n">
         <v>371000</v>
@@ -3762,7 +3762,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>3.91312623023987</v>
+        <v>3.91312646865845</v>
       </c>
       <c r="H117" t="n">
         <v>152000</v>
@@ -3791,7 +3791,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>3.86060166358948</v>
+        <v>3.8606014251709</v>
       </c>
       <c r="H118" t="n">
         <v>82000</v>
@@ -3820,7 +3820,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G119" t="n">
-        <v>3.79932260513306</v>
+        <v>3.79932188987732</v>
       </c>
       <c r="H119" t="n">
         <v>66000</v>
@@ -3878,7 +3878,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G121" t="n">
-        <v>3.89124178886414</v>
+        <v>3.89124155044556</v>
       </c>
       <c r="H121" t="n">
         <v>84000</v>
@@ -3907,7 +3907,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G122" t="n">
-        <v>3.92625784873962</v>
+        <v>3.92625856399536</v>
       </c>
       <c r="H122" t="n">
         <v>35000</v>
@@ -3965,7 +3965,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G124" t="n">
-        <v>4.1713752746582</v>
+        <v>4.17137575149536</v>
       </c>
       <c r="H124" t="n">
         <v>181000</v>
@@ -4052,7 +4052,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>4.28518009185791</v>
+        <v>4.28517961502075</v>
       </c>
       <c r="H127" t="n">
         <v>152000</v>
@@ -4081,7 +4081,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G128" t="n">
-        <v>4.16699886322021</v>
+        <v>4.16699838638306</v>
       </c>
       <c r="H128" t="n">
         <v>58000</v>
@@ -4168,7 +4168,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G131" t="n">
-        <v>4.04006290435791</v>
+        <v>4.04006242752075</v>
       </c>
       <c r="H131" t="n">
         <v>36000</v>
@@ -4226,7 +4226,7 @@
         <v>4.625</v>
       </c>
       <c r="G133" t="n">
-        <v>4.0488166809082</v>
+        <v>4.04881715774536</v>
       </c>
       <c r="H133" t="n">
         <v>7000</v>
@@ -4255,7 +4255,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G134" t="n">
-        <v>4.02693128585815</v>
+        <v>4.026930809021</v>
       </c>
       <c r="H134" t="n">
         <v>58000</v>
@@ -4284,7 +4284,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>3.9568977355957</v>
+        <v>3.95689749717712</v>
       </c>
       <c r="H135" t="n">
         <v>25000</v>
@@ -4342,7 +4342,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G137" t="n">
-        <v>3.98753666877747</v>
+        <v>3.9875373840332</v>
       </c>
       <c r="H137" t="n">
         <v>27000</v>
@@ -4371,7 +4371,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G138" t="n">
-        <v>3.99629139900208</v>
+        <v>3.99629187583923</v>
       </c>
       <c r="H138" t="n">
         <v>9000</v>
@@ -4400,7 +4400,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G139" t="n">
-        <v>4.21952390670776</v>
+        <v>4.21952438354492</v>
       </c>
       <c r="H139" t="n">
         <v>149000</v>
@@ -4429,7 +4429,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G140" t="n">
-        <v>4.13635873794556</v>
+        <v>4.13635921478271</v>
       </c>
       <c r="H140" t="n">
         <v>97000</v>
@@ -4516,7 +4516,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G143" t="n">
-        <v>5.16497707366943</v>
+        <v>5.16497755050659</v>
       </c>
       <c r="H143" t="n">
         <v>670000</v>
@@ -4545,7 +4545,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G144" t="n">
-        <v>4.76228380203247</v>
+        <v>4.76228427886963</v>
       </c>
       <c r="H144" t="n">
         <v>733000</v>
@@ -4574,7 +4574,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G145" t="n">
-        <v>4.46464061737061</v>
+        <v>4.46464157104492</v>
       </c>
       <c r="H145" t="n">
         <v>522000</v>
@@ -4603,7 +4603,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G146" t="n">
-        <v>4.38585376739502</v>
+        <v>4.38585329055786</v>
       </c>
       <c r="H146" t="n">
         <v>548000</v>
@@ -4632,7 +4632,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G147" t="n">
-        <v>4.25454044342041</v>
+        <v>4.25454092025757</v>
       </c>
       <c r="H147" t="n">
         <v>160000</v>
@@ -4690,7 +4690,7 @@
         <v>4.625</v>
       </c>
       <c r="G149" t="n">
-        <v>4.0488166809082</v>
+        <v>4.04881715774536</v>
       </c>
       <c r="H149" t="n">
         <v>105000</v>
@@ -4777,7 +4777,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>3.79932260513306</v>
+        <v>3.79932188987732</v>
       </c>
       <c r="H152" t="n">
         <v>69000</v>
@@ -4806,7 +4806,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G153" t="n">
-        <v>3.33097267150879</v>
+        <v>3.33097243309021</v>
       </c>
       <c r="H153" t="n">
         <v>164000</v>
@@ -4864,7 +4864,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G155" t="n">
-        <v>3.19965958595276</v>
+        <v>3.19965934753418</v>
       </c>
       <c r="H155" t="n">
         <v>17000</v>
@@ -4893,7 +4893,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G156" t="n">
-        <v>2.72255563735962</v>
+        <v>2.7225558757782</v>
       </c>
       <c r="H156" t="n">
         <v>96000</v>
@@ -4922,7 +4922,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G157" t="n">
-        <v>2.45555257797241</v>
+        <v>2.45555233955383</v>
       </c>
       <c r="H157" t="n">
         <v>83000</v>
@@ -4980,7 +4980,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>2.77508115768433</v>
+        <v>2.77508091926575</v>
       </c>
       <c r="H159" t="n">
         <v>58000</v>
@@ -5009,7 +5009,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G160" t="n">
-        <v>2.8888852596283</v>
+        <v>2.88888549804688</v>
       </c>
       <c r="H160" t="n">
         <v>26000</v>
@@ -5038,7 +5038,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G161" t="n">
-        <v>2.95891952514648</v>
+        <v>2.95891928672791</v>
       </c>
       <c r="H161" t="n">
         <v>30000</v>
@@ -5154,7 +5154,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G165" t="n">
-        <v>3.58046722412109</v>
+        <v>3.58046746253967</v>
       </c>
       <c r="H165" t="n">
         <v>47000</v>
@@ -5183,7 +5183,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.75555109977722</v>
+        <v>3.75555086135864</v>
       </c>
       <c r="H166" t="n">
         <v>119000</v>
@@ -5212,7 +5212,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G167" t="n">
-        <v>3.71177983283997</v>
+        <v>3.71177959442139</v>
       </c>
       <c r="H167" t="n">
         <v>54000</v>
@@ -5241,7 +5241,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>3.62861514091492</v>
+        <v>3.6286153793335</v>
       </c>
       <c r="H168" t="n">
         <v>19000</v>
@@ -5270,7 +5270,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G169" t="n">
-        <v>3.60672926902771</v>
+        <v>3.60672974586487</v>
       </c>
       <c r="H169" t="n">
         <v>15000</v>
@@ -5328,7 +5328,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G171" t="n">
-        <v>3.73366546630859</v>
+        <v>3.73366570472717</v>
       </c>
       <c r="H171" t="n">
         <v>10000</v>
@@ -5357,7 +5357,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G172" t="n">
-        <v>3.68551754951477</v>
+        <v>3.68551802635193</v>
       </c>
       <c r="H172" t="n">
         <v>16000</v>
@@ -5444,7 +5444,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G175" t="n">
-        <v>3.94376683235168</v>
+        <v>3.94376659393311</v>
       </c>
       <c r="H175" t="n">
         <v>24000</v>
@@ -5473,7 +5473,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>4.07070255279541</v>
+        <v>4.07070207595825</v>
       </c>
       <c r="H176" t="n">
         <v>44000</v>
@@ -5502,7 +5502,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>4.07070255279541</v>
+        <v>4.07070207595825</v>
       </c>
       <c r="H177" t="n">
         <v>17000</v>
@@ -5560,7 +5560,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G179" t="n">
-        <v>3.70302581787109</v>
+        <v>3.70302605628967</v>
       </c>
       <c r="H179" t="n">
         <v>30000</v>
@@ -5589,7 +5589,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G180" t="n">
-        <v>3.83433890342712</v>
+        <v>3.83433866500854</v>
       </c>
       <c r="H180" t="n">
         <v>29000</v>
@@ -5618,7 +5618,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G181" t="n">
-        <v>3.87810969352722</v>
+        <v>3.8781099319458</v>
       </c>
       <c r="H181" t="n">
         <v>9000</v>
@@ -5647,7 +5647,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G182" t="n">
-        <v>3.70302581787109</v>
+        <v>3.70302605628967</v>
       </c>
       <c r="H182" t="n">
         <v>15000</v>
@@ -5676,7 +5676,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>3.80807614326477</v>
+        <v>3.80807638168335</v>
       </c>
       <c r="H183" t="n">
         <v>2000</v>
@@ -5734,7 +5734,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G185" t="n">
-        <v>3.79056787490845</v>
+        <v>3.79056763648987</v>
       </c>
       <c r="H185" t="n">
         <v>4000</v>
@@ -5763,7 +5763,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>3.86935591697693</v>
+        <v>3.86935544013977</v>
       </c>
       <c r="H186" t="n">
         <v>15000</v>
@@ -5792,7 +5792,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G187" t="n">
-        <v>3.86060166358948</v>
+        <v>3.8606014251709</v>
       </c>
       <c r="H187" t="n">
         <v>5000</v>
@@ -5821,7 +5821,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>3.77743649482727</v>
+        <v>3.77743697166443</v>
       </c>
       <c r="H188" t="n">
         <v>7000</v>
@@ -5879,7 +5879,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G190" t="n">
-        <v>3.78224873542786</v>
+        <v>3.78224897384644</v>
       </c>
       <c r="H190" t="n">
         <v>11000</v>
@@ -5937,7 +5937,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G192" t="n">
-        <v>3.78668785095215</v>
+        <v>3.78668808937073</v>
       </c>
       <c r="H192" t="n">
         <v>2000</v>
@@ -5966,7 +5966,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G193" t="n">
-        <v>3.66682815551758</v>
+        <v>3.66682839393616</v>
       </c>
       <c r="H193" t="n">
         <v>9000</v>
@@ -6024,7 +6024,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G195" t="n">
-        <v>3.78224873542786</v>
+        <v>3.78224897384644</v>
       </c>
       <c r="H195" t="n">
         <v>8000</v>
@@ -6053,7 +6053,7 @@
         <v>4.25</v>
       </c>
       <c r="G196" t="n">
-        <v>3.77337002754211</v>
+        <v>3.77337026596069</v>
       </c>
       <c r="H196" t="n">
         <v>7000</v>
@@ -6082,7 +6082,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>3.79112696647644</v>
+        <v>3.79112720489502</v>
       </c>
       <c r="H197" t="n">
         <v>2000</v>
@@ -6140,7 +6140,7 @@
         <v>4.5</v>
       </c>
       <c r="G199" t="n">
-        <v>3.99533343315125</v>
+        <v>3.99533319473267</v>
       </c>
       <c r="H199" t="n">
         <v>99000</v>
@@ -6169,7 +6169,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G200" t="n">
-        <v>3.86215496063232</v>
+        <v>3.86215543746948</v>
       </c>
       <c r="H200" t="n">
         <v>46000</v>
@@ -6227,7 +6227,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>3.83108067512512</v>
+        <v>3.8310809135437</v>
       </c>
       <c r="H202" t="n">
         <v>10000</v>
@@ -6256,7 +6256,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G203" t="n">
-        <v>3.71122050285339</v>
+        <v>3.71122074127197</v>
       </c>
       <c r="H203" t="n">
         <v>67000</v>
@@ -6285,7 +6285,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G204" t="n">
-        <v>3.82220196723938</v>
+        <v>3.82220220565796</v>
       </c>
       <c r="H204" t="n">
         <v>7000</v>
@@ -6314,7 +6314,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G205" t="n">
-        <v>3.82220196723938</v>
+        <v>3.82220220565796</v>
       </c>
       <c r="H205" t="n">
         <v>12000</v>
@@ -6401,7 +6401,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90654802322388</v>
+        <v>3.9065477848053</v>
       </c>
       <c r="H208" t="n">
         <v>30000</v>
@@ -6430,7 +6430,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>3.86215496063232</v>
+        <v>3.86215543746948</v>
       </c>
       <c r="H209" t="n">
         <v>8000</v>
@@ -6459,7 +6459,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>3.86215496063232</v>
+        <v>3.86215543746948</v>
       </c>
       <c r="H210" t="n">
         <v>2000</v>
@@ -6517,7 +6517,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>3.95981955528259</v>
+        <v>3.95981884002686</v>
       </c>
       <c r="H212" t="n">
         <v>9000</v>
@@ -6546,7 +6546,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>3.91986584663391</v>
+        <v>3.91986608505249</v>
       </c>
       <c r="H213" t="n">
         <v>11000</v>
@@ -6633,7 +6633,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G216" t="n">
-        <v>3.91542625427246</v>
+        <v>3.91542649269104</v>
       </c>
       <c r="H216" t="n">
         <v>19000</v>
@@ -6662,7 +6662,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G217" t="n">
-        <v>3.94206213951111</v>
+        <v>3.94206190109253</v>
       </c>
       <c r="H217" t="n">
         <v>13000</v>
@@ -6691,7 +6691,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G218" t="n">
-        <v>3.96425914764404</v>
+        <v>3.96425890922546</v>
       </c>
       <c r="H218" t="n">
         <v>43000</v>
@@ -6778,7 +6778,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G221" t="n">
-        <v>4.0486044883728</v>
+        <v>4.04860401153564</v>
       </c>
       <c r="H221" t="n">
         <v>13000</v>
@@ -6807,7 +6807,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G222" t="n">
-        <v>4.06636142730713</v>
+        <v>4.06636095046997</v>
       </c>
       <c r="H222" t="n">
         <v>3000</v>
@@ -6836,7 +6836,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G223" t="n">
-        <v>4.04416561126709</v>
+        <v>4.04416513442993</v>
       </c>
       <c r="H223" t="n">
         <v>17000</v>
@@ -6865,7 +6865,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G224" t="n">
-        <v>4.0486044883728</v>
+        <v>4.04860401153564</v>
       </c>
       <c r="H224" t="n">
         <v>5000</v>
@@ -6894,7 +6894,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>3.95981955528259</v>
+        <v>3.95981884002686</v>
       </c>
       <c r="H225" t="n">
         <v>10000</v>
@@ -6952,7 +6952,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>3.97313737869263</v>
+        <v>3.97313666343689</v>
       </c>
       <c r="H227" t="n">
         <v>9000</v>
@@ -6981,7 +6981,7 @@
         <v>4.5</v>
       </c>
       <c r="G228" t="n">
-        <v>3.99533343315125</v>
+        <v>3.99533319473267</v>
       </c>
       <c r="H228" t="n">
         <v>7000</v>
@@ -7039,7 +7039,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G230" t="n">
-        <v>3.9864547252655</v>
+        <v>3.98645424842834</v>
       </c>
       <c r="H230" t="n">
         <v>16000</v>
@@ -7068,7 +7068,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G231" t="n">
-        <v>4.06636142730713</v>
+        <v>4.06636095046997</v>
       </c>
       <c r="H231" t="n">
         <v>61000</v>
@@ -7097,7 +7097,7 @@
         <v>4.5</v>
       </c>
       <c r="G232" t="n">
-        <v>3.99533343315125</v>
+        <v>3.99533319473267</v>
       </c>
       <c r="H232" t="n">
         <v>19000</v>
@@ -7126,7 +7126,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G233" t="n">
-        <v>4.0486044883728</v>
+        <v>4.04860401153564</v>
       </c>
       <c r="H233" t="n">
         <v>9000</v>
@@ -7155,7 +7155,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G234" t="n">
-        <v>4.06636142730713</v>
+        <v>4.06636095046997</v>
       </c>
       <c r="H234" t="n">
         <v>13000</v>
@@ -7184,7 +7184,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G235" t="n">
-        <v>4.08411836624146</v>
+        <v>4.0841178894043</v>
       </c>
       <c r="H235" t="n">
         <v>10000</v>
@@ -7271,7 +7271,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.48365211486816</v>
+        <v>4.48365163803101</v>
       </c>
       <c r="H238" t="n">
         <v>99000</v>
@@ -7329,7 +7329,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G240" t="n">
-        <v>4.43481969833374</v>
+        <v>4.43481922149658</v>
       </c>
       <c r="H240" t="n">
         <v>39000</v>
@@ -7358,7 +7358,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>4.33271741867065</v>
+        <v>4.3327169418335</v>
       </c>
       <c r="H241" t="n">
         <v>24000</v>
@@ -7387,7 +7387,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G242" t="n">
-        <v>4.4126238822937</v>
+        <v>4.41262340545654</v>
       </c>
       <c r="H242" t="n">
         <v>26000</v>
@@ -7474,7 +7474,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G245" t="n">
-        <v>4.24393224716187</v>
+        <v>4.24393177032471</v>
       </c>
       <c r="H245" t="n">
         <v>12000</v>
@@ -7503,7 +7503,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>4.3105206489563</v>
+        <v>4.31052017211914</v>
       </c>
       <c r="H246" t="n">
         <v>21000</v>
@@ -7706,7 +7706,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G253" t="n">
-        <v>3.86215496063232</v>
+        <v>3.86215543746948</v>
       </c>
       <c r="H253" t="n">
         <v>21000</v>
@@ -7735,7 +7735,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G254" t="n">
-        <v>3.88879108428955</v>
+        <v>3.88879084587097</v>
       </c>
       <c r="H254" t="n">
         <v>21000</v>
@@ -7764,7 +7764,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G255" t="n">
-        <v>3.96425914764404</v>
+        <v>3.96425890922546</v>
       </c>
       <c r="H255" t="n">
         <v>2000</v>
@@ -7793,7 +7793,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>4.06636142730713</v>
+        <v>4.06636095046997</v>
       </c>
       <c r="H256" t="n">
         <v>12000</v>
@@ -7909,7 +7909,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>4.19509983062744</v>
+        <v>4.1951003074646</v>
       </c>
       <c r="H260" t="n">
         <v>17000</v>
@@ -8083,7 +8083,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>4.04416561126709</v>
+        <v>4.04416513442993</v>
       </c>
       <c r="H266" t="n">
         <v>23000</v>
@@ -8112,7 +8112,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>4.08411836624146</v>
+        <v>4.0841178894043</v>
       </c>
       <c r="H267" t="n">
         <v>3000</v>
@@ -8170,7 +8170,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G269" t="n">
-        <v>3.94206213951111</v>
+        <v>3.94206190109253</v>
       </c>
       <c r="H269" t="n">
         <v>21000</v>
@@ -8199,7 +8199,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>3.90654802322388</v>
+        <v>3.9065477848053</v>
       </c>
       <c r="H270" t="n">
         <v>13000</v>
@@ -8257,7 +8257,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>3.95981955528259</v>
+        <v>3.95981884002686</v>
       </c>
       <c r="H272" t="n">
         <v>11000</v>
@@ -8286,7 +8286,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>3.99089431762695</v>
+        <v>3.99089407920837</v>
       </c>
       <c r="H273" t="n">
         <v>16000</v>
@@ -8373,7 +8373,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G276" t="n">
-        <v>3.844398021698</v>
+        <v>3.84439826011658</v>
       </c>
       <c r="H276" t="n">
         <v>17000</v>
@@ -8402,7 +8402,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>3.84883761405945</v>
+        <v>3.84883785247803</v>
       </c>
       <c r="H277" t="n">
         <v>9000</v>
@@ -8431,7 +8431,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G278" t="n">
-        <v>3.84883761405945</v>
+        <v>3.84883785247803</v>
       </c>
       <c r="H278" t="n">
         <v>4000</v>
@@ -8489,7 +8489,7 @@
         <v>4.25</v>
       </c>
       <c r="G280" t="n">
-        <v>3.77337002754211</v>
+        <v>3.77337026596069</v>
       </c>
       <c r="H280" t="n">
         <v>5000</v>
@@ -8518,7 +8518,7 @@
         <v>4.25</v>
       </c>
       <c r="G281" t="n">
-        <v>3.77337002754211</v>
+        <v>3.77337026596069</v>
       </c>
       <c r="H281" t="n">
         <v>4000</v>
@@ -8605,7 +8605,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G284" t="n">
-        <v>3.80444478988647</v>
+        <v>3.80444502830505</v>
       </c>
       <c r="H284" t="n">
         <v>10000</v>
@@ -8634,7 +8634,7 @@
         <v>4.25</v>
       </c>
       <c r="G285" t="n">
-        <v>3.77337002754211</v>
+        <v>3.77337026596069</v>
       </c>
       <c r="H285" t="n">
         <v>8000</v>
@@ -8779,7 +8779,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G290" t="n">
-        <v>3.58692121505737</v>
+        <v>3.58692145347595</v>
       </c>
       <c r="H290" t="n">
         <v>3000</v>
@@ -8808,7 +8808,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G291" t="n">
-        <v>3.71122050285339</v>
+        <v>3.71122074127197</v>
       </c>
       <c r="H291" t="n">
         <v>14000</v>
@@ -8866,7 +8866,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G293" t="n">
-        <v>3.82220196723938</v>
+        <v>3.82220220565796</v>
       </c>
       <c r="H293" t="n">
         <v>28000</v>
@@ -8953,7 +8953,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>3.69346356391907</v>
+        <v>3.69346380233765</v>
       </c>
       <c r="H296" t="n">
         <v>5000</v>
@@ -9040,7 +9040,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>3.58692121505737</v>
+        <v>3.58692145347595</v>
       </c>
       <c r="H299" t="n">
         <v>25000</v>
@@ -9069,7 +9069,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G300" t="n">
-        <v>3.59136056900024</v>
+        <v>3.59136080741882</v>
       </c>
       <c r="H300" t="n">
         <v>6000</v>
@@ -9127,7 +9127,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G302" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H302" t="n">
         <v>6000</v>
@@ -9156,7 +9156,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G303" t="n">
-        <v>3.63131403923035</v>
+        <v>3.63131427764893</v>
       </c>
       <c r="H303" t="n">
         <v>5000</v>
@@ -9243,7 +9243,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G306" t="n">
-        <v>3.57804298400879</v>
+        <v>3.57804322242737</v>
       </c>
       <c r="H306" t="n">
         <v>6000</v>
@@ -9272,7 +9272,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G307" t="n">
-        <v>3.6224353313446</v>
+        <v>3.62243556976318</v>
       </c>
       <c r="H307" t="n">
         <v>16000</v>
@@ -9330,7 +9330,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>3.58692121505737</v>
+        <v>3.58692145347595</v>
       </c>
       <c r="H309" t="n">
         <v>2000</v>
@@ -9504,7 +9504,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G315" t="n">
-        <v>3.33388352394104</v>
+        <v>3.33388376235962</v>
       </c>
       <c r="H315" t="n">
         <v>16000</v>
@@ -9562,7 +9562,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G317" t="n">
-        <v>3.2317807674408</v>
+        <v>3.23178052902222</v>
       </c>
       <c r="H317" t="n">
         <v>10000</v>
@@ -9678,7 +9678,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G321" t="n">
-        <v>3.09860301017761</v>
+        <v>3.09860277175903</v>
       </c>
       <c r="H321" t="n">
         <v>6000</v>
@@ -9707,7 +9707,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G322" t="n">
-        <v>3.1651918888092</v>
+        <v>3.16519212722778</v>
       </c>
       <c r="H322" t="n">
         <v>4000</v>
@@ -9765,7 +9765,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G324" t="n">
-        <v>3.2317807674408</v>
+        <v>3.23178052902222</v>
       </c>
       <c r="H324" t="n">
         <v>4000</v>
@@ -9881,7 +9881,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G328" t="n">
-        <v>3.29393005371094</v>
+        <v>3.29393029212952</v>
       </c>
       <c r="H328" t="n">
         <v>17000</v>
@@ -9910,7 +9910,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G329" t="n">
-        <v>3.17407059669495</v>
+        <v>3.17407035827637</v>
       </c>
       <c r="H329" t="n">
         <v>5000</v>
@@ -10026,7 +10026,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G333" t="n">
-        <v>3.49813628196716</v>
+        <v>3.49813604354858</v>
       </c>
       <c r="H333" t="n">
         <v>5000</v>
@@ -10142,7 +10142,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>3.43598651885986</v>
+        <v>3.43598628044128</v>
       </c>
       <c r="H337" t="n">
         <v>6000</v>
@@ -10287,7 +10287,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G342" t="n">
-        <v>3.64907121658325</v>
+        <v>3.64907145500183</v>
       </c>
       <c r="H342" t="n">
         <v>9000</v>
@@ -10316,7 +10316,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G343" t="n">
-        <v>3.5824818611145</v>
+        <v>3.58248209953308</v>
       </c>
       <c r="H343" t="n">
         <v>7000</v>
@@ -10345,7 +10345,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G344" t="n">
-        <v>3.57804298400879</v>
+        <v>3.57804322242737</v>
       </c>
       <c r="H344" t="n">
         <v>8000</v>
@@ -10374,7 +10374,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H345" t="n">
         <v>7000</v>
@@ -10403,7 +10403,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G346" t="n">
-        <v>3.56028604507446</v>
+        <v>3.56028628349304</v>
       </c>
       <c r="H346" t="n">
         <v>11000</v>
@@ -10490,7 +10490,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G349" t="n">
-        <v>3.76893091201782</v>
+        <v>3.7689311504364</v>
       </c>
       <c r="H349" t="n">
         <v>2000</v>
@@ -10519,7 +10519,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G350" t="n">
-        <v>3.76893091201782</v>
+        <v>3.7689311504364</v>
       </c>
       <c r="H350" t="n">
         <v>8000</v>
@@ -10577,7 +10577,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G352" t="n">
-        <v>3.893230676651</v>
+        <v>3.89323091506958</v>
       </c>
       <c r="H352" t="n">
         <v>36000</v>
@@ -10664,7 +10664,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G355" t="n">
-        <v>3.91542625427246</v>
+        <v>3.91542649269104</v>
       </c>
       <c r="H355" t="n">
         <v>77000</v>
@@ -10693,7 +10693,7 @@
         <v>4.5</v>
       </c>
       <c r="G356" t="n">
-        <v>3.99533343315125</v>
+        <v>3.99533319473267</v>
       </c>
       <c r="H356" t="n">
         <v>22000</v>
@@ -10722,7 +10722,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>3.97313737869263</v>
+        <v>3.97313666343689</v>
       </c>
       <c r="H357" t="n">
         <v>25000</v>
@@ -10751,7 +10751,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G358" t="n">
-        <v>3.9997730255127</v>
+        <v>3.99977278709412</v>
       </c>
       <c r="H358" t="n">
         <v>13000</v>
@@ -10809,7 +10809,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G360" t="n">
-        <v>3.90654802322388</v>
+        <v>3.9065477848053</v>
       </c>
       <c r="H360" t="n">
         <v>11000</v>
@@ -10838,7 +10838,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>3.96425914764404</v>
+        <v>3.96425890922546</v>
       </c>
       <c r="H361" t="n">
         <v>20000</v>
@@ -10867,7 +10867,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>3.92874455451965</v>
+        <v>3.92874479293823</v>
       </c>
       <c r="H362" t="n">
         <v>34000</v>
@@ -10925,7 +10925,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G364" t="n">
-        <v>3.96869778633118</v>
+        <v>3.9686975479126</v>
       </c>
       <c r="H364" t="n">
         <v>5000</v>
@@ -10954,7 +10954,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G365" t="n">
-        <v>3.9864547252655</v>
+        <v>3.98645424842834</v>
       </c>
       <c r="H365" t="n">
         <v>4000</v>
@@ -10983,7 +10983,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G366" t="n">
-        <v>3.9997730255127</v>
+        <v>3.99977278709412</v>
       </c>
       <c r="H366" t="n">
         <v>31000</v>
@@ -11012,7 +11012,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>3.96425914764404</v>
+        <v>3.96425890922546</v>
       </c>
       <c r="H367" t="n">
         <v>13000</v>
@@ -11041,7 +11041,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G368" t="n">
-        <v>3.9997730255127</v>
+        <v>3.99977278709412</v>
       </c>
       <c r="H368" t="n">
         <v>61000</v>
@@ -11070,7 +11070,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>3.97313737869263</v>
+        <v>3.97313666343689</v>
       </c>
       <c r="H369" t="n">
         <v>37000</v>
@@ -11128,7 +11128,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G371" t="n">
-        <v>3.76449155807495</v>
+        <v>3.76449131965637</v>
       </c>
       <c r="H371" t="n">
         <v>26000</v>
@@ -11157,7 +11157,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G372" t="n">
-        <v>3.73341703414917</v>
+        <v>3.73341679573059</v>
       </c>
       <c r="H372" t="n">
         <v>16000</v>
@@ -11186,7 +11186,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G373" t="n">
-        <v>3.71122050285339</v>
+        <v>3.71122074127197</v>
       </c>
       <c r="H373" t="n">
         <v>18000</v>
@@ -11215,7 +11215,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G374" t="n">
-        <v>3.76449155807495</v>
+        <v>3.76449131965637</v>
       </c>
       <c r="H374" t="n">
         <v>7000</v>
@@ -11244,7 +11244,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G375" t="n">
-        <v>3.71122050285339</v>
+        <v>3.71122074127197</v>
       </c>
       <c r="H375" t="n">
         <v>7000</v>
@@ -11273,7 +11273,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G376" t="n">
-        <v>3.76449155807495</v>
+        <v>3.76449131965637</v>
       </c>
       <c r="H376" t="n">
         <v>12000</v>
@@ -11331,7 +11331,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G378" t="n">
-        <v>3.63131403923035</v>
+        <v>3.63131427764893</v>
       </c>
       <c r="H378" t="n">
         <v>15000</v>
@@ -11476,7 +11476,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G383" t="n">
-        <v>3.63575291633606</v>
+        <v>3.63575315475464</v>
       </c>
       <c r="H383" t="n">
         <v>39000</v>
@@ -11534,7 +11534,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G385" t="n">
-        <v>3.60467839241028</v>
+        <v>3.60467863082886</v>
       </c>
       <c r="H385" t="n">
         <v>23000</v>
@@ -11563,7 +11563,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G386" t="n">
-        <v>3.63131403923035</v>
+        <v>3.63131427764893</v>
       </c>
       <c r="H386" t="n">
         <v>13000</v>
@@ -11592,7 +11592,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G387" t="n">
-        <v>3.63131403923035</v>
+        <v>3.63131427764893</v>
       </c>
       <c r="H387" t="n">
         <v>18000</v>
@@ -11621,7 +11621,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H388" t="n">
         <v>31000</v>
@@ -11650,7 +11650,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G389" t="n">
-        <v>3.64907121658325</v>
+        <v>3.64907145500183</v>
       </c>
       <c r="H389" t="n">
         <v>25000</v>
@@ -11679,7 +11679,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>3.79112696647644</v>
+        <v>3.79112720489502</v>
       </c>
       <c r="H390" t="n">
         <v>21000</v>
@@ -11737,7 +11737,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G392" t="n">
-        <v>3.75561308860779</v>
+        <v>3.75561332702637</v>
       </c>
       <c r="H392" t="n">
         <v>102000</v>
@@ -11766,7 +11766,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G393" t="n">
-        <v>3.6224353313446</v>
+        <v>3.62243556976318</v>
       </c>
       <c r="H393" t="n">
         <v>30000</v>
@@ -11795,7 +11795,7 @@
         <v>4</v>
       </c>
       <c r="G394" t="n">
-        <v>3.55140709877014</v>
+        <v>3.5514075756073</v>
       </c>
       <c r="H394" t="n">
         <v>26000</v>
@@ -11824,7 +11824,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G395" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H395" t="n">
         <v>9000</v>
@@ -11853,7 +11853,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G396" t="n">
-        <v>3.56916427612305</v>
+        <v>3.56916451454163</v>
       </c>
       <c r="H396" t="n">
         <v>9000</v>
@@ -11882,7 +11882,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G397" t="n">
-        <v>3.61355710029602</v>
+        <v>3.6135573387146</v>
       </c>
       <c r="H397" t="n">
         <v>22000</v>
@@ -11911,7 +11911,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G398" t="n">
-        <v>3.56028604507446</v>
+        <v>3.56028628349304</v>
       </c>
       <c r="H398" t="n">
         <v>24000</v>
@@ -11940,7 +11940,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>3.59136056900024</v>
+        <v>3.59136080741882</v>
       </c>
       <c r="H399" t="n">
         <v>54000</v>
@@ -11969,7 +11969,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G400" t="n">
-        <v>3.5824818611145</v>
+        <v>3.58248209953308</v>
       </c>
       <c r="H400" t="n">
         <v>10000</v>
@@ -11998,7 +11998,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G401" t="n">
-        <v>3.57804298400879</v>
+        <v>3.57804322242737</v>
       </c>
       <c r="H401" t="n">
         <v>18000</v>
@@ -12114,7 +12114,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G405" t="n">
-        <v>3.53808927536011</v>
+        <v>3.53808951377869</v>
       </c>
       <c r="H405" t="n">
         <v>9000</v>
@@ -12143,7 +12143,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>3.58692121505737</v>
+        <v>3.58692145347595</v>
       </c>
       <c r="H406" t="n">
         <v>10000</v>
@@ -12172,7 +12172,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G407" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H407" t="n">
         <v>15000</v>
@@ -12259,7 +12259,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G410" t="n">
-        <v>3.60467839241028</v>
+        <v>3.60467863082886</v>
       </c>
       <c r="H410" t="n">
         <v>28000</v>
@@ -12288,7 +12288,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G411" t="n">
-        <v>3.58692121505737</v>
+        <v>3.58692145347595</v>
       </c>
       <c r="H411" t="n">
         <v>6000</v>
@@ -12317,7 +12317,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G412" t="n">
-        <v>3.58692121505737</v>
+        <v>3.58692145347595</v>
       </c>
       <c r="H412" t="n">
         <v>10000</v>
@@ -12375,7 +12375,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G414" t="n">
-        <v>3.60467839241028</v>
+        <v>3.60467863082886</v>
       </c>
       <c r="H414" t="n">
         <v>8000</v>
@@ -12462,7 +12462,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G417" t="n">
-        <v>3.64552783966064</v>
+        <v>3.64552760124207</v>
       </c>
       <c r="H417" t="n">
         <v>9000</v>
@@ -12520,7 +12520,7 @@
         <v>4</v>
       </c>
       <c r="G419" t="n">
-        <v>3.64097619056702</v>
+        <v>3.6409764289856</v>
       </c>
       <c r="H419" t="n">
         <v>13000</v>
@@ -12694,7 +12694,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>3.75020551681519</v>
+        <v>3.75020575523376</v>
       </c>
       <c r="H425" t="n">
         <v>18000</v>
@@ -12723,7 +12723,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G426" t="n">
-        <v>3.7593080997467</v>
+        <v>3.75930833816528</v>
       </c>
       <c r="H426" t="n">
         <v>5000</v>
@@ -12926,7 +12926,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G433" t="n">
-        <v>3.70469355583191</v>
+        <v>3.70469379425049</v>
       </c>
       <c r="H433" t="n">
         <v>5000</v>
@@ -12984,7 +12984,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G435" t="n">
-        <v>3.6136691570282</v>
+        <v>3.61366891860962</v>
       </c>
       <c r="H435" t="n">
         <v>6000</v>
@@ -13013,7 +13013,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G436" t="n">
-        <v>3.63187384605408</v>
+        <v>3.63187408447266</v>
       </c>
       <c r="H436" t="n">
         <v>17000</v>
@@ -13042,7 +13042,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G437" t="n">
-        <v>3.7593080997467</v>
+        <v>3.75930833816528</v>
       </c>
       <c r="H437" t="n">
         <v>23000</v>
@@ -13100,7 +13100,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G439" t="n">
-        <v>3.70469355583191</v>
+        <v>3.70469379425049</v>
       </c>
       <c r="H439" t="n">
         <v>20000</v>
@@ -13274,7 +13274,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G445" t="n">
-        <v>3.75020551681519</v>
+        <v>3.75020575523376</v>
       </c>
       <c r="H445" t="n">
         <v>7000</v>
@@ -13361,7 +13361,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G448" t="n">
-        <v>3.80482006072998</v>
+        <v>3.80482029914856</v>
       </c>
       <c r="H448" t="n">
         <v>12000</v>
@@ -13390,7 +13390,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G449" t="n">
-        <v>3.7593080997467</v>
+        <v>3.75930833816528</v>
       </c>
       <c r="H449" t="n">
         <v>17000</v>
@@ -13419,7 +13419,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G450" t="n">
-        <v>3.75020551681519</v>
+        <v>3.75020575523376</v>
       </c>
       <c r="H450" t="n">
         <v>8000</v>
@@ -13477,7 +13477,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G452" t="n">
-        <v>3.75020551681519</v>
+        <v>3.75020575523376</v>
       </c>
       <c r="H452" t="n">
         <v>7000</v>
@@ -13535,7 +13535,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G454" t="n">
-        <v>3.70469355583191</v>
+        <v>3.70469379425049</v>
       </c>
       <c r="H454" t="n">
         <v>25000</v>
@@ -13593,7 +13593,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G456" t="n">
-        <v>3.68648862838745</v>
+        <v>3.68648886680603</v>
       </c>
       <c r="H456" t="n">
         <v>10000</v>
@@ -13651,7 +13651,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>3.68648862838745</v>
+        <v>3.68648886680603</v>
       </c>
       <c r="H458" t="n">
         <v>15000</v>
@@ -13680,7 +13680,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G459" t="n">
-        <v>3.67738604545593</v>
+        <v>3.67738628387451</v>
       </c>
       <c r="H459" t="n">
         <v>6000</v>
@@ -13796,7 +13796,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G463" t="n">
-        <v>3.51354217529297</v>
+        <v>3.51354193687439</v>
       </c>
       <c r="H463" t="n">
         <v>21000</v>
@@ -14637,7 +14637,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>3.39521050453186</v>
+        <v>3.39521026611328</v>
       </c>
       <c r="H492" t="n">
         <v>13000</v>
@@ -14724,7 +14724,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G495" t="n">
-        <v>3.56815695762634</v>
+        <v>3.56815671920776</v>
       </c>
       <c r="H495" t="n">
         <v>69000</v>
@@ -14753,7 +14753,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G496" t="n">
-        <v>3.52264451980591</v>
+        <v>3.52264428138733</v>
       </c>
       <c r="H496" t="n">
         <v>12000</v>
@@ -14811,7 +14811,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G498" t="n">
-        <v>3.52264451980591</v>
+        <v>3.52264428138733</v>
       </c>
       <c r="H498" t="n">
         <v>5000</v>
@@ -15014,7 +15014,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G505" t="n">
-        <v>3.49533724784851</v>
+        <v>3.49533700942993</v>
       </c>
       <c r="H505" t="n">
         <v>5000</v>
@@ -15043,7 +15043,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>3.44982504844666</v>
+        <v>3.44982481002808</v>
       </c>
       <c r="H506" t="n">
         <v>32000</v>
@@ -15362,7 +15362,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G517" t="n">
-        <v>3.34969830513</v>
+        <v>3.34969806671143</v>
       </c>
       <c r="H517" t="n">
         <v>14000</v>
@@ -15565,7 +15565,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G524" t="n">
-        <v>3.30418610572815</v>
+        <v>3.30418586730957</v>
       </c>
       <c r="H524" t="n">
         <v>6000</v>
@@ -15623,7 +15623,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G526" t="n">
-        <v>3.30418610572815</v>
+        <v>3.30418586730957</v>
       </c>
       <c r="H526" t="n">
         <v>2000</v>
@@ -15652,7 +15652,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G527" t="n">
-        <v>3.29508352279663</v>
+        <v>3.29508328437805</v>
       </c>
       <c r="H527" t="n">
         <v>5000</v>
@@ -15681,7 +15681,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>3.29508352279663</v>
+        <v>3.29508328437805</v>
       </c>
       <c r="H528" t="n">
         <v>4000</v>
@@ -16116,7 +16116,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G543" t="n">
-        <v>3.29508352279663</v>
+        <v>3.29508328437805</v>
       </c>
       <c r="H543" t="n">
         <v>21000</v>
@@ -16174,7 +16174,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G545" t="n">
-        <v>3.2313666343689</v>
+        <v>3.23136639595032</v>
       </c>
       <c r="H545" t="n">
         <v>3000</v>
@@ -16203,7 +16203,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G546" t="n">
-        <v>3.1767520904541</v>
+        <v>3.17675185203552</v>
       </c>
       <c r="H546" t="n">
         <v>9000</v>
@@ -16290,7 +16290,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G549" t="n">
-        <v>3.13123989105225</v>
+        <v>3.13123965263367</v>
       </c>
       <c r="H549" t="n">
         <v>15000</v>
@@ -16319,7 +16319,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G550" t="n">
-        <v>3.13123989105225</v>
+        <v>3.13123965263367</v>
       </c>
       <c r="H550" t="n">
         <v>10000</v>
@@ -16348,7 +16348,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G551" t="n">
-        <v>3.1767520904541</v>
+        <v>3.17675185203552</v>
       </c>
       <c r="H551" t="n">
         <v>1000</v>
@@ -16377,7 +16377,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G552" t="n">
-        <v>3.1767520904541</v>
+        <v>3.17675185203552</v>
       </c>
       <c r="H552" t="n">
         <v>1000</v>
@@ -16464,7 +16464,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G555" t="n">
-        <v>3.15854692459106</v>
+        <v>3.15854716300964</v>
       </c>
       <c r="H555" t="n">
         <v>12000</v>
@@ -16638,7 +16638,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G561" t="n">
-        <v>2.62150287628174</v>
+        <v>2.62150311470032</v>
       </c>
       <c r="H561" t="n">
         <v>88000</v>
@@ -16696,7 +16696,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G563" t="n">
-        <v>2.62150287628174</v>
+        <v>2.62150311470032</v>
       </c>
       <c r="H563" t="n">
         <v>98000</v>
@@ -16725,7 +16725,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>2.63970804214478</v>
+        <v>2.6397078037262</v>
       </c>
       <c r="H564" t="n">
         <v>5000</v>
@@ -16754,7 +16754,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G565" t="n">
-        <v>2.66701507568359</v>
+        <v>2.66701531410217</v>
       </c>
       <c r="H565" t="n">
         <v>16000</v>
@@ -16812,7 +16812,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.67611742019653</v>
+        <v>2.67611765861511</v>
       </c>
       <c r="H567" t="n">
         <v>12000</v>
@@ -16957,7 +16957,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G572" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H572" t="n">
         <v>20000</v>
@@ -17044,7 +17044,7 @@
         <v>2.75</v>
       </c>
       <c r="G575" t="n">
-        <v>2.50317120552063</v>
+        <v>2.50317144393921</v>
       </c>
       <c r="H575" t="n">
         <v>5000</v>
@@ -17102,7 +17102,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H577" t="n">
         <v>1000</v>
@@ -17160,7 +17160,7 @@
         <v>2.75</v>
       </c>
       <c r="G579" t="n">
-        <v>2.50317120552063</v>
+        <v>2.50317144393921</v>
       </c>
       <c r="H579" t="n">
         <v>7000</v>
@@ -17363,7 +17363,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G586" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H586" t="n">
         <v>13000</v>
@@ -17392,7 +17392,7 @@
         <v>2.75</v>
       </c>
       <c r="G587" t="n">
-        <v>2.50317120552063</v>
+        <v>2.50317144393921</v>
       </c>
       <c r="H587" t="n">
         <v>7000</v>
@@ -17537,7 +17537,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G592" t="n">
-        <v>2.45765900611877</v>
+        <v>2.45765924453735</v>
       </c>
       <c r="H592" t="n">
         <v>4000</v>
@@ -17972,7 +17972,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G607" t="n">
-        <v>2.33022475242615</v>
+        <v>2.33022499084473</v>
       </c>
       <c r="H607" t="n">
         <v>3000</v>
@@ -18001,7 +18001,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G608" t="n">
-        <v>2.33022475242615</v>
+        <v>2.33022499084473</v>
       </c>
       <c r="H608" t="n">
         <v>2000</v>
@@ -18117,7 +18117,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G612" t="n">
-        <v>2.40304446220398</v>
+        <v>2.40304470062256</v>
       </c>
       <c r="H612" t="n">
         <v>7000</v>
@@ -18146,7 +18146,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G613" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H613" t="n">
         <v>9000</v>
@@ -18204,7 +18204,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G615" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H615" t="n">
         <v>6000</v>
@@ -18262,7 +18262,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G617" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H617" t="n">
         <v>5000</v>
@@ -18291,7 +18291,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G618" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18465,7 +18465,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>2.34842967987061</v>
+        <v>2.34842991828918</v>
       </c>
       <c r="H624" t="n">
         <v>4000</v>
@@ -18494,7 +18494,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G625" t="n">
-        <v>2.34842967987061</v>
+        <v>2.34842991828918</v>
       </c>
       <c r="H625" t="n">
         <v>0</v>
@@ -18523,7 +18523,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G626" t="n">
-        <v>2.34842967987061</v>
+        <v>2.34842991828918</v>
       </c>
       <c r="H626" t="n">
         <v>1000</v>
@@ -18639,7 +18639,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G630" t="n">
-        <v>2.45765900611877</v>
+        <v>2.45765924453735</v>
       </c>
       <c r="H630" t="n">
         <v>8000</v>
@@ -18668,7 +18668,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G631" t="n">
-        <v>2.44855666160583</v>
+        <v>2.44855690002441</v>
       </c>
       <c r="H631" t="n">
         <v>6000</v>
@@ -18784,7 +18784,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G635" t="n">
-        <v>2.44855666160583</v>
+        <v>2.44855690002441</v>
       </c>
       <c r="H635" t="n">
         <v>2000</v>
@@ -18813,7 +18813,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G636" t="n">
-        <v>2.44855666160583</v>
+        <v>2.44855690002441</v>
       </c>
       <c r="H636" t="n">
         <v>0</v>
@@ -18900,7 +18900,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G639" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H639" t="n">
         <v>27000</v>
@@ -18929,7 +18929,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G640" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H640" t="n">
         <v>5000</v>
@@ -19132,7 +19132,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H647" t="n">
         <v>33000</v>
@@ -19161,7 +19161,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G648" t="n">
-        <v>2.16638112068176</v>
+        <v>2.16638088226318</v>
       </c>
       <c r="H648" t="n">
         <v>7000</v>
@@ -19190,7 +19190,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G649" t="n">
-        <v>2.07535648345947</v>
+        <v>2.07535624504089</v>
       </c>
       <c r="H649" t="n">
         <v>31000</v>
@@ -19219,7 +19219,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G650" t="n">
-        <v>2.09356141090393</v>
+        <v>2.09356117248535</v>
       </c>
       <c r="H650" t="n">
         <v>14000</v>
@@ -19306,7 +19306,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G653" t="n">
-        <v>2.19368815422058</v>
+        <v>2.19368839263916</v>
       </c>
       <c r="H653" t="n">
         <v>52000</v>
@@ -19335,7 +19335,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G654" t="n">
-        <v>2.12086868286133</v>
+        <v>2.12086844444275</v>
       </c>
       <c r="H654" t="n">
         <v>10000</v>
@@ -19393,7 +19393,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.46676182746887</v>
+        <v>2.46676158905029</v>
       </c>
       <c r="H656" t="n">
         <v>160000</v>
@@ -19422,7 +19422,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G657" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H657" t="n">
         <v>114000</v>
@@ -19480,7 +19480,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G659" t="n">
-        <v>2.40304446220398</v>
+        <v>2.40304470062256</v>
       </c>
       <c r="H659" t="n">
         <v>20000</v>
@@ -19509,7 +19509,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>2.2027907371521</v>
+        <v>2.20279097557068</v>
       </c>
       <c r="H660" t="n">
         <v>51000</v>
@@ -19567,7 +19567,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>2.15727829933167</v>
+        <v>2.15727853775024</v>
       </c>
       <c r="H662" t="n">
         <v>37000</v>
@@ -19683,7 +19683,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G666" t="n">
-        <v>2.15727829933167</v>
+        <v>2.15727853775024</v>
       </c>
       <c r="H666" t="n">
         <v>3000</v>
@@ -19770,7 +19770,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G669" t="n">
-        <v>2.16638112068176</v>
+        <v>2.16638088226318</v>
       </c>
       <c r="H669" t="n">
         <v>22000</v>
@@ -19799,7 +19799,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H670" t="n">
         <v>3000</v>
@@ -19828,7 +19828,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H671" t="n">
         <v>5000</v>
@@ -19857,7 +19857,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G672" t="n">
-        <v>2.14817595481873</v>
+        <v>2.14817571640015</v>
       </c>
       <c r="H672" t="n">
         <v>11000</v>
@@ -19973,7 +19973,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>2.12086868286133</v>
+        <v>2.12086844444275</v>
       </c>
       <c r="H676" t="n">
         <v>12000</v>
@@ -20031,7 +20031,7 @@
         <v>2.25</v>
       </c>
       <c r="G678" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H678" t="n">
         <v>3000</v>
@@ -20060,7 +20060,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G679" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H679" t="n">
         <v>1000</v>
@@ -20089,7 +20089,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G680" t="n">
-        <v>2.07535648345947</v>
+        <v>2.07535624504089</v>
       </c>
       <c r="H680" t="n">
         <v>2000</v>
@@ -20176,7 +20176,7 @@
         <v>2.25</v>
       </c>
       <c r="G683" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H683" t="n">
         <v>2000</v>
@@ -20205,7 +20205,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>2.12086868286133</v>
+        <v>2.12086844444275</v>
       </c>
       <c r="H684" t="n">
         <v>4000</v>
@@ -20263,7 +20263,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G686" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H686" t="n">
         <v>3000</v>
@@ -20292,7 +20292,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G687" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H687" t="n">
         <v>0</v>
@@ -20321,7 +20321,7 @@
         <v>2.25</v>
       </c>
       <c r="G688" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H688" t="n">
         <v>4000</v>
@@ -20350,7 +20350,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G689" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H689" t="n">
         <v>2000</v>
@@ -20379,7 +20379,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G690" t="n">
-        <v>2.00253701210022</v>
+        <v>2.00253677368164</v>
       </c>
       <c r="H690" t="n">
         <v>2000</v>
@@ -20408,7 +20408,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G691" t="n">
-        <v>1.96612727642059</v>
+        <v>1.9661271572113</v>
       </c>
       <c r="H691" t="n">
         <v>5000</v>
@@ -20437,7 +20437,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G692" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H692" t="n">
         <v>6000</v>
@@ -20466,7 +20466,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G693" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -20495,7 +20495,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G694" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H694" t="n">
         <v>0</v>
@@ -20553,7 +20553,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G696" t="n">
-        <v>2.00253701210022</v>
+        <v>2.00253677368164</v>
       </c>
       <c r="H696" t="n">
         <v>2000</v>
@@ -20756,7 +20756,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G703" t="n">
-        <v>1.90241003036499</v>
+        <v>1.90241014957428</v>
       </c>
       <c r="H703" t="n">
         <v>2000</v>
@@ -20785,7 +20785,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G704" t="n">
-        <v>1.90241003036499</v>
+        <v>1.90241014957428</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -20814,7 +20814,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G705" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H705" t="n">
         <v>13000</v>
@@ -20843,7 +20843,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G706" t="n">
-        <v>1.61568331718445</v>
+        <v>1.61568319797516</v>
       </c>
       <c r="H706" t="n">
         <v>35000</v>
@@ -20872,7 +20872,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G707" t="n">
-        <v>1.674849152565</v>
+        <v>1.67484903335571</v>
       </c>
       <c r="H707" t="n">
         <v>25000</v>
@@ -20901,7 +20901,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>1.72491252422333</v>
+        <v>1.72491240501404</v>
       </c>
       <c r="H708" t="n">
         <v>4000</v>
@@ -20930,7 +20930,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G709" t="n">
-        <v>1.69760525226593</v>
+        <v>1.69760513305664</v>
       </c>
       <c r="H709" t="n">
         <v>7000</v>
@@ -20959,7 +20959,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G710" t="n">
-        <v>1.73856616020203</v>
+        <v>1.73856604099274</v>
       </c>
       <c r="H710" t="n">
         <v>5000</v>
@@ -20988,7 +20988,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G711" t="n">
-        <v>1.77497601509094</v>
+        <v>1.77497589588165</v>
       </c>
       <c r="H711" t="n">
         <v>8000</v>
@@ -21133,7 +21133,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G716" t="n">
-        <v>1.73856616020203</v>
+        <v>1.73856604099274</v>
       </c>
       <c r="H716" t="n">
         <v>14000</v>
@@ -21162,7 +21162,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G717" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132214069366</v>
       </c>
       <c r="H717" t="n">
         <v>1000</v>
@@ -21191,7 +21191,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G718" t="n">
-        <v>1.73856616020203</v>
+        <v>1.73856604099274</v>
       </c>
       <c r="H718" t="n">
         <v>2000</v>
@@ -21278,7 +21278,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G721" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H721" t="n">
         <v>2000</v>
@@ -21307,7 +21307,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G722" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H722" t="n">
         <v>0</v>
@@ -21336,7 +21336,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G723" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H723" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G724" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H724" t="n">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G736" t="n">
-        <v>1.64754176139832</v>
+        <v>1.64754164218903</v>
       </c>
       <c r="H736" t="n">
         <v>5000</v>
@@ -21742,7 +21742,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G737" t="n">
-        <v>1.66574656963348</v>
+        <v>1.66574668884277</v>
       </c>
       <c r="H737" t="n">
         <v>2000</v>
@@ -21771,7 +21771,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G738" t="n">
-        <v>1.66574656963348</v>
+        <v>1.66574668884277</v>
       </c>
       <c r="H738" t="n">
         <v>8000</v>
@@ -21829,7 +21829,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G740" t="n">
-        <v>2.12086868286133</v>
+        <v>2.12086844444275</v>
       </c>
       <c r="H740" t="n">
         <v>43000</v>
@@ -21858,7 +21858,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G741" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H741" t="n">
         <v>81000</v>
@@ -21945,7 +21945,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G744" t="n">
-        <v>1.96612727642059</v>
+        <v>1.9661271572113</v>
       </c>
       <c r="H744" t="n">
         <v>12000</v>
@@ -22032,7 +22032,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G747" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H747" t="n">
         <v>12000</v>
@@ -22264,7 +22264,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G755" t="n">
-        <v>1.90241003036499</v>
+        <v>1.90241014957428</v>
       </c>
       <c r="H755" t="n">
         <v>3000</v>
@@ -22322,7 +22322,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G757" t="n">
-        <v>1.90241003036499</v>
+        <v>1.90241014957428</v>
       </c>
       <c r="H757" t="n">
         <v>3000</v>
@@ -22525,7 +22525,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G764" t="n">
-        <v>2.14817595481873</v>
+        <v>2.14817571640015</v>
       </c>
       <c r="H764" t="n">
         <v>1000</v>
@@ -22554,7 +22554,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G765" t="n">
-        <v>2.14817595481873</v>
+        <v>2.14817571640015</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G766" t="n">
-        <v>2.09356141090393</v>
+        <v>2.09356117248535</v>
       </c>
       <c r="H766" t="n">
         <v>3000</v>
@@ -22612,7 +22612,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>2.09356141090393</v>
+        <v>2.09356117248535</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -22641,7 +22641,7 @@
         <v>2.25</v>
       </c>
       <c r="G768" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H768" t="n">
         <v>1000</v>
@@ -22670,7 +22670,7 @@
         <v>2.25</v>
       </c>
       <c r="G769" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H769" t="n">
         <v>0</v>
@@ -22699,7 +22699,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G770" t="n">
-        <v>2.00253701210022</v>
+        <v>2.00253677368164</v>
       </c>
       <c r="H770" t="n">
         <v>1000</v>
@@ -22728,7 +22728,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G771" t="n">
-        <v>2.00253701210022</v>
+        <v>2.00253677368164</v>
       </c>
       <c r="H771" t="n">
         <v>0</v>
@@ -22873,7 +22873,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>2.09356141090393</v>
+        <v>2.09356117248535</v>
       </c>
       <c r="H776" t="n">
         <v>3000</v>
@@ -22902,7 +22902,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G777" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H777" t="n">
         <v>7000</v>
@@ -22931,7 +22931,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G778" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H778" t="n">
         <v>0</v>
@@ -23047,7 +23047,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G782" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H782" t="n">
         <v>6000</v>
@@ -23076,7 +23076,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G783" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H783" t="n">
         <v>5000</v>
@@ -23105,7 +23105,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G784" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H784" t="n">
         <v>0</v>
@@ -23134,7 +23134,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G785" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H785" t="n">
         <v>0</v>
@@ -23163,7 +23163,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G786" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H786" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G787" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H787" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G788" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H788" t="n">
         <v>0</v>
@@ -23250,7 +23250,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G789" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H789" t="n">
         <v>0</v>
@@ -23279,7 +23279,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G790" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H790" t="n">
         <v>0</v>
@@ -23308,7 +23308,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G791" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H791" t="n">
         <v>2000</v>
@@ -23424,7 +23424,7 @@
         <v>2.25</v>
       </c>
       <c r="G795" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H795" t="n">
         <v>1000</v>
@@ -23453,7 +23453,7 @@
         <v>2.25</v>
       </c>
       <c r="G796" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H796" t="n">
         <v>0</v>
@@ -23482,7 +23482,7 @@
         <v>2.25</v>
       </c>
       <c r="G797" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H797" t="n">
         <v>0</v>
@@ -23540,7 +23540,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G799" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H799" t="n">
         <v>2000</v>
@@ -23569,7 +23569,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G800" t="n">
-        <v>1.95702481269836</v>
+        <v>1.95702469348907</v>
       </c>
       <c r="H800" t="n">
         <v>5000</v>
@@ -23685,7 +23685,7 @@
         <v>2</v>
       </c>
       <c r="G804" t="n">
-        <v>1.82048809528351</v>
+        <v>1.8204882144928</v>
       </c>
       <c r="H804" t="n">
         <v>3000</v>
@@ -23714,7 +23714,7 @@
         <v>2</v>
       </c>
       <c r="G805" t="n">
-        <v>1.82048809528351</v>
+        <v>1.8204882144928</v>
       </c>
       <c r="H805" t="n">
         <v>0</v>
@@ -23801,7 +23801,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G808" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H808" t="n">
         <v>9000</v>
@@ -23830,7 +23830,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G809" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H809" t="n">
         <v>0</v>
@@ -23917,7 +23917,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G812" t="n">
-        <v>1.87510275840759</v>
+        <v>1.87510287761688</v>
       </c>
       <c r="H812" t="n">
         <v>4000</v>
@@ -24091,7 +24091,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G818" t="n">
-        <v>1.90241003036499</v>
+        <v>1.90241014957428</v>
       </c>
       <c r="H818" t="n">
         <v>2000</v>
@@ -24149,7 +24149,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G820" t="n">
-        <v>1.7795273065567</v>
+        <v>1.77952718734741</v>
       </c>
       <c r="H820" t="n">
         <v>8000</v>
@@ -24265,7 +24265,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H824" t="n">
         <v>1000</v>
@@ -24294,7 +24294,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H825" t="n">
         <v>0</v>
@@ -24323,7 +24323,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G826" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H826" t="n">
         <v>0</v>
@@ -24352,7 +24352,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -24381,7 +24381,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H828" t="n">
         <v>0</v>
@@ -24410,7 +24410,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G829" t="n">
-        <v>1.75677108764648</v>
+        <v>1.75677096843719</v>
       </c>
       <c r="H829" t="n">
         <v>1000</v>
@@ -24526,7 +24526,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.72491252422333</v>
+        <v>1.72491240501404</v>
       </c>
       <c r="H833" t="n">
         <v>5000</v>
@@ -24642,7 +24642,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G837" t="n">
-        <v>1.66574656963348</v>
+        <v>1.66574668884277</v>
       </c>
       <c r="H837" t="n">
         <v>1000</v>
@@ -24671,7 +24671,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G838" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H838" t="n">
         <v>15000</v>
@@ -24903,7 +24903,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G846" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H846" t="n">
         <v>7000</v>
@@ -24990,7 +24990,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G849" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H849" t="n">
         <v>9000</v>
@@ -25019,7 +25019,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G850" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H850" t="n">
         <v>8000</v>
@@ -25106,7 +25106,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G853" t="n">
-        <v>1.81593692302704</v>
+        <v>1.81593704223633</v>
       </c>
       <c r="H853" t="n">
         <v>3000</v>
@@ -25135,7 +25135,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G854" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H854" t="n">
         <v>1000</v>
@@ -25193,7 +25193,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G856" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132214069366</v>
       </c>
       <c r="H856" t="n">
         <v>1000</v>
@@ -25222,7 +25222,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G857" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132214069366</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -25280,7 +25280,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G859" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H859" t="n">
         <v>7000</v>
@@ -25309,7 +25309,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G860" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H860" t="n">
         <v>0</v>
@@ -25396,7 +25396,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G863" t="n">
-        <v>1.73401498794556</v>
+        <v>1.73401486873627</v>
       </c>
       <c r="H863" t="n">
         <v>2000</v>
@@ -25541,7 +25541,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G868" t="n">
-        <v>1.674849152565</v>
+        <v>1.67484903335571</v>
       </c>
       <c r="H868" t="n">
         <v>4000</v>
@@ -25570,7 +25570,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G869" t="n">
-        <v>1.64754176139832</v>
+        <v>1.64754164218903</v>
       </c>
       <c r="H869" t="n">
         <v>7000</v>
@@ -25715,7 +25715,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G874" t="n">
-        <v>1.66574656963348</v>
+        <v>1.66574668884277</v>
       </c>
       <c r="H874" t="n">
         <v>7000</v>
@@ -25744,7 +25744,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>1.72491252422333</v>
+        <v>1.72491240501404</v>
       </c>
       <c r="H875" t="n">
         <v>3000</v>
@@ -25831,7 +25831,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G878" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H878" t="n">
         <v>9000</v>
@@ -25947,7 +25947,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G882" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H882" t="n">
         <v>12000</v>
@@ -26121,7 +26121,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G888" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H888" t="n">
         <v>20000</v>
@@ -26179,7 +26179,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G890" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H890" t="n">
         <v>9000</v>
@@ -26382,7 +26382,7 @@
         <v>2</v>
       </c>
       <c r="G897" t="n">
-        <v>1.82048809528351</v>
+        <v>1.8204882144928</v>
       </c>
       <c r="H897" t="n">
         <v>10000</v>
@@ -26469,7 +26469,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G900" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H900" t="n">
         <v>1000</v>
@@ -26498,7 +26498,7 @@
         <v>2</v>
       </c>
       <c r="G901" t="n">
-        <v>1.82048809528351</v>
+        <v>1.8204882144928</v>
       </c>
       <c r="H901" t="n">
         <v>1000</v>
@@ -26672,7 +26672,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H907" t="n">
         <v>2000</v>
@@ -26701,7 +26701,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G908" t="n">
-        <v>1.81593692302704</v>
+        <v>1.81593704223633</v>
       </c>
       <c r="H908" t="n">
         <v>6000</v>
@@ -26730,7 +26730,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G909" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H909" t="n">
         <v>7000</v>
@@ -26788,7 +26788,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G911" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H911" t="n">
         <v>2000</v>
@@ -26817,7 +26817,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G912" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -26846,7 +26846,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G913" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -26875,7 +26875,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G914" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H914" t="n">
         <v>3000</v>
@@ -26904,7 +26904,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G915" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -26933,7 +26933,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G916" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -26962,7 +26962,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G917" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -26991,7 +26991,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132214069366</v>
       </c>
       <c r="H918" t="n">
         <v>7000</v>
@@ -27020,7 +27020,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G919" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H919" t="n">
         <v>1000</v>
@@ -27049,7 +27049,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G920" t="n">
-        <v>1.75677108764648</v>
+        <v>1.75677096843719</v>
       </c>
       <c r="H920" t="n">
         <v>2000</v>
@@ -27136,7 +27136,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G923" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132214069366</v>
       </c>
       <c r="H923" t="n">
         <v>5000</v>
@@ -27165,7 +27165,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G924" t="n">
-        <v>1.7795273065567</v>
+        <v>1.77952718734741</v>
       </c>
       <c r="H924" t="n">
         <v>3000</v>
@@ -27194,7 +27194,7 @@
         <v>2</v>
       </c>
       <c r="G925" t="n">
-        <v>1.82048809528351</v>
+        <v>1.8204882144928</v>
       </c>
       <c r="H925" t="n">
         <v>3000</v>
@@ -27223,7 +27223,7 @@
         <v>2</v>
       </c>
       <c r="G926" t="n">
-        <v>1.82048809528351</v>
+        <v>1.8204882144928</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -27252,7 +27252,7 @@
         <v>2</v>
       </c>
       <c r="G927" t="n">
-        <v>1.82048809528351</v>
+        <v>1.8204882144928</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>2</v>
       </c>
       <c r="G935" t="n">
-        <v>1.82048809528351</v>
+        <v>1.8204882144928</v>
       </c>
       <c r="H935" t="n">
         <v>3000</v>
@@ -27571,7 +27571,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G938" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H938" t="n">
         <v>1000</v>
@@ -27629,7 +27629,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G940" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H940" t="n">
         <v>6000</v>
@@ -27658,7 +27658,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H941" t="n">
         <v>2000</v>
@@ -27687,7 +27687,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G942" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H942" t="n">
         <v>2000</v>
@@ -27716,7 +27716,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G943" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -27745,7 +27745,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G944" t="n">
-        <v>1.87510275840759</v>
+        <v>1.87510287761688</v>
       </c>
       <c r="H944" t="n">
         <v>1000</v>
@@ -27774,7 +27774,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G945" t="n">
-        <v>1.87510275840759</v>
+        <v>1.87510287761688</v>
       </c>
       <c r="H945" t="n">
         <v>0</v>
@@ -27803,7 +27803,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G946" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H946" t="n">
         <v>2000</v>
@@ -27832,7 +27832,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G947" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -27861,7 +27861,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G948" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H948" t="n">
         <v>12000</v>
@@ -27890,7 +27890,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H949" t="n">
         <v>1000</v>
@@ -27919,7 +27919,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G950" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H950" t="n">
         <v>2000</v>
@@ -27948,7 +27948,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G951" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H951" t="n">
         <v>1000</v>
@@ -28006,7 +28006,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G953" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H953" t="n">
         <v>5000</v>
@@ -28035,7 +28035,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G954" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H954" t="n">
         <v>2000</v>
@@ -28093,7 +28093,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G956" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H956" t="n">
         <v>2000</v>
@@ -28122,7 +28122,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G957" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H957" t="n">
         <v>1000</v>
@@ -28383,7 +28383,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G966" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H966" t="n">
         <v>18000</v>
@@ -28412,7 +28412,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G967" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H967" t="n">
         <v>13000</v>
@@ -29021,7 +29021,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G988" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H988" t="n">
         <v>3000</v>
@@ -29050,7 +29050,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G989" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H989" t="n">
         <v>0</v>
@@ -29079,7 +29079,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G990" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -29311,7 +29311,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G998" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H998" t="n">
         <v>2000</v>
@@ -29340,7 +29340,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G999" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -29398,7 +29398,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1001" t="n">
         <v>2000</v>
@@ -29427,7 +29427,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1002" t="n">
         <v>0</v>
@@ -29601,7 +29601,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1008" t="n">
         <v>14000</v>
@@ -29630,7 +29630,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -29659,7 +29659,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -29688,7 +29688,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -29717,7 +29717,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1012" t="n">
         <v>3000</v>
@@ -29746,7 +29746,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1013" t="n">
         <v>4000</v>
@@ -29775,7 +29775,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -29862,7 +29862,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1017" t="n">
         <v>1000</v>
@@ -29891,7 +29891,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -29920,7 +29920,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1019" t="n">
         <v>1000</v>
@@ -29949,7 +29949,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1020" t="n">
         <v>5000</v>
@@ -29978,7 +29978,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1021" t="n">
         <v>1000</v>
@@ -30007,7 +30007,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1022" t="n">
         <v>0</v>
@@ -30036,7 +30036,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1023" t="n">
         <v>1000</v>
@@ -30065,7 +30065,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1024" t="n">
         <v>2000</v>
@@ -30094,7 +30094,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1025" t="n">
         <v>14000</v>
@@ -30123,7 +30123,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1026" t="n">
         <v>5000</v>
@@ -30384,7 +30384,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1035" t="n">
         <v>5000</v>
@@ -30413,7 +30413,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -30442,7 +30442,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1037" t="n">
         <v>1000</v>
@@ -30500,7 +30500,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1039" t="n">
         <v>5000</v>
@@ -30529,7 +30529,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1040" t="n">
         <v>3000</v>
@@ -30558,7 +30558,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1041" t="n">
         <v>2000</v>
@@ -30587,7 +30587,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -30616,7 +30616,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1043" t="n">
         <v>1000</v>
@@ -30732,7 +30732,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1047" t="n">
         <v>3000</v>
@@ -30761,7 +30761,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1048" t="n">
         <v>3000</v>
@@ -30790,7 +30790,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1049" t="n">
         <v>0</v>
@@ -30848,7 +30848,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1051" t="n">
         <v>3000</v>
@@ -30877,7 +30877,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -30906,7 +30906,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1053" t="n">
         <v>0</v>
@@ -30935,7 +30935,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1054" t="n">
         <v>2000</v>
@@ -31080,7 +31080,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1059" t="n">
         <v>12000</v>
@@ -31109,7 +31109,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1060" t="n">
         <v>2000</v>
@@ -31138,7 +31138,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1061" t="n">
         <v>2000</v>
@@ -31167,7 +31167,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1062" t="n">
         <v>4000</v>
@@ -31196,7 +31196,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1063" t="n">
         <v>3000</v>
@@ -31225,7 +31225,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1064" t="n">
         <v>6000</v>
@@ -31312,7 +31312,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1067" t="n">
         <v>11000</v>
@@ -31341,7 +31341,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1068" t="n">
         <v>2000</v>
@@ -31370,7 +31370,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1069" t="n">
         <v>10000</v>
@@ -31399,7 +31399,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1070" t="n">
         <v>12000</v>
@@ -31428,7 +31428,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1071" t="n">
         <v>3000</v>
@@ -31457,7 +31457,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1072" t="n">
         <v>1000</v>
@@ -31486,7 +31486,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1073" t="n">
         <v>0</v>
@@ -31515,7 +31515,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1074" t="n">
         <v>0</v>
@@ -31631,7 +31631,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1078" t="n">
         <v>5000</v>
@@ -31863,7 +31863,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1086" t="n">
         <v>6000</v>
@@ -31892,7 +31892,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1087" t="n">
         <v>3000</v>
@@ -32037,7 +32037,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1092" t="n">
         <v>12000</v>
@@ -32066,7 +32066,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1093" t="n">
         <v>5000</v>
@@ -32095,7 +32095,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1094" t="n">
         <v>20000</v>
@@ -32124,7 +32124,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.47795939445496</v>
+        <v>1.47795927524567</v>
       </c>
       <c r="H1095" t="n">
         <v>11000</v>
@@ -32153,7 +32153,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1096" t="n">
         <v>11000</v>
@@ -32240,7 +32240,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1099" t="n">
         <v>2000</v>
@@ -32356,7 +32356,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1103" t="n">
         <v>14000</v>
@@ -32385,7 +32385,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1104" t="n">
         <v>3000</v>
@@ -32472,7 +32472,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1107" t="n">
         <v>6000</v>
@@ -32501,7 +32501,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1108" t="n">
         <v>0</v>
@@ -32617,7 +32617,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1112" t="n">
         <v>3000</v>
@@ -32646,7 +32646,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1113" t="n">
         <v>0</v>
@@ -32733,7 +32733,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.47795939445496</v>
+        <v>1.47795927524567</v>
       </c>
       <c r="H1116" t="n">
         <v>23000</v>
@@ -32849,7 +32849,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1120" t="n">
         <v>32000</v>
@@ -32965,7 +32965,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1124" t="n">
         <v>33000</v>
@@ -33023,7 +33023,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1126" t="n">
         <v>6000</v>
@@ -33081,7 +33081,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1128" t="n">
         <v>3000</v>
@@ -33168,7 +33168,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1131" t="n">
         <v>5000</v>
@@ -33255,7 +33255,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.4971536397934</v>
+        <v>1.49715352058411</v>
       </c>
       <c r="H1134" t="n">
         <v>4000</v>
@@ -33516,7 +33516,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.36279356479645</v>
+        <v>1.36279368400574</v>
       </c>
       <c r="H1143" t="n">
         <v>2000</v>
@@ -33545,7 +33545,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1144" t="n">
         <v>2000</v>
@@ -33661,7 +33661,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1148" t="n">
         <v>9000</v>
@@ -33690,7 +33690,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1149" t="n">
         <v>5000</v>
@@ -33864,7 +33864,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.36279356479645</v>
+        <v>1.36279368400574</v>
       </c>
       <c r="H1155" t="n">
         <v>10000</v>
@@ -33893,7 +33893,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.36279356479645</v>
+        <v>1.36279368400574</v>
       </c>
       <c r="H1156" t="n">
         <v>0</v>
@@ -33922,7 +33922,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.42997372150421</v>
+        <v>1.42997360229492</v>
       </c>
       <c r="H1157" t="n">
         <v>28000</v>
@@ -34009,7 +34009,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1160" t="n">
         <v>5000</v>
@@ -34067,7 +34067,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.42997372150421</v>
+        <v>1.42997360229492</v>
       </c>
       <c r="H1162" t="n">
         <v>8000</v>
@@ -34096,7 +34096,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1163" t="n">
         <v>6000</v>
@@ -34154,7 +34154,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1165" t="n">
         <v>8000</v>
@@ -34183,7 +34183,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.42997372150421</v>
+        <v>1.42997360229492</v>
       </c>
       <c r="H1166" t="n">
         <v>8000</v>
@@ -34241,7 +34241,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.42997372150421</v>
+        <v>1.42997360229492</v>
       </c>
       <c r="H1168" t="n">
         <v>4000</v>
@@ -34270,7 +34270,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1169" t="n">
         <v>6000</v>
@@ -34357,7 +34357,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1172" t="n">
         <v>8000</v>
@@ -34444,7 +34444,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1175" t="n">
         <v>21000</v>
@@ -34502,7 +34502,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1177" t="n">
         <v>2000</v>
@@ -34647,7 +34647,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1182" t="n">
         <v>8000</v>
@@ -34908,7 +34908,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1191" t="n">
         <v>75000</v>
@@ -34937,7 +34937,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1192" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1192" t="n">
         <v>77000</v>
@@ -34995,7 +34995,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1194" t="n">
         <v>95000</v>
@@ -35053,7 +35053,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1196" t="n">
         <v>16000</v>
@@ -35140,7 +35140,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1199" t="n">
         <v>60000</v>
@@ -35169,7 +35169,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.95781624317169</v>
+        <v>1.95781636238098</v>
       </c>
       <c r="H1200" t="n">
         <v>89000</v>
@@ -35198,7 +35198,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.95781624317169</v>
+        <v>1.95781636238098</v>
       </c>
       <c r="H1201" t="n">
         <v>148000</v>
@@ -35256,7 +35256,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.84265053272247</v>
+        <v>1.84265065193176</v>
       </c>
       <c r="H1203" t="n">
         <v>24000</v>
@@ -35314,7 +35314,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1205" t="n">
         <v>72000</v>
@@ -35343,7 +35343,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1206" t="n">
         <v>18000</v>
@@ -35401,7 +35401,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1208" t="n">
         <v>4000</v>
@@ -35430,7 +35430,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1209" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1209" t="n">
         <v>10000</v>
@@ -35488,7 +35488,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1211" t="n">
         <v>36000</v>
@@ -35517,7 +35517,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1212" t="n">
         <v>3000</v>
@@ -35546,7 +35546,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1213" t="n">
         <v>11000</v>
@@ -35575,7 +35575,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1214" t="n">
         <v>1000</v>
@@ -35604,7 +35604,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.4971536397934</v>
+        <v>1.49715352058411</v>
       </c>
       <c r="H1215" t="n">
         <v>7000</v>
@@ -35633,7 +35633,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1216" t="n">
         <v>4000</v>
@@ -35662,7 +35662,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1217" t="n">
         <v>68000</v>
@@ -35749,7 +35749,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1220" t="n">
         <v>10000</v>
@@ -35778,7 +35778,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1221" t="n">
         <v>11000</v>
@@ -35894,7 +35894,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1225" t="n">
         <v>9000</v>
@@ -35923,7 +35923,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1226" t="n">
         <v>14000</v>
@@ -35952,7 +35952,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1227" t="n">
         <v>7000</v>
@@ -36213,7 +36213,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1236" t="n">
         <v>19000</v>
@@ -36242,7 +36242,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1237" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1237" t="n">
         <v>18000</v>
@@ -36271,7 +36271,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1238" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1238" t="n">
         <v>1000</v>
@@ -36300,7 +36300,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1239" t="n">
         <v>4000</v>
@@ -36387,7 +36387,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1242" t="n">
         <v>2000</v>
@@ -36416,7 +36416,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1243" t="n">
         <v>0</v>
@@ -36445,7 +36445,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1244" t="n">
         <v>0</v>
@@ -36706,7 +36706,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1253" t="n">
         <v>4000</v>
@@ -36735,7 +36735,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1254" t="n">
         <v>0</v>
@@ -36851,7 +36851,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1258" t="n">
         <v>4000</v>
@@ -37141,7 +37141,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1268" t="n">
         <v>2000</v>
@@ -37170,7 +37170,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1269" t="n">
         <v>3000</v>
@@ -37199,7 +37199,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1270" t="n">
         <v>1000</v>
@@ -37228,7 +37228,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1271" t="n">
         <v>0</v>
@@ -37257,7 +37257,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1272" t="n">
         <v>1000</v>
@@ -37286,7 +37286,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1273" t="n">
         <v>12000</v>
@@ -37315,7 +37315,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1274" t="n">
         <v>0</v>
@@ -37344,7 +37344,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1275" t="n">
         <v>0</v>
@@ -37373,7 +37373,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1276" t="n">
         <v>0</v>
@@ -37518,7 +37518,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1281" t="n">
         <v>2000</v>
@@ -37547,7 +37547,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1282" t="n">
         <v>4000</v>
@@ -37576,7 +37576,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1283" t="n">
         <v>3000</v>
@@ -37605,7 +37605,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1284" t="n">
         <v>0</v>
@@ -37663,7 +37663,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1286" t="n">
         <v>6000</v>
@@ -37692,7 +37692,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1287" t="n">
         <v>2000</v>
@@ -37721,7 +37721,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.01539897918701</v>
+        <v>2.01539921760559</v>
       </c>
       <c r="H1288" t="n">
         <v>205000</v>
@@ -37779,7 +37779,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1290" t="n">
         <v>56000</v>
@@ -37924,7 +37924,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1295" t="n">
         <v>15000</v>
@@ -38011,7 +38011,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1298" t="n">
         <v>17000</v>
@@ -38040,7 +38040,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1299" t="n">
         <v>0</v>
@@ -38330,7 +38330,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.8906364440918</v>
+        <v>1.89063632488251</v>
       </c>
       <c r="H1309" t="n">
         <v>14000</v>
@@ -38359,7 +38359,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.8906364440918</v>
+        <v>1.89063632488251</v>
       </c>
       <c r="H1310" t="n">
         <v>17000</v>
@@ -38475,7 +38475,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1314" t="n">
-        <v>1.8618448972702</v>
+        <v>1.86184501647949</v>
       </c>
       <c r="H1314" t="n">
         <v>20000</v>
@@ -38504,7 +38504,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.8906364440918</v>
+        <v>1.89063632488251</v>
       </c>
       <c r="H1315" t="n">
         <v>27000</v>
@@ -38620,7 +38620,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1319" t="n">
         <v>4000</v>
@@ -38649,7 +38649,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1320" t="n">
         <v>3000</v>
@@ -38707,7 +38707,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1322" t="n">
         <v>3000</v>
@@ -38765,7 +38765,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1324" t="n">
         <v>11000</v>
@@ -38794,7 +38794,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1325" t="n">
         <v>7000</v>
@@ -38823,7 +38823,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1326" t="n">
         <v>8000</v>
@@ -38881,7 +38881,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1328" t="n">
         <v>25000</v>
@@ -39026,7 +39026,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1333" t="n">
         <v>2000</v>
@@ -39055,7 +39055,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1334" t="n">
         <v>8000</v>
@@ -39084,7 +39084,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1335" t="n">
         <v>2000</v>
@@ -39229,7 +39229,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1340" t="n">
         <v>4000</v>
@@ -39258,7 +39258,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1341" t="n">
         <v>0</v>
@@ -39432,7 +39432,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1347" t="n">
         <v>9000</v>
@@ -39461,7 +39461,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1348" t="n">
         <v>4000</v>
@@ -39490,7 +39490,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1349" t="n">
         <v>0</v>
@@ -39606,7 +39606,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1353" t="n">
         <v>5000</v>
@@ -39664,7 +39664,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1355" t="n">
         <v>8000</v>
@@ -39722,7 +39722,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1357" t="n">
         <v>3000</v>
@@ -39751,7 +39751,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1358" t="n">
         <v>2000</v>
@@ -53648,6 +53648,35 @@
         <v>12000</v>
       </c>
       <c r="I1837" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1838" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1838" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="D1838" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="E1838" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="F1838" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="G1838" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="H1838" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I1838" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>1.30437552928925</v>
+        <v>1.30437564849854</v>
       </c>
       <c r="H2" t="n">
         <v>322000</v>
@@ -456,7 +456,7 @@
         <v>1.50020003318787</v>
       </c>
       <c r="G3" t="n">
-        <v>1.31330502033234</v>
+        <v>1.31330490112305</v>
       </c>
       <c r="H3" t="n">
         <v>35000</v>
@@ -514,7 +514,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G5" t="n">
-        <v>1.62828087806702</v>
+        <v>1.62828099727631</v>
       </c>
       <c r="H5" t="n">
         <v>169000</v>
@@ -543,7 +543,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G6" t="n">
-        <v>1.62828087806702</v>
+        <v>1.62828099727631</v>
       </c>
       <c r="H6" t="n">
         <v>470000</v>
@@ -601,7 +601,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G8" t="n">
-        <v>1.63265800476074</v>
+        <v>1.63265812397003</v>
       </c>
       <c r="H8" t="n">
         <v>69000</v>
@@ -659,7 +659,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G10" t="n">
-        <v>1.87339866161346</v>
+        <v>1.87339854240417</v>
       </c>
       <c r="H10" t="n">
         <v>464000</v>
@@ -688,7 +688,7 @@
         <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.18854975700378</v>
+        <v>2.18854928016663</v>
       </c>
       <c r="H11" t="n">
         <v>315000</v>
@@ -775,7 +775,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G14" t="n">
-        <v>3.69427132606506</v>
+        <v>3.69427156448364</v>
       </c>
       <c r="H14" t="n">
         <v>633000</v>
@@ -862,7 +862,7 @@
         <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>3.50167965888977</v>
+        <v>3.50167942047119</v>
       </c>
       <c r="H17" t="n">
         <v>598000</v>
@@ -920,7 +920,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>3.8781099319458</v>
+        <v>3.87810945510864</v>
       </c>
       <c r="H19" t="n">
         <v>592000</v>
@@ -978,7 +978,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G21" t="n">
-        <v>3.52794241905212</v>
+        <v>3.52794218063354</v>
       </c>
       <c r="H21" t="n">
         <v>356000</v>
@@ -1007,7 +1007,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>3.57171297073364</v>
+        <v>3.57171320915222</v>
       </c>
       <c r="H22" t="n">
         <v>212000</v>
@@ -1036,7 +1036,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>3.43164563179016</v>
+        <v>3.43164587020874</v>
       </c>
       <c r="H23" t="n">
         <v>116000</v>
@@ -1065,7 +1065,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G24" t="n">
-        <v>3.69427132606506</v>
+        <v>3.69427156448364</v>
       </c>
       <c r="H24" t="n">
         <v>227000</v>
@@ -1094,7 +1094,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G25" t="n">
-        <v>3.55420470237732</v>
+        <v>3.55420446395874</v>
       </c>
       <c r="H25" t="n">
         <v>275000</v>
@@ -1123,7 +1123,7 @@
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>3.50167965888977</v>
+        <v>3.50167942047119</v>
       </c>
       <c r="H26" t="n">
         <v>145000</v>
@@ -1181,7 +1181,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G28" t="n">
-        <v>3.42289161682129</v>
+        <v>3.42289185523987</v>
       </c>
       <c r="H28" t="n">
         <v>30000</v>
@@ -1210,7 +1210,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G29" t="n">
-        <v>3.51918792724609</v>
+        <v>3.51918768882751</v>
       </c>
       <c r="H29" t="n">
         <v>87000</v>
@@ -1297,7 +1297,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G32" t="n">
-        <v>3.45353126525879</v>
+        <v>3.45353102684021</v>
       </c>
       <c r="H32" t="n">
         <v>39000</v>
@@ -1326,7 +1326,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>3.40976047515869</v>
+        <v>3.40976023674011</v>
       </c>
       <c r="H33" t="n">
         <v>38000</v>
@@ -1355,7 +1355,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G34" t="n">
-        <v>3.43164563179016</v>
+        <v>3.43164587020874</v>
       </c>
       <c r="H34" t="n">
         <v>27000</v>
@@ -1384,7 +1384,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G35" t="n">
-        <v>3.43164563179016</v>
+        <v>3.43164587020874</v>
       </c>
       <c r="H35" t="n">
         <v>28000</v>
@@ -1413,7 +1413,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G36" t="n">
-        <v>3.41413736343384</v>
+        <v>3.41413760185242</v>
       </c>
       <c r="H36" t="n">
         <v>60000</v>
@@ -1442,7 +1442,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G37" t="n">
-        <v>3.41413736343384</v>
+        <v>3.41413760185242</v>
       </c>
       <c r="H37" t="n">
         <v>48000</v>
@@ -1471,7 +1471,7 @@
         <v>3.75</v>
       </c>
       <c r="G38" t="n">
-        <v>3.28282427787781</v>
+        <v>3.28282451629639</v>
       </c>
       <c r="H38" t="n">
         <v>41000</v>
@@ -1500,7 +1500,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>3.28720164299011</v>
+        <v>3.28720188140869</v>
       </c>
       <c r="H39" t="n">
         <v>64000</v>
@@ -1558,7 +1558,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G41" t="n">
-        <v>2.93703365325928</v>
+        <v>2.9370334148407</v>
       </c>
       <c r="H41" t="n">
         <v>317000</v>
@@ -1587,7 +1587,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G42" t="n">
-        <v>2.78383541107178</v>
+        <v>2.7838351726532</v>
       </c>
       <c r="H42" t="n">
         <v>113000</v>
@@ -1645,7 +1645,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>2.34612536430359</v>
+        <v>2.34612512588501</v>
       </c>
       <c r="H44" t="n">
         <v>226000</v>
@@ -1674,7 +1674,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G45" t="n">
-        <v>2.98518204689026</v>
+        <v>2.98518180847168</v>
       </c>
       <c r="H45" t="n">
         <v>262000</v>
@@ -1790,7 +1790,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>2.73130965232849</v>
+        <v>2.73130989074707</v>
       </c>
       <c r="H49" t="n">
         <v>52000</v>
@@ -1819,7 +1819,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G50" t="n">
-        <v>2.74881815910339</v>
+        <v>2.74881839752197</v>
       </c>
       <c r="H50" t="n">
         <v>29000</v>
@@ -1848,7 +1848,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>2.77945780754089</v>
+        <v>2.77945804595947</v>
       </c>
       <c r="H51" t="n">
         <v>28000</v>
@@ -1877,7 +1877,7 @@
         <v>3.125</v>
       </c>
       <c r="G52" t="n">
-        <v>2.73568677902222</v>
+        <v>2.73568725585938</v>
       </c>
       <c r="H52" t="n">
         <v>24000</v>
@@ -1906,7 +1906,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>2.88450860977173</v>
+        <v>2.88450837135315</v>
       </c>
       <c r="H53" t="n">
         <v>253000</v>
@@ -2080,7 +2080,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G59" t="n">
-        <v>2.78383541107178</v>
+        <v>2.7838351726532</v>
       </c>
       <c r="H59" t="n">
         <v>31000</v>
@@ -2138,7 +2138,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G61" t="n">
-        <v>2.85824608802795</v>
+        <v>2.85824584960938</v>
       </c>
       <c r="H61" t="n">
         <v>55000</v>
@@ -2254,7 +2254,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G65" t="n">
-        <v>2.82322883605957</v>
+        <v>2.82322907447815</v>
       </c>
       <c r="H65" t="n">
         <v>17000</v>
@@ -2283,7 +2283,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G66" t="n">
-        <v>2.82322883605957</v>
+        <v>2.82322907447815</v>
       </c>
       <c r="H66" t="n">
         <v>15000</v>
@@ -2312,7 +2312,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>2.82322883605957</v>
+        <v>2.82322907447815</v>
       </c>
       <c r="H67" t="n">
         <v>1000</v>
@@ -2457,7 +2457,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>2.78383541107178</v>
+        <v>2.7838351726532</v>
       </c>
       <c r="H72" t="n">
         <v>7000</v>
@@ -2515,7 +2515,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G74" t="n">
-        <v>2.8494918346405</v>
+        <v>2.84949159622192</v>
       </c>
       <c r="H74" t="n">
         <v>3000</v>
@@ -2573,7 +2573,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G76" t="n">
-        <v>2.78383541107178</v>
+        <v>2.7838351726532</v>
       </c>
       <c r="H76" t="n">
         <v>2000</v>
@@ -2602,7 +2602,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>2.77945780754089</v>
+        <v>2.77945804595947</v>
       </c>
       <c r="H77" t="n">
         <v>18000</v>
@@ -2631,7 +2631,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>2.77070379257202</v>
+        <v>2.7707040309906</v>
       </c>
       <c r="H78" t="n">
         <v>13000</v>
@@ -2660,7 +2660,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>2.72693276405334</v>
+        <v>2.72693300247192</v>
       </c>
       <c r="H79" t="n">
         <v>6000</v>
@@ -3182,7 +3182,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>2.88450860977173</v>
+        <v>2.88450837135315</v>
       </c>
       <c r="H97" t="n">
         <v>14000</v>
@@ -3240,7 +3240,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.86700010299683</v>
+        <v>2.86699986457825</v>
       </c>
       <c r="H99" t="n">
         <v>3000</v>
@@ -3269,7 +3269,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G100" t="n">
-        <v>2.88450860977173</v>
+        <v>2.88450837135315</v>
       </c>
       <c r="H100" t="n">
         <v>5000</v>
@@ -3298,7 +3298,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G101" t="n">
-        <v>2.88450860977173</v>
+        <v>2.88450837135315</v>
       </c>
       <c r="H101" t="n">
         <v>8000</v>
@@ -3327,7 +3327,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G102" t="n">
-        <v>2.88450860977173</v>
+        <v>2.88450837135315</v>
       </c>
       <c r="H102" t="n">
         <v>5000</v>
@@ -3443,7 +3443,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G106" t="n">
-        <v>2.99831295013428</v>
+        <v>2.9983127117157</v>
       </c>
       <c r="H106" t="n">
         <v>52000</v>
@@ -3472,7 +3472,7 @@
         <v>4</v>
       </c>
       <c r="G107" t="n">
-        <v>3.50167965888977</v>
+        <v>3.50167942047119</v>
       </c>
       <c r="H107" t="n">
         <v>164000</v>
@@ -3501,7 +3501,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>4.39460802078247</v>
+        <v>4.39460706710815</v>
       </c>
       <c r="H108" t="n">
         <v>137000</v>
@@ -3559,7 +3559,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>4.11447286605835</v>
+        <v>4.11447334289551</v>
       </c>
       <c r="H110" t="n">
         <v>568000</v>
@@ -3588,7 +3588,7 @@
         <v>4.375</v>
       </c>
       <c r="G111" t="n">
-        <v>3.8299617767334</v>
+        <v>3.82996225357056</v>
       </c>
       <c r="H111" t="n">
         <v>247000</v>
@@ -3646,7 +3646,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G113" t="n">
-        <v>3.52794241905212</v>
+        <v>3.52794218063354</v>
       </c>
       <c r="H113" t="n">
         <v>87000</v>
@@ -3675,7 +3675,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>3.65487813949585</v>
+        <v>3.65487790107727</v>
       </c>
       <c r="H114" t="n">
         <v>318000</v>
@@ -3704,7 +3704,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G115" t="n">
-        <v>3.77305936813354</v>
+        <v>3.77305960655212</v>
       </c>
       <c r="H115" t="n">
         <v>88000</v>
@@ -3733,7 +3733,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>3.97878360748291</v>
+        <v>3.97878336906433</v>
       </c>
       <c r="H116" t="n">
         <v>371000</v>
@@ -3762,7 +3762,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>3.91312646865845</v>
+        <v>3.91312670707703</v>
       </c>
       <c r="H117" t="n">
         <v>152000</v>
@@ -3820,7 +3820,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G119" t="n">
-        <v>3.79932188987732</v>
+        <v>3.79932236671448</v>
       </c>
       <c r="H119" t="n">
         <v>66000</v>
@@ -3907,7 +3907,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G122" t="n">
-        <v>3.92625856399536</v>
+        <v>3.92625832557678</v>
       </c>
       <c r="H122" t="n">
         <v>35000</v>
@@ -3965,7 +3965,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G124" t="n">
-        <v>4.17137575149536</v>
+        <v>4.1713752746582</v>
       </c>
       <c r="H124" t="n">
         <v>181000</v>
@@ -3994,7 +3994,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>4.18013000488281</v>
+        <v>4.18012952804565</v>
       </c>
       <c r="H125" t="n">
         <v>73000</v>
@@ -4052,7 +4052,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>4.28517961502075</v>
+        <v>4.28518009185791</v>
       </c>
       <c r="H127" t="n">
         <v>152000</v>
@@ -4081,7 +4081,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G128" t="n">
-        <v>4.16699838638306</v>
+        <v>4.16699886322021</v>
       </c>
       <c r="H128" t="n">
         <v>58000</v>
@@ -4139,7 +4139,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>3.97002911567688</v>
+        <v>3.9700288772583</v>
       </c>
       <c r="H130" t="n">
         <v>38000</v>
@@ -4226,7 +4226,7 @@
         <v>4.625</v>
       </c>
       <c r="G133" t="n">
-        <v>4.04881715774536</v>
+        <v>4.0488166809082</v>
       </c>
       <c r="H133" t="n">
         <v>7000</v>
@@ -4255,7 +4255,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G134" t="n">
-        <v>4.026930809021</v>
+        <v>4.02693128585815</v>
       </c>
       <c r="H134" t="n">
         <v>58000</v>
@@ -4284,7 +4284,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>3.95689749717712</v>
+        <v>3.9568977355957</v>
       </c>
       <c r="H135" t="n">
         <v>25000</v>
@@ -4313,7 +4313,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G136" t="n">
-        <v>4.02255392074585</v>
+        <v>4.02255439758301</v>
       </c>
       <c r="H136" t="n">
         <v>19000</v>
@@ -4400,7 +4400,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G139" t="n">
-        <v>4.21952438354492</v>
+        <v>4.21952390670776</v>
       </c>
       <c r="H139" t="n">
         <v>149000</v>
@@ -4429,7 +4429,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G140" t="n">
-        <v>4.13635921478271</v>
+        <v>4.13635873794556</v>
       </c>
       <c r="H140" t="n">
         <v>97000</v>
@@ -4545,7 +4545,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G144" t="n">
-        <v>4.76228427886963</v>
+        <v>4.76228380203247</v>
       </c>
       <c r="H144" t="n">
         <v>733000</v>
@@ -4574,7 +4574,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G145" t="n">
-        <v>4.46464157104492</v>
+        <v>4.46464109420776</v>
       </c>
       <c r="H145" t="n">
         <v>522000</v>
@@ -4632,7 +4632,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G147" t="n">
-        <v>4.25454092025757</v>
+        <v>4.25454044342041</v>
       </c>
       <c r="H147" t="n">
         <v>160000</v>
@@ -4661,7 +4661,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>3.85184693336487</v>
+        <v>3.85184741020203</v>
       </c>
       <c r="H148" t="n">
         <v>192000</v>
@@ -4690,7 +4690,7 @@
         <v>4.625</v>
       </c>
       <c r="G149" t="n">
-        <v>4.04881715774536</v>
+        <v>4.0488166809082</v>
       </c>
       <c r="H149" t="n">
         <v>105000</v>
@@ -4719,7 +4719,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G150" t="n">
-        <v>3.781813621521</v>
+        <v>3.78181409835815</v>
       </c>
       <c r="H150" t="n">
         <v>94000</v>
@@ -4777,7 +4777,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>3.79932188987732</v>
+        <v>3.79932236671448</v>
       </c>
       <c r="H152" t="n">
         <v>69000</v>
@@ -4806,7 +4806,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G153" t="n">
-        <v>3.33097243309021</v>
+        <v>3.33097267150879</v>
       </c>
       <c r="H153" t="n">
         <v>164000</v>
@@ -4864,7 +4864,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G155" t="n">
-        <v>3.19965934753418</v>
+        <v>3.19965958595276</v>
       </c>
       <c r="H155" t="n">
         <v>17000</v>
@@ -4893,7 +4893,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G156" t="n">
-        <v>2.7225558757782</v>
+        <v>2.72255563735962</v>
       </c>
       <c r="H156" t="n">
         <v>96000</v>
@@ -4922,7 +4922,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G157" t="n">
-        <v>2.45555233955383</v>
+        <v>2.45555257797241</v>
       </c>
       <c r="H157" t="n">
         <v>83000</v>
@@ -4951,7 +4951,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>2.73130965232849</v>
+        <v>2.73130989074707</v>
       </c>
       <c r="H158" t="n">
         <v>60000</v>
@@ -5038,7 +5038,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G161" t="n">
-        <v>2.95891928672791</v>
+        <v>2.95891904830933</v>
       </c>
       <c r="H161" t="n">
         <v>30000</v>
@@ -5154,7 +5154,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G165" t="n">
-        <v>3.58046746253967</v>
+        <v>3.58046722412109</v>
       </c>
       <c r="H165" t="n">
         <v>47000</v>
@@ -5183,7 +5183,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.75555086135864</v>
+        <v>3.75555109977722</v>
       </c>
       <c r="H166" t="n">
         <v>119000</v>
@@ -5212,7 +5212,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G167" t="n">
-        <v>3.71177959442139</v>
+        <v>3.71177983283997</v>
       </c>
       <c r="H167" t="n">
         <v>54000</v>
@@ -5241,7 +5241,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>3.6286153793335</v>
+        <v>3.62861514091492</v>
       </c>
       <c r="H168" t="n">
         <v>19000</v>
@@ -5270,7 +5270,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G169" t="n">
-        <v>3.60672974586487</v>
+        <v>3.60672998428345</v>
       </c>
       <c r="H169" t="n">
         <v>15000</v>
@@ -5328,7 +5328,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G171" t="n">
-        <v>3.73366570472717</v>
+        <v>3.73366546630859</v>
       </c>
       <c r="H171" t="n">
         <v>10000</v>
@@ -5357,7 +5357,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G172" t="n">
-        <v>3.68551802635193</v>
+        <v>3.68551754951477</v>
       </c>
       <c r="H172" t="n">
         <v>16000</v>
@@ -5415,7 +5415,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.85184693336487</v>
+        <v>3.85184741020203</v>
       </c>
       <c r="H174" t="n">
         <v>74000</v>
@@ -5444,7 +5444,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G175" t="n">
-        <v>3.94376659393311</v>
+        <v>3.94376683235168</v>
       </c>
       <c r="H175" t="n">
         <v>24000</v>
@@ -5473,7 +5473,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>4.07070207595825</v>
+        <v>4.07070255279541</v>
       </c>
       <c r="H176" t="n">
         <v>44000</v>
@@ -5502,7 +5502,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>4.07070207595825</v>
+        <v>4.07070255279541</v>
       </c>
       <c r="H177" t="n">
         <v>17000</v>
@@ -5589,7 +5589,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G180" t="n">
-        <v>3.83433866500854</v>
+        <v>3.83433890342712</v>
       </c>
       <c r="H180" t="n">
         <v>29000</v>
@@ -5618,7 +5618,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G181" t="n">
-        <v>3.8781099319458</v>
+        <v>3.87810945510864</v>
       </c>
       <c r="H181" t="n">
         <v>9000</v>
@@ -5705,7 +5705,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>3.85184693336487</v>
+        <v>3.85184741020203</v>
       </c>
       <c r="H184" t="n">
         <v>8000</v>
@@ -5734,7 +5734,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G185" t="n">
-        <v>3.79056763648987</v>
+        <v>3.79056811332703</v>
       </c>
       <c r="H185" t="n">
         <v>4000</v>
@@ -5763,7 +5763,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>3.86935544013977</v>
+        <v>3.86935591697693</v>
       </c>
       <c r="H186" t="n">
         <v>15000</v>
@@ -5821,7 +5821,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>3.77743697166443</v>
+        <v>3.77743649482727</v>
       </c>
       <c r="H188" t="n">
         <v>7000</v>
@@ -5879,7 +5879,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G190" t="n">
-        <v>3.78224897384644</v>
+        <v>3.78224921226501</v>
       </c>
       <c r="H190" t="n">
         <v>11000</v>
@@ -5937,7 +5937,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G192" t="n">
-        <v>3.78668808937073</v>
+        <v>3.78668785095215</v>
       </c>
       <c r="H192" t="n">
         <v>2000</v>
@@ -5966,7 +5966,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G193" t="n">
-        <v>3.66682839393616</v>
+        <v>3.66682815551758</v>
       </c>
       <c r="H193" t="n">
         <v>9000</v>
@@ -5995,7 +5995,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G194" t="n">
-        <v>3.74673438072205</v>
+        <v>3.74673461914062</v>
       </c>
       <c r="H194" t="n">
         <v>3000</v>
@@ -6024,7 +6024,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G195" t="n">
-        <v>3.78224897384644</v>
+        <v>3.78224921226501</v>
       </c>
       <c r="H195" t="n">
         <v>8000</v>
@@ -6140,7 +6140,7 @@
         <v>4.5</v>
       </c>
       <c r="G199" t="n">
-        <v>3.99533319473267</v>
+        <v>3.99533367156982</v>
       </c>
       <c r="H199" t="n">
         <v>99000</v>
@@ -6198,7 +6198,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G201" t="n">
-        <v>3.83551979064941</v>
+        <v>3.83552026748657</v>
       </c>
       <c r="H201" t="n">
         <v>15000</v>
@@ -6401,7 +6401,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G208" t="n">
-        <v>3.9065477848053</v>
+        <v>3.90654826164246</v>
       </c>
       <c r="H208" t="n">
         <v>30000</v>
@@ -6488,7 +6488,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G211" t="n">
-        <v>3.81776285171509</v>
+        <v>3.81776332855225</v>
       </c>
       <c r="H211" t="n">
         <v>14000</v>
@@ -6517,7 +6517,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>3.95981884002686</v>
+        <v>3.95981931686401</v>
       </c>
       <c r="H212" t="n">
         <v>9000</v>
@@ -6604,7 +6604,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>4.03084707260132</v>
+        <v>4.03084754943848</v>
       </c>
       <c r="H215" t="n">
         <v>41000</v>
@@ -6662,7 +6662,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G217" t="n">
-        <v>3.94206190109253</v>
+        <v>3.94206237792969</v>
       </c>
       <c r="H217" t="n">
         <v>13000</v>
@@ -6778,7 +6778,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G221" t="n">
-        <v>4.04860401153564</v>
+        <v>4.0486044883728</v>
       </c>
       <c r="H221" t="n">
         <v>13000</v>
@@ -6807,7 +6807,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G222" t="n">
-        <v>4.06636095046997</v>
+        <v>4.06636142730713</v>
       </c>
       <c r="H222" t="n">
         <v>3000</v>
@@ -6865,7 +6865,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G224" t="n">
-        <v>4.04860401153564</v>
+        <v>4.0486044883728</v>
       </c>
       <c r="H224" t="n">
         <v>5000</v>
@@ -6894,7 +6894,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>3.95981884002686</v>
+        <v>3.95981931686401</v>
       </c>
       <c r="H225" t="n">
         <v>10000</v>
@@ -6981,7 +6981,7 @@
         <v>4.5</v>
       </c>
       <c r="G228" t="n">
-        <v>3.99533319473267</v>
+        <v>3.99533367156982</v>
       </c>
       <c r="H228" t="n">
         <v>7000</v>
@@ -7010,7 +7010,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>4.01309013366699</v>
+        <v>4.01309061050415</v>
       </c>
       <c r="H229" t="n">
         <v>13000</v>
@@ -7068,7 +7068,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G231" t="n">
-        <v>4.06636095046997</v>
+        <v>4.06636142730713</v>
       </c>
       <c r="H231" t="n">
         <v>61000</v>
@@ -7097,7 +7097,7 @@
         <v>4.5</v>
       </c>
       <c r="G232" t="n">
-        <v>3.99533319473267</v>
+        <v>3.99533367156982</v>
       </c>
       <c r="H232" t="n">
         <v>19000</v>
@@ -7126,7 +7126,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G233" t="n">
-        <v>4.04860401153564</v>
+        <v>4.0486044883728</v>
       </c>
       <c r="H233" t="n">
         <v>9000</v>
@@ -7155,7 +7155,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G234" t="n">
-        <v>4.06636095046997</v>
+        <v>4.06636142730713</v>
       </c>
       <c r="H234" t="n">
         <v>13000</v>
@@ -7184,7 +7184,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G235" t="n">
-        <v>4.0841178894043</v>
+        <v>4.08411836624146</v>
       </c>
       <c r="H235" t="n">
         <v>10000</v>
@@ -7213,7 +7213,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G236" t="n">
-        <v>4.10187530517578</v>
+        <v>4.10187578201294</v>
       </c>
       <c r="H236" t="n">
         <v>72000</v>
@@ -7300,7 +7300,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>4.40374565124512</v>
+        <v>4.40374517440796</v>
       </c>
       <c r="H239" t="n">
         <v>37000</v>
@@ -7329,7 +7329,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G240" t="n">
-        <v>4.43481922149658</v>
+        <v>4.43481969833374</v>
       </c>
       <c r="H240" t="n">
         <v>39000</v>
@@ -7358,7 +7358,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>4.3327169418335</v>
+        <v>4.33271646499634</v>
       </c>
       <c r="H241" t="n">
         <v>24000</v>
@@ -7445,7 +7445,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G244" t="n">
-        <v>4.16846466064453</v>
+        <v>4.16846418380737</v>
       </c>
       <c r="H244" t="n">
         <v>27000</v>
@@ -7532,7 +7532,7 @@
         <v>4.875</v>
       </c>
       <c r="G247" t="n">
-        <v>4.32827758789062</v>
+        <v>4.32827806472778</v>
       </c>
       <c r="H247" t="n">
         <v>9000</v>
@@ -7561,7 +7561,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>4.26168918609619</v>
+        <v>4.26168870925903</v>
       </c>
       <c r="H248" t="n">
         <v>29000</v>
@@ -7590,7 +7590,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G249" t="n">
-        <v>4.26168918609619</v>
+        <v>4.26168870925903</v>
       </c>
       <c r="H249" t="n">
         <v>15000</v>
@@ -7619,7 +7619,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G250" t="n">
-        <v>4.29720306396484</v>
+        <v>4.29720258712769</v>
       </c>
       <c r="H250" t="n">
         <v>11000</v>
@@ -7735,7 +7735,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G254" t="n">
-        <v>3.88879084587097</v>
+        <v>3.88879132270813</v>
       </c>
       <c r="H254" t="n">
         <v>21000</v>
@@ -7793,7 +7793,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>4.06636095046997</v>
+        <v>4.06636142730713</v>
       </c>
       <c r="H256" t="n">
         <v>12000</v>
@@ -7880,7 +7880,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>4.15070772171021</v>
+        <v>4.15070724487305</v>
       </c>
       <c r="H259" t="n">
         <v>48000</v>
@@ -7909,7 +7909,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>4.1951003074646</v>
+        <v>4.19509983062744</v>
       </c>
       <c r="H260" t="n">
         <v>17000</v>
@@ -7996,7 +7996,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>4.01309013366699</v>
+        <v>4.01309061050415</v>
       </c>
       <c r="H263" t="n">
         <v>9000</v>
@@ -8112,7 +8112,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>4.0841178894043</v>
+        <v>4.08411836624146</v>
       </c>
       <c r="H267" t="n">
         <v>3000</v>
@@ -8170,7 +8170,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G269" t="n">
-        <v>3.94206190109253</v>
+        <v>3.94206237792969</v>
       </c>
       <c r="H269" t="n">
         <v>21000</v>
@@ -8199,7 +8199,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>3.9065477848053</v>
+        <v>3.90654826164246</v>
       </c>
       <c r="H270" t="n">
         <v>13000</v>
@@ -8257,7 +8257,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>3.95981884002686</v>
+        <v>3.95981931686401</v>
       </c>
       <c r="H272" t="n">
         <v>11000</v>
@@ -8460,7 +8460,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G279" t="n">
-        <v>3.81776285171509</v>
+        <v>3.81776332855225</v>
       </c>
       <c r="H279" t="n">
         <v>3000</v>
@@ -8576,7 +8576,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G283" t="n">
-        <v>3.81776285171509</v>
+        <v>3.81776332855225</v>
       </c>
       <c r="H283" t="n">
         <v>2000</v>
@@ -8605,7 +8605,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G284" t="n">
-        <v>3.80444502830505</v>
+        <v>3.80444526672363</v>
       </c>
       <c r="H284" t="n">
         <v>10000</v>
@@ -8721,7 +8721,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G288" t="n">
-        <v>3.74673438072205</v>
+        <v>3.74673461914062</v>
       </c>
       <c r="H288" t="n">
         <v>1000</v>
@@ -8750,7 +8750,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G289" t="n">
-        <v>3.74673438072205</v>
+        <v>3.74673461914062</v>
       </c>
       <c r="H289" t="n">
         <v>2000</v>
@@ -8779,7 +8779,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G290" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692121505737</v>
       </c>
       <c r="H290" t="n">
         <v>3000</v>
@@ -8895,7 +8895,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G294" t="n">
-        <v>3.81776285171509</v>
+        <v>3.81776332855225</v>
       </c>
       <c r="H294" t="n">
         <v>6000</v>
@@ -8924,7 +8924,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>3.69790291786194</v>
+        <v>3.69790267944336</v>
       </c>
       <c r="H295" t="n">
         <v>13000</v>
@@ -9040,7 +9040,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692121505737</v>
       </c>
       <c r="H299" t="n">
         <v>25000</v>
@@ -9098,7 +9098,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G301" t="n">
-        <v>3.50701475143433</v>
+        <v>3.50701498985291</v>
       </c>
       <c r="H301" t="n">
         <v>10000</v>
@@ -9127,7 +9127,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G302" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59579992294312</v>
       </c>
       <c r="H302" t="n">
         <v>6000</v>
@@ -9156,7 +9156,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G303" t="n">
-        <v>3.63131427764893</v>
+        <v>3.63131403923035</v>
       </c>
       <c r="H303" t="n">
         <v>5000</v>
@@ -9243,7 +9243,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G306" t="n">
-        <v>3.57804322242737</v>
+        <v>3.57804298400879</v>
       </c>
       <c r="H306" t="n">
         <v>6000</v>
@@ -9330,7 +9330,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692121505737</v>
       </c>
       <c r="H309" t="n">
         <v>2000</v>
@@ -9417,7 +9417,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G312" t="n">
-        <v>3.46262216567993</v>
+        <v>3.46262240409851</v>
       </c>
       <c r="H312" t="n">
         <v>4000</v>
@@ -9446,7 +9446,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>3.41822934150696</v>
+        <v>3.41822957992554</v>
       </c>
       <c r="H313" t="n">
         <v>2000</v>
@@ -9475,7 +9475,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G314" t="n">
-        <v>3.41822934150696</v>
+        <v>3.41822957992554</v>
       </c>
       <c r="H314" t="n">
         <v>1000</v>
@@ -9939,7 +9939,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G330" t="n">
-        <v>3.19182753562927</v>
+        <v>3.19182729721069</v>
       </c>
       <c r="H330" t="n">
         <v>20000</v>
@@ -9968,7 +9968,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G331" t="n">
-        <v>3.4271080493927</v>
+        <v>3.42710828781128</v>
       </c>
       <c r="H331" t="n">
         <v>21000</v>
@@ -9997,7 +9997,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G332" t="n">
-        <v>3.50701475143433</v>
+        <v>3.50701498985291</v>
       </c>
       <c r="H332" t="n">
         <v>20000</v>
@@ -10026,7 +10026,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G333" t="n">
-        <v>3.49813604354858</v>
+        <v>3.49813628196716</v>
       </c>
       <c r="H333" t="n">
         <v>5000</v>
@@ -10055,7 +10055,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>3.46262216567993</v>
+        <v>3.46262240409851</v>
       </c>
       <c r="H334" t="n">
         <v>5000</v>
@@ -10084,7 +10084,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>3.46262216567993</v>
+        <v>3.46262240409851</v>
       </c>
       <c r="H335" t="n">
         <v>11000</v>
@@ -10113,7 +10113,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>3.38271546363831</v>
+        <v>3.38271570205688</v>
       </c>
       <c r="H336" t="n">
         <v>4000</v>
@@ -10142,7 +10142,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>3.43598628044128</v>
+        <v>3.43598651885986</v>
       </c>
       <c r="H337" t="n">
         <v>6000</v>
@@ -10287,7 +10287,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G342" t="n">
-        <v>3.64907145500183</v>
+        <v>3.64907121658325</v>
       </c>
       <c r="H342" t="n">
         <v>9000</v>
@@ -10345,7 +10345,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G344" t="n">
-        <v>3.57804322242737</v>
+        <v>3.57804298400879</v>
       </c>
       <c r="H344" t="n">
         <v>8000</v>
@@ -10374,7 +10374,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59579992294312</v>
       </c>
       <c r="H345" t="n">
         <v>7000</v>
@@ -10403,7 +10403,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G346" t="n">
-        <v>3.56028628349304</v>
+        <v>3.56028604507446</v>
       </c>
       <c r="H346" t="n">
         <v>11000</v>
@@ -10432,7 +10432,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G347" t="n">
-        <v>3.81776285171509</v>
+        <v>3.81776332855225</v>
       </c>
       <c r="H347" t="n">
         <v>29000</v>
@@ -10461,7 +10461,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G348" t="n">
-        <v>3.74673438072205</v>
+        <v>3.74673461914062</v>
       </c>
       <c r="H348" t="n">
         <v>35000</v>
@@ -10490,7 +10490,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G349" t="n">
-        <v>3.7689311504364</v>
+        <v>3.76893091201782</v>
       </c>
       <c r="H349" t="n">
         <v>2000</v>
@@ -10519,7 +10519,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G350" t="n">
-        <v>3.7689311504364</v>
+        <v>3.76893091201782</v>
       </c>
       <c r="H350" t="n">
         <v>8000</v>
@@ -10635,7 +10635,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>4.03084707260132</v>
+        <v>4.03084754943848</v>
       </c>
       <c r="H354" t="n">
         <v>28000</v>
@@ -10693,7 +10693,7 @@
         <v>4.5</v>
       </c>
       <c r="G356" t="n">
-        <v>3.99533319473267</v>
+        <v>3.99533367156982</v>
       </c>
       <c r="H356" t="n">
         <v>22000</v>
@@ -10809,7 +10809,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G360" t="n">
-        <v>3.9065477848053</v>
+        <v>3.90654826164246</v>
       </c>
       <c r="H360" t="n">
         <v>11000</v>
@@ -11099,7 +11099,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>3.85327672958374</v>
+        <v>3.8532772064209</v>
       </c>
       <c r="H370" t="n">
         <v>50000</v>
@@ -11128,7 +11128,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G371" t="n">
-        <v>3.76449131965637</v>
+        <v>3.76449155807495</v>
       </c>
       <c r="H371" t="n">
         <v>26000</v>
@@ -11157,7 +11157,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G372" t="n">
-        <v>3.73341679573059</v>
+        <v>3.73341655731201</v>
       </c>
       <c r="H372" t="n">
         <v>16000</v>
@@ -11215,7 +11215,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G374" t="n">
-        <v>3.76449131965637</v>
+        <v>3.76449155807495</v>
       </c>
       <c r="H374" t="n">
         <v>7000</v>
@@ -11273,7 +11273,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G376" t="n">
-        <v>3.76449131965637</v>
+        <v>3.76449155807495</v>
       </c>
       <c r="H376" t="n">
         <v>12000</v>
@@ -11331,7 +11331,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G378" t="n">
-        <v>3.63131427764893</v>
+        <v>3.63131403923035</v>
       </c>
       <c r="H378" t="n">
         <v>15000</v>
@@ -11389,7 +11389,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G380" t="n">
-        <v>3.51589322090149</v>
+        <v>3.51589345932007</v>
       </c>
       <c r="H380" t="n">
         <v>16000</v>
@@ -11418,7 +11418,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>3.51589322090149</v>
+        <v>3.51589345932007</v>
       </c>
       <c r="H381" t="n">
         <v>21000</v>
@@ -11534,7 +11534,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G385" t="n">
-        <v>3.60467863082886</v>
+        <v>3.60467839241028</v>
       </c>
       <c r="H385" t="n">
         <v>23000</v>
@@ -11563,7 +11563,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G386" t="n">
-        <v>3.63131427764893</v>
+        <v>3.63131403923035</v>
       </c>
       <c r="H386" t="n">
         <v>13000</v>
@@ -11592,7 +11592,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G387" t="n">
-        <v>3.63131427764893</v>
+        <v>3.63131403923035</v>
       </c>
       <c r="H387" t="n">
         <v>18000</v>
@@ -11621,7 +11621,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59579992294312</v>
       </c>
       <c r="H388" t="n">
         <v>31000</v>
@@ -11650,7 +11650,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G389" t="n">
-        <v>3.64907145500183</v>
+        <v>3.64907121658325</v>
       </c>
       <c r="H389" t="n">
         <v>25000</v>
@@ -11824,7 +11824,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G395" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59579992294312</v>
       </c>
       <c r="H395" t="n">
         <v>9000</v>
@@ -11853,7 +11853,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G396" t="n">
-        <v>3.56916451454163</v>
+        <v>3.56916427612305</v>
       </c>
       <c r="H396" t="n">
         <v>9000</v>
@@ -11882,7 +11882,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G397" t="n">
-        <v>3.6135573387146</v>
+        <v>3.61355710029602</v>
       </c>
       <c r="H397" t="n">
         <v>22000</v>
@@ -11911,7 +11911,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G398" t="n">
-        <v>3.56028628349304</v>
+        <v>3.56028604507446</v>
       </c>
       <c r="H398" t="n">
         <v>24000</v>
@@ -11998,7 +11998,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G401" t="n">
-        <v>3.57804322242737</v>
+        <v>3.57804298400879</v>
       </c>
       <c r="H401" t="n">
         <v>18000</v>
@@ -12143,7 +12143,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692121505737</v>
       </c>
       <c r="H406" t="n">
         <v>10000</v>
@@ -12172,7 +12172,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G407" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59579992294312</v>
       </c>
       <c r="H407" t="n">
         <v>15000</v>
@@ -12201,7 +12201,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>3.68458533287048</v>
+        <v>3.6845850944519</v>
       </c>
       <c r="H408" t="n">
         <v>8000</v>
@@ -12259,7 +12259,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G410" t="n">
-        <v>3.60467863082886</v>
+        <v>3.60467839241028</v>
       </c>
       <c r="H410" t="n">
         <v>28000</v>
@@ -12288,7 +12288,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G411" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692121505737</v>
       </c>
       <c r="H411" t="n">
         <v>6000</v>
@@ -12317,7 +12317,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G412" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692121505737</v>
       </c>
       <c r="H412" t="n">
         <v>10000</v>
@@ -12346,7 +12346,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>3.62687468528748</v>
+        <v>3.6268744468689</v>
       </c>
       <c r="H413" t="n">
         <v>9000</v>
@@ -12375,7 +12375,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G414" t="n">
-        <v>3.60467863082886</v>
+        <v>3.60467839241028</v>
       </c>
       <c r="H414" t="n">
         <v>8000</v>
@@ -12433,7 +12433,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G416" t="n">
-        <v>3.71834707260132</v>
+        <v>3.71834683418274</v>
       </c>
       <c r="H416" t="n">
         <v>18000</v>
@@ -12491,7 +12491,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G418" t="n">
-        <v>3.66828393936157</v>
+        <v>3.66828370094299</v>
       </c>
       <c r="H418" t="n">
         <v>49000</v>
@@ -12578,7 +12578,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G421" t="n">
-        <v>3.69559097290039</v>
+        <v>3.69559073448181</v>
       </c>
       <c r="H421" t="n">
         <v>9000</v>
@@ -12607,7 +12607,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G422" t="n">
-        <v>3.69559097290039</v>
+        <v>3.69559073448181</v>
       </c>
       <c r="H422" t="n">
         <v>2000</v>
@@ -12665,7 +12665,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G424" t="n">
-        <v>3.72289848327637</v>
+        <v>3.72289824485779</v>
       </c>
       <c r="H424" t="n">
         <v>6000</v>
@@ -12723,7 +12723,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G426" t="n">
-        <v>3.75930833816528</v>
+        <v>3.7593080997467</v>
       </c>
       <c r="H426" t="n">
         <v>5000</v>
@@ -12781,7 +12781,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G428" t="n">
-        <v>3.72289848327637</v>
+        <v>3.72289824485779</v>
       </c>
       <c r="H428" t="n">
         <v>8000</v>
@@ -12810,7 +12810,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G429" t="n">
-        <v>3.72289848327637</v>
+        <v>3.72289824485779</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G431" t="n">
-        <v>3.66828393936157</v>
+        <v>3.66828370094299</v>
       </c>
       <c r="H431" t="n">
         <v>2000</v>
@@ -12897,7 +12897,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G432" t="n">
-        <v>3.66828393936157</v>
+        <v>3.66828370094299</v>
       </c>
       <c r="H432" t="n">
         <v>9000</v>
@@ -12926,7 +12926,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G433" t="n">
-        <v>3.70469379425049</v>
+        <v>3.70469355583191</v>
       </c>
       <c r="H433" t="n">
         <v>5000</v>
@@ -12955,7 +12955,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>3.65918135643005</v>
+        <v>3.65918111801147</v>
       </c>
       <c r="H434" t="n">
         <v>20000</v>
@@ -12984,7 +12984,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G435" t="n">
-        <v>3.61366891860962</v>
+        <v>3.6136691570282</v>
       </c>
       <c r="H435" t="n">
         <v>6000</v>
@@ -13042,7 +13042,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G437" t="n">
-        <v>3.75930833816528</v>
+        <v>3.7593080997467</v>
       </c>
       <c r="H437" t="n">
         <v>23000</v>
@@ -13100,7 +13100,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G439" t="n">
-        <v>3.70469379425049</v>
+        <v>3.70469355583191</v>
       </c>
       <c r="H439" t="n">
         <v>20000</v>
@@ -13129,7 +13129,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G440" t="n">
-        <v>3.74110341072083</v>
+        <v>3.74110317230225</v>
       </c>
       <c r="H440" t="n">
         <v>16000</v>
@@ -13216,7 +13216,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G443" t="n">
-        <v>3.77751326560974</v>
+        <v>3.77751302719116</v>
       </c>
       <c r="H443" t="n">
         <v>17000</v>
@@ -13245,7 +13245,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G444" t="n">
-        <v>3.74110341072083</v>
+        <v>3.74110317230225</v>
       </c>
       <c r="H444" t="n">
         <v>23000</v>
@@ -13303,7 +13303,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G446" t="n">
-        <v>3.72289848327637</v>
+        <v>3.72289824485779</v>
       </c>
       <c r="H446" t="n">
         <v>14000</v>
@@ -13390,7 +13390,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G449" t="n">
-        <v>3.75930833816528</v>
+        <v>3.7593080997467</v>
       </c>
       <c r="H449" t="n">
         <v>17000</v>
@@ -13448,7 +13448,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>3.77751326560974</v>
+        <v>3.77751302719116</v>
       </c>
       <c r="H451" t="n">
         <v>7000</v>
@@ -13506,7 +13506,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G453" t="n">
-        <v>3.74110341072083</v>
+        <v>3.74110317230225</v>
       </c>
       <c r="H453" t="n">
         <v>6000</v>
@@ -13535,7 +13535,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G454" t="n">
-        <v>3.70469379425049</v>
+        <v>3.70469355583191</v>
       </c>
       <c r="H454" t="n">
         <v>25000</v>
@@ -13564,7 +13564,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>3.69559097290039</v>
+        <v>3.69559073448181</v>
       </c>
       <c r="H455" t="n">
         <v>6000</v>
@@ -13593,7 +13593,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G456" t="n">
-        <v>3.68648886680603</v>
+        <v>3.68648862838745</v>
       </c>
       <c r="H456" t="n">
         <v>10000</v>
@@ -13622,7 +13622,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G457" t="n">
-        <v>3.65918135643005</v>
+        <v>3.65918111801147</v>
       </c>
       <c r="H457" t="n">
         <v>15000</v>
@@ -13651,7 +13651,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>3.68648886680603</v>
+        <v>3.68648862838745</v>
       </c>
       <c r="H458" t="n">
         <v>15000</v>
@@ -13680,7 +13680,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G459" t="n">
-        <v>3.67738628387451</v>
+        <v>3.67738604545593</v>
       </c>
       <c r="H459" t="n">
         <v>6000</v>
@@ -13709,7 +13709,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G460" t="n">
-        <v>3.66828393936157</v>
+        <v>3.66828370094299</v>
       </c>
       <c r="H460" t="n">
         <v>24000</v>
@@ -13738,7 +13738,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G461" t="n">
-        <v>3.65918135643005</v>
+        <v>3.65918111801147</v>
       </c>
       <c r="H461" t="n">
         <v>12000</v>
@@ -13767,7 +13767,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G462" t="n">
-        <v>3.50443959236145</v>
+        <v>3.50443983078003</v>
       </c>
       <c r="H462" t="n">
         <v>214000</v>
@@ -13796,7 +13796,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G463" t="n">
-        <v>3.51354193687439</v>
+        <v>3.51354217529297</v>
       </c>
       <c r="H463" t="n">
         <v>21000</v>
@@ -13825,7 +13825,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G464" t="n">
-        <v>3.50443959236145</v>
+        <v>3.50443983078003</v>
       </c>
       <c r="H464" t="n">
         <v>24000</v>
@@ -13854,7 +13854,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G465" t="n">
-        <v>3.45892739295959</v>
+        <v>3.45892763137817</v>
       </c>
       <c r="H465" t="n">
         <v>17000</v>
@@ -13883,7 +13883,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G466" t="n">
-        <v>3.42251753807068</v>
+        <v>3.42251777648926</v>
       </c>
       <c r="H466" t="n">
         <v>3000</v>
@@ -13999,7 +13999,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G470" t="n">
-        <v>3.4043128490448</v>
+        <v>3.40431308746338</v>
       </c>
       <c r="H470" t="n">
         <v>20000</v>
@@ -14028,7 +14028,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G471" t="n">
-        <v>3.42251753807068</v>
+        <v>3.42251777648926</v>
       </c>
       <c r="H471" t="n">
         <v>13000</v>
@@ -14086,7 +14086,7 @@
         <v>3.75</v>
       </c>
       <c r="G473" t="n">
-        <v>3.41341519355774</v>
+        <v>3.41341543197632</v>
       </c>
       <c r="H473" t="n">
         <v>7000</v>
@@ -14173,7 +14173,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G476" t="n">
-        <v>3.44072246551514</v>
+        <v>3.44072270393372</v>
       </c>
       <c r="H476" t="n">
         <v>8000</v>
@@ -14202,7 +14202,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>3.4316201210022</v>
+        <v>3.43162035942078</v>
       </c>
       <c r="H477" t="n">
         <v>2000</v>
@@ -14231,7 +14231,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>3.4316201210022</v>
+        <v>3.43162035942078</v>
       </c>
       <c r="H478" t="n">
         <v>2000</v>
@@ -14260,7 +14260,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G479" t="n">
-        <v>3.4043128490448</v>
+        <v>3.40431308746338</v>
       </c>
       <c r="H479" t="n">
         <v>3000</v>
@@ -14347,7 +14347,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G482" t="n">
-        <v>3.45892739295959</v>
+        <v>3.45892763137817</v>
       </c>
       <c r="H482" t="n">
         <v>10000</v>
@@ -14376,7 +14376,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G483" t="n">
-        <v>3.45892739295959</v>
+        <v>3.45892763137817</v>
       </c>
       <c r="H483" t="n">
         <v>2000</v>
@@ -14405,7 +14405,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G484" t="n">
-        <v>3.45892739295959</v>
+        <v>3.45892763137817</v>
       </c>
       <c r="H484" t="n">
         <v>0</v>
@@ -14434,7 +14434,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G485" t="n">
-        <v>3.48623466491699</v>
+        <v>3.48623490333557</v>
       </c>
       <c r="H485" t="n">
         <v>9000</v>
@@ -14463,7 +14463,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>3.45892739295959</v>
+        <v>3.45892763137817</v>
       </c>
       <c r="H486" t="n">
         <v>11000</v>
@@ -14492,7 +14492,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G487" t="n">
-        <v>3.45892739295959</v>
+        <v>3.45892763137817</v>
       </c>
       <c r="H487" t="n">
         <v>0</v>
@@ -14521,7 +14521,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G488" t="n">
-        <v>3.38610792160034</v>
+        <v>3.38610816001892</v>
       </c>
       <c r="H488" t="n">
         <v>25000</v>
@@ -14608,7 +14608,7 @@
         <v>3.75</v>
       </c>
       <c r="G491" t="n">
-        <v>3.41341519355774</v>
+        <v>3.41341543197632</v>
       </c>
       <c r="H491" t="n">
         <v>30000</v>
@@ -14637,7 +14637,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>3.39521026611328</v>
+        <v>3.39521050453186</v>
       </c>
       <c r="H492" t="n">
         <v>13000</v>
@@ -14695,7 +14695,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G494" t="n">
-        <v>3.45892739295959</v>
+        <v>3.45892763137817</v>
       </c>
       <c r="H494" t="n">
         <v>37000</v>
@@ -14724,7 +14724,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G495" t="n">
-        <v>3.56815671920776</v>
+        <v>3.56815695762634</v>
       </c>
       <c r="H495" t="n">
         <v>69000</v>
@@ -14753,7 +14753,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G496" t="n">
-        <v>3.52264428138733</v>
+        <v>3.52264451980591</v>
       </c>
       <c r="H496" t="n">
         <v>12000</v>
@@ -14782,7 +14782,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G497" t="n">
-        <v>3.50443959236145</v>
+        <v>3.50443983078003</v>
       </c>
       <c r="H497" t="n">
         <v>6000</v>
@@ -14811,7 +14811,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G498" t="n">
-        <v>3.52264428138733</v>
+        <v>3.52264451980591</v>
       </c>
       <c r="H498" t="n">
         <v>5000</v>
@@ -14840,7 +14840,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G499" t="n">
-        <v>3.4316201210022</v>
+        <v>3.43162035942078</v>
       </c>
       <c r="H499" t="n">
         <v>25000</v>
@@ -14869,7 +14869,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>3.4316201210022</v>
+        <v>3.43162035942078</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -14898,7 +14898,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G501" t="n">
-        <v>3.53174710273743</v>
+        <v>3.53174734115601</v>
       </c>
       <c r="H501" t="n">
         <v>6000</v>
@@ -14927,7 +14927,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G502" t="n">
-        <v>3.45892739295959</v>
+        <v>3.45892763137817</v>
       </c>
       <c r="H502" t="n">
         <v>4000</v>
@@ -14956,7 +14956,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G503" t="n">
-        <v>3.53174710273743</v>
+        <v>3.53174734115601</v>
       </c>
       <c r="H503" t="n">
         <v>4000</v>
@@ -14985,7 +14985,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G504" t="n">
-        <v>3.44072246551514</v>
+        <v>3.44072270393372</v>
       </c>
       <c r="H504" t="n">
         <v>5000</v>
@@ -15014,7 +15014,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G505" t="n">
-        <v>3.49533700942993</v>
+        <v>3.49533724784851</v>
       </c>
       <c r="H505" t="n">
         <v>5000</v>
@@ -15043,7 +15043,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>3.44982481002808</v>
+        <v>3.44982504844666</v>
       </c>
       <c r="H506" t="n">
         <v>32000</v>
@@ -15072,7 +15072,7 @@
         <v>3.75</v>
       </c>
       <c r="G507" t="n">
-        <v>3.41341519355774</v>
+        <v>3.41341543197632</v>
       </c>
       <c r="H507" t="n">
         <v>26000</v>
@@ -15188,7 +15188,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G511" t="n">
-        <v>3.42251753807068</v>
+        <v>3.42251777648926</v>
       </c>
       <c r="H511" t="n">
         <v>3000</v>
@@ -15217,7 +15217,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G512" t="n">
-        <v>3.38610792160034</v>
+        <v>3.38610816001892</v>
       </c>
       <c r="H512" t="n">
         <v>7000</v>
@@ -15246,7 +15246,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G513" t="n">
-        <v>3.45892739295959</v>
+        <v>3.45892763137817</v>
       </c>
       <c r="H513" t="n">
         <v>17000</v>
@@ -15478,7 +15478,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G521" t="n">
-        <v>3.28598117828369</v>
+        <v>3.28598093986511</v>
       </c>
       <c r="H521" t="n">
         <v>14000</v>
@@ -15739,7 +15739,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G530" t="n">
-        <v>3.28598117828369</v>
+        <v>3.28598093986511</v>
       </c>
       <c r="H530" t="n">
         <v>17000</v>
@@ -15768,7 +15768,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G531" t="n">
-        <v>3.28598117828369</v>
+        <v>3.28598093986511</v>
       </c>
       <c r="H531" t="n">
         <v>19000</v>
@@ -15855,7 +15855,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G534" t="n">
-        <v>3.28598117828369</v>
+        <v>3.28598093986511</v>
       </c>
       <c r="H534" t="n">
         <v>4000</v>
@@ -16957,7 +16957,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G572" t="n">
-        <v>2.54868364334106</v>
+        <v>2.54868340492249</v>
       </c>
       <c r="H572" t="n">
         <v>20000</v>
@@ -16986,7 +16986,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>2.53958106040955</v>
+        <v>2.53958082199097</v>
       </c>
       <c r="H573" t="n">
         <v>5000</v>
@@ -17044,7 +17044,7 @@
         <v>2.75</v>
       </c>
       <c r="G575" t="n">
-        <v>2.50317144393921</v>
+        <v>2.50317120552063</v>
       </c>
       <c r="H575" t="n">
         <v>5000</v>
@@ -17073,7 +17073,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>2.53958106040955</v>
+        <v>2.53958082199097</v>
       </c>
       <c r="H576" t="n">
         <v>1000</v>
@@ -17102,7 +17102,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>2.54868364334106</v>
+        <v>2.54868340492249</v>
       </c>
       <c r="H577" t="n">
         <v>1000</v>
@@ -17160,7 +17160,7 @@
         <v>2.75</v>
       </c>
       <c r="G579" t="n">
-        <v>2.50317144393921</v>
+        <v>2.50317120552063</v>
       </c>
       <c r="H579" t="n">
         <v>7000</v>
@@ -17305,7 +17305,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G584" t="n">
-        <v>2.53047871589661</v>
+        <v>2.53047847747803</v>
       </c>
       <c r="H584" t="n">
         <v>9000</v>
@@ -17334,7 +17334,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G585" t="n">
-        <v>2.51227378845215</v>
+        <v>2.51227355003357</v>
       </c>
       <c r="H585" t="n">
         <v>11000</v>
@@ -17363,7 +17363,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G586" t="n">
-        <v>2.54868364334106</v>
+        <v>2.54868340492249</v>
       </c>
       <c r="H586" t="n">
         <v>13000</v>
@@ -17392,7 +17392,7 @@
         <v>2.75</v>
       </c>
       <c r="G587" t="n">
-        <v>2.50317144393921</v>
+        <v>2.50317120552063</v>
       </c>
       <c r="H587" t="n">
         <v>7000</v>
@@ -17421,7 +17421,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>2.53958106040955</v>
+        <v>2.53958082199097</v>
       </c>
       <c r="H588" t="n">
         <v>18000</v>
@@ -17450,7 +17450,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G589" t="n">
-        <v>2.53958106040955</v>
+        <v>2.53958082199097</v>
       </c>
       <c r="H589" t="n">
         <v>8000</v>
@@ -17479,7 +17479,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G590" t="n">
-        <v>2.49406886100769</v>
+        <v>2.49406862258911</v>
       </c>
       <c r="H590" t="n">
         <v>10000</v>
@@ -17566,7 +17566,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G593" t="n">
-        <v>2.52137637138367</v>
+        <v>2.52137613296509</v>
       </c>
       <c r="H593" t="n">
         <v>27000</v>
@@ -17972,7 +17972,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G607" t="n">
-        <v>2.33022499084473</v>
+        <v>2.33022475242615</v>
       </c>
       <c r="H607" t="n">
         <v>3000</v>
@@ -18001,7 +18001,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G608" t="n">
-        <v>2.33022499084473</v>
+        <v>2.33022475242615</v>
       </c>
       <c r="H608" t="n">
         <v>2000</v>
@@ -18030,7 +18030,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G609" t="n">
-        <v>2.24830293655396</v>
+        <v>2.24830269813538</v>
       </c>
       <c r="H609" t="n">
         <v>6000</v>
@@ -18059,7 +18059,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G610" t="n">
-        <v>2.32112240791321</v>
+        <v>2.32112216949463</v>
       </c>
       <c r="H610" t="n">
         <v>21000</v>
@@ -18146,7 +18146,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G613" t="n">
-        <v>2.54868364334106</v>
+        <v>2.54868340492249</v>
       </c>
       <c r="H613" t="n">
         <v>9000</v>
@@ -18175,7 +18175,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G614" t="n">
-        <v>2.51227378845215</v>
+        <v>2.51227355003357</v>
       </c>
       <c r="H614" t="n">
         <v>2000</v>
@@ -18204,7 +18204,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G615" t="n">
-        <v>2.54868364334106</v>
+        <v>2.54868340492249</v>
       </c>
       <c r="H615" t="n">
         <v>6000</v>
@@ -18233,7 +18233,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G616" t="n">
-        <v>2.52137637138367</v>
+        <v>2.52137613296509</v>
       </c>
       <c r="H616" t="n">
         <v>1000</v>
@@ -18262,7 +18262,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G617" t="n">
-        <v>2.54868364334106</v>
+        <v>2.54868340492249</v>
       </c>
       <c r="H617" t="n">
         <v>5000</v>
@@ -18291,7 +18291,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G618" t="n">
-        <v>2.54868364334106</v>
+        <v>2.54868340492249</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18842,7 +18842,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G637" t="n">
-        <v>2.32112240791321</v>
+        <v>2.32112216949463</v>
       </c>
       <c r="H637" t="n">
         <v>35000</v>
@@ -18871,7 +18871,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G638" t="n">
-        <v>2.25740551948547</v>
+        <v>2.25740528106689</v>
       </c>
       <c r="H638" t="n">
         <v>20000</v>
@@ -18900,7 +18900,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G639" t="n">
-        <v>2.18458604812622</v>
+        <v>2.18458580970764</v>
       </c>
       <c r="H639" t="n">
         <v>27000</v>
@@ -18929,7 +18929,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G640" t="n">
-        <v>2.18458604812622</v>
+        <v>2.18458580970764</v>
       </c>
       <c r="H640" t="n">
         <v>5000</v>
@@ -18958,7 +18958,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G641" t="n">
-        <v>2.11176609992981</v>
+        <v>2.11176633834839</v>
       </c>
       <c r="H641" t="n">
         <v>31000</v>
@@ -18987,7 +18987,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G642" t="n">
-        <v>2.11176609992981</v>
+        <v>2.11176633834839</v>
       </c>
       <c r="H642" t="n">
         <v>40000</v>
@@ -19016,7 +19016,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>2.08445882797241</v>
+        <v>2.08445906639099</v>
       </c>
       <c r="H643" t="n">
         <v>51000</v>
@@ -19045,7 +19045,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G644" t="n">
-        <v>2.05715155601501</v>
+        <v>2.05715179443359</v>
       </c>
       <c r="H644" t="n">
         <v>11000</v>
@@ -19074,7 +19074,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G645" t="n">
-        <v>2.01163935661316</v>
+        <v>2.01163959503174</v>
       </c>
       <c r="H645" t="n">
         <v>18000</v>
@@ -19103,7 +19103,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>2.08445882797241</v>
+        <v>2.08445906639099</v>
       </c>
       <c r="H646" t="n">
         <v>20000</v>
@@ -19132,7 +19132,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>2.18458604812622</v>
+        <v>2.18458580970764</v>
       </c>
       <c r="H647" t="n">
         <v>33000</v>
@@ -19190,7 +19190,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G649" t="n">
-        <v>2.07535624504089</v>
+        <v>2.07535648345947</v>
       </c>
       <c r="H649" t="n">
         <v>31000</v>
@@ -19219,7 +19219,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G650" t="n">
-        <v>2.09356117248535</v>
+        <v>2.09356141090393</v>
       </c>
       <c r="H650" t="n">
         <v>14000</v>
@@ -19248,7 +19248,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>2.08445882797241</v>
+        <v>2.08445906639099</v>
       </c>
       <c r="H651" t="n">
         <v>14000</v>
@@ -19277,7 +19277,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G652" t="n">
-        <v>2.11176609992981</v>
+        <v>2.11176633834839</v>
       </c>
       <c r="H652" t="n">
         <v>13000</v>
@@ -19306,7 +19306,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G653" t="n">
-        <v>2.19368839263916</v>
+        <v>2.19368815422058</v>
       </c>
       <c r="H653" t="n">
         <v>52000</v>
@@ -19422,7 +19422,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G657" t="n">
-        <v>2.54868364334106</v>
+        <v>2.54868340492249</v>
       </c>
       <c r="H657" t="n">
         <v>114000</v>
@@ -19451,7 +19451,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G658" t="n">
-        <v>2.51227378845215</v>
+        <v>2.51227355003357</v>
       </c>
       <c r="H658" t="n">
         <v>43000</v>
@@ -19509,7 +19509,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>2.20279097557068</v>
+        <v>2.2027907371521</v>
       </c>
       <c r="H660" t="n">
         <v>51000</v>
@@ -19538,7 +19538,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G661" t="n">
-        <v>2.11176609992981</v>
+        <v>2.11176633834839</v>
       </c>
       <c r="H661" t="n">
         <v>21000</v>
@@ -19567,7 +19567,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>2.15727853775024</v>
+        <v>2.15727829933167</v>
       </c>
       <c r="H662" t="n">
         <v>37000</v>
@@ -19596,7 +19596,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G663" t="n">
-        <v>2.29381513595581</v>
+        <v>2.29381489753723</v>
       </c>
       <c r="H663" t="n">
         <v>24000</v>
@@ -19625,7 +19625,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G664" t="n">
-        <v>2.25740551948547</v>
+        <v>2.25740528106689</v>
       </c>
       <c r="H664" t="n">
         <v>29000</v>
@@ -19683,7 +19683,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G666" t="n">
-        <v>2.15727853775024</v>
+        <v>2.15727829933167</v>
       </c>
       <c r="H666" t="n">
         <v>3000</v>
@@ -19712,7 +19712,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G667" t="n">
-        <v>2.21189332008362</v>
+        <v>2.21189308166504</v>
       </c>
       <c r="H667" t="n">
         <v>9000</v>
@@ -19741,7 +19741,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G668" t="n">
-        <v>2.21189332008362</v>
+        <v>2.21189308166504</v>
       </c>
       <c r="H668" t="n">
         <v>0</v>
@@ -19799,7 +19799,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>2.18458604812622</v>
+        <v>2.18458580970764</v>
       </c>
       <c r="H670" t="n">
         <v>3000</v>
@@ -19828,7 +19828,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>2.18458604812622</v>
+        <v>2.18458580970764</v>
       </c>
       <c r="H671" t="n">
         <v>5000</v>
@@ -19886,7 +19886,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G673" t="n">
-        <v>2.11176609992981</v>
+        <v>2.11176633834839</v>
       </c>
       <c r="H673" t="n">
         <v>4000</v>
@@ -19944,7 +19944,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>2.08445882797241</v>
+        <v>2.08445906639099</v>
       </c>
       <c r="H675" t="n">
         <v>4000</v>
@@ -20002,7 +20002,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>2.08445882797241</v>
+        <v>2.08445906639099</v>
       </c>
       <c r="H677" t="n">
         <v>1000</v>
@@ -20031,7 +20031,7 @@
         <v>2.25</v>
       </c>
       <c r="G678" t="n">
-        <v>2.0480489730835</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H678" t="n">
         <v>3000</v>
@@ -20060,7 +20060,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G679" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H679" t="n">
         <v>1000</v>
@@ -20089,7 +20089,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G680" t="n">
-        <v>2.07535624504089</v>
+        <v>2.07535648345947</v>
       </c>
       <c r="H680" t="n">
         <v>2000</v>
@@ -20118,7 +20118,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G681" t="n">
-        <v>2.10266375541687</v>
+        <v>2.10266399383545</v>
       </c>
       <c r="H681" t="n">
         <v>1000</v>
@@ -20147,7 +20147,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G682" t="n">
-        <v>2.05715155601501</v>
+        <v>2.05715179443359</v>
       </c>
       <c r="H682" t="n">
         <v>5000</v>
@@ -20176,7 +20176,7 @@
         <v>2.25</v>
       </c>
       <c r="G683" t="n">
-        <v>2.0480489730835</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H683" t="n">
         <v>2000</v>
@@ -20234,7 +20234,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G685" t="n">
-        <v>2.05715155601501</v>
+        <v>2.05715179443359</v>
       </c>
       <c r="H685" t="n">
         <v>4000</v>
@@ -20263,7 +20263,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G686" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H686" t="n">
         <v>3000</v>
@@ -20292,7 +20292,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G687" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H687" t="n">
         <v>0</v>
@@ -20321,7 +20321,7 @@
         <v>2.25</v>
       </c>
       <c r="G688" t="n">
-        <v>2.0480489730835</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H688" t="n">
         <v>4000</v>
@@ -20350,7 +20350,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G689" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H689" t="n">
         <v>2000</v>
@@ -20379,7 +20379,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G690" t="n">
-        <v>2.00253677368164</v>
+        <v>2.00253701210022</v>
       </c>
       <c r="H690" t="n">
         <v>2000</v>
@@ -20408,7 +20408,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G691" t="n">
-        <v>1.9661271572113</v>
+        <v>1.96612739562988</v>
       </c>
       <c r="H691" t="n">
         <v>5000</v>
@@ -20437,7 +20437,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G692" t="n">
-        <v>1.9934344291687</v>
+        <v>1.99343466758728</v>
       </c>
       <c r="H692" t="n">
         <v>6000</v>
@@ -20466,7 +20466,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G693" t="n">
-        <v>1.9934344291687</v>
+        <v>1.99343466758728</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -20495,7 +20495,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G694" t="n">
-        <v>1.9934344291687</v>
+        <v>1.99343466758728</v>
       </c>
       <c r="H694" t="n">
         <v>0</v>
@@ -20524,7 +20524,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G695" t="n">
-        <v>1.98433196544647</v>
+        <v>1.98433220386505</v>
       </c>
       <c r="H695" t="n">
         <v>1000</v>
@@ -20553,7 +20553,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G696" t="n">
-        <v>2.00253677368164</v>
+        <v>2.00253701210022</v>
       </c>
       <c r="H696" t="n">
         <v>2000</v>
@@ -20582,7 +20582,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G697" t="n">
-        <v>1.94792234897614</v>
+        <v>1.94792246818542</v>
       </c>
       <c r="H697" t="n">
         <v>1000</v>
@@ -20611,7 +20611,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G698" t="n">
-        <v>1.94792234897614</v>
+        <v>1.94792246818542</v>
       </c>
       <c r="H698" t="n">
         <v>2000</v>
@@ -20640,7 +20640,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G699" t="n">
-        <v>1.94792234897614</v>
+        <v>1.94792246818542</v>
       </c>
       <c r="H699" t="n">
         <v>1000</v>
@@ -20669,7 +20669,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G700" t="n">
-        <v>1.94792234897614</v>
+        <v>1.94792246818542</v>
       </c>
       <c r="H700" t="n">
         <v>0</v>
@@ -20698,7 +20698,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G701" t="n">
-        <v>1.94792234897614</v>
+        <v>1.94792246818542</v>
       </c>
       <c r="H701" t="n">
         <v>0</v>
@@ -20727,7 +20727,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G702" t="n">
-        <v>1.92971730232239</v>
+        <v>1.92971742153168</v>
       </c>
       <c r="H702" t="n">
         <v>4000</v>
@@ -20814,7 +20814,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G705" t="n">
-        <v>1.80683445930481</v>
+        <v>1.8068345785141</v>
       </c>
       <c r="H705" t="n">
         <v>13000</v>
@@ -20901,7 +20901,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>1.72491240501404</v>
+        <v>1.72491252422333</v>
       </c>
       <c r="H708" t="n">
         <v>4000</v>
@@ -20930,7 +20930,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G709" t="n">
-        <v>1.69760513305664</v>
+        <v>1.69760525226593</v>
       </c>
       <c r="H709" t="n">
         <v>7000</v>
@@ -20959,7 +20959,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G710" t="n">
-        <v>1.73856604099274</v>
+        <v>1.73856616020203</v>
       </c>
       <c r="H710" t="n">
         <v>5000</v>
@@ -20988,7 +20988,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G711" t="n">
-        <v>1.77497589588165</v>
+        <v>1.77497601509094</v>
       </c>
       <c r="H711" t="n">
         <v>8000</v>
@@ -21017,7 +21017,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G712" t="n">
-        <v>1.7294636964798</v>
+        <v>1.72946381568909</v>
       </c>
       <c r="H712" t="n">
         <v>1000</v>
@@ -21046,7 +21046,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G713" t="n">
-        <v>1.7294636964798</v>
+        <v>1.72946381568909</v>
       </c>
       <c r="H713" t="n">
         <v>0</v>
@@ -21075,7 +21075,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G714" t="n">
-        <v>1.7294636964798</v>
+        <v>1.72946381568909</v>
       </c>
       <c r="H714" t="n">
         <v>1000</v>
@@ -21133,7 +21133,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G716" t="n">
-        <v>1.73856604099274</v>
+        <v>1.73856616020203</v>
       </c>
       <c r="H716" t="n">
         <v>14000</v>
@@ -21162,7 +21162,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G717" t="n">
-        <v>1.76132214069366</v>
+        <v>1.76132225990295</v>
       </c>
       <c r="H717" t="n">
         <v>1000</v>
@@ -21191,7 +21191,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G718" t="n">
-        <v>1.73856604099274</v>
+        <v>1.73856616020203</v>
       </c>
       <c r="H718" t="n">
         <v>2000</v>
@@ -21220,7 +21220,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G719" t="n">
-        <v>1.7294636964798</v>
+        <v>1.72946381568909</v>
       </c>
       <c r="H719" t="n">
         <v>10000</v>
@@ -21249,7 +21249,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G720" t="n">
-        <v>1.71125876903534</v>
+        <v>1.71125888824463</v>
       </c>
       <c r="H720" t="n">
         <v>1000</v>
@@ -21278,7 +21278,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G721" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H721" t="n">
         <v>2000</v>
@@ -21307,7 +21307,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G722" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H722" t="n">
         <v>0</v>
@@ -21336,7 +21336,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G723" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H723" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G724" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H724" t="n">
         <v>0</v>
@@ -21394,7 +21394,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G725" t="n">
-        <v>1.7294636964798</v>
+        <v>1.72946381568909</v>
       </c>
       <c r="H725" t="n">
         <v>3000</v>
@@ -21423,7 +21423,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G726" t="n">
-        <v>1.71125876903534</v>
+        <v>1.71125888824463</v>
       </c>
       <c r="H726" t="n">
         <v>12000</v>
@@ -21452,7 +21452,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G727" t="n">
-        <v>1.7294636964798</v>
+        <v>1.72946381568909</v>
       </c>
       <c r="H727" t="n">
         <v>3000</v>
@@ -21481,7 +21481,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G728" t="n">
-        <v>1.72036123275757</v>
+        <v>1.72036135196686</v>
       </c>
       <c r="H728" t="n">
         <v>5000</v>
@@ -21510,7 +21510,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G729" t="n">
-        <v>1.69305396080017</v>
+        <v>1.69305408000946</v>
       </c>
       <c r="H729" t="n">
         <v>1000</v>
@@ -21800,7 +21800,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G739" t="n">
-        <v>1.76587355136871</v>
+        <v>1.765873670578</v>
       </c>
       <c r="H739" t="n">
         <v>23000</v>
@@ -21858,7 +21858,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G741" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H741" t="n">
         <v>81000</v>
@@ -21887,7 +21887,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G742" t="n">
-        <v>2.02984428405762</v>
+        <v>2.0298445224762</v>
       </c>
       <c r="H742" t="n">
         <v>23000</v>
@@ -21916,7 +21916,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G743" t="n">
-        <v>1.92061483860016</v>
+        <v>1.92061495780945</v>
       </c>
       <c r="H743" t="n">
         <v>18000</v>
@@ -21945,7 +21945,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G744" t="n">
-        <v>1.9661271572113</v>
+        <v>1.96612739562988</v>
       </c>
       <c r="H744" t="n">
         <v>12000</v>
@@ -21974,7 +21974,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G745" t="n">
-        <v>1.98433196544647</v>
+        <v>1.98433220386505</v>
       </c>
       <c r="H745" t="n">
         <v>45000</v>
@@ -22003,7 +22003,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G746" t="n">
-        <v>1.92971730232239</v>
+        <v>1.92971742153168</v>
       </c>
       <c r="H746" t="n">
         <v>10000</v>
@@ -22032,7 +22032,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G747" t="n">
-        <v>1.9934344291687</v>
+        <v>1.99343466758728</v>
       </c>
       <c r="H747" t="n">
         <v>12000</v>
@@ -22061,7 +22061,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G748" t="n">
-        <v>1.97522962093353</v>
+        <v>1.97522985935211</v>
       </c>
       <c r="H748" t="n">
         <v>9000</v>
@@ -22090,7 +22090,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G749" t="n">
-        <v>1.92061483860016</v>
+        <v>1.92061495780945</v>
       </c>
       <c r="H749" t="n">
         <v>13000</v>
@@ -22148,7 +22148,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G751" t="n">
-        <v>1.92061483860016</v>
+        <v>1.92061495780945</v>
       </c>
       <c r="H751" t="n">
         <v>11000</v>
@@ -22293,7 +22293,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G756" t="n">
-        <v>1.92971730232239</v>
+        <v>1.92971742153168</v>
       </c>
       <c r="H756" t="n">
         <v>1000</v>
@@ -22351,7 +22351,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G758" t="n">
-        <v>1.92971730232239</v>
+        <v>1.92971742153168</v>
       </c>
       <c r="H758" t="n">
         <v>2000</v>
@@ -22380,7 +22380,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G759" t="n">
-        <v>1.94792234897614</v>
+        <v>1.94792246818542</v>
       </c>
       <c r="H759" t="n">
         <v>2000</v>
@@ -22409,7 +22409,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G760" t="n">
-        <v>1.9388200044632</v>
+        <v>1.93882012367249</v>
       </c>
       <c r="H760" t="n">
         <v>1000</v>
@@ -22438,7 +22438,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G761" t="n">
-        <v>2.02984428405762</v>
+        <v>2.0298445224762</v>
       </c>
       <c r="H761" t="n">
         <v>16000</v>
@@ -22467,7 +22467,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G762" t="n">
-        <v>2.24830293655396</v>
+        <v>2.24830269813538</v>
       </c>
       <c r="H762" t="n">
         <v>21000</v>
@@ -22583,7 +22583,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G766" t="n">
-        <v>2.09356117248535</v>
+        <v>2.09356141090393</v>
       </c>
       <c r="H766" t="n">
         <v>3000</v>
@@ -22612,7 +22612,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>2.09356117248535</v>
+        <v>2.09356141090393</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -22641,7 +22641,7 @@
         <v>2.25</v>
       </c>
       <c r="G768" t="n">
-        <v>2.0480489730835</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H768" t="n">
         <v>1000</v>
@@ -22670,7 +22670,7 @@
         <v>2.25</v>
       </c>
       <c r="G769" t="n">
-        <v>2.0480489730835</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H769" t="n">
         <v>0</v>
@@ -22699,7 +22699,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G770" t="n">
-        <v>2.00253677368164</v>
+        <v>2.00253701210022</v>
       </c>
       <c r="H770" t="n">
         <v>1000</v>
@@ -22728,7 +22728,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G771" t="n">
-        <v>2.00253677368164</v>
+        <v>2.00253701210022</v>
       </c>
       <c r="H771" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G772" t="n">
-        <v>2.05715155601501</v>
+        <v>2.05715179443359</v>
       </c>
       <c r="H772" t="n">
         <v>7000</v>
@@ -22786,7 +22786,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G773" t="n">
-        <v>2.05715155601501</v>
+        <v>2.05715179443359</v>
       </c>
       <c r="H773" t="n">
         <v>2000</v>
@@ -22815,7 +22815,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G774" t="n">
-        <v>2.05715155601501</v>
+        <v>2.05715179443359</v>
       </c>
       <c r="H774" t="n">
         <v>0</v>
@@ -22873,7 +22873,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>2.09356117248535</v>
+        <v>2.09356141090393</v>
       </c>
       <c r="H776" t="n">
         <v>3000</v>
@@ -22902,7 +22902,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G777" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H777" t="n">
         <v>7000</v>
@@ -22931,7 +22931,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G778" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H778" t="n">
         <v>0</v>
@@ -22960,7 +22960,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G779" t="n">
-        <v>2.06625390052795</v>
+        <v>2.06625413894653</v>
       </c>
       <c r="H779" t="n">
         <v>2000</v>
@@ -22989,7 +22989,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G780" t="n">
-        <v>2.06625390052795</v>
+        <v>2.06625413894653</v>
       </c>
       <c r="H780" t="n">
         <v>0</v>
@@ -23018,7 +23018,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G781" t="n">
-        <v>2.06625390052795</v>
+        <v>2.06625413894653</v>
       </c>
       <c r="H781" t="n">
         <v>0</v>
@@ -23047,7 +23047,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G782" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H782" t="n">
         <v>6000</v>
@@ -23076,7 +23076,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G783" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H783" t="n">
         <v>5000</v>
@@ -23105,7 +23105,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G784" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H784" t="n">
         <v>0</v>
@@ -23134,7 +23134,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G785" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H785" t="n">
         <v>0</v>
@@ -23163,7 +23163,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G786" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H786" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G787" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H787" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G788" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H788" t="n">
         <v>0</v>
@@ -23250,7 +23250,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G789" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H789" t="n">
         <v>0</v>
@@ -23279,7 +23279,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G790" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H790" t="n">
         <v>0</v>
@@ -23308,7 +23308,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G791" t="n">
-        <v>1.9934344291687</v>
+        <v>1.99343466758728</v>
       </c>
       <c r="H791" t="n">
         <v>2000</v>
@@ -23337,7 +23337,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>2.01163935661316</v>
+        <v>2.01163959503174</v>
       </c>
       <c r="H792" t="n">
         <v>3000</v>
@@ -23366,7 +23366,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>2.01163935661316</v>
+        <v>2.01163959503174</v>
       </c>
       <c r="H793" t="n">
         <v>0</v>
@@ -23395,7 +23395,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G794" t="n">
-        <v>2.02984428405762</v>
+        <v>2.0298445224762</v>
       </c>
       <c r="H794" t="n">
         <v>3000</v>
@@ -23424,7 +23424,7 @@
         <v>2.25</v>
       </c>
       <c r="G795" t="n">
-        <v>2.0480489730835</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H795" t="n">
         <v>1000</v>
@@ -23453,7 +23453,7 @@
         <v>2.25</v>
       </c>
       <c r="G796" t="n">
-        <v>2.0480489730835</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H796" t="n">
         <v>0</v>
@@ -23482,7 +23482,7 @@
         <v>2.25</v>
       </c>
       <c r="G797" t="n">
-        <v>2.0480489730835</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H797" t="n">
         <v>0</v>
@@ -23511,7 +23511,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G798" t="n">
-        <v>2.02984428405762</v>
+        <v>2.0298445224762</v>
       </c>
       <c r="H798" t="n">
         <v>5000</v>
@@ -23540,7 +23540,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G799" t="n">
-        <v>1.9934344291687</v>
+        <v>1.99343466758728</v>
       </c>
       <c r="H799" t="n">
         <v>2000</v>
@@ -23569,7 +23569,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G800" t="n">
-        <v>1.95702469348907</v>
+        <v>1.95702493190765</v>
       </c>
       <c r="H800" t="n">
         <v>5000</v>
@@ -23801,7 +23801,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G808" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H808" t="n">
         <v>9000</v>
@@ -23830,7 +23830,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G809" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H809" t="n">
         <v>0</v>
@@ -23859,7 +23859,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G810" t="n">
-        <v>1.8477954864502</v>
+        <v>1.84779536724091</v>
       </c>
       <c r="H810" t="n">
         <v>4000</v>
@@ -23946,7 +23946,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G813" t="n">
-        <v>1.8477954864502</v>
+        <v>1.84779536724091</v>
       </c>
       <c r="H813" t="n">
         <v>4000</v>
@@ -24004,7 +24004,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G815" t="n">
-        <v>1.82959067821503</v>
+        <v>1.82959055900574</v>
       </c>
       <c r="H815" t="n">
         <v>2000</v>
@@ -24033,7 +24033,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G816" t="n">
-        <v>1.82959067821503</v>
+        <v>1.82959055900574</v>
       </c>
       <c r="H816" t="n">
         <v>0</v>
@@ -24120,7 +24120,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G819" t="n">
-        <v>1.82959067821503</v>
+        <v>1.82959055900574</v>
       </c>
       <c r="H819" t="n">
         <v>6000</v>
@@ -24149,7 +24149,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G820" t="n">
-        <v>1.77952718734741</v>
+        <v>1.7795273065567</v>
       </c>
       <c r="H820" t="n">
         <v>8000</v>
@@ -24178,7 +24178,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G821" t="n">
-        <v>1.76587355136871</v>
+        <v>1.765873670578</v>
       </c>
       <c r="H821" t="n">
         <v>2000</v>
@@ -24207,7 +24207,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G822" t="n">
-        <v>1.76587355136871</v>
+        <v>1.765873670578</v>
       </c>
       <c r="H822" t="n">
         <v>7000</v>
@@ -24236,7 +24236,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G823" t="n">
-        <v>1.76587355136871</v>
+        <v>1.765873670578</v>
       </c>
       <c r="H823" t="n">
         <v>0</v>
@@ -24265,7 +24265,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>1.78407835960388</v>
+        <v>1.78407847881317</v>
       </c>
       <c r="H824" t="n">
         <v>1000</v>
@@ -24294,7 +24294,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>1.78407835960388</v>
+        <v>1.78407847881317</v>
       </c>
       <c r="H825" t="n">
         <v>0</v>
@@ -24323,7 +24323,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G826" t="n">
-        <v>1.78407835960388</v>
+        <v>1.78407847881317</v>
       </c>
       <c r="H826" t="n">
         <v>0</v>
@@ -24352,7 +24352,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>1.78407835960388</v>
+        <v>1.78407847881317</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -24381,7 +24381,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>1.78407835960388</v>
+        <v>1.78407847881317</v>
       </c>
       <c r="H828" t="n">
         <v>0</v>
@@ -24410,7 +24410,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G829" t="n">
-        <v>1.75677096843719</v>
+        <v>1.75677108764648</v>
       </c>
       <c r="H829" t="n">
         <v>1000</v>
@@ -24439,7 +24439,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G830" t="n">
-        <v>1.79318082332611</v>
+        <v>1.7931809425354</v>
       </c>
       <c r="H830" t="n">
         <v>2000</v>
@@ -24468,7 +24468,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G831" t="n">
-        <v>1.77042472362518</v>
+        <v>1.77042484283447</v>
       </c>
       <c r="H831" t="n">
         <v>1000</v>
@@ -24497,7 +24497,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G832" t="n">
-        <v>1.71125876903534</v>
+        <v>1.71125888824463</v>
       </c>
       <c r="H832" t="n">
         <v>8000</v>
@@ -24526,7 +24526,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.72491240501404</v>
+        <v>1.72491252422333</v>
       </c>
       <c r="H833" t="n">
         <v>5000</v>
@@ -24555,7 +24555,7 @@
         <v>1.875</v>
       </c>
       <c r="G834" t="n">
-        <v>1.70670759677887</v>
+        <v>1.70670771598816</v>
       </c>
       <c r="H834" t="n">
         <v>5000</v>
@@ -24671,7 +24671,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G838" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H838" t="n">
         <v>15000</v>
@@ -24700,7 +24700,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G839" t="n">
-        <v>1.7294636964798</v>
+        <v>1.72946381568909</v>
       </c>
       <c r="H839" t="n">
         <v>1000</v>
@@ -24729,7 +24729,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G840" t="n">
-        <v>1.7294636964798</v>
+        <v>1.72946381568909</v>
       </c>
       <c r="H840" t="n">
         <v>0</v>
@@ -24758,7 +24758,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G841" t="n">
-        <v>1.71125876903534</v>
+        <v>1.71125888824463</v>
       </c>
       <c r="H841" t="n">
         <v>2000</v>
@@ -24787,7 +24787,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G842" t="n">
-        <v>1.71125876903534</v>
+        <v>1.71125888824463</v>
       </c>
       <c r="H842" t="n">
         <v>1000</v>
@@ -24816,7 +24816,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G843" t="n">
-        <v>1.71125876903534</v>
+        <v>1.71125888824463</v>
       </c>
       <c r="H843" t="n">
         <v>0</v>
@@ -24845,7 +24845,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G844" t="n">
-        <v>1.71125876903534</v>
+        <v>1.71125888824463</v>
       </c>
       <c r="H844" t="n">
         <v>0</v>
@@ -24874,7 +24874,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G845" t="n">
-        <v>1.71125876903534</v>
+        <v>1.71125888824463</v>
       </c>
       <c r="H845" t="n">
         <v>0</v>
@@ -24903,7 +24903,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G846" t="n">
-        <v>1.80228328704834</v>
+        <v>1.80228340625763</v>
       </c>
       <c r="H846" t="n">
         <v>7000</v>
@@ -24990,7 +24990,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G849" t="n">
-        <v>1.78407835960388</v>
+        <v>1.78407847881317</v>
       </c>
       <c r="H849" t="n">
         <v>9000</v>
@@ -25019,7 +25019,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G850" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H850" t="n">
         <v>8000</v>
@@ -25135,7 +25135,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G854" t="n">
-        <v>1.80683445930481</v>
+        <v>1.8068345785141</v>
       </c>
       <c r="H854" t="n">
         <v>1000</v>
@@ -25164,7 +25164,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G855" t="n">
-        <v>1.77042472362518</v>
+        <v>1.77042484283447</v>
       </c>
       <c r="H855" t="n">
         <v>1000</v>
@@ -25193,7 +25193,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G856" t="n">
-        <v>1.76132214069366</v>
+        <v>1.76132225990295</v>
       </c>
       <c r="H856" t="n">
         <v>1000</v>
@@ -25222,7 +25222,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G857" t="n">
-        <v>1.76132214069366</v>
+        <v>1.76132225990295</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -25251,7 +25251,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G858" t="n">
-        <v>1.76587355136871</v>
+        <v>1.765873670578</v>
       </c>
       <c r="H858" t="n">
         <v>3000</v>
@@ -25280,7 +25280,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G859" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H859" t="n">
         <v>7000</v>
@@ -25309,7 +25309,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G860" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H860" t="n">
         <v>0</v>
@@ -25338,7 +25338,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G861" t="n">
-        <v>1.7431173324585</v>
+        <v>1.74311745166779</v>
       </c>
       <c r="H861" t="n">
         <v>1000</v>
@@ -25367,7 +25367,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G862" t="n">
-        <v>1.7431173324585</v>
+        <v>1.74311745166779</v>
       </c>
       <c r="H862" t="n">
         <v>0</v>
@@ -25396,7 +25396,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G863" t="n">
-        <v>1.73401486873627</v>
+        <v>1.73401498794556</v>
       </c>
       <c r="H863" t="n">
         <v>2000</v>
@@ -25425,7 +25425,7 @@
         <v>1.875</v>
       </c>
       <c r="G864" t="n">
-        <v>1.70670759677887</v>
+        <v>1.70670771598816</v>
       </c>
       <c r="H864" t="n">
         <v>7000</v>
@@ -25454,7 +25454,7 @@
         <v>1.875</v>
       </c>
       <c r="G865" t="n">
-        <v>1.70670759677887</v>
+        <v>1.70670771598816</v>
       </c>
       <c r="H865" t="n">
         <v>0</v>
@@ -25744,7 +25744,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>1.72491240501404</v>
+        <v>1.72491252422333</v>
       </c>
       <c r="H875" t="n">
         <v>3000</v>
@@ -25773,7 +25773,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G876" t="n">
-        <v>1.7294636964798</v>
+        <v>1.72946381568909</v>
       </c>
       <c r="H876" t="n">
         <v>2000</v>
@@ -25831,7 +25831,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G878" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H878" t="n">
         <v>9000</v>
@@ -25860,7 +25860,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G879" t="n">
-        <v>1.79773199558258</v>
+        <v>1.79773211479187</v>
       </c>
       <c r="H879" t="n">
         <v>6000</v>
@@ -25889,7 +25889,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G880" t="n">
-        <v>1.79773199558258</v>
+        <v>1.79773211479187</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -25918,7 +25918,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G881" t="n">
-        <v>1.79773199558258</v>
+        <v>1.79773211479187</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -25947,7 +25947,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G882" t="n">
-        <v>1.78407835960388</v>
+        <v>1.78407847881317</v>
       </c>
       <c r="H882" t="n">
         <v>12000</v>
@@ -26121,7 +26121,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G888" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H888" t="n">
         <v>20000</v>
@@ -26179,7 +26179,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G890" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H890" t="n">
         <v>9000</v>
@@ -26266,7 +26266,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G893" t="n">
-        <v>1.79318082332611</v>
+        <v>1.7931809425354</v>
       </c>
       <c r="H893" t="n">
         <v>12000</v>
@@ -26295,7 +26295,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G894" t="n">
-        <v>1.79318082332611</v>
+        <v>1.7931809425354</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -26353,7 +26353,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G896" t="n">
-        <v>1.82959067821503</v>
+        <v>1.82959055900574</v>
       </c>
       <c r="H896" t="n">
         <v>47000</v>
@@ -26469,7 +26469,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G900" t="n">
-        <v>1.80228328704834</v>
+        <v>1.80228340625763</v>
       </c>
       <c r="H900" t="n">
         <v>1000</v>
@@ -26527,7 +26527,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G902" t="n">
-        <v>1.82959067821503</v>
+        <v>1.82959055900574</v>
       </c>
       <c r="H902" t="n">
         <v>1000</v>
@@ -26556,7 +26556,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G903" t="n">
-        <v>1.8477954864502</v>
+        <v>1.84779536724091</v>
       </c>
       <c r="H903" t="n">
         <v>2000</v>
@@ -26585,7 +26585,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G904" t="n">
-        <v>1.8477954864502</v>
+        <v>1.84779536724091</v>
       </c>
       <c r="H904" t="n">
         <v>0</v>
@@ -26614,7 +26614,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G905" t="n">
-        <v>1.82959067821503</v>
+        <v>1.82959055900574</v>
       </c>
       <c r="H905" t="n">
         <v>3000</v>
@@ -26643,7 +26643,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G906" t="n">
-        <v>1.82959067821503</v>
+        <v>1.82959055900574</v>
       </c>
       <c r="H906" t="n">
         <v>13000</v>
@@ -26672,7 +26672,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>1.80228328704834</v>
+        <v>1.80228340625763</v>
       </c>
       <c r="H907" t="n">
         <v>2000</v>
@@ -26730,7 +26730,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G909" t="n">
-        <v>1.80228328704834</v>
+        <v>1.80228340625763</v>
       </c>
       <c r="H909" t="n">
         <v>7000</v>
@@ -26759,7 +26759,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G910" t="n">
-        <v>1.78862965106964</v>
+        <v>1.78862977027893</v>
       </c>
       <c r="H910" t="n">
         <v>5000</v>
@@ -26788,7 +26788,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G911" t="n">
-        <v>1.78407835960388</v>
+        <v>1.78407847881317</v>
       </c>
       <c r="H911" t="n">
         <v>2000</v>
@@ -26817,7 +26817,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G912" t="n">
-        <v>1.78407835960388</v>
+        <v>1.78407847881317</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -26846,7 +26846,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G913" t="n">
-        <v>1.78407835960388</v>
+        <v>1.78407847881317</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -26875,7 +26875,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G914" t="n">
-        <v>1.80683445930481</v>
+        <v>1.8068345785141</v>
       </c>
       <c r="H914" t="n">
         <v>3000</v>
@@ -26904,7 +26904,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G915" t="n">
-        <v>1.80683445930481</v>
+        <v>1.8068345785141</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -26933,7 +26933,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G916" t="n">
-        <v>1.80683445930481</v>
+        <v>1.8068345785141</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -26962,7 +26962,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G917" t="n">
-        <v>1.80683445930481</v>
+        <v>1.8068345785141</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -26991,7 +26991,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>1.76132214069366</v>
+        <v>1.76132225990295</v>
       </c>
       <c r="H918" t="n">
         <v>7000</v>
@@ -27020,7 +27020,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G919" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H919" t="n">
         <v>1000</v>
@@ -27049,7 +27049,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G920" t="n">
-        <v>1.75677096843719</v>
+        <v>1.75677108764648</v>
       </c>
       <c r="H920" t="n">
         <v>2000</v>
@@ -27078,7 +27078,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G921" t="n">
-        <v>1.7294636964798</v>
+        <v>1.72946381568909</v>
       </c>
       <c r="H921" t="n">
         <v>7000</v>
@@ -27107,7 +27107,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G922" t="n">
-        <v>1.7294636964798</v>
+        <v>1.72946381568909</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -27136,7 +27136,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G923" t="n">
-        <v>1.76132214069366</v>
+        <v>1.76132225990295</v>
       </c>
       <c r="H923" t="n">
         <v>5000</v>
@@ -27165,7 +27165,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G924" t="n">
-        <v>1.77952718734741</v>
+        <v>1.7795273065567</v>
       </c>
       <c r="H924" t="n">
         <v>3000</v>
@@ -27281,7 +27281,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G928" t="n">
-        <v>1.8477954864502</v>
+        <v>1.84779536724091</v>
       </c>
       <c r="H928" t="n">
         <v>29000</v>
@@ -27368,7 +27368,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G931" t="n">
-        <v>1.8477954864502</v>
+        <v>1.84779536724091</v>
       </c>
       <c r="H931" t="n">
         <v>2000</v>
@@ -27397,7 +27397,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G932" t="n">
-        <v>1.8477954864502</v>
+        <v>1.84779536724091</v>
       </c>
       <c r="H932" t="n">
         <v>3000</v>
@@ -27513,7 +27513,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G936" t="n">
-        <v>1.8477954864502</v>
+        <v>1.84779536724091</v>
       </c>
       <c r="H936" t="n">
         <v>6000</v>
@@ -27542,7 +27542,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G937" t="n">
-        <v>1.8477954864502</v>
+        <v>1.84779536724091</v>
       </c>
       <c r="H937" t="n">
         <v>0</v>
@@ -27571,7 +27571,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G938" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H938" t="n">
         <v>1000</v>
@@ -27629,7 +27629,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G940" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H940" t="n">
         <v>6000</v>
@@ -27658,7 +27658,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>1.80228328704834</v>
+        <v>1.80228340625763</v>
       </c>
       <c r="H941" t="n">
         <v>2000</v>
@@ -27687,7 +27687,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G942" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H942" t="n">
         <v>2000</v>
@@ -27716,7 +27716,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G943" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -27803,7 +27803,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G946" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H946" t="n">
         <v>2000</v>
@@ -27832,7 +27832,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G947" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -27861,7 +27861,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G948" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H948" t="n">
         <v>12000</v>
@@ -27890,7 +27890,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H949" t="n">
         <v>1000</v>
@@ -27919,7 +27919,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G950" t="n">
-        <v>1.80228328704834</v>
+        <v>1.80228340625763</v>
       </c>
       <c r="H950" t="n">
         <v>2000</v>
@@ -27948,7 +27948,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G951" t="n">
-        <v>1.80228328704834</v>
+        <v>1.80228340625763</v>
       </c>
       <c r="H951" t="n">
         <v>1000</v>
@@ -28006,7 +28006,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G953" t="n">
-        <v>1.80228328704834</v>
+        <v>1.80228340625763</v>
       </c>
       <c r="H953" t="n">
         <v>5000</v>
@@ -28035,7 +28035,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G954" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H954" t="n">
         <v>2000</v>
@@ -28064,7 +28064,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G955" t="n">
-        <v>1.79318082332611</v>
+        <v>1.7931809425354</v>
       </c>
       <c r="H955" t="n">
         <v>1000</v>
@@ -28093,7 +28093,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G956" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H956" t="n">
         <v>2000</v>
@@ -28122,7 +28122,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G957" t="n">
-        <v>1.80228328704834</v>
+        <v>1.80228340625763</v>
       </c>
       <c r="H957" t="n">
         <v>1000</v>
@@ -28151,7 +28151,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G958" t="n">
-        <v>1.76587355136871</v>
+        <v>1.765873670578</v>
       </c>
       <c r="H958" t="n">
         <v>14000</v>
@@ -28180,7 +28180,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G959" t="n">
-        <v>1.72036123275757</v>
+        <v>1.72036135196686</v>
       </c>
       <c r="H959" t="n">
         <v>2000</v>
@@ -28209,7 +28209,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G960" t="n">
-        <v>1.72036123275757</v>
+        <v>1.72036135196686</v>
       </c>
       <c r="H960" t="n">
         <v>7000</v>
@@ -28238,7 +28238,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G961" t="n">
-        <v>1.72036123275757</v>
+        <v>1.72036135196686</v>
       </c>
       <c r="H961" t="n">
         <v>6000</v>
@@ -28267,7 +28267,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G962" t="n">
-        <v>1.72036123275757</v>
+        <v>1.72036135196686</v>
       </c>
       <c r="H962" t="n">
         <v>0</v>
@@ -28296,7 +28296,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G963" t="n">
-        <v>1.72036123275757</v>
+        <v>1.72036135196686</v>
       </c>
       <c r="H963" t="n">
         <v>2000</v>
@@ -28325,7 +28325,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G964" t="n">
-        <v>1.76587355136871</v>
+        <v>1.765873670578</v>
       </c>
       <c r="H964" t="n">
         <v>29000</v>
@@ -53677,6 +53677,35 @@
         <v>25000</v>
       </c>
       <c r="I1838" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1839" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1839" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="D1839" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="E1839" t="n">
+        <v>1.9099999666214</v>
+      </c>
+      <c r="F1839" t="n">
+        <v>1.95000004768372</v>
+      </c>
+      <c r="G1839" t="n">
+        <v>1.95000004768372</v>
+      </c>
+      <c r="H1839" t="n">
+        <v>45000</v>
+      </c>
+      <c r="I1839" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -456,7 +456,7 @@
         <v>1.50020003318787</v>
       </c>
       <c r="G3" t="n">
-        <v>1.31330490112305</v>
+        <v>1.31330502033234</v>
       </c>
       <c r="H3" t="n">
         <v>35000</v>
@@ -485,7 +485,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G4" t="n">
-        <v>1.40067183971405</v>
+        <v>1.40067172050476</v>
       </c>
       <c r="H4" t="n">
         <v>193000</v>
@@ -514,7 +514,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G5" t="n">
-        <v>1.62828099727631</v>
+        <v>1.62828075885773</v>
       </c>
       <c r="H5" t="n">
         <v>169000</v>
@@ -543,7 +543,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G6" t="n">
-        <v>1.62828099727631</v>
+        <v>1.62828075885773</v>
       </c>
       <c r="H6" t="n">
         <v>470000</v>
@@ -601,7 +601,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G8" t="n">
-        <v>1.63265812397003</v>
+        <v>1.63265800476074</v>
       </c>
       <c r="H8" t="n">
         <v>69000</v>
@@ -659,7 +659,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G10" t="n">
-        <v>1.87339854240417</v>
+        <v>1.87339866161346</v>
       </c>
       <c r="H10" t="n">
         <v>464000</v>
@@ -775,7 +775,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G14" t="n">
-        <v>3.69427156448364</v>
+        <v>3.69427180290222</v>
       </c>
       <c r="H14" t="n">
         <v>633000</v>
@@ -920,7 +920,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>3.87810945510864</v>
+        <v>3.87810969352722</v>
       </c>
       <c r="H19" t="n">
         <v>592000</v>
@@ -1007,7 +1007,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>3.57171320915222</v>
+        <v>3.57171297073364</v>
       </c>
       <c r="H22" t="n">
         <v>212000</v>
@@ -1065,7 +1065,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G24" t="n">
-        <v>3.69427156448364</v>
+        <v>3.69427180290222</v>
       </c>
       <c r="H24" t="n">
         <v>227000</v>
@@ -1181,7 +1181,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G28" t="n">
-        <v>3.42289185523987</v>
+        <v>3.42289161682129</v>
       </c>
       <c r="H28" t="n">
         <v>30000</v>
@@ -1297,7 +1297,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G32" t="n">
-        <v>3.45353102684021</v>
+        <v>3.45353126525879</v>
       </c>
       <c r="H32" t="n">
         <v>39000</v>
@@ -1471,7 +1471,7 @@
         <v>3.75</v>
       </c>
       <c r="G38" t="n">
-        <v>3.28282451629639</v>
+        <v>3.28282427787781</v>
       </c>
       <c r="H38" t="n">
         <v>41000</v>
@@ -1558,7 +1558,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G41" t="n">
-        <v>2.9370334148407</v>
+        <v>2.93703365325928</v>
       </c>
       <c r="H41" t="n">
         <v>317000</v>
@@ -1616,7 +1616,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G43" t="n">
-        <v>2.62188220024109</v>
+        <v>2.62188243865967</v>
       </c>
       <c r="H43" t="n">
         <v>68000</v>
@@ -1645,7 +1645,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>2.34612512588501</v>
+        <v>2.34612536430359</v>
       </c>
       <c r="H44" t="n">
         <v>226000</v>
@@ -1703,7 +1703,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G46" t="n">
-        <v>2.98080468177795</v>
+        <v>2.98080444335938</v>
       </c>
       <c r="H46" t="n">
         <v>492000</v>
@@ -1732,7 +1732,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G47" t="n">
-        <v>2.78821229934692</v>
+        <v>2.78821206092834</v>
       </c>
       <c r="H47" t="n">
         <v>132000</v>
@@ -1761,7 +1761,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G48" t="n">
-        <v>2.83636021614075</v>
+        <v>2.83636045455933</v>
       </c>
       <c r="H48" t="n">
         <v>52000</v>
@@ -1790,7 +1790,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>2.73130989074707</v>
+        <v>2.73130965232849</v>
       </c>
       <c r="H49" t="n">
         <v>52000</v>
@@ -1819,7 +1819,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G50" t="n">
-        <v>2.74881839752197</v>
+        <v>2.74881863594055</v>
       </c>
       <c r="H50" t="n">
         <v>29000</v>
@@ -1848,7 +1848,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>2.77945804595947</v>
+        <v>2.77945780754089</v>
       </c>
       <c r="H51" t="n">
         <v>28000</v>
@@ -1877,7 +1877,7 @@
         <v>3.125</v>
       </c>
       <c r="G52" t="n">
-        <v>2.73568725585938</v>
+        <v>2.7356870174408</v>
       </c>
       <c r="H52" t="n">
         <v>24000</v>
@@ -1906,7 +1906,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H53" t="n">
         <v>253000</v>
@@ -1935,7 +1935,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G54" t="n">
-        <v>2.89763975143433</v>
+        <v>2.89763998985291</v>
       </c>
       <c r="H54" t="n">
         <v>60000</v>
@@ -1993,7 +1993,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G56" t="n">
-        <v>2.9063937664032</v>
+        <v>2.90639400482178</v>
       </c>
       <c r="H56" t="n">
         <v>179000</v>
@@ -2022,7 +2022,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G57" t="n">
-        <v>2.85386872291565</v>
+        <v>2.85386848449707</v>
       </c>
       <c r="H57" t="n">
         <v>52000</v>
@@ -2051,7 +2051,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>2.8013436794281</v>
+        <v>2.80134344100952</v>
       </c>
       <c r="H58" t="n">
         <v>74000</v>
@@ -2225,7 +2225,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G64" t="n">
-        <v>2.84073734283447</v>
+        <v>2.84073758125305</v>
       </c>
       <c r="H64" t="n">
         <v>61000</v>
@@ -2399,7 +2399,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>2.83636021614075</v>
+        <v>2.83636045455933</v>
       </c>
       <c r="H70" t="n">
         <v>21000</v>
@@ -2428,7 +2428,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>2.78821229934692</v>
+        <v>2.78821206092834</v>
       </c>
       <c r="H71" t="n">
         <v>15000</v>
@@ -2486,7 +2486,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G73" t="n">
-        <v>2.87137699127197</v>
+        <v>2.87137722969055</v>
       </c>
       <c r="H73" t="n">
         <v>14000</v>
@@ -2515,7 +2515,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G74" t="n">
-        <v>2.84949159622192</v>
+        <v>2.8494918346405</v>
       </c>
       <c r="H74" t="n">
         <v>3000</v>
@@ -2544,7 +2544,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G75" t="n">
-        <v>2.78821229934692</v>
+        <v>2.78821206092834</v>
       </c>
       <c r="H75" t="n">
         <v>10000</v>
@@ -2602,7 +2602,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>2.77945804595947</v>
+        <v>2.77945780754089</v>
       </c>
       <c r="H77" t="n">
         <v>18000</v>
@@ -2660,7 +2660,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>2.72693300247192</v>
+        <v>2.72693276405334</v>
       </c>
       <c r="H79" t="n">
         <v>6000</v>
@@ -2689,7 +2689,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G80" t="n">
-        <v>2.8319833278656</v>
+        <v>2.83198285102844</v>
       </c>
       <c r="H80" t="n">
         <v>24000</v>
@@ -2718,7 +2718,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.8013436794281</v>
+        <v>2.80134344100952</v>
       </c>
       <c r="H81" t="n">
         <v>20000</v>
@@ -2805,7 +2805,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G84" t="n">
-        <v>2.83636021614075</v>
+        <v>2.83636045455933</v>
       </c>
       <c r="H84" t="n">
         <v>12000</v>
@@ -2834,7 +2834,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G85" t="n">
-        <v>2.78821229934692</v>
+        <v>2.78821206092834</v>
       </c>
       <c r="H85" t="n">
         <v>8000</v>
@@ -2863,7 +2863,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>2.84073734283447</v>
+        <v>2.84073758125305</v>
       </c>
       <c r="H86" t="n">
         <v>8000</v>
@@ -2892,7 +2892,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G87" t="n">
-        <v>2.8013436794281</v>
+        <v>2.80134344100952</v>
       </c>
       <c r="H87" t="n">
         <v>20000</v>
@@ -2921,7 +2921,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G88" t="n">
-        <v>2.8013436794281</v>
+        <v>2.80134344100952</v>
       </c>
       <c r="H88" t="n">
         <v>49000</v>
@@ -2950,7 +2950,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G89" t="n">
-        <v>2.85386872291565</v>
+        <v>2.85386848449707</v>
       </c>
       <c r="H89" t="n">
         <v>20000</v>
@@ -2979,7 +2979,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G90" t="n">
-        <v>2.88888549804688</v>
+        <v>2.8888852596283</v>
       </c>
       <c r="H90" t="n">
         <v>39000</v>
@@ -3037,7 +3037,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G92" t="n">
-        <v>2.87137699127197</v>
+        <v>2.87137722969055</v>
       </c>
       <c r="H92" t="n">
         <v>8000</v>
@@ -3066,7 +3066,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G93" t="n">
-        <v>2.88888549804688</v>
+        <v>2.8888852596283</v>
       </c>
       <c r="H93" t="n">
         <v>20000</v>
@@ -3095,7 +3095,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G94" t="n">
-        <v>2.83636021614075</v>
+        <v>2.83636045455933</v>
       </c>
       <c r="H94" t="n">
         <v>27000</v>
@@ -3124,7 +3124,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G95" t="n">
-        <v>2.83636021614075</v>
+        <v>2.83636045455933</v>
       </c>
       <c r="H95" t="n">
         <v>11000</v>
@@ -3153,7 +3153,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G96" t="n">
-        <v>2.8013436794281</v>
+        <v>2.80134344100952</v>
       </c>
       <c r="H96" t="n">
         <v>9000</v>
@@ -3182,7 +3182,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H97" t="n">
         <v>14000</v>
@@ -3269,7 +3269,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G100" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H100" t="n">
         <v>5000</v>
@@ -3298,7 +3298,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G101" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H101" t="n">
         <v>8000</v>
@@ -3327,7 +3327,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G102" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H102" t="n">
         <v>5000</v>
@@ -3356,7 +3356,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G103" t="n">
-        <v>2.88888549804688</v>
+        <v>2.8888852596283</v>
       </c>
       <c r="H103" t="n">
         <v>8000</v>
@@ -3385,7 +3385,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G104" t="n">
-        <v>2.88888549804688</v>
+        <v>2.8888852596283</v>
       </c>
       <c r="H104" t="n">
         <v>9000</v>
@@ -3414,7 +3414,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88888549804688</v>
+        <v>2.8888852596283</v>
       </c>
       <c r="H105" t="n">
         <v>13000</v>
@@ -3501,7 +3501,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>4.39460706710815</v>
+        <v>4.39460754394531</v>
       </c>
       <c r="H108" t="n">
         <v>137000</v>
@@ -3588,7 +3588,7 @@
         <v>4.375</v>
       </c>
       <c r="G111" t="n">
-        <v>3.82996225357056</v>
+        <v>3.8299617767334</v>
       </c>
       <c r="H111" t="n">
         <v>247000</v>
@@ -3617,7 +3617,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G112" t="n">
-        <v>3.64174675941467</v>
+        <v>3.64174699783325</v>
       </c>
       <c r="H112" t="n">
         <v>202000</v>
@@ -3675,7 +3675,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>3.65487790107727</v>
+        <v>3.65487813949585</v>
       </c>
       <c r="H114" t="n">
         <v>318000</v>
@@ -3704,7 +3704,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G115" t="n">
-        <v>3.77305960655212</v>
+        <v>3.77305912971497</v>
       </c>
       <c r="H115" t="n">
         <v>88000</v>
@@ -3733,7 +3733,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>3.97878336906433</v>
+        <v>3.97878289222717</v>
       </c>
       <c r="H116" t="n">
         <v>371000</v>
@@ -3791,7 +3791,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>3.8606014251709</v>
+        <v>3.86060118675232</v>
       </c>
       <c r="H118" t="n">
         <v>82000</v>
@@ -3820,7 +3820,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G119" t="n">
-        <v>3.79932236671448</v>
+        <v>3.7993221282959</v>
       </c>
       <c r="H119" t="n">
         <v>66000</v>
@@ -3849,7 +3849,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>3.8474702835083</v>
+        <v>3.84747052192688</v>
       </c>
       <c r="H120" t="n">
         <v>40000</v>
@@ -3878,7 +3878,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G121" t="n">
-        <v>3.89124155044556</v>
+        <v>3.89124131202698</v>
       </c>
       <c r="H121" t="n">
         <v>84000</v>
@@ -3936,7 +3936,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>4.28955745697021</v>
+        <v>4.28955698013306</v>
       </c>
       <c r="H123" t="n">
         <v>537000</v>
@@ -3965,7 +3965,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G124" t="n">
-        <v>4.1713752746582</v>
+        <v>4.17137575149536</v>
       </c>
       <c r="H124" t="n">
         <v>181000</v>
@@ -4110,7 +4110,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G129" t="n">
-        <v>4.0619478225708</v>
+        <v>4.06194734573364</v>
       </c>
       <c r="H129" t="n">
         <v>76000</v>
@@ -4139,7 +4139,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>3.9700288772583</v>
+        <v>3.97002935409546</v>
       </c>
       <c r="H130" t="n">
         <v>38000</v>
@@ -4168,7 +4168,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G131" t="n">
-        <v>4.04006242752075</v>
+        <v>4.04006290435791</v>
       </c>
       <c r="H131" t="n">
         <v>36000</v>
@@ -4197,7 +4197,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G132" t="n">
-        <v>4.00504589080811</v>
+        <v>4.00504541397095</v>
       </c>
       <c r="H132" t="n">
         <v>14000</v>
@@ -4255,7 +4255,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G134" t="n">
-        <v>4.02693128585815</v>
+        <v>4.02693176269531</v>
       </c>
       <c r="H134" t="n">
         <v>58000</v>
@@ -4313,7 +4313,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G136" t="n">
-        <v>4.02255439758301</v>
+        <v>4.02255392074585</v>
       </c>
       <c r="H136" t="n">
         <v>19000</v>
@@ -4371,7 +4371,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G138" t="n">
-        <v>3.99629187583923</v>
+        <v>3.99629139900208</v>
       </c>
       <c r="H138" t="n">
         <v>9000</v>
@@ -4429,7 +4429,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G140" t="n">
-        <v>4.13635873794556</v>
+        <v>4.1363582611084</v>
       </c>
       <c r="H140" t="n">
         <v>97000</v>
@@ -4487,7 +4487,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G142" t="n">
-        <v>4.32895135879517</v>
+        <v>4.32895088195801</v>
       </c>
       <c r="H142" t="n">
         <v>162000</v>
@@ -4516,7 +4516,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G143" t="n">
-        <v>5.16497755050659</v>
+        <v>5.16497707366943</v>
       </c>
       <c r="H143" t="n">
         <v>670000</v>
@@ -4574,7 +4574,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G145" t="n">
-        <v>4.46464109420776</v>
+        <v>4.46464157104492</v>
       </c>
       <c r="H145" t="n">
         <v>522000</v>
@@ -4603,7 +4603,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G146" t="n">
-        <v>4.38585329055786</v>
+        <v>4.38585376739502</v>
       </c>
       <c r="H146" t="n">
         <v>548000</v>
@@ -4632,7 +4632,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G147" t="n">
-        <v>4.25454044342041</v>
+        <v>4.25454092025757</v>
       </c>
       <c r="H147" t="n">
         <v>160000</v>
@@ -4661,7 +4661,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>3.85184741020203</v>
+        <v>3.85184717178345</v>
       </c>
       <c r="H148" t="n">
         <v>192000</v>
@@ -4748,7 +4748,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G151" t="n">
-        <v>3.80369925498962</v>
+        <v>3.80369901657104</v>
       </c>
       <c r="H151" t="n">
         <v>89000</v>
@@ -4777,7 +4777,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>3.79932236671448</v>
+        <v>3.7993221282959</v>
       </c>
       <c r="H152" t="n">
         <v>69000</v>
@@ -4835,7 +4835,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G154" t="n">
-        <v>3.08147788047791</v>
+        <v>3.08147764205933</v>
       </c>
       <c r="H154" t="n">
         <v>57000</v>
@@ -4864,7 +4864,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G155" t="n">
-        <v>3.19965958595276</v>
+        <v>3.19965934753418</v>
       </c>
       <c r="H155" t="n">
         <v>17000</v>
@@ -4951,7 +4951,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>2.73130989074707</v>
+        <v>2.73130965232849</v>
       </c>
       <c r="H158" t="n">
         <v>60000</v>
@@ -5009,7 +5009,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G160" t="n">
-        <v>2.88888549804688</v>
+        <v>2.8888852596283</v>
       </c>
       <c r="H160" t="n">
         <v>26000</v>
@@ -5038,7 +5038,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G161" t="n">
-        <v>2.95891904830933</v>
+        <v>2.95891928672791</v>
       </c>
       <c r="H161" t="n">
         <v>30000</v>
@@ -5067,7 +5067,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G162" t="n">
-        <v>3.08147788047791</v>
+        <v>3.08147764205933</v>
       </c>
       <c r="H162" t="n">
         <v>37000</v>
@@ -5212,7 +5212,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G167" t="n">
-        <v>3.71177983283997</v>
+        <v>3.71177959442139</v>
       </c>
       <c r="H167" t="n">
         <v>54000</v>
@@ -5270,7 +5270,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G169" t="n">
-        <v>3.60672998428345</v>
+        <v>3.60672974586487</v>
       </c>
       <c r="H169" t="n">
         <v>15000</v>
@@ -5328,7 +5328,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G171" t="n">
-        <v>3.73366546630859</v>
+        <v>3.73366570472717</v>
       </c>
       <c r="H171" t="n">
         <v>10000</v>
@@ -5357,7 +5357,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G172" t="n">
-        <v>3.68551754951477</v>
+        <v>3.68551731109619</v>
       </c>
       <c r="H172" t="n">
         <v>16000</v>
@@ -5386,7 +5386,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G173" t="n">
-        <v>3.95252084732056</v>
+        <v>3.95251989364624</v>
       </c>
       <c r="H173" t="n">
         <v>72000</v>
@@ -5415,7 +5415,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.85184741020203</v>
+        <v>3.85184717178345</v>
       </c>
       <c r="H174" t="n">
         <v>74000</v>
@@ -5531,7 +5531,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>3.68114018440247</v>
+        <v>3.68114042282104</v>
       </c>
       <c r="H178" t="n">
         <v>51000</v>
@@ -5560,7 +5560,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G179" t="n">
-        <v>3.70302605628967</v>
+        <v>3.70302581787109</v>
       </c>
       <c r="H179" t="n">
         <v>30000</v>
@@ -5589,7 +5589,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G180" t="n">
-        <v>3.83433890342712</v>
+        <v>3.8343391418457</v>
       </c>
       <c r="H180" t="n">
         <v>29000</v>
@@ -5618,7 +5618,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G181" t="n">
-        <v>3.87810945510864</v>
+        <v>3.87810969352722</v>
       </c>
       <c r="H181" t="n">
         <v>9000</v>
@@ -5647,7 +5647,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G182" t="n">
-        <v>3.70302605628967</v>
+        <v>3.70302581787109</v>
       </c>
       <c r="H182" t="n">
         <v>15000</v>
@@ -5705,7 +5705,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>3.85184741020203</v>
+        <v>3.85184717178345</v>
       </c>
       <c r="H184" t="n">
         <v>8000</v>
@@ -5734,7 +5734,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G185" t="n">
-        <v>3.79056811332703</v>
+        <v>3.79056835174561</v>
       </c>
       <c r="H185" t="n">
         <v>4000</v>
@@ -5792,7 +5792,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G187" t="n">
-        <v>3.8606014251709</v>
+        <v>3.86060118675232</v>
       </c>
       <c r="H187" t="n">
         <v>5000</v>
@@ -5850,7 +5850,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G189" t="n">
-        <v>3.7511739730835</v>
+        <v>3.75117349624634</v>
       </c>
       <c r="H189" t="n">
         <v>22000</v>
@@ -5879,7 +5879,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G190" t="n">
-        <v>3.78224921226501</v>
+        <v>3.78224873542786</v>
       </c>
       <c r="H190" t="n">
         <v>11000</v>
@@ -5937,7 +5937,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G192" t="n">
-        <v>3.78668785095215</v>
+        <v>3.78668832778931</v>
       </c>
       <c r="H192" t="n">
         <v>2000</v>
@@ -5995,7 +5995,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G194" t="n">
-        <v>3.74673461914062</v>
+        <v>3.74673438072205</v>
       </c>
       <c r="H194" t="n">
         <v>3000</v>
@@ -6024,7 +6024,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G195" t="n">
-        <v>3.78224921226501</v>
+        <v>3.78224873542786</v>
       </c>
       <c r="H195" t="n">
         <v>8000</v>
@@ -6082,7 +6082,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>3.79112720489502</v>
+        <v>3.7911274433136</v>
       </c>
       <c r="H197" t="n">
         <v>2000</v>
@@ -6140,7 +6140,7 @@
         <v>4.5</v>
       </c>
       <c r="G199" t="n">
-        <v>3.99533367156982</v>
+        <v>3.99533319473267</v>
       </c>
       <c r="H199" t="n">
         <v>99000</v>
@@ -6198,7 +6198,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G201" t="n">
-        <v>3.83552026748657</v>
+        <v>3.83552002906799</v>
       </c>
       <c r="H201" t="n">
         <v>15000</v>
@@ -6285,7 +6285,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G204" t="n">
-        <v>3.82220220565796</v>
+        <v>3.82220196723938</v>
       </c>
       <c r="H204" t="n">
         <v>7000</v>
@@ -6314,7 +6314,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G205" t="n">
-        <v>3.82220220565796</v>
+        <v>3.82220196723938</v>
       </c>
       <c r="H205" t="n">
         <v>12000</v>
@@ -6343,7 +6343,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G206" t="n">
-        <v>3.80888414382935</v>
+        <v>3.80888438224792</v>
       </c>
       <c r="H206" t="n">
         <v>6000</v>
@@ -6401,7 +6401,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90654826164246</v>
+        <v>3.90654802322388</v>
       </c>
       <c r="H208" t="n">
         <v>30000</v>
@@ -6546,7 +6546,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>3.91986608505249</v>
+        <v>3.91986560821533</v>
       </c>
       <c r="H213" t="n">
         <v>11000</v>
@@ -6575,7 +6575,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>3.80888414382935</v>
+        <v>3.80888438224792</v>
       </c>
       <c r="H214" t="n">
         <v>28000</v>
@@ -6604,7 +6604,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>4.03084754943848</v>
+        <v>4.03084707260132</v>
       </c>
       <c r="H215" t="n">
         <v>41000</v>
@@ -6691,7 +6691,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G218" t="n">
-        <v>3.96425890922546</v>
+        <v>3.96425843238831</v>
       </c>
       <c r="H218" t="n">
         <v>43000</v>
@@ -6836,7 +6836,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G223" t="n">
-        <v>4.04416513442993</v>
+        <v>4.04416465759277</v>
       </c>
       <c r="H223" t="n">
         <v>17000</v>
@@ -6952,7 +6952,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>3.97313666343689</v>
+        <v>3.97313714027405</v>
       </c>
       <c r="H227" t="n">
         <v>9000</v>
@@ -6981,7 +6981,7 @@
         <v>4.5</v>
       </c>
       <c r="G228" t="n">
-        <v>3.99533367156982</v>
+        <v>3.99533319473267</v>
       </c>
       <c r="H228" t="n">
         <v>7000</v>
@@ -7039,7 +7039,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G230" t="n">
-        <v>3.98645424842834</v>
+        <v>3.9864547252655</v>
       </c>
       <c r="H230" t="n">
         <v>16000</v>
@@ -7097,7 +7097,7 @@
         <v>4.5</v>
       </c>
       <c r="G232" t="n">
-        <v>3.99533367156982</v>
+        <v>3.99533319473267</v>
       </c>
       <c r="H232" t="n">
         <v>19000</v>
@@ -7358,7 +7358,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>4.33271646499634</v>
+        <v>4.3327169418335</v>
       </c>
       <c r="H241" t="n">
         <v>24000</v>
@@ -7416,7 +7416,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G243" t="n">
-        <v>4.31939888000488</v>
+        <v>4.31939840316772</v>
       </c>
       <c r="H243" t="n">
         <v>53000</v>
@@ -7474,7 +7474,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G245" t="n">
-        <v>4.24393177032471</v>
+        <v>4.24393129348755</v>
       </c>
       <c r="H245" t="n">
         <v>12000</v>
@@ -7503,7 +7503,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>4.31052017211914</v>
+        <v>4.3105206489563</v>
       </c>
       <c r="H246" t="n">
         <v>21000</v>
@@ -7561,7 +7561,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>4.26168870925903</v>
+        <v>4.26168918609619</v>
       </c>
       <c r="H248" t="n">
         <v>29000</v>
@@ -7590,7 +7590,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G249" t="n">
-        <v>4.26168870925903</v>
+        <v>4.26168918609619</v>
       </c>
       <c r="H249" t="n">
         <v>15000</v>
@@ -7619,7 +7619,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G250" t="n">
-        <v>4.29720258712769</v>
+        <v>4.29720306396484</v>
       </c>
       <c r="H250" t="n">
         <v>11000</v>
@@ -7648,7 +7648,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G251" t="n">
-        <v>4.25281047821045</v>
+        <v>4.25281095504761</v>
       </c>
       <c r="H251" t="n">
         <v>4000</v>
@@ -7677,7 +7677,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G252" t="n">
-        <v>4.02196884155273</v>
+        <v>4.02196931838989</v>
       </c>
       <c r="H252" t="n">
         <v>35000</v>
@@ -7764,7 +7764,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G255" t="n">
-        <v>3.96425890922546</v>
+        <v>3.96425843238831</v>
       </c>
       <c r="H255" t="n">
         <v>2000</v>
@@ -7967,7 +7967,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G262" t="n">
-        <v>4.08855819702148</v>
+        <v>4.08855772018433</v>
       </c>
       <c r="H262" t="n">
         <v>17000</v>
@@ -8025,7 +8025,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G264" t="n">
-        <v>4.05748319625854</v>
+        <v>4.05748271942139</v>
       </c>
       <c r="H264" t="n">
         <v>17000</v>
@@ -8083,7 +8083,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>4.04416513442993</v>
+        <v>4.04416465759277</v>
       </c>
       <c r="H266" t="n">
         <v>23000</v>
@@ -8141,7 +8141,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G268" t="n">
-        <v>4.05748319625854</v>
+        <v>4.05748271942139</v>
       </c>
       <c r="H268" t="n">
         <v>4000</v>
@@ -8199,7 +8199,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>3.90654826164246</v>
+        <v>3.90654802322388</v>
       </c>
       <c r="H270" t="n">
         <v>13000</v>
@@ -8344,7 +8344,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G275" t="n">
-        <v>3.89766931533813</v>
+        <v>3.89766955375671</v>
       </c>
       <c r="H275" t="n">
         <v>17000</v>
@@ -8721,7 +8721,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G288" t="n">
-        <v>3.74673461914062</v>
+        <v>3.74673438072205</v>
       </c>
       <c r="H288" t="n">
         <v>1000</v>
@@ -8750,7 +8750,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G289" t="n">
-        <v>3.74673461914062</v>
+        <v>3.74673438072205</v>
       </c>
       <c r="H289" t="n">
         <v>2000</v>
@@ -8779,7 +8779,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G290" t="n">
-        <v>3.58692121505737</v>
+        <v>3.58692145347595</v>
       </c>
       <c r="H290" t="n">
         <v>3000</v>
@@ -8837,7 +8837,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G292" t="n">
-        <v>3.80888414382935</v>
+        <v>3.80888438224792</v>
       </c>
       <c r="H292" t="n">
         <v>14000</v>
@@ -8866,7 +8866,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G293" t="n">
-        <v>3.82220220565796</v>
+        <v>3.82220196723938</v>
       </c>
       <c r="H293" t="n">
         <v>28000</v>
@@ -8924,7 +8924,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>3.69790267944336</v>
+        <v>3.69790315628052</v>
       </c>
       <c r="H295" t="n">
         <v>13000</v>
@@ -9040,7 +9040,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>3.58692121505737</v>
+        <v>3.58692145347595</v>
       </c>
       <c r="H299" t="n">
         <v>25000</v>
@@ -9098,7 +9098,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G301" t="n">
-        <v>3.50701498985291</v>
+        <v>3.50701475143433</v>
       </c>
       <c r="H301" t="n">
         <v>10000</v>
@@ -9127,7 +9127,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G302" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H302" t="n">
         <v>6000</v>
@@ -9214,7 +9214,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>3.64019250869751</v>
+        <v>3.64019227027893</v>
       </c>
       <c r="H305" t="n">
         <v>4000</v>
@@ -9243,7 +9243,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G306" t="n">
-        <v>3.57804298400879</v>
+        <v>3.57804322242737</v>
       </c>
       <c r="H306" t="n">
         <v>6000</v>
@@ -9330,7 +9330,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>3.58692121505737</v>
+        <v>3.58692145347595</v>
       </c>
       <c r="H309" t="n">
         <v>2000</v>
@@ -9388,7 +9388,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G311" t="n">
-        <v>3.50257539749146</v>
+        <v>3.50257563591003</v>
       </c>
       <c r="H311" t="n">
         <v>3000</v>
@@ -9562,7 +9562,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G317" t="n">
-        <v>3.23178052902222</v>
+        <v>3.2317807674408</v>
       </c>
       <c r="H317" t="n">
         <v>10000</v>
@@ -9591,7 +9591,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G318" t="n">
-        <v>3.19626665115356</v>
+        <v>3.19626641273499</v>
       </c>
       <c r="H318" t="n">
         <v>6000</v>
@@ -9620,7 +9620,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>3.19626665115356</v>
+        <v>3.19626641273499</v>
       </c>
       <c r="H319" t="n">
         <v>1000</v>
@@ -9707,7 +9707,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G322" t="n">
-        <v>3.16519212722778</v>
+        <v>3.1651918888092</v>
       </c>
       <c r="H322" t="n">
         <v>4000</v>
@@ -9765,7 +9765,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G324" t="n">
-        <v>3.23178052902222</v>
+        <v>3.2317807674408</v>
       </c>
       <c r="H324" t="n">
         <v>4000</v>
@@ -9794,7 +9794,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>3.19626665115356</v>
+        <v>3.19626641273499</v>
       </c>
       <c r="H325" t="n">
         <v>8000</v>
@@ -9852,7 +9852,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G327" t="n">
-        <v>3.19626665115356</v>
+        <v>3.19626641273499</v>
       </c>
       <c r="H327" t="n">
         <v>6000</v>
@@ -9881,7 +9881,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G328" t="n">
-        <v>3.29393029212952</v>
+        <v>3.2939305305481</v>
       </c>
       <c r="H328" t="n">
         <v>17000</v>
@@ -9910,7 +9910,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G329" t="n">
-        <v>3.17407035827637</v>
+        <v>3.17407011985779</v>
       </c>
       <c r="H329" t="n">
         <v>5000</v>
@@ -9939,7 +9939,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G330" t="n">
-        <v>3.19182729721069</v>
+        <v>3.19182753562927</v>
       </c>
       <c r="H330" t="n">
         <v>20000</v>
@@ -9968,7 +9968,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G331" t="n">
-        <v>3.42710828781128</v>
+        <v>3.4271080493927</v>
       </c>
       <c r="H331" t="n">
         <v>21000</v>
@@ -9997,7 +9997,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G332" t="n">
-        <v>3.50701498985291</v>
+        <v>3.50701475143433</v>
       </c>
       <c r="H332" t="n">
         <v>20000</v>
@@ -10113,7 +10113,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>3.38271570205688</v>
+        <v>3.38271546363831</v>
       </c>
       <c r="H336" t="n">
         <v>4000</v>
@@ -10171,7 +10171,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G338" t="n">
-        <v>3.37827610969543</v>
+        <v>3.37827634811401</v>
       </c>
       <c r="H338" t="n">
         <v>5000</v>
@@ -10258,7 +10258,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>3.64019250869751</v>
+        <v>3.64019227027893</v>
       </c>
       <c r="H341" t="n">
         <v>43000</v>
@@ -10287,7 +10287,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G342" t="n">
-        <v>3.64907121658325</v>
+        <v>3.64907145500183</v>
       </c>
       <c r="H342" t="n">
         <v>9000</v>
@@ -10345,7 +10345,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G344" t="n">
-        <v>3.57804298400879</v>
+        <v>3.57804322242737</v>
       </c>
       <c r="H344" t="n">
         <v>8000</v>
@@ -10374,7 +10374,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H345" t="n">
         <v>7000</v>
@@ -10461,7 +10461,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G348" t="n">
-        <v>3.74673461914062</v>
+        <v>3.74673438072205</v>
       </c>
       <c r="H348" t="n">
         <v>35000</v>
@@ -10490,7 +10490,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G349" t="n">
-        <v>3.76893091201782</v>
+        <v>3.7689311504364</v>
       </c>
       <c r="H349" t="n">
         <v>2000</v>
@@ -10519,7 +10519,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G350" t="n">
-        <v>3.76893091201782</v>
+        <v>3.7689311504364</v>
       </c>
       <c r="H350" t="n">
         <v>8000</v>
@@ -10635,7 +10635,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>4.03084754943848</v>
+        <v>4.03084707260132</v>
       </c>
       <c r="H354" t="n">
         <v>28000</v>
@@ -10693,7 +10693,7 @@
         <v>4.5</v>
       </c>
       <c r="G356" t="n">
-        <v>3.99533367156982</v>
+        <v>3.99533319473267</v>
       </c>
       <c r="H356" t="n">
         <v>22000</v>
@@ -10722,7 +10722,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>3.97313666343689</v>
+        <v>3.97313714027405</v>
       </c>
       <c r="H357" t="n">
         <v>25000</v>
@@ -10751,7 +10751,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G358" t="n">
-        <v>3.99977278709412</v>
+        <v>3.99977231025696</v>
       </c>
       <c r="H358" t="n">
         <v>13000</v>
@@ -10809,7 +10809,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G360" t="n">
-        <v>3.90654826164246</v>
+        <v>3.90654802322388</v>
       </c>
       <c r="H360" t="n">
         <v>11000</v>
@@ -10838,7 +10838,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>3.96425890922546</v>
+        <v>3.96425843238831</v>
       </c>
       <c r="H361" t="n">
         <v>20000</v>
@@ -10867,7 +10867,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>3.92874479293823</v>
+        <v>3.92874431610107</v>
       </c>
       <c r="H362" t="n">
         <v>34000</v>
@@ -10896,7 +10896,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>3.98201608657837</v>
+        <v>3.98201560974121</v>
       </c>
       <c r="H363" t="n">
         <v>37000</v>
@@ -10925,7 +10925,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G364" t="n">
-        <v>3.9686975479126</v>
+        <v>3.96869707107544</v>
       </c>
       <c r="H364" t="n">
         <v>5000</v>
@@ -10954,7 +10954,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G365" t="n">
-        <v>3.98645424842834</v>
+        <v>3.9864547252655</v>
       </c>
       <c r="H365" t="n">
         <v>4000</v>
@@ -10983,7 +10983,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G366" t="n">
-        <v>3.99977278709412</v>
+        <v>3.99977231025696</v>
       </c>
       <c r="H366" t="n">
         <v>31000</v>
@@ -11012,7 +11012,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>3.96425890922546</v>
+        <v>3.96425843238831</v>
       </c>
       <c r="H367" t="n">
         <v>13000</v>
@@ -11041,7 +11041,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G368" t="n">
-        <v>3.99977278709412</v>
+        <v>3.99977231025696</v>
       </c>
       <c r="H368" t="n">
         <v>61000</v>
@@ -11070,7 +11070,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>3.97313666343689</v>
+        <v>3.97313714027405</v>
       </c>
       <c r="H369" t="n">
         <v>37000</v>
@@ -11099,7 +11099,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>3.8532772064209</v>
+        <v>3.85327696800232</v>
       </c>
       <c r="H370" t="n">
         <v>50000</v>
@@ -11128,7 +11128,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G371" t="n">
-        <v>3.76449155807495</v>
+        <v>3.76449131965637</v>
       </c>
       <c r="H371" t="n">
         <v>26000</v>
@@ -11157,7 +11157,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G372" t="n">
-        <v>3.73341655731201</v>
+        <v>3.73341679573059</v>
       </c>
       <c r="H372" t="n">
         <v>16000</v>
@@ -11215,7 +11215,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G374" t="n">
-        <v>3.76449155807495</v>
+        <v>3.76449131965637</v>
       </c>
       <c r="H374" t="n">
         <v>7000</v>
@@ -11273,7 +11273,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G376" t="n">
-        <v>3.76449155807495</v>
+        <v>3.76449131965637</v>
       </c>
       <c r="H376" t="n">
         <v>12000</v>
@@ -11360,7 +11360,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>3.64019250869751</v>
+        <v>3.64019227027893</v>
       </c>
       <c r="H379" t="n">
         <v>43000</v>
@@ -11389,7 +11389,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G380" t="n">
-        <v>3.51589345932007</v>
+        <v>3.51589322090149</v>
       </c>
       <c r="H380" t="n">
         <v>16000</v>
@@ -11418,7 +11418,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>3.51589345932007</v>
+        <v>3.51589322090149</v>
       </c>
       <c r="H381" t="n">
         <v>21000</v>
@@ -11447,7 +11447,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>3.52921080589294</v>
+        <v>3.52921104431152</v>
       </c>
       <c r="H382" t="n">
         <v>24000</v>
@@ -11505,7 +11505,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G384" t="n">
-        <v>3.64019250869751</v>
+        <v>3.64019227027893</v>
       </c>
       <c r="H384" t="n">
         <v>15000</v>
@@ -11534,7 +11534,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G385" t="n">
-        <v>3.60467839241028</v>
+        <v>3.60467863082886</v>
       </c>
       <c r="H385" t="n">
         <v>23000</v>
@@ -11621,7 +11621,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H388" t="n">
         <v>31000</v>
@@ -11650,7 +11650,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G389" t="n">
-        <v>3.64907121658325</v>
+        <v>3.64907145500183</v>
       </c>
       <c r="H389" t="n">
         <v>25000</v>
@@ -11679,7 +11679,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>3.79112720489502</v>
+        <v>3.7911274433136</v>
       </c>
       <c r="H390" t="n">
         <v>21000</v>
@@ -11795,7 +11795,7 @@
         <v>4</v>
       </c>
       <c r="G394" t="n">
-        <v>3.5514075756073</v>
+        <v>3.55140733718872</v>
       </c>
       <c r="H394" t="n">
         <v>26000</v>
@@ -11824,7 +11824,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G395" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H395" t="n">
         <v>9000</v>
@@ -11998,7 +11998,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G401" t="n">
-        <v>3.57804298400879</v>
+        <v>3.57804322242737</v>
       </c>
       <c r="H401" t="n">
         <v>18000</v>
@@ -12056,7 +12056,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G403" t="n">
-        <v>3.56472492218018</v>
+        <v>3.56472516059875</v>
       </c>
       <c r="H403" t="n">
         <v>20000</v>
@@ -12143,7 +12143,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>3.58692121505737</v>
+        <v>3.58692145347595</v>
       </c>
       <c r="H406" t="n">
         <v>10000</v>
@@ -12172,7 +12172,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G407" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H407" t="n">
         <v>15000</v>
@@ -12259,7 +12259,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G410" t="n">
-        <v>3.60467839241028</v>
+        <v>3.60467863082886</v>
       </c>
       <c r="H410" t="n">
         <v>28000</v>
@@ -12288,7 +12288,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G411" t="n">
-        <v>3.58692121505737</v>
+        <v>3.58692145347595</v>
       </c>
       <c r="H411" t="n">
         <v>6000</v>
@@ -12317,7 +12317,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G412" t="n">
-        <v>3.58692121505737</v>
+        <v>3.58692145347595</v>
       </c>
       <c r="H412" t="n">
         <v>10000</v>
@@ -12346,7 +12346,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>3.6268744468689</v>
+        <v>3.62687492370605</v>
       </c>
       <c r="H413" t="n">
         <v>9000</v>
@@ -12375,7 +12375,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G414" t="n">
-        <v>3.60467839241028</v>
+        <v>3.60467863082886</v>
       </c>
       <c r="H414" t="n">
         <v>8000</v>
@@ -53706,6 +53706,35 @@
         <v>45000</v>
       </c>
       <c r="I1839" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1840" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1840" t="n">
+        <v>1.95000004768372</v>
+      </c>
+      <c r="D1840" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1840" t="n">
+        <v>1.92999994754791</v>
+      </c>
+      <c r="F1840" t="n">
+        <v>1.98000001907349</v>
+      </c>
+      <c r="G1840" t="n">
+        <v>1.98000001907349</v>
+      </c>
+      <c r="H1840" t="n">
+        <v>37000</v>
+      </c>
+      <c r="I1840" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>1.30437564849854</v>
+        <v>1.30437552928925</v>
       </c>
       <c r="H2" t="n">
         <v>322000</v>
@@ -456,7 +456,7 @@
         <v>1.50020003318787</v>
       </c>
       <c r="G3" t="n">
-        <v>1.31330502033234</v>
+        <v>1.31330490112305</v>
       </c>
       <c r="H3" t="n">
         <v>35000</v>
@@ -485,7 +485,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G4" t="n">
-        <v>1.40067172050476</v>
+        <v>1.40067183971405</v>
       </c>
       <c r="H4" t="n">
         <v>193000</v>
@@ -514,7 +514,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G5" t="n">
-        <v>1.62828075885773</v>
+        <v>1.62828099727631</v>
       </c>
       <c r="H5" t="n">
         <v>169000</v>
@@ -543,7 +543,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G6" t="n">
-        <v>1.62828075885773</v>
+        <v>1.62828099727631</v>
       </c>
       <c r="H6" t="n">
         <v>470000</v>
@@ -601,7 +601,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G8" t="n">
-        <v>1.63265800476074</v>
+        <v>1.63265812397003</v>
       </c>
       <c r="H8" t="n">
         <v>69000</v>
@@ -659,7 +659,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G10" t="n">
-        <v>1.87339866161346</v>
+        <v>1.87339854240417</v>
       </c>
       <c r="H10" t="n">
         <v>464000</v>
@@ -688,7 +688,7 @@
         <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.18854928016663</v>
+        <v>2.18854951858521</v>
       </c>
       <c r="H11" t="n">
         <v>315000</v>
@@ -833,7 +833,7 @@
         <v>4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3.9393892288208</v>
+        <v>3.93938946723938</v>
       </c>
       <c r="H16" t="n">
         <v>669000</v>
@@ -891,7 +891,7 @@
         <v>4.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3.9393892288208</v>
+        <v>3.93938946723938</v>
       </c>
       <c r="H18" t="n">
         <v>489000</v>
@@ -920,7 +920,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>3.87810969352722</v>
+        <v>3.8781099319458</v>
       </c>
       <c r="H19" t="n">
         <v>592000</v>
@@ -1007,7 +1007,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>3.57171297073364</v>
+        <v>3.57171320915222</v>
       </c>
       <c r="H22" t="n">
         <v>212000</v>
@@ -1036,7 +1036,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>3.43164587020874</v>
+        <v>3.43164563179016</v>
       </c>
       <c r="H23" t="n">
         <v>116000</v>
@@ -1152,7 +1152,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G27" t="n">
-        <v>3.51043391227722</v>
+        <v>3.51043367385864</v>
       </c>
       <c r="H27" t="n">
         <v>25000</v>
@@ -1181,7 +1181,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G28" t="n">
-        <v>3.42289161682129</v>
+        <v>3.42289185523987</v>
       </c>
       <c r="H28" t="n">
         <v>30000</v>
@@ -1297,7 +1297,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G32" t="n">
-        <v>3.45353126525879</v>
+        <v>3.45353102684021</v>
       </c>
       <c r="H32" t="n">
         <v>39000</v>
@@ -1326,7 +1326,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>3.40976023674011</v>
+        <v>3.40976047515869</v>
       </c>
       <c r="H33" t="n">
         <v>38000</v>
@@ -1355,7 +1355,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G34" t="n">
-        <v>3.43164587020874</v>
+        <v>3.43164563179016</v>
       </c>
       <c r="H34" t="n">
         <v>27000</v>
@@ -1384,7 +1384,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G35" t="n">
-        <v>3.43164587020874</v>
+        <v>3.43164563179016</v>
       </c>
       <c r="H35" t="n">
         <v>28000</v>
@@ -1471,7 +1471,7 @@
         <v>3.75</v>
       </c>
       <c r="G38" t="n">
-        <v>3.28282427787781</v>
+        <v>3.28282475471497</v>
       </c>
       <c r="H38" t="n">
         <v>41000</v>
@@ -1500,7 +1500,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>3.28720188140869</v>
+        <v>3.28720164299011</v>
       </c>
       <c r="H39" t="n">
         <v>64000</v>
@@ -1558,7 +1558,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G41" t="n">
-        <v>2.93703365325928</v>
+        <v>2.9370334148407</v>
       </c>
       <c r="H41" t="n">
         <v>317000</v>
@@ -1587,7 +1587,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G42" t="n">
-        <v>2.7838351726532</v>
+        <v>2.78383541107178</v>
       </c>
       <c r="H42" t="n">
         <v>113000</v>
@@ -1790,7 +1790,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>2.73130965232849</v>
+        <v>2.73130989074707</v>
       </c>
       <c r="H49" t="n">
         <v>52000</v>
@@ -1819,7 +1819,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G50" t="n">
-        <v>2.74881863594055</v>
+        <v>2.74881815910339</v>
       </c>
       <c r="H50" t="n">
         <v>29000</v>
@@ -1848,7 +1848,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>2.77945780754089</v>
+        <v>2.77945804595947</v>
       </c>
       <c r="H51" t="n">
         <v>28000</v>
@@ -1906,7 +1906,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>2.88450860977173</v>
+        <v>2.88450837135315</v>
       </c>
       <c r="H53" t="n">
         <v>253000</v>
@@ -1935,7 +1935,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G54" t="n">
-        <v>2.89763998985291</v>
+        <v>2.89763975143433</v>
       </c>
       <c r="H54" t="n">
         <v>60000</v>
@@ -1964,7 +1964,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>2.81009769439697</v>
+        <v>2.81009793281555</v>
       </c>
       <c r="H55" t="n">
         <v>73000</v>
@@ -1993,7 +1993,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G56" t="n">
-        <v>2.90639400482178</v>
+        <v>2.9063937664032</v>
       </c>
       <c r="H56" t="n">
         <v>179000</v>
@@ -2051,7 +2051,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>2.80134344100952</v>
+        <v>2.8013436794281</v>
       </c>
       <c r="H58" t="n">
         <v>74000</v>
@@ -2080,7 +2080,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G59" t="n">
-        <v>2.7838351726532</v>
+        <v>2.78383541107178</v>
       </c>
       <c r="H59" t="n">
         <v>31000</v>
@@ -2138,7 +2138,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G61" t="n">
-        <v>2.85824584960938</v>
+        <v>2.8582456111908</v>
       </c>
       <c r="H61" t="n">
         <v>55000</v>
@@ -2167,7 +2167,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G62" t="n">
-        <v>2.81009769439697</v>
+        <v>2.81009793281555</v>
       </c>
       <c r="H62" t="n">
         <v>11000</v>
@@ -2225,7 +2225,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G64" t="n">
-        <v>2.84073758125305</v>
+        <v>2.84073710441589</v>
       </c>
       <c r="H64" t="n">
         <v>61000</v>
@@ -2254,7 +2254,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G65" t="n">
-        <v>2.82322907447815</v>
+        <v>2.82322883605957</v>
       </c>
       <c r="H65" t="n">
         <v>17000</v>
@@ -2283,7 +2283,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G66" t="n">
-        <v>2.82322907447815</v>
+        <v>2.82322883605957</v>
       </c>
       <c r="H66" t="n">
         <v>15000</v>
@@ -2312,7 +2312,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>2.82322907447815</v>
+        <v>2.82322883605957</v>
       </c>
       <c r="H67" t="n">
         <v>1000</v>
@@ -2341,7 +2341,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>2.82760620117188</v>
+        <v>2.8276059627533</v>
       </c>
       <c r="H68" t="n">
         <v>24000</v>
@@ -2370,7 +2370,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>2.82760620117188</v>
+        <v>2.8276059627533</v>
       </c>
       <c r="H69" t="n">
         <v>9000</v>
@@ -2457,7 +2457,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>2.7838351726532</v>
+        <v>2.78383541107178</v>
       </c>
       <c r="H72" t="n">
         <v>7000</v>
@@ -2515,7 +2515,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G74" t="n">
-        <v>2.8494918346405</v>
+        <v>2.84949159622192</v>
       </c>
       <c r="H74" t="n">
         <v>3000</v>
@@ -2573,7 +2573,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G76" t="n">
-        <v>2.7838351726532</v>
+        <v>2.78383541107178</v>
       </c>
       <c r="H76" t="n">
         <v>2000</v>
@@ -2602,7 +2602,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>2.77945780754089</v>
+        <v>2.77945804595947</v>
       </c>
       <c r="H77" t="n">
         <v>18000</v>
@@ -2631,7 +2631,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>2.7707040309906</v>
+        <v>2.77070379257202</v>
       </c>
       <c r="H78" t="n">
         <v>13000</v>
@@ -2689,7 +2689,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G80" t="n">
-        <v>2.83198285102844</v>
+        <v>2.8319833278656</v>
       </c>
       <c r="H80" t="n">
         <v>24000</v>
@@ -2718,7 +2718,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.80134344100952</v>
+        <v>2.8013436794281</v>
       </c>
       <c r="H81" t="n">
         <v>20000</v>
@@ -2747,7 +2747,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G82" t="n">
-        <v>2.7400643825531</v>
+        <v>2.74006414413452</v>
       </c>
       <c r="H82" t="n">
         <v>7000</v>
@@ -2863,7 +2863,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>2.84073758125305</v>
+        <v>2.84073710441589</v>
       </c>
       <c r="H86" t="n">
         <v>8000</v>
@@ -2892,7 +2892,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G87" t="n">
-        <v>2.80134344100952</v>
+        <v>2.8013436794281</v>
       </c>
       <c r="H87" t="n">
         <v>20000</v>
@@ -2921,7 +2921,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G88" t="n">
-        <v>2.80134344100952</v>
+        <v>2.8013436794281</v>
       </c>
       <c r="H88" t="n">
         <v>49000</v>
@@ -2979,7 +2979,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G90" t="n">
-        <v>2.8888852596283</v>
+        <v>2.88888549804688</v>
       </c>
       <c r="H90" t="n">
         <v>39000</v>
@@ -3066,7 +3066,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G93" t="n">
-        <v>2.8888852596283</v>
+        <v>2.88888549804688</v>
       </c>
       <c r="H93" t="n">
         <v>20000</v>
@@ -3153,7 +3153,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G96" t="n">
-        <v>2.80134344100952</v>
+        <v>2.8013436794281</v>
       </c>
       <c r="H96" t="n">
         <v>9000</v>
@@ -3182,7 +3182,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>2.88450860977173</v>
+        <v>2.88450837135315</v>
       </c>
       <c r="H97" t="n">
         <v>14000</v>
@@ -3211,7 +3211,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>2.82760620117188</v>
+        <v>2.8276059627533</v>
       </c>
       <c r="H98" t="n">
         <v>4000</v>
@@ -3240,7 +3240,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.86699986457825</v>
+        <v>2.86700010299683</v>
       </c>
       <c r="H99" t="n">
         <v>3000</v>
@@ -3269,7 +3269,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G100" t="n">
-        <v>2.88450860977173</v>
+        <v>2.88450837135315</v>
       </c>
       <c r="H100" t="n">
         <v>5000</v>
@@ -3298,7 +3298,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G101" t="n">
-        <v>2.88450860977173</v>
+        <v>2.88450837135315</v>
       </c>
       <c r="H101" t="n">
         <v>8000</v>
@@ -3327,7 +3327,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G102" t="n">
-        <v>2.88450860977173</v>
+        <v>2.88450837135315</v>
       </c>
       <c r="H102" t="n">
         <v>5000</v>
@@ -3356,7 +3356,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G103" t="n">
-        <v>2.8888852596283</v>
+        <v>2.88888549804688</v>
       </c>
       <c r="H103" t="n">
         <v>8000</v>
@@ -3385,7 +3385,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G104" t="n">
-        <v>2.8888852596283</v>
+        <v>2.88888549804688</v>
       </c>
       <c r="H104" t="n">
         <v>9000</v>
@@ -3414,7 +3414,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G105" t="n">
-        <v>2.8888852596283</v>
+        <v>2.88888549804688</v>
       </c>
       <c r="H105" t="n">
         <v>13000</v>
@@ -3443,7 +3443,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G106" t="n">
-        <v>2.9983127117157</v>
+        <v>2.99831295013428</v>
       </c>
       <c r="H106" t="n">
         <v>52000</v>
@@ -3530,7 +3530,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G109" t="n">
-        <v>3.96565198898315</v>
+        <v>3.965651512146</v>
       </c>
       <c r="H109" t="n">
         <v>596000</v>
@@ -3588,7 +3588,7 @@
         <v>4.375</v>
       </c>
       <c r="G111" t="n">
-        <v>3.8299617767334</v>
+        <v>3.82996153831482</v>
       </c>
       <c r="H111" t="n">
         <v>247000</v>
@@ -3617,7 +3617,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G112" t="n">
-        <v>3.64174699783325</v>
+        <v>3.64174652099609</v>
       </c>
       <c r="H112" t="n">
         <v>202000</v>
@@ -3675,7 +3675,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>3.65487813949585</v>
+        <v>3.65487790107727</v>
       </c>
       <c r="H114" t="n">
         <v>318000</v>
@@ -3733,7 +3733,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>3.97878289222717</v>
+        <v>3.97878360748291</v>
       </c>
       <c r="H116" t="n">
         <v>371000</v>
@@ -3762,7 +3762,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>3.91312670707703</v>
+        <v>3.91312646865845</v>
       </c>
       <c r="H117" t="n">
         <v>152000</v>
@@ -3791,7 +3791,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>3.86060118675232</v>
+        <v>3.8606014251709</v>
       </c>
       <c r="H118" t="n">
         <v>82000</v>
@@ -3820,7 +3820,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G119" t="n">
-        <v>3.7993221282959</v>
+        <v>3.79932188987732</v>
       </c>
       <c r="H119" t="n">
         <v>66000</v>
@@ -3849,7 +3849,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>3.84747052192688</v>
+        <v>3.8474702835083</v>
       </c>
       <c r="H120" t="n">
         <v>40000</v>
@@ -3878,7 +3878,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G121" t="n">
-        <v>3.89124131202698</v>
+        <v>3.89124202728271</v>
       </c>
       <c r="H121" t="n">
         <v>84000</v>
@@ -3907,7 +3907,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G122" t="n">
-        <v>3.92625832557678</v>
+        <v>3.9262580871582</v>
       </c>
       <c r="H122" t="n">
         <v>35000</v>
@@ -4023,7 +4023,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>4.24578619003296</v>
+        <v>4.24578666687012</v>
       </c>
       <c r="H126" t="n">
         <v>238000</v>
@@ -4052,7 +4052,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>4.28518009185791</v>
+        <v>4.28518056869507</v>
       </c>
       <c r="H127" t="n">
         <v>152000</v>
@@ -4081,7 +4081,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G128" t="n">
-        <v>4.16699886322021</v>
+        <v>4.16699838638306</v>
       </c>
       <c r="H128" t="n">
         <v>58000</v>
@@ -4110,7 +4110,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G129" t="n">
-        <v>4.06194734573364</v>
+        <v>4.0619478225708</v>
       </c>
       <c r="H129" t="n">
         <v>76000</v>
@@ -4139,7 +4139,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>3.97002935409546</v>
+        <v>3.97002863883972</v>
       </c>
       <c r="H130" t="n">
         <v>38000</v>
@@ -4168,7 +4168,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G131" t="n">
-        <v>4.04006290435791</v>
+        <v>4.04006242752075</v>
       </c>
       <c r="H131" t="n">
         <v>36000</v>
@@ -4197,7 +4197,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G132" t="n">
-        <v>4.00504541397095</v>
+        <v>4.00504589080811</v>
       </c>
       <c r="H132" t="n">
         <v>14000</v>
@@ -4255,7 +4255,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G134" t="n">
-        <v>4.02693176269531</v>
+        <v>4.02693128585815</v>
       </c>
       <c r="H134" t="n">
         <v>58000</v>
@@ -4284,7 +4284,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>3.9568977355957</v>
+        <v>3.95689749717712</v>
       </c>
       <c r="H135" t="n">
         <v>25000</v>
@@ -4342,7 +4342,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G137" t="n">
-        <v>3.9875373840332</v>
+        <v>3.98753690719604</v>
       </c>
       <c r="H137" t="n">
         <v>27000</v>
@@ -4371,7 +4371,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G138" t="n">
-        <v>3.99629139900208</v>
+        <v>3.99629235267639</v>
       </c>
       <c r="H138" t="n">
         <v>9000</v>
@@ -4400,7 +4400,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G139" t="n">
-        <v>4.21952390670776</v>
+        <v>4.21952342987061</v>
       </c>
       <c r="H139" t="n">
         <v>149000</v>
@@ -4429,7 +4429,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G140" t="n">
-        <v>4.1363582611084</v>
+        <v>4.13635873794556</v>
       </c>
       <c r="H140" t="n">
         <v>97000</v>
@@ -4487,7 +4487,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G142" t="n">
-        <v>4.32895088195801</v>
+        <v>4.32895135879517</v>
       </c>
       <c r="H142" t="n">
         <v>162000</v>
@@ -4545,7 +4545,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G144" t="n">
-        <v>4.76228380203247</v>
+        <v>4.76228427886963</v>
       </c>
       <c r="H144" t="n">
         <v>733000</v>
@@ -4574,7 +4574,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G145" t="n">
-        <v>4.46464157104492</v>
+        <v>4.46464109420776</v>
       </c>
       <c r="H145" t="n">
         <v>522000</v>
@@ -4661,7 +4661,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>3.85184717178345</v>
+        <v>3.85184693336487</v>
       </c>
       <c r="H148" t="n">
         <v>192000</v>
@@ -4748,7 +4748,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G151" t="n">
-        <v>3.80369901657104</v>
+        <v>3.80369925498962</v>
       </c>
       <c r="H151" t="n">
         <v>89000</v>
@@ -4777,7 +4777,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>3.7993221282959</v>
+        <v>3.79932188987732</v>
       </c>
       <c r="H152" t="n">
         <v>69000</v>
@@ -4806,7 +4806,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G153" t="n">
-        <v>3.33097267150879</v>
+        <v>3.33097243309021</v>
       </c>
       <c r="H153" t="n">
         <v>164000</v>
@@ -4835,7 +4835,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G154" t="n">
-        <v>3.08147764205933</v>
+        <v>3.08147811889648</v>
       </c>
       <c r="H154" t="n">
         <v>57000</v>
@@ -4864,7 +4864,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G155" t="n">
-        <v>3.19965934753418</v>
+        <v>3.19965958595276</v>
       </c>
       <c r="H155" t="n">
         <v>17000</v>
@@ -4951,7 +4951,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>2.73130965232849</v>
+        <v>2.73130989074707</v>
       </c>
       <c r="H158" t="n">
         <v>60000</v>
@@ -5009,7 +5009,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G160" t="n">
-        <v>2.8888852596283</v>
+        <v>2.88888549804688</v>
       </c>
       <c r="H160" t="n">
         <v>26000</v>
@@ -5067,7 +5067,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G162" t="n">
-        <v>3.08147764205933</v>
+        <v>3.08147811889648</v>
       </c>
       <c r="H162" t="n">
         <v>37000</v>
@@ -5096,7 +5096,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G163" t="n">
-        <v>3.22154498100281</v>
+        <v>3.22154521942139</v>
       </c>
       <c r="H163" t="n">
         <v>30000</v>
@@ -5183,7 +5183,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.75555109977722</v>
+        <v>3.7555513381958</v>
       </c>
       <c r="H166" t="n">
         <v>119000</v>
@@ -5212,7 +5212,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G167" t="n">
-        <v>3.71177959442139</v>
+        <v>3.71178007125854</v>
       </c>
       <c r="H167" t="n">
         <v>54000</v>
@@ -5270,7 +5270,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G169" t="n">
-        <v>3.60672974586487</v>
+        <v>3.60672998428345</v>
       </c>
       <c r="H169" t="n">
         <v>15000</v>
@@ -5328,7 +5328,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G171" t="n">
-        <v>3.73366570472717</v>
+        <v>3.73366546630859</v>
       </c>
       <c r="H171" t="n">
         <v>10000</v>
@@ -5357,7 +5357,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G172" t="n">
-        <v>3.68551731109619</v>
+        <v>3.68551754951477</v>
       </c>
       <c r="H172" t="n">
         <v>16000</v>
@@ -5386,7 +5386,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G173" t="n">
-        <v>3.95251989364624</v>
+        <v>3.9525203704834</v>
       </c>
       <c r="H173" t="n">
         <v>72000</v>
@@ -5415,7 +5415,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.85184717178345</v>
+        <v>3.85184693336487</v>
       </c>
       <c r="H174" t="n">
         <v>74000</v>
@@ -5473,7 +5473,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>4.07070255279541</v>
+        <v>4.07070207595825</v>
       </c>
       <c r="H176" t="n">
         <v>44000</v>
@@ -5502,7 +5502,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>4.07070255279541</v>
+        <v>4.07070207595825</v>
       </c>
       <c r="H177" t="n">
         <v>17000</v>
@@ -5531,7 +5531,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>3.68114042282104</v>
+        <v>3.68114018440247</v>
       </c>
       <c r="H178" t="n">
         <v>51000</v>
@@ -5560,7 +5560,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G179" t="n">
-        <v>3.70302581787109</v>
+        <v>3.70302605628967</v>
       </c>
       <c r="H179" t="n">
         <v>30000</v>
@@ -5618,7 +5618,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G181" t="n">
-        <v>3.87810969352722</v>
+        <v>3.8781099319458</v>
       </c>
       <c r="H181" t="n">
         <v>9000</v>
@@ -5647,7 +5647,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G182" t="n">
-        <v>3.70302581787109</v>
+        <v>3.70302605628967</v>
       </c>
       <c r="H182" t="n">
         <v>15000</v>
@@ -5676,7 +5676,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>3.80807638168335</v>
+        <v>3.80807662010193</v>
       </c>
       <c r="H183" t="n">
         <v>2000</v>
@@ -5705,7 +5705,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>3.85184717178345</v>
+        <v>3.85184693336487</v>
       </c>
       <c r="H184" t="n">
         <v>8000</v>
@@ -5734,7 +5734,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G185" t="n">
-        <v>3.79056835174561</v>
+        <v>3.79056763648987</v>
       </c>
       <c r="H185" t="n">
         <v>4000</v>
@@ -5792,7 +5792,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G187" t="n">
-        <v>3.86060118675232</v>
+        <v>3.8606014251709</v>
       </c>
       <c r="H187" t="n">
         <v>5000</v>
@@ -5821,7 +5821,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>3.77743649482727</v>
+        <v>3.77743697166443</v>
       </c>
       <c r="H188" t="n">
         <v>7000</v>
@@ -5850,7 +5850,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G189" t="n">
-        <v>3.75117349624634</v>
+        <v>3.75117421150208</v>
       </c>
       <c r="H189" t="n">
         <v>22000</v>
@@ -5879,7 +5879,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G190" t="n">
-        <v>3.78224873542786</v>
+        <v>3.78224897384644</v>
       </c>
       <c r="H190" t="n">
         <v>11000</v>
@@ -5937,7 +5937,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G192" t="n">
-        <v>3.78668832778931</v>
+        <v>3.78668785095215</v>
       </c>
       <c r="H192" t="n">
         <v>2000</v>
@@ -5995,7 +5995,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G194" t="n">
-        <v>3.74673438072205</v>
+        <v>3.7467348575592</v>
       </c>
       <c r="H194" t="n">
         <v>3000</v>
@@ -6024,7 +6024,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G195" t="n">
-        <v>3.78224873542786</v>
+        <v>3.78224897384644</v>
       </c>
       <c r="H195" t="n">
         <v>8000</v>
@@ -6082,7 +6082,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>3.7911274433136</v>
+        <v>3.79112720489502</v>
       </c>
       <c r="H197" t="n">
         <v>2000</v>
@@ -6140,7 +6140,7 @@
         <v>4.5</v>
       </c>
       <c r="G199" t="n">
-        <v>3.99533319473267</v>
+        <v>3.99533343315125</v>
       </c>
       <c r="H199" t="n">
         <v>99000</v>
@@ -6169,7 +6169,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G200" t="n">
-        <v>3.86215543746948</v>
+        <v>3.86215567588806</v>
       </c>
       <c r="H200" t="n">
         <v>46000</v>
@@ -6198,7 +6198,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G201" t="n">
-        <v>3.83552002906799</v>
+        <v>3.83552026748657</v>
       </c>
       <c r="H201" t="n">
         <v>15000</v>
@@ -6285,7 +6285,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G204" t="n">
-        <v>3.82220196723938</v>
+        <v>3.82220220565796</v>
       </c>
       <c r="H204" t="n">
         <v>7000</v>
@@ -6314,7 +6314,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G205" t="n">
-        <v>3.82220196723938</v>
+        <v>3.82220220565796</v>
       </c>
       <c r="H205" t="n">
         <v>12000</v>
@@ -6343,7 +6343,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G206" t="n">
-        <v>3.80888438224792</v>
+        <v>3.8088846206665</v>
       </c>
       <c r="H206" t="n">
         <v>6000</v>
@@ -6401,7 +6401,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90654802322388</v>
+        <v>3.9065477848053</v>
       </c>
       <c r="H208" t="n">
         <v>30000</v>
@@ -6430,7 +6430,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>3.86215543746948</v>
+        <v>3.86215567588806</v>
       </c>
       <c r="H209" t="n">
         <v>8000</v>
@@ -6459,7 +6459,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>3.86215543746948</v>
+        <v>3.86215567588806</v>
       </c>
       <c r="H210" t="n">
         <v>2000</v>
@@ -6546,7 +6546,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>3.91986560821533</v>
+        <v>3.91986584663391</v>
       </c>
       <c r="H213" t="n">
         <v>11000</v>
@@ -6575,7 +6575,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>3.80888438224792</v>
+        <v>3.8088846206665</v>
       </c>
       <c r="H214" t="n">
         <v>28000</v>
@@ -6604,7 +6604,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>4.03084707260132</v>
+        <v>4.03084754943848</v>
       </c>
       <c r="H215" t="n">
         <v>41000</v>
@@ -6691,7 +6691,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G218" t="n">
-        <v>3.96425843238831</v>
+        <v>3.96425867080688</v>
       </c>
       <c r="H218" t="n">
         <v>43000</v>
@@ -6720,7 +6720,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>3.95094037055969</v>
+        <v>3.95094013214111</v>
       </c>
       <c r="H219" t="n">
         <v>12000</v>
@@ -6749,7 +6749,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>4.01752996444702</v>
+        <v>4.01752948760986</v>
       </c>
       <c r="H220" t="n">
         <v>10000</v>
@@ -6923,7 +6923,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G226" t="n">
-        <v>4.00421190261841</v>
+        <v>4.00421142578125</v>
       </c>
       <c r="H226" t="n">
         <v>2000</v>
@@ -6952,7 +6952,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>3.97313714027405</v>
+        <v>3.97313690185547</v>
       </c>
       <c r="H227" t="n">
         <v>9000</v>
@@ -6981,7 +6981,7 @@
         <v>4.5</v>
       </c>
       <c r="G228" t="n">
-        <v>3.99533319473267</v>
+        <v>3.99533343315125</v>
       </c>
       <c r="H228" t="n">
         <v>7000</v>
@@ -7010,7 +7010,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>4.01309061050415</v>
+        <v>4.01309013366699</v>
       </c>
       <c r="H229" t="n">
         <v>13000</v>
@@ -7039,7 +7039,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G230" t="n">
-        <v>3.9864547252655</v>
+        <v>3.98645448684692</v>
       </c>
       <c r="H230" t="n">
         <v>16000</v>
@@ -7097,7 +7097,7 @@
         <v>4.5</v>
       </c>
       <c r="G232" t="n">
-        <v>3.99533319473267</v>
+        <v>3.99533343315125</v>
       </c>
       <c r="H232" t="n">
         <v>19000</v>
@@ -7213,7 +7213,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G236" t="n">
-        <v>4.10187578201294</v>
+        <v>4.10187530517578</v>
       </c>
       <c r="H236" t="n">
         <v>72000</v>
@@ -7242,7 +7242,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G237" t="n">
-        <v>4.33715629577637</v>
+        <v>4.33715677261353</v>
       </c>
       <c r="H237" t="n">
         <v>92000</v>
@@ -7271,7 +7271,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.48365163803101</v>
+        <v>4.48365211486816</v>
       </c>
       <c r="H238" t="n">
         <v>99000</v>
@@ -7300,7 +7300,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>4.40374517440796</v>
+        <v>4.4037446975708</v>
       </c>
       <c r="H239" t="n">
         <v>37000</v>
@@ -7416,7 +7416,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G243" t="n">
-        <v>4.31939840316772</v>
+        <v>4.31939888000488</v>
       </c>
       <c r="H243" t="n">
         <v>53000</v>
@@ -7445,7 +7445,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G244" t="n">
-        <v>4.16846418380737</v>
+        <v>4.16846466064453</v>
       </c>
       <c r="H244" t="n">
         <v>27000</v>
@@ -7474,7 +7474,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G245" t="n">
-        <v>4.24393129348755</v>
+        <v>4.24393177032471</v>
       </c>
       <c r="H245" t="n">
         <v>12000</v>
@@ -7561,7 +7561,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>4.26168918609619</v>
+        <v>4.26168870925903</v>
       </c>
       <c r="H248" t="n">
         <v>29000</v>
@@ -7590,7 +7590,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G249" t="n">
-        <v>4.26168918609619</v>
+        <v>4.26168870925903</v>
       </c>
       <c r="H249" t="n">
         <v>15000</v>
@@ -7619,7 +7619,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G250" t="n">
-        <v>4.29720306396484</v>
+        <v>4.29720258712769</v>
       </c>
       <c r="H250" t="n">
         <v>11000</v>
@@ -7648,7 +7648,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G251" t="n">
-        <v>4.25281095504761</v>
+        <v>4.25281047821045</v>
       </c>
       <c r="H251" t="n">
         <v>4000</v>
@@ -7677,7 +7677,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G252" t="n">
-        <v>4.02196931838989</v>
+        <v>4.02196836471558</v>
       </c>
       <c r="H252" t="n">
         <v>35000</v>
@@ -7706,7 +7706,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G253" t="n">
-        <v>3.86215543746948</v>
+        <v>3.86215567588806</v>
       </c>
       <c r="H253" t="n">
         <v>21000</v>
@@ -7764,7 +7764,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G255" t="n">
-        <v>3.96425843238831</v>
+        <v>3.96425867080688</v>
       </c>
       <c r="H255" t="n">
         <v>2000</v>
@@ -7822,7 +7822,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>4.2883243560791</v>
+        <v>4.28832387924194</v>
       </c>
       <c r="H257" t="n">
         <v>48000</v>
@@ -7851,7 +7851,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>4.19953918457031</v>
+        <v>4.19953966140747</v>
       </c>
       <c r="H258" t="n">
         <v>30000</v>
@@ -7938,7 +7938,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G261" t="n">
-        <v>4.0929970741272</v>
+        <v>4.09299755096436</v>
       </c>
       <c r="H261" t="n">
         <v>28000</v>
@@ -7996,7 +7996,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>4.01309061050415</v>
+        <v>4.01309013366699</v>
       </c>
       <c r="H263" t="n">
         <v>9000</v>
@@ -8199,7 +8199,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>3.90654802322388</v>
+        <v>3.9065477848053</v>
       </c>
       <c r="H270" t="n">
         <v>13000</v>
@@ -8228,7 +8228,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G271" t="n">
-        <v>3.95094037055969</v>
+        <v>3.95094013214111</v>
       </c>
       <c r="H271" t="n">
         <v>7000</v>
@@ -8286,7 +8286,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>3.99089407920837</v>
+        <v>3.99089360237122</v>
       </c>
       <c r="H273" t="n">
         <v>16000</v>
@@ -8344,7 +8344,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G275" t="n">
-        <v>3.89766955375671</v>
+        <v>3.89766907691956</v>
       </c>
       <c r="H275" t="n">
         <v>17000</v>
@@ -8373,7 +8373,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G276" t="n">
-        <v>3.84439826011658</v>
+        <v>3.844398021698</v>
       </c>
       <c r="H276" t="n">
         <v>17000</v>
@@ -8547,7 +8547,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>3.8133237361908</v>
+        <v>3.81332349777222</v>
       </c>
       <c r="H282" t="n">
         <v>8000</v>
@@ -8721,7 +8721,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G288" t="n">
-        <v>3.74673438072205</v>
+        <v>3.7467348575592</v>
       </c>
       <c r="H288" t="n">
         <v>1000</v>
@@ -8750,7 +8750,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G289" t="n">
-        <v>3.74673438072205</v>
+        <v>3.7467348575592</v>
       </c>
       <c r="H289" t="n">
         <v>2000</v>
@@ -8837,7 +8837,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G292" t="n">
-        <v>3.80888438224792</v>
+        <v>3.8088846206665</v>
       </c>
       <c r="H292" t="n">
         <v>14000</v>
@@ -8866,7 +8866,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G293" t="n">
-        <v>3.82220196723938</v>
+        <v>3.82220220565796</v>
       </c>
       <c r="H293" t="n">
         <v>28000</v>
@@ -8924,7 +8924,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>3.69790315628052</v>
+        <v>3.69790267944336</v>
       </c>
       <c r="H295" t="n">
         <v>13000</v>
@@ -8953,7 +8953,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>3.69346380233765</v>
+        <v>3.69346356391907</v>
       </c>
       <c r="H296" t="n">
         <v>5000</v>
@@ -9127,7 +9127,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G302" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59580039978027</v>
       </c>
       <c r="H302" t="n">
         <v>6000</v>
@@ -9185,7 +9185,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G304" t="n">
-        <v>3.65794944763184</v>
+        <v>3.65794968605042</v>
       </c>
       <c r="H304" t="n">
         <v>1000</v>
@@ -9214,7 +9214,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>3.64019227027893</v>
+        <v>3.64019250869751</v>
       </c>
       <c r="H305" t="n">
         <v>4000</v>
@@ -9243,7 +9243,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G306" t="n">
-        <v>3.57804322242737</v>
+        <v>3.57804298400879</v>
       </c>
       <c r="H306" t="n">
         <v>6000</v>
@@ -9272,7 +9272,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G307" t="n">
-        <v>3.62243556976318</v>
+        <v>3.62243580818176</v>
       </c>
       <c r="H307" t="n">
         <v>16000</v>
@@ -9301,7 +9301,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>3.60911774635315</v>
+        <v>3.60911798477173</v>
       </c>
       <c r="H308" t="n">
         <v>4000</v>
@@ -9359,7 +9359,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>3.57360363006592</v>
+        <v>3.5736038684845</v>
       </c>
       <c r="H310" t="n">
         <v>10000</v>
@@ -9388,7 +9388,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G311" t="n">
-        <v>3.50257563591003</v>
+        <v>3.50257515907288</v>
       </c>
       <c r="H311" t="n">
         <v>3000</v>
@@ -9562,7 +9562,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G317" t="n">
-        <v>3.2317807674408</v>
+        <v>3.23178052902222</v>
       </c>
       <c r="H317" t="n">
         <v>10000</v>
@@ -9649,7 +9649,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G320" t="n">
-        <v>3.16075253486633</v>
+        <v>3.16075229644775</v>
       </c>
       <c r="H320" t="n">
         <v>3000</v>
@@ -9765,7 +9765,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G324" t="n">
-        <v>3.2317807674408</v>
+        <v>3.23178052902222</v>
       </c>
       <c r="H324" t="n">
         <v>4000</v>
@@ -9823,7 +9823,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G326" t="n">
-        <v>3.16075253486633</v>
+        <v>3.16075229644775</v>
       </c>
       <c r="H326" t="n">
         <v>7000</v>
@@ -9881,7 +9881,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G328" t="n">
-        <v>3.2939305305481</v>
+        <v>3.29393029212952</v>
       </c>
       <c r="H328" t="n">
         <v>17000</v>
@@ -9910,7 +9910,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G329" t="n">
-        <v>3.17407011985779</v>
+        <v>3.17407035827637</v>
       </c>
       <c r="H329" t="n">
         <v>5000</v>
@@ -10113,7 +10113,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>3.38271546363831</v>
+        <v>3.38271570205688</v>
       </c>
       <c r="H336" t="n">
         <v>4000</v>
@@ -10171,7 +10171,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G338" t="n">
-        <v>3.37827634811401</v>
+        <v>3.37827610969543</v>
       </c>
       <c r="H338" t="n">
         <v>5000</v>
@@ -10229,7 +10229,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G340" t="n">
-        <v>3.8133237361908</v>
+        <v>3.81332349777222</v>
       </c>
       <c r="H340" t="n">
         <v>152000</v>
@@ -10258,7 +10258,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>3.64019227027893</v>
+        <v>3.64019250869751</v>
       </c>
       <c r="H341" t="n">
         <v>43000</v>
@@ -10287,7 +10287,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G342" t="n">
-        <v>3.64907145500183</v>
+        <v>3.64907097816467</v>
       </c>
       <c r="H342" t="n">
         <v>9000</v>
@@ -10345,7 +10345,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G344" t="n">
-        <v>3.57804322242737</v>
+        <v>3.57804298400879</v>
       </c>
       <c r="H344" t="n">
         <v>8000</v>
@@ -10374,7 +10374,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59580039978027</v>
       </c>
       <c r="H345" t="n">
         <v>7000</v>
@@ -10461,7 +10461,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G348" t="n">
-        <v>3.74673438072205</v>
+        <v>3.7467348575592</v>
       </c>
       <c r="H348" t="n">
         <v>35000</v>
@@ -10490,7 +10490,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G349" t="n">
-        <v>3.7689311504364</v>
+        <v>3.76893043518066</v>
       </c>
       <c r="H349" t="n">
         <v>2000</v>
@@ -10519,7 +10519,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G350" t="n">
-        <v>3.7689311504364</v>
+        <v>3.76893043518066</v>
       </c>
       <c r="H350" t="n">
         <v>8000</v>
@@ -10548,7 +10548,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G351" t="n">
-        <v>3.95094037055969</v>
+        <v>3.95094013214111</v>
       </c>
       <c r="H351" t="n">
         <v>52000</v>
@@ -10577,7 +10577,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G352" t="n">
-        <v>3.89323091506958</v>
+        <v>3.893230676651</v>
       </c>
       <c r="H352" t="n">
         <v>36000</v>
@@ -10606,7 +10606,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G353" t="n">
-        <v>3.94650173187256</v>
+        <v>3.94650220870972</v>
       </c>
       <c r="H353" t="n">
         <v>36000</v>
@@ -10635,7 +10635,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>4.03084707260132</v>
+        <v>4.03084754943848</v>
       </c>
       <c r="H354" t="n">
         <v>28000</v>
@@ -10693,7 +10693,7 @@
         <v>4.5</v>
       </c>
       <c r="G356" t="n">
-        <v>3.99533319473267</v>
+        <v>3.99533343315125</v>
       </c>
       <c r="H356" t="n">
         <v>22000</v>
@@ -10722,7 +10722,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>3.97313714027405</v>
+        <v>3.97313690185547</v>
       </c>
       <c r="H357" t="n">
         <v>25000</v>
@@ -10751,7 +10751,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G358" t="n">
-        <v>3.99977231025696</v>
+        <v>3.9997730255127</v>
       </c>
       <c r="H358" t="n">
         <v>13000</v>
@@ -10809,7 +10809,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G360" t="n">
-        <v>3.90654802322388</v>
+        <v>3.9065477848053</v>
       </c>
       <c r="H360" t="n">
         <v>11000</v>
@@ -10838,7 +10838,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>3.96425843238831</v>
+        <v>3.96425867080688</v>
       </c>
       <c r="H361" t="n">
         <v>20000</v>
@@ -10867,7 +10867,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>3.92874431610107</v>
+        <v>3.92874455451965</v>
       </c>
       <c r="H362" t="n">
         <v>34000</v>
@@ -10925,7 +10925,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G364" t="n">
-        <v>3.96869707107544</v>
+        <v>3.9686975479126</v>
       </c>
       <c r="H364" t="n">
         <v>5000</v>
@@ -10954,7 +10954,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G365" t="n">
-        <v>3.9864547252655</v>
+        <v>3.98645448684692</v>
       </c>
       <c r="H365" t="n">
         <v>4000</v>
@@ -10983,7 +10983,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G366" t="n">
-        <v>3.99977231025696</v>
+        <v>3.9997730255127</v>
       </c>
       <c r="H366" t="n">
         <v>31000</v>
@@ -11012,7 +11012,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>3.96425843238831</v>
+        <v>3.96425867080688</v>
       </c>
       <c r="H367" t="n">
         <v>13000</v>
@@ -11041,7 +11041,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G368" t="n">
-        <v>3.99977231025696</v>
+        <v>3.9997730255127</v>
       </c>
       <c r="H368" t="n">
         <v>61000</v>
@@ -11070,7 +11070,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>3.97313714027405</v>
+        <v>3.97313690185547</v>
       </c>
       <c r="H369" t="n">
         <v>37000</v>
@@ -11099,7 +11099,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>3.85327696800232</v>
+        <v>3.85327672958374</v>
       </c>
       <c r="H370" t="n">
         <v>50000</v>
@@ -11128,7 +11128,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G371" t="n">
-        <v>3.76449131965637</v>
+        <v>3.76449179649353</v>
       </c>
       <c r="H371" t="n">
         <v>26000</v>
@@ -11215,7 +11215,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G374" t="n">
-        <v>3.76449131965637</v>
+        <v>3.76449179649353</v>
       </c>
       <c r="H374" t="n">
         <v>7000</v>
@@ -11273,7 +11273,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G376" t="n">
-        <v>3.76449131965637</v>
+        <v>3.76449179649353</v>
       </c>
       <c r="H376" t="n">
         <v>12000</v>
@@ -11360,7 +11360,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>3.64019227027893</v>
+        <v>3.64019250869751</v>
       </c>
       <c r="H379" t="n">
         <v>43000</v>
@@ -11447,7 +11447,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>3.52921104431152</v>
+        <v>3.52921080589294</v>
       </c>
       <c r="H382" t="n">
         <v>24000</v>
@@ -11505,7 +11505,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G384" t="n">
-        <v>3.64019227027893</v>
+        <v>3.64019250869751</v>
       </c>
       <c r="H384" t="n">
         <v>15000</v>
@@ -11534,7 +11534,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G385" t="n">
-        <v>3.60467863082886</v>
+        <v>3.60467839241028</v>
       </c>
       <c r="H385" t="n">
         <v>23000</v>
@@ -11621,7 +11621,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59580039978027</v>
       </c>
       <c r="H388" t="n">
         <v>31000</v>
@@ -11650,7 +11650,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G389" t="n">
-        <v>3.64907145500183</v>
+        <v>3.64907097816467</v>
       </c>
       <c r="H389" t="n">
         <v>25000</v>
@@ -11679,7 +11679,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>3.7911274433136</v>
+        <v>3.79112720489502</v>
       </c>
       <c r="H390" t="n">
         <v>21000</v>
@@ -11766,7 +11766,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G393" t="n">
-        <v>3.62243556976318</v>
+        <v>3.62243580818176</v>
       </c>
       <c r="H393" t="n">
         <v>30000</v>
@@ -11824,7 +11824,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G395" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59580039978027</v>
       </c>
       <c r="H395" t="n">
         <v>9000</v>
@@ -11998,7 +11998,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G401" t="n">
-        <v>3.57804322242737</v>
+        <v>3.57804298400879</v>
       </c>
       <c r="H401" t="n">
         <v>18000</v>
@@ -12027,7 +12027,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>3.57360363006592</v>
+        <v>3.5736038684845</v>
       </c>
       <c r="H402" t="n">
         <v>9000</v>
@@ -12056,7 +12056,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G403" t="n">
-        <v>3.56472516059875</v>
+        <v>3.56472492218018</v>
       </c>
       <c r="H403" t="n">
         <v>20000</v>
@@ -12085,7 +12085,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>3.60911774635315</v>
+        <v>3.60911798477173</v>
       </c>
       <c r="H404" t="n">
         <v>20000</v>
@@ -12172,7 +12172,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G407" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59580039978027</v>
       </c>
       <c r="H407" t="n">
         <v>15000</v>
@@ -12201,7 +12201,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>3.6845850944519</v>
+        <v>3.68458533287048</v>
       </c>
       <c r="H408" t="n">
         <v>8000</v>
@@ -12259,7 +12259,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G410" t="n">
-        <v>3.60467863082886</v>
+        <v>3.60467839241028</v>
       </c>
       <c r="H410" t="n">
         <v>28000</v>
@@ -12346,7 +12346,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>3.62687492370605</v>
+        <v>3.62687468528748</v>
       </c>
       <c r="H413" t="n">
         <v>9000</v>
@@ -12375,7 +12375,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G414" t="n">
-        <v>3.60467863082886</v>
+        <v>3.60467839241028</v>
       </c>
       <c r="H414" t="n">
         <v>8000</v>
@@ -12404,7 +12404,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G415" t="n">
-        <v>3.60911774635315</v>
+        <v>3.60911798477173</v>
       </c>
       <c r="H415" t="n">
         <v>9000</v>
@@ -12433,7 +12433,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G416" t="n">
-        <v>3.71834683418274</v>
+        <v>3.71834707260132</v>
       </c>
       <c r="H416" t="n">
         <v>18000</v>
@@ -12462,7 +12462,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G417" t="n">
-        <v>3.64552760124207</v>
+        <v>3.64552783966064</v>
       </c>
       <c r="H417" t="n">
         <v>9000</v>
@@ -12491,7 +12491,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G418" t="n">
-        <v>3.66828370094299</v>
+        <v>3.66828393936157</v>
       </c>
       <c r="H418" t="n">
         <v>49000</v>
@@ -12578,7 +12578,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G421" t="n">
-        <v>3.69559073448181</v>
+        <v>3.69559097290039</v>
       </c>
       <c r="H421" t="n">
         <v>9000</v>
@@ -12607,7 +12607,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G422" t="n">
-        <v>3.69559073448181</v>
+        <v>3.69559097290039</v>
       </c>
       <c r="H422" t="n">
         <v>2000</v>
@@ -12868,7 +12868,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G431" t="n">
-        <v>3.66828370094299</v>
+        <v>3.66828393936157</v>
       </c>
       <c r="H431" t="n">
         <v>2000</v>
@@ -12897,7 +12897,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G432" t="n">
-        <v>3.66828370094299</v>
+        <v>3.66828393936157</v>
       </c>
       <c r="H432" t="n">
         <v>9000</v>
@@ -12955,7 +12955,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>3.65918111801147</v>
+        <v>3.65918135643005</v>
       </c>
       <c r="H434" t="n">
         <v>20000</v>
@@ -12984,7 +12984,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G435" t="n">
-        <v>3.6136691570282</v>
+        <v>3.61366891860962</v>
       </c>
       <c r="H435" t="n">
         <v>6000</v>
@@ -13129,7 +13129,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G440" t="n">
-        <v>3.74110317230225</v>
+        <v>3.74110341072083</v>
       </c>
       <c r="H440" t="n">
         <v>16000</v>
@@ -13245,7 +13245,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G444" t="n">
-        <v>3.74110317230225</v>
+        <v>3.74110341072083</v>
       </c>
       <c r="H444" t="n">
         <v>23000</v>
@@ -13361,7 +13361,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G448" t="n">
-        <v>3.80482029914856</v>
+        <v>3.80482006072998</v>
       </c>
       <c r="H448" t="n">
         <v>12000</v>
@@ -13506,7 +13506,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G453" t="n">
-        <v>3.74110317230225</v>
+        <v>3.74110341072083</v>
       </c>
       <c r="H453" t="n">
         <v>6000</v>
@@ -13564,7 +13564,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>3.69559073448181</v>
+        <v>3.69559097290039</v>
       </c>
       <c r="H455" t="n">
         <v>6000</v>
@@ -13622,7 +13622,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G457" t="n">
-        <v>3.65918111801147</v>
+        <v>3.65918135643005</v>
       </c>
       <c r="H457" t="n">
         <v>15000</v>
@@ -13709,7 +13709,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G460" t="n">
-        <v>3.66828370094299</v>
+        <v>3.66828393936157</v>
       </c>
       <c r="H460" t="n">
         <v>24000</v>
@@ -13738,7 +13738,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G461" t="n">
-        <v>3.65918111801147</v>
+        <v>3.65918135643005</v>
       </c>
       <c r="H461" t="n">
         <v>12000</v>
@@ -13767,7 +13767,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G462" t="n">
-        <v>3.50443983078003</v>
+        <v>3.50443959236145</v>
       </c>
       <c r="H462" t="n">
         <v>214000</v>
@@ -13796,7 +13796,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G463" t="n">
-        <v>3.51354217529297</v>
+        <v>3.51354193687439</v>
       </c>
       <c r="H463" t="n">
         <v>21000</v>
@@ -13825,7 +13825,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G464" t="n">
-        <v>3.50443983078003</v>
+        <v>3.50443959236145</v>
       </c>
       <c r="H464" t="n">
         <v>24000</v>
@@ -13883,7 +13883,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G466" t="n">
-        <v>3.42251777648926</v>
+        <v>3.42251801490784</v>
       </c>
       <c r="H466" t="n">
         <v>3000</v>
@@ -13999,7 +13999,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G470" t="n">
-        <v>3.40431308746338</v>
+        <v>3.4043128490448</v>
       </c>
       <c r="H470" t="n">
         <v>20000</v>
@@ -14028,7 +14028,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G471" t="n">
-        <v>3.42251777648926</v>
+        <v>3.42251801490784</v>
       </c>
       <c r="H471" t="n">
         <v>13000</v>
@@ -14260,7 +14260,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G479" t="n">
-        <v>3.40431308746338</v>
+        <v>3.4043128490448</v>
       </c>
       <c r="H479" t="n">
         <v>3000</v>
@@ -14753,7 +14753,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G496" t="n">
-        <v>3.52264451980591</v>
+        <v>3.52264475822449</v>
       </c>
       <c r="H496" t="n">
         <v>12000</v>
@@ -14782,7 +14782,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G497" t="n">
-        <v>3.50443983078003</v>
+        <v>3.50443959236145</v>
       </c>
       <c r="H497" t="n">
         <v>6000</v>
@@ -14811,7 +14811,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G498" t="n">
-        <v>3.52264451980591</v>
+        <v>3.52264475822449</v>
       </c>
       <c r="H498" t="n">
         <v>5000</v>
@@ -15043,7 +15043,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>3.44982504844666</v>
+        <v>3.44982528686523</v>
       </c>
       <c r="H506" t="n">
         <v>32000</v>
@@ -15188,7 +15188,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G511" t="n">
-        <v>3.42251777648926</v>
+        <v>3.42251801490784</v>
       </c>
       <c r="H511" t="n">
         <v>3000</v>
@@ -15362,7 +15362,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G517" t="n">
-        <v>3.34969806671143</v>
+        <v>3.34969830513</v>
       </c>
       <c r="H517" t="n">
         <v>14000</v>
@@ -15420,7 +15420,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G519" t="n">
-        <v>3.31328845024109</v>
+        <v>3.31328868865967</v>
       </c>
       <c r="H519" t="n">
         <v>13000</v>
@@ -15449,7 +15449,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G520" t="n">
-        <v>3.31328845024109</v>
+        <v>3.31328868865967</v>
       </c>
       <c r="H520" t="n">
         <v>16000</v>
@@ -15536,7 +15536,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G523" t="n">
-        <v>3.25867390632629</v>
+        <v>3.25867366790771</v>
       </c>
       <c r="H523" t="n">
         <v>9000</v>
@@ -15594,7 +15594,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G525" t="n">
-        <v>3.31328845024109</v>
+        <v>3.31328868865967</v>
       </c>
       <c r="H525" t="n">
         <v>5000</v>
@@ -15710,7 +15710,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G529" t="n">
-        <v>3.31328845024109</v>
+        <v>3.31328868865967</v>
       </c>
       <c r="H529" t="n">
         <v>14000</v>
@@ -15826,7 +15826,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G533" t="n">
-        <v>3.32239079475403</v>
+        <v>3.32239103317261</v>
       </c>
       <c r="H533" t="n">
         <v>4000</v>
@@ -16000,7 +16000,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G539" t="n">
-        <v>3.19495677947998</v>
+        <v>3.1949565410614</v>
       </c>
       <c r="H539" t="n">
         <v>7000</v>
@@ -16058,7 +16058,7 @@
         <v>3.5</v>
       </c>
       <c r="G541" t="n">
-        <v>3.18585443496704</v>
+        <v>3.18585419654846</v>
       </c>
       <c r="H541" t="n">
         <v>18000</v>
@@ -16087,7 +16087,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G542" t="n">
-        <v>3.19495677947998</v>
+        <v>3.1949565410614</v>
       </c>
       <c r="H542" t="n">
         <v>5000</v>
@@ -16261,7 +16261,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G548" t="n">
-        <v>3.19495677947998</v>
+        <v>3.1949565410614</v>
       </c>
       <c r="H548" t="n">
         <v>9000</v>
@@ -16464,7 +16464,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G555" t="n">
-        <v>3.15854716300964</v>
+        <v>3.15854692459106</v>
       </c>
       <c r="H555" t="n">
         <v>12000</v>
@@ -16493,7 +16493,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G556" t="n">
-        <v>3.09483003616333</v>
+        <v>3.09482979774475</v>
       </c>
       <c r="H556" t="n">
         <v>4000</v>
@@ -16754,7 +16754,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G565" t="n">
-        <v>2.66701531410217</v>
+        <v>2.66701507568359</v>
       </c>
       <c r="H565" t="n">
         <v>16000</v>
@@ -16812,7 +16812,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.67611765861511</v>
+        <v>2.67611742019653</v>
       </c>
       <c r="H567" t="n">
         <v>12000</v>
@@ -16986,7 +16986,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H573" t="n">
         <v>5000</v>
@@ -17044,7 +17044,7 @@
         <v>2.75</v>
       </c>
       <c r="G575" t="n">
-        <v>2.50317120552063</v>
+        <v>2.50317144393921</v>
       </c>
       <c r="H575" t="n">
         <v>5000</v>
@@ -17073,7 +17073,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H576" t="n">
         <v>1000</v>
@@ -17160,7 +17160,7 @@
         <v>2.75</v>
       </c>
       <c r="G579" t="n">
-        <v>2.50317120552063</v>
+        <v>2.50317144393921</v>
       </c>
       <c r="H579" t="n">
         <v>7000</v>
@@ -17189,7 +17189,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G580" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H580" t="n">
         <v>23000</v>
@@ -17218,7 +17218,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H581" t="n">
         <v>1000</v>
@@ -17276,7 +17276,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H583" t="n">
         <v>10000</v>
@@ -17334,7 +17334,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G585" t="n">
-        <v>2.51227355003357</v>
+        <v>2.51227378845215</v>
       </c>
       <c r="H585" t="n">
         <v>11000</v>
@@ -17392,7 +17392,7 @@
         <v>2.75</v>
       </c>
       <c r="G587" t="n">
-        <v>2.50317120552063</v>
+        <v>2.50317144393921</v>
       </c>
       <c r="H587" t="n">
         <v>7000</v>
@@ -17421,7 +17421,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H588" t="n">
         <v>18000</v>
@@ -17450,7 +17450,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G589" t="n">
-        <v>2.53958082199097</v>
+        <v>2.53958106040955</v>
       </c>
       <c r="H589" t="n">
         <v>8000</v>
@@ -17479,7 +17479,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G590" t="n">
-        <v>2.49406862258911</v>
+        <v>2.49406886100769</v>
       </c>
       <c r="H590" t="n">
         <v>10000</v>
@@ -17537,7 +17537,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G592" t="n">
-        <v>2.45765924453735</v>
+        <v>2.45765900611877</v>
       </c>
       <c r="H592" t="n">
         <v>4000</v>
@@ -17595,7 +17595,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H594" t="n">
         <v>6000</v>
@@ -17624,7 +17624,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H595" t="n">
         <v>4000</v>
@@ -17653,7 +17653,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>2.57599067687988</v>
+        <v>2.57599091529846</v>
       </c>
       <c r="H596" t="n">
         <v>1000</v>
@@ -17856,7 +17856,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.35753226280212</v>
+        <v>2.35753202438354</v>
       </c>
       <c r="H603" t="n">
         <v>4000</v>
@@ -17885,7 +17885,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G604" t="n">
-        <v>2.35753226280212</v>
+        <v>2.35753202438354</v>
       </c>
       <c r="H604" t="n">
         <v>8000</v>
@@ -18175,7 +18175,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G614" t="n">
-        <v>2.51227355003357</v>
+        <v>2.51227378845215</v>
       </c>
       <c r="H614" t="n">
         <v>2000</v>
@@ -18465,7 +18465,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>2.34842991828918</v>
+        <v>2.34842967987061</v>
       </c>
       <c r="H624" t="n">
         <v>4000</v>
@@ -18494,7 +18494,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G625" t="n">
-        <v>2.34842991828918</v>
+        <v>2.34842967987061</v>
       </c>
       <c r="H625" t="n">
         <v>0</v>
@@ -18523,7 +18523,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G626" t="n">
-        <v>2.34842991828918</v>
+        <v>2.34842967987061</v>
       </c>
       <c r="H626" t="n">
         <v>1000</v>
@@ -18639,7 +18639,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G630" t="n">
-        <v>2.45765924453735</v>
+        <v>2.45765900611877</v>
       </c>
       <c r="H630" t="n">
         <v>8000</v>
@@ -18668,7 +18668,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G631" t="n">
-        <v>2.44855690002441</v>
+        <v>2.44855666160583</v>
       </c>
       <c r="H631" t="n">
         <v>6000</v>
@@ -18784,7 +18784,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G635" t="n">
-        <v>2.44855690002441</v>
+        <v>2.44855666160583</v>
       </c>
       <c r="H635" t="n">
         <v>2000</v>
@@ -18813,7 +18813,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G636" t="n">
-        <v>2.44855690002441</v>
+        <v>2.44855666160583</v>
       </c>
       <c r="H636" t="n">
         <v>0</v>
@@ -18958,7 +18958,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G641" t="n">
-        <v>2.11176633834839</v>
+        <v>2.11176609992981</v>
       </c>
       <c r="H641" t="n">
         <v>31000</v>
@@ -18987,7 +18987,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G642" t="n">
-        <v>2.11176633834839</v>
+        <v>2.11176609992981</v>
       </c>
       <c r="H642" t="n">
         <v>40000</v>
@@ -19074,7 +19074,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G645" t="n">
-        <v>2.01163959503174</v>
+        <v>2.01163935661316</v>
       </c>
       <c r="H645" t="n">
         <v>18000</v>
@@ -19161,7 +19161,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G648" t="n">
-        <v>2.16638088226318</v>
+        <v>2.16638112068176</v>
       </c>
       <c r="H648" t="n">
         <v>7000</v>
@@ -19277,7 +19277,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G652" t="n">
-        <v>2.11176633834839</v>
+        <v>2.11176609992981</v>
       </c>
       <c r="H652" t="n">
         <v>13000</v>
@@ -19306,7 +19306,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G653" t="n">
-        <v>2.19368815422058</v>
+        <v>2.19368839263916</v>
       </c>
       <c r="H653" t="n">
         <v>52000</v>
@@ -19335,7 +19335,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G654" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H654" t="n">
         <v>10000</v>
@@ -19393,7 +19393,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.46676158905029</v>
+        <v>2.46676135063171</v>
       </c>
       <c r="H656" t="n">
         <v>160000</v>
@@ -19451,7 +19451,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G658" t="n">
-        <v>2.51227355003357</v>
+        <v>2.51227378845215</v>
       </c>
       <c r="H658" t="n">
         <v>43000</v>
@@ -19538,7 +19538,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G661" t="n">
-        <v>2.11176633834839</v>
+        <v>2.11176609992981</v>
       </c>
       <c r="H661" t="n">
         <v>21000</v>
@@ -19567,7 +19567,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>2.15727829933167</v>
+        <v>2.15727853775024</v>
       </c>
       <c r="H662" t="n">
         <v>37000</v>
@@ -19596,7 +19596,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G663" t="n">
-        <v>2.29381489753723</v>
+        <v>2.29381513595581</v>
       </c>
       <c r="H663" t="n">
         <v>24000</v>
@@ -19683,7 +19683,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G666" t="n">
-        <v>2.15727829933167</v>
+        <v>2.15727853775024</v>
       </c>
       <c r="H666" t="n">
         <v>3000</v>
@@ -19770,7 +19770,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G669" t="n">
-        <v>2.16638088226318</v>
+        <v>2.16638112068176</v>
       </c>
       <c r="H669" t="n">
         <v>22000</v>
@@ -19886,7 +19886,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G673" t="n">
-        <v>2.11176633834839</v>
+        <v>2.11176609992981</v>
       </c>
       <c r="H673" t="n">
         <v>4000</v>
@@ -19973,7 +19973,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H676" t="n">
         <v>12000</v>
@@ -20060,7 +20060,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G679" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H679" t="n">
         <v>1000</v>
@@ -20118,7 +20118,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G681" t="n">
-        <v>2.10266399383545</v>
+        <v>2.10266375541687</v>
       </c>
       <c r="H681" t="n">
         <v>1000</v>
@@ -20205,7 +20205,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H684" t="n">
         <v>4000</v>
@@ -20263,7 +20263,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G686" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H686" t="n">
         <v>3000</v>
@@ -20292,7 +20292,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G687" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H687" t="n">
         <v>0</v>
@@ -20350,7 +20350,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G689" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H689" t="n">
         <v>2000</v>
@@ -20408,7 +20408,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G691" t="n">
-        <v>1.96612739562988</v>
+        <v>1.96612727642059</v>
       </c>
       <c r="H691" t="n">
         <v>5000</v>
@@ -20524,7 +20524,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G695" t="n">
-        <v>1.98433220386505</v>
+        <v>1.98433232307434</v>
       </c>
       <c r="H695" t="n">
         <v>1000</v>
@@ -20582,7 +20582,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G697" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H697" t="n">
         <v>1000</v>
@@ -20611,7 +20611,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G698" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H698" t="n">
         <v>2000</v>
@@ -20640,7 +20640,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G699" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H699" t="n">
         <v>1000</v>
@@ -20669,7 +20669,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G700" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H700" t="n">
         <v>0</v>
@@ -20698,7 +20698,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G701" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H701" t="n">
         <v>0</v>
@@ -20756,7 +20756,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G703" t="n">
-        <v>1.90241014957428</v>
+        <v>1.90241003036499</v>
       </c>
       <c r="H703" t="n">
         <v>2000</v>
@@ -20785,7 +20785,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G704" t="n">
-        <v>1.90241014957428</v>
+        <v>1.90241003036499</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -20814,7 +20814,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G705" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H705" t="n">
         <v>13000</v>
@@ -20872,7 +20872,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G707" t="n">
-        <v>1.67484903335571</v>
+        <v>1.674849152565</v>
       </c>
       <c r="H707" t="n">
         <v>25000</v>
@@ -20901,7 +20901,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>1.72491252422333</v>
+        <v>1.72491264343262</v>
       </c>
       <c r="H708" t="n">
         <v>4000</v>
@@ -21162,7 +21162,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G717" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132237911224</v>
       </c>
       <c r="H717" t="n">
         <v>1000</v>
@@ -21249,7 +21249,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G720" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H720" t="n">
         <v>1000</v>
@@ -21423,7 +21423,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G726" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H726" t="n">
         <v>12000</v>
@@ -21539,7 +21539,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G730" t="n">
-        <v>1.65664422512054</v>
+        <v>1.65664434432983</v>
       </c>
       <c r="H730" t="n">
         <v>3000</v>
@@ -21829,7 +21829,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G740" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H740" t="n">
         <v>43000</v>
@@ -21858,7 +21858,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G741" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H741" t="n">
         <v>81000</v>
@@ -21887,7 +21887,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G742" t="n">
-        <v>2.0298445224762</v>
+        <v>2.02984428405762</v>
       </c>
       <c r="H742" t="n">
         <v>23000</v>
@@ -21916,7 +21916,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G743" t="n">
-        <v>1.92061495780945</v>
+        <v>1.92061507701874</v>
       </c>
       <c r="H743" t="n">
         <v>18000</v>
@@ -21945,7 +21945,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G744" t="n">
-        <v>1.96612739562988</v>
+        <v>1.96612727642059</v>
       </c>
       <c r="H744" t="n">
         <v>12000</v>
@@ -21974,7 +21974,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G745" t="n">
-        <v>1.98433220386505</v>
+        <v>1.98433232307434</v>
       </c>
       <c r="H745" t="n">
         <v>45000</v>
@@ -22061,7 +22061,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G748" t="n">
-        <v>1.97522985935211</v>
+        <v>1.97522974014282</v>
       </c>
       <c r="H748" t="n">
         <v>9000</v>
@@ -22090,7 +22090,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G749" t="n">
-        <v>1.92061495780945</v>
+        <v>1.92061507701874</v>
       </c>
       <c r="H749" t="n">
         <v>13000</v>
@@ -22148,7 +22148,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G751" t="n">
-        <v>1.92061495780945</v>
+        <v>1.92061507701874</v>
       </c>
       <c r="H751" t="n">
         <v>11000</v>
@@ -22264,7 +22264,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G755" t="n">
-        <v>1.90241014957428</v>
+        <v>1.90241003036499</v>
       </c>
       <c r="H755" t="n">
         <v>3000</v>
@@ -22322,7 +22322,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G757" t="n">
-        <v>1.90241014957428</v>
+        <v>1.90241003036499</v>
       </c>
       <c r="H757" t="n">
         <v>3000</v>
@@ -22380,7 +22380,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G759" t="n">
-        <v>1.94792246818542</v>
+        <v>1.94792258739471</v>
       </c>
       <c r="H759" t="n">
         <v>2000</v>
@@ -22409,7 +22409,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G760" t="n">
-        <v>1.93882012367249</v>
+        <v>1.9388200044632</v>
       </c>
       <c r="H760" t="n">
         <v>1000</v>
@@ -22438,7 +22438,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G761" t="n">
-        <v>2.0298445224762</v>
+        <v>2.02984428405762</v>
       </c>
       <c r="H761" t="n">
         <v>16000</v>
@@ -22902,7 +22902,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G777" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H777" t="n">
         <v>7000</v>
@@ -22931,7 +22931,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G778" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H778" t="n">
         <v>0</v>
@@ -23047,7 +23047,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G782" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H782" t="n">
         <v>6000</v>
@@ -23076,7 +23076,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G783" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H783" t="n">
         <v>5000</v>
@@ -23105,7 +23105,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G784" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H784" t="n">
         <v>0</v>
@@ -23134,7 +23134,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G785" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H785" t="n">
         <v>0</v>
@@ -23163,7 +23163,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G786" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H786" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G787" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H787" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G788" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H788" t="n">
         <v>0</v>
@@ -23250,7 +23250,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G789" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H789" t="n">
         <v>0</v>
@@ -23279,7 +23279,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G790" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H790" t="n">
         <v>0</v>
@@ -23337,7 +23337,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>2.01163959503174</v>
+        <v>2.01163935661316</v>
       </c>
       <c r="H792" t="n">
         <v>3000</v>
@@ -23366,7 +23366,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>2.01163959503174</v>
+        <v>2.01163935661316</v>
       </c>
       <c r="H793" t="n">
         <v>0</v>
@@ -23395,7 +23395,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G794" t="n">
-        <v>2.0298445224762</v>
+        <v>2.02984428405762</v>
       </c>
       <c r="H794" t="n">
         <v>3000</v>
@@ -23511,7 +23511,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G798" t="n">
-        <v>2.0298445224762</v>
+        <v>2.02984428405762</v>
       </c>
       <c r="H798" t="n">
         <v>5000</v>
@@ -23859,7 +23859,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G810" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H810" t="n">
         <v>4000</v>
@@ -23946,7 +23946,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G813" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H813" t="n">
         <v>4000</v>
@@ -24004,7 +24004,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G815" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H815" t="n">
         <v>2000</v>
@@ -24033,7 +24033,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G816" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H816" t="n">
         <v>0</v>
@@ -24091,7 +24091,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G818" t="n">
-        <v>1.90241014957428</v>
+        <v>1.90241003036499</v>
       </c>
       <c r="H818" t="n">
         <v>2000</v>
@@ -24120,7 +24120,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G819" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H819" t="n">
         <v>6000</v>
@@ -24410,7 +24410,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G829" t="n">
-        <v>1.75677108764648</v>
+        <v>1.75677096843719</v>
       </c>
       <c r="H829" t="n">
         <v>1000</v>
@@ -24439,7 +24439,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G830" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H830" t="n">
         <v>2000</v>
@@ -24497,7 +24497,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G832" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H832" t="n">
         <v>8000</v>
@@ -24526,7 +24526,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.72491252422333</v>
+        <v>1.72491264343262</v>
       </c>
       <c r="H833" t="n">
         <v>5000</v>
@@ -24758,7 +24758,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G841" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H841" t="n">
         <v>2000</v>
@@ -24787,7 +24787,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G842" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H842" t="n">
         <v>1000</v>
@@ -24816,7 +24816,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G843" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H843" t="n">
         <v>0</v>
@@ -24845,7 +24845,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G844" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H844" t="n">
         <v>0</v>
@@ -24874,7 +24874,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G845" t="n">
-        <v>1.71125888824463</v>
+        <v>1.71125900745392</v>
       </c>
       <c r="H845" t="n">
         <v>0</v>
@@ -24903,7 +24903,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G846" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H846" t="n">
         <v>7000</v>
@@ -25048,7 +25048,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G851" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H851" t="n">
         <v>2000</v>
@@ -25077,7 +25077,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G852" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H852" t="n">
         <v>0</v>
@@ -25135,7 +25135,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G854" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H854" t="n">
         <v>1000</v>
@@ -25193,7 +25193,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G856" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132237911224</v>
       </c>
       <c r="H856" t="n">
         <v>1000</v>
@@ -25222,7 +25222,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G857" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132237911224</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -25541,7 +25541,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G868" t="n">
-        <v>1.67484903335571</v>
+        <v>1.674849152565</v>
       </c>
       <c r="H868" t="n">
         <v>4000</v>
@@ -25657,7 +25657,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G872" t="n">
-        <v>1.66119539737701</v>
+        <v>1.6611955165863</v>
       </c>
       <c r="H872" t="n">
         <v>1000</v>
@@ -25686,7 +25686,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G873" t="n">
-        <v>1.66119539737701</v>
+        <v>1.6611955165863</v>
       </c>
       <c r="H873" t="n">
         <v>3000</v>
@@ -25744,7 +25744,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>1.72491252422333</v>
+        <v>1.72491264343262</v>
       </c>
       <c r="H875" t="n">
         <v>3000</v>
@@ -26092,7 +26092,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G887" t="n">
-        <v>1.88420522212982</v>
+        <v>1.88420534133911</v>
       </c>
       <c r="H887" t="n">
         <v>7000</v>
@@ -26266,7 +26266,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G893" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H893" t="n">
         <v>12000</v>
@@ -26295,7 +26295,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G894" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -26324,7 +26324,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G895" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H895" t="n">
         <v>9000</v>
@@ -26353,7 +26353,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G896" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H896" t="n">
         <v>47000</v>
@@ -26411,7 +26411,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G898" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H898" t="n">
         <v>16000</v>
@@ -26440,7 +26440,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G899" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H899" t="n">
         <v>5000</v>
@@ -26469,7 +26469,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G900" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H900" t="n">
         <v>1000</v>
@@ -26527,7 +26527,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G902" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H902" t="n">
         <v>1000</v>
@@ -26556,7 +26556,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G903" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H903" t="n">
         <v>2000</v>
@@ -26585,7 +26585,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G904" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H904" t="n">
         <v>0</v>
@@ -26614,7 +26614,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G905" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H905" t="n">
         <v>3000</v>
@@ -26643,7 +26643,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G906" t="n">
-        <v>1.82959055900574</v>
+        <v>1.82959067821503</v>
       </c>
       <c r="H906" t="n">
         <v>13000</v>
@@ -26672,7 +26672,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H907" t="n">
         <v>2000</v>
@@ -26730,7 +26730,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G909" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H909" t="n">
         <v>7000</v>
@@ -26759,7 +26759,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G910" t="n">
-        <v>1.78862977027893</v>
+        <v>1.78862965106964</v>
       </c>
       <c r="H910" t="n">
         <v>5000</v>
@@ -26875,7 +26875,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G914" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H914" t="n">
         <v>3000</v>
@@ -26904,7 +26904,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G915" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -26933,7 +26933,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G916" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -26962,7 +26962,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G917" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -26991,7 +26991,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132237911224</v>
       </c>
       <c r="H918" t="n">
         <v>7000</v>
@@ -27049,7 +27049,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G920" t="n">
-        <v>1.75677108764648</v>
+        <v>1.75677096843719</v>
       </c>
       <c r="H920" t="n">
         <v>2000</v>
@@ -27136,7 +27136,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G923" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132237911224</v>
       </c>
       <c r="H923" t="n">
         <v>5000</v>
@@ -27281,7 +27281,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G928" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H928" t="n">
         <v>29000</v>
@@ -27310,7 +27310,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G929" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H929" t="n">
         <v>3000</v>
@@ -27339,7 +27339,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G930" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H930" t="n">
         <v>0</v>
@@ -27368,7 +27368,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G931" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H931" t="n">
         <v>2000</v>
@@ -27397,7 +27397,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G932" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H932" t="n">
         <v>3000</v>
@@ -27513,7 +27513,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G936" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H936" t="n">
         <v>6000</v>
@@ -27542,7 +27542,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G937" t="n">
-        <v>1.84779536724091</v>
+        <v>1.8477954864502</v>
       </c>
       <c r="H937" t="n">
         <v>0</v>
@@ -27658,7 +27658,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H941" t="n">
         <v>2000</v>
@@ -27919,7 +27919,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G950" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H950" t="n">
         <v>2000</v>
@@ -27948,7 +27948,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G951" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H951" t="n">
         <v>1000</v>
@@ -27977,7 +27977,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G952" t="n">
-        <v>1.81138575077057</v>
+        <v>1.81138563156128</v>
       </c>
       <c r="H952" t="n">
         <v>2000</v>
@@ -28006,7 +28006,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G953" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H953" t="n">
         <v>5000</v>
@@ -28064,7 +28064,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G955" t="n">
-        <v>1.7931809425354</v>
+        <v>1.79318082332611</v>
       </c>
       <c r="H955" t="n">
         <v>1000</v>
@@ -28122,7 +28122,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G957" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H957" t="n">
         <v>1000</v>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -456,7 +456,7 @@
         <v>1.50020003318787</v>
       </c>
       <c r="G3" t="n">
-        <v>1.31330490112305</v>
+        <v>1.31330502033234</v>
       </c>
       <c r="H3" t="n">
         <v>35000</v>
@@ -514,7 +514,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G5" t="n">
-        <v>1.62828099727631</v>
+        <v>1.62828087806702</v>
       </c>
       <c r="H5" t="n">
         <v>169000</v>
@@ -543,7 +543,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G6" t="n">
-        <v>1.62828099727631</v>
+        <v>1.62828087806702</v>
       </c>
       <c r="H6" t="n">
         <v>470000</v>
@@ -601,7 +601,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G8" t="n">
-        <v>1.63265812397003</v>
+        <v>1.63265788555145</v>
       </c>
       <c r="H8" t="n">
         <v>69000</v>
@@ -659,7 +659,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G10" t="n">
-        <v>1.87339854240417</v>
+        <v>1.87339842319489</v>
       </c>
       <c r="H10" t="n">
         <v>464000</v>
@@ -688,7 +688,7 @@
         <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.18854951858521</v>
+        <v>2.18854975700378</v>
       </c>
       <c r="H11" t="n">
         <v>315000</v>
@@ -775,7 +775,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G14" t="n">
-        <v>3.69427180290222</v>
+        <v>3.69427156448364</v>
       </c>
       <c r="H14" t="n">
         <v>633000</v>
@@ -833,7 +833,7 @@
         <v>4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3.93938946723938</v>
+        <v>3.93938875198364</v>
       </c>
       <c r="H16" t="n">
         <v>669000</v>
@@ -891,7 +891,7 @@
         <v>4.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3.93938946723938</v>
+        <v>3.93938875198364</v>
       </c>
       <c r="H18" t="n">
         <v>489000</v>
@@ -920,7 +920,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>3.8781099319458</v>
+        <v>3.87810969352722</v>
       </c>
       <c r="H19" t="n">
         <v>592000</v>
@@ -978,7 +978,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G21" t="n">
-        <v>3.52794218063354</v>
+        <v>3.52794241905212</v>
       </c>
       <c r="H21" t="n">
         <v>356000</v>
@@ -1007,7 +1007,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>3.57171320915222</v>
+        <v>3.57171297073364</v>
       </c>
       <c r="H22" t="n">
         <v>212000</v>
@@ -1065,7 +1065,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G24" t="n">
-        <v>3.69427180290222</v>
+        <v>3.69427156448364</v>
       </c>
       <c r="H24" t="n">
         <v>227000</v>
@@ -1094,7 +1094,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G25" t="n">
-        <v>3.55420446395874</v>
+        <v>3.55420470237732</v>
       </c>
       <c r="H25" t="n">
         <v>275000</v>
@@ -1152,7 +1152,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G27" t="n">
-        <v>3.51043367385864</v>
+        <v>3.51043391227722</v>
       </c>
       <c r="H27" t="n">
         <v>25000</v>
@@ -1181,7 +1181,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G28" t="n">
-        <v>3.42289185523987</v>
+        <v>3.42289161682129</v>
       </c>
       <c r="H28" t="n">
         <v>30000</v>
@@ -1210,7 +1210,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G29" t="n">
-        <v>3.51918768882751</v>
+        <v>3.51918792724609</v>
       </c>
       <c r="H29" t="n">
         <v>87000</v>
@@ -1239,7 +1239,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>3.53669619560242</v>
+        <v>3.536696434021</v>
       </c>
       <c r="H30" t="n">
         <v>95000</v>
@@ -1297,7 +1297,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G32" t="n">
-        <v>3.45353102684021</v>
+        <v>3.45353126525879</v>
       </c>
       <c r="H32" t="n">
         <v>39000</v>
@@ -1326,7 +1326,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>3.40976047515869</v>
+        <v>3.40976023674011</v>
       </c>
       <c r="H33" t="n">
         <v>38000</v>
@@ -1413,7 +1413,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G36" t="n">
-        <v>3.41413760185242</v>
+        <v>3.41413712501526</v>
       </c>
       <c r="H36" t="n">
         <v>60000</v>
@@ -1442,7 +1442,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G37" t="n">
-        <v>3.41413760185242</v>
+        <v>3.41413712501526</v>
       </c>
       <c r="H37" t="n">
         <v>48000</v>
@@ -1471,7 +1471,7 @@
         <v>3.75</v>
       </c>
       <c r="G38" t="n">
-        <v>3.28282475471497</v>
+        <v>3.28282427787781</v>
       </c>
       <c r="H38" t="n">
         <v>41000</v>
@@ -1558,7 +1558,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G41" t="n">
-        <v>2.9370334148407</v>
+        <v>2.93703365325928</v>
       </c>
       <c r="H41" t="n">
         <v>317000</v>
@@ -1616,7 +1616,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G43" t="n">
-        <v>2.62188243865967</v>
+        <v>2.62188220024109</v>
       </c>
       <c r="H43" t="n">
         <v>68000</v>
@@ -1703,7 +1703,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G46" t="n">
-        <v>2.98080444335938</v>
+        <v>2.98080468177795</v>
       </c>
       <c r="H46" t="n">
         <v>492000</v>
@@ -1732,7 +1732,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G47" t="n">
-        <v>2.78821206092834</v>
+        <v>2.78821229934692</v>
       </c>
       <c r="H47" t="n">
         <v>132000</v>
@@ -1761,7 +1761,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G48" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H48" t="n">
         <v>52000</v>
@@ -1819,7 +1819,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G50" t="n">
-        <v>2.74881815910339</v>
+        <v>2.74881839752197</v>
       </c>
       <c r="H50" t="n">
         <v>29000</v>
@@ -1848,7 +1848,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>2.77945804595947</v>
+        <v>2.77945828437805</v>
       </c>
       <c r="H51" t="n">
         <v>28000</v>
@@ -1906,7 +1906,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H53" t="n">
         <v>253000</v>
@@ -2022,7 +2022,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G57" t="n">
-        <v>2.85386848449707</v>
+        <v>2.85386872291565</v>
       </c>
       <c r="H57" t="n">
         <v>52000</v>
@@ -2109,7 +2109,7 @@
         <v>3.25</v>
       </c>
       <c r="G60" t="n">
-        <v>2.8451144695282</v>
+        <v>2.84511423110962</v>
       </c>
       <c r="H60" t="n">
         <v>46000</v>
@@ -2138,7 +2138,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G61" t="n">
-        <v>2.8582456111908</v>
+        <v>2.85824608802795</v>
       </c>
       <c r="H61" t="n">
         <v>55000</v>
@@ -2196,7 +2196,7 @@
         <v>3.25</v>
       </c>
       <c r="G63" t="n">
-        <v>2.8451144695282</v>
+        <v>2.84511423110962</v>
       </c>
       <c r="H63" t="n">
         <v>14000</v>
@@ -2225,7 +2225,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G64" t="n">
-        <v>2.84073710441589</v>
+        <v>2.84073734283447</v>
       </c>
       <c r="H64" t="n">
         <v>61000</v>
@@ -2254,7 +2254,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G65" t="n">
-        <v>2.82322883605957</v>
+        <v>2.82322907447815</v>
       </c>
       <c r="H65" t="n">
         <v>17000</v>
@@ -2283,7 +2283,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G66" t="n">
-        <v>2.82322883605957</v>
+        <v>2.82322907447815</v>
       </c>
       <c r="H66" t="n">
         <v>15000</v>
@@ -2312,7 +2312,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>2.82322883605957</v>
+        <v>2.82322907447815</v>
       </c>
       <c r="H67" t="n">
         <v>1000</v>
@@ -2341,7 +2341,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>2.8276059627533</v>
+        <v>2.82760620117188</v>
       </c>
       <c r="H68" t="n">
         <v>24000</v>
@@ -2370,7 +2370,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>2.8276059627533</v>
+        <v>2.82760620117188</v>
       </c>
       <c r="H69" t="n">
         <v>9000</v>
@@ -2399,7 +2399,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H70" t="n">
         <v>21000</v>
@@ -2428,7 +2428,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>2.78821206092834</v>
+        <v>2.78821229934692</v>
       </c>
       <c r="H71" t="n">
         <v>15000</v>
@@ -2486,7 +2486,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G73" t="n">
-        <v>2.87137722969055</v>
+        <v>2.87137699127197</v>
       </c>
       <c r="H73" t="n">
         <v>14000</v>
@@ -2515,7 +2515,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G74" t="n">
-        <v>2.84949159622192</v>
+        <v>2.8494918346405</v>
       </c>
       <c r="H74" t="n">
         <v>3000</v>
@@ -2544,7 +2544,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G75" t="n">
-        <v>2.78821206092834</v>
+        <v>2.78821229934692</v>
       </c>
       <c r="H75" t="n">
         <v>10000</v>
@@ -2602,7 +2602,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>2.77945804595947</v>
+        <v>2.77945828437805</v>
       </c>
       <c r="H77" t="n">
         <v>18000</v>
@@ -2631,7 +2631,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>2.77070379257202</v>
+        <v>2.77070355415344</v>
       </c>
       <c r="H78" t="n">
         <v>13000</v>
@@ -2660,7 +2660,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>2.72693276405334</v>
+        <v>2.72693252563477</v>
       </c>
       <c r="H79" t="n">
         <v>6000</v>
@@ -2689,7 +2689,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G80" t="n">
-        <v>2.8319833278656</v>
+        <v>2.83198308944702</v>
       </c>
       <c r="H80" t="n">
         <v>24000</v>
@@ -2776,7 +2776,7 @@
         <v>3.25</v>
       </c>
       <c r="G83" t="n">
-        <v>2.8451144695282</v>
+        <v>2.84511423110962</v>
       </c>
       <c r="H83" t="n">
         <v>61000</v>
@@ -2805,7 +2805,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G84" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H84" t="n">
         <v>12000</v>
@@ -2834,7 +2834,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G85" t="n">
-        <v>2.78821206092834</v>
+        <v>2.78821229934692</v>
       </c>
       <c r="H85" t="n">
         <v>8000</v>
@@ -2863,7 +2863,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>2.84073710441589</v>
+        <v>2.84073734283447</v>
       </c>
       <c r="H86" t="n">
         <v>8000</v>
@@ -2950,7 +2950,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G89" t="n">
-        <v>2.85386848449707</v>
+        <v>2.85386872291565</v>
       </c>
       <c r="H89" t="n">
         <v>20000</v>
@@ -3008,7 +3008,7 @@
         <v>3.25</v>
       </c>
       <c r="G91" t="n">
-        <v>2.8451144695282</v>
+        <v>2.84511423110962</v>
       </c>
       <c r="H91" t="n">
         <v>16000</v>
@@ -3037,7 +3037,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G92" t="n">
-        <v>2.87137722969055</v>
+        <v>2.87137699127197</v>
       </c>
       <c r="H92" t="n">
         <v>8000</v>
@@ -3095,7 +3095,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G94" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H94" t="n">
         <v>27000</v>
@@ -3124,7 +3124,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G95" t="n">
-        <v>2.83636045455933</v>
+        <v>2.83636021614075</v>
       </c>
       <c r="H95" t="n">
         <v>11000</v>
@@ -3182,7 +3182,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H97" t="n">
         <v>14000</v>
@@ -3211,7 +3211,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>2.8276059627533</v>
+        <v>2.82760620117188</v>
       </c>
       <c r="H98" t="n">
         <v>4000</v>
@@ -3269,7 +3269,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G100" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H100" t="n">
         <v>5000</v>
@@ -3298,7 +3298,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G101" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H101" t="n">
         <v>8000</v>
@@ -3327,7 +3327,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G102" t="n">
-        <v>2.88450837135315</v>
+        <v>2.88450860977173</v>
       </c>
       <c r="H102" t="n">
         <v>5000</v>
@@ -3443,7 +3443,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G106" t="n">
-        <v>2.99831295013428</v>
+        <v>2.99831318855286</v>
       </c>
       <c r="H106" t="n">
         <v>52000</v>
@@ -3501,7 +3501,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>4.39460754394531</v>
+        <v>4.39460802078247</v>
       </c>
       <c r="H108" t="n">
         <v>137000</v>
@@ -3530,7 +3530,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G109" t="n">
-        <v>3.965651512146</v>
+        <v>3.96565198898315</v>
       </c>
       <c r="H109" t="n">
         <v>596000</v>
@@ -3559,7 +3559,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>4.11447334289551</v>
+        <v>4.11447286605835</v>
       </c>
       <c r="H110" t="n">
         <v>568000</v>
@@ -3588,7 +3588,7 @@
         <v>4.375</v>
       </c>
       <c r="G111" t="n">
-        <v>3.82996153831482</v>
+        <v>3.8299617767334</v>
       </c>
       <c r="H111" t="n">
         <v>247000</v>
@@ -3646,7 +3646,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G113" t="n">
-        <v>3.52794218063354</v>
+        <v>3.52794241905212</v>
       </c>
       <c r="H113" t="n">
         <v>87000</v>
@@ -3675,7 +3675,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>3.65487790107727</v>
+        <v>3.65487813949585</v>
       </c>
       <c r="H114" t="n">
         <v>318000</v>
@@ -3704,7 +3704,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G115" t="n">
-        <v>3.77305912971497</v>
+        <v>3.77305936813354</v>
       </c>
       <c r="H115" t="n">
         <v>88000</v>
@@ -3733,7 +3733,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>3.97878360748291</v>
+        <v>3.97878336906433</v>
       </c>
       <c r="H116" t="n">
         <v>371000</v>
@@ -3762,7 +3762,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>3.91312646865845</v>
+        <v>3.91312670707703</v>
       </c>
       <c r="H117" t="n">
         <v>152000</v>
@@ -3820,7 +3820,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G119" t="n">
-        <v>3.79932188987732</v>
+        <v>3.7993221282959</v>
       </c>
       <c r="H119" t="n">
         <v>66000</v>
@@ -3849,7 +3849,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>3.8474702835083</v>
+        <v>3.84747004508972</v>
       </c>
       <c r="H120" t="n">
         <v>40000</v>
@@ -3878,7 +3878,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G121" t="n">
-        <v>3.89124202728271</v>
+        <v>3.89124155044556</v>
       </c>
       <c r="H121" t="n">
         <v>84000</v>
@@ -3907,7 +3907,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G122" t="n">
-        <v>3.9262580871582</v>
+        <v>3.92625832557678</v>
       </c>
       <c r="H122" t="n">
         <v>35000</v>
@@ -3936,7 +3936,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>4.28955698013306</v>
+        <v>4.28955745697021</v>
       </c>
       <c r="H123" t="n">
         <v>537000</v>
@@ -3994,7 +3994,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>4.18012952804565</v>
+        <v>4.18013000488281</v>
       </c>
       <c r="H125" t="n">
         <v>73000</v>
@@ -4023,7 +4023,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>4.24578666687012</v>
+        <v>4.24578619003296</v>
       </c>
       <c r="H126" t="n">
         <v>238000</v>
@@ -4052,7 +4052,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>4.28518056869507</v>
+        <v>4.28518009185791</v>
       </c>
       <c r="H127" t="n">
         <v>152000</v>
@@ -4139,7 +4139,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>3.97002863883972</v>
+        <v>3.97002911567688</v>
       </c>
       <c r="H130" t="n">
         <v>38000</v>
@@ -4168,7 +4168,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G131" t="n">
-        <v>4.04006242752075</v>
+        <v>4.04006195068359</v>
       </c>
       <c r="H131" t="n">
         <v>36000</v>
@@ -4226,7 +4226,7 @@
         <v>4.625</v>
       </c>
       <c r="G133" t="n">
-        <v>4.0488166809082</v>
+        <v>4.04881715774536</v>
       </c>
       <c r="H133" t="n">
         <v>7000</v>
@@ -4255,7 +4255,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G134" t="n">
-        <v>4.02693128585815</v>
+        <v>4.026930809021</v>
       </c>
       <c r="H134" t="n">
         <v>58000</v>
@@ -4284,7 +4284,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>3.95689749717712</v>
+        <v>3.95689725875854</v>
       </c>
       <c r="H135" t="n">
         <v>25000</v>
@@ -4342,7 +4342,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G137" t="n">
-        <v>3.98753690719604</v>
+        <v>3.98753714561462</v>
       </c>
       <c r="H137" t="n">
         <v>27000</v>
@@ -4400,7 +4400,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G139" t="n">
-        <v>4.21952342987061</v>
+        <v>4.21952390670776</v>
       </c>
       <c r="H139" t="n">
         <v>149000</v>
@@ -4487,7 +4487,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G142" t="n">
-        <v>4.32895135879517</v>
+        <v>4.32895183563232</v>
       </c>
       <c r="H142" t="n">
         <v>162000</v>
@@ -4690,7 +4690,7 @@
         <v>4.625</v>
       </c>
       <c r="G149" t="n">
-        <v>4.0488166809082</v>
+        <v>4.04881715774536</v>
       </c>
       <c r="H149" t="n">
         <v>105000</v>
@@ -4719,7 +4719,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G150" t="n">
-        <v>3.78181409835815</v>
+        <v>3.781813621521</v>
       </c>
       <c r="H150" t="n">
         <v>94000</v>
@@ -4777,7 +4777,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>3.79932188987732</v>
+        <v>3.7993221282959</v>
       </c>
       <c r="H152" t="n">
         <v>69000</v>
@@ -4806,7 +4806,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G153" t="n">
-        <v>3.33097243309021</v>
+        <v>3.33097267150879</v>
       </c>
       <c r="H153" t="n">
         <v>164000</v>
@@ -4835,7 +4835,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G154" t="n">
-        <v>3.08147811889648</v>
+        <v>3.08147788047791</v>
       </c>
       <c r="H154" t="n">
         <v>57000</v>
@@ -4864,7 +4864,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G155" t="n">
-        <v>3.19965958595276</v>
+        <v>3.19965934753418</v>
       </c>
       <c r="H155" t="n">
         <v>17000</v>
@@ -4922,7 +4922,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G157" t="n">
-        <v>2.45555257797241</v>
+        <v>2.45555281639099</v>
       </c>
       <c r="H157" t="n">
         <v>83000</v>
@@ -5067,7 +5067,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G162" t="n">
-        <v>3.08147811889648</v>
+        <v>3.08147788047791</v>
       </c>
       <c r="H162" t="n">
         <v>37000</v>
@@ -5096,7 +5096,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G163" t="n">
-        <v>3.22154521942139</v>
+        <v>3.22154474258423</v>
       </c>
       <c r="H163" t="n">
         <v>30000</v>
@@ -5125,7 +5125,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G164" t="n">
-        <v>3.53669619560242</v>
+        <v>3.536696434021</v>
       </c>
       <c r="H164" t="n">
         <v>67000</v>
@@ -5183,7 +5183,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.7555513381958</v>
+        <v>3.75555086135864</v>
       </c>
       <c r="H166" t="n">
         <v>119000</v>
@@ -5212,7 +5212,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G167" t="n">
-        <v>3.71178007125854</v>
+        <v>3.71177983283997</v>
       </c>
       <c r="H167" t="n">
         <v>54000</v>
@@ -5241,7 +5241,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>3.62861514091492</v>
+        <v>3.6286153793335</v>
       </c>
       <c r="H168" t="n">
         <v>19000</v>
@@ -5270,7 +5270,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G169" t="n">
-        <v>3.60672998428345</v>
+        <v>3.60672974586487</v>
       </c>
       <c r="H169" t="n">
         <v>15000</v>
@@ -5328,7 +5328,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G171" t="n">
-        <v>3.73366546630859</v>
+        <v>3.73366570472717</v>
       </c>
       <c r="H171" t="n">
         <v>10000</v>
@@ -5357,7 +5357,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G172" t="n">
-        <v>3.68551754951477</v>
+        <v>3.68551778793335</v>
       </c>
       <c r="H172" t="n">
         <v>16000</v>
@@ -5386,7 +5386,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G173" t="n">
-        <v>3.9525203704834</v>
+        <v>3.95252060890198</v>
       </c>
       <c r="H173" t="n">
         <v>72000</v>
@@ -5444,7 +5444,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G175" t="n">
-        <v>3.94376683235168</v>
+        <v>3.94376635551453</v>
       </c>
       <c r="H175" t="n">
         <v>24000</v>
@@ -5473,7 +5473,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>4.07070207595825</v>
+        <v>4.07070255279541</v>
       </c>
       <c r="H176" t="n">
         <v>44000</v>
@@ -5502,7 +5502,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>4.07070207595825</v>
+        <v>4.07070255279541</v>
       </c>
       <c r="H177" t="n">
         <v>17000</v>
@@ -5531,7 +5531,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>3.68114018440247</v>
+        <v>3.68114042282104</v>
       </c>
       <c r="H178" t="n">
         <v>51000</v>
@@ -5589,7 +5589,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G180" t="n">
-        <v>3.8343391418457</v>
+        <v>3.83433866500854</v>
       </c>
       <c r="H180" t="n">
         <v>29000</v>
@@ -5618,7 +5618,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G181" t="n">
-        <v>3.8781099319458</v>
+        <v>3.87810969352722</v>
       </c>
       <c r="H181" t="n">
         <v>9000</v>
@@ -5676,7 +5676,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>3.80807662010193</v>
+        <v>3.80807614326477</v>
       </c>
       <c r="H183" t="n">
         <v>2000</v>
@@ -5763,7 +5763,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>3.86935591697693</v>
+        <v>3.86935567855835</v>
       </c>
       <c r="H186" t="n">
         <v>15000</v>
@@ -5821,7 +5821,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>3.77743697166443</v>
+        <v>3.77743673324585</v>
       </c>
       <c r="H188" t="n">
         <v>7000</v>
@@ -5850,7 +5850,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G189" t="n">
-        <v>3.75117421150208</v>
+        <v>3.7511739730835</v>
       </c>
       <c r="H189" t="n">
         <v>22000</v>
@@ -5937,7 +5937,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G192" t="n">
-        <v>3.78668785095215</v>
+        <v>3.78668808937073</v>
       </c>
       <c r="H192" t="n">
         <v>2000</v>
@@ -5966,7 +5966,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G193" t="n">
-        <v>3.66682815551758</v>
+        <v>3.66682839393616</v>
       </c>
       <c r="H193" t="n">
         <v>9000</v>
@@ -5995,7 +5995,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G194" t="n">
-        <v>3.7467348575592</v>
+        <v>3.74673438072205</v>
       </c>
       <c r="H194" t="n">
         <v>3000</v>
@@ -6053,7 +6053,7 @@
         <v>4.25</v>
       </c>
       <c r="G196" t="n">
-        <v>3.77337026596069</v>
+        <v>3.77337002754211</v>
       </c>
       <c r="H196" t="n">
         <v>7000</v>
@@ -6111,7 +6111,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G198" t="n">
-        <v>3.91098761558533</v>
+        <v>3.91098809242249</v>
       </c>
       <c r="H198" t="n">
         <v>27000</v>
@@ -6140,7 +6140,7 @@
         <v>4.5</v>
       </c>
       <c r="G199" t="n">
-        <v>3.99533343315125</v>
+        <v>3.99533295631409</v>
       </c>
       <c r="H199" t="n">
         <v>99000</v>
@@ -6169,7 +6169,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G200" t="n">
-        <v>3.86215567588806</v>
+        <v>3.8621551990509</v>
       </c>
       <c r="H200" t="n">
         <v>46000</v>
@@ -6198,7 +6198,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G201" t="n">
-        <v>3.83552026748657</v>
+        <v>3.83551979064941</v>
       </c>
       <c r="H201" t="n">
         <v>15000</v>
@@ -6343,7 +6343,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G206" t="n">
-        <v>3.8088846206665</v>
+        <v>3.80888438224792</v>
       </c>
       <c r="H206" t="n">
         <v>6000</v>
@@ -6430,7 +6430,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>3.86215567588806</v>
+        <v>3.8621551990509</v>
       </c>
       <c r="H209" t="n">
         <v>8000</v>
@@ -6459,7 +6459,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>3.86215567588806</v>
+        <v>3.8621551990509</v>
       </c>
       <c r="H210" t="n">
         <v>2000</v>
@@ -6488,7 +6488,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G211" t="n">
-        <v>3.81776332855225</v>
+        <v>3.81776261329651</v>
       </c>
       <c r="H211" t="n">
         <v>14000</v>
@@ -6517,7 +6517,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>3.95981931686401</v>
+        <v>3.95981907844543</v>
       </c>
       <c r="H212" t="n">
         <v>9000</v>
@@ -6546,7 +6546,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>3.91986584663391</v>
+        <v>3.91986608505249</v>
       </c>
       <c r="H213" t="n">
         <v>11000</v>
@@ -6575,7 +6575,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>3.8088846206665</v>
+        <v>3.80888438224792</v>
       </c>
       <c r="H214" t="n">
         <v>28000</v>
@@ -6604,7 +6604,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>4.03084754943848</v>
+        <v>4.03084707260132</v>
       </c>
       <c r="H215" t="n">
         <v>41000</v>
@@ -6662,7 +6662,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G217" t="n">
-        <v>3.94206237792969</v>
+        <v>3.94206190109253</v>
       </c>
       <c r="H217" t="n">
         <v>13000</v>
@@ -6691,7 +6691,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G218" t="n">
-        <v>3.96425867080688</v>
+        <v>3.96425914764404</v>
       </c>
       <c r="H218" t="n">
         <v>43000</v>
@@ -6720,7 +6720,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>3.95094013214111</v>
+        <v>3.95094037055969</v>
       </c>
       <c r="H219" t="n">
         <v>12000</v>
@@ -6749,7 +6749,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>4.01752948760986</v>
+        <v>4.01752996444702</v>
       </c>
       <c r="H220" t="n">
         <v>10000</v>
@@ -6778,7 +6778,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G221" t="n">
-        <v>4.0486044883728</v>
+        <v>4.04860401153564</v>
       </c>
       <c r="H221" t="n">
         <v>13000</v>
@@ -6807,7 +6807,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G222" t="n">
-        <v>4.06636142730713</v>
+        <v>4.06636095046997</v>
       </c>
       <c r="H222" t="n">
         <v>3000</v>
@@ -6865,7 +6865,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G224" t="n">
-        <v>4.0486044883728</v>
+        <v>4.04860401153564</v>
       </c>
       <c r="H224" t="n">
         <v>5000</v>
@@ -6894,7 +6894,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>3.95981931686401</v>
+        <v>3.95981907844543</v>
       </c>
       <c r="H225" t="n">
         <v>10000</v>
@@ -6923,7 +6923,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G226" t="n">
-        <v>4.00421142578125</v>
+        <v>4.00421237945557</v>
       </c>
       <c r="H226" t="n">
         <v>2000</v>
@@ -6981,7 +6981,7 @@
         <v>4.5</v>
       </c>
       <c r="G228" t="n">
-        <v>3.99533343315125</v>
+        <v>3.99533295631409</v>
       </c>
       <c r="H228" t="n">
         <v>7000</v>
@@ -7068,7 +7068,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G231" t="n">
-        <v>4.06636142730713</v>
+        <v>4.06636095046997</v>
       </c>
       <c r="H231" t="n">
         <v>61000</v>
@@ -7097,7 +7097,7 @@
         <v>4.5</v>
       </c>
       <c r="G232" t="n">
-        <v>3.99533343315125</v>
+        <v>3.99533295631409</v>
       </c>
       <c r="H232" t="n">
         <v>19000</v>
@@ -7126,7 +7126,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G233" t="n">
-        <v>4.0486044883728</v>
+        <v>4.04860401153564</v>
       </c>
       <c r="H233" t="n">
         <v>9000</v>
@@ -7155,7 +7155,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G234" t="n">
-        <v>4.06636142730713</v>
+        <v>4.06636095046997</v>
       </c>
       <c r="H234" t="n">
         <v>13000</v>
@@ -7184,7 +7184,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G235" t="n">
-        <v>4.08411836624146</v>
+        <v>4.0841178894043</v>
       </c>
       <c r="H235" t="n">
         <v>10000</v>
@@ -7242,7 +7242,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G237" t="n">
-        <v>4.33715677261353</v>
+        <v>4.33715629577637</v>
       </c>
       <c r="H237" t="n">
         <v>92000</v>
@@ -7300,7 +7300,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>4.4037446975708</v>
+        <v>4.40374565124512</v>
       </c>
       <c r="H239" t="n">
         <v>37000</v>
@@ -7503,7 +7503,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>4.3105206489563</v>
+        <v>4.31052017211914</v>
       </c>
       <c r="H246" t="n">
         <v>21000</v>
@@ -7532,7 +7532,7 @@
         <v>4.875</v>
       </c>
       <c r="G247" t="n">
-        <v>4.32827806472778</v>
+        <v>4.32827711105347</v>
       </c>
       <c r="H247" t="n">
         <v>9000</v>
@@ -7561,7 +7561,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>4.26168870925903</v>
+        <v>4.26168918609619</v>
       </c>
       <c r="H248" t="n">
         <v>29000</v>
@@ -7590,7 +7590,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G249" t="n">
-        <v>4.26168870925903</v>
+        <v>4.26168918609619</v>
       </c>
       <c r="H249" t="n">
         <v>15000</v>
@@ -7619,7 +7619,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G250" t="n">
-        <v>4.29720258712769</v>
+        <v>4.297203540802</v>
       </c>
       <c r="H250" t="n">
         <v>11000</v>
@@ -7677,7 +7677,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G252" t="n">
-        <v>4.02196836471558</v>
+        <v>4.02196884155273</v>
       </c>
       <c r="H252" t="n">
         <v>35000</v>
@@ -7706,7 +7706,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G253" t="n">
-        <v>3.86215567588806</v>
+        <v>3.8621551990509</v>
       </c>
       <c r="H253" t="n">
         <v>21000</v>
@@ -7735,7 +7735,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G254" t="n">
-        <v>3.88879132270813</v>
+        <v>3.88879084587097</v>
       </c>
       <c r="H254" t="n">
         <v>21000</v>
@@ -7764,7 +7764,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G255" t="n">
-        <v>3.96425867080688</v>
+        <v>3.96425914764404</v>
       </c>
       <c r="H255" t="n">
         <v>2000</v>
@@ -7793,7 +7793,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>4.06636142730713</v>
+        <v>4.06636095046997</v>
       </c>
       <c r="H256" t="n">
         <v>12000</v>
@@ -7851,7 +7851,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>4.19953966140747</v>
+        <v>4.19953918457031</v>
       </c>
       <c r="H258" t="n">
         <v>30000</v>
@@ -7880,7 +7880,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>4.15070724487305</v>
+        <v>4.15070772171021</v>
       </c>
       <c r="H259" t="n">
         <v>48000</v>
@@ -7938,7 +7938,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G261" t="n">
-        <v>4.09299755096436</v>
+        <v>4.0929970741272</v>
       </c>
       <c r="H261" t="n">
         <v>28000</v>
@@ -8025,7 +8025,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G264" t="n">
-        <v>4.05748271942139</v>
+        <v>4.05748319625854</v>
       </c>
       <c r="H264" t="n">
         <v>17000</v>
@@ -8112,7 +8112,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>4.08411836624146</v>
+        <v>4.0841178894043</v>
       </c>
       <c r="H267" t="n">
         <v>3000</v>
@@ -8141,7 +8141,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G268" t="n">
-        <v>4.05748271942139</v>
+        <v>4.05748319625854</v>
       </c>
       <c r="H268" t="n">
         <v>4000</v>
@@ -8170,7 +8170,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G269" t="n">
-        <v>3.94206237792969</v>
+        <v>3.94206190109253</v>
       </c>
       <c r="H269" t="n">
         <v>21000</v>
@@ -8228,7 +8228,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G271" t="n">
-        <v>3.95094013214111</v>
+        <v>3.95094037055969</v>
       </c>
       <c r="H271" t="n">
         <v>7000</v>
@@ -8257,7 +8257,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>3.95981931686401</v>
+        <v>3.95981907844543</v>
       </c>
       <c r="H272" t="n">
         <v>11000</v>
@@ -8286,7 +8286,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>3.99089360237122</v>
+        <v>3.99089384078979</v>
       </c>
       <c r="H273" t="n">
         <v>16000</v>
@@ -8315,7 +8315,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G274" t="n">
-        <v>3.95537996292114</v>
+        <v>3.95537972450256</v>
       </c>
       <c r="H274" t="n">
         <v>2000</v>
@@ -8344,7 +8344,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G275" t="n">
-        <v>3.89766907691956</v>
+        <v>3.89766955375671</v>
       </c>
       <c r="H275" t="n">
         <v>17000</v>
@@ -8373,7 +8373,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G276" t="n">
-        <v>3.844398021698</v>
+        <v>3.84439826011658</v>
       </c>
       <c r="H276" t="n">
         <v>17000</v>
@@ -8460,7 +8460,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G279" t="n">
-        <v>3.81776332855225</v>
+        <v>3.81776261329651</v>
       </c>
       <c r="H279" t="n">
         <v>3000</v>
@@ -8489,7 +8489,7 @@
         <v>4.25</v>
       </c>
       <c r="G280" t="n">
-        <v>3.77337026596069</v>
+        <v>3.77337002754211</v>
       </c>
       <c r="H280" t="n">
         <v>5000</v>
@@ -8518,7 +8518,7 @@
         <v>4.25</v>
       </c>
       <c r="G281" t="n">
-        <v>3.77337026596069</v>
+        <v>3.77337002754211</v>
       </c>
       <c r="H281" t="n">
         <v>4000</v>
@@ -8547,7 +8547,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>3.81332349777222</v>
+        <v>3.8133237361908</v>
       </c>
       <c r="H282" t="n">
         <v>8000</v>
@@ -8576,7 +8576,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G283" t="n">
-        <v>3.81776332855225</v>
+        <v>3.81776261329651</v>
       </c>
       <c r="H283" t="n">
         <v>2000</v>
@@ -8605,7 +8605,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G284" t="n">
-        <v>3.80444526672363</v>
+        <v>3.80444502830505</v>
       </c>
       <c r="H284" t="n">
         <v>10000</v>
@@ -8634,7 +8634,7 @@
         <v>4.25</v>
       </c>
       <c r="G285" t="n">
-        <v>3.77337026596069</v>
+        <v>3.77337002754211</v>
       </c>
       <c r="H285" t="n">
         <v>8000</v>
@@ -8721,7 +8721,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G288" t="n">
-        <v>3.7467348575592</v>
+        <v>3.74673438072205</v>
       </c>
       <c r="H288" t="n">
         <v>1000</v>
@@ -8750,7 +8750,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G289" t="n">
-        <v>3.7467348575592</v>
+        <v>3.74673438072205</v>
       </c>
       <c r="H289" t="n">
         <v>2000</v>
@@ -8779,7 +8779,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G290" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692169189453</v>
       </c>
       <c r="H290" t="n">
         <v>3000</v>
@@ -8837,7 +8837,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G292" t="n">
-        <v>3.8088846206665</v>
+        <v>3.80888438224792</v>
       </c>
       <c r="H292" t="n">
         <v>14000</v>
@@ -8895,7 +8895,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G294" t="n">
-        <v>3.81776332855225</v>
+        <v>3.81776261329651</v>
       </c>
       <c r="H294" t="n">
         <v>6000</v>
@@ -8924,7 +8924,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>3.69790267944336</v>
+        <v>3.69790291786194</v>
       </c>
       <c r="H295" t="n">
         <v>13000</v>
@@ -8982,7 +8982,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G297" t="n">
-        <v>3.72453880310059</v>
+        <v>3.72453856468201</v>
       </c>
       <c r="H297" t="n">
         <v>3000</v>
@@ -9040,7 +9040,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692169189453</v>
       </c>
       <c r="H299" t="n">
         <v>25000</v>
@@ -9098,7 +9098,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G301" t="n">
-        <v>3.50701475143433</v>
+        <v>3.50701451301575</v>
       </c>
       <c r="H301" t="n">
         <v>10000</v>
@@ -9127,7 +9127,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G302" t="n">
-        <v>3.59580039978027</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H302" t="n">
         <v>6000</v>
@@ -9156,7 +9156,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G303" t="n">
-        <v>3.63131403923035</v>
+        <v>3.63131427764893</v>
       </c>
       <c r="H303" t="n">
         <v>5000</v>
@@ -9243,7 +9243,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G306" t="n">
-        <v>3.57804298400879</v>
+        <v>3.57804322242737</v>
       </c>
       <c r="H306" t="n">
         <v>6000</v>
@@ -9272,7 +9272,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G307" t="n">
-        <v>3.62243580818176</v>
+        <v>3.62243556976318</v>
       </c>
       <c r="H307" t="n">
         <v>16000</v>
@@ -9330,7 +9330,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692169189453</v>
       </c>
       <c r="H309" t="n">
         <v>2000</v>
@@ -9359,7 +9359,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>3.5736038684845</v>
+        <v>3.57360363006592</v>
       </c>
       <c r="H310" t="n">
         <v>10000</v>
@@ -9388,7 +9388,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G311" t="n">
-        <v>3.50257515907288</v>
+        <v>3.50257539749146</v>
       </c>
       <c r="H311" t="n">
         <v>3000</v>
@@ -9417,7 +9417,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G312" t="n">
-        <v>3.46262240409851</v>
+        <v>3.46262192726135</v>
       </c>
       <c r="H312" t="n">
         <v>4000</v>
@@ -9446,7 +9446,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>3.41822957992554</v>
+        <v>3.41822934150696</v>
       </c>
       <c r="H313" t="n">
         <v>2000</v>
@@ -9475,7 +9475,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G314" t="n">
-        <v>3.41822957992554</v>
+        <v>3.41822934150696</v>
       </c>
       <c r="H314" t="n">
         <v>1000</v>
@@ -9562,7 +9562,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G317" t="n">
-        <v>3.23178052902222</v>
+        <v>3.2317807674408</v>
       </c>
       <c r="H317" t="n">
         <v>10000</v>
@@ -9649,7 +9649,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G320" t="n">
-        <v>3.16075229644775</v>
+        <v>3.16075253486633</v>
       </c>
       <c r="H320" t="n">
         <v>3000</v>
@@ -9678,7 +9678,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G321" t="n">
-        <v>3.09860277175903</v>
+        <v>3.09860301017761</v>
       </c>
       <c r="H321" t="n">
         <v>6000</v>
@@ -9707,7 +9707,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G322" t="n">
-        <v>3.1651918888092</v>
+        <v>3.16519212722778</v>
       </c>
       <c r="H322" t="n">
         <v>4000</v>
@@ -9736,7 +9736,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>3.24065923690796</v>
+        <v>3.24065899848938</v>
       </c>
       <c r="H323" t="n">
         <v>3000</v>
@@ -9765,7 +9765,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G324" t="n">
-        <v>3.23178052902222</v>
+        <v>3.2317807674408</v>
       </c>
       <c r="H324" t="n">
         <v>4000</v>
@@ -9823,7 +9823,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G326" t="n">
-        <v>3.16075229644775</v>
+        <v>3.16075253486633</v>
       </c>
       <c r="H326" t="n">
         <v>7000</v>
@@ -9881,7 +9881,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G328" t="n">
-        <v>3.29393029212952</v>
+        <v>3.29393005371094</v>
       </c>
       <c r="H328" t="n">
         <v>17000</v>
@@ -9968,7 +9968,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G331" t="n">
-        <v>3.4271080493927</v>
+        <v>3.42710781097412</v>
       </c>
       <c r="H331" t="n">
         <v>21000</v>
@@ -9997,7 +9997,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G332" t="n">
-        <v>3.50701475143433</v>
+        <v>3.50701451301575</v>
       </c>
       <c r="H332" t="n">
         <v>20000</v>
@@ -10055,7 +10055,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>3.46262240409851</v>
+        <v>3.46262192726135</v>
       </c>
       <c r="H334" t="n">
         <v>5000</v>
@@ -10084,7 +10084,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>3.46262240409851</v>
+        <v>3.46262192726135</v>
       </c>
       <c r="H335" t="n">
         <v>11000</v>
@@ -10113,7 +10113,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>3.38271570205688</v>
+        <v>3.38271522521973</v>
       </c>
       <c r="H336" t="n">
         <v>4000</v>
@@ -10142,7 +10142,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>3.43598651885986</v>
+        <v>3.43598628044128</v>
       </c>
       <c r="H337" t="n">
         <v>6000</v>
@@ -10171,7 +10171,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G338" t="n">
-        <v>3.37827610969543</v>
+        <v>3.37827634811401</v>
       </c>
       <c r="H338" t="n">
         <v>5000</v>
@@ -10229,7 +10229,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G340" t="n">
-        <v>3.81332349777222</v>
+        <v>3.8133237361908</v>
       </c>
       <c r="H340" t="n">
         <v>152000</v>
@@ -10287,7 +10287,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G342" t="n">
-        <v>3.64907097816467</v>
+        <v>3.64907121658325</v>
       </c>
       <c r="H342" t="n">
         <v>9000</v>
@@ -10316,7 +10316,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G343" t="n">
-        <v>3.58248209953308</v>
+        <v>3.5824818611145</v>
       </c>
       <c r="H343" t="n">
         <v>7000</v>
@@ -10345,7 +10345,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G344" t="n">
-        <v>3.57804298400879</v>
+        <v>3.57804322242737</v>
       </c>
       <c r="H344" t="n">
         <v>8000</v>
@@ -10374,7 +10374,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>3.59580039978027</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H345" t="n">
         <v>7000</v>
@@ -10432,7 +10432,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G347" t="n">
-        <v>3.81776332855225</v>
+        <v>3.81776261329651</v>
       </c>
       <c r="H347" t="n">
         <v>29000</v>
@@ -10461,7 +10461,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G348" t="n">
-        <v>3.7467348575592</v>
+        <v>3.74673438072205</v>
       </c>
       <c r="H348" t="n">
         <v>35000</v>
@@ -10490,7 +10490,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G349" t="n">
-        <v>3.76893043518066</v>
+        <v>3.76893091201782</v>
       </c>
       <c r="H349" t="n">
         <v>2000</v>
@@ -10519,7 +10519,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G350" t="n">
-        <v>3.76893043518066</v>
+        <v>3.76893091201782</v>
       </c>
       <c r="H350" t="n">
         <v>8000</v>
@@ -10548,7 +10548,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G351" t="n">
-        <v>3.95094013214111</v>
+        <v>3.95094037055969</v>
       </c>
       <c r="H351" t="n">
         <v>52000</v>
@@ -10606,7 +10606,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G353" t="n">
-        <v>3.94650220870972</v>
+        <v>3.94650173187256</v>
       </c>
       <c r="H353" t="n">
         <v>36000</v>
@@ -10635,7 +10635,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>4.03084754943848</v>
+        <v>4.03084707260132</v>
       </c>
       <c r="H354" t="n">
         <v>28000</v>
@@ -10693,7 +10693,7 @@
         <v>4.5</v>
       </c>
       <c r="G356" t="n">
-        <v>3.99533343315125</v>
+        <v>3.99533295631409</v>
       </c>
       <c r="H356" t="n">
         <v>22000</v>
@@ -10751,7 +10751,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G358" t="n">
-        <v>3.9997730255127</v>
+        <v>3.99977278709412</v>
       </c>
       <c r="H358" t="n">
         <v>13000</v>
@@ -10780,7 +10780,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G359" t="n">
-        <v>3.90210890769958</v>
+        <v>3.90210866928101</v>
       </c>
       <c r="H359" t="n">
         <v>11000</v>
@@ -10838,7 +10838,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>3.96425867080688</v>
+        <v>3.96425914764404</v>
       </c>
       <c r="H361" t="n">
         <v>20000</v>
@@ -10867,7 +10867,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>3.92874455451965</v>
+        <v>3.92874479293823</v>
       </c>
       <c r="H362" t="n">
         <v>34000</v>
@@ -10896,7 +10896,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>3.98201560974121</v>
+        <v>3.98201584815979</v>
       </c>
       <c r="H363" t="n">
         <v>37000</v>
@@ -10983,7 +10983,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G366" t="n">
-        <v>3.9997730255127</v>
+        <v>3.99977278709412</v>
       </c>
       <c r="H366" t="n">
         <v>31000</v>
@@ -11012,7 +11012,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>3.96425867080688</v>
+        <v>3.96425914764404</v>
       </c>
       <c r="H367" t="n">
         <v>13000</v>
@@ -11041,7 +11041,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G368" t="n">
-        <v>3.9997730255127</v>
+        <v>3.99977278709412</v>
       </c>
       <c r="H368" t="n">
         <v>61000</v>
@@ -11099,7 +11099,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>3.85327672958374</v>
+        <v>3.85327696800232</v>
       </c>
       <c r="H370" t="n">
         <v>50000</v>
@@ -11128,7 +11128,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G371" t="n">
-        <v>3.76449179649353</v>
+        <v>3.76449155807495</v>
       </c>
       <c r="H371" t="n">
         <v>26000</v>
@@ -11157,7 +11157,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G372" t="n">
-        <v>3.73341679573059</v>
+        <v>3.73341703414917</v>
       </c>
       <c r="H372" t="n">
         <v>16000</v>
@@ -11215,7 +11215,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G374" t="n">
-        <v>3.76449179649353</v>
+        <v>3.76449155807495</v>
       </c>
       <c r="H374" t="n">
         <v>7000</v>
@@ -11273,7 +11273,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G376" t="n">
-        <v>3.76449179649353</v>
+        <v>3.76449155807495</v>
       </c>
       <c r="H376" t="n">
         <v>12000</v>
@@ -11331,7 +11331,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G378" t="n">
-        <v>3.63131403923035</v>
+        <v>3.63131427764893</v>
       </c>
       <c r="H378" t="n">
         <v>15000</v>
@@ -11563,7 +11563,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G386" t="n">
-        <v>3.63131403923035</v>
+        <v>3.63131427764893</v>
       </c>
       <c r="H386" t="n">
         <v>13000</v>
@@ -11592,7 +11592,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G387" t="n">
-        <v>3.63131403923035</v>
+        <v>3.63131427764893</v>
       </c>
       <c r="H387" t="n">
         <v>18000</v>
@@ -11621,7 +11621,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>3.59580039978027</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H388" t="n">
         <v>31000</v>
@@ -11650,7 +11650,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G389" t="n">
-        <v>3.64907097816467</v>
+        <v>3.64907121658325</v>
       </c>
       <c r="H389" t="n">
         <v>25000</v>
@@ -11708,7 +11708,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G391" t="n">
-        <v>3.90210890769958</v>
+        <v>3.90210866928101</v>
       </c>
       <c r="H391" t="n">
         <v>56000</v>
@@ -11766,7 +11766,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G393" t="n">
-        <v>3.62243580818176</v>
+        <v>3.62243556976318</v>
       </c>
       <c r="H393" t="n">
         <v>30000</v>
@@ -11824,7 +11824,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G395" t="n">
-        <v>3.59580039978027</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H395" t="n">
         <v>9000</v>
@@ -11853,7 +11853,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G396" t="n">
-        <v>3.56916427612305</v>
+        <v>3.56916451454163</v>
       </c>
       <c r="H396" t="n">
         <v>9000</v>
@@ -11882,7 +11882,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G397" t="n">
-        <v>3.61355710029602</v>
+        <v>3.6135573387146</v>
       </c>
       <c r="H397" t="n">
         <v>22000</v>
@@ -11969,7 +11969,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G400" t="n">
-        <v>3.58248209953308</v>
+        <v>3.5824818611145</v>
       </c>
       <c r="H400" t="n">
         <v>10000</v>
@@ -11998,7 +11998,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G401" t="n">
-        <v>3.57804298400879</v>
+        <v>3.57804322242737</v>
       </c>
       <c r="H401" t="n">
         <v>18000</v>
@@ -12027,7 +12027,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>3.5736038684845</v>
+        <v>3.57360363006592</v>
       </c>
       <c r="H402" t="n">
         <v>9000</v>
@@ -12056,7 +12056,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G403" t="n">
-        <v>3.56472492218018</v>
+        <v>3.56472516059875</v>
       </c>
       <c r="H403" t="n">
         <v>20000</v>
@@ -12143,7 +12143,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692169189453</v>
       </c>
       <c r="H406" t="n">
         <v>10000</v>
@@ -12172,7 +12172,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G407" t="n">
-        <v>3.59580039978027</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H407" t="n">
         <v>15000</v>
@@ -12288,7 +12288,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G411" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692169189453</v>
       </c>
       <c r="H411" t="n">
         <v>6000</v>
@@ -12317,7 +12317,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G412" t="n">
-        <v>3.58692145347595</v>
+        <v>3.58692169189453</v>
       </c>
       <c r="H412" t="n">
         <v>10000</v>
@@ -12462,7 +12462,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G417" t="n">
-        <v>3.64552783966064</v>
+        <v>3.64552760124207</v>
       </c>
       <c r="H417" t="n">
         <v>9000</v>
@@ -12665,7 +12665,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G424" t="n">
-        <v>3.72289824485779</v>
+        <v>3.72289848327637</v>
       </c>
       <c r="H424" t="n">
         <v>6000</v>
@@ -12723,7 +12723,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G426" t="n">
-        <v>3.7593080997467</v>
+        <v>3.75930833816528</v>
       </c>
       <c r="H426" t="n">
         <v>5000</v>
@@ -12781,7 +12781,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G428" t="n">
-        <v>3.72289824485779</v>
+        <v>3.72289848327637</v>
       </c>
       <c r="H428" t="n">
         <v>8000</v>
@@ -12810,7 +12810,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G429" t="n">
-        <v>3.72289824485779</v>
+        <v>3.72289848327637</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G433" t="n">
-        <v>3.70469355583191</v>
+        <v>3.70469379425049</v>
       </c>
       <c r="H433" t="n">
         <v>5000</v>
@@ -13042,7 +13042,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G437" t="n">
-        <v>3.7593080997467</v>
+        <v>3.75930833816528</v>
       </c>
       <c r="H437" t="n">
         <v>23000</v>
@@ -13100,7 +13100,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G439" t="n">
-        <v>3.70469355583191</v>
+        <v>3.70469379425049</v>
       </c>
       <c r="H439" t="n">
         <v>20000</v>
@@ -13216,7 +13216,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G443" t="n">
-        <v>3.77751302719116</v>
+        <v>3.77751326560974</v>
       </c>
       <c r="H443" t="n">
         <v>17000</v>
@@ -13303,7 +13303,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G446" t="n">
-        <v>3.72289824485779</v>
+        <v>3.72289848327637</v>
       </c>
       <c r="H446" t="n">
         <v>14000</v>
@@ -13361,7 +13361,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G448" t="n">
-        <v>3.80482006072998</v>
+        <v>3.80482029914856</v>
       </c>
       <c r="H448" t="n">
         <v>12000</v>
@@ -13390,7 +13390,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G449" t="n">
-        <v>3.7593080997467</v>
+        <v>3.75930833816528</v>
       </c>
       <c r="H449" t="n">
         <v>17000</v>
@@ -13448,7 +13448,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>3.77751302719116</v>
+        <v>3.77751326560974</v>
       </c>
       <c r="H451" t="n">
         <v>7000</v>
@@ -13535,7 +13535,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G454" t="n">
-        <v>3.70469355583191</v>
+        <v>3.70469379425049</v>
       </c>
       <c r="H454" t="n">
         <v>25000</v>
@@ -13593,7 +13593,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G456" t="n">
-        <v>3.68648862838745</v>
+        <v>3.68648886680603</v>
       </c>
       <c r="H456" t="n">
         <v>10000</v>
@@ -13651,7 +13651,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>3.68648862838745</v>
+        <v>3.68648886680603</v>
       </c>
       <c r="H458" t="n">
         <v>15000</v>
@@ -13680,7 +13680,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G459" t="n">
-        <v>3.67738604545593</v>
+        <v>3.67738628387451</v>
       </c>
       <c r="H459" t="n">
         <v>6000</v>
@@ -13854,7 +13854,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G465" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H465" t="n">
         <v>17000</v>
@@ -13883,7 +13883,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G466" t="n">
-        <v>3.42251801490784</v>
+        <v>3.42251753807068</v>
       </c>
       <c r="H466" t="n">
         <v>3000</v>
@@ -14028,7 +14028,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G471" t="n">
-        <v>3.42251801490784</v>
+        <v>3.42251753807068</v>
       </c>
       <c r="H471" t="n">
         <v>13000</v>
@@ -14086,7 +14086,7 @@
         <v>3.75</v>
       </c>
       <c r="G473" t="n">
-        <v>3.41341543197632</v>
+        <v>3.41341519355774</v>
       </c>
       <c r="H473" t="n">
         <v>7000</v>
@@ -14173,7 +14173,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G476" t="n">
-        <v>3.44072270393372</v>
+        <v>3.44072246551514</v>
       </c>
       <c r="H476" t="n">
         <v>8000</v>
@@ -14202,7 +14202,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>3.43162035942078</v>
+        <v>3.4316201210022</v>
       </c>
       <c r="H477" t="n">
         <v>2000</v>
@@ -14231,7 +14231,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>3.43162035942078</v>
+        <v>3.4316201210022</v>
       </c>
       <c r="H478" t="n">
         <v>2000</v>
@@ -14347,7 +14347,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G482" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H482" t="n">
         <v>10000</v>
@@ -14376,7 +14376,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G483" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H483" t="n">
         <v>2000</v>
@@ -14405,7 +14405,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G484" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H484" t="n">
         <v>0</v>
@@ -14434,7 +14434,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G485" t="n">
-        <v>3.48623490333557</v>
+        <v>3.48623466491699</v>
       </c>
       <c r="H485" t="n">
         <v>9000</v>
@@ -14463,7 +14463,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H486" t="n">
         <v>11000</v>
@@ -14492,7 +14492,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G487" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H487" t="n">
         <v>0</v>
@@ -14521,7 +14521,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G488" t="n">
-        <v>3.38610816001892</v>
+        <v>3.38610792160034</v>
       </c>
       <c r="H488" t="n">
         <v>25000</v>
@@ -14608,7 +14608,7 @@
         <v>3.75</v>
       </c>
       <c r="G491" t="n">
-        <v>3.41341543197632</v>
+        <v>3.41341519355774</v>
       </c>
       <c r="H491" t="n">
         <v>30000</v>
@@ -14637,7 +14637,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>3.39521050453186</v>
+        <v>3.39521026611328</v>
       </c>
       <c r="H492" t="n">
         <v>13000</v>
@@ -14695,7 +14695,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G494" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H494" t="n">
         <v>37000</v>
@@ -14724,7 +14724,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G495" t="n">
-        <v>3.56815695762634</v>
+        <v>3.56815671920776</v>
       </c>
       <c r="H495" t="n">
         <v>69000</v>
@@ -14753,7 +14753,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G496" t="n">
-        <v>3.52264475822449</v>
+        <v>3.52264428138733</v>
       </c>
       <c r="H496" t="n">
         <v>12000</v>
@@ -14811,7 +14811,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G498" t="n">
-        <v>3.52264475822449</v>
+        <v>3.52264428138733</v>
       </c>
       <c r="H498" t="n">
         <v>5000</v>
@@ -14840,7 +14840,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G499" t="n">
-        <v>3.43162035942078</v>
+        <v>3.4316201210022</v>
       </c>
       <c r="H499" t="n">
         <v>25000</v>
@@ -14869,7 +14869,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>3.43162035942078</v>
+        <v>3.4316201210022</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -14898,7 +14898,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G501" t="n">
-        <v>3.53174734115601</v>
+        <v>3.53174710273743</v>
       </c>
       <c r="H501" t="n">
         <v>6000</v>
@@ -14927,7 +14927,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G502" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H502" t="n">
         <v>4000</v>
@@ -14956,7 +14956,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G503" t="n">
-        <v>3.53174734115601</v>
+        <v>3.53174710273743</v>
       </c>
       <c r="H503" t="n">
         <v>4000</v>
@@ -14985,7 +14985,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G504" t="n">
-        <v>3.44072270393372</v>
+        <v>3.44072246551514</v>
       </c>
       <c r="H504" t="n">
         <v>5000</v>
@@ -15014,7 +15014,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G505" t="n">
-        <v>3.49533724784851</v>
+        <v>3.49533700942993</v>
       </c>
       <c r="H505" t="n">
         <v>5000</v>
@@ -15043,7 +15043,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>3.44982528686523</v>
+        <v>3.44982481002808</v>
       </c>
       <c r="H506" t="n">
         <v>32000</v>
@@ -15072,7 +15072,7 @@
         <v>3.75</v>
       </c>
       <c r="G507" t="n">
-        <v>3.41341543197632</v>
+        <v>3.41341519355774</v>
       </c>
       <c r="H507" t="n">
         <v>26000</v>
@@ -15188,7 +15188,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G511" t="n">
-        <v>3.42251801490784</v>
+        <v>3.42251753807068</v>
       </c>
       <c r="H511" t="n">
         <v>3000</v>
@@ -15217,7 +15217,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G512" t="n">
-        <v>3.38610816001892</v>
+        <v>3.38610792160034</v>
       </c>
       <c r="H512" t="n">
         <v>7000</v>
@@ -15246,7 +15246,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G513" t="n">
-        <v>3.45892763137817</v>
+        <v>3.45892739295959</v>
       </c>
       <c r="H513" t="n">
         <v>17000</v>
@@ -15362,7 +15362,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G517" t="n">
-        <v>3.34969830513</v>
+        <v>3.34969806671143</v>
       </c>
       <c r="H517" t="n">
         <v>14000</v>
@@ -15420,7 +15420,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G519" t="n">
-        <v>3.31328868865967</v>
+        <v>3.31328845024109</v>
       </c>
       <c r="H519" t="n">
         <v>13000</v>
@@ -15449,7 +15449,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G520" t="n">
-        <v>3.31328868865967</v>
+        <v>3.31328845024109</v>
       </c>
       <c r="H520" t="n">
         <v>16000</v>
@@ -15478,7 +15478,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G521" t="n">
-        <v>3.28598093986511</v>
+        <v>3.28598117828369</v>
       </c>
       <c r="H521" t="n">
         <v>14000</v>
@@ -15536,7 +15536,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G523" t="n">
-        <v>3.25867366790771</v>
+        <v>3.25867390632629</v>
       </c>
       <c r="H523" t="n">
         <v>9000</v>
@@ -15594,7 +15594,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G525" t="n">
-        <v>3.31328868865967</v>
+        <v>3.31328845024109</v>
       </c>
       <c r="H525" t="n">
         <v>5000</v>
@@ -15710,7 +15710,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G529" t="n">
-        <v>3.31328868865967</v>
+        <v>3.31328845024109</v>
       </c>
       <c r="H529" t="n">
         <v>14000</v>
@@ -15739,7 +15739,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G530" t="n">
-        <v>3.28598093986511</v>
+        <v>3.28598117828369</v>
       </c>
       <c r="H530" t="n">
         <v>17000</v>
@@ -15768,7 +15768,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G531" t="n">
-        <v>3.28598093986511</v>
+        <v>3.28598117828369</v>
       </c>
       <c r="H531" t="n">
         <v>19000</v>
@@ -15826,7 +15826,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G533" t="n">
-        <v>3.32239103317261</v>
+        <v>3.32239079475403</v>
       </c>
       <c r="H533" t="n">
         <v>4000</v>
@@ -15855,7 +15855,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G534" t="n">
-        <v>3.28598093986511</v>
+        <v>3.28598117828369</v>
       </c>
       <c r="H534" t="n">
         <v>4000</v>
@@ -16000,7 +16000,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G539" t="n">
-        <v>3.1949565410614</v>
+        <v>3.19495677947998</v>
       </c>
       <c r="H539" t="n">
         <v>7000</v>
@@ -16058,7 +16058,7 @@
         <v>3.5</v>
       </c>
       <c r="G541" t="n">
-        <v>3.18585419654846</v>
+        <v>3.18585443496704</v>
       </c>
       <c r="H541" t="n">
         <v>18000</v>
@@ -16087,7 +16087,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G542" t="n">
-        <v>3.1949565410614</v>
+        <v>3.19495677947998</v>
       </c>
       <c r="H542" t="n">
         <v>5000</v>
@@ -16261,7 +16261,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G548" t="n">
-        <v>3.1949565410614</v>
+        <v>3.19495677947998</v>
       </c>
       <c r="H548" t="n">
         <v>9000</v>
@@ -16464,7 +16464,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G555" t="n">
-        <v>3.15854692459106</v>
+        <v>3.15854716300964</v>
       </c>
       <c r="H555" t="n">
         <v>12000</v>
@@ -16493,7 +16493,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G556" t="n">
-        <v>3.09482979774475</v>
+        <v>3.09483003616333</v>
       </c>
       <c r="H556" t="n">
         <v>4000</v>
@@ -16754,7 +16754,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G565" t="n">
-        <v>2.66701507568359</v>
+        <v>2.66701531410217</v>
       </c>
       <c r="H565" t="n">
         <v>16000</v>
@@ -16812,7 +16812,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.67611742019653</v>
+        <v>2.67611765861511</v>
       </c>
       <c r="H567" t="n">
         <v>12000</v>
@@ -16957,7 +16957,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G572" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H572" t="n">
         <v>20000</v>
@@ -17102,7 +17102,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H577" t="n">
         <v>1000</v>
@@ -17189,7 +17189,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G580" t="n">
-        <v>2.57599091529846</v>
+        <v>2.57599067687988</v>
       </c>
       <c r="H580" t="n">
         <v>23000</v>
@@ -17218,7 +17218,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>2.57599091529846</v>
+        <v>2.57599067687988</v>
       </c>
       <c r="H581" t="n">
         <v>1000</v>
@@ -17276,7 +17276,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>2.57599091529846</v>
+        <v>2.57599067687988</v>
       </c>
       <c r="H583" t="n">
         <v>10000</v>
@@ -17305,7 +17305,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G584" t="n">
-        <v>2.53047847747803</v>
+        <v>2.53047871589661</v>
       </c>
       <c r="H584" t="n">
         <v>9000</v>
@@ -17363,7 +17363,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G586" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H586" t="n">
         <v>13000</v>
@@ -17537,7 +17537,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G592" t="n">
-        <v>2.45765900611877</v>
+        <v>2.45765924453735</v>
       </c>
       <c r="H592" t="n">
         <v>4000</v>
@@ -17566,7 +17566,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G593" t="n">
-        <v>2.52137613296509</v>
+        <v>2.52137637138367</v>
       </c>
       <c r="H593" t="n">
         <v>27000</v>
@@ -17595,7 +17595,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>2.57599091529846</v>
+        <v>2.57599067687988</v>
       </c>
       <c r="H594" t="n">
         <v>6000</v>
@@ -17624,7 +17624,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>2.57599091529846</v>
+        <v>2.57599067687988</v>
       </c>
       <c r="H595" t="n">
         <v>4000</v>
@@ -17653,7 +17653,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>2.57599091529846</v>
+        <v>2.57599067687988</v>
       </c>
       <c r="H596" t="n">
         <v>1000</v>
@@ -17856,7 +17856,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.35753202438354</v>
+        <v>2.35753226280212</v>
       </c>
       <c r="H603" t="n">
         <v>4000</v>
@@ -17885,7 +17885,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G604" t="n">
-        <v>2.35753202438354</v>
+        <v>2.35753226280212</v>
       </c>
       <c r="H604" t="n">
         <v>8000</v>
@@ -17972,7 +17972,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G607" t="n">
-        <v>2.33022475242615</v>
+        <v>2.33022499084473</v>
       </c>
       <c r="H607" t="n">
         <v>3000</v>
@@ -18001,7 +18001,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G608" t="n">
-        <v>2.33022475242615</v>
+        <v>2.33022499084473</v>
       </c>
       <c r="H608" t="n">
         <v>2000</v>
@@ -18030,7 +18030,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G609" t="n">
-        <v>2.24830269813538</v>
+        <v>2.24830293655396</v>
       </c>
       <c r="H609" t="n">
         <v>6000</v>
@@ -18059,7 +18059,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G610" t="n">
-        <v>2.32112216949463</v>
+        <v>2.32112240791321</v>
       </c>
       <c r="H610" t="n">
         <v>21000</v>
@@ -18146,7 +18146,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G613" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H613" t="n">
         <v>9000</v>
@@ -18204,7 +18204,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G615" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H615" t="n">
         <v>6000</v>
@@ -18233,7 +18233,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G616" t="n">
-        <v>2.52137613296509</v>
+        <v>2.52137637138367</v>
       </c>
       <c r="H616" t="n">
         <v>1000</v>
@@ -18262,7 +18262,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G617" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H617" t="n">
         <v>5000</v>
@@ -18291,7 +18291,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G618" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18465,7 +18465,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>2.34842967987061</v>
+        <v>2.34842991828918</v>
       </c>
       <c r="H624" t="n">
         <v>4000</v>
@@ -18494,7 +18494,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G625" t="n">
-        <v>2.34842967987061</v>
+        <v>2.34842991828918</v>
       </c>
       <c r="H625" t="n">
         <v>0</v>
@@ -18523,7 +18523,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G626" t="n">
-        <v>2.34842967987061</v>
+        <v>2.34842991828918</v>
       </c>
       <c r="H626" t="n">
         <v>1000</v>
@@ -18639,7 +18639,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G630" t="n">
-        <v>2.45765900611877</v>
+        <v>2.45765924453735</v>
       </c>
       <c r="H630" t="n">
         <v>8000</v>
@@ -18668,7 +18668,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G631" t="n">
-        <v>2.44855666160583</v>
+        <v>2.44855690002441</v>
       </c>
       <c r="H631" t="n">
         <v>6000</v>
@@ -18784,7 +18784,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G635" t="n">
-        <v>2.44855666160583</v>
+        <v>2.44855690002441</v>
       </c>
       <c r="H635" t="n">
         <v>2000</v>
@@ -18813,7 +18813,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G636" t="n">
-        <v>2.44855666160583</v>
+        <v>2.44855690002441</v>
       </c>
       <c r="H636" t="n">
         <v>0</v>
@@ -18842,7 +18842,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G637" t="n">
-        <v>2.32112216949463</v>
+        <v>2.32112240791321</v>
       </c>
       <c r="H637" t="n">
         <v>35000</v>
@@ -18871,7 +18871,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G638" t="n">
-        <v>2.25740528106689</v>
+        <v>2.25740551948547</v>
       </c>
       <c r="H638" t="n">
         <v>20000</v>
@@ -18900,7 +18900,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G639" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H639" t="n">
         <v>27000</v>
@@ -18929,7 +18929,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G640" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H640" t="n">
         <v>5000</v>
@@ -19016,7 +19016,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>2.08445906639099</v>
+        <v>2.08445882797241</v>
       </c>
       <c r="H643" t="n">
         <v>51000</v>
@@ -19045,7 +19045,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G644" t="n">
-        <v>2.05715179443359</v>
+        <v>2.05715155601501</v>
       </c>
       <c r="H644" t="n">
         <v>11000</v>
@@ -19103,7 +19103,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>2.08445906639099</v>
+        <v>2.08445882797241</v>
       </c>
       <c r="H646" t="n">
         <v>20000</v>
@@ -19132,7 +19132,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H647" t="n">
         <v>33000</v>
@@ -19161,7 +19161,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G648" t="n">
-        <v>2.16638112068176</v>
+        <v>2.16638088226318</v>
       </c>
       <c r="H648" t="n">
         <v>7000</v>
@@ -19190,7 +19190,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G649" t="n">
-        <v>2.07535648345947</v>
+        <v>2.07535624504089</v>
       </c>
       <c r="H649" t="n">
         <v>31000</v>
@@ -19219,7 +19219,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G650" t="n">
-        <v>2.09356141090393</v>
+        <v>2.09356117248535</v>
       </c>
       <c r="H650" t="n">
         <v>14000</v>
@@ -19248,7 +19248,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>2.08445906639099</v>
+        <v>2.08445882797241</v>
       </c>
       <c r="H651" t="n">
         <v>14000</v>
@@ -19335,7 +19335,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G654" t="n">
-        <v>2.12086868286133</v>
+        <v>2.12086844444275</v>
       </c>
       <c r="H654" t="n">
         <v>10000</v>
@@ -19393,7 +19393,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.46676135063171</v>
+        <v>2.46676158905029</v>
       </c>
       <c r="H656" t="n">
         <v>160000</v>
@@ -19422,7 +19422,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G657" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H657" t="n">
         <v>114000</v>
@@ -19509,7 +19509,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>2.2027907371521</v>
+        <v>2.20279097557068</v>
       </c>
       <c r="H660" t="n">
         <v>51000</v>
@@ -19625,7 +19625,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G664" t="n">
-        <v>2.25740528106689</v>
+        <v>2.25740551948547</v>
       </c>
       <c r="H664" t="n">
         <v>29000</v>
@@ -19712,7 +19712,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G667" t="n">
-        <v>2.21189308166504</v>
+        <v>2.21189332008362</v>
       </c>
       <c r="H667" t="n">
         <v>9000</v>
@@ -19741,7 +19741,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G668" t="n">
-        <v>2.21189308166504</v>
+        <v>2.21189332008362</v>
       </c>
       <c r="H668" t="n">
         <v>0</v>
@@ -19770,7 +19770,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G669" t="n">
-        <v>2.16638112068176</v>
+        <v>2.16638088226318</v>
       </c>
       <c r="H669" t="n">
         <v>22000</v>
@@ -19799,7 +19799,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H670" t="n">
         <v>3000</v>
@@ -19828,7 +19828,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H671" t="n">
         <v>5000</v>
@@ -19944,7 +19944,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>2.08445906639099</v>
+        <v>2.08445882797241</v>
       </c>
       <c r="H675" t="n">
         <v>4000</v>
@@ -19973,7 +19973,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>2.12086868286133</v>
+        <v>2.12086844444275</v>
       </c>
       <c r="H676" t="n">
         <v>12000</v>
@@ -20002,7 +20002,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>2.08445906639099</v>
+        <v>2.08445882797241</v>
       </c>
       <c r="H677" t="n">
         <v>1000</v>
@@ -20031,7 +20031,7 @@
         <v>2.25</v>
       </c>
       <c r="G678" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H678" t="n">
         <v>3000</v>
@@ -20089,7 +20089,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G680" t="n">
-        <v>2.07535648345947</v>
+        <v>2.07535624504089</v>
       </c>
       <c r="H680" t="n">
         <v>2000</v>
@@ -20147,7 +20147,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G682" t="n">
-        <v>2.05715179443359</v>
+        <v>2.05715155601501</v>
       </c>
       <c r="H682" t="n">
         <v>5000</v>
@@ -20176,7 +20176,7 @@
         <v>2.25</v>
       </c>
       <c r="G683" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H683" t="n">
         <v>2000</v>
@@ -20205,7 +20205,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>2.12086868286133</v>
+        <v>2.12086844444275</v>
       </c>
       <c r="H684" t="n">
         <v>4000</v>
@@ -20234,7 +20234,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G685" t="n">
-        <v>2.05715179443359</v>
+        <v>2.05715155601501</v>
       </c>
       <c r="H685" t="n">
         <v>4000</v>
@@ -20321,7 +20321,7 @@
         <v>2.25</v>
       </c>
       <c r="G688" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H688" t="n">
         <v>4000</v>
@@ -20379,7 +20379,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G690" t="n">
-        <v>2.00253701210022</v>
+        <v>2.00253677368164</v>
       </c>
       <c r="H690" t="n">
         <v>2000</v>
@@ -20408,7 +20408,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G691" t="n">
-        <v>1.96612727642059</v>
+        <v>1.9661271572113</v>
       </c>
       <c r="H691" t="n">
         <v>5000</v>
@@ -20437,7 +20437,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G692" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H692" t="n">
         <v>6000</v>
@@ -20466,7 +20466,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G693" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -20495,7 +20495,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G694" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H694" t="n">
         <v>0</v>
@@ -20524,7 +20524,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G695" t="n">
-        <v>1.98433232307434</v>
+        <v>1.98433196544647</v>
       </c>
       <c r="H695" t="n">
         <v>1000</v>
@@ -20553,7 +20553,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G696" t="n">
-        <v>2.00253701210022</v>
+        <v>2.00253677368164</v>
       </c>
       <c r="H696" t="n">
         <v>2000</v>
@@ -20582,7 +20582,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G697" t="n">
-        <v>1.94792258739471</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H697" t="n">
         <v>1000</v>
@@ -20611,7 +20611,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G698" t="n">
-        <v>1.94792258739471</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H698" t="n">
         <v>2000</v>
@@ -20640,7 +20640,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G699" t="n">
-        <v>1.94792258739471</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H699" t="n">
         <v>1000</v>
@@ -20669,7 +20669,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G700" t="n">
-        <v>1.94792258739471</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H700" t="n">
         <v>0</v>
@@ -20698,7 +20698,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G701" t="n">
-        <v>1.94792258739471</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H701" t="n">
         <v>0</v>
@@ -20727,7 +20727,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G702" t="n">
-        <v>1.92971742153168</v>
+        <v>1.92971730232239</v>
       </c>
       <c r="H702" t="n">
         <v>4000</v>
@@ -20756,7 +20756,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G703" t="n">
-        <v>1.90241003036499</v>
+        <v>1.90241014957428</v>
       </c>
       <c r="H703" t="n">
         <v>2000</v>
@@ -20785,7 +20785,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G704" t="n">
-        <v>1.90241003036499</v>
+        <v>1.90241014957428</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -20872,7 +20872,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G707" t="n">
-        <v>1.674849152565</v>
+        <v>1.67484903335571</v>
       </c>
       <c r="H707" t="n">
         <v>25000</v>
@@ -20901,7 +20901,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>1.72491264343262</v>
+        <v>1.72491240501404</v>
       </c>
       <c r="H708" t="n">
         <v>4000</v>
@@ -20930,7 +20930,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G709" t="n">
-        <v>1.69760525226593</v>
+        <v>1.69760513305664</v>
       </c>
       <c r="H709" t="n">
         <v>7000</v>
@@ -20959,7 +20959,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G710" t="n">
-        <v>1.73856616020203</v>
+        <v>1.73856604099274</v>
       </c>
       <c r="H710" t="n">
         <v>5000</v>
@@ -20988,7 +20988,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G711" t="n">
-        <v>1.77497601509094</v>
+        <v>1.77497589588165</v>
       </c>
       <c r="H711" t="n">
         <v>8000</v>
@@ -21017,7 +21017,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G712" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H712" t="n">
         <v>1000</v>
@@ -21046,7 +21046,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G713" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H713" t="n">
         <v>0</v>
@@ -21075,7 +21075,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G714" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H714" t="n">
         <v>1000</v>
@@ -21133,7 +21133,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G716" t="n">
-        <v>1.73856616020203</v>
+        <v>1.73856604099274</v>
       </c>
       <c r="H716" t="n">
         <v>14000</v>
@@ -21162,7 +21162,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G717" t="n">
-        <v>1.76132237911224</v>
+        <v>1.76132214069366</v>
       </c>
       <c r="H717" t="n">
         <v>1000</v>
@@ -21191,7 +21191,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G718" t="n">
-        <v>1.73856616020203</v>
+        <v>1.73856604099274</v>
       </c>
       <c r="H718" t="n">
         <v>2000</v>
@@ -21220,7 +21220,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G719" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H719" t="n">
         <v>10000</v>
@@ -21249,7 +21249,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G720" t="n">
-        <v>1.71125900745392</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H720" t="n">
         <v>1000</v>
@@ -21278,7 +21278,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G721" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H721" t="n">
         <v>2000</v>
@@ -21307,7 +21307,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G722" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H722" t="n">
         <v>0</v>
@@ -21336,7 +21336,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G723" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H723" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G724" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H724" t="n">
         <v>0</v>
@@ -21394,7 +21394,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G725" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H725" t="n">
         <v>3000</v>
@@ -21423,7 +21423,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G726" t="n">
-        <v>1.71125900745392</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H726" t="n">
         <v>12000</v>
@@ -21452,7 +21452,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G727" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H727" t="n">
         <v>3000</v>
@@ -21481,7 +21481,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G728" t="n">
-        <v>1.72036135196686</v>
+        <v>1.72036123275757</v>
       </c>
       <c r="H728" t="n">
         <v>5000</v>
@@ -21510,7 +21510,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G729" t="n">
-        <v>1.69305408000946</v>
+        <v>1.69305396080017</v>
       </c>
       <c r="H729" t="n">
         <v>1000</v>
@@ -21539,7 +21539,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G730" t="n">
-        <v>1.65664434432983</v>
+        <v>1.65664422512054</v>
       </c>
       <c r="H730" t="n">
         <v>3000</v>
@@ -21800,7 +21800,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G739" t="n">
-        <v>1.765873670578</v>
+        <v>1.76587355136871</v>
       </c>
       <c r="H739" t="n">
         <v>23000</v>
@@ -21829,7 +21829,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G740" t="n">
-        <v>2.12086868286133</v>
+        <v>2.12086844444275</v>
       </c>
       <c r="H740" t="n">
         <v>43000</v>
@@ -21916,7 +21916,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G743" t="n">
-        <v>1.92061507701874</v>
+        <v>1.92061483860016</v>
       </c>
       <c r="H743" t="n">
         <v>18000</v>
@@ -21945,7 +21945,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G744" t="n">
-        <v>1.96612727642059</v>
+        <v>1.9661271572113</v>
       </c>
       <c r="H744" t="n">
         <v>12000</v>
@@ -21974,7 +21974,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G745" t="n">
-        <v>1.98433232307434</v>
+        <v>1.98433196544647</v>
       </c>
       <c r="H745" t="n">
         <v>45000</v>
@@ -22003,7 +22003,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G746" t="n">
-        <v>1.92971742153168</v>
+        <v>1.92971730232239</v>
       </c>
       <c r="H746" t="n">
         <v>10000</v>
@@ -22032,7 +22032,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G747" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H747" t="n">
         <v>12000</v>
@@ -22061,7 +22061,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G748" t="n">
-        <v>1.97522974014282</v>
+        <v>1.97522962093353</v>
       </c>
       <c r="H748" t="n">
         <v>9000</v>
@@ -22090,7 +22090,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G749" t="n">
-        <v>1.92061507701874</v>
+        <v>1.92061483860016</v>
       </c>
       <c r="H749" t="n">
         <v>13000</v>
@@ -22148,7 +22148,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G751" t="n">
-        <v>1.92061507701874</v>
+        <v>1.92061483860016</v>
       </c>
       <c r="H751" t="n">
         <v>11000</v>
@@ -22264,7 +22264,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G755" t="n">
-        <v>1.90241003036499</v>
+        <v>1.90241014957428</v>
       </c>
       <c r="H755" t="n">
         <v>3000</v>
@@ -22293,7 +22293,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G756" t="n">
-        <v>1.92971742153168</v>
+        <v>1.92971730232239</v>
       </c>
       <c r="H756" t="n">
         <v>1000</v>
@@ -22322,7 +22322,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G757" t="n">
-        <v>1.90241003036499</v>
+        <v>1.90241014957428</v>
       </c>
       <c r="H757" t="n">
         <v>3000</v>
@@ -22351,7 +22351,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G758" t="n">
-        <v>1.92971742153168</v>
+        <v>1.92971730232239</v>
       </c>
       <c r="H758" t="n">
         <v>2000</v>
@@ -22380,7 +22380,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G759" t="n">
-        <v>1.94792258739471</v>
+        <v>1.94792234897614</v>
       </c>
       <c r="H759" t="n">
         <v>2000</v>
@@ -22467,7 +22467,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G762" t="n">
-        <v>2.24830269813538</v>
+        <v>2.24830293655396</v>
       </c>
       <c r="H762" t="n">
         <v>21000</v>
@@ -22583,7 +22583,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G766" t="n">
-        <v>2.09356141090393</v>
+        <v>2.09356117248535</v>
       </c>
       <c r="H766" t="n">
         <v>3000</v>
@@ -22612,7 +22612,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>2.09356141090393</v>
+        <v>2.09356117248535</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -22641,7 +22641,7 @@
         <v>2.25</v>
       </c>
       <c r="G768" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H768" t="n">
         <v>1000</v>
@@ -22670,7 +22670,7 @@
         <v>2.25</v>
       </c>
       <c r="G769" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H769" t="n">
         <v>0</v>
@@ -22699,7 +22699,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G770" t="n">
-        <v>2.00253701210022</v>
+        <v>2.00253677368164</v>
       </c>
       <c r="H770" t="n">
         <v>1000</v>
@@ -22728,7 +22728,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G771" t="n">
-        <v>2.00253701210022</v>
+        <v>2.00253677368164</v>
       </c>
       <c r="H771" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G772" t="n">
-        <v>2.05715179443359</v>
+        <v>2.05715155601501</v>
       </c>
       <c r="H772" t="n">
         <v>7000</v>
@@ -22786,7 +22786,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G773" t="n">
-        <v>2.05715179443359</v>
+        <v>2.05715155601501</v>
       </c>
       <c r="H773" t="n">
         <v>2000</v>
@@ -22815,7 +22815,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G774" t="n">
-        <v>2.05715179443359</v>
+        <v>2.05715155601501</v>
       </c>
       <c r="H774" t="n">
         <v>0</v>
@@ -22873,7 +22873,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>2.09356141090393</v>
+        <v>2.09356117248535</v>
       </c>
       <c r="H776" t="n">
         <v>3000</v>
@@ -22960,7 +22960,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G779" t="n">
-        <v>2.06625413894653</v>
+        <v>2.06625390052795</v>
       </c>
       <c r="H779" t="n">
         <v>2000</v>
@@ -22989,7 +22989,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G780" t="n">
-        <v>2.06625413894653</v>
+        <v>2.06625390052795</v>
       </c>
       <c r="H780" t="n">
         <v>0</v>
@@ -23018,7 +23018,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G781" t="n">
-        <v>2.06625413894653</v>
+        <v>2.06625390052795</v>
       </c>
       <c r="H781" t="n">
         <v>0</v>
@@ -23308,7 +23308,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G791" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H791" t="n">
         <v>2000</v>
@@ -23424,7 +23424,7 @@
         <v>2.25</v>
       </c>
       <c r="G795" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H795" t="n">
         <v>1000</v>
@@ -23453,7 +23453,7 @@
         <v>2.25</v>
       </c>
       <c r="G796" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H796" t="n">
         <v>0</v>
@@ -23482,7 +23482,7 @@
         <v>2.25</v>
       </c>
       <c r="G797" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H797" t="n">
         <v>0</v>
@@ -23540,7 +23540,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G799" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H799" t="n">
         <v>2000</v>
@@ -23569,7 +23569,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G800" t="n">
-        <v>1.95702493190765</v>
+        <v>1.95702469348907</v>
       </c>
       <c r="H800" t="n">
         <v>5000</v>
@@ -23801,7 +23801,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G808" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H808" t="n">
         <v>9000</v>
@@ -23830,7 +23830,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G809" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H809" t="n">
         <v>0</v>
@@ -24091,7 +24091,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G818" t="n">
-        <v>1.90241003036499</v>
+        <v>1.90241014957428</v>
       </c>
       <c r="H818" t="n">
         <v>2000</v>
@@ -24149,7 +24149,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G820" t="n">
-        <v>1.7795273065567</v>
+        <v>1.77952718734741</v>
       </c>
       <c r="H820" t="n">
         <v>8000</v>
@@ -24178,7 +24178,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G821" t="n">
-        <v>1.765873670578</v>
+        <v>1.76587355136871</v>
       </c>
       <c r="H821" t="n">
         <v>2000</v>
@@ -24207,7 +24207,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G822" t="n">
-        <v>1.765873670578</v>
+        <v>1.76587355136871</v>
       </c>
       <c r="H822" t="n">
         <v>7000</v>
@@ -24236,7 +24236,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G823" t="n">
-        <v>1.765873670578</v>
+        <v>1.76587355136871</v>
       </c>
       <c r="H823" t="n">
         <v>0</v>
@@ -24265,7 +24265,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H824" t="n">
         <v>1000</v>
@@ -24294,7 +24294,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H825" t="n">
         <v>0</v>
@@ -24323,7 +24323,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G826" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H826" t="n">
         <v>0</v>
@@ -24352,7 +24352,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -24381,7 +24381,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H828" t="n">
         <v>0</v>
@@ -24468,7 +24468,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G831" t="n">
-        <v>1.77042484283447</v>
+        <v>1.77042472362518</v>
       </c>
       <c r="H831" t="n">
         <v>1000</v>
@@ -24497,7 +24497,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G832" t="n">
-        <v>1.71125900745392</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H832" t="n">
         <v>8000</v>
@@ -24526,7 +24526,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.72491264343262</v>
+        <v>1.72491240501404</v>
       </c>
       <c r="H833" t="n">
         <v>5000</v>
@@ -24555,7 +24555,7 @@
         <v>1.875</v>
       </c>
       <c r="G834" t="n">
-        <v>1.70670771598816</v>
+        <v>1.70670759677887</v>
       </c>
       <c r="H834" t="n">
         <v>5000</v>
@@ -24671,7 +24671,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G838" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H838" t="n">
         <v>15000</v>
@@ -24700,7 +24700,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G839" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H839" t="n">
         <v>1000</v>
@@ -24729,7 +24729,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G840" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H840" t="n">
         <v>0</v>
@@ -24758,7 +24758,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G841" t="n">
-        <v>1.71125900745392</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H841" t="n">
         <v>2000</v>
@@ -24787,7 +24787,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G842" t="n">
-        <v>1.71125900745392</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H842" t="n">
         <v>1000</v>
@@ -24816,7 +24816,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G843" t="n">
-        <v>1.71125900745392</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H843" t="n">
         <v>0</v>
@@ -24845,7 +24845,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G844" t="n">
-        <v>1.71125900745392</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H844" t="n">
         <v>0</v>
@@ -24874,7 +24874,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G845" t="n">
-        <v>1.71125900745392</v>
+        <v>1.71125876903534</v>
       </c>
       <c r="H845" t="n">
         <v>0</v>
@@ -24990,7 +24990,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G849" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H849" t="n">
         <v>9000</v>
@@ -25019,7 +25019,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G850" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H850" t="n">
         <v>8000</v>
@@ -25048,7 +25048,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G851" t="n">
-        <v>1.81138563156128</v>
+        <v>1.81138575077057</v>
       </c>
       <c r="H851" t="n">
         <v>2000</v>
@@ -25077,7 +25077,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G852" t="n">
-        <v>1.81138563156128</v>
+        <v>1.81138575077057</v>
       </c>
       <c r="H852" t="n">
         <v>0</v>
@@ -25164,7 +25164,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G855" t="n">
-        <v>1.77042484283447</v>
+        <v>1.77042472362518</v>
       </c>
       <c r="H855" t="n">
         <v>1000</v>
@@ -25193,7 +25193,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G856" t="n">
-        <v>1.76132237911224</v>
+        <v>1.76132214069366</v>
       </c>
       <c r="H856" t="n">
         <v>1000</v>
@@ -25222,7 +25222,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G857" t="n">
-        <v>1.76132237911224</v>
+        <v>1.76132214069366</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -25251,7 +25251,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G858" t="n">
-        <v>1.765873670578</v>
+        <v>1.76587355136871</v>
       </c>
       <c r="H858" t="n">
         <v>3000</v>
@@ -25280,7 +25280,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G859" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H859" t="n">
         <v>7000</v>
@@ -25309,7 +25309,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G860" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H860" t="n">
         <v>0</v>
@@ -25338,7 +25338,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G861" t="n">
-        <v>1.74311745166779</v>
+        <v>1.7431173324585</v>
       </c>
       <c r="H861" t="n">
         <v>1000</v>
@@ -25367,7 +25367,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G862" t="n">
-        <v>1.74311745166779</v>
+        <v>1.7431173324585</v>
       </c>
       <c r="H862" t="n">
         <v>0</v>
@@ -25396,7 +25396,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G863" t="n">
-        <v>1.73401498794556</v>
+        <v>1.73401486873627</v>
       </c>
       <c r="H863" t="n">
         <v>2000</v>
@@ -25425,7 +25425,7 @@
         <v>1.875</v>
       </c>
       <c r="G864" t="n">
-        <v>1.70670771598816</v>
+        <v>1.70670759677887</v>
       </c>
       <c r="H864" t="n">
         <v>7000</v>
@@ -25454,7 +25454,7 @@
         <v>1.875</v>
       </c>
       <c r="G865" t="n">
-        <v>1.70670771598816</v>
+        <v>1.70670759677887</v>
       </c>
       <c r="H865" t="n">
         <v>0</v>
@@ -25541,7 +25541,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G868" t="n">
-        <v>1.674849152565</v>
+        <v>1.67484903335571</v>
       </c>
       <c r="H868" t="n">
         <v>4000</v>
@@ -25657,7 +25657,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G872" t="n">
-        <v>1.6611955165863</v>
+        <v>1.66119539737701</v>
       </c>
       <c r="H872" t="n">
         <v>1000</v>
@@ -25686,7 +25686,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G873" t="n">
-        <v>1.6611955165863</v>
+        <v>1.66119539737701</v>
       </c>
       <c r="H873" t="n">
         <v>3000</v>
@@ -25744,7 +25744,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>1.72491264343262</v>
+        <v>1.72491240501404</v>
       </c>
       <c r="H875" t="n">
         <v>3000</v>
@@ -25773,7 +25773,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G876" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H876" t="n">
         <v>2000</v>
@@ -25831,7 +25831,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G878" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H878" t="n">
         <v>9000</v>
@@ -25860,7 +25860,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G879" t="n">
-        <v>1.79773211479187</v>
+        <v>1.79773199558258</v>
       </c>
       <c r="H879" t="n">
         <v>6000</v>
@@ -25889,7 +25889,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G880" t="n">
-        <v>1.79773211479187</v>
+        <v>1.79773199558258</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -25918,7 +25918,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G881" t="n">
-        <v>1.79773211479187</v>
+        <v>1.79773199558258</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -25947,7 +25947,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G882" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H882" t="n">
         <v>12000</v>
@@ -26092,7 +26092,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G887" t="n">
-        <v>1.88420534133911</v>
+        <v>1.88420522212982</v>
       </c>
       <c r="H887" t="n">
         <v>7000</v>
@@ -26121,7 +26121,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G888" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H888" t="n">
         <v>20000</v>
@@ -26179,7 +26179,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G890" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H890" t="n">
         <v>9000</v>
@@ -26324,7 +26324,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G895" t="n">
-        <v>1.81138563156128</v>
+        <v>1.81138575077057</v>
       </c>
       <c r="H895" t="n">
         <v>9000</v>
@@ -26411,7 +26411,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G898" t="n">
-        <v>1.81138563156128</v>
+        <v>1.81138575077057</v>
       </c>
       <c r="H898" t="n">
         <v>16000</v>
@@ -26440,7 +26440,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G899" t="n">
-        <v>1.81138563156128</v>
+        <v>1.81138575077057</v>
       </c>
       <c r="H899" t="n">
         <v>5000</v>
@@ -26788,7 +26788,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G911" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H911" t="n">
         <v>2000</v>
@@ -26817,7 +26817,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G912" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -26846,7 +26846,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G913" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -26991,7 +26991,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>1.76132237911224</v>
+        <v>1.76132214069366</v>
       </c>
       <c r="H918" t="n">
         <v>7000</v>
@@ -27020,7 +27020,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G919" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H919" t="n">
         <v>1000</v>
@@ -27078,7 +27078,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G921" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H921" t="n">
         <v>7000</v>
@@ -27107,7 +27107,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G922" t="n">
-        <v>1.72946381568909</v>
+        <v>1.7294636964798</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -27136,7 +27136,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G923" t="n">
-        <v>1.76132237911224</v>
+        <v>1.76132214069366</v>
       </c>
       <c r="H923" t="n">
         <v>5000</v>
@@ -27165,7 +27165,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G924" t="n">
-        <v>1.7795273065567</v>
+        <v>1.77952718734741</v>
       </c>
       <c r="H924" t="n">
         <v>3000</v>
@@ -27310,7 +27310,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G929" t="n">
-        <v>1.81138563156128</v>
+        <v>1.81138575077057</v>
       </c>
       <c r="H929" t="n">
         <v>3000</v>
@@ -27339,7 +27339,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G930" t="n">
-        <v>1.81138563156128</v>
+        <v>1.81138575077057</v>
       </c>
       <c r="H930" t="n">
         <v>0</v>
@@ -27571,7 +27571,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G938" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H938" t="n">
         <v>1000</v>
@@ -27629,7 +27629,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G940" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H940" t="n">
         <v>6000</v>
@@ -27687,7 +27687,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G942" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H942" t="n">
         <v>2000</v>
@@ -27716,7 +27716,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G943" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -27803,7 +27803,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G946" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H946" t="n">
         <v>2000</v>
@@ -27832,7 +27832,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G947" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -27861,7 +27861,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G948" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H948" t="n">
         <v>12000</v>
@@ -27890,7 +27890,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H949" t="n">
         <v>1000</v>
@@ -27977,7 +27977,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G952" t="n">
-        <v>1.81138563156128</v>
+        <v>1.81138575077057</v>
       </c>
       <c r="H952" t="n">
         <v>2000</v>
@@ -28035,7 +28035,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G954" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H954" t="n">
         <v>2000</v>
@@ -28093,7 +28093,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G956" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H956" t="n">
         <v>2000</v>
@@ -28151,7 +28151,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G958" t="n">
-        <v>1.765873670578</v>
+        <v>1.76587355136871</v>
       </c>
       <c r="H958" t="n">
         <v>14000</v>
@@ -28180,7 +28180,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G959" t="n">
-        <v>1.72036135196686</v>
+        <v>1.72036123275757</v>
       </c>
       <c r="H959" t="n">
         <v>2000</v>
@@ -28209,7 +28209,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G960" t="n">
-        <v>1.72036135196686</v>
+        <v>1.72036123275757</v>
       </c>
       <c r="H960" t="n">
         <v>7000</v>
@@ -28238,7 +28238,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G961" t="n">
-        <v>1.72036135196686</v>
+        <v>1.72036123275757</v>
       </c>
       <c r="H961" t="n">
         <v>6000</v>
@@ -28267,7 +28267,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G962" t="n">
-        <v>1.72036135196686</v>
+        <v>1.72036123275757</v>
       </c>
       <c r="H962" t="n">
         <v>0</v>
@@ -28296,7 +28296,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G963" t="n">
-        <v>1.72036135196686</v>
+        <v>1.72036123275757</v>
       </c>
       <c r="H963" t="n">
         <v>2000</v>
@@ -28325,7 +28325,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G964" t="n">
-        <v>1.765873670578</v>
+        <v>1.76587355136871</v>
       </c>
       <c r="H964" t="n">
         <v>29000</v>
@@ -53735,6 +53735,64 @@
         <v>37000</v>
       </c>
       <c r="I1840" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1841" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1841" t="n">
+        <v>1.98000001907349</v>
+      </c>
+      <c r="D1841" t="n">
+        <v>1.98000001907349</v>
+      </c>
+      <c r="E1841" t="n">
+        <v>1.98000001907349</v>
+      </c>
+      <c r="F1841" t="n">
+        <v>1.98000001907349</v>
+      </c>
+      <c r="G1841" t="n">
+        <v>1.98000001907349</v>
+      </c>
+      <c r="H1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1841" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1842" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1842" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1842" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1842" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="F1842" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="G1842" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="H1842" t="n">
+        <v>11000</v>
+      </c>
+      <c r="I1842" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>1.30437552928925</v>
+        <v>1.30437564849854</v>
       </c>
       <c r="H2" t="n">
         <v>322000</v>
@@ -456,7 +456,7 @@
         <v>1.50020003318787</v>
       </c>
       <c r="G3" t="n">
-        <v>1.31330502033234</v>
+        <v>1.31330490112305</v>
       </c>
       <c r="H3" t="n">
         <v>35000</v>
@@ -485,7 +485,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G4" t="n">
-        <v>1.40067183971405</v>
+        <v>1.40067172050476</v>
       </c>
       <c r="H4" t="n">
         <v>193000</v>
@@ -514,7 +514,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G5" t="n">
-        <v>1.62828087806702</v>
+        <v>1.62828099727631</v>
       </c>
       <c r="H5" t="n">
         <v>169000</v>
@@ -543,7 +543,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G6" t="n">
-        <v>1.62828087806702</v>
+        <v>1.62828099727631</v>
       </c>
       <c r="H6" t="n">
         <v>470000</v>
@@ -572,7 +572,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G7" t="n">
-        <v>1.58888697624207</v>
+        <v>1.58888709545135</v>
       </c>
       <c r="H7" t="n">
         <v>113000</v>
@@ -601,7 +601,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G8" t="n">
-        <v>1.63265788555145</v>
+        <v>1.63265800476074</v>
       </c>
       <c r="H8" t="n">
         <v>69000</v>
@@ -659,7 +659,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G10" t="n">
-        <v>1.87339842319489</v>
+        <v>1.87339878082275</v>
       </c>
       <c r="H10" t="n">
         <v>464000</v>
@@ -688,7 +688,7 @@
         <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.18854975700378</v>
+        <v>2.18854951858521</v>
       </c>
       <c r="H11" t="n">
         <v>315000</v>
@@ -717,7 +717,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G12" t="n">
-        <v>2.59124279022217</v>
+        <v>2.59124255180359</v>
       </c>
       <c r="H12" t="n">
         <v>261000</v>
@@ -746,7 +746,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G13" t="n">
-        <v>3.17777395248413</v>
+        <v>3.17777419090271</v>
       </c>
       <c r="H13" t="n">
         <v>203000</v>
@@ -833,7 +833,7 @@
         <v>4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3.93938875198364</v>
+        <v>3.93938994407654</v>
       </c>
       <c r="H16" t="n">
         <v>669000</v>
@@ -891,7 +891,7 @@
         <v>4.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3.93938875198364</v>
+        <v>3.93938994407654</v>
       </c>
       <c r="H18" t="n">
         <v>489000</v>
@@ -978,7 +978,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G21" t="n">
-        <v>3.52794241905212</v>
+        <v>3.52794218063354</v>
       </c>
       <c r="H21" t="n">
         <v>356000</v>
@@ -1094,7 +1094,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G25" t="n">
-        <v>3.55420470237732</v>
+        <v>3.55420446395874</v>
       </c>
       <c r="H25" t="n">
         <v>275000</v>
@@ -1152,7 +1152,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G27" t="n">
-        <v>3.51043391227722</v>
+        <v>3.51043367385864</v>
       </c>
       <c r="H27" t="n">
         <v>25000</v>
@@ -1210,7 +1210,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G29" t="n">
-        <v>3.51918792724609</v>
+        <v>3.51918768882751</v>
       </c>
       <c r="H29" t="n">
         <v>87000</v>
@@ -1239,7 +1239,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>3.536696434021</v>
+        <v>3.53669619560242</v>
       </c>
       <c r="H30" t="n">
         <v>95000</v>
@@ -1326,7 +1326,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>3.40976023674011</v>
+        <v>3.40976047515869</v>
       </c>
       <c r="H33" t="n">
         <v>38000</v>
@@ -1413,7 +1413,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G36" t="n">
-        <v>3.41413712501526</v>
+        <v>3.41413760185242</v>
       </c>
       <c r="H36" t="n">
         <v>60000</v>
@@ -1442,7 +1442,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G37" t="n">
-        <v>3.41413712501526</v>
+        <v>3.41413760185242</v>
       </c>
       <c r="H37" t="n">
         <v>48000</v>
@@ -1529,7 +1529,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>3.17777395248413</v>
+        <v>3.17777419090271</v>
       </c>
       <c r="H40" t="n">
         <v>66000</v>
@@ -1558,7 +1558,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G41" t="n">
-        <v>2.93703365325928</v>
+        <v>2.9370334148407</v>
       </c>
       <c r="H41" t="n">
         <v>317000</v>
@@ -1616,7 +1616,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G43" t="n">
-        <v>2.62188220024109</v>
+        <v>2.62188243865967</v>
       </c>
       <c r="H43" t="n">
         <v>68000</v>
@@ -1674,7 +1674,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G45" t="n">
-        <v>2.98518180847168</v>
+        <v>2.98518204689026</v>
       </c>
       <c r="H45" t="n">
         <v>262000</v>
@@ -1703,7 +1703,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G46" t="n">
-        <v>2.98080468177795</v>
+        <v>2.98080444335938</v>
       </c>
       <c r="H46" t="n">
         <v>492000</v>
@@ -1732,7 +1732,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G47" t="n">
-        <v>2.78821229934692</v>
+        <v>2.78821206092834</v>
       </c>
       <c r="H47" t="n">
         <v>132000</v>
@@ -1790,7 +1790,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>2.73130989074707</v>
+        <v>2.73130965232849</v>
       </c>
       <c r="H49" t="n">
         <v>52000</v>
@@ -1819,7 +1819,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G50" t="n">
-        <v>2.74881839752197</v>
+        <v>2.74881863594055</v>
       </c>
       <c r="H50" t="n">
         <v>29000</v>
@@ -1848,7 +1848,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G51" t="n">
-        <v>2.77945828437805</v>
+        <v>2.77945780754089</v>
       </c>
       <c r="H51" t="n">
         <v>28000</v>
@@ -2051,7 +2051,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>2.8013436794281</v>
+        <v>2.80134344100952</v>
       </c>
       <c r="H58" t="n">
         <v>74000</v>
@@ -2109,7 +2109,7 @@
         <v>3.25</v>
       </c>
       <c r="G60" t="n">
-        <v>2.84511423110962</v>
+        <v>2.84511494636536</v>
       </c>
       <c r="H60" t="n">
         <v>46000</v>
@@ -2196,7 +2196,7 @@
         <v>3.25</v>
       </c>
       <c r="G63" t="n">
-        <v>2.84511423110962</v>
+        <v>2.84511494636536</v>
       </c>
       <c r="H63" t="n">
         <v>14000</v>
@@ -2341,7 +2341,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>2.82760620117188</v>
+        <v>2.8276059627533</v>
       </c>
       <c r="H68" t="n">
         <v>24000</v>
@@ -2370,7 +2370,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>2.82760620117188</v>
+        <v>2.8276059627533</v>
       </c>
       <c r="H69" t="n">
         <v>9000</v>
@@ -2428,7 +2428,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>2.78821229934692</v>
+        <v>2.78821206092834</v>
       </c>
       <c r="H71" t="n">
         <v>15000</v>
@@ -2486,7 +2486,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G73" t="n">
-        <v>2.87137699127197</v>
+        <v>2.87137722969055</v>
       </c>
       <c r="H73" t="n">
         <v>14000</v>
@@ -2515,7 +2515,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G74" t="n">
-        <v>2.8494918346405</v>
+        <v>2.84949159622192</v>
       </c>
       <c r="H74" t="n">
         <v>3000</v>
@@ -2544,7 +2544,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G75" t="n">
-        <v>2.78821229934692</v>
+        <v>2.78821206092834</v>
       </c>
       <c r="H75" t="n">
         <v>10000</v>
@@ -2602,7 +2602,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>2.77945828437805</v>
+        <v>2.77945780754089</v>
       </c>
       <c r="H77" t="n">
         <v>18000</v>
@@ -2631,7 +2631,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>2.77070355415344</v>
+        <v>2.77070379257202</v>
       </c>
       <c r="H78" t="n">
         <v>13000</v>
@@ -2660,7 +2660,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>2.72693252563477</v>
+        <v>2.72693276405334</v>
       </c>
       <c r="H79" t="n">
         <v>6000</v>
@@ -2689,7 +2689,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G80" t="n">
-        <v>2.83198308944702</v>
+        <v>2.83198285102844</v>
       </c>
       <c r="H80" t="n">
         <v>24000</v>
@@ -2718,7 +2718,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.8013436794281</v>
+        <v>2.80134344100952</v>
       </c>
       <c r="H81" t="n">
         <v>20000</v>
@@ -2776,7 +2776,7 @@
         <v>3.25</v>
       </c>
       <c r="G83" t="n">
-        <v>2.84511423110962</v>
+        <v>2.84511494636536</v>
       </c>
       <c r="H83" t="n">
         <v>61000</v>
@@ -2834,7 +2834,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G85" t="n">
-        <v>2.78821229934692</v>
+        <v>2.78821206092834</v>
       </c>
       <c r="H85" t="n">
         <v>8000</v>
@@ -2892,7 +2892,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G87" t="n">
-        <v>2.8013436794281</v>
+        <v>2.80134344100952</v>
       </c>
       <c r="H87" t="n">
         <v>20000</v>
@@ -2921,7 +2921,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G88" t="n">
-        <v>2.8013436794281</v>
+        <v>2.80134344100952</v>
       </c>
       <c r="H88" t="n">
         <v>49000</v>
@@ -2979,7 +2979,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G90" t="n">
-        <v>2.88888549804688</v>
+        <v>2.8888852596283</v>
       </c>
       <c r="H90" t="n">
         <v>39000</v>
@@ -3008,7 +3008,7 @@
         <v>3.25</v>
       </c>
       <c r="G91" t="n">
-        <v>2.84511423110962</v>
+        <v>2.84511494636536</v>
       </c>
       <c r="H91" t="n">
         <v>16000</v>
@@ -3037,7 +3037,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G92" t="n">
-        <v>2.87137699127197</v>
+        <v>2.87137722969055</v>
       </c>
       <c r="H92" t="n">
         <v>8000</v>
@@ -3066,7 +3066,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G93" t="n">
-        <v>2.88888549804688</v>
+        <v>2.8888852596283</v>
       </c>
       <c r="H93" t="n">
         <v>20000</v>
@@ -3153,7 +3153,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G96" t="n">
-        <v>2.8013436794281</v>
+        <v>2.80134344100952</v>
       </c>
       <c r="H96" t="n">
         <v>9000</v>
@@ -3211,7 +3211,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>2.82760620117188</v>
+        <v>2.8276059627533</v>
       </c>
       <c r="H98" t="n">
         <v>4000</v>
@@ -3240,7 +3240,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.86700010299683</v>
+        <v>2.86699986457825</v>
       </c>
       <c r="H99" t="n">
         <v>3000</v>
@@ -3356,7 +3356,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G103" t="n">
-        <v>2.88888549804688</v>
+        <v>2.8888852596283</v>
       </c>
       <c r="H103" t="n">
         <v>8000</v>
@@ -3385,7 +3385,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G104" t="n">
-        <v>2.88888549804688</v>
+        <v>2.8888852596283</v>
       </c>
       <c r="H104" t="n">
         <v>9000</v>
@@ -3414,7 +3414,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88888549804688</v>
+        <v>2.8888852596283</v>
       </c>
       <c r="H105" t="n">
         <v>13000</v>
@@ -3443,7 +3443,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G106" t="n">
-        <v>2.99831318855286</v>
+        <v>2.99831295013428</v>
       </c>
       <c r="H106" t="n">
         <v>52000</v>
@@ -3501,7 +3501,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>4.39460802078247</v>
+        <v>4.39460754394531</v>
       </c>
       <c r="H108" t="n">
         <v>137000</v>
@@ -3530,7 +3530,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G109" t="n">
-        <v>3.96565198898315</v>
+        <v>3.96565222740173</v>
       </c>
       <c r="H109" t="n">
         <v>596000</v>
@@ -3559,7 +3559,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>4.11447286605835</v>
+        <v>4.11447334289551</v>
       </c>
       <c r="H110" t="n">
         <v>568000</v>
@@ -3646,7 +3646,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G113" t="n">
-        <v>3.52794241905212</v>
+        <v>3.52794218063354</v>
       </c>
       <c r="H113" t="n">
         <v>87000</v>
@@ -3675,7 +3675,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>3.65487813949585</v>
+        <v>3.65487790107727</v>
       </c>
       <c r="H114" t="n">
         <v>318000</v>
@@ -3704,7 +3704,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G115" t="n">
-        <v>3.77305936813354</v>
+        <v>3.77305960655212</v>
       </c>
       <c r="H115" t="n">
         <v>88000</v>
@@ -3733,7 +3733,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>3.97878336906433</v>
+        <v>3.97878313064575</v>
       </c>
       <c r="H116" t="n">
         <v>371000</v>
@@ -3762,7 +3762,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>3.91312670707703</v>
+        <v>3.91312623023987</v>
       </c>
       <c r="H117" t="n">
         <v>152000</v>
@@ -3791,7 +3791,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>3.8606014251709</v>
+        <v>3.86060166358948</v>
       </c>
       <c r="H118" t="n">
         <v>82000</v>
@@ -3820,7 +3820,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G119" t="n">
-        <v>3.7993221282959</v>
+        <v>3.79932260513306</v>
       </c>
       <c r="H119" t="n">
         <v>66000</v>
@@ -3849,7 +3849,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>3.84747004508972</v>
+        <v>3.8474702835083</v>
       </c>
       <c r="H120" t="n">
         <v>40000</v>
@@ -3878,7 +3878,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G121" t="n">
-        <v>3.89124155044556</v>
+        <v>3.89124178886414</v>
       </c>
       <c r="H121" t="n">
         <v>84000</v>
@@ -3907,7 +3907,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G122" t="n">
-        <v>3.92625832557678</v>
+        <v>3.92625784873962</v>
       </c>
       <c r="H122" t="n">
         <v>35000</v>
@@ -3965,7 +3965,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G124" t="n">
-        <v>4.17137575149536</v>
+        <v>4.1713752746582</v>
       </c>
       <c r="H124" t="n">
         <v>181000</v>
@@ -4081,7 +4081,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G128" t="n">
-        <v>4.16699838638306</v>
+        <v>4.16699886322021</v>
       </c>
       <c r="H128" t="n">
         <v>58000</v>
@@ -4168,7 +4168,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G131" t="n">
-        <v>4.04006195068359</v>
+        <v>4.04006290435791</v>
       </c>
       <c r="H131" t="n">
         <v>36000</v>
@@ -4226,7 +4226,7 @@
         <v>4.625</v>
       </c>
       <c r="G133" t="n">
-        <v>4.04881715774536</v>
+        <v>4.0488166809082</v>
       </c>
       <c r="H133" t="n">
         <v>7000</v>
@@ -4255,7 +4255,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G134" t="n">
-        <v>4.026930809021</v>
+        <v>4.02693128585815</v>
       </c>
       <c r="H134" t="n">
         <v>58000</v>
@@ -4284,7 +4284,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>3.95689725875854</v>
+        <v>3.9568977355957</v>
       </c>
       <c r="H135" t="n">
         <v>25000</v>
@@ -4342,7 +4342,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G137" t="n">
-        <v>3.98753714561462</v>
+        <v>3.98753666877747</v>
       </c>
       <c r="H137" t="n">
         <v>27000</v>
@@ -4371,7 +4371,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G138" t="n">
-        <v>3.99629235267639</v>
+        <v>3.99629139900208</v>
       </c>
       <c r="H138" t="n">
         <v>9000</v>
@@ -4487,7 +4487,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G142" t="n">
-        <v>4.32895183563232</v>
+        <v>4.32895135879517</v>
       </c>
       <c r="H142" t="n">
         <v>162000</v>
@@ -4545,7 +4545,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G144" t="n">
-        <v>4.76228427886963</v>
+        <v>4.76228380203247</v>
       </c>
       <c r="H144" t="n">
         <v>733000</v>
@@ -4574,7 +4574,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G145" t="n">
-        <v>4.46464109420776</v>
+        <v>4.46464061737061</v>
       </c>
       <c r="H145" t="n">
         <v>522000</v>
@@ -4632,7 +4632,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G147" t="n">
-        <v>4.25454092025757</v>
+        <v>4.25454044342041</v>
       </c>
       <c r="H147" t="n">
         <v>160000</v>
@@ -4690,7 +4690,7 @@
         <v>4.625</v>
       </c>
       <c r="G149" t="n">
-        <v>4.04881715774536</v>
+        <v>4.0488166809082</v>
       </c>
       <c r="H149" t="n">
         <v>105000</v>
@@ -4777,7 +4777,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>3.7993221282959</v>
+        <v>3.79932260513306</v>
       </c>
       <c r="H152" t="n">
         <v>69000</v>
@@ -4864,7 +4864,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G155" t="n">
-        <v>3.19965934753418</v>
+        <v>3.19965958595276</v>
       </c>
       <c r="H155" t="n">
         <v>17000</v>
@@ -4922,7 +4922,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G157" t="n">
-        <v>2.45555281639099</v>
+        <v>2.45555257797241</v>
       </c>
       <c r="H157" t="n">
         <v>83000</v>
@@ -4951,7 +4951,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G158" t="n">
-        <v>2.73130989074707</v>
+        <v>2.73130965232849</v>
       </c>
       <c r="H158" t="n">
         <v>60000</v>
@@ -4980,7 +4980,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>2.77508091926575</v>
+        <v>2.77508115768433</v>
       </c>
       <c r="H159" t="n">
         <v>58000</v>
@@ -5009,7 +5009,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G160" t="n">
-        <v>2.88888549804688</v>
+        <v>2.8888852596283</v>
       </c>
       <c r="H160" t="n">
         <v>26000</v>
@@ -5038,7 +5038,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G161" t="n">
-        <v>2.95891928672791</v>
+        <v>2.95891952514648</v>
       </c>
       <c r="H161" t="n">
         <v>30000</v>
@@ -5096,7 +5096,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G163" t="n">
-        <v>3.22154474258423</v>
+        <v>3.22154498100281</v>
       </c>
       <c r="H163" t="n">
         <v>30000</v>
@@ -5125,7 +5125,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G164" t="n">
-        <v>3.536696434021</v>
+        <v>3.53669619560242</v>
       </c>
       <c r="H164" t="n">
         <v>67000</v>
@@ -5183,7 +5183,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.75555086135864</v>
+        <v>3.75555109977722</v>
       </c>
       <c r="H166" t="n">
         <v>119000</v>
@@ -5241,7 +5241,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>3.6286153793335</v>
+        <v>3.62861514091492</v>
       </c>
       <c r="H168" t="n">
         <v>19000</v>
@@ -5270,7 +5270,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G169" t="n">
-        <v>3.60672974586487</v>
+        <v>3.60672926902771</v>
       </c>
       <c r="H169" t="n">
         <v>15000</v>
@@ -5328,7 +5328,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G171" t="n">
-        <v>3.73366570472717</v>
+        <v>3.73366546630859</v>
       </c>
       <c r="H171" t="n">
         <v>10000</v>
@@ -5357,7 +5357,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G172" t="n">
-        <v>3.68551778793335</v>
+        <v>3.68551754951477</v>
       </c>
       <c r="H172" t="n">
         <v>16000</v>
@@ -5386,7 +5386,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G173" t="n">
-        <v>3.95252060890198</v>
+        <v>3.95252084732056</v>
       </c>
       <c r="H173" t="n">
         <v>72000</v>
@@ -5444,7 +5444,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G175" t="n">
-        <v>3.94376635551453</v>
+        <v>3.94376683235168</v>
       </c>
       <c r="H175" t="n">
         <v>24000</v>
@@ -5531,7 +5531,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>3.68114042282104</v>
+        <v>3.68114018440247</v>
       </c>
       <c r="H178" t="n">
         <v>51000</v>
@@ -5560,7 +5560,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G179" t="n">
-        <v>3.70302605628967</v>
+        <v>3.70302581787109</v>
       </c>
       <c r="H179" t="n">
         <v>30000</v>
@@ -5589,7 +5589,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G180" t="n">
-        <v>3.83433866500854</v>
+        <v>3.83433890342712</v>
       </c>
       <c r="H180" t="n">
         <v>29000</v>
@@ -5647,7 +5647,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G182" t="n">
-        <v>3.70302605628967</v>
+        <v>3.70302581787109</v>
       </c>
       <c r="H182" t="n">
         <v>15000</v>
@@ -5734,7 +5734,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G185" t="n">
-        <v>3.79056763648987</v>
+        <v>3.79056787490845</v>
       </c>
       <c r="H185" t="n">
         <v>4000</v>
@@ -5763,7 +5763,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>3.86935567855835</v>
+        <v>3.86935591697693</v>
       </c>
       <c r="H186" t="n">
         <v>15000</v>
@@ -5792,7 +5792,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G187" t="n">
-        <v>3.8606014251709</v>
+        <v>3.86060166358948</v>
       </c>
       <c r="H187" t="n">
         <v>5000</v>
@@ -5821,7 +5821,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>3.77743673324585</v>
+        <v>3.77743649482727</v>
       </c>
       <c r="H188" t="n">
         <v>7000</v>
@@ -5879,7 +5879,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G190" t="n">
-        <v>3.78224897384644</v>
+        <v>3.78224873542786</v>
       </c>
       <c r="H190" t="n">
         <v>11000</v>
@@ -5937,7 +5937,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G192" t="n">
-        <v>3.78668808937073</v>
+        <v>3.78668785095215</v>
       </c>
       <c r="H192" t="n">
         <v>2000</v>
@@ -5966,7 +5966,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G193" t="n">
-        <v>3.66682839393616</v>
+        <v>3.66682815551758</v>
       </c>
       <c r="H193" t="n">
         <v>9000</v>
@@ -6024,7 +6024,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G195" t="n">
-        <v>3.78224897384644</v>
+        <v>3.78224873542786</v>
       </c>
       <c r="H195" t="n">
         <v>8000</v>
@@ -6082,7 +6082,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>3.79112720489502</v>
+        <v>3.79112696647644</v>
       </c>
       <c r="H197" t="n">
         <v>2000</v>
@@ -6111,7 +6111,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G198" t="n">
-        <v>3.91098809242249</v>
+        <v>3.91098761558533</v>
       </c>
       <c r="H198" t="n">
         <v>27000</v>
@@ -6140,7 +6140,7 @@
         <v>4.5</v>
       </c>
       <c r="G199" t="n">
-        <v>3.99533295631409</v>
+        <v>3.99533343315125</v>
       </c>
       <c r="H199" t="n">
         <v>99000</v>
@@ -6169,7 +6169,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G200" t="n">
-        <v>3.8621551990509</v>
+        <v>3.86215496063232</v>
       </c>
       <c r="H200" t="n">
         <v>46000</v>
@@ -6227,7 +6227,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>3.8310809135437</v>
+        <v>3.83108067512512</v>
       </c>
       <c r="H202" t="n">
         <v>10000</v>
@@ -6256,7 +6256,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G203" t="n">
-        <v>3.71122074127197</v>
+        <v>3.71122050285339</v>
       </c>
       <c r="H203" t="n">
         <v>67000</v>
@@ -6285,7 +6285,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G204" t="n">
-        <v>3.82220220565796</v>
+        <v>3.82220196723938</v>
       </c>
       <c r="H204" t="n">
         <v>7000</v>
@@ -6314,7 +6314,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G205" t="n">
-        <v>3.82220220565796</v>
+        <v>3.82220196723938</v>
       </c>
       <c r="H205" t="n">
         <v>12000</v>
@@ -6343,7 +6343,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G206" t="n">
-        <v>3.80888438224792</v>
+        <v>3.80888414382935</v>
       </c>
       <c r="H206" t="n">
         <v>6000</v>
@@ -6401,7 +6401,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G208" t="n">
-        <v>3.9065477848053</v>
+        <v>3.90654802322388</v>
       </c>
       <c r="H208" t="n">
         <v>30000</v>
@@ -6430,7 +6430,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>3.8621551990509</v>
+        <v>3.86215496063232</v>
       </c>
       <c r="H209" t="n">
         <v>8000</v>
@@ -6459,7 +6459,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>3.8621551990509</v>
+        <v>3.86215496063232</v>
       </c>
       <c r="H210" t="n">
         <v>2000</v>
@@ -6488,7 +6488,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G211" t="n">
-        <v>3.81776261329651</v>
+        <v>3.81776285171509</v>
       </c>
       <c r="H211" t="n">
         <v>14000</v>
@@ -6517,7 +6517,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>3.95981907844543</v>
+        <v>3.95981955528259</v>
       </c>
       <c r="H212" t="n">
         <v>9000</v>
@@ -6546,7 +6546,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>3.91986608505249</v>
+        <v>3.91986584663391</v>
       </c>
       <c r="H213" t="n">
         <v>11000</v>
@@ -6575,7 +6575,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>3.80888438224792</v>
+        <v>3.80888414382935</v>
       </c>
       <c r="H214" t="n">
         <v>28000</v>
@@ -6633,7 +6633,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G216" t="n">
-        <v>3.91542649269104</v>
+        <v>3.91542625427246</v>
       </c>
       <c r="H216" t="n">
         <v>19000</v>
@@ -6662,7 +6662,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G217" t="n">
-        <v>3.94206190109253</v>
+        <v>3.94206213951111</v>
       </c>
       <c r="H217" t="n">
         <v>13000</v>
@@ -6778,7 +6778,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G221" t="n">
-        <v>4.04860401153564</v>
+        <v>4.0486044883728</v>
       </c>
       <c r="H221" t="n">
         <v>13000</v>
@@ -6807,7 +6807,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G222" t="n">
-        <v>4.06636095046997</v>
+        <v>4.06636142730713</v>
       </c>
       <c r="H222" t="n">
         <v>3000</v>
@@ -6836,7 +6836,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G223" t="n">
-        <v>4.04416465759277</v>
+        <v>4.04416561126709</v>
       </c>
       <c r="H223" t="n">
         <v>17000</v>
@@ -6865,7 +6865,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G224" t="n">
-        <v>4.04860401153564</v>
+        <v>4.0486044883728</v>
       </c>
       <c r="H224" t="n">
         <v>5000</v>
@@ -6894,7 +6894,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>3.95981907844543</v>
+        <v>3.95981955528259</v>
       </c>
       <c r="H225" t="n">
         <v>10000</v>
@@ -6923,7 +6923,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G226" t="n">
-        <v>4.00421237945557</v>
+        <v>4.00421190261841</v>
       </c>
       <c r="H226" t="n">
         <v>2000</v>
@@ -6952,7 +6952,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>3.97313690185547</v>
+        <v>3.97313737869263</v>
       </c>
       <c r="H227" t="n">
         <v>9000</v>
@@ -6981,7 +6981,7 @@
         <v>4.5</v>
       </c>
       <c r="G228" t="n">
-        <v>3.99533295631409</v>
+        <v>3.99533343315125</v>
       </c>
       <c r="H228" t="n">
         <v>7000</v>
@@ -7039,7 +7039,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G230" t="n">
-        <v>3.98645448684692</v>
+        <v>3.9864547252655</v>
       </c>
       <c r="H230" t="n">
         <v>16000</v>
@@ -7068,7 +7068,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G231" t="n">
-        <v>4.06636095046997</v>
+        <v>4.06636142730713</v>
       </c>
       <c r="H231" t="n">
         <v>61000</v>
@@ -7097,7 +7097,7 @@
         <v>4.5</v>
       </c>
       <c r="G232" t="n">
-        <v>3.99533295631409</v>
+        <v>3.99533343315125</v>
       </c>
       <c r="H232" t="n">
         <v>19000</v>
@@ -7126,7 +7126,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G233" t="n">
-        <v>4.04860401153564</v>
+        <v>4.0486044883728</v>
       </c>
       <c r="H233" t="n">
         <v>9000</v>
@@ -7155,7 +7155,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G234" t="n">
-        <v>4.06636095046997</v>
+        <v>4.06636142730713</v>
       </c>
       <c r="H234" t="n">
         <v>13000</v>
@@ -7184,7 +7184,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G235" t="n">
-        <v>4.0841178894043</v>
+        <v>4.08411836624146</v>
       </c>
       <c r="H235" t="n">
         <v>10000</v>
@@ -7358,7 +7358,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>4.3327169418335</v>
+        <v>4.33271741867065</v>
       </c>
       <c r="H241" t="n">
         <v>24000</v>
@@ -7387,7 +7387,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G242" t="n">
-        <v>4.41262340545654</v>
+        <v>4.4126238822937</v>
       </c>
       <c r="H242" t="n">
         <v>26000</v>
@@ -7474,7 +7474,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G245" t="n">
-        <v>4.24393177032471</v>
+        <v>4.24393224716187</v>
       </c>
       <c r="H245" t="n">
         <v>12000</v>
@@ -7503,7 +7503,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>4.31052017211914</v>
+        <v>4.3105206489563</v>
       </c>
       <c r="H246" t="n">
         <v>21000</v>
@@ -7532,7 +7532,7 @@
         <v>4.875</v>
       </c>
       <c r="G247" t="n">
-        <v>4.32827711105347</v>
+        <v>4.32827758789062</v>
       </c>
       <c r="H247" t="n">
         <v>9000</v>
@@ -7619,7 +7619,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G250" t="n">
-        <v>4.297203540802</v>
+        <v>4.29720306396484</v>
       </c>
       <c r="H250" t="n">
         <v>11000</v>
@@ -7706,7 +7706,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G253" t="n">
-        <v>3.8621551990509</v>
+        <v>3.86215496063232</v>
       </c>
       <c r="H253" t="n">
         <v>21000</v>
@@ -7735,7 +7735,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G254" t="n">
-        <v>3.88879084587097</v>
+        <v>3.88879108428955</v>
       </c>
       <c r="H254" t="n">
         <v>21000</v>
@@ -7793,7 +7793,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>4.06636095046997</v>
+        <v>4.06636142730713</v>
       </c>
       <c r="H256" t="n">
         <v>12000</v>
@@ -7822,7 +7822,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>4.28832387924194</v>
+        <v>4.2883243560791</v>
       </c>
       <c r="H257" t="n">
         <v>48000</v>
@@ -7967,7 +7967,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G262" t="n">
-        <v>4.08855772018433</v>
+        <v>4.08855819702148</v>
       </c>
       <c r="H262" t="n">
         <v>17000</v>
@@ -8083,7 +8083,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>4.04416465759277</v>
+        <v>4.04416561126709</v>
       </c>
       <c r="H266" t="n">
         <v>23000</v>
@@ -8112,7 +8112,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>4.0841178894043</v>
+        <v>4.08411836624146</v>
       </c>
       <c r="H267" t="n">
         <v>3000</v>
@@ -8170,7 +8170,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G269" t="n">
-        <v>3.94206190109253</v>
+        <v>3.94206213951111</v>
       </c>
       <c r="H269" t="n">
         <v>21000</v>
@@ -8199,7 +8199,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>3.9065477848053</v>
+        <v>3.90654802322388</v>
       </c>
       <c r="H270" t="n">
         <v>13000</v>
@@ -8257,7 +8257,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>3.95981907844543</v>
+        <v>3.95981955528259</v>
       </c>
       <c r="H272" t="n">
         <v>11000</v>
@@ -8286,7 +8286,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>3.99089384078979</v>
+        <v>3.99089431762695</v>
       </c>
       <c r="H273" t="n">
         <v>16000</v>
@@ -8315,7 +8315,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G274" t="n">
-        <v>3.95537972450256</v>
+        <v>3.95537996292114</v>
       </c>
       <c r="H274" t="n">
         <v>2000</v>
@@ -8344,7 +8344,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G275" t="n">
-        <v>3.89766955375671</v>
+        <v>3.89766931533813</v>
       </c>
       <c r="H275" t="n">
         <v>17000</v>
@@ -8373,7 +8373,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G276" t="n">
-        <v>3.84439826011658</v>
+        <v>3.844398021698</v>
       </c>
       <c r="H276" t="n">
         <v>17000</v>
@@ -8402,7 +8402,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>3.84883785247803</v>
+        <v>3.84883761405945</v>
       </c>
       <c r="H277" t="n">
         <v>9000</v>
@@ -8431,7 +8431,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G278" t="n">
-        <v>3.84883785247803</v>
+        <v>3.84883761405945</v>
       </c>
       <c r="H278" t="n">
         <v>4000</v>
@@ -8460,7 +8460,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G279" t="n">
-        <v>3.81776261329651</v>
+        <v>3.81776285171509</v>
       </c>
       <c r="H279" t="n">
         <v>3000</v>
@@ -8576,7 +8576,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G283" t="n">
-        <v>3.81776261329651</v>
+        <v>3.81776285171509</v>
       </c>
       <c r="H283" t="n">
         <v>2000</v>
@@ -8605,7 +8605,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G284" t="n">
-        <v>3.80444502830505</v>
+        <v>3.80444478988647</v>
       </c>
       <c r="H284" t="n">
         <v>10000</v>
@@ -8779,7 +8779,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G290" t="n">
-        <v>3.58692169189453</v>
+        <v>3.58692121505737</v>
       </c>
       <c r="H290" t="n">
         <v>3000</v>
@@ -8808,7 +8808,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G291" t="n">
-        <v>3.71122074127197</v>
+        <v>3.71122050285339</v>
       </c>
       <c r="H291" t="n">
         <v>14000</v>
@@ -8837,7 +8837,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G292" t="n">
-        <v>3.80888438224792</v>
+        <v>3.80888414382935</v>
       </c>
       <c r="H292" t="n">
         <v>14000</v>
@@ -8866,7 +8866,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G293" t="n">
-        <v>3.82220220565796</v>
+        <v>3.82220196723938</v>
       </c>
       <c r="H293" t="n">
         <v>28000</v>
@@ -8895,7 +8895,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G294" t="n">
-        <v>3.81776261329651</v>
+        <v>3.81776285171509</v>
       </c>
       <c r="H294" t="n">
         <v>6000</v>
@@ -8982,7 +8982,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G297" t="n">
-        <v>3.72453856468201</v>
+        <v>3.72453880310059</v>
       </c>
       <c r="H297" t="n">
         <v>3000</v>
@@ -9040,7 +9040,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>3.58692169189453</v>
+        <v>3.58692121505737</v>
       </c>
       <c r="H299" t="n">
         <v>25000</v>
@@ -9069,7 +9069,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G300" t="n">
-        <v>3.59136080741882</v>
+        <v>3.59136056900024</v>
       </c>
       <c r="H300" t="n">
         <v>6000</v>
@@ -9098,7 +9098,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G301" t="n">
-        <v>3.50701451301575</v>
+        <v>3.50701475143433</v>
       </c>
       <c r="H301" t="n">
         <v>10000</v>
@@ -9127,7 +9127,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G302" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59579992294312</v>
       </c>
       <c r="H302" t="n">
         <v>6000</v>
@@ -9156,7 +9156,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G303" t="n">
-        <v>3.63131427764893</v>
+        <v>3.63131403923035</v>
       </c>
       <c r="H303" t="n">
         <v>5000</v>
@@ -9185,7 +9185,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G304" t="n">
-        <v>3.65794968605042</v>
+        <v>3.65794944763184</v>
       </c>
       <c r="H304" t="n">
         <v>1000</v>
@@ -9243,7 +9243,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G306" t="n">
-        <v>3.57804322242737</v>
+        <v>3.57804298400879</v>
       </c>
       <c r="H306" t="n">
         <v>6000</v>
@@ -9272,7 +9272,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G307" t="n">
-        <v>3.62243556976318</v>
+        <v>3.6224353313446</v>
       </c>
       <c r="H307" t="n">
         <v>16000</v>
@@ -9301,7 +9301,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>3.60911798477173</v>
+        <v>3.60911774635315</v>
       </c>
       <c r="H308" t="n">
         <v>4000</v>
@@ -9330,7 +9330,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>3.58692169189453</v>
+        <v>3.58692121505737</v>
       </c>
       <c r="H309" t="n">
         <v>2000</v>
@@ -9417,7 +9417,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G312" t="n">
-        <v>3.46262192726135</v>
+        <v>3.46262216567993</v>
       </c>
       <c r="H312" t="n">
         <v>4000</v>
@@ -9504,7 +9504,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G315" t="n">
-        <v>3.33388376235962</v>
+        <v>3.33388352394104</v>
       </c>
       <c r="H315" t="n">
         <v>16000</v>
@@ -9591,7 +9591,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G318" t="n">
-        <v>3.19626641273499</v>
+        <v>3.19626665115356</v>
       </c>
       <c r="H318" t="n">
         <v>6000</v>
@@ -9620,7 +9620,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>3.19626641273499</v>
+        <v>3.19626665115356</v>
       </c>
       <c r="H319" t="n">
         <v>1000</v>
@@ -9707,7 +9707,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G322" t="n">
-        <v>3.16519212722778</v>
+        <v>3.1651918888092</v>
       </c>
       <c r="H322" t="n">
         <v>4000</v>
@@ -9736,7 +9736,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>3.24065899848938</v>
+        <v>3.24065923690796</v>
       </c>
       <c r="H323" t="n">
         <v>3000</v>
@@ -9794,7 +9794,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>3.19626641273499</v>
+        <v>3.19626665115356</v>
       </c>
       <c r="H325" t="n">
         <v>8000</v>
@@ -9852,7 +9852,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G327" t="n">
-        <v>3.19626641273499</v>
+        <v>3.19626665115356</v>
       </c>
       <c r="H327" t="n">
         <v>6000</v>
@@ -9910,7 +9910,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G329" t="n">
-        <v>3.17407035827637</v>
+        <v>3.17407059669495</v>
       </c>
       <c r="H329" t="n">
         <v>5000</v>
@@ -9968,7 +9968,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G331" t="n">
-        <v>3.42710781097412</v>
+        <v>3.4271080493927</v>
       </c>
       <c r="H331" t="n">
         <v>21000</v>
@@ -9997,7 +9997,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G332" t="n">
-        <v>3.50701451301575</v>
+        <v>3.50701475143433</v>
       </c>
       <c r="H332" t="n">
         <v>20000</v>
@@ -10055,7 +10055,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>3.46262192726135</v>
+        <v>3.46262216567993</v>
       </c>
       <c r="H334" t="n">
         <v>5000</v>
@@ -10084,7 +10084,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>3.46262192726135</v>
+        <v>3.46262216567993</v>
       </c>
       <c r="H335" t="n">
         <v>11000</v>
@@ -10113,7 +10113,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>3.38271522521973</v>
+        <v>3.38271546363831</v>
       </c>
       <c r="H336" t="n">
         <v>4000</v>
@@ -10142,7 +10142,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>3.43598628044128</v>
+        <v>3.43598651885986</v>
       </c>
       <c r="H337" t="n">
         <v>6000</v>
@@ -10171,7 +10171,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G338" t="n">
-        <v>3.37827634811401</v>
+        <v>3.37827610969543</v>
       </c>
       <c r="H338" t="n">
         <v>5000</v>
@@ -10345,7 +10345,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G344" t="n">
-        <v>3.57804322242737</v>
+        <v>3.57804298400879</v>
       </c>
       <c r="H344" t="n">
         <v>8000</v>
@@ -10374,7 +10374,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59579992294312</v>
       </c>
       <c r="H345" t="n">
         <v>7000</v>
@@ -10432,7 +10432,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G347" t="n">
-        <v>3.81776261329651</v>
+        <v>3.81776285171509</v>
       </c>
       <c r="H347" t="n">
         <v>29000</v>
@@ -10664,7 +10664,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G355" t="n">
-        <v>3.91542649269104</v>
+        <v>3.91542625427246</v>
       </c>
       <c r="H355" t="n">
         <v>77000</v>
@@ -10693,7 +10693,7 @@
         <v>4.5</v>
       </c>
       <c r="G356" t="n">
-        <v>3.99533295631409</v>
+        <v>3.99533343315125</v>
       </c>
       <c r="H356" t="n">
         <v>22000</v>
@@ -10722,7 +10722,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>3.97313690185547</v>
+        <v>3.97313737869263</v>
       </c>
       <c r="H357" t="n">
         <v>25000</v>
@@ -10751,7 +10751,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G358" t="n">
-        <v>3.99977278709412</v>
+        <v>3.9997730255127</v>
       </c>
       <c r="H358" t="n">
         <v>13000</v>
@@ -10780,7 +10780,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G359" t="n">
-        <v>3.90210866928101</v>
+        <v>3.90210890769958</v>
       </c>
       <c r="H359" t="n">
         <v>11000</v>
@@ -10809,7 +10809,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G360" t="n">
-        <v>3.9065477848053</v>
+        <v>3.90654802322388</v>
       </c>
       <c r="H360" t="n">
         <v>11000</v>
@@ -10867,7 +10867,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>3.92874479293823</v>
+        <v>3.92874455451965</v>
       </c>
       <c r="H362" t="n">
         <v>34000</v>
@@ -10896,7 +10896,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>3.98201584815979</v>
+        <v>3.98201608657837</v>
       </c>
       <c r="H363" t="n">
         <v>37000</v>
@@ -10925,7 +10925,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G364" t="n">
-        <v>3.9686975479126</v>
+        <v>3.96869778633118</v>
       </c>
       <c r="H364" t="n">
         <v>5000</v>
@@ -10954,7 +10954,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G365" t="n">
-        <v>3.98645448684692</v>
+        <v>3.9864547252655</v>
       </c>
       <c r="H365" t="n">
         <v>4000</v>
@@ -10983,7 +10983,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G366" t="n">
-        <v>3.99977278709412</v>
+        <v>3.9997730255127</v>
       </c>
       <c r="H366" t="n">
         <v>31000</v>
@@ -11041,7 +11041,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G368" t="n">
-        <v>3.99977278709412</v>
+        <v>3.9997730255127</v>
       </c>
       <c r="H368" t="n">
         <v>61000</v>
@@ -11070,7 +11070,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>3.97313690185547</v>
+        <v>3.97313737869263</v>
       </c>
       <c r="H369" t="n">
         <v>37000</v>
@@ -11099,7 +11099,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>3.85327696800232</v>
+        <v>3.85327672958374</v>
       </c>
       <c r="H370" t="n">
         <v>50000</v>
@@ -11186,7 +11186,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G373" t="n">
-        <v>3.71122074127197</v>
+        <v>3.71122050285339</v>
       </c>
       <c r="H373" t="n">
         <v>18000</v>
@@ -11244,7 +11244,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G375" t="n">
-        <v>3.71122074127197</v>
+        <v>3.71122050285339</v>
       </c>
       <c r="H375" t="n">
         <v>7000</v>
@@ -11331,7 +11331,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G378" t="n">
-        <v>3.63131427764893</v>
+        <v>3.63131403923035</v>
       </c>
       <c r="H378" t="n">
         <v>15000</v>
@@ -11476,7 +11476,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G383" t="n">
-        <v>3.63575315475464</v>
+        <v>3.63575291633606</v>
       </c>
       <c r="H383" t="n">
         <v>39000</v>
@@ -11563,7 +11563,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G386" t="n">
-        <v>3.63131427764893</v>
+        <v>3.63131403923035</v>
       </c>
       <c r="H386" t="n">
         <v>13000</v>
@@ -11592,7 +11592,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G387" t="n">
-        <v>3.63131427764893</v>
+        <v>3.63131403923035</v>
       </c>
       <c r="H387" t="n">
         <v>18000</v>
@@ -11621,7 +11621,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59579992294312</v>
       </c>
       <c r="H388" t="n">
         <v>31000</v>
@@ -11679,7 +11679,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>3.79112720489502</v>
+        <v>3.79112696647644</v>
       </c>
       <c r="H390" t="n">
         <v>21000</v>
@@ -11708,7 +11708,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G391" t="n">
-        <v>3.90210866928101</v>
+        <v>3.90210890769958</v>
       </c>
       <c r="H391" t="n">
         <v>56000</v>
@@ -11737,7 +11737,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G392" t="n">
-        <v>3.75561332702637</v>
+        <v>3.75561308860779</v>
       </c>
       <c r="H392" t="n">
         <v>102000</v>
@@ -11766,7 +11766,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G393" t="n">
-        <v>3.62243556976318</v>
+        <v>3.6224353313446</v>
       </c>
       <c r="H393" t="n">
         <v>30000</v>
@@ -11795,7 +11795,7 @@
         <v>4</v>
       </c>
       <c r="G394" t="n">
-        <v>3.55140733718872</v>
+        <v>3.55140709877014</v>
       </c>
       <c r="H394" t="n">
         <v>26000</v>
@@ -11824,7 +11824,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G395" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59579992294312</v>
       </c>
       <c r="H395" t="n">
         <v>9000</v>
@@ -11853,7 +11853,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G396" t="n">
-        <v>3.56916451454163</v>
+        <v>3.56916427612305</v>
       </c>
       <c r="H396" t="n">
         <v>9000</v>
@@ -11882,7 +11882,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G397" t="n">
-        <v>3.6135573387146</v>
+        <v>3.61355710029602</v>
       </c>
       <c r="H397" t="n">
         <v>22000</v>
@@ -11940,7 +11940,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>3.59136080741882</v>
+        <v>3.59136056900024</v>
       </c>
       <c r="H399" t="n">
         <v>54000</v>
@@ -11998,7 +11998,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G401" t="n">
-        <v>3.57804322242737</v>
+        <v>3.57804298400879</v>
       </c>
       <c r="H401" t="n">
         <v>18000</v>
@@ -12056,7 +12056,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G403" t="n">
-        <v>3.56472516059875</v>
+        <v>3.56472492218018</v>
       </c>
       <c r="H403" t="n">
         <v>20000</v>
@@ -12085,7 +12085,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>3.60911798477173</v>
+        <v>3.60911774635315</v>
       </c>
       <c r="H404" t="n">
         <v>20000</v>
@@ -12114,7 +12114,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G405" t="n">
-        <v>3.53808951377869</v>
+        <v>3.53808927536011</v>
       </c>
       <c r="H405" t="n">
         <v>9000</v>
@@ -12143,7 +12143,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>3.58692169189453</v>
+        <v>3.58692121505737</v>
       </c>
       <c r="H406" t="n">
         <v>10000</v>
@@ -12172,7 +12172,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G407" t="n">
-        <v>3.59580016136169</v>
+        <v>3.59579992294312</v>
       </c>
       <c r="H407" t="n">
         <v>15000</v>
@@ -12288,7 +12288,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G411" t="n">
-        <v>3.58692169189453</v>
+        <v>3.58692121505737</v>
       </c>
       <c r="H411" t="n">
         <v>6000</v>
@@ -12317,7 +12317,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G412" t="n">
-        <v>3.58692169189453</v>
+        <v>3.58692121505737</v>
       </c>
       <c r="H412" t="n">
         <v>10000</v>
@@ -12404,7 +12404,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G415" t="n">
-        <v>3.60911798477173</v>
+        <v>3.60911774635315</v>
       </c>
       <c r="H415" t="n">
         <v>9000</v>
@@ -12462,7 +12462,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G417" t="n">
-        <v>3.64552760124207</v>
+        <v>3.64552783966064</v>
       </c>
       <c r="H417" t="n">
         <v>9000</v>
@@ -12520,7 +12520,7 @@
         <v>4</v>
       </c>
       <c r="G419" t="n">
-        <v>3.6409764289856</v>
+        <v>3.64097619056702</v>
       </c>
       <c r="H419" t="n">
         <v>13000</v>
@@ -12694,7 +12694,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>3.75020575523376</v>
+        <v>3.75020551681519</v>
       </c>
       <c r="H425" t="n">
         <v>18000</v>
@@ -12723,7 +12723,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G426" t="n">
-        <v>3.75930833816528</v>
+        <v>3.7593080997467</v>
       </c>
       <c r="H426" t="n">
         <v>5000</v>
@@ -12926,7 +12926,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G433" t="n">
-        <v>3.70469379425049</v>
+        <v>3.70469355583191</v>
       </c>
       <c r="H433" t="n">
         <v>5000</v>
@@ -12984,7 +12984,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G435" t="n">
-        <v>3.61366891860962</v>
+        <v>3.6136691570282</v>
       </c>
       <c r="H435" t="n">
         <v>6000</v>
@@ -13013,7 +13013,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G436" t="n">
-        <v>3.63187408447266</v>
+        <v>3.63187384605408</v>
       </c>
       <c r="H436" t="n">
         <v>17000</v>
@@ -13042,7 +13042,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G437" t="n">
-        <v>3.75930833816528</v>
+        <v>3.7593080997467</v>
       </c>
       <c r="H437" t="n">
         <v>23000</v>
@@ -13100,7 +13100,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G439" t="n">
-        <v>3.70469379425049</v>
+        <v>3.70469355583191</v>
       </c>
       <c r="H439" t="n">
         <v>20000</v>
@@ -13274,7 +13274,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G445" t="n">
-        <v>3.75020575523376</v>
+        <v>3.75020551681519</v>
       </c>
       <c r="H445" t="n">
         <v>7000</v>
@@ -13361,7 +13361,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G448" t="n">
-        <v>3.80482029914856</v>
+        <v>3.80482006072998</v>
       </c>
       <c r="H448" t="n">
         <v>12000</v>
@@ -13390,7 +13390,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G449" t="n">
-        <v>3.75930833816528</v>
+        <v>3.7593080997467</v>
       </c>
       <c r="H449" t="n">
         <v>17000</v>
@@ -13419,7 +13419,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G450" t="n">
-        <v>3.75020575523376</v>
+        <v>3.75020551681519</v>
       </c>
       <c r="H450" t="n">
         <v>8000</v>
@@ -13477,7 +13477,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G452" t="n">
-        <v>3.75020575523376</v>
+        <v>3.75020551681519</v>
       </c>
       <c r="H452" t="n">
         <v>7000</v>
@@ -13535,7 +13535,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G454" t="n">
-        <v>3.70469379425049</v>
+        <v>3.70469355583191</v>
       </c>
       <c r="H454" t="n">
         <v>25000</v>
@@ -13593,7 +13593,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G456" t="n">
-        <v>3.68648886680603</v>
+        <v>3.68648862838745</v>
       </c>
       <c r="H456" t="n">
         <v>10000</v>
@@ -13651,7 +13651,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>3.68648886680603</v>
+        <v>3.68648862838745</v>
       </c>
       <c r="H458" t="n">
         <v>15000</v>
@@ -13680,7 +13680,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G459" t="n">
-        <v>3.67738628387451</v>
+        <v>3.67738604545593</v>
       </c>
       <c r="H459" t="n">
         <v>6000</v>
@@ -13796,7 +13796,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G463" t="n">
-        <v>3.51354193687439</v>
+        <v>3.51354217529297</v>
       </c>
       <c r="H463" t="n">
         <v>21000</v>
@@ -14637,7 +14637,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>3.39521026611328</v>
+        <v>3.39521050453186</v>
       </c>
       <c r="H492" t="n">
         <v>13000</v>
@@ -14724,7 +14724,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G495" t="n">
-        <v>3.56815671920776</v>
+        <v>3.56815695762634</v>
       </c>
       <c r="H495" t="n">
         <v>69000</v>
@@ -14753,7 +14753,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G496" t="n">
-        <v>3.52264428138733</v>
+        <v>3.52264451980591</v>
       </c>
       <c r="H496" t="n">
         <v>12000</v>
@@ -14811,7 +14811,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G498" t="n">
-        <v>3.52264428138733</v>
+        <v>3.52264451980591</v>
       </c>
       <c r="H498" t="n">
         <v>5000</v>
@@ -15014,7 +15014,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G505" t="n">
-        <v>3.49533700942993</v>
+        <v>3.49533724784851</v>
       </c>
       <c r="H505" t="n">
         <v>5000</v>
@@ -15043,7 +15043,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>3.44982481002808</v>
+        <v>3.44982504844666</v>
       </c>
       <c r="H506" t="n">
         <v>32000</v>
@@ -15362,7 +15362,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G517" t="n">
-        <v>3.34969806671143</v>
+        <v>3.34969830513</v>
       </c>
       <c r="H517" t="n">
         <v>14000</v>
@@ -15565,7 +15565,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G524" t="n">
-        <v>3.30418586730957</v>
+        <v>3.30418610572815</v>
       </c>
       <c r="H524" t="n">
         <v>6000</v>
@@ -15623,7 +15623,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G526" t="n">
-        <v>3.30418586730957</v>
+        <v>3.30418610572815</v>
       </c>
       <c r="H526" t="n">
         <v>2000</v>
@@ -15652,7 +15652,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G527" t="n">
-        <v>3.29508328437805</v>
+        <v>3.29508352279663</v>
       </c>
       <c r="H527" t="n">
         <v>5000</v>
@@ -15681,7 +15681,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>3.29508328437805</v>
+        <v>3.29508352279663</v>
       </c>
       <c r="H528" t="n">
         <v>4000</v>
@@ -16116,7 +16116,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G543" t="n">
-        <v>3.29508328437805</v>
+        <v>3.29508352279663</v>
       </c>
       <c r="H543" t="n">
         <v>21000</v>
@@ -16174,7 +16174,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G545" t="n">
-        <v>3.23136639595032</v>
+        <v>3.2313666343689</v>
       </c>
       <c r="H545" t="n">
         <v>3000</v>
@@ -16203,7 +16203,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G546" t="n">
-        <v>3.17675185203552</v>
+        <v>3.1767520904541</v>
       </c>
       <c r="H546" t="n">
         <v>9000</v>
@@ -16290,7 +16290,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G549" t="n">
-        <v>3.13123965263367</v>
+        <v>3.13123989105225</v>
       </c>
       <c r="H549" t="n">
         <v>15000</v>
@@ -16319,7 +16319,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G550" t="n">
-        <v>3.13123965263367</v>
+        <v>3.13123989105225</v>
       </c>
       <c r="H550" t="n">
         <v>10000</v>
@@ -16348,7 +16348,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G551" t="n">
-        <v>3.17675185203552</v>
+        <v>3.1767520904541</v>
       </c>
       <c r="H551" t="n">
         <v>1000</v>
@@ -16377,7 +16377,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G552" t="n">
-        <v>3.17675185203552</v>
+        <v>3.1767520904541</v>
       </c>
       <c r="H552" t="n">
         <v>1000</v>
@@ -16464,7 +16464,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G555" t="n">
-        <v>3.15854716300964</v>
+        <v>3.15854692459106</v>
       </c>
       <c r="H555" t="n">
         <v>12000</v>
@@ -16638,7 +16638,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G561" t="n">
-        <v>2.62150311470032</v>
+        <v>2.62150287628174</v>
       </c>
       <c r="H561" t="n">
         <v>88000</v>
@@ -16696,7 +16696,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G563" t="n">
-        <v>2.62150311470032</v>
+        <v>2.62150287628174</v>
       </c>
       <c r="H563" t="n">
         <v>98000</v>
@@ -16725,7 +16725,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>2.6397078037262</v>
+        <v>2.63970804214478</v>
       </c>
       <c r="H564" t="n">
         <v>5000</v>
@@ -16754,7 +16754,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G565" t="n">
-        <v>2.66701531410217</v>
+        <v>2.66701507568359</v>
       </c>
       <c r="H565" t="n">
         <v>16000</v>
@@ -16812,7 +16812,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.67611765861511</v>
+        <v>2.67611742019653</v>
       </c>
       <c r="H567" t="n">
         <v>12000</v>
@@ -16957,7 +16957,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G572" t="n">
-        <v>2.54868364334106</v>
+        <v>2.54868340492249</v>
       </c>
       <c r="H572" t="n">
         <v>20000</v>
@@ -17044,7 +17044,7 @@
         <v>2.75</v>
       </c>
       <c r="G575" t="n">
-        <v>2.50317144393921</v>
+        <v>2.50317120552063</v>
       </c>
       <c r="H575" t="n">
         <v>5000</v>
@@ -17102,7 +17102,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>2.54868364334106</v>
+        <v>2.54868340492249</v>
       </c>
       <c r="H577" t="n">
         <v>1000</v>
@@ -17160,7 +17160,7 @@
         <v>2.75</v>
       </c>
       <c r="G579" t="n">
-        <v>2.50317144393921</v>
+        <v>2.50317120552063</v>
       </c>
       <c r="H579" t="n">
         <v>7000</v>
@@ -17363,7 +17363,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G586" t="n">
-        <v>2.54868364334106</v>
+        <v>2.54868340492249</v>
       </c>
       <c r="H586" t="n">
         <v>13000</v>
@@ -17392,7 +17392,7 @@
         <v>2.75</v>
       </c>
       <c r="G587" t="n">
-        <v>2.50317144393921</v>
+        <v>2.50317120552063</v>
       </c>
       <c r="H587" t="n">
         <v>7000</v>
@@ -17537,7 +17537,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G592" t="n">
-        <v>2.45765924453735</v>
+        <v>2.45765900611877</v>
       </c>
       <c r="H592" t="n">
         <v>4000</v>
@@ -17972,7 +17972,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G607" t="n">
-        <v>2.33022499084473</v>
+        <v>2.33022475242615</v>
       </c>
       <c r="H607" t="n">
         <v>3000</v>
@@ -18001,7 +18001,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G608" t="n">
-        <v>2.33022499084473</v>
+        <v>2.33022475242615</v>
       </c>
       <c r="H608" t="n">
         <v>2000</v>
@@ -18117,7 +18117,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G612" t="n">
-        <v>2.40304470062256</v>
+        <v>2.40304446220398</v>
       </c>
       <c r="H612" t="n">
         <v>7000</v>
@@ -18146,7 +18146,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G613" t="n">
-        <v>2.54868364334106</v>
+        <v>2.54868340492249</v>
       </c>
       <c r="H613" t="n">
         <v>9000</v>
@@ -18204,7 +18204,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G615" t="n">
-        <v>2.54868364334106</v>
+        <v>2.54868340492249</v>
       </c>
       <c r="H615" t="n">
         <v>6000</v>
@@ -18262,7 +18262,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G617" t="n">
-        <v>2.54868364334106</v>
+        <v>2.54868340492249</v>
       </c>
       <c r="H617" t="n">
         <v>5000</v>
@@ -18291,7 +18291,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G618" t="n">
-        <v>2.54868364334106</v>
+        <v>2.54868340492249</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18465,7 +18465,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>2.34842991828918</v>
+        <v>2.34842967987061</v>
       </c>
       <c r="H624" t="n">
         <v>4000</v>
@@ -18494,7 +18494,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G625" t="n">
-        <v>2.34842991828918</v>
+        <v>2.34842967987061</v>
       </c>
       <c r="H625" t="n">
         <v>0</v>
@@ -18523,7 +18523,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G626" t="n">
-        <v>2.34842991828918</v>
+        <v>2.34842967987061</v>
       </c>
       <c r="H626" t="n">
         <v>1000</v>
@@ -18639,7 +18639,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G630" t="n">
-        <v>2.45765924453735</v>
+        <v>2.45765900611877</v>
       </c>
       <c r="H630" t="n">
         <v>8000</v>
@@ -18668,7 +18668,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G631" t="n">
-        <v>2.44855690002441</v>
+        <v>2.44855666160583</v>
       </c>
       <c r="H631" t="n">
         <v>6000</v>
@@ -18784,7 +18784,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G635" t="n">
-        <v>2.44855690002441</v>
+        <v>2.44855666160583</v>
       </c>
       <c r="H635" t="n">
         <v>2000</v>
@@ -18813,7 +18813,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G636" t="n">
-        <v>2.44855690002441</v>
+        <v>2.44855666160583</v>
       </c>
       <c r="H636" t="n">
         <v>0</v>
@@ -18900,7 +18900,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G639" t="n">
-        <v>2.18458604812622</v>
+        <v>2.18458580970764</v>
       </c>
       <c r="H639" t="n">
         <v>27000</v>
@@ -18929,7 +18929,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G640" t="n">
-        <v>2.18458604812622</v>
+        <v>2.18458580970764</v>
       </c>
       <c r="H640" t="n">
         <v>5000</v>
@@ -19132,7 +19132,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>2.18458604812622</v>
+        <v>2.18458580970764</v>
       </c>
       <c r="H647" t="n">
         <v>33000</v>
@@ -19161,7 +19161,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G648" t="n">
-        <v>2.16638088226318</v>
+        <v>2.16638112068176</v>
       </c>
       <c r="H648" t="n">
         <v>7000</v>
@@ -19190,7 +19190,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G649" t="n">
-        <v>2.07535624504089</v>
+        <v>2.07535648345947</v>
       </c>
       <c r="H649" t="n">
         <v>31000</v>
@@ -19219,7 +19219,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G650" t="n">
-        <v>2.09356117248535</v>
+        <v>2.09356141090393</v>
       </c>
       <c r="H650" t="n">
         <v>14000</v>
@@ -19306,7 +19306,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G653" t="n">
-        <v>2.19368839263916</v>
+        <v>2.19368815422058</v>
       </c>
       <c r="H653" t="n">
         <v>52000</v>
@@ -19335,7 +19335,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G654" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H654" t="n">
         <v>10000</v>
@@ -19393,7 +19393,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.46676158905029</v>
+        <v>2.46676182746887</v>
       </c>
       <c r="H656" t="n">
         <v>160000</v>
@@ -19422,7 +19422,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G657" t="n">
-        <v>2.54868364334106</v>
+        <v>2.54868340492249</v>
       </c>
       <c r="H657" t="n">
         <v>114000</v>
@@ -19480,7 +19480,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G659" t="n">
-        <v>2.40304470062256</v>
+        <v>2.40304446220398</v>
       </c>
       <c r="H659" t="n">
         <v>20000</v>
@@ -19509,7 +19509,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>2.20279097557068</v>
+        <v>2.2027907371521</v>
       </c>
       <c r="H660" t="n">
         <v>51000</v>
@@ -19567,7 +19567,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>2.15727853775024</v>
+        <v>2.15727829933167</v>
       </c>
       <c r="H662" t="n">
         <v>37000</v>
@@ -19683,7 +19683,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G666" t="n">
-        <v>2.15727853775024</v>
+        <v>2.15727829933167</v>
       </c>
       <c r="H666" t="n">
         <v>3000</v>
@@ -19770,7 +19770,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G669" t="n">
-        <v>2.16638088226318</v>
+        <v>2.16638112068176</v>
       </c>
       <c r="H669" t="n">
         <v>22000</v>
@@ -19799,7 +19799,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>2.18458604812622</v>
+        <v>2.18458580970764</v>
       </c>
       <c r="H670" t="n">
         <v>3000</v>
@@ -19828,7 +19828,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>2.18458604812622</v>
+        <v>2.18458580970764</v>
       </c>
       <c r="H671" t="n">
         <v>5000</v>
@@ -19857,7 +19857,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G672" t="n">
-        <v>2.14817571640015</v>
+        <v>2.14817595481873</v>
       </c>
       <c r="H672" t="n">
         <v>11000</v>
@@ -19973,7 +19973,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H676" t="n">
         <v>12000</v>
@@ -20031,7 +20031,7 @@
         <v>2.25</v>
       </c>
       <c r="G678" t="n">
-        <v>2.0480489730835</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H678" t="n">
         <v>3000</v>
@@ -20060,7 +20060,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G679" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H679" t="n">
         <v>1000</v>
@@ -20089,7 +20089,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G680" t="n">
-        <v>2.07535624504089</v>
+        <v>2.07535648345947</v>
       </c>
       <c r="H680" t="n">
         <v>2000</v>
@@ -20176,7 +20176,7 @@
         <v>2.25</v>
       </c>
       <c r="G683" t="n">
-        <v>2.0480489730835</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H683" t="n">
         <v>2000</v>
@@ -20205,7 +20205,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H684" t="n">
         <v>4000</v>
@@ -20263,7 +20263,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G686" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H686" t="n">
         <v>3000</v>
@@ -20292,7 +20292,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G687" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H687" t="n">
         <v>0</v>
@@ -20321,7 +20321,7 @@
         <v>2.25</v>
       </c>
       <c r="G688" t="n">
-        <v>2.0480489730835</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H688" t="n">
         <v>4000</v>
@@ -20350,7 +20350,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G689" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H689" t="n">
         <v>2000</v>
@@ -20379,7 +20379,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G690" t="n">
-        <v>2.00253677368164</v>
+        <v>2.00253701210022</v>
       </c>
       <c r="H690" t="n">
         <v>2000</v>
@@ -20408,7 +20408,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G691" t="n">
-        <v>1.9661271572113</v>
+        <v>1.96612727642059</v>
       </c>
       <c r="H691" t="n">
         <v>5000</v>
@@ -20437,7 +20437,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G692" t="n">
-        <v>1.9934344291687</v>
+        <v>1.99343466758728</v>
       </c>
       <c r="H692" t="n">
         <v>6000</v>
@@ -20466,7 +20466,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G693" t="n">
-        <v>1.9934344291687</v>
+        <v>1.99343466758728</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -20495,7 +20495,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G694" t="n">
-        <v>1.9934344291687</v>
+        <v>1.99343466758728</v>
       </c>
       <c r="H694" t="n">
         <v>0</v>
@@ -20553,7 +20553,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G696" t="n">
-        <v>2.00253677368164</v>
+        <v>2.00253701210022</v>
       </c>
       <c r="H696" t="n">
         <v>2000</v>
@@ -20756,7 +20756,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G703" t="n">
-        <v>1.90241014957428</v>
+        <v>1.90241003036499</v>
       </c>
       <c r="H703" t="n">
         <v>2000</v>
@@ -20785,7 +20785,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G704" t="n">
-        <v>1.90241014957428</v>
+        <v>1.90241003036499</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -20814,7 +20814,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G705" t="n">
-        <v>1.80683445930481</v>
+        <v>1.8068345785141</v>
       </c>
       <c r="H705" t="n">
         <v>13000</v>
@@ -20843,7 +20843,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G706" t="n">
-        <v>1.61568319797516</v>
+        <v>1.61568331718445</v>
       </c>
       <c r="H706" t="n">
         <v>35000</v>
@@ -20872,7 +20872,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G707" t="n">
-        <v>1.67484903335571</v>
+        <v>1.674849152565</v>
       </c>
       <c r="H707" t="n">
         <v>25000</v>
@@ -20901,7 +20901,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>1.72491240501404</v>
+        <v>1.72491252422333</v>
       </c>
       <c r="H708" t="n">
         <v>4000</v>
@@ -20930,7 +20930,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G709" t="n">
-        <v>1.69760513305664</v>
+        <v>1.69760525226593</v>
       </c>
       <c r="H709" t="n">
         <v>7000</v>
@@ -20959,7 +20959,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G710" t="n">
-        <v>1.73856604099274</v>
+        <v>1.73856616020203</v>
       </c>
       <c r="H710" t="n">
         <v>5000</v>
@@ -20988,7 +20988,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G711" t="n">
-        <v>1.77497589588165</v>
+        <v>1.77497601509094</v>
       </c>
       <c r="H711" t="n">
         <v>8000</v>
@@ -21133,7 +21133,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G716" t="n">
-        <v>1.73856604099274</v>
+        <v>1.73856616020203</v>
       </c>
       <c r="H716" t="n">
         <v>14000</v>
@@ -21162,7 +21162,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G717" t="n">
-        <v>1.76132214069366</v>
+        <v>1.76132225990295</v>
       </c>
       <c r="H717" t="n">
         <v>1000</v>
@@ -21191,7 +21191,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G718" t="n">
-        <v>1.73856604099274</v>
+        <v>1.73856616020203</v>
       </c>
       <c r="H718" t="n">
         <v>2000</v>
@@ -21278,7 +21278,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G721" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H721" t="n">
         <v>2000</v>
@@ -21307,7 +21307,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G722" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H722" t="n">
         <v>0</v>
@@ -21336,7 +21336,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G723" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H723" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G724" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H724" t="n">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G736" t="n">
-        <v>1.64754164218903</v>
+        <v>1.64754176139832</v>
       </c>
       <c r="H736" t="n">
         <v>5000</v>
@@ -21742,7 +21742,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G737" t="n">
-        <v>1.66574668884277</v>
+        <v>1.66574656963348</v>
       </c>
       <c r="H737" t="n">
         <v>2000</v>
@@ -21771,7 +21771,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G738" t="n">
-        <v>1.66574668884277</v>
+        <v>1.66574656963348</v>
       </c>
       <c r="H738" t="n">
         <v>8000</v>
@@ -21829,7 +21829,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G740" t="n">
-        <v>2.12086844444275</v>
+        <v>2.12086868286133</v>
       </c>
       <c r="H740" t="n">
         <v>43000</v>
@@ -21858,7 +21858,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G741" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H741" t="n">
         <v>81000</v>
@@ -21945,7 +21945,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G744" t="n">
-        <v>1.9661271572113</v>
+        <v>1.96612727642059</v>
       </c>
       <c r="H744" t="n">
         <v>12000</v>
@@ -22032,7 +22032,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G747" t="n">
-        <v>1.9934344291687</v>
+        <v>1.99343466758728</v>
       </c>
       <c r="H747" t="n">
         <v>12000</v>
@@ -22264,7 +22264,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G755" t="n">
-        <v>1.90241014957428</v>
+        <v>1.90241003036499</v>
       </c>
       <c r="H755" t="n">
         <v>3000</v>
@@ -22322,7 +22322,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G757" t="n">
-        <v>1.90241014957428</v>
+        <v>1.90241003036499</v>
       </c>
       <c r="H757" t="n">
         <v>3000</v>
@@ -22525,7 +22525,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G764" t="n">
-        <v>2.14817571640015</v>
+        <v>2.14817595481873</v>
       </c>
       <c r="H764" t="n">
         <v>1000</v>
@@ -22554,7 +22554,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G765" t="n">
-        <v>2.14817571640015</v>
+        <v>2.14817595481873</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G766" t="n">
-        <v>2.09356117248535</v>
+        <v>2.09356141090393</v>
       </c>
       <c r="H766" t="n">
         <v>3000</v>
@@ -22612,7 +22612,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>2.09356117248535</v>
+        <v>2.09356141090393</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -22641,7 +22641,7 @@
         <v>2.25</v>
       </c>
       <c r="G768" t="n">
-        <v>2.0480489730835</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H768" t="n">
         <v>1000</v>
@@ -22670,7 +22670,7 @@
         <v>2.25</v>
       </c>
       <c r="G769" t="n">
-        <v>2.0480489730835</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H769" t="n">
         <v>0</v>
@@ -22699,7 +22699,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G770" t="n">
-        <v>2.00253677368164</v>
+        <v>2.00253701210022</v>
       </c>
       <c r="H770" t="n">
         <v>1000</v>
@@ -22728,7 +22728,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G771" t="n">
-        <v>2.00253677368164</v>
+        <v>2.00253701210022</v>
       </c>
       <c r="H771" t="n">
         <v>0</v>
@@ -22873,7 +22873,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>2.09356117248535</v>
+        <v>2.09356141090393</v>
       </c>
       <c r="H776" t="n">
         <v>3000</v>
@@ -22902,7 +22902,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G777" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H777" t="n">
         <v>7000</v>
@@ -22931,7 +22931,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G778" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H778" t="n">
         <v>0</v>
@@ -23047,7 +23047,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G782" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H782" t="n">
         <v>6000</v>
@@ -23076,7 +23076,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G783" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H783" t="n">
         <v>5000</v>
@@ -23105,7 +23105,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G784" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H784" t="n">
         <v>0</v>
@@ -23134,7 +23134,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G785" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H785" t="n">
         <v>0</v>
@@ -23163,7 +23163,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G786" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H786" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G787" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H787" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G788" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H788" t="n">
         <v>0</v>
@@ -23250,7 +23250,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G789" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H789" t="n">
         <v>0</v>
@@ -23279,7 +23279,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G790" t="n">
-        <v>2.03894662857056</v>
+        <v>2.03894686698914</v>
       </c>
       <c r="H790" t="n">
         <v>0</v>
@@ -23308,7 +23308,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G791" t="n">
-        <v>1.9934344291687</v>
+        <v>1.99343466758728</v>
       </c>
       <c r="H791" t="n">
         <v>2000</v>
@@ -23424,7 +23424,7 @@
         <v>2.25</v>
       </c>
       <c r="G795" t="n">
-        <v>2.0480489730835</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H795" t="n">
         <v>1000</v>
@@ -23453,7 +23453,7 @@
         <v>2.25</v>
       </c>
       <c r="G796" t="n">
-        <v>2.0480489730835</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H796" t="n">
         <v>0</v>
@@ -23482,7 +23482,7 @@
         <v>2.25</v>
       </c>
       <c r="G797" t="n">
-        <v>2.0480489730835</v>
+        <v>2.04804921150208</v>
       </c>
       <c r="H797" t="n">
         <v>0</v>
@@ -23540,7 +23540,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G799" t="n">
-        <v>1.9934344291687</v>
+        <v>1.99343466758728</v>
       </c>
       <c r="H799" t="n">
         <v>2000</v>
@@ -23569,7 +23569,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G800" t="n">
-        <v>1.95702469348907</v>
+        <v>1.95702481269836</v>
       </c>
       <c r="H800" t="n">
         <v>5000</v>
@@ -23685,7 +23685,7 @@
         <v>2</v>
       </c>
       <c r="G804" t="n">
-        <v>1.8204882144928</v>
+        <v>1.82048809528351</v>
       </c>
       <c r="H804" t="n">
         <v>3000</v>
@@ -23714,7 +23714,7 @@
         <v>2</v>
       </c>
       <c r="G805" t="n">
-        <v>1.8204882144928</v>
+        <v>1.82048809528351</v>
       </c>
       <c r="H805" t="n">
         <v>0</v>
@@ -23801,7 +23801,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G808" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H808" t="n">
         <v>9000</v>
@@ -23830,7 +23830,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G809" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H809" t="n">
         <v>0</v>
@@ -23917,7 +23917,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G812" t="n">
-        <v>1.87510287761688</v>
+        <v>1.87510275840759</v>
       </c>
       <c r="H812" t="n">
         <v>4000</v>
@@ -24091,7 +24091,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G818" t="n">
-        <v>1.90241014957428</v>
+        <v>1.90241003036499</v>
       </c>
       <c r="H818" t="n">
         <v>2000</v>
@@ -24149,7 +24149,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G820" t="n">
-        <v>1.77952718734741</v>
+        <v>1.7795273065567</v>
       </c>
       <c r="H820" t="n">
         <v>8000</v>
@@ -24265,7 +24265,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>1.78407835960388</v>
+        <v>1.78407847881317</v>
       </c>
       <c r="H824" t="n">
         <v>1000</v>
@@ -24294,7 +24294,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>1.78407835960388</v>
+        <v>1.78407847881317</v>
       </c>
       <c r="H825" t="n">
         <v>0</v>
@@ -24323,7 +24323,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G826" t="n">
-        <v>1.78407835960388</v>
+        <v>1.78407847881317</v>
       </c>
       <c r="H826" t="n">
         <v>0</v>
@@ -24352,7 +24352,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>1.78407835960388</v>
+        <v>1.78407847881317</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -24381,7 +24381,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>1.78407835960388</v>
+        <v>1.78407847881317</v>
       </c>
       <c r="H828" t="n">
         <v>0</v>
@@ -24410,7 +24410,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G829" t="n">
-        <v>1.75677096843719</v>
+        <v>1.75677108764648</v>
       </c>
       <c r="H829" t="n">
         <v>1000</v>
@@ -24526,7 +24526,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.72491240501404</v>
+        <v>1.72491252422333</v>
       </c>
       <c r="H833" t="n">
         <v>5000</v>
@@ -24642,7 +24642,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G837" t="n">
-        <v>1.66574668884277</v>
+        <v>1.66574656963348</v>
       </c>
       <c r="H837" t="n">
         <v>1000</v>
@@ -24671,7 +24671,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G838" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H838" t="n">
         <v>15000</v>
@@ -24903,7 +24903,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G846" t="n">
-        <v>1.80228328704834</v>
+        <v>1.80228340625763</v>
       </c>
       <c r="H846" t="n">
         <v>7000</v>
@@ -24990,7 +24990,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G849" t="n">
-        <v>1.78407835960388</v>
+        <v>1.78407847881317</v>
       </c>
       <c r="H849" t="n">
         <v>9000</v>
@@ -25019,7 +25019,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G850" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H850" t="n">
         <v>8000</v>
@@ -25106,7 +25106,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G853" t="n">
-        <v>1.81593704223633</v>
+        <v>1.81593692302704</v>
       </c>
       <c r="H853" t="n">
         <v>3000</v>
@@ -25135,7 +25135,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G854" t="n">
-        <v>1.80683445930481</v>
+        <v>1.8068345785141</v>
       </c>
       <c r="H854" t="n">
         <v>1000</v>
@@ -25193,7 +25193,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G856" t="n">
-        <v>1.76132214069366</v>
+        <v>1.76132225990295</v>
       </c>
       <c r="H856" t="n">
         <v>1000</v>
@@ -25222,7 +25222,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G857" t="n">
-        <v>1.76132214069366</v>
+        <v>1.76132225990295</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -25280,7 +25280,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G859" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H859" t="n">
         <v>7000</v>
@@ -25309,7 +25309,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G860" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H860" t="n">
         <v>0</v>
@@ -25396,7 +25396,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G863" t="n">
-        <v>1.73401486873627</v>
+        <v>1.73401498794556</v>
       </c>
       <c r="H863" t="n">
         <v>2000</v>
@@ -25541,7 +25541,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G868" t="n">
-        <v>1.67484903335571</v>
+        <v>1.674849152565</v>
       </c>
       <c r="H868" t="n">
         <v>4000</v>
@@ -25570,7 +25570,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G869" t="n">
-        <v>1.64754164218903</v>
+        <v>1.64754176139832</v>
       </c>
       <c r="H869" t="n">
         <v>7000</v>
@@ -25715,7 +25715,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G874" t="n">
-        <v>1.66574668884277</v>
+        <v>1.66574656963348</v>
       </c>
       <c r="H874" t="n">
         <v>7000</v>
@@ -25744,7 +25744,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>1.72491240501404</v>
+        <v>1.72491252422333</v>
       </c>
       <c r="H875" t="n">
         <v>3000</v>
@@ -25831,7 +25831,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G878" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H878" t="n">
         <v>9000</v>
@@ -25947,7 +25947,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G882" t="n">
-        <v>1.78407835960388</v>
+        <v>1.78407847881317</v>
       </c>
       <c r="H882" t="n">
         <v>12000</v>
@@ -26121,7 +26121,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G888" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H888" t="n">
         <v>20000</v>
@@ -26179,7 +26179,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G890" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H890" t="n">
         <v>9000</v>
@@ -26382,7 +26382,7 @@
         <v>2</v>
       </c>
       <c r="G897" t="n">
-        <v>1.8204882144928</v>
+        <v>1.82048809528351</v>
       </c>
       <c r="H897" t="n">
         <v>10000</v>
@@ -26469,7 +26469,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G900" t="n">
-        <v>1.80228328704834</v>
+        <v>1.80228340625763</v>
       </c>
       <c r="H900" t="n">
         <v>1000</v>
@@ -26498,7 +26498,7 @@
         <v>2</v>
       </c>
       <c r="G901" t="n">
-        <v>1.8204882144928</v>
+        <v>1.82048809528351</v>
       </c>
       <c r="H901" t="n">
         <v>1000</v>
@@ -26672,7 +26672,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>1.80228328704834</v>
+        <v>1.80228340625763</v>
       </c>
       <c r="H907" t="n">
         <v>2000</v>
@@ -26701,7 +26701,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G908" t="n">
-        <v>1.81593704223633</v>
+        <v>1.81593692302704</v>
       </c>
       <c r="H908" t="n">
         <v>6000</v>
@@ -26730,7 +26730,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G909" t="n">
-        <v>1.80228328704834</v>
+        <v>1.80228340625763</v>
       </c>
       <c r="H909" t="n">
         <v>7000</v>
@@ -26788,7 +26788,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G911" t="n">
-        <v>1.78407835960388</v>
+        <v>1.78407847881317</v>
       </c>
       <c r="H911" t="n">
         <v>2000</v>
@@ -26817,7 +26817,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G912" t="n">
-        <v>1.78407835960388</v>
+        <v>1.78407847881317</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -26846,7 +26846,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G913" t="n">
-        <v>1.78407835960388</v>
+        <v>1.78407847881317</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -26875,7 +26875,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G914" t="n">
-        <v>1.80683445930481</v>
+        <v>1.8068345785141</v>
       </c>
       <c r="H914" t="n">
         <v>3000</v>
@@ -26904,7 +26904,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G915" t="n">
-        <v>1.80683445930481</v>
+        <v>1.8068345785141</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -26933,7 +26933,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G916" t="n">
-        <v>1.80683445930481</v>
+        <v>1.8068345785141</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -26962,7 +26962,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G917" t="n">
-        <v>1.80683445930481</v>
+        <v>1.8068345785141</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -26991,7 +26991,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>1.76132214069366</v>
+        <v>1.76132225990295</v>
       </c>
       <c r="H918" t="n">
         <v>7000</v>
@@ -27020,7 +27020,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G919" t="n">
-        <v>1.74766850471497</v>
+        <v>1.74766862392426</v>
       </c>
       <c r="H919" t="n">
         <v>1000</v>
@@ -27049,7 +27049,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G920" t="n">
-        <v>1.75677096843719</v>
+        <v>1.75677108764648</v>
       </c>
       <c r="H920" t="n">
         <v>2000</v>
@@ -27136,7 +27136,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G923" t="n">
-        <v>1.76132214069366</v>
+        <v>1.76132225990295</v>
       </c>
       <c r="H923" t="n">
         <v>5000</v>
@@ -27165,7 +27165,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G924" t="n">
-        <v>1.77952718734741</v>
+        <v>1.7795273065567</v>
       </c>
       <c r="H924" t="n">
         <v>3000</v>
@@ -27194,7 +27194,7 @@
         <v>2</v>
       </c>
       <c r="G925" t="n">
-        <v>1.8204882144928</v>
+        <v>1.82048809528351</v>
       </c>
       <c r="H925" t="n">
         <v>3000</v>
@@ -27223,7 +27223,7 @@
         <v>2</v>
       </c>
       <c r="G926" t="n">
-        <v>1.8204882144928</v>
+        <v>1.82048809528351</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -27252,7 +27252,7 @@
         <v>2</v>
       </c>
       <c r="G927" t="n">
-        <v>1.8204882144928</v>
+        <v>1.82048809528351</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>2</v>
       </c>
       <c r="G935" t="n">
-        <v>1.8204882144928</v>
+        <v>1.82048809528351</v>
       </c>
       <c r="H935" t="n">
         <v>3000</v>
@@ -27571,7 +27571,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G938" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H938" t="n">
         <v>1000</v>
@@ -27629,7 +27629,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G940" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H940" t="n">
         <v>6000</v>
@@ -27658,7 +27658,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>1.80228328704834</v>
+        <v>1.80228340625763</v>
       </c>
       <c r="H941" t="n">
         <v>2000</v>
@@ -27687,7 +27687,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G942" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H942" t="n">
         <v>2000</v>
@@ -27716,7 +27716,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G943" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -27745,7 +27745,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G944" t="n">
-        <v>1.87510287761688</v>
+        <v>1.87510275840759</v>
       </c>
       <c r="H944" t="n">
         <v>1000</v>
@@ -27774,7 +27774,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G945" t="n">
-        <v>1.87510287761688</v>
+        <v>1.87510275840759</v>
       </c>
       <c r="H945" t="n">
         <v>0</v>
@@ -27803,7 +27803,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G946" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H946" t="n">
         <v>2000</v>
@@ -27832,7 +27832,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G947" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -27861,7 +27861,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G948" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H948" t="n">
         <v>12000</v>
@@ -27890,7 +27890,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H949" t="n">
         <v>1000</v>
@@ -27919,7 +27919,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G950" t="n">
-        <v>1.80228328704834</v>
+        <v>1.80228340625763</v>
       </c>
       <c r="H950" t="n">
         <v>2000</v>
@@ -27948,7 +27948,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G951" t="n">
-        <v>1.80228328704834</v>
+        <v>1.80228340625763</v>
       </c>
       <c r="H951" t="n">
         <v>1000</v>
@@ -28006,7 +28006,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G953" t="n">
-        <v>1.80228328704834</v>
+        <v>1.80228340625763</v>
       </c>
       <c r="H953" t="n">
         <v>5000</v>
@@ -28035,7 +28035,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G954" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H954" t="n">
         <v>2000</v>
@@ -28093,7 +28093,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G956" t="n">
-        <v>1.83869314193726</v>
+        <v>1.83869302272797</v>
       </c>
       <c r="H956" t="n">
         <v>2000</v>
@@ -28122,7 +28122,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G957" t="n">
-        <v>1.80228328704834</v>
+        <v>1.80228340625763</v>
       </c>
       <c r="H957" t="n">
         <v>1000</v>
@@ -28383,7 +28383,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G966" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H966" t="n">
         <v>18000</v>
@@ -28412,7 +28412,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G967" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H967" t="n">
         <v>13000</v>
@@ -29021,7 +29021,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G988" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H988" t="n">
         <v>3000</v>
@@ -29050,7 +29050,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G989" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H989" t="n">
         <v>0</v>
@@ -29079,7 +29079,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G990" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -29311,7 +29311,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G998" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H998" t="n">
         <v>2000</v>
@@ -29340,7 +29340,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G999" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -29398,7 +29398,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1001" t="n">
         <v>2000</v>
@@ -29427,7 +29427,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1002" t="n">
         <v>0</v>
@@ -29601,7 +29601,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1008" t="n">
         <v>14000</v>
@@ -29630,7 +29630,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -29659,7 +29659,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -29688,7 +29688,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -29717,7 +29717,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1012" t="n">
         <v>3000</v>
@@ -29746,7 +29746,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1013" t="n">
         <v>4000</v>
@@ -29775,7 +29775,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -29862,7 +29862,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1017" t="n">
         <v>1000</v>
@@ -29891,7 +29891,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -29920,7 +29920,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1019" t="n">
         <v>1000</v>
@@ -29949,7 +29949,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1020" t="n">
         <v>5000</v>
@@ -29978,7 +29978,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1021" t="n">
         <v>1000</v>
@@ -30007,7 +30007,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1022" t="n">
         <v>0</v>
@@ -30036,7 +30036,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1023" t="n">
         <v>1000</v>
@@ -30065,7 +30065,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1024" t="n">
         <v>2000</v>
@@ -30094,7 +30094,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1025" t="n">
         <v>14000</v>
@@ -30123,7 +30123,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1026" t="n">
         <v>5000</v>
@@ -30384,7 +30384,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1035" t="n">
         <v>5000</v>
@@ -30413,7 +30413,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -30442,7 +30442,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1037" t="n">
         <v>1000</v>
@@ -30500,7 +30500,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1039" t="n">
         <v>5000</v>
@@ -30529,7 +30529,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1040" t="n">
         <v>3000</v>
@@ -30558,7 +30558,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1041" t="n">
         <v>2000</v>
@@ -30587,7 +30587,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -30616,7 +30616,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1043" t="n">
         <v>1000</v>
@@ -30732,7 +30732,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1047" t="n">
         <v>3000</v>
@@ -30761,7 +30761,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1048" t="n">
         <v>3000</v>
@@ -30790,7 +30790,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1049" t="n">
         <v>0</v>
@@ -30848,7 +30848,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1051" t="n">
         <v>3000</v>
@@ -30877,7 +30877,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -30906,7 +30906,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1053" t="n">
         <v>0</v>
@@ -30935,7 +30935,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1054" t="n">
         <v>2000</v>
@@ -31080,7 +31080,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1059" t="n">
         <v>12000</v>
@@ -31109,7 +31109,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1060" t="n">
         <v>2000</v>
@@ -31138,7 +31138,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1061" t="n">
         <v>2000</v>
@@ -31167,7 +31167,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1062" t="n">
         <v>4000</v>
@@ -31196,7 +31196,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1063" t="n">
         <v>3000</v>
@@ -31225,7 +31225,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1064" t="n">
         <v>6000</v>
@@ -31312,7 +31312,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1067" t="n">
         <v>11000</v>
@@ -31341,7 +31341,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1068" t="n">
         <v>2000</v>
@@ -31370,7 +31370,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1069" t="n">
         <v>10000</v>
@@ -31399,7 +31399,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1070" t="n">
         <v>12000</v>
@@ -31428,7 +31428,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.62191653251648</v>
+        <v>1.62191641330719</v>
       </c>
       <c r="H1071" t="n">
         <v>3000</v>
@@ -31457,7 +31457,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1072" t="n">
         <v>1000</v>
@@ -31486,7 +31486,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1073" t="n">
         <v>0</v>
@@ -31515,7 +31515,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1074" t="n">
         <v>0</v>
@@ -31631,7 +31631,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1078" t="n">
         <v>5000</v>
@@ -31863,7 +31863,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1086" t="n">
         <v>6000</v>
@@ -31892,7 +31892,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1087" t="n">
         <v>3000</v>
@@ -32037,7 +32037,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1092" t="n">
         <v>12000</v>
@@ -32066,7 +32066,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.52594518661499</v>
+        <v>1.5259450674057</v>
       </c>
       <c r="H1093" t="n">
         <v>5000</v>
@@ -32095,7 +32095,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.41077935695648</v>
+        <v>1.41077947616577</v>
       </c>
       <c r="H1094" t="n">
         <v>20000</v>
@@ -32124,7 +32124,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.47795927524567</v>
+        <v>1.47795939445496</v>
       </c>
       <c r="H1095" t="n">
         <v>11000</v>
@@ -32153,7 +32153,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.52594518661499</v>
+        <v>1.5259450674057</v>
       </c>
       <c r="H1096" t="n">
         <v>11000</v>
@@ -32240,7 +32240,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1099" t="n">
         <v>2000</v>
@@ -32356,7 +32356,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1103" t="n">
         <v>14000</v>
@@ -32385,7 +32385,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1104" t="n">
         <v>3000</v>
@@ -32472,7 +32472,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1107" t="n">
         <v>6000</v>
@@ -32501,7 +32501,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1108" t="n">
         <v>0</v>
@@ -32617,7 +32617,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.52594518661499</v>
+        <v>1.5259450674057</v>
       </c>
       <c r="H1112" t="n">
         <v>3000</v>
@@ -32646,7 +32646,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.52594518661499</v>
+        <v>1.5259450674057</v>
       </c>
       <c r="H1113" t="n">
         <v>0</v>
@@ -32733,7 +32733,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.47795927524567</v>
+        <v>1.47795939445496</v>
       </c>
       <c r="H1116" t="n">
         <v>23000</v>
@@ -32849,7 +32849,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1120" t="n">
         <v>32000</v>
@@ -32965,7 +32965,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.52594518661499</v>
+        <v>1.5259450674057</v>
       </c>
       <c r="H1124" t="n">
         <v>33000</v>
@@ -33023,7 +33023,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1126" t="n">
         <v>6000</v>
@@ -33081,7 +33081,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1128" t="n">
         <v>3000</v>
@@ -33168,7 +33168,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1131" t="n">
         <v>5000</v>
@@ -33255,7 +33255,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.49715352058411</v>
+        <v>1.4971536397934</v>
       </c>
       <c r="H1134" t="n">
         <v>4000</v>
@@ -33516,7 +33516,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.36279368400574</v>
+        <v>1.36279356479645</v>
       </c>
       <c r="H1143" t="n">
         <v>2000</v>
@@ -33545,7 +33545,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.41077935695648</v>
+        <v>1.41077947616577</v>
       </c>
       <c r="H1144" t="n">
         <v>2000</v>
@@ -33661,7 +33661,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.41077935695648</v>
+        <v>1.41077947616577</v>
       </c>
       <c r="H1148" t="n">
         <v>9000</v>
@@ -33690,7 +33690,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.39158511161804</v>
+        <v>1.39158523082733</v>
       </c>
       <c r="H1149" t="n">
         <v>5000</v>
@@ -33864,7 +33864,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.36279368400574</v>
+        <v>1.36279356479645</v>
       </c>
       <c r="H1155" t="n">
         <v>10000</v>
@@ -33893,7 +33893,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.36279368400574</v>
+        <v>1.36279356479645</v>
       </c>
       <c r="H1156" t="n">
         <v>0</v>
@@ -33922,7 +33922,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.42997360229492</v>
+        <v>1.42997372150421</v>
       </c>
       <c r="H1157" t="n">
         <v>28000</v>
@@ -34009,7 +34009,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.39158511161804</v>
+        <v>1.39158523082733</v>
       </c>
       <c r="H1160" t="n">
         <v>5000</v>
@@ -34067,7 +34067,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.42997360229492</v>
+        <v>1.42997372150421</v>
       </c>
       <c r="H1162" t="n">
         <v>8000</v>
@@ -34096,7 +34096,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.41077935695648</v>
+        <v>1.41077947616577</v>
       </c>
       <c r="H1163" t="n">
         <v>6000</v>
@@ -34154,7 +34154,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.39158511161804</v>
+        <v>1.39158523082733</v>
       </c>
       <c r="H1165" t="n">
         <v>8000</v>
@@ -34183,7 +34183,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.42997360229492</v>
+        <v>1.42997372150421</v>
       </c>
       <c r="H1166" t="n">
         <v>8000</v>
@@ -34241,7 +34241,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.42997360229492</v>
+        <v>1.42997372150421</v>
       </c>
       <c r="H1168" t="n">
         <v>4000</v>
@@ -34270,7 +34270,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.41077935695648</v>
+        <v>1.41077947616577</v>
       </c>
       <c r="H1169" t="n">
         <v>6000</v>
@@ -34357,7 +34357,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.39158511161804</v>
+        <v>1.39158523082733</v>
       </c>
       <c r="H1172" t="n">
         <v>8000</v>
@@ -34444,7 +34444,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.39158511161804</v>
+        <v>1.39158523082733</v>
       </c>
       <c r="H1175" t="n">
         <v>21000</v>
@@ -34502,7 +34502,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.39158511161804</v>
+        <v>1.39158523082733</v>
       </c>
       <c r="H1177" t="n">
         <v>2000</v>
@@ -34647,7 +34647,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.39158511161804</v>
+        <v>1.39158523082733</v>
       </c>
       <c r="H1182" t="n">
         <v>8000</v>
@@ -34908,7 +34908,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.62191653251648</v>
+        <v>1.62191641330719</v>
       </c>
       <c r="H1191" t="n">
         <v>75000</v>
@@ -34937,7 +34937,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1192" t="n">
-        <v>1.52594518661499</v>
+        <v>1.5259450674057</v>
       </c>
       <c r="H1192" t="n">
         <v>77000</v>
@@ -34995,7 +34995,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1194" t="n">
         <v>95000</v>
@@ -35053,7 +35053,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1196" t="n">
         <v>16000</v>
@@ -35140,7 +35140,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1199" t="n">
         <v>60000</v>
@@ -35169,7 +35169,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.95781636238098</v>
+        <v>1.95781624317169</v>
       </c>
       <c r="H1200" t="n">
         <v>89000</v>
@@ -35198,7 +35198,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.95781636238098</v>
+        <v>1.95781624317169</v>
       </c>
       <c r="H1201" t="n">
         <v>148000</v>
@@ -35256,7 +35256,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.84265065193176</v>
+        <v>1.84265053272247</v>
       </c>
       <c r="H1203" t="n">
         <v>24000</v>
@@ -35314,7 +35314,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1205" t="n">
         <v>72000</v>
@@ -35343,7 +35343,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1206" t="n">
         <v>18000</v>
@@ -35401,7 +35401,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1208" t="n">
         <v>4000</v>
@@ -35430,7 +35430,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1209" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1209" t="n">
         <v>10000</v>
@@ -35488,7 +35488,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1211" t="n">
         <v>36000</v>
@@ -35517,7 +35517,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1212" t="n">
         <v>3000</v>
@@ -35546,7 +35546,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1213" t="n">
         <v>11000</v>
@@ -35575,7 +35575,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1214" t="n">
         <v>1000</v>
@@ -35604,7 +35604,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.49715352058411</v>
+        <v>1.4971536397934</v>
       </c>
       <c r="H1215" t="n">
         <v>7000</v>
@@ -35633,7 +35633,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1216" t="n">
         <v>4000</v>
@@ -35662,7 +35662,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1217" t="n">
         <v>68000</v>
@@ -35749,7 +35749,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.71788775920868</v>
+        <v>1.71788787841797</v>
       </c>
       <c r="H1220" t="n">
         <v>10000</v>
@@ -35778,7 +35778,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1221" t="n">
         <v>11000</v>
@@ -35894,7 +35894,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1225" t="n">
         <v>9000</v>
@@ -35923,7 +35923,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1226" t="n">
         <v>14000</v>
@@ -35952,7 +35952,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1227" t="n">
         <v>7000</v>
@@ -36213,7 +36213,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1236" t="n">
         <v>19000</v>
@@ -36242,7 +36242,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1237" t="n">
-        <v>1.62191653251648</v>
+        <v>1.62191641330719</v>
       </c>
       <c r="H1237" t="n">
         <v>18000</v>
@@ -36271,7 +36271,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1238" t="n">
-        <v>1.62191653251648</v>
+        <v>1.62191641330719</v>
       </c>
       <c r="H1238" t="n">
         <v>1000</v>
@@ -36300,7 +36300,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1239" t="n">
         <v>4000</v>
@@ -36387,7 +36387,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1242" t="n">
         <v>2000</v>
@@ -36416,7 +36416,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1243" t="n">
         <v>0</v>
@@ -36445,7 +36445,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1244" t="n">
         <v>0</v>
@@ -36706,7 +36706,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1253" t="n">
         <v>4000</v>
@@ -36735,7 +36735,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.53554224967957</v>
+        <v>1.53554213047028</v>
       </c>
       <c r="H1254" t="n">
         <v>0</v>
@@ -36851,7 +36851,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1258" t="n">
         <v>4000</v>
@@ -37141,7 +37141,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1268" t="n">
         <v>2000</v>
@@ -37170,7 +37170,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1269" t="n">
         <v>3000</v>
@@ -37199,7 +37199,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.62191653251648</v>
+        <v>1.62191641330719</v>
       </c>
       <c r="H1270" t="n">
         <v>1000</v>
@@ -37228,7 +37228,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.62191653251648</v>
+        <v>1.62191641330719</v>
       </c>
       <c r="H1271" t="n">
         <v>0</v>
@@ -37257,7 +37257,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1272" t="n">
         <v>1000</v>
@@ -37286,7 +37286,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1273" t="n">
         <v>12000</v>
@@ -37315,7 +37315,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1274" t="n">
         <v>0</v>
@@ -37344,7 +37344,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1275" t="n">
         <v>0</v>
@@ -37373,7 +37373,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.60272216796875</v>
+        <v>1.60272204875946</v>
       </c>
       <c r="H1276" t="n">
         <v>0</v>
@@ -37518,7 +37518,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.62191653251648</v>
+        <v>1.62191641330719</v>
       </c>
       <c r="H1281" t="n">
         <v>2000</v>
@@ -37547,7 +37547,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1282" t="n">
         <v>4000</v>
@@ -37576,7 +37576,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1283" t="n">
         <v>3000</v>
@@ -37605,7 +37605,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1284" t="n">
         <v>0</v>
@@ -37663,7 +37663,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1286" t="n">
         <v>6000</v>
@@ -37692,7 +37692,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1287" t="n">
         <v>2000</v>
@@ -37721,7 +37721,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.01539921760559</v>
+        <v>2.01539897918701</v>
       </c>
       <c r="H1288" t="n">
         <v>205000</v>
@@ -37779,7 +37779,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1290" t="n">
         <v>56000</v>
@@ -37924,7 +37924,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1295" t="n">
         <v>15000</v>
@@ -38011,7 +38011,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1298" t="n">
         <v>17000</v>
@@ -38040,7 +38040,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1299" t="n">
         <v>0</v>
@@ -38330,7 +38330,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.89063632488251</v>
+        <v>1.8906364440918</v>
       </c>
       <c r="H1309" t="n">
         <v>14000</v>
@@ -38359,7 +38359,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.89063632488251</v>
+        <v>1.8906364440918</v>
       </c>
       <c r="H1310" t="n">
         <v>17000</v>
@@ -38475,7 +38475,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1314" t="n">
-        <v>1.86184501647949</v>
+        <v>1.8618448972702</v>
       </c>
       <c r="H1314" t="n">
         <v>20000</v>
@@ -38504,7 +38504,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.89063632488251</v>
+        <v>1.8906364440918</v>
       </c>
       <c r="H1315" t="n">
         <v>27000</v>
@@ -38620,7 +38620,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1319" t="n">
         <v>4000</v>
@@ -38649,7 +38649,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1320" t="n">
         <v>3000</v>
@@ -38707,7 +38707,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1322" t="n">
         <v>3000</v>
@@ -38765,7 +38765,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1324" t="n">
         <v>11000</v>
@@ -38794,7 +38794,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.78506791591644</v>
+        <v>1.78506779670715</v>
       </c>
       <c r="H1325" t="n">
         <v>7000</v>
@@ -38823,7 +38823,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1326" t="n">
         <v>8000</v>
@@ -38881,7 +38881,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.73708200454712</v>
+        <v>1.73708212375641</v>
       </c>
       <c r="H1328" t="n">
         <v>25000</v>
@@ -39026,7 +39026,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1333" t="n">
         <v>2000</v>
@@ -39055,7 +39055,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1334" t="n">
         <v>8000</v>
@@ -39084,7 +39084,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1335" t="n">
         <v>2000</v>
@@ -39229,7 +39229,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1340" t="n">
         <v>4000</v>
@@ -39258,7 +39258,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.75627636909485</v>
+        <v>1.75627648830414</v>
       </c>
       <c r="H1341" t="n">
         <v>0</v>
@@ -39432,7 +39432,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1347" t="n">
         <v>9000</v>
@@ -39461,7 +39461,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1348" t="n">
         <v>4000</v>
@@ -39490,7 +39490,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.7082906961441</v>
+        <v>1.70829057693481</v>
       </c>
       <c r="H1349" t="n">
         <v>0</v>
@@ -39606,7 +39606,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.68909645080566</v>
+        <v>1.68909633159637</v>
       </c>
       <c r="H1353" t="n">
         <v>5000</v>
@@ -39664,7 +39664,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.66990208625793</v>
+        <v>1.66990220546722</v>
       </c>
       <c r="H1355" t="n">
         <v>8000</v>
@@ -39722,7 +39722,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.63151359558105</v>
+        <v>1.63151371479034</v>
       </c>
       <c r="H1357" t="n">
         <v>3000</v>
@@ -39751,7 +39751,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.65070784091949</v>
+        <v>1.65070796012878</v>
       </c>
       <c r="H1358" t="n">
         <v>2000</v>
@@ -53793,6 +53793,35 @@
         <v>11000</v>
       </c>
       <c r="I1842" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1843" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1843" t="n">
+        <v>1.95000004768372</v>
+      </c>
+      <c r="D1843" t="n">
+        <v>1.96000003814697</v>
+      </c>
+      <c r="E1843" t="n">
+        <v>1.9099999666214</v>
+      </c>
+      <c r="F1843" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="G1843" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="H1843" t="n">
+        <v>27000</v>
+      </c>
+      <c r="I1843" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CFV.MI.xlsx
+++ b/data/CFV.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>1.30437564849854</v>
+        <v>1.30437552928925</v>
       </c>
       <c r="H2" t="n">
         <v>322000</v>
@@ -456,7 +456,7 @@
         <v>1.50020003318787</v>
       </c>
       <c r="G3" t="n">
-        <v>1.31330490112305</v>
+        <v>1.31330502033234</v>
       </c>
       <c r="H3" t="n">
         <v>35000</v>
@@ -485,7 +485,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G4" t="n">
-        <v>1.40067172050476</v>
+        <v>1.40067183971405</v>
       </c>
       <c r="H4" t="n">
         <v>193000</v>
@@ -514,7 +514,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G5" t="n">
-        <v>1.62828099727631</v>
+        <v>1.62828087806702</v>
       </c>
       <c r="H5" t="n">
         <v>169000</v>
@@ -543,7 +543,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G6" t="n">
-        <v>1.62828099727631</v>
+        <v>1.62828087806702</v>
       </c>
       <c r="H6" t="n">
         <v>470000</v>
@@ -659,7 +659,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G10" t="n">
-        <v>1.87339878082275</v>
+        <v>1.87339854240417</v>
       </c>
       <c r="H10" t="n">
         <v>464000</v>
@@ -717,7 +717,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G12" t="n">
-        <v>2.59124255180359</v>
+        <v>2.59124279022217</v>
       </c>
       <c r="H12" t="n">
         <v>261000</v>
@@ -775,7 +775,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G14" t="n">
-        <v>3.69427156448364</v>
+        <v>3.69427132606506</v>
       </c>
       <c r="H14" t="n">
         <v>633000</v>
@@ -833,7 +833,7 @@
         <v>4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3.93938994407654</v>
+        <v>3.9393892288208</v>
       </c>
       <c r="H16" t="n">
         <v>669000</v>
@@ -891,7 +891,7 @@
         <v>4.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3.93938994407654</v>
+        <v>3.9393892288208</v>
       </c>
       <c r="H18" t="n">
         <v>489000</v>
@@ -920,7 +920,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G19" t="n">
-        <v>3.87810969352722</v>
+        <v>3.8781099319458</v>
       </c>
       <c r="H19" t="n">
         <v>592000</v>
@@ -949,7 +949,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G20" t="n">
-        <v>3.66800928115845</v>
+        <v>3.66800951957703</v>
       </c>
       <c r="H20" t="n">
         <v>302000</v>
@@ -978,7 +978,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G21" t="n">
-        <v>3.52794218063354</v>
+        <v>3.52794241905212</v>
       </c>
       <c r="H21" t="n">
         <v>356000</v>
@@ -1007,7 +1007,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>3.57171297073364</v>
+        <v>3.57171273231506</v>
       </c>
       <c r="H22" t="n">
         <v>212000</v>
@@ -1065,7 +1065,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G24" t="n">
-        <v>3.69427156448364</v>
+        <v>3.69427132606506</v>
       </c>
       <c r="H24" t="n">
         <v>227000</v>
@@ -1094,7 +1094,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G25" t="n">
-        <v>3.55420446395874</v>
+        <v>3.55420470237732</v>
       </c>
       <c r="H25" t="n">
         <v>275000</v>
@@ -1152,7 +1152,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G27" t="n">
-        <v>3.51043367385864</v>
+        <v>3.51043391227722</v>
       </c>
       <c r="H27" t="n">
         <v>25000</v>
@@ -1181,7 +1181,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G28" t="n">
-        <v>3.42289161682129</v>
+        <v>3.42289185523987</v>
       </c>
       <c r="H28" t="n">
         <v>30000</v>
@@ -1239,7 +1239,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>3.53669619560242</v>
+        <v>3.53669595718384</v>
       </c>
       <c r="H30" t="n">
         <v>95000</v>
@@ -1297,7 +1297,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G32" t="n">
-        <v>3.45353126525879</v>
+        <v>3.45353150367737</v>
       </c>
       <c r="H32" t="n">
         <v>39000</v>
@@ -1471,7 +1471,7 @@
         <v>3.75</v>
       </c>
       <c r="G38" t="n">
-        <v>3.28282427787781</v>
+        <v>3.28282451629639</v>
       </c>
       <c r="H38" t="n">
         <v>41000</v>
@@ -1558,7 +1558,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G41" t="n">
-        <v>2.9370334148407</v>
+        <v>2.93703365325928</v>
       </c>
       <c r="H41" t="n">
         <v>317000</v>
@@ -1616,7 +1616,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G43" t="n">
-        <v>2.62188243865967</v>
+        <v>2.62188220024109</v>
       </c>
       <c r="H43" t="n">
         <v>68000</v>
@@ -1703,7 +1703,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G46" t="n">
-        <v>2.98080444335938</v>
+        <v>2.98080468177795</v>
       </c>
       <c r="H46" t="n">
         <v>492000</v>
@@ -1819,7 +1819,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G50" t="n">
-        <v>2.74881863594055</v>
+        <v>2.74881815910339</v>
       </c>
       <c r="H50" t="n">
         <v>29000</v>
@@ -1877,7 +1877,7 @@
         <v>3.125</v>
       </c>
       <c r="G52" t="n">
-        <v>2.7356870174408</v>
+        <v>2.73568677902222</v>
       </c>
       <c r="H52" t="n">
         <v>24000</v>
@@ -1906,7 +1906,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>2.88450860977173</v>
+        <v>2.88450837135315</v>
       </c>
       <c r="H53" t="n">
         <v>253000</v>
@@ -2022,7 +2022,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G57" t="n">
-        <v>2.85386872291565</v>
+        <v>2.85386896133423</v>
       </c>
       <c r="H57" t="n">
         <v>52000</v>
@@ -2051,7 +2051,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>2.80134344100952</v>
+        <v>2.8013436794281</v>
       </c>
       <c r="H58" t="n">
         <v>74000</v>
@@ -2109,7 +2109,7 @@
         <v>3.25</v>
       </c>
       <c r="G60" t="n">
-        <v>2.84511494636536</v>
+        <v>2.8451144695282</v>
       </c>
       <c r="H60" t="n">
         <v>46000</v>
@@ -2138,7 +2138,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G61" t="n">
-        <v>2.85824608802795</v>
+        <v>2.85824584960938</v>
       </c>
       <c r="H61" t="n">
         <v>55000</v>
@@ -2196,7 +2196,7 @@
         <v>3.25</v>
       </c>
       <c r="G63" t="n">
-        <v>2.84511494636536</v>
+        <v>2.8451144695282</v>
       </c>
       <c r="H63" t="n">
         <v>14000</v>
@@ -2254,7 +2254,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G65" t="n">
-        <v>2.82322907447815</v>
+        <v>2.82322883605957</v>
       </c>
       <c r="H65" t="n">
         <v>17000</v>
@@ -2283,7 +2283,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G66" t="n">
-        <v>2.82322907447815</v>
+        <v>2.82322883605957</v>
       </c>
       <c r="H66" t="n">
         <v>15000</v>
@@ -2312,7 +2312,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>2.82322907447815</v>
+        <v>2.82322883605957</v>
       </c>
       <c r="H67" t="n">
         <v>1000</v>
@@ -2486,7 +2486,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G73" t="n">
-        <v>2.87137722969055</v>
+        <v>2.87137699127197</v>
       </c>
       <c r="H73" t="n">
         <v>14000</v>
@@ -2515,7 +2515,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G74" t="n">
-        <v>2.84949159622192</v>
+        <v>2.8494918346405</v>
       </c>
       <c r="H74" t="n">
         <v>3000</v>
@@ -2631,7 +2631,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>2.77070379257202</v>
+        <v>2.7707040309906</v>
       </c>
       <c r="H78" t="n">
         <v>13000</v>
@@ -2660,7 +2660,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>2.72693276405334</v>
+        <v>2.72693300247192</v>
       </c>
       <c r="H79" t="n">
         <v>6000</v>
@@ -2689,7 +2689,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G80" t="n">
-        <v>2.83198285102844</v>
+        <v>2.83198308944702</v>
       </c>
       <c r="H80" t="n">
         <v>24000</v>
@@ -2718,7 +2718,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.80134344100952</v>
+        <v>2.8013436794281</v>
       </c>
       <c r="H81" t="n">
         <v>20000</v>
@@ -2747,7 +2747,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G82" t="n">
-        <v>2.74006414413452</v>
+        <v>2.7400643825531</v>
       </c>
       <c r="H82" t="n">
         <v>7000</v>
@@ -2776,7 +2776,7 @@
         <v>3.25</v>
       </c>
       <c r="G83" t="n">
-        <v>2.84511494636536</v>
+        <v>2.8451144695282</v>
       </c>
       <c r="H83" t="n">
         <v>61000</v>
@@ -2892,7 +2892,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G87" t="n">
-        <v>2.80134344100952</v>
+        <v>2.8013436794281</v>
       </c>
       <c r="H87" t="n">
         <v>20000</v>
@@ -2921,7 +2921,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G88" t="n">
-        <v>2.80134344100952</v>
+        <v>2.8013436794281</v>
       </c>
       <c r="H88" t="n">
         <v>49000</v>
@@ -2950,7 +2950,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G89" t="n">
-        <v>2.85386872291565</v>
+        <v>2.85386896133423</v>
       </c>
       <c r="H89" t="n">
         <v>20000</v>
@@ -2979,7 +2979,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G90" t="n">
-        <v>2.8888852596283</v>
+        <v>2.88888549804688</v>
       </c>
       <c r="H90" t="n">
         <v>39000</v>
@@ -3008,7 +3008,7 @@
         <v>3.25</v>
       </c>
       <c r="G91" t="n">
-        <v>2.84511494636536</v>
+        <v>2.8451144695282</v>
       </c>
       <c r="H91" t="n">
         <v>16000</v>
@@ -3037,7 +3037,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G92" t="n">
-        <v>2.87137722969055</v>
+        <v>2.87137699127197</v>
       </c>
       <c r="H92" t="n">
         <v>8000</v>
@@ -3066,7 +3066,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G93" t="n">
-        <v>2.8888852596283</v>
+        <v>2.88888549804688</v>
       </c>
       <c r="H93" t="n">
         <v>20000</v>
@@ -3153,7 +3153,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G96" t="n">
-        <v>2.80134344100952</v>
+        <v>2.8013436794281</v>
       </c>
       <c r="H96" t="n">
         <v>9000</v>
@@ -3182,7 +3182,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>2.88450860977173</v>
+        <v>2.88450837135315</v>
       </c>
       <c r="H97" t="n">
         <v>14000</v>
@@ -3240,7 +3240,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.86699986457825</v>
+        <v>2.86700010299683</v>
       </c>
       <c r="H99" t="n">
         <v>3000</v>
@@ -3269,7 +3269,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G100" t="n">
-        <v>2.88450860977173</v>
+        <v>2.88450837135315</v>
       </c>
       <c r="H100" t="n">
         <v>5000</v>
@@ -3298,7 +3298,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G101" t="n">
-        <v>2.88450860977173</v>
+        <v>2.88450837135315</v>
       </c>
       <c r="H101" t="n">
         <v>8000</v>
@@ -3327,7 +3327,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G102" t="n">
-        <v>2.88450860977173</v>
+        <v>2.88450837135315</v>
       </c>
       <c r="H102" t="n">
         <v>5000</v>
@@ -3356,7 +3356,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G103" t="n">
-        <v>2.8888852596283</v>
+        <v>2.88888549804688</v>
       </c>
       <c r="H103" t="n">
         <v>8000</v>
@@ -3385,7 +3385,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G104" t="n">
-        <v>2.8888852596283</v>
+        <v>2.88888549804688</v>
       </c>
       <c r="H104" t="n">
         <v>9000</v>
@@ -3414,7 +3414,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G105" t="n">
-        <v>2.8888852596283</v>
+        <v>2.88888549804688</v>
       </c>
       <c r="H105" t="n">
         <v>13000</v>
@@ -3443,7 +3443,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G106" t="n">
-        <v>2.99831295013428</v>
+        <v>2.9983127117157</v>
       </c>
       <c r="H106" t="n">
         <v>52000</v>
@@ -3501,7 +3501,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>4.39460754394531</v>
+        <v>4.39460802078247</v>
       </c>
       <c r="H108" t="n">
         <v>137000</v>
@@ -3530,7 +3530,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G109" t="n">
-        <v>3.96565222740173</v>
+        <v>3.96565246582031</v>
       </c>
       <c r="H109" t="n">
         <v>596000</v>
@@ -3559,7 +3559,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>4.11447334289551</v>
+        <v>4.11447286605835</v>
       </c>
       <c r="H110" t="n">
         <v>568000</v>
@@ -3646,7 +3646,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G113" t="n">
-        <v>3.52794218063354</v>
+        <v>3.52794241905212</v>
       </c>
       <c r="H113" t="n">
         <v>87000</v>
@@ -3704,7 +3704,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G115" t="n">
-        <v>3.77305960655212</v>
+        <v>3.77305936813354</v>
       </c>
       <c r="H115" t="n">
         <v>88000</v>
@@ -3733,7 +3733,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>3.97878313064575</v>
+        <v>3.97878360748291</v>
       </c>
       <c r="H116" t="n">
         <v>371000</v>
@@ -3762,7 +3762,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>3.91312623023987</v>
+        <v>3.91312646865845</v>
       </c>
       <c r="H117" t="n">
         <v>152000</v>
@@ -3791,7 +3791,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>3.86060166358948</v>
+        <v>3.86060094833374</v>
       </c>
       <c r="H118" t="n">
         <v>82000</v>
@@ -3820,7 +3820,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G119" t="n">
-        <v>3.79932260513306</v>
+        <v>3.79932236671448</v>
       </c>
       <c r="H119" t="n">
         <v>66000</v>
@@ -3878,7 +3878,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G121" t="n">
-        <v>3.89124178886414</v>
+        <v>3.89124155044556</v>
       </c>
       <c r="H121" t="n">
         <v>84000</v>
@@ -3907,7 +3907,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G122" t="n">
-        <v>3.92625784873962</v>
+        <v>3.92625856399536</v>
       </c>
       <c r="H122" t="n">
         <v>35000</v>
@@ -3936,7 +3936,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>4.28955745697021</v>
+        <v>4.28955698013306</v>
       </c>
       <c r="H123" t="n">
         <v>537000</v>
@@ -3965,7 +3965,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G124" t="n">
-        <v>4.1713752746582</v>
+        <v>4.17137575149536</v>
       </c>
       <c r="H124" t="n">
         <v>181000</v>
@@ -3994,7 +3994,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>4.18013000488281</v>
+        <v>4.18013048171997</v>
       </c>
       <c r="H125" t="n">
         <v>73000</v>
@@ -4081,7 +4081,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G128" t="n">
-        <v>4.16699886322021</v>
+        <v>4.16699838638306</v>
       </c>
       <c r="H128" t="n">
         <v>58000</v>
@@ -4197,7 +4197,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G132" t="n">
-        <v>4.00504589080811</v>
+        <v>4.00504636764526</v>
       </c>
       <c r="H132" t="n">
         <v>14000</v>
@@ -4284,7 +4284,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>3.9568977355957</v>
+        <v>3.95689797401428</v>
       </c>
       <c r="H135" t="n">
         <v>25000</v>
@@ -4342,7 +4342,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G137" t="n">
-        <v>3.98753666877747</v>
+        <v>3.98753690719604</v>
       </c>
       <c r="H137" t="n">
         <v>27000</v>
@@ -4371,7 +4371,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G138" t="n">
-        <v>3.99629139900208</v>
+        <v>3.99629187583923</v>
       </c>
       <c r="H138" t="n">
         <v>9000</v>
@@ -4400,7 +4400,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G139" t="n">
-        <v>4.21952390670776</v>
+        <v>4.21952438354492</v>
       </c>
       <c r="H139" t="n">
         <v>149000</v>
@@ -4487,7 +4487,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G142" t="n">
-        <v>4.32895135879517</v>
+        <v>4.32895088195801</v>
       </c>
       <c r="H142" t="n">
         <v>162000</v>
@@ -4516,7 +4516,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G143" t="n">
-        <v>5.16497707366943</v>
+        <v>5.16497755050659</v>
       </c>
       <c r="H143" t="n">
         <v>670000</v>
@@ -4545,7 +4545,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G144" t="n">
-        <v>4.76228380203247</v>
+        <v>4.76228427886963</v>
       </c>
       <c r="H144" t="n">
         <v>733000</v>
@@ -4574,7 +4574,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G145" t="n">
-        <v>4.46464061737061</v>
+        <v>4.46464109420776</v>
       </c>
       <c r="H145" t="n">
         <v>522000</v>
@@ -4661,7 +4661,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>3.85184693336487</v>
+        <v>3.85184741020203</v>
       </c>
       <c r="H148" t="n">
         <v>192000</v>
@@ -4777,7 +4777,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>3.79932260513306</v>
+        <v>3.79932236671448</v>
       </c>
       <c r="H152" t="n">
         <v>69000</v>
@@ -4864,7 +4864,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G155" t="n">
-        <v>3.19965958595276</v>
+        <v>3.19965934753418</v>
       </c>
       <c r="H155" t="n">
         <v>17000</v>
@@ -4893,7 +4893,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G156" t="n">
-        <v>2.72255563735962</v>
+        <v>2.7225558757782</v>
       </c>
       <c r="H156" t="n">
         <v>96000</v>
@@ -4980,7 +4980,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>2.77508115768433</v>
+        <v>2.77508091926575</v>
       </c>
       <c r="H159" t="n">
         <v>58000</v>
@@ -5009,7 +5009,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G160" t="n">
-        <v>2.8888852596283</v>
+        <v>2.88888549804688</v>
       </c>
       <c r="H160" t="n">
         <v>26000</v>
@@ -5038,7 +5038,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G161" t="n">
-        <v>2.95891952514648</v>
+        <v>2.95891928672791</v>
       </c>
       <c r="H161" t="n">
         <v>30000</v>
@@ -5125,7 +5125,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G164" t="n">
-        <v>3.53669619560242</v>
+        <v>3.53669595718384</v>
       </c>
       <c r="H164" t="n">
         <v>67000</v>
@@ -5183,7 +5183,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.75555109977722</v>
+        <v>3.75555086135864</v>
       </c>
       <c r="H166" t="n">
         <v>119000</v>
@@ -5241,7 +5241,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>3.62861514091492</v>
+        <v>3.6286153793335</v>
       </c>
       <c r="H168" t="n">
         <v>19000</v>
@@ -5270,7 +5270,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G169" t="n">
-        <v>3.60672926902771</v>
+        <v>3.60672974586487</v>
       </c>
       <c r="H169" t="n">
         <v>15000</v>
@@ -5299,7 +5299,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>3.66800928115845</v>
+        <v>3.66800951957703</v>
       </c>
       <c r="H170" t="n">
         <v>26000</v>
@@ -5328,7 +5328,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G171" t="n">
-        <v>3.73366546630859</v>
+        <v>3.73366570472717</v>
       </c>
       <c r="H171" t="n">
         <v>10000</v>
@@ -5357,7 +5357,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G172" t="n">
-        <v>3.68551754951477</v>
+        <v>3.68551778793335</v>
       </c>
       <c r="H172" t="n">
         <v>16000</v>
@@ -5415,7 +5415,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.85184693336487</v>
+        <v>3.85184741020203</v>
       </c>
       <c r="H174" t="n">
         <v>74000</v>
@@ -5444,7 +5444,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G175" t="n">
-        <v>3.94376683235168</v>
+        <v>3.94376659393311</v>
       </c>
       <c r="H175" t="n">
         <v>24000</v>
@@ -5473,7 +5473,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>4.07070255279541</v>
+        <v>4.07070207595825</v>
       </c>
       <c r="H176" t="n">
         <v>44000</v>
@@ -5502,7 +5502,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>4.07070255279541</v>
+        <v>4.07070207595825</v>
       </c>
       <c r="H177" t="n">
         <v>17000</v>
@@ -5531,7 +5531,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>3.68114018440247</v>
+        <v>3.68114042282104</v>
       </c>
       <c r="H178" t="n">
         <v>51000</v>
@@ -5589,7 +5589,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G180" t="n">
-        <v>3.83433890342712</v>
+        <v>3.83433866500854</v>
       </c>
       <c r="H180" t="n">
         <v>29000</v>
@@ -5618,7 +5618,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G181" t="n">
-        <v>3.87810969352722</v>
+        <v>3.8781099319458</v>
       </c>
       <c r="H181" t="n">
         <v>9000</v>
@@ -5705,7 +5705,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>3.85184693336487</v>
+        <v>3.85184741020203</v>
       </c>
       <c r="H184" t="n">
         <v>8000</v>
@@ -5734,7 +5734,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G185" t="n">
-        <v>3.79056787490845</v>
+        <v>3.79056763648987</v>
       </c>
       <c r="H185" t="n">
         <v>4000</v>
@@ -5792,7 +5792,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G187" t="n">
-        <v>3.86060166358948</v>
+        <v>3.86060094833374</v>
       </c>
       <c r="H187" t="n">
         <v>5000</v>
@@ -5821,7 +5821,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>3.77743649482727</v>
+        <v>3.77743697166443</v>
       </c>
       <c r="H188" t="n">
         <v>7000</v>
@@ -5879,7 +5879,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G190" t="n">
-        <v>3.78224873542786</v>
+        <v>3.78224897384644</v>
       </c>
       <c r="H190" t="n">
         <v>11000</v>
@@ -5937,7 +5937,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G192" t="n">
-        <v>3.78668785095215</v>
+        <v>3.78668808937073</v>
       </c>
       <c r="H192" t="n">
         <v>2000</v>
@@ -6024,7 +6024,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G195" t="n">
-        <v>3.78224873542786</v>
+        <v>3.78224897384644</v>
       </c>
       <c r="H195" t="n">
         <v>8000</v>
@@ -6053,7 +6053,7 @@
         <v>4.25</v>
       </c>
       <c r="G196" t="n">
-        <v>3.77337002754211</v>
+        <v>3.77337026596069</v>
       </c>
       <c r="H196" t="n">
         <v>7000</v>
@@ -6082,7 +6082,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>3.79112696647644</v>
+        <v>3.79112720489502</v>
       </c>
       <c r="H197" t="n">
         <v>2000</v>
@@ -6140,7 +6140,7 @@
         <v>4.5</v>
       </c>
       <c r="G199" t="n">
-        <v>3.99533343315125</v>
+        <v>3.99533319473267</v>
       </c>
       <c r="H199" t="n">
         <v>99000</v>
@@ -6169,7 +6169,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G200" t="n">
-        <v>3.86215496063232</v>
+        <v>3.8621551990509</v>
       </c>
       <c r="H200" t="n">
         <v>46000</v>
@@ -6227,7 +6227,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>3.83108067512512</v>
+        <v>3.8310809135437</v>
       </c>
       <c r="H202" t="n">
         <v>10000</v>
@@ -6401,7 +6401,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90654802322388</v>
+        <v>3.90654826164246</v>
       </c>
       <c r="H208" t="n">
         <v>30000</v>
@@ -6430,7 +6430,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>3.86215496063232</v>
+        <v>3.8621551990509</v>
       </c>
       <c r="H209" t="n">
         <v>8000</v>
@@ -6459,7 +6459,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>3.86215496063232</v>
+        <v>3.8621551990509</v>
       </c>
       <c r="H210" t="n">
         <v>2000</v>
@@ -6488,7 +6488,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G211" t="n">
-        <v>3.81776285171509</v>
+        <v>3.81776309013367</v>
       </c>
       <c r="H211" t="n">
         <v>14000</v>
@@ -6517,7 +6517,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>3.95981955528259</v>
+        <v>3.95981931686401</v>
       </c>
       <c r="H212" t="n">
         <v>9000</v>
@@ -6546,7 +6546,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>3.91986584663391</v>
+        <v>3.91986608505249</v>
       </c>
       <c r="H213" t="n">
         <v>11000</v>
@@ -6633,7 +6633,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G216" t="n">
-        <v>3.91542625427246</v>
+        <v>3.91542601585388</v>
       </c>
       <c r="H216" t="n">
         <v>19000</v>
@@ -6662,7 +6662,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G217" t="n">
-        <v>3.94206213951111</v>
+        <v>3.94206190109253</v>
       </c>
       <c r="H217" t="n">
         <v>13000</v>
@@ -6691,7 +6691,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G218" t="n">
-        <v>3.96425914764404</v>
+        <v>3.96425890922546</v>
       </c>
       <c r="H218" t="n">
         <v>43000</v>
@@ -6749,7 +6749,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>4.01752996444702</v>
+        <v>4.01752948760986</v>
       </c>
       <c r="H220" t="n">
         <v>10000</v>
@@ -6807,7 +6807,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G222" t="n">
-        <v>4.06636142730713</v>
+        <v>4.06636095046997</v>
       </c>
       <c r="H222" t="n">
         <v>3000</v>
@@ -6836,7 +6836,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G223" t="n">
-        <v>4.04416561126709</v>
+        <v>4.04416465759277</v>
       </c>
       <c r="H223" t="n">
         <v>17000</v>
@@ -6894,7 +6894,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>3.95981955528259</v>
+        <v>3.95981931686401</v>
       </c>
       <c r="H225" t="n">
         <v>10000</v>
@@ -6923,7 +6923,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G226" t="n">
-        <v>4.00421190261841</v>
+        <v>4.00421142578125</v>
       </c>
       <c r="H226" t="n">
         <v>2000</v>
@@ -6952,7 +6952,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>3.97313737869263</v>
+        <v>3.97313714027405</v>
       </c>
       <c r="H227" t="n">
         <v>9000</v>
@@ -6981,7 +6981,7 @@
         <v>4.5</v>
       </c>
       <c r="G228" t="n">
-        <v>3.99533343315125</v>
+        <v>3.99533319473267</v>
       </c>
       <c r="H228" t="n">
         <v>7000</v>
@@ -7010,7 +7010,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>4.01309013366699</v>
+        <v>4.01309061050415</v>
       </c>
       <c r="H229" t="n">
         <v>13000</v>
@@ -7039,7 +7039,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G230" t="n">
-        <v>3.9864547252655</v>
+        <v>3.98645424842834</v>
       </c>
       <c r="H230" t="n">
         <v>16000</v>
@@ -7068,7 +7068,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G231" t="n">
-        <v>4.06636142730713</v>
+        <v>4.06636095046997</v>
       </c>
       <c r="H231" t="n">
         <v>61000</v>
@@ -7097,7 +7097,7 @@
         <v>4.5</v>
       </c>
       <c r="G232" t="n">
-        <v>3.99533343315125</v>
+        <v>3.99533319473267</v>
       </c>
       <c r="H232" t="n">
         <v>19000</v>
@@ -7155,7 +7155,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G234" t="n">
-        <v>4.06636142730713</v>
+        <v>4.06636095046997</v>
       </c>
       <c r="H234" t="n">
         <v>13000</v>
@@ -7213,7 +7213,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G236" t="n">
-        <v>4.10187530517578</v>
+        <v>4.10187578201294</v>
       </c>
       <c r="H236" t="n">
         <v>72000</v>
@@ -7271,7 +7271,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.48365211486816</v>
+        <v>4.48365163803101</v>
       </c>
       <c r="H238" t="n">
         <v>99000</v>
@@ -7300,7 +7300,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>4.40374565124512</v>
+        <v>4.40374517440796</v>
       </c>
       <c r="H239" t="n">
         <v>37000</v>
@@ -7358,7 +7358,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>4.33271741867065</v>
+        <v>4.3327169418335</v>
       </c>
       <c r="H241" t="n">
         <v>24000</v>
@@ -7387,7 +7387,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G242" t="n">
-        <v>4.4126238822937</v>
+        <v>4.41262340545654</v>
       </c>
       <c r="H242" t="n">
         <v>26000</v>
@@ -7474,7 +7474,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G245" t="n">
-        <v>4.24393224716187</v>
+        <v>4.24393177032471</v>
       </c>
       <c r="H245" t="n">
         <v>12000</v>
@@ -7503,7 +7503,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G246" t="n">
-        <v>4.3105206489563</v>
+        <v>4.31052017211914</v>
       </c>
       <c r="H246" t="n">
         <v>21000</v>
@@ -7561,7 +7561,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>4.26168918609619</v>
+        <v>4.26168870925903</v>
       </c>
       <c r="H248" t="n">
         <v>29000</v>
@@ -7590,7 +7590,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G249" t="n">
-        <v>4.26168918609619</v>
+        <v>4.26168870925903</v>
       </c>
       <c r="H249" t="n">
         <v>15000</v>
@@ -7677,7 +7677,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G252" t="n">
-        <v>4.02196884155273</v>
+        <v>4.02196931838989</v>
       </c>
       <c r="H252" t="n">
         <v>35000</v>
@@ -7706,7 +7706,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G253" t="n">
-        <v>3.86215496063232</v>
+        <v>3.8621551990509</v>
       </c>
       <c r="H253" t="n">
         <v>21000</v>
@@ -7735,7 +7735,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G254" t="n">
-        <v>3.88879108428955</v>
+        <v>3.88879084587097</v>
       </c>
       <c r="H254" t="n">
         <v>21000</v>
@@ -7764,7 +7764,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G255" t="n">
-        <v>3.96425914764404</v>
+        <v>3.96425890922546</v>
       </c>
       <c r="H255" t="n">
         <v>2000</v>
@@ -7793,7 +7793,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>4.06636142730713</v>
+        <v>4.06636095046997</v>
       </c>
       <c r="H256" t="n">
         <v>12000</v>
@@ -7880,7 +7880,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>4.15070772171021</v>
+        <v>4.15070819854736</v>
       </c>
       <c r="H259" t="n">
         <v>48000</v>
@@ -7938,7 +7938,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G261" t="n">
-        <v>4.0929970741272</v>
+        <v>4.09299659729004</v>
       </c>
       <c r="H261" t="n">
         <v>28000</v>
@@ -7996,7 +7996,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>4.01309013366699</v>
+        <v>4.01309061050415</v>
       </c>
       <c r="H263" t="n">
         <v>9000</v>
@@ -8025,7 +8025,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G264" t="n">
-        <v>4.05748319625854</v>
+        <v>4.05748271942139</v>
       </c>
       <c r="H264" t="n">
         <v>17000</v>
@@ -8083,7 +8083,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>4.04416561126709</v>
+        <v>4.04416465759277</v>
       </c>
       <c r="H266" t="n">
         <v>23000</v>
@@ -8141,7 +8141,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G268" t="n">
-        <v>4.05748319625854</v>
+        <v>4.05748271942139</v>
       </c>
       <c r="H268" t="n">
         <v>4000</v>
@@ -8170,7 +8170,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G269" t="n">
-        <v>3.94206213951111</v>
+        <v>3.94206190109253</v>
       </c>
       <c r="H269" t="n">
         <v>21000</v>
@@ -8199,7 +8199,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>3.90654802322388</v>
+        <v>3.90654826164246</v>
       </c>
       <c r="H270" t="n">
         <v>13000</v>
@@ -8257,7 +8257,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>3.95981955528259</v>
+        <v>3.95981931686401</v>
       </c>
       <c r="H272" t="n">
         <v>11000</v>
@@ -8286,7 +8286,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>3.99089431762695</v>
+        <v>3.99089407920837</v>
       </c>
       <c r="H273" t="n">
         <v>16000</v>
@@ -8373,7 +8373,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G276" t="n">
-        <v>3.844398021698</v>
+        <v>3.84439826011658</v>
       </c>
       <c r="H276" t="n">
         <v>17000</v>
@@ -8460,7 +8460,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G279" t="n">
-        <v>3.81776285171509</v>
+        <v>3.81776309013367</v>
       </c>
       <c r="H279" t="n">
         <v>3000</v>
@@ -8489,7 +8489,7 @@
         <v>4.25</v>
       </c>
       <c r="G280" t="n">
-        <v>3.77337002754211</v>
+        <v>3.77337026596069</v>
       </c>
       <c r="H280" t="n">
         <v>5000</v>
@@ -8518,7 +8518,7 @@
         <v>4.25</v>
       </c>
       <c r="G281" t="n">
-        <v>3.77337002754211</v>
+        <v>3.77337026596069</v>
       </c>
       <c r="H281" t="n">
         <v>4000</v>
@@ -8547,7 +8547,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>3.8133237361908</v>
+        <v>3.81332397460938</v>
       </c>
       <c r="H282" t="n">
         <v>8000</v>
@@ -8576,7 +8576,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G283" t="n">
-        <v>3.81776285171509</v>
+        <v>3.81776309013367</v>
       </c>
       <c r="H283" t="n">
         <v>2000</v>
@@ -8605,7 +8605,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G284" t="n">
-        <v>3.80444478988647</v>
+        <v>3.80444502830505</v>
       </c>
       <c r="H284" t="n">
         <v>10000</v>
@@ -8634,7 +8634,7 @@
         <v>4.25</v>
       </c>
       <c r="G285" t="n">
-        <v>3.77337002754211</v>
+        <v>3.77337026596069</v>
       </c>
       <c r="H285" t="n">
         <v>8000</v>
@@ -8895,7 +8895,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G294" t="n">
-        <v>3.81776285171509</v>
+        <v>3.81776309013367</v>
       </c>
       <c r="H294" t="n">
         <v>6000</v>
@@ -9069,7 +9069,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G300" t="n">
-        <v>3.59136056900024</v>
+        <v>3.5913610458374</v>
       </c>
       <c r="H300" t="n">
         <v>6000</v>
@@ -9098,7 +9098,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G301" t="n">
-        <v>3.50701475143433</v>
+        <v>3.50701498985291</v>
       </c>
       <c r="H301" t="n">
         <v>10000</v>
@@ -9127,7 +9127,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G302" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H302" t="n">
         <v>6000</v>
@@ -9243,7 +9243,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G306" t="n">
-        <v>3.57804298400879</v>
+        <v>3.57804322242737</v>
       </c>
       <c r="H306" t="n">
         <v>6000</v>
@@ -9388,7 +9388,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G311" t="n">
-        <v>3.50257539749146</v>
+        <v>3.50257563591003</v>
       </c>
       <c r="H311" t="n">
         <v>3000</v>
@@ -9417,7 +9417,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G312" t="n">
-        <v>3.46262216567993</v>
+        <v>3.46262240409851</v>
       </c>
       <c r="H312" t="n">
         <v>4000</v>
@@ -9446,7 +9446,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>3.41822934150696</v>
+        <v>3.41822957992554</v>
       </c>
       <c r="H313" t="n">
         <v>2000</v>
@@ -9475,7 +9475,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G314" t="n">
-        <v>3.41822934150696</v>
+        <v>3.41822957992554</v>
       </c>
       <c r="H314" t="n">
         <v>1000</v>
@@ -9504,7 +9504,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G315" t="n">
-        <v>3.33388352394104</v>
+        <v>3.33388376235962</v>
       </c>
       <c r="H315" t="n">
         <v>16000</v>
@@ -9562,7 +9562,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G317" t="n">
-        <v>3.2317807674408</v>
+        <v>3.23178052902222</v>
       </c>
       <c r="H317" t="n">
         <v>10000</v>
@@ -9649,7 +9649,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G320" t="n">
-        <v>3.16075253486633</v>
+        <v>3.16075277328491</v>
       </c>
       <c r="H320" t="n">
         <v>3000</v>
@@ -9678,7 +9678,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G321" t="n">
-        <v>3.09860301017761</v>
+        <v>3.09860277175903</v>
       </c>
       <c r="H321" t="n">
         <v>6000</v>
@@ -9707,7 +9707,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G322" t="n">
-        <v>3.1651918888092</v>
+        <v>3.16519212722778</v>
       </c>
       <c r="H322" t="n">
         <v>4000</v>
@@ -9765,7 +9765,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G324" t="n">
-        <v>3.2317807674408</v>
+        <v>3.23178052902222</v>
       </c>
       <c r="H324" t="n">
         <v>4000</v>
@@ -9823,7 +9823,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G326" t="n">
-        <v>3.16075253486633</v>
+        <v>3.16075277328491</v>
       </c>
       <c r="H326" t="n">
         <v>7000</v>
@@ -9881,7 +9881,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G328" t="n">
-        <v>3.29393005371094</v>
+        <v>3.2939305305481</v>
       </c>
       <c r="H328" t="n">
         <v>17000</v>
@@ -9910,7 +9910,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G329" t="n">
-        <v>3.17407059669495</v>
+        <v>3.17407035827637</v>
       </c>
       <c r="H329" t="n">
         <v>5000</v>
@@ -9939,7 +9939,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G330" t="n">
-        <v>3.19182753562927</v>
+        <v>3.19182777404785</v>
       </c>
       <c r="H330" t="n">
         <v>20000</v>
@@ -9997,7 +9997,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G332" t="n">
-        <v>3.50701475143433</v>
+        <v>3.50701498985291</v>
       </c>
       <c r="H332" t="n">
         <v>20000</v>
@@ -10026,7 +10026,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G333" t="n">
-        <v>3.49813628196716</v>
+        <v>3.49813604354858</v>
       </c>
       <c r="H333" t="n">
         <v>5000</v>
@@ -10055,7 +10055,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>3.46262216567993</v>
+        <v>3.46262240409851</v>
       </c>
       <c r="H334" t="n">
         <v>5000</v>
@@ -10084,7 +10084,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>3.46262216567993</v>
+        <v>3.46262240409851</v>
       </c>
       <c r="H335" t="n">
         <v>11000</v>
@@ -10171,7 +10171,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G338" t="n">
-        <v>3.37827610969543</v>
+        <v>3.37827634811401</v>
       </c>
       <c r="H338" t="n">
         <v>5000</v>
@@ -10229,7 +10229,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G340" t="n">
-        <v>3.8133237361908</v>
+        <v>3.81332397460938</v>
       </c>
       <c r="H340" t="n">
         <v>152000</v>
@@ -10287,7 +10287,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G342" t="n">
-        <v>3.64907121658325</v>
+        <v>3.64907145500183</v>
       </c>
       <c r="H342" t="n">
         <v>9000</v>
@@ -10345,7 +10345,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G344" t="n">
-        <v>3.57804298400879</v>
+        <v>3.57804322242737</v>
       </c>
       <c r="H344" t="n">
         <v>8000</v>
@@ -10374,7 +10374,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H345" t="n">
         <v>7000</v>
@@ -10403,7 +10403,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G346" t="n">
-        <v>3.56028604507446</v>
+        <v>3.56028628349304</v>
       </c>
       <c r="H346" t="n">
         <v>11000</v>
@@ -10432,7 +10432,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G347" t="n">
-        <v>3.81776285171509</v>
+        <v>3.81776309013367</v>
       </c>
       <c r="H347" t="n">
         <v>29000</v>
@@ -10490,7 +10490,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G349" t="n">
-        <v>3.76893091201782</v>
+        <v>3.7689311504364</v>
       </c>
       <c r="H349" t="n">
         <v>2000</v>
@@ -10519,7 +10519,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G350" t="n">
-        <v>3.76893091201782</v>
+        <v>3.7689311504364</v>
       </c>
       <c r="H350" t="n">
         <v>8000</v>
@@ -10664,7 +10664,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G355" t="n">
-        <v>3.91542625427246</v>
+        <v>3.91542601585388</v>
       </c>
       <c r="H355" t="n">
         <v>77000</v>
@@ -10693,7 +10693,7 @@
         <v>4.5</v>
       </c>
       <c r="G356" t="n">
-        <v>3.99533343315125</v>
+        <v>3.99533319473267</v>
       </c>
       <c r="H356" t="n">
         <v>22000</v>
@@ -10722,7 +10722,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>3.97313737869263</v>
+        <v>3.97313714027405</v>
       </c>
       <c r="H357" t="n">
         <v>25000</v>
@@ -10751,7 +10751,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G358" t="n">
-        <v>3.9997730255127</v>
+        <v>3.99977278709412</v>
       </c>
       <c r="H358" t="n">
         <v>13000</v>
@@ -10809,7 +10809,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G360" t="n">
-        <v>3.90654802322388</v>
+        <v>3.90654826164246</v>
       </c>
       <c r="H360" t="n">
         <v>11000</v>
@@ -10838,7 +10838,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>3.96425914764404</v>
+        <v>3.96425890922546</v>
       </c>
       <c r="H361" t="n">
         <v>20000</v>
@@ -10867,7 +10867,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>3.92874455451965</v>
+        <v>3.92874431610107</v>
       </c>
       <c r="H362" t="n">
         <v>34000</v>
@@ -10925,7 +10925,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G364" t="n">
-        <v>3.96869778633118</v>
+        <v>3.9686975479126</v>
       </c>
       <c r="H364" t="n">
         <v>5000</v>
@@ -10954,7 +10954,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G365" t="n">
-        <v>3.9864547252655</v>
+        <v>3.98645424842834</v>
       </c>
       <c r="H365" t="n">
         <v>4000</v>
@@ -10983,7 +10983,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G366" t="n">
-        <v>3.9997730255127</v>
+        <v>3.99977278709412</v>
       </c>
       <c r="H366" t="n">
         <v>31000</v>
@@ -11012,7 +11012,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>3.96425914764404</v>
+        <v>3.96425890922546</v>
       </c>
       <c r="H367" t="n">
         <v>13000</v>
@@ -11041,7 +11041,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G368" t="n">
-        <v>3.9997730255127</v>
+        <v>3.99977278709412</v>
       </c>
       <c r="H368" t="n">
         <v>61000</v>
@@ -11070,7 +11070,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>3.97313737869263</v>
+        <v>3.97313714027405</v>
       </c>
       <c r="H369" t="n">
         <v>37000</v>
@@ -11099,7 +11099,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>3.85327672958374</v>
+        <v>3.8532772064209</v>
       </c>
       <c r="H370" t="n">
         <v>50000</v>
@@ -11389,7 +11389,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G380" t="n">
-        <v>3.51589322090149</v>
+        <v>3.51589345932007</v>
       </c>
       <c r="H380" t="n">
         <v>16000</v>
@@ -11418,7 +11418,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>3.51589322090149</v>
+        <v>3.51589345932007</v>
       </c>
       <c r="H381" t="n">
         <v>21000</v>
@@ -11476,7 +11476,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G383" t="n">
-        <v>3.63575291633606</v>
+        <v>3.63575339317322</v>
       </c>
       <c r="H383" t="n">
         <v>39000</v>
@@ -11534,7 +11534,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G385" t="n">
-        <v>3.60467839241028</v>
+        <v>3.60467863082886</v>
       </c>
       <c r="H385" t="n">
         <v>23000</v>
@@ -11621,7 +11621,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H388" t="n">
         <v>31000</v>
@@ -11650,7 +11650,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G389" t="n">
-        <v>3.64907121658325</v>
+        <v>3.64907145500183</v>
       </c>
       <c r="H389" t="n">
         <v>25000</v>
@@ -11679,7 +11679,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G390" t="n">
-        <v>3.79112696647644</v>
+        <v>3.79112720489502</v>
       </c>
       <c r="H390" t="n">
         <v>21000</v>
@@ -11795,7 +11795,7 @@
         <v>4</v>
       </c>
       <c r="G394" t="n">
-        <v>3.55140709877014</v>
+        <v>3.55140733718872</v>
       </c>
       <c r="H394" t="n">
         <v>26000</v>
@@ -11824,7 +11824,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G395" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H395" t="n">
         <v>9000</v>
@@ -11911,7 +11911,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G398" t="n">
-        <v>3.56028604507446</v>
+        <v>3.56028628349304</v>
       </c>
       <c r="H398" t="n">
         <v>24000</v>
@@ -11940,7 +11940,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>3.59136056900024</v>
+        <v>3.5913610458374</v>
       </c>
       <c r="H399" t="n">
         <v>54000</v>
@@ -11998,7 +11998,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G401" t="n">
-        <v>3.57804298400879</v>
+        <v>3.57804322242737</v>
       </c>
       <c r="H401" t="n">
         <v>18000</v>
@@ -12056,7 +12056,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G403" t="n">
-        <v>3.56472492218018</v>
+        <v>3.56472516059875</v>
       </c>
       <c r="H403" t="n">
         <v>20000</v>
@@ -12172,7 +12172,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G407" t="n">
-        <v>3.59579992294312</v>
+        <v>3.59580016136169</v>
       </c>
       <c r="H407" t="n">
         <v>15000</v>
@@ -12259,7 +12259,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G410" t="n">
-        <v>3.60467839241028</v>
+        <v>3.60467863082886</v>
       </c>
       <c r="H410" t="n">
         <v>28000</v>
@@ -12375,7 +12375,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G414" t="n">
-        <v>3.60467839241028</v>
+        <v>3.60467863082886</v>
       </c>
       <c r="H414" t="n">
         <v>8000</v>
@@ -12462,7 +12462,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G417" t="n">
-        <v>3.64552783966064</v>
+        <v>3.64552760124207</v>
       </c>
       <c r="H417" t="n">
         <v>9000</v>
@@ -12520,7 +12520,7 @@
         <v>4</v>
       </c>
       <c r="G419" t="n">
-        <v>3.64097619056702</v>
+        <v>3.6409764289856</v>
       </c>
       <c r="H419" t="n">
         <v>13000</v>
@@ -12694,7 +12694,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>3.75020551681519</v>
+        <v>3.75020575523376</v>
       </c>
       <c r="H425" t="n">
         <v>18000</v>
@@ -12723,7 +12723,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G426" t="n">
-        <v>3.7593080997467</v>
+        <v>3.75930833816528</v>
       </c>
       <c r="H426" t="n">
         <v>5000</v>
@@ -12926,7 +12926,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G433" t="n">
-        <v>3.70469355583191</v>
+        <v>3.70469379425049</v>
       </c>
       <c r="H433" t="n">
         <v>5000</v>
@@ -12984,7 +12984,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G435" t="n">
-        <v>3.6136691570282</v>
+        <v>3.61366891860962</v>
       </c>
       <c r="H435" t="n">
         <v>6000</v>
@@ -13013,7 +13013,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G436" t="n">
-        <v>3.63187384605408</v>
+        <v>3.63187408447266</v>
       </c>
       <c r="H436" t="n">
         <v>17000</v>
@@ -13042,7 +13042,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G437" t="n">
-        <v>3.7593080997467</v>
+        <v>3.75930833816528</v>
       </c>
       <c r="H437" t="n">
         <v>23000</v>
@@ -13100,7 +13100,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G439" t="n">
-        <v>3.70469355583191</v>
+        <v>3.70469379425049</v>
       </c>
       <c r="H439" t="n">
         <v>20000</v>
@@ -13274,7 +13274,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G445" t="n">
-        <v>3.75020551681519</v>
+        <v>3.75020575523376</v>
       </c>
       <c r="H445" t="n">
         <v>7000</v>
@@ -13361,7 +13361,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G448" t="n">
-        <v>3.80482006072998</v>
+        <v>3.80482029914856</v>
       </c>
       <c r="H448" t="n">
         <v>12000</v>
@@ -13390,7 +13390,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G449" t="n">
-        <v>3.7593080997467</v>
+        <v>3.75930833816528</v>
       </c>
       <c r="H449" t="n">
         <v>17000</v>
@@ -13419,7 +13419,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G450" t="n">
-        <v>3.75020551681519</v>
+        <v>3.75020575523376</v>
       </c>
       <c r="H450" t="n">
         <v>8000</v>
@@ -13477,7 +13477,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G452" t="n">
-        <v>3.75020551681519</v>
+        <v>3.75020575523376</v>
       </c>
       <c r="H452" t="n">
         <v>7000</v>
@@ -13535,7 +13535,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G454" t="n">
-        <v>3.70469355583191</v>
+        <v>3.70469379425049</v>
       </c>
       <c r="H454" t="n">
         <v>25000</v>
@@ -13593,7 +13593,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G456" t="n">
-        <v>3.68648862838745</v>
+        <v>3.68648886680603</v>
       </c>
       <c r="H456" t="n">
         <v>10000</v>
@@ -13651,7 +13651,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>3.68648862838745</v>
+        <v>3.68648886680603</v>
       </c>
       <c r="H458" t="n">
         <v>15000</v>
@@ -13680,7 +13680,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G459" t="n">
-        <v>3.67738604545593</v>
+        <v>3.67738628387451</v>
       </c>
       <c r="H459" t="n">
         <v>6000</v>
@@ -13796,7 +13796,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G463" t="n">
-        <v>3.51354217529297</v>
+        <v>3.51354193687439</v>
       </c>
       <c r="H463" t="n">
         <v>21000</v>
@@ -14637,7 +14637,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>3.39521050453186</v>
+        <v>3.39521026611328</v>
       </c>
       <c r="H492" t="n">
         <v>13000</v>
@@ -14724,7 +14724,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G495" t="n">
-        <v>3.56815695762634</v>
+        <v>3.56815671920776</v>
       </c>
       <c r="H495" t="n">
         <v>69000</v>
@@ -14753,7 +14753,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G496" t="n">
-        <v>3.52264451980591</v>
+        <v>3.52264428138733</v>
       </c>
       <c r="H496" t="n">
         <v>12000</v>
@@ -14811,7 +14811,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G498" t="n">
-        <v>3.52264451980591</v>
+        <v>3.52264428138733</v>
       </c>
       <c r="H498" t="n">
         <v>5000</v>
@@ -15014,7 +15014,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G505" t="n">
-        <v>3.49533724784851</v>
+        <v>3.49533700942993</v>
       </c>
       <c r="H505" t="n">
         <v>5000</v>
@@ -15043,7 +15043,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>3.44982504844666</v>
+        <v>3.44982481002808</v>
       </c>
       <c r="H506" t="n">
         <v>32000</v>
@@ -15362,7 +15362,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G517" t="n">
-        <v>3.34969830513</v>
+        <v>3.34969806671143</v>
       </c>
       <c r="H517" t="n">
         <v>14000</v>
@@ -15565,7 +15565,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G524" t="n">
-        <v>3.30418610572815</v>
+        <v>3.30418586730957</v>
       </c>
       <c r="H524" t="n">
         <v>6000</v>
@@ -15623,7 +15623,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G526" t="n">
-        <v>3.30418610572815</v>
+        <v>3.30418586730957</v>
       </c>
       <c r="H526" t="n">
         <v>2000</v>
@@ -15652,7 +15652,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G527" t="n">
-        <v>3.29508352279663</v>
+        <v>3.29508328437805</v>
       </c>
       <c r="H527" t="n">
         <v>5000</v>
@@ -15681,7 +15681,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>3.29508352279663</v>
+        <v>3.29508328437805</v>
       </c>
       <c r="H528" t="n">
         <v>4000</v>
@@ -16116,7 +16116,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G543" t="n">
-        <v>3.29508352279663</v>
+        <v>3.29508328437805</v>
       </c>
       <c r="H543" t="n">
         <v>21000</v>
@@ -16174,7 +16174,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G545" t="n">
-        <v>3.2313666343689</v>
+        <v>3.23136639595032</v>
       </c>
       <c r="H545" t="n">
         <v>3000</v>
@@ -16203,7 +16203,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G546" t="n">
-        <v>3.1767520904541</v>
+        <v>3.17675185203552</v>
       </c>
       <c r="H546" t="n">
         <v>9000</v>
@@ -16290,7 +16290,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G549" t="n">
-        <v>3.13123989105225</v>
+        <v>3.13123965263367</v>
       </c>
       <c r="H549" t="n">
         <v>15000</v>
@@ -16319,7 +16319,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G550" t="n">
-        <v>3.13123989105225</v>
+        <v>3.13123965263367</v>
       </c>
       <c r="H550" t="n">
         <v>10000</v>
@@ -16348,7 +16348,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G551" t="n">
-        <v>3.1767520904541</v>
+        <v>3.17675185203552</v>
       </c>
       <c r="H551" t="n">
         <v>1000</v>
@@ -16377,7 +16377,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G552" t="n">
-        <v>3.1767520904541</v>
+        <v>3.17675185203552</v>
       </c>
       <c r="H552" t="n">
         <v>1000</v>
@@ -16464,7 +16464,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G555" t="n">
-        <v>3.15854692459106</v>
+        <v>3.15854716300964</v>
       </c>
       <c r="H555" t="n">
         <v>12000</v>
@@ -16638,7 +16638,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G561" t="n">
-        <v>2.62150287628174</v>
+        <v>2.62150311470032</v>
       </c>
       <c r="H561" t="n">
         <v>88000</v>
@@ -16696,7 +16696,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G563" t="n">
-        <v>2.62150287628174</v>
+        <v>2.62150311470032</v>
       </c>
       <c r="H563" t="n">
         <v>98000</v>
@@ -16725,7 +16725,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>2.63970804214478</v>
+        <v>2.6397078037262</v>
       </c>
       <c r="H564" t="n">
         <v>5000</v>
@@ -16754,7 +16754,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G565" t="n">
-        <v>2.66701507568359</v>
+        <v>2.66701531410217</v>
       </c>
       <c r="H565" t="n">
         <v>16000</v>
@@ -16812,7 +16812,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.67611742019653</v>
+        <v>2.67611765861511</v>
       </c>
       <c r="H567" t="n">
         <v>12000</v>
@@ -16957,7 +16957,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G572" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H572" t="n">
         <v>20000</v>
@@ -17044,7 +17044,7 @@
         <v>2.75</v>
       </c>
       <c r="G575" t="n">
-        <v>2.50317120552063</v>
+        <v>2.50317144393921</v>
       </c>
       <c r="H575" t="n">
         <v>5000</v>
@@ -17102,7 +17102,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H577" t="n">
         <v>1000</v>
@@ -17160,7 +17160,7 @@
         <v>2.75</v>
       </c>
       <c r="G579" t="n">
-        <v>2.50317120552063</v>
+        <v>2.50317144393921</v>
       </c>
       <c r="H579" t="n">
         <v>7000</v>
@@ -17363,7 +17363,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G586" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H586" t="n">
         <v>13000</v>
@@ -17392,7 +17392,7 @@
         <v>2.75</v>
       </c>
       <c r="G587" t="n">
-        <v>2.50317120552063</v>
+        <v>2.50317144393921</v>
       </c>
       <c r="H587" t="n">
         <v>7000</v>
@@ -17537,7 +17537,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G592" t="n">
-        <v>2.45765900611877</v>
+        <v>2.45765924453735</v>
       </c>
       <c r="H592" t="n">
         <v>4000</v>
@@ -17972,7 +17972,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G607" t="n">
-        <v>2.33022475242615</v>
+        <v>2.33022499084473</v>
       </c>
       <c r="H607" t="n">
         <v>3000</v>
@@ -18001,7 +18001,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G608" t="n">
-        <v>2.33022475242615</v>
+        <v>2.33022499084473</v>
       </c>
       <c r="H608" t="n">
         <v>2000</v>
@@ -18117,7 +18117,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G612" t="n">
-        <v>2.40304446220398</v>
+        <v>2.40304470062256</v>
       </c>
       <c r="H612" t="n">
         <v>7000</v>
@@ -18146,7 +18146,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G613" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H613" t="n">
         <v>9000</v>
@@ -18204,7 +18204,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G615" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H615" t="n">
         <v>6000</v>
@@ -18262,7 +18262,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G617" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H617" t="n">
         <v>5000</v>
@@ -18291,7 +18291,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G618" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18465,7 +18465,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>2.34842967987061</v>
+        <v>2.34842991828918</v>
       </c>
       <c r="H624" t="n">
         <v>4000</v>
@@ -18494,7 +18494,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G625" t="n">
-        <v>2.34842967987061</v>
+        <v>2.34842991828918</v>
       </c>
       <c r="H625" t="n">
         <v>0</v>
@@ -18523,7 +18523,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G626" t="n">
-        <v>2.34842967987061</v>
+        <v>2.34842991828918</v>
       </c>
       <c r="H626" t="n">
         <v>1000</v>
@@ -18639,7 +18639,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G630" t="n">
-        <v>2.45765900611877</v>
+        <v>2.45765924453735</v>
       </c>
       <c r="H630" t="n">
         <v>8000</v>
@@ -18668,7 +18668,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G631" t="n">
-        <v>2.44855666160583</v>
+        <v>2.44855690002441</v>
       </c>
       <c r="H631" t="n">
         <v>6000</v>
@@ -18784,7 +18784,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G635" t="n">
-        <v>2.44855666160583</v>
+        <v>2.44855690002441</v>
       </c>
       <c r="H635" t="n">
         <v>2000</v>
@@ -18813,7 +18813,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G636" t="n">
-        <v>2.44855666160583</v>
+        <v>2.44855690002441</v>
       </c>
       <c r="H636" t="n">
         <v>0</v>
@@ -18900,7 +18900,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G639" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H639" t="n">
         <v>27000</v>
@@ -18929,7 +18929,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G640" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H640" t="n">
         <v>5000</v>
@@ -19132,7 +19132,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H647" t="n">
         <v>33000</v>
@@ -19161,7 +19161,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G648" t="n">
-        <v>2.16638112068176</v>
+        <v>2.16638088226318</v>
       </c>
       <c r="H648" t="n">
         <v>7000</v>
@@ -19190,7 +19190,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G649" t="n">
-        <v>2.07535648345947</v>
+        <v>2.07535624504089</v>
       </c>
       <c r="H649" t="n">
         <v>31000</v>
@@ -19219,7 +19219,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G650" t="n">
-        <v>2.09356141090393</v>
+        <v>2.09356117248535</v>
       </c>
       <c r="H650" t="n">
         <v>14000</v>
@@ -19306,7 +19306,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G653" t="n">
-        <v>2.19368815422058</v>
+        <v>2.19368839263916</v>
       </c>
       <c r="H653" t="n">
         <v>52000</v>
@@ -19335,7 +19335,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G654" t="n">
-        <v>2.12086868286133</v>
+        <v>2.12086844444275</v>
       </c>
       <c r="H654" t="n">
         <v>10000</v>
@@ -19393,7 +19393,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.46676182746887</v>
+        <v>2.46676158905029</v>
       </c>
       <c r="H656" t="n">
         <v>160000</v>
@@ -19422,7 +19422,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G657" t="n">
-        <v>2.54868340492249</v>
+        <v>2.54868364334106</v>
       </c>
       <c r="H657" t="n">
         <v>114000</v>
@@ -19480,7 +19480,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G659" t="n">
-        <v>2.40304446220398</v>
+        <v>2.40304470062256</v>
       </c>
       <c r="H659" t="n">
         <v>20000</v>
@@ -19509,7 +19509,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>2.2027907371521</v>
+        <v>2.20279097557068</v>
       </c>
       <c r="H660" t="n">
         <v>51000</v>
@@ -19567,7 +19567,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>2.15727829933167</v>
+        <v>2.15727853775024</v>
       </c>
       <c r="H662" t="n">
         <v>37000</v>
@@ -19683,7 +19683,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G666" t="n">
-        <v>2.15727829933167</v>
+        <v>2.15727853775024</v>
       </c>
       <c r="H666" t="n">
         <v>3000</v>
@@ -19770,7 +19770,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G669" t="n">
-        <v>2.16638112068176</v>
+        <v>2.16638088226318</v>
       </c>
       <c r="H669" t="n">
         <v>22000</v>
@@ -19799,7 +19799,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H670" t="n">
         <v>3000</v>
@@ -19828,7 +19828,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>2.18458580970764</v>
+        <v>2.18458604812622</v>
       </c>
       <c r="H671" t="n">
         <v>5000</v>
@@ -19857,7 +19857,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G672" t="n">
-        <v>2.14817595481873</v>
+        <v>2.14817571640015</v>
       </c>
       <c r="H672" t="n">
         <v>11000</v>
@@ -19973,7 +19973,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>2.12086868286133</v>
+        <v>2.12086844444275</v>
       </c>
       <c r="H676" t="n">
         <v>12000</v>
@@ -20031,7 +20031,7 @@
         <v>2.25</v>
       </c>
       <c r="G678" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H678" t="n">
         <v>3000</v>
@@ -20060,7 +20060,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G679" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H679" t="n">
         <v>1000</v>
@@ -20089,7 +20089,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G680" t="n">
-        <v>2.07535648345947</v>
+        <v>2.07535624504089</v>
       </c>
       <c r="H680" t="n">
         <v>2000</v>
@@ -20176,7 +20176,7 @@
         <v>2.25</v>
       </c>
       <c r="G683" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H683" t="n">
         <v>2000</v>
@@ -20205,7 +20205,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>2.12086868286133</v>
+        <v>2.12086844444275</v>
       </c>
       <c r="H684" t="n">
         <v>4000</v>
@@ -20263,7 +20263,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G686" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H686" t="n">
         <v>3000</v>
@@ -20292,7 +20292,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G687" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H687" t="n">
         <v>0</v>
@@ -20321,7 +20321,7 @@
         <v>2.25</v>
       </c>
       <c r="G688" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H688" t="n">
         <v>4000</v>
@@ -20350,7 +20350,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G689" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H689" t="n">
         <v>2000</v>
@@ -20379,7 +20379,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G690" t="n">
-        <v>2.00253701210022</v>
+        <v>2.00253677368164</v>
       </c>
       <c r="H690" t="n">
         <v>2000</v>
@@ -20408,7 +20408,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G691" t="n">
-        <v>1.96612727642059</v>
+        <v>1.9661271572113</v>
       </c>
       <c r="H691" t="n">
         <v>5000</v>
@@ -20437,7 +20437,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G692" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H692" t="n">
         <v>6000</v>
@@ -20466,7 +20466,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G693" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -20495,7 +20495,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G694" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H694" t="n">
         <v>0</v>
@@ -20553,7 +20553,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G696" t="n">
-        <v>2.00253701210022</v>
+        <v>2.00253677368164</v>
       </c>
       <c r="H696" t="n">
         <v>2000</v>
@@ -20756,7 +20756,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G703" t="n">
-        <v>1.90241003036499</v>
+        <v>1.90241014957428</v>
       </c>
       <c r="H703" t="n">
         <v>2000</v>
@@ -20785,7 +20785,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G704" t="n">
-        <v>1.90241003036499</v>
+        <v>1.90241014957428</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -20814,7 +20814,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G705" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H705" t="n">
         <v>13000</v>
@@ -20843,7 +20843,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G706" t="n">
-        <v>1.61568331718445</v>
+        <v>1.61568319797516</v>
       </c>
       <c r="H706" t="n">
         <v>35000</v>
@@ -20872,7 +20872,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G707" t="n">
-        <v>1.674849152565</v>
+        <v>1.67484903335571</v>
       </c>
       <c r="H707" t="n">
         <v>25000</v>
@@ -20901,7 +20901,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>1.72491252422333</v>
+        <v>1.72491240501404</v>
       </c>
       <c r="H708" t="n">
         <v>4000</v>
@@ -20930,7 +20930,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G709" t="n">
-        <v>1.69760525226593</v>
+        <v>1.69760513305664</v>
       </c>
       <c r="H709" t="n">
         <v>7000</v>
@@ -20959,7 +20959,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G710" t="n">
-        <v>1.73856616020203</v>
+        <v>1.73856604099274</v>
       </c>
       <c r="H710" t="n">
         <v>5000</v>
@@ -20988,7 +20988,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G711" t="n">
-        <v>1.77497601509094</v>
+        <v>1.77497589588165</v>
       </c>
       <c r="H711" t="n">
         <v>8000</v>
@@ -21133,7 +21133,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G716" t="n">
-        <v>1.73856616020203</v>
+        <v>1.73856604099274</v>
       </c>
       <c r="H716" t="n">
         <v>14000</v>
@@ -21162,7 +21162,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G717" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132214069366</v>
       </c>
       <c r="H717" t="n">
         <v>1000</v>
@@ -21191,7 +21191,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G718" t="n">
-        <v>1.73856616020203</v>
+        <v>1.73856604099274</v>
       </c>
       <c r="H718" t="n">
         <v>2000</v>
@@ -21278,7 +21278,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G721" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H721" t="n">
         <v>2000</v>
@@ -21307,7 +21307,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G722" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H722" t="n">
         <v>0</v>
@@ -21336,7 +21336,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G723" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H723" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G724" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H724" t="n">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G736" t="n">
-        <v>1.64754176139832</v>
+        <v>1.64754164218903</v>
       </c>
       <c r="H736" t="n">
         <v>5000</v>
@@ -21742,7 +21742,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G737" t="n">
-        <v>1.66574656963348</v>
+        <v>1.66574668884277</v>
       </c>
       <c r="H737" t="n">
         <v>2000</v>
@@ -21771,7 +21771,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G738" t="n">
-        <v>1.66574656963348</v>
+        <v>1.66574668884277</v>
       </c>
       <c r="H738" t="n">
         <v>8000</v>
@@ -21829,7 +21829,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G740" t="n">
-        <v>2.12086868286133</v>
+        <v>2.12086844444275</v>
       </c>
       <c r="H740" t="n">
         <v>43000</v>
@@ -21858,7 +21858,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G741" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H741" t="n">
         <v>81000</v>
@@ -21945,7 +21945,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G744" t="n">
-        <v>1.96612727642059</v>
+        <v>1.9661271572113</v>
       </c>
       <c r="H744" t="n">
         <v>12000</v>
@@ -22032,7 +22032,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G747" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H747" t="n">
         <v>12000</v>
@@ -22264,7 +22264,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G755" t="n">
-        <v>1.90241003036499</v>
+        <v>1.90241014957428</v>
       </c>
       <c r="H755" t="n">
         <v>3000</v>
@@ -22322,7 +22322,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G757" t="n">
-        <v>1.90241003036499</v>
+        <v>1.90241014957428</v>
       </c>
       <c r="H757" t="n">
         <v>3000</v>
@@ -22525,7 +22525,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G764" t="n">
-        <v>2.14817595481873</v>
+        <v>2.14817571640015</v>
       </c>
       <c r="H764" t="n">
         <v>1000</v>
@@ -22554,7 +22554,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G765" t="n">
-        <v>2.14817595481873</v>
+        <v>2.14817571640015</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G766" t="n">
-        <v>2.09356141090393</v>
+        <v>2.09356117248535</v>
       </c>
       <c r="H766" t="n">
         <v>3000</v>
@@ -22612,7 +22612,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>2.09356141090393</v>
+        <v>2.09356117248535</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -22641,7 +22641,7 @@
         <v>2.25</v>
       </c>
       <c r="G768" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H768" t="n">
         <v>1000</v>
@@ -22670,7 +22670,7 @@
         <v>2.25</v>
       </c>
       <c r="G769" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H769" t="n">
         <v>0</v>
@@ -22699,7 +22699,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G770" t="n">
-        <v>2.00253701210022</v>
+        <v>2.00253677368164</v>
       </c>
       <c r="H770" t="n">
         <v>1000</v>
@@ -22728,7 +22728,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G771" t="n">
-        <v>2.00253701210022</v>
+        <v>2.00253677368164</v>
       </c>
       <c r="H771" t="n">
         <v>0</v>
@@ -22873,7 +22873,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>2.09356141090393</v>
+        <v>2.09356117248535</v>
       </c>
       <c r="H776" t="n">
         <v>3000</v>
@@ -22902,7 +22902,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G777" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H777" t="n">
         <v>7000</v>
@@ -22931,7 +22931,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G778" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H778" t="n">
         <v>0</v>
@@ -23047,7 +23047,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G782" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H782" t="n">
         <v>6000</v>
@@ -23076,7 +23076,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G783" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H783" t="n">
         <v>5000</v>
@@ -23105,7 +23105,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G784" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H784" t="n">
         <v>0</v>
@@ -23134,7 +23134,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G785" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H785" t="n">
         <v>0</v>
@@ -23163,7 +23163,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G786" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H786" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G787" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H787" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G788" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H788" t="n">
         <v>0</v>
@@ -23250,7 +23250,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G789" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H789" t="n">
         <v>0</v>
@@ -23279,7 +23279,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G790" t="n">
-        <v>2.03894686698914</v>
+        <v>2.03894662857056</v>
       </c>
       <c r="H790" t="n">
         <v>0</v>
@@ -23308,7 +23308,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G791" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H791" t="n">
         <v>2000</v>
@@ -23424,7 +23424,7 @@
         <v>2.25</v>
       </c>
       <c r="G795" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H795" t="n">
         <v>1000</v>
@@ -23453,7 +23453,7 @@
         <v>2.25</v>
       </c>
       <c r="G796" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H796" t="n">
         <v>0</v>
@@ -23482,7 +23482,7 @@
         <v>2.25</v>
       </c>
       <c r="G797" t="n">
-        <v>2.04804921150208</v>
+        <v>2.0480489730835</v>
       </c>
       <c r="H797" t="n">
         <v>0</v>
@@ -23540,7 +23540,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G799" t="n">
-        <v>1.99343466758728</v>
+        <v>1.9934344291687</v>
       </c>
       <c r="H799" t="n">
         <v>2000</v>
@@ -23569,7 +23569,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G800" t="n">
-        <v>1.95702481269836</v>
+        <v>1.95702469348907</v>
       </c>
       <c r="H800" t="n">
         <v>5000</v>
@@ -23685,7 +23685,7 @@
         <v>2</v>
       </c>
       <c r="G804" t="n">
-        <v>1.82048809528351</v>
+        <v>1.8204882144928</v>
       </c>
       <c r="H804" t="n">
         <v>3000</v>
@@ -23714,7 +23714,7 @@
         <v>2</v>
       </c>
       <c r="G805" t="n">
-        <v>1.82048809528351</v>
+        <v>1.8204882144928</v>
       </c>
       <c r="H805" t="n">
         <v>0</v>
@@ -23801,7 +23801,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G808" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H808" t="n">
         <v>9000</v>
@@ -23830,7 +23830,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G809" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H809" t="n">
         <v>0</v>
@@ -23917,7 +23917,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G812" t="n">
-        <v>1.87510275840759</v>
+        <v>1.87510287761688</v>
       </c>
       <c r="H812" t="n">
         <v>4000</v>
@@ -24091,7 +24091,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G818" t="n">
-        <v>1.90241003036499</v>
+        <v>1.90241014957428</v>
       </c>
       <c r="H818" t="n">
         <v>2000</v>
@@ -24149,7 +24149,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G820" t="n">
-        <v>1.7795273065567</v>
+        <v>1.77952718734741</v>
       </c>
       <c r="H820" t="n">
         <v>8000</v>
@@ -24265,7 +24265,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H824" t="n">
         <v>1000</v>
@@ -24294,7 +24294,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H825" t="n">
         <v>0</v>
@@ -24323,7 +24323,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G826" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H826" t="n">
         <v>0</v>
@@ -24352,7 +24352,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -24381,7 +24381,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H828" t="n">
         <v>0</v>
@@ -24410,7 +24410,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G829" t="n">
-        <v>1.75677108764648</v>
+        <v>1.75677096843719</v>
       </c>
       <c r="H829" t="n">
         <v>1000</v>
@@ -24526,7 +24526,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.72491252422333</v>
+        <v>1.72491240501404</v>
       </c>
       <c r="H833" t="n">
         <v>5000</v>
@@ -24642,7 +24642,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G837" t="n">
-        <v>1.66574656963348</v>
+        <v>1.66574668884277</v>
       </c>
       <c r="H837" t="n">
         <v>1000</v>
@@ -24671,7 +24671,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G838" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H838" t="n">
         <v>15000</v>
@@ -24903,7 +24903,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G846" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H846" t="n">
         <v>7000</v>
@@ -24990,7 +24990,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G849" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H849" t="n">
         <v>9000</v>
@@ -25019,7 +25019,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G850" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H850" t="n">
         <v>8000</v>
@@ -25106,7 +25106,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G853" t="n">
-        <v>1.81593692302704</v>
+        <v>1.81593704223633</v>
       </c>
       <c r="H853" t="n">
         <v>3000</v>
@@ -25135,7 +25135,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G854" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H854" t="n">
         <v>1000</v>
@@ -25193,7 +25193,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G856" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132214069366</v>
       </c>
       <c r="H856" t="n">
         <v>1000</v>
@@ -25222,7 +25222,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G857" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132214069366</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -25280,7 +25280,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G859" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H859" t="n">
         <v>7000</v>
@@ -25309,7 +25309,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G860" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H860" t="n">
         <v>0</v>
@@ -25396,7 +25396,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G863" t="n">
-        <v>1.73401498794556</v>
+        <v>1.73401486873627</v>
       </c>
       <c r="H863" t="n">
         <v>2000</v>
@@ -25541,7 +25541,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G868" t="n">
-        <v>1.674849152565</v>
+        <v>1.67484903335571</v>
       </c>
       <c r="H868" t="n">
         <v>4000</v>
@@ -25570,7 +25570,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G869" t="n">
-        <v>1.64754176139832</v>
+        <v>1.64754164218903</v>
       </c>
       <c r="H869" t="n">
         <v>7000</v>
@@ -25715,7 +25715,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G874" t="n">
-        <v>1.66574656963348</v>
+        <v>1.66574668884277</v>
       </c>
       <c r="H874" t="n">
         <v>7000</v>
@@ -25744,7 +25744,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>1.72491252422333</v>
+        <v>1.72491240501404</v>
       </c>
       <c r="H875" t="n">
         <v>3000</v>
@@ -25831,7 +25831,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G878" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H878" t="n">
         <v>9000</v>
@@ -25947,7 +25947,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G882" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H882" t="n">
         <v>12000</v>
@@ -26121,7 +26121,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G888" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H888" t="n">
         <v>20000</v>
@@ -26179,7 +26179,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G890" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H890" t="n">
         <v>9000</v>
@@ -26382,7 +26382,7 @@
         <v>2</v>
       </c>
       <c r="G897" t="n">
-        <v>1.82048809528351</v>
+        <v>1.8204882144928</v>
       </c>
       <c r="H897" t="n">
         <v>10000</v>
@@ -26469,7 +26469,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G900" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H900" t="n">
         <v>1000</v>
@@ -26498,7 +26498,7 @@
         <v>2</v>
       </c>
       <c r="G901" t="n">
-        <v>1.82048809528351</v>
+        <v>1.8204882144928</v>
       </c>
       <c r="H901" t="n">
         <v>1000</v>
@@ -26672,7 +26672,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H907" t="n">
         <v>2000</v>
@@ -26701,7 +26701,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G908" t="n">
-        <v>1.81593692302704</v>
+        <v>1.81593704223633</v>
       </c>
       <c r="H908" t="n">
         <v>6000</v>
@@ -26730,7 +26730,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G909" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H909" t="n">
         <v>7000</v>
@@ -26788,7 +26788,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G911" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H911" t="n">
         <v>2000</v>
@@ -26817,7 +26817,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G912" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -26846,7 +26846,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G913" t="n">
-        <v>1.78407847881317</v>
+        <v>1.78407835960388</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -26875,7 +26875,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G914" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H914" t="n">
         <v>3000</v>
@@ -26904,7 +26904,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G915" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -26933,7 +26933,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G916" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -26962,7 +26962,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G917" t="n">
-        <v>1.8068345785141</v>
+        <v>1.80683445930481</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -26991,7 +26991,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132214069366</v>
       </c>
       <c r="H918" t="n">
         <v>7000</v>
@@ -27020,7 +27020,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G919" t="n">
-        <v>1.74766862392426</v>
+        <v>1.74766850471497</v>
       </c>
       <c r="H919" t="n">
         <v>1000</v>
@@ -27049,7 +27049,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G920" t="n">
-        <v>1.75677108764648</v>
+        <v>1.75677096843719</v>
       </c>
       <c r="H920" t="n">
         <v>2000</v>
@@ -27136,7 +27136,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G923" t="n">
-        <v>1.76132225990295</v>
+        <v>1.76132214069366</v>
       </c>
       <c r="H923" t="n">
         <v>5000</v>
@@ -27165,7 +27165,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G924" t="n">
-        <v>1.7795273065567</v>
+        <v>1.77952718734741</v>
       </c>
       <c r="H924" t="n">
         <v>3000</v>
@@ -27194,7 +27194,7 @@
         <v>2</v>
       </c>
       <c r="G925" t="n">
-        <v>1.82048809528351</v>
+        <v>1.8204882144928</v>
       </c>
       <c r="H925" t="n">
         <v>3000</v>
@@ -27223,7 +27223,7 @@
         <v>2</v>
       </c>
       <c r="G926" t="n">
-        <v>1.82048809528351</v>
+        <v>1.8204882144928</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -27252,7 +27252,7 @@
         <v>2</v>
       </c>
       <c r="G927" t="n">
-        <v>1.82048809528351</v>
+        <v>1.8204882144928</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>2</v>
       </c>
       <c r="G935" t="n">
-        <v>1.82048809528351</v>
+        <v>1.8204882144928</v>
       </c>
       <c r="H935" t="n">
         <v>3000</v>
@@ -27571,7 +27571,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G938" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H938" t="n">
         <v>1000</v>
@@ -27629,7 +27629,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G940" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H940" t="n">
         <v>6000</v>
@@ -27658,7 +27658,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H941" t="n">
         <v>2000</v>
@@ -27687,7 +27687,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G942" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H942" t="n">
         <v>2000</v>
@@ -27716,7 +27716,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G943" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -27745,7 +27745,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G944" t="n">
-        <v>1.87510275840759</v>
+        <v>1.87510287761688</v>
       </c>
       <c r="H944" t="n">
         <v>1000</v>
@@ -27774,7 +27774,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G945" t="n">
-        <v>1.87510275840759</v>
+        <v>1.87510287761688</v>
       </c>
       <c r="H945" t="n">
         <v>0</v>
@@ -27803,7 +27803,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G946" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H946" t="n">
         <v>2000</v>
@@ -27832,7 +27832,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G947" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -27861,7 +27861,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G948" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H948" t="n">
         <v>12000</v>
@@ -27890,7 +27890,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H949" t="n">
         <v>1000</v>
@@ -27919,7 +27919,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G950" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H950" t="n">
         <v>2000</v>
@@ -27948,7 +27948,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G951" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H951" t="n">
         <v>1000</v>
@@ -28006,7 +28006,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G953" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H953" t="n">
         <v>5000</v>
@@ -28035,7 +28035,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G954" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H954" t="n">
         <v>2000</v>
@@ -28093,7 +28093,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G956" t="n">
-        <v>1.83869302272797</v>
+        <v>1.83869314193726</v>
       </c>
       <c r="H956" t="n">
         <v>2000</v>
@@ -28122,7 +28122,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G957" t="n">
-        <v>1.80228340625763</v>
+        <v>1.80228328704834</v>
       </c>
       <c r="H957" t="n">
         <v>1000</v>
@@ -28383,7 +28383,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G966" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H966" t="n">
         <v>18000</v>
@@ -28412,7 +28412,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G967" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H967" t="n">
         <v>13000</v>
@@ -29021,7 +29021,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G988" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H988" t="n">
         <v>3000</v>
@@ -29050,7 +29050,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G989" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H989" t="n">
         <v>0</v>
@@ -29079,7 +29079,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G990" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -29311,7 +29311,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G998" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H998" t="n">
         <v>2000</v>
@@ -29340,7 +29340,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G999" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -29398,7 +29398,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1001" t="n">
         <v>2000</v>
@@ -29427,7 +29427,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1002" t="n">
         <v>0</v>
@@ -29601,7 +29601,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1008" t="n">
         <v>14000</v>
@@ -29630,7 +29630,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -29659,7 +29659,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -29688,7 +29688,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -29717,7 +29717,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1012" t="n">
         <v>3000</v>
@@ -29746,7 +29746,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1013" t="n">
         <v>4000</v>
@@ -29775,7 +29775,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -29862,7 +29862,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1017" t="n">
         <v>1000</v>
@@ -29891,7 +29891,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -29920,7 +29920,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1019" t="n">
         <v>1000</v>
@@ -29949,7 +29949,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1020" t="n">
         <v>5000</v>
@@ -29978,7 +29978,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1021" t="n">
         <v>1000</v>
@@ -30007,7 +30007,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1022" t="n">
         <v>0</v>
@@ -30036,7 +30036,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1023" t="n">
         <v>1000</v>
@@ -30065,7 +30065,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1024" t="n">
         <v>2000</v>
@@ -30094,7 +30094,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1025" t="n">
         <v>14000</v>
@@ -30123,7 +30123,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1026" t="n">
         <v>5000</v>
@@ -30384,7 +30384,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1035" t="n">
         <v>5000</v>
@@ -30413,7 +30413,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -30442,7 +30442,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1037" t="n">
         <v>1000</v>
@@ -30500,7 +30500,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1039" t="n">
         <v>5000</v>
@@ -30529,7 +30529,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1040" t="n">
         <v>3000</v>
@@ -30558,7 +30558,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1041" t="n">
         <v>2000</v>
@@ -30587,7 +30587,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -30616,7 +30616,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1043" t="n">
         <v>1000</v>
@@ -30732,7 +30732,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1047" t="n">
         <v>3000</v>
@@ -30761,7 +30761,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1048" t="n">
         <v>3000</v>
@@ -30790,7 +30790,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1049" t="n">
         <v>0</v>
@@ -30848,7 +30848,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1051" t="n">
         <v>3000</v>
@@ -30877,7 +30877,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -30906,7 +30906,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1053" t="n">
         <v>0</v>
@@ -30935,7 +30935,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1054" t="n">
         <v>2000</v>
@@ -31080,7 +31080,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1059" t="n">
         <v>12000</v>
@@ -31109,7 +31109,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1060" t="n">
         <v>2000</v>
@@ -31138,7 +31138,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1061" t="n">
         <v>2000</v>
@@ -31167,7 +31167,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1062" t="n">
         <v>4000</v>
@@ -31196,7 +31196,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1063" t="n">
         <v>3000</v>
@@ -31225,7 +31225,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1064" t="n">
         <v>6000</v>
@@ -31312,7 +31312,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1067" t="n">
         <v>11000</v>
@@ -31341,7 +31341,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1068" t="n">
         <v>2000</v>
@@ -31370,7 +31370,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1069" t="n">
         <v>10000</v>
@@ -31399,7 +31399,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1070" t="n">
         <v>12000</v>
@@ -31428,7 +31428,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1071" t="n">
         <v>3000</v>
@@ -31457,7 +31457,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1072" t="n">
         <v>1000</v>
@@ -31486,7 +31486,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1073" t="n">
         <v>0</v>
@@ -31515,7 +31515,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1074" t="n">
         <v>0</v>
@@ -31631,7 +31631,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1078" t="n">
         <v>5000</v>
@@ -31863,7 +31863,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1086" t="n">
         <v>6000</v>
@@ -31892,7 +31892,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1087" t="n">
         <v>3000</v>
@@ -32037,7 +32037,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1092" t="n">
         <v>12000</v>
@@ -32066,7 +32066,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1093" t="n">
         <v>5000</v>
@@ -32095,7 +32095,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1094" t="n">
         <v>20000</v>
@@ -32124,7 +32124,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.47795939445496</v>
+        <v>1.47795927524567</v>
       </c>
       <c r="H1095" t="n">
         <v>11000</v>
@@ -32153,7 +32153,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1096" t="n">
         <v>11000</v>
@@ -32240,7 +32240,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1099" t="n">
         <v>2000</v>
@@ -32356,7 +32356,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1103" t="n">
         <v>14000</v>
@@ -32385,7 +32385,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1104" t="n">
         <v>3000</v>
@@ -32472,7 +32472,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1107" t="n">
         <v>6000</v>
@@ -32501,7 +32501,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1108" t="n">
         <v>0</v>
@@ -32617,7 +32617,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1112" t="n">
         <v>3000</v>
@@ -32646,7 +32646,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1113" t="n">
         <v>0</v>
@@ -32733,7 +32733,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.47795939445496</v>
+        <v>1.47795927524567</v>
       </c>
       <c r="H1116" t="n">
         <v>23000</v>
@@ -32849,7 +32849,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1120" t="n">
         <v>32000</v>
@@ -32965,7 +32965,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1124" t="n">
         <v>33000</v>
@@ -33023,7 +33023,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1126" t="n">
         <v>6000</v>
@@ -33081,7 +33081,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1128" t="n">
         <v>3000</v>
@@ -33168,7 +33168,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1131" t="n">
         <v>5000</v>
@@ -33255,7 +33255,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.4971536397934</v>
+        <v>1.49715352058411</v>
       </c>
       <c r="H1134" t="n">
         <v>4000</v>
@@ -33516,7 +33516,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.36279356479645</v>
+        <v>1.36279368400574</v>
       </c>
       <c r="H1143" t="n">
         <v>2000</v>
@@ -33545,7 +33545,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1144" t="n">
         <v>2000</v>
@@ -33661,7 +33661,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1148" t="n">
         <v>9000</v>
@@ -33690,7 +33690,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1149" t="n">
         <v>5000</v>
@@ -33864,7 +33864,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.36279356479645</v>
+        <v>1.36279368400574</v>
       </c>
       <c r="H1155" t="n">
         <v>10000</v>
@@ -33893,7 +33893,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.36279356479645</v>
+        <v>1.36279368400574</v>
       </c>
       <c r="H1156" t="n">
         <v>0</v>
@@ -33922,7 +33922,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.42997372150421</v>
+        <v>1.42997360229492</v>
       </c>
       <c r="H1157" t="n">
         <v>28000</v>
@@ -34009,7 +34009,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1160" t="n">
         <v>5000</v>
@@ -34067,7 +34067,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.42997372150421</v>
+        <v>1.42997360229492</v>
       </c>
       <c r="H1162" t="n">
         <v>8000</v>
@@ -34096,7 +34096,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1163" t="n">
         <v>6000</v>
@@ -34154,7 +34154,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1165" t="n">
         <v>8000</v>
@@ -34183,7 +34183,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.42997372150421</v>
+        <v>1.42997360229492</v>
       </c>
       <c r="H1166" t="n">
         <v>8000</v>
@@ -34241,7 +34241,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.42997372150421</v>
+        <v>1.42997360229492</v>
       </c>
       <c r="H1168" t="n">
         <v>4000</v>
@@ -34270,7 +34270,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.41077947616577</v>
+        <v>1.41077935695648</v>
       </c>
       <c r="H1169" t="n">
         <v>6000</v>
@@ -34357,7 +34357,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1172" t="n">
         <v>8000</v>
@@ -34444,7 +34444,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1175" t="n">
         <v>21000</v>
@@ -34502,7 +34502,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1177" t="n">
         <v>2000</v>
@@ -34647,7 +34647,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.39158523082733</v>
+        <v>1.39158511161804</v>
       </c>
       <c r="H1182" t="n">
         <v>8000</v>
@@ -34908,7 +34908,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1191" t="n">
         <v>75000</v>
@@ -34937,7 +34937,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1192" t="n">
-        <v>1.5259450674057</v>
+        <v>1.52594518661499</v>
       </c>
       <c r="H1192" t="n">
         <v>77000</v>
@@ -34995,7 +34995,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1194" t="n">
         <v>95000</v>
@@ -35053,7 +35053,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1196" t="n">
         <v>16000</v>
@@ -35140,7 +35140,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1199" t="n">
         <v>60000</v>
@@ -35169,7 +35169,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.95781624317169</v>
+        <v>1.95781636238098</v>
       </c>
       <c r="H1200" t="n">
         <v>89000</v>
@@ -35198,7 +35198,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.95781624317169</v>
+        <v>1.95781636238098</v>
       </c>
       <c r="H1201" t="n">
         <v>148000</v>
@@ -35256,7 +35256,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.84265053272247</v>
+        <v>1.84265065193176</v>
       </c>
       <c r="H1203" t="n">
         <v>24000</v>
@@ -35314,7 +35314,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1205" t="n">
         <v>72000</v>
@@ -35343,7 +35343,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1206" t="n">
         <v>18000</v>
@@ -35401,7 +35401,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1208" t="n">
         <v>4000</v>
@@ -35430,7 +35430,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1209" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1209" t="n">
         <v>10000</v>
@@ -35488,7 +35488,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1211" t="n">
         <v>36000</v>
@@ -35517,7 +35517,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1212" t="n">
         <v>3000</v>
@@ -35546,7 +35546,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1213" t="n">
         <v>11000</v>
@@ -35575,7 +35575,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1214" t="n">
         <v>1000</v>
@@ -35604,7 +35604,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.4971536397934</v>
+        <v>1.49715352058411</v>
       </c>
       <c r="H1215" t="n">
         <v>7000</v>
@@ -35633,7 +35633,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1216" t="n">
         <v>4000</v>
@@ -35662,7 +35662,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1217" t="n">
         <v>68000</v>
@@ -35749,7 +35749,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.71788787841797</v>
+        <v>1.71788775920868</v>
       </c>
       <c r="H1220" t="n">
         <v>10000</v>
@@ -35778,7 +35778,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1221" t="n">
         <v>11000</v>
@@ -35894,7 +35894,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1225" t="n">
         <v>9000</v>
@@ -35923,7 +35923,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1226" t="n">
         <v>14000</v>
@@ -35952,7 +35952,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1227" t="n">
         <v>7000</v>
@@ -36213,7 +36213,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1236" t="n">
         <v>19000</v>
@@ -36242,7 +36242,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1237" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1237" t="n">
         <v>18000</v>
@@ -36271,7 +36271,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1238" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1238" t="n">
         <v>1000</v>
@@ -36300,7 +36300,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1239" t="n">
         <v>4000</v>
@@ -36387,7 +36387,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1242" t="n">
         <v>2000</v>
@@ -36416,7 +36416,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1243" t="n">
         <v>0</v>
@@ -36445,7 +36445,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1244" t="n">
         <v>0</v>
@@ -36706,7 +36706,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1253" t="n">
         <v>4000</v>
@@ -36735,7 +36735,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.53554213047028</v>
+        <v>1.53554224967957</v>
       </c>
       <c r="H1254" t="n">
         <v>0</v>
@@ -36851,7 +36851,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1258" t="n">
         <v>4000</v>
@@ -37141,7 +37141,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1268" t="n">
         <v>2000</v>
@@ -37170,7 +37170,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1269" t="n">
         <v>3000</v>
@@ -37199,7 +37199,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1270" t="n">
         <v>1000</v>
@@ -37228,7 +37228,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1271" t="n">
         <v>0</v>
@@ -37257,7 +37257,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1272" t="n">
         <v>1000</v>
@@ -37286,7 +37286,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1273" t="n">
         <v>12000</v>
@@ -37315,7 +37315,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1274" t="n">
         <v>0</v>
@@ -37344,7 +37344,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1275" t="n">
         <v>0</v>
@@ -37373,7 +37373,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.60272204875946</v>
+        <v>1.60272216796875</v>
       </c>
       <c r="H1276" t="n">
         <v>0</v>
@@ -37518,7 +37518,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.62191641330719</v>
+        <v>1.62191653251648</v>
       </c>
       <c r="H1281" t="n">
         <v>2000</v>
@@ -37547,7 +37547,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1282" t="n">
         <v>4000</v>
@@ -37576,7 +37576,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1283" t="n">
         <v>3000</v>
@@ -37605,7 +37605,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1284" t="n">
         <v>0</v>
@@ -37663,7 +37663,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1286" t="n">
         <v>6000</v>
@@ -37692,7 +37692,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1287" t="n">
         <v>2000</v>
@@ -37721,7 +37721,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.01539897918701</v>
+        <v>2.01539921760559</v>
       </c>
       <c r="H1288" t="n">
         <v>205000</v>
@@ -37779,7 +37779,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1290" t="n">
         <v>56000</v>
@@ -37924,7 +37924,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1295" t="n">
         <v>15000</v>
@@ -38011,7 +38011,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1298" t="n">
         <v>17000</v>
@@ -38040,7 +38040,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1299" t="n">
         <v>0</v>
@@ -38330,7 +38330,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.8906364440918</v>
+        <v>1.89063632488251</v>
       </c>
       <c r="H1309" t="n">
         <v>14000</v>
@@ -38359,7 +38359,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.8906364440918</v>
+        <v>1.89063632488251</v>
       </c>
       <c r="H1310" t="n">
         <v>17000</v>
@@ -38475,7 +38475,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1314" t="n">
-        <v>1.8618448972702</v>
+        <v>1.86184501647949</v>
       </c>
       <c r="H1314" t="n">
         <v>20000</v>
@@ -38504,7 +38504,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.8906364440918</v>
+        <v>1.89063632488251</v>
       </c>
       <c r="H1315" t="n">
         <v>27000</v>
@@ -38620,7 +38620,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1319" t="n">
         <v>4000</v>
@@ -38649,7 +38649,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1320" t="n">
         <v>3000</v>
@@ -38707,7 +38707,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1322" t="n">
         <v>3000</v>
@@ -38765,7 +38765,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1324" t="n">
         <v>11000</v>
@@ -38794,7 +38794,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.78506779670715</v>
+        <v>1.78506791591644</v>
       </c>
       <c r="H1325" t="n">
         <v>7000</v>
@@ -38823,7 +38823,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1326" t="n">
         <v>8000</v>
@@ -38881,7 +38881,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.73708212375641</v>
+        <v>1.73708200454712</v>
       </c>
       <c r="H1328" t="n">
         <v>25000</v>
@@ -39026,7 +39026,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1333" t="n">
         <v>2000</v>
@@ -39055,7 +39055,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1334" t="n">
         <v>8000</v>
@@ -39084,7 +39084,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1335" t="n">
         <v>2000</v>
@@ -39229,7 +39229,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1340" t="n">
         <v>4000</v>
@@ -39258,7 +39258,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.75627648830414</v>
+        <v>1.75627636909485</v>
       </c>
       <c r="H1341" t="n">
         <v>0</v>
@@ -39432,7 +39432,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1347" t="n">
         <v>9000</v>
@@ -39461,7 +39461,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1348" t="n">
         <v>4000</v>
@@ -39490,7 +39490,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.70829057693481</v>
+        <v>1.7082906961441</v>
       </c>
       <c r="H1349" t="n">
         <v>0</v>
@@ -39606,7 +39606,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.68909633159637</v>
+        <v>1.68909645080566</v>
       </c>
       <c r="H1353" t="n">
         <v>5000</v>
@@ -39664,7 +39664,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.66990220546722</v>
+        <v>1.66990208625793</v>
       </c>
       <c r="H1355" t="n">
         <v>8000</v>
@@ -39722,7 +39722,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.63151371479034</v>
+        <v>1.63151359558105</v>
       </c>
       <c r="H1357" t="n">
         <v>3000</v>
@@ -39751,7 +39751,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.65070796012878</v>
+        <v>1.65070784091949</v>
       </c>
       <c r="H1358" t="n">
         <v>2000</v>
@@ -53822,6 +53822,35 @@
         <v>27000</v>
       </c>
       <c r="I1843" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1844" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1844" t="n">
+        <v>1.92999994754791</v>
+      </c>
+      <c r="D1844" t="n">
+        <v>1.96000003814697</v>
+      </c>
+      <c r="E1844" t="n">
+        <v>1.92999994754791</v>
+      </c>
+      <c r="F1844" t="n">
+        <v>1.96000003814697</v>
+      </c>
+      <c r="G1844" t="n">
+        <v>1.96000003814697</v>
+      </c>
+      <c r="H1844" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I1844" t="s">
         <v>9</v>
       </c>
     </row>
